--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-13</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-14</t>
         </is>
       </c>
     </row>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -556,10 +556,10 @@
         <v>330</v>
       </c>
       <c r="N4" t="n">
-        <v>27000</v>
+        <v>27021.686746988</v>
       </c>
       <c r="O4" t="n">
-        <v>8910000</v>
+        <v>8917156.62650604</v>
       </c>
       <c r="P4" t="n">
         <v>20000</v>
@@ -1394,10 +1394,10 @@
         <v>17</v>
       </c>
       <c r="N25" t="n">
-        <v>15403.521040462</v>
+        <v>15403.521104651</v>
       </c>
       <c r="O25" t="n">
-        <v>261859.857687854</v>
+        <v>261859.858779067</v>
       </c>
       <c r="P25" t="n">
         <v>33500</v>
@@ -3155,10 +3155,10 @@
         <v>1232</v>
       </c>
       <c r="N66" t="n">
-        <v>5216.8959816133</v>
+        <v>5216.8959810174</v>
       </c>
       <c r="O66" t="n">
-        <v>6427215.849347586</v>
+        <v>6427215.848613437</v>
       </c>
       <c r="P66" t="n">
         <v>8500</v>
@@ -3792,10 +3792,10 @@
         <v>240</v>
       </c>
       <c r="N80" t="n">
-        <v>3594.2533147632</v>
+        <v>3596.7580209059</v>
       </c>
       <c r="O80" t="n">
-        <v>862620.795543168</v>
+        <v>863221.925017416</v>
       </c>
       <c r="P80" t="n">
         <v>6500</v>
@@ -4341,10 +4341,10 @@
         <v>1356</v>
       </c>
       <c r="N92" t="n">
-        <v>4371.1712612367</v>
+        <v>4371.766707533</v>
       </c>
       <c r="O92" t="n">
-        <v>5927308.230236965</v>
+        <v>5928115.655414748</v>
       </c>
       <c r="P92" t="n">
         <v>8900</v>
@@ -11865,10 +11865,10 @@
         <v>864</v>
       </c>
       <c r="N257" t="n">
-        <v>1516.0387548048</v>
+        <v>1516.0387544268</v>
       </c>
       <c r="O257" t="n">
-        <v>1309857.484151347</v>
+        <v>1309857.483824755</v>
       </c>
       <c r="P257" t="n">
         <v>2300</v>
@@ -12461,10 +12461,10 @@
         <v>1440</v>
       </c>
       <c r="N270" t="n">
-        <v>1690.8700092894</v>
+        <v>1690.870009298</v>
       </c>
       <c r="O270" t="n">
-        <v>2434852.813376736</v>
+        <v>2434852.81338912</v>
       </c>
       <c r="P270" t="n">
         <v>3000</v>
@@ -13015,10 +13015,10 @@
         <v>15264</v>
       </c>
       <c r="N282" t="n">
-        <v>703.79483731577</v>
+        <v>703.86725350482</v>
       </c>
       <c r="O282" t="n">
-        <v>10742724.39678791</v>
+        <v>10743829.75749757</v>
       </c>
       <c r="P282" t="n">
         <v>900</v>
@@ -14592,10 +14592,10 @@
         <v>29</v>
       </c>
       <c r="N315" t="n">
-        <v>8919.16</v>
+        <v>8975.6103797468</v>
       </c>
       <c r="O315" t="n">
-        <v>258655.64</v>
+        <v>260292.7010126572</v>
       </c>
       <c r="P315" t="n">
         <v>10000</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -1735,10 +1735,10 @@
         <v>65</v>
       </c>
       <c r="N33" t="n">
-        <v>141416.88462046</v>
+        <v>141885.15245033</v>
       </c>
       <c r="O33" t="n">
-        <v>9192097.500329901</v>
+        <v>9222534.909271451</v>
       </c>
       <c r="P33" t="n">
         <v>251900</v>
@@ -1777,10 +1777,10 @@
         <v>36</v>
       </c>
       <c r="N34" t="n">
-        <v>200072.20216981</v>
+        <v>201977.65171429</v>
       </c>
       <c r="O34" t="n">
-        <v>7202599.27811316</v>
+        <v>7271195.46171444</v>
       </c>
       <c r="P34" t="n">
         <v>312000</v>
@@ -2027,10 +2027,10 @@
         <v>77</v>
       </c>
       <c r="N40" t="n">
-        <v>61666.874171271</v>
+        <v>62706.203511236</v>
       </c>
       <c r="O40" t="n">
-        <v>4748349.311187867</v>
+        <v>4828377.670365172</v>
       </c>
       <c r="P40" t="n">
         <v>98900</v>
@@ -3109,10 +3109,10 @@
         <v>350</v>
       </c>
       <c r="N65" t="n">
-        <v>2582.2551367187</v>
+        <v>2582.2551307749</v>
       </c>
       <c r="O65" t="n">
-        <v>903789.297851545</v>
+        <v>903789.295771215</v>
       </c>
       <c r="P65" t="n">
         <v>4500</v>
@@ -5214,10 +5214,10 @@
         <v>432</v>
       </c>
       <c r="N111" t="n">
-        <v>11921.4</v>
+        <v>11949.761776368</v>
       </c>
       <c r="O111" t="n">
-        <v>5150044.8</v>
+        <v>5162297.087390976</v>
       </c>
       <c r="P111" t="n">
         <v>19900</v>
@@ -6596,10 +6596,10 @@
         <v>948</v>
       </c>
       <c r="N142" t="n">
-        <v>4814.2679274047</v>
+        <v>4814.2679269747</v>
       </c>
       <c r="O142" t="n">
-        <v>4563925.995179655</v>
+        <v>4563925.994772015</v>
       </c>
       <c r="P142" t="n">
         <v>9900</v>
@@ -7046,10 +7046,10 @@
         <v>72</v>
       </c>
       <c r="N152" t="n">
-        <v>16974.69</v>
+        <v>17078.829202454</v>
       </c>
       <c r="O152" t="n">
-        <v>1222177.68</v>
+        <v>1229675.702576688</v>
       </c>
       <c r="P152" t="n">
         <v>26900</v>
@@ -12003,10 +12003,10 @@
         <v>864</v>
       </c>
       <c r="N260" t="n">
-        <v>1516.0387516479</v>
+        <v>1516.0387513947</v>
       </c>
       <c r="O260" t="n">
-        <v>1309857.481423786</v>
+        <v>1309857.481205021</v>
       </c>
       <c r="P260" t="n">
         <v>2300</v>
@@ -13398,10 +13398,10 @@
         <v>15264</v>
       </c>
       <c r="N290" t="n">
-        <v>703.79482873668</v>
+        <v>703.79482793718</v>
       </c>
       <c r="O290" t="n">
-        <v>10742724.26583668</v>
+        <v>10742724.25363312</v>
       </c>
       <c r="P290" t="n">
         <v>900</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -3201,10 +3201,10 @@
         <v>2592</v>
       </c>
       <c r="N67" t="n">
-        <v>3158.8608362663</v>
+        <v>3158.8608369301</v>
       </c>
       <c r="O67" t="n">
-        <v>8187767.28760225</v>
+        <v>8187767.28932282</v>
       </c>
       <c r="P67" t="n">
         <v>5600</v>
@@ -3385,10 +3385,10 @@
         <v>480</v>
       </c>
       <c r="N71" t="n">
-        <v>3795.7100076147</v>
+        <v>3795.7100076161</v>
       </c>
       <c r="O71" t="n">
-        <v>1821940.803655056</v>
+        <v>1821940.803655728</v>
       </c>
       <c r="P71" t="n">
         <v>6200</v>
@@ -5884,10 +5884,10 @@
         <v>432</v>
       </c>
       <c r="N126" t="n">
-        <v>2029.8740849673</v>
+        <v>2029.874091653</v>
       </c>
       <c r="O126" t="n">
-        <v>876905.6047058735</v>
+        <v>876905.607594096</v>
       </c>
       <c r="P126" t="n">
         <v>3600</v>
@@ -11957,10 +11957,10 @@
         <v>864</v>
       </c>
       <c r="N259" t="n">
-        <v>1516.0387513947</v>
+        <v>1516.0387508879</v>
       </c>
       <c r="O259" t="n">
-        <v>1309857.481205021</v>
+        <v>1309857.480767146</v>
       </c>
       <c r="P259" t="n">
         <v>2300</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -798,10 +798,10 @@
         <v>1</v>
       </c>
       <c r="N10" t="n">
-        <v>4072</v>
+        <v>4088.8962655602</v>
       </c>
       <c r="O10" t="n">
-        <v>4072</v>
+        <v>4088.8962655602</v>
       </c>
       <c r="P10" t="n">
         <v>7500</v>
@@ -2888,10 +2888,10 @@
         <v>248</v>
       </c>
       <c r="N60" t="n">
-        <v>13593.35</v>
+        <v>13626.343567961</v>
       </c>
       <c r="O60" t="n">
-        <v>3371150.8</v>
+        <v>3379333.204854328</v>
       </c>
       <c r="P60" t="n">
         <v>25500</v>
@@ -3065,10 +3065,10 @@
         <v>350</v>
       </c>
       <c r="N64" t="n">
-        <v>2582.2550509317</v>
+        <v>2582.2550435432</v>
       </c>
       <c r="O64" t="n">
-        <v>903789.2678260951</v>
+        <v>903789.26524012</v>
       </c>
       <c r="P64" t="n">
         <v>4500</v>
@@ -3111,10 +3111,10 @@
         <v>1232</v>
       </c>
       <c r="N65" t="n">
-        <v>5216.8959642591</v>
+        <v>5220.0054239309</v>
       </c>
       <c r="O65" t="n">
-        <v>6427215.827967211</v>
+        <v>6431046.682282869</v>
       </c>
       <c r="P65" t="n">
         <v>8500</v>
@@ -3653,10 +3653,10 @@
         <v>246</v>
       </c>
       <c r="N77" t="n">
-        <v>7041</v>
+        <v>7062.9802289282</v>
       </c>
       <c r="O77" t="n">
-        <v>1732086</v>
+        <v>1737493.136316337</v>
       </c>
       <c r="P77" t="n">
         <v>11500</v>
@@ -3748,10 +3748,10 @@
         <v>216</v>
       </c>
       <c r="N79" t="n">
-        <v>3594.2531526391</v>
+        <v>3594.2531477516</v>
       </c>
       <c r="O79" t="n">
-        <v>776358.6809700456</v>
+        <v>776358.6799143456</v>
       </c>
       <c r="P79" t="n">
         <v>6500</v>
@@ -3886,10 +3886,10 @@
         <v>316</v>
       </c>
       <c r="N82" t="n">
-        <v>14822.378827839</v>
+        <v>14840.499095355</v>
       </c>
       <c r="O82" t="n">
-        <v>4683871.709597124</v>
+        <v>4689597.71413218</v>
       </c>
       <c r="P82" t="n">
         <v>24900</v>
@@ -4299,10 +4299,10 @@
         <v>1800</v>
       </c>
       <c r="N91" t="n">
-        <v>3472.2761671707</v>
+        <v>3490.9933434692</v>
       </c>
       <c r="O91" t="n">
-        <v>6250097.10090726</v>
+        <v>6283788.018244561</v>
       </c>
       <c r="P91" t="n">
         <v>5900</v>
@@ -5258,10 +5258,10 @@
         <v>525</v>
       </c>
       <c r="N112" t="n">
-        <v>9903</v>
+        <v>9918.473437500001</v>
       </c>
       <c r="O112" t="n">
-        <v>5199075</v>
+        <v>5207198.5546875</v>
       </c>
       <c r="P112" t="n">
         <v>15900</v>
@@ -5794,10 +5794,10 @@
         <v>432</v>
       </c>
       <c r="N124" t="n">
-        <v>2029.8740983607</v>
+        <v>2029.8741050903</v>
       </c>
       <c r="O124" t="n">
-        <v>876905.6104918224</v>
+        <v>876905.6133990096</v>
       </c>
       <c r="P124" t="n">
         <v>3600</v>
@@ -6460,10 +6460,10 @@
         <v>948</v>
       </c>
       <c r="N139" t="n">
-        <v>4814.2679269747</v>
+        <v>4817.516083662</v>
       </c>
       <c r="O139" t="n">
-        <v>4563925.994772015</v>
+        <v>4567005.247311576</v>
       </c>
       <c r="P139" t="n">
         <v>9900</v>
@@ -7823,10 +7823,10 @@
         <v>240</v>
       </c>
       <c r="N169" t="n">
-        <v>22739</v>
+        <v>22855.411262799</v>
       </c>
       <c r="O169" t="n">
-        <v>5457360</v>
+        <v>5485298.70307176</v>
       </c>
       <c r="P169" t="n">
         <v>36900</v>
@@ -9298,10 +9298,10 @@
         <v>129</v>
       </c>
       <c r="N201" t="n">
-        <v>3903.7390742358</v>
+        <v>3903.7391243433</v>
       </c>
       <c r="O201" t="n">
-        <v>503582.3405764182</v>
+        <v>503582.3470402857</v>
       </c>
       <c r="P201" t="n">
         <v>7500</v>
@@ -9339,10 +9339,10 @@
         <v>40</v>
       </c>
       <c r="N202" t="n">
-        <v>20726</v>
+        <v>21127.148387097</v>
       </c>
       <c r="O202" t="n">
-        <v>829040</v>
+        <v>845085.93548388</v>
       </c>
       <c r="P202" t="n">
         <v>33900</v>
@@ -9702,10 +9702,10 @@
         <v>443</v>
       </c>
       <c r="N210" t="n">
-        <v>6849.2</v>
+        <v>6855.7044634378</v>
       </c>
       <c r="O210" t="n">
-        <v>3034195.6</v>
+        <v>3037077.077302945</v>
       </c>
       <c r="P210" t="n">
         <v>11500</v>
@@ -10809,10 +10809,10 @@
         <v>30</v>
       </c>
       <c r="N234" t="n">
-        <v>20014</v>
+        <v>21040.358974359</v>
       </c>
       <c r="O234" t="n">
-        <v>600420</v>
+        <v>631210.7692307699</v>
       </c>
       <c r="P234" t="n">
         <v>33900</v>
@@ -11821,10 +11821,10 @@
         <v>864</v>
       </c>
       <c r="N256" t="n">
-        <v>1516.0387464358</v>
+        <v>1516.0387455416</v>
       </c>
       <c r="O256" t="n">
-        <v>1309857.476920531</v>
+        <v>1309857.476147942</v>
       </c>
       <c r="P256" t="n">
         <v>2300</v>
@@ -12147,10 +12147,10 @@
         <v>360</v>
       </c>
       <c r="N263" t="n">
-        <v>13518</v>
+        <v>13559.454697519</v>
       </c>
       <c r="O263" t="n">
-        <v>4866480</v>
+        <v>4881403.69110684</v>
       </c>
       <c r="P263" t="n">
         <v>21900</v>
@@ -12196,10 +12196,10 @@
         <v>432</v>
       </c>
       <c r="N264" t="n">
-        <v>9736</v>
+        <v>9760.865567680499</v>
       </c>
       <c r="O264" t="n">
-        <v>4205952</v>
+        <v>4216693.925237976</v>
       </c>
       <c r="P264" t="n">
         <v>15900</v>
@@ -12245,10 +12245,10 @@
         <v>36</v>
       </c>
       <c r="N265" t="n">
-        <v>44470</v>
+        <v>45032.911392405</v>
       </c>
       <c r="O265" t="n">
-        <v>1600920</v>
+        <v>1621184.81012658</v>
       </c>
       <c r="P265" t="n">
         <v>71900</v>
@@ -12294,10 +12294,10 @@
         <v>720</v>
       </c>
       <c r="N266" t="n">
-        <v>5215</v>
+        <v>5227.7693437806</v>
       </c>
       <c r="O266" t="n">
-        <v>3754800</v>
+        <v>3763993.927522032</v>
       </c>
       <c r="P266" t="n">
         <v>8900</v>
@@ -12338,10 +12338,10 @@
         <v>55</v>
       </c>
       <c r="N267" t="n">
-        <v>15423.36</v>
+        <v>15646.886956522</v>
       </c>
       <c r="O267" t="n">
-        <v>848284.8</v>
+        <v>860578.78260871</v>
       </c>
       <c r="P267" t="n">
         <v>24900</v>
@@ -13170,10 +13170,10 @@
         <v>15264</v>
       </c>
       <c r="N285" t="n">
-        <v>703.79481075491</v>
+        <v>703.79479136392</v>
       </c>
       <c r="O285" t="n">
-        <v>10742723.99136295</v>
+        <v>10742723.69537888</v>
       </c>
       <c r="P285" t="n">
         <v>900</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q341"/>
+  <dimension ref="A1:Q338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-17</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-18</t>
         </is>
       </c>
     </row>
@@ -720,10 +720,10 @@
         <v>376</v>
       </c>
       <c r="N8" t="n">
-        <v>3376.7464388093</v>
+        <v>3376.7464140994</v>
       </c>
       <c r="O8" t="n">
-        <v>1269656.660992297</v>
+        <v>1269656.651701374</v>
       </c>
       <c r="P8" t="n">
         <v>4500</v>
@@ -1824,10 +1824,10 @@
         <v>4</v>
       </c>
       <c r="N35" t="n">
-        <v>344599.17847826</v>
+        <v>344599.17844444</v>
       </c>
       <c r="O35" t="n">
-        <v>1378396.71391304</v>
+        <v>1378396.71377776</v>
       </c>
       <c r="P35" t="n">
         <v>532900</v>
@@ -2365,10 +2365,10 @@
         <v>96</v>
       </c>
       <c r="N48" t="n">
-        <v>2570.16</v>
+        <v>2644.1214388489</v>
       </c>
       <c r="O48" t="n">
-        <v>246735.36</v>
+        <v>253835.6581294944</v>
       </c>
       <c r="P48" t="n">
         <v>4700</v>
@@ -2675,10 +2675,10 @@
         <v>40</v>
       </c>
       <c r="N55" t="n">
-        <v>10752.93</v>
+        <v>10897.588251121</v>
       </c>
       <c r="O55" t="n">
-        <v>430117.2</v>
+        <v>435903.53004484</v>
       </c>
       <c r="P55" t="n">
         <v>18400</v>
@@ -2888,10 +2888,10 @@
         <v>248</v>
       </c>
       <c r="N60" t="n">
-        <v>13626.343567961</v>
+        <v>13593.35</v>
       </c>
       <c r="O60" t="n">
-        <v>3379333.204854328</v>
+        <v>3371150.8</v>
       </c>
       <c r="P60" t="n">
         <v>25500</v>
@@ -3065,10 +3065,10 @@
         <v>350</v>
       </c>
       <c r="N64" t="n">
-        <v>2582.2550435432</v>
+        <v>2582.25501002</v>
       </c>
       <c r="O64" t="n">
-        <v>903789.26524012</v>
+        <v>903789.253507</v>
       </c>
       <c r="P64" t="n">
         <v>4500</v>
@@ -3111,10 +3111,10 @@
         <v>1232</v>
       </c>
       <c r="N65" t="n">
-        <v>5220.0054239309</v>
+        <v>5216.8959455416</v>
       </c>
       <c r="O65" t="n">
-        <v>6431046.682282869</v>
+        <v>6427215.804907251</v>
       </c>
       <c r="P65" t="n">
         <v>8500</v>
@@ -3157,10 +3157,10 @@
         <v>2592</v>
       </c>
       <c r="N66" t="n">
-        <v>3158.8608375534</v>
+        <v>3158.8608386776</v>
       </c>
       <c r="O66" t="n">
-        <v>8187767.290938413</v>
+        <v>8187767.293852339</v>
       </c>
       <c r="P66" t="n">
         <v>5600</v>
@@ -3191,7 +3191,7 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -3200,19 +3200,19 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="N67" t="n">
-        <v>3841.6250362694</v>
+        <v>3841.6251265823</v>
       </c>
       <c r="O67" t="n">
-        <v>284280.2526839356</v>
+        <v>222814.2573417734</v>
       </c>
       <c r="P67" t="n">
         <v>6900</v>
       </c>
       <c r="Q67" t="n">
-        <v>510600</v>
+        <v>400200</v>
       </c>
     </row>
     <row r="68">
@@ -3520,10 +3520,10 @@
         <v>346</v>
       </c>
       <c r="N74" t="n">
-        <v>4890.9300511182</v>
+        <v>4890.9300513149</v>
       </c>
       <c r="O74" t="n">
-        <v>1692261.797686897</v>
+        <v>1692261.797754955</v>
       </c>
       <c r="P74" t="n">
         <v>8200</v>
@@ -3653,10 +3653,10 @@
         <v>246</v>
       </c>
       <c r="N77" t="n">
-        <v>7062.9802289282</v>
+        <v>7041</v>
       </c>
       <c r="O77" t="n">
-        <v>1737493.136316337</v>
+        <v>1732086</v>
       </c>
       <c r="P77" t="n">
         <v>11500</v>
@@ -3748,10 +3748,10 @@
         <v>216</v>
       </c>
       <c r="N79" t="n">
-        <v>3594.2531477516</v>
+        <v>3594.2531182796</v>
       </c>
       <c r="O79" t="n">
-        <v>776358.6799143456</v>
+        <v>776358.6735483936</v>
       </c>
       <c r="P79" t="n">
         <v>6500</v>
@@ -3886,10 +3886,10 @@
         <v>316</v>
       </c>
       <c r="N82" t="n">
-        <v>14840.499095355</v>
+        <v>14822.378819914</v>
       </c>
       <c r="O82" t="n">
-        <v>4689597.71413218</v>
+        <v>4683871.707092824</v>
       </c>
       <c r="P82" t="n">
         <v>24900</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="J89" t="n">
-        <v>375</v>
+        <v>336</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -4204,19 +4204,19 @@
         <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>375</v>
+        <v>336</v>
       </c>
       <c r="N89" t="n">
-        <v>12422.462941685</v>
+        <v>12422.462946776</v>
       </c>
       <c r="O89" t="n">
-        <v>4658423.603131875</v>
+        <v>4173947.550116736</v>
       </c>
       <c r="P89" t="n">
         <v>19900</v>
       </c>
       <c r="Q89" t="n">
-        <v>7462500</v>
+        <v>6686400</v>
       </c>
     </row>
     <row r="90">
@@ -4299,10 +4299,10 @@
         <v>1800</v>
       </c>
       <c r="N91" t="n">
-        <v>3490.9933434692</v>
+        <v>3472.2761773616</v>
       </c>
       <c r="O91" t="n">
-        <v>6283788.018244561</v>
+        <v>6250097.11925088</v>
       </c>
       <c r="P91" t="n">
         <v>5900</v>
@@ -5258,10 +5258,10 @@
         <v>525</v>
       </c>
       <c r="N112" t="n">
-        <v>9918.473437500001</v>
+        <v>9903</v>
       </c>
       <c r="O112" t="n">
-        <v>5207198.5546875</v>
+        <v>5199075</v>
       </c>
       <c r="P112" t="n">
         <v>15900</v>
@@ -5304,10 +5304,10 @@
         <v>2</v>
       </c>
       <c r="N113" t="n">
-        <v>14778</v>
+        <v>17733.6</v>
       </c>
       <c r="O113" t="n">
-        <v>29556</v>
+        <v>35467.2</v>
       </c>
       <c r="P113" t="n">
         <v>24900</v>
@@ -5794,10 +5794,10 @@
         <v>432</v>
       </c>
       <c r="N124" t="n">
-        <v>2029.8741050903</v>
+        <v>2029.8741413584</v>
       </c>
       <c r="O124" t="n">
-        <v>876905.6133990096</v>
+        <v>876905.6290668289</v>
       </c>
       <c r="P124" t="n">
         <v>3600</v>
@@ -5835,10 +5835,10 @@
         <v>528</v>
       </c>
       <c r="N125" t="n">
-        <v>22485.695483061</v>
+        <v>22485.695471698</v>
       </c>
       <c r="O125" t="n">
-        <v>11872447.21505621</v>
+        <v>11872447.20905654</v>
       </c>
       <c r="P125" t="n">
         <v>36500</v>
@@ -6191,10 +6191,10 @@
         <v>799</v>
       </c>
       <c r="N133" t="n">
-        <v>998.76126229508</v>
+        <v>998.76126436782</v>
       </c>
       <c r="O133" t="n">
-        <v>798010.2485737689</v>
+        <v>798010.2502298881</v>
       </c>
       <c r="P133" t="n">
         <v>1600</v>
@@ -6286,10 +6286,10 @@
         <v>36</v>
       </c>
       <c r="N135" t="n">
-        <v>4285.1962331288</v>
+        <v>4285.1962793572</v>
       </c>
       <c r="O135" t="n">
-        <v>154267.0643926368</v>
+        <v>154267.0660568592</v>
       </c>
       <c r="P135" t="n">
         <v>6900</v>
@@ -6414,10 +6414,10 @@
         <v>55</v>
       </c>
       <c r="N138" t="n">
-        <v>30244.600034924</v>
+        <v>30262.214828189</v>
       </c>
       <c r="O138" t="n">
-        <v>1663453.00192082</v>
+        <v>1664421.815550395</v>
       </c>
       <c r="P138" t="n">
         <v>48900</v>
@@ -6460,10 +6460,10 @@
         <v>948</v>
       </c>
       <c r="N139" t="n">
-        <v>4817.516083662</v>
+        <v>4814.2679265446</v>
       </c>
       <c r="O139" t="n">
-        <v>4567005.247311576</v>
+        <v>4563925.994364281</v>
       </c>
       <c r="P139" t="n">
         <v>9900</v>
@@ -6547,10 +6547,10 @@
         <v>94</v>
       </c>
       <c r="N141" t="n">
-        <v>60174</v>
+        <v>61248.535714286</v>
       </c>
       <c r="O141" t="n">
-        <v>5656356</v>
+        <v>5757362.357142884</v>
       </c>
       <c r="P141" t="n">
         <v>96900</v>
@@ -6864,10 +6864,10 @@
         <v>144</v>
       </c>
       <c r="N148" t="n">
-        <v>27123.764849095</v>
+        <v>27233.355818182</v>
       </c>
       <c r="O148" t="n">
-        <v>3905822.13826968</v>
+        <v>3921603.237818208</v>
       </c>
       <c r="P148" t="n">
         <v>44500</v>
@@ -7777,10 +7777,10 @@
         <v>680</v>
       </c>
       <c r="N168" t="n">
-        <v>1778.4728156749</v>
+        <v>1778.4728179471</v>
       </c>
       <c r="O168" t="n">
-        <v>1209361.514658932</v>
+        <v>1209361.516204028</v>
       </c>
       <c r="P168" t="n">
         <v>4900</v>
@@ -7811,7 +7811,7 @@
         </is>
       </c>
       <c r="J169" t="n">
-        <v>240</v>
+        <v>192</v>
       </c>
       <c r="K169" t="n">
         <v>0</v>
@@ -7820,19 +7820,19 @@
         <v>0</v>
       </c>
       <c r="M169" t="n">
-        <v>240</v>
+        <v>192</v>
       </c>
       <c r="N169" t="n">
-        <v>22855.411262799</v>
+        <v>22739</v>
       </c>
       <c r="O169" t="n">
-        <v>5485298.70307176</v>
+        <v>4365888</v>
       </c>
       <c r="P169" t="n">
         <v>36900</v>
       </c>
       <c r="Q169" t="n">
-        <v>8856000</v>
+        <v>7084800</v>
       </c>
     </row>
     <row r="170">
@@ -7915,10 +7915,10 @@
         <v>160</v>
       </c>
       <c r="N171" t="n">
-        <v>16058</v>
+        <v>16092.984749455</v>
       </c>
       <c r="O171" t="n">
-        <v>2569280</v>
+        <v>2574877.5599128</v>
       </c>
       <c r="P171" t="n">
         <v>25900</v>
@@ -7961,10 +7961,10 @@
         <v>396</v>
       </c>
       <c r="N172" t="n">
-        <v>25534</v>
+        <v>25576.890257559</v>
       </c>
       <c r="O172" t="n">
-        <v>10111464</v>
+        <v>10128448.54199336</v>
       </c>
       <c r="P172" t="n">
         <v>40900</v>
@@ -8470,10 +8470,10 @@
         <v>210</v>
       </c>
       <c r="N183" t="n">
-        <v>10411</v>
+        <v>10485.899280576</v>
       </c>
       <c r="O183" t="n">
-        <v>2186310</v>
+        <v>2202038.84892096</v>
       </c>
       <c r="P183" t="n">
         <v>16900</v>
@@ -8746,10 +8746,10 @@
         <v>123</v>
       </c>
       <c r="N189" t="n">
-        <v>32332</v>
+        <v>32566.857142857</v>
       </c>
       <c r="O189" t="n">
-        <v>3976836</v>
+        <v>4005723.428571411</v>
       </c>
       <c r="P189" t="n">
         <v>55900</v>
@@ -9160,10 +9160,10 @@
         <v>12</v>
       </c>
       <c r="N198" t="n">
-        <v>23376.36</v>
+        <v>23932.94</v>
       </c>
       <c r="O198" t="n">
-        <v>280516.32</v>
+        <v>287195.28</v>
       </c>
       <c r="P198" t="n">
         <v>40900</v>
@@ -9206,10 +9206,10 @@
         <v>502</v>
       </c>
       <c r="N199" t="n">
-        <v>13210</v>
+        <v>13233.257042254</v>
       </c>
       <c r="O199" t="n">
-        <v>6631420</v>
+        <v>6643095.035211507</v>
       </c>
       <c r="P199" t="n">
         <v>23900</v>
@@ -9298,10 +9298,10 @@
         <v>129</v>
       </c>
       <c r="N201" t="n">
-        <v>3903.7391243433</v>
+        <v>3903.7391411043</v>
       </c>
       <c r="O201" t="n">
-        <v>503582.3470402857</v>
+        <v>503582.3492024547</v>
       </c>
       <c r="P201" t="n">
         <v>7500</v>
@@ -9339,10 +9339,10 @@
         <v>40</v>
       </c>
       <c r="N202" t="n">
-        <v>21127.148387097</v>
+        <v>20726</v>
       </c>
       <c r="O202" t="n">
-        <v>845085.93548388</v>
+        <v>829040</v>
       </c>
       <c r="P202" t="n">
         <v>33900</v>
@@ -9380,10 +9380,10 @@
         <v>51</v>
       </c>
       <c r="N203" t="n">
-        <v>35864.602142857</v>
+        <v>36516.685818182</v>
       </c>
       <c r="O203" t="n">
-        <v>1829094.709285707</v>
+        <v>1862350.976727282</v>
       </c>
       <c r="P203" t="n">
         <v>62900</v>
@@ -9564,10 +9564,10 @@
         <v>18</v>
       </c>
       <c r="N207" t="n">
-        <v>11922</v>
+        <v>12498.870967742</v>
       </c>
       <c r="O207" t="n">
-        <v>214596</v>
+        <v>224979.677419356</v>
       </c>
       <c r="P207" t="n">
         <v>19900</v>
@@ -9702,10 +9702,10 @@
         <v>443</v>
       </c>
       <c r="N210" t="n">
-        <v>6855.7044634378</v>
+        <v>6881.8463298379</v>
       </c>
       <c r="O210" t="n">
-        <v>3037077.077302945</v>
+        <v>3048657.92411819</v>
       </c>
       <c r="P210" t="n">
         <v>11500</v>
@@ -10070,10 +10070,10 @@
         <v>1162</v>
       </c>
       <c r="N218" t="n">
-        <v>7635</v>
+        <v>7639.2713286713</v>
       </c>
       <c r="O218" t="n">
-        <v>8871870</v>
+        <v>8876833.283916051</v>
       </c>
       <c r="P218" t="n">
         <v>13900</v>
@@ -10392,10 +10392,10 @@
         <v>290</v>
       </c>
       <c r="N225" t="n">
-        <v>11348</v>
+        <v>11478.737327189</v>
       </c>
       <c r="O225" t="n">
-        <v>3290920</v>
+        <v>3328833.82488481</v>
       </c>
       <c r="P225" t="n">
         <v>19900</v>
@@ -10809,10 +10809,10 @@
         <v>30</v>
       </c>
       <c r="N234" t="n">
-        <v>21040.358974359</v>
+        <v>20014</v>
       </c>
       <c r="O234" t="n">
-        <v>631210.7692307699</v>
+        <v>600420</v>
       </c>
       <c r="P234" t="n">
         <v>33900</v>
@@ -11085,10 +11085,10 @@
         <v>78</v>
       </c>
       <c r="N240" t="n">
-        <v>14050</v>
+        <v>14369.318181818</v>
       </c>
       <c r="O240" t="n">
-        <v>1095900</v>
+        <v>1120806.818181804</v>
       </c>
       <c r="P240" t="n">
         <v>23900</v>
@@ -11131,10 +11131,10 @@
         <v>285</v>
       </c>
       <c r="N241" t="n">
-        <v>8700</v>
+        <v>8721.3759213759</v>
       </c>
       <c r="O241" t="n">
-        <v>2479500</v>
+        <v>2485592.137592132</v>
       </c>
       <c r="P241" t="n">
         <v>14900</v>
@@ -11453,10 +11453,10 @@
         <v>181</v>
       </c>
       <c r="N248" t="n">
-        <v>21762</v>
+        <v>21884.258426966</v>
       </c>
       <c r="O248" t="n">
-        <v>3938922</v>
+        <v>3961050.775280846</v>
       </c>
       <c r="P248" t="n">
         <v>35900</v>
@@ -11499,10 +11499,10 @@
         <v>934</v>
       </c>
       <c r="N249" t="n">
-        <v>3821</v>
+        <v>3823.6153319644</v>
       </c>
       <c r="O249" t="n">
-        <v>3568814</v>
+        <v>3571256.720054749</v>
       </c>
       <c r="P249" t="n">
         <v>5900</v>
@@ -11591,10 +11591,10 @@
         <v>8</v>
       </c>
       <c r="N251" t="n">
-        <v>48522</v>
+        <v>50038.3125</v>
       </c>
       <c r="O251" t="n">
-        <v>388176</v>
+        <v>400306.5</v>
       </c>
       <c r="P251" t="n">
         <v>77900</v>
@@ -11606,12 +11606,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>C4617</t>
+          <t>C4622</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>CARRO TRANSFORME AZUL RECARGABLE C4617</t>
+          <t>CARRO COLECCION X8 C4622</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -11625,7 +11625,7 @@
         </is>
       </c>
       <c r="J252" t="n">
-        <v>10</v>
+        <v>240</v>
       </c>
       <c r="K252" t="n">
         <v>0</v>
@@ -11634,30 +11634,30 @@
         <v>0</v>
       </c>
       <c r="M252" t="n">
-        <v>10</v>
+        <v>240</v>
       </c>
       <c r="N252" t="n">
-        <v>53814.84</v>
+        <v>5476</v>
       </c>
       <c r="O252" t="n">
-        <v>538148.3999999999</v>
+        <v>1314240</v>
       </c>
       <c r="P252" t="n">
-        <v>88900</v>
+        <v>8900</v>
       </c>
       <c r="Q252" t="n">
-        <v>889000</v>
+        <v>2136000</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>C4622</t>
+          <t>C4629</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>CARRO COLECCION X8 C4622</t>
+          <t>COMPUTADOR USB CABLE C4629</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="J253" t="n">
-        <v>240</v>
+        <v>36</v>
       </c>
       <c r="K253" t="n">
         <v>0</v>
@@ -11680,30 +11680,30 @@
         <v>0</v>
       </c>
       <c r="M253" t="n">
-        <v>240</v>
+        <v>36</v>
       </c>
       <c r="N253" t="n">
-        <v>5476</v>
+        <v>64612</v>
       </c>
       <c r="O253" t="n">
-        <v>1314240</v>
+        <v>2326032</v>
       </c>
       <c r="P253" t="n">
-        <v>8900</v>
+        <v>103900</v>
       </c>
       <c r="Q253" t="n">
-        <v>2136000</v>
+        <v>3740400</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>C4629</t>
+          <t>C4630</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>COMPUTADOR USB CABLE C4629</t>
+          <t>COMPUTADOR USB INGLES/ESPAÑOL C4630</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -11717,7 +11717,7 @@
         </is>
       </c>
       <c r="J254" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="K254" t="n">
         <v>0</v>
@@ -11726,30 +11726,30 @@
         <v>0</v>
       </c>
       <c r="M254" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="N254" t="n">
-        <v>64612</v>
+        <v>38252</v>
       </c>
       <c r="O254" t="n">
-        <v>2326032</v>
+        <v>2142112</v>
       </c>
       <c r="P254" t="n">
-        <v>103900</v>
+        <v>61900</v>
       </c>
       <c r="Q254" t="n">
-        <v>3740400</v>
+        <v>3466400</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>C4630</t>
+          <t>C4631</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>COMPUTADOR USB INGLES/ESPAÑOL C4630</t>
+          <t>SQUISHY MOSTRICO STD C4631</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -11763,7 +11763,7 @@
         </is>
       </c>
       <c r="J255" t="n">
-        <v>56</v>
+        <v>864</v>
       </c>
       <c r="K255" t="n">
         <v>0</v>
@@ -11772,30 +11772,30 @@
         <v>0</v>
       </c>
       <c r="M255" t="n">
-        <v>56</v>
+        <v>864</v>
       </c>
       <c r="N255" t="n">
-        <v>38252</v>
+        <v>1516.0387429797</v>
       </c>
       <c r="O255" t="n">
-        <v>2142112</v>
+        <v>1309857.473934461</v>
       </c>
       <c r="P255" t="n">
-        <v>61900</v>
+        <v>2300</v>
       </c>
       <c r="Q255" t="n">
-        <v>3466400</v>
+        <v>1987200</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>C4631</t>
+          <t>C466-IO</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>SQUISHY MOSTRICO STD C4631</t>
+          <t>GLOBO FIGURAS TORNASOL Y MATE</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -11809,7 +11809,7 @@
         </is>
       </c>
       <c r="J256" t="n">
-        <v>864</v>
+        <v>1050</v>
       </c>
       <c r="K256" t="n">
         <v>0</v>
@@ -11818,30 +11818,30 @@
         <v>0</v>
       </c>
       <c r="M256" t="n">
-        <v>864</v>
+        <v>1050</v>
       </c>
       <c r="N256" t="n">
-        <v>1516.0387455416</v>
+        <v>356.78</v>
       </c>
       <c r="O256" t="n">
-        <v>1309857.476147942</v>
+        <v>374619</v>
       </c>
       <c r="P256" t="n">
-        <v>2300</v>
+        <v>300</v>
       </c>
       <c r="Q256" t="n">
-        <v>1987200</v>
+        <v>315000</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>C466-IO</t>
+          <t>C4728</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>GLOBO FIGURAS TORNASOL Y MATE</t>
+          <t>FLIOTADOR DONA DINOSAURIO #60 C4728</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -11855,7 +11855,7 @@
         </is>
       </c>
       <c r="J257" t="n">
-        <v>1050</v>
+        <v>550</v>
       </c>
       <c r="K257" t="n">
         <v>0</v>
@@ -11864,44 +11864,42 @@
         <v>0</v>
       </c>
       <c r="M257" t="n">
-        <v>1050</v>
+        <v>550</v>
       </c>
       <c r="N257" t="n">
-        <v>356.78</v>
+        <v>2454</v>
       </c>
       <c r="O257" t="n">
-        <v>374619</v>
+        <v>1349700</v>
       </c>
       <c r="P257" t="n">
-        <v>300</v>
+        <v>4200</v>
       </c>
       <c r="Q257" t="n">
-        <v>315000</v>
+        <v>2310000</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>C4728</t>
-        </is>
+          <t>C476</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>6932001041468</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>FLIOTADOR DONA DINOSAURIO #60 C4728</t>
-        </is>
-      </c>
-      <c r="E258" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>YENGA MADERA GRABDE</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J258" t="n">
-        <v>550</v>
+        <v>54</v>
       </c>
       <c r="K258" t="n">
         <v>0</v>
@@ -11910,42 +11908,44 @@
         <v>0</v>
       </c>
       <c r="M258" t="n">
-        <v>550</v>
+        <v>54</v>
       </c>
       <c r="N258" t="n">
-        <v>2454</v>
+        <v>5347.73</v>
       </c>
       <c r="O258" t="n">
-        <v>1349700</v>
+        <v>288777.42</v>
       </c>
       <c r="P258" t="n">
-        <v>4200</v>
+        <v>9500</v>
       </c>
       <c r="Q258" t="n">
-        <v>2310000</v>
+        <v>513000</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>C476</t>
-        </is>
-      </c>
-      <c r="B259" t="n">
-        <v>6932001041468</v>
+          <t>C4812</t>
+        </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>YENGA MADERA GRABDE</t>
+          <t>BURBUJERO DE ESPADA 44cm</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J259" t="n">
-        <v>54</v>
+        <v>4464</v>
       </c>
       <c r="K259" t="n">
         <v>0</v>
@@ -11954,30 +11954,30 @@
         <v>0</v>
       </c>
       <c r="M259" t="n">
-        <v>54</v>
+        <v>4464</v>
       </c>
       <c r="N259" t="n">
-        <v>5347.73</v>
+        <v>1801</v>
       </c>
       <c r="O259" t="n">
-        <v>288777.42</v>
+        <v>8039664</v>
       </c>
       <c r="P259" t="n">
-        <v>9500</v>
+        <v>2900</v>
       </c>
       <c r="Q259" t="n">
-        <v>513000</v>
+        <v>12945600</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>C4812</t>
+          <t>C494-IO</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>BURBUJERO DE ESPADA 44cm</t>
+          <t>GLOBO METALIZADO DULCES</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -11991,7 +11991,7 @@
         </is>
       </c>
       <c r="J260" t="n">
-        <v>4464</v>
+        <v>1352</v>
       </c>
       <c r="K260" t="n">
         <v>0</v>
@@ -12000,30 +12000,33 @@
         <v>0</v>
       </c>
       <c r="M260" t="n">
-        <v>4464</v>
+        <v>1352</v>
       </c>
       <c r="N260" t="n">
-        <v>1801</v>
+        <v>1200</v>
       </c>
       <c r="O260" t="n">
-        <v>8039664</v>
+        <v>1622400</v>
       </c>
       <c r="P260" t="n">
-        <v>2900</v>
+        <v>1500</v>
       </c>
       <c r="Q260" t="n">
-        <v>12945600</v>
+        <v>2028000</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>C494-IO</t>
-        </is>
+          <t>C4945</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>7700154271143</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>GLOBO METALIZADO DULCES</t>
+          <t>MUÑECA CON MASCOTA Y COCHE C4945</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -12037,7 +12040,7 @@
         </is>
       </c>
       <c r="J261" t="n">
-        <v>1352</v>
+        <v>432</v>
       </c>
       <c r="K261" t="n">
         <v>0</v>
@@ -12046,25 +12049,25 @@
         <v>0</v>
       </c>
       <c r="M261" t="n">
-        <v>1352</v>
+        <v>432</v>
       </c>
       <c r="N261" t="n">
-        <v>1200</v>
+        <v>11690</v>
       </c>
       <c r="O261" t="n">
-        <v>1622400</v>
+        <v>5050080</v>
       </c>
       <c r="P261" t="n">
-        <v>1500</v>
+        <v>18900</v>
       </c>
       <c r="Q261" t="n">
-        <v>2028000</v>
+        <v>8164800</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>C4945</t>
+          <t>C4946</t>
         </is>
       </c>
       <c r="B262" t="n">
@@ -12072,7 +12075,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>MUÑECA CON MASCOTA Y COCHE C4945</t>
+          <t>MUÑECA CON ODONTOLOGIA C4946</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -12086,7 +12089,7 @@
         </is>
       </c>
       <c r="J262" t="n">
-        <v>432</v>
+        <v>360</v>
       </c>
       <c r="K262" t="n">
         <v>0</v>
@@ -12095,25 +12098,25 @@
         <v>0</v>
       </c>
       <c r="M262" t="n">
-        <v>432</v>
+        <v>360</v>
       </c>
       <c r="N262" t="n">
-        <v>11690</v>
+        <v>13518</v>
       </c>
       <c r="O262" t="n">
-        <v>5050080</v>
+        <v>4866480</v>
       </c>
       <c r="P262" t="n">
-        <v>18900</v>
+        <v>21900</v>
       </c>
       <c r="Q262" t="n">
-        <v>8164800</v>
+        <v>7884000</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>C4946</t>
+          <t>C4947</t>
         </is>
       </c>
       <c r="B263" t="n">
@@ -12121,7 +12124,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>MUÑECA CON ODONTOLOGIA C4946</t>
+          <t>MUÑECA CON MASCOTAS   C4947</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -12135,7 +12138,7 @@
         </is>
       </c>
       <c r="J263" t="n">
-        <v>360</v>
+        <v>432</v>
       </c>
       <c r="K263" t="n">
         <v>0</v>
@@ -12144,25 +12147,25 @@
         <v>0</v>
       </c>
       <c r="M263" t="n">
-        <v>360</v>
+        <v>432</v>
       </c>
       <c r="N263" t="n">
-        <v>13559.454697519</v>
+        <v>9736</v>
       </c>
       <c r="O263" t="n">
-        <v>4881403.69110684</v>
+        <v>4205952</v>
       </c>
       <c r="P263" t="n">
-        <v>21900</v>
+        <v>15900</v>
       </c>
       <c r="Q263" t="n">
-        <v>7884000</v>
+        <v>6868800</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>C4947</t>
+          <t>C4958</t>
         </is>
       </c>
       <c r="B264" t="n">
@@ -12170,7 +12173,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>MUÑECA CON MASCOTAS   C4947</t>
+          <t>MUÑECA PATINADORA CONTROL REMOTO</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -12184,7 +12187,7 @@
         </is>
       </c>
       <c r="J264" t="n">
-        <v>432</v>
+        <v>36</v>
       </c>
       <c r="K264" t="n">
         <v>0</v>
@@ -12193,25 +12196,25 @@
         <v>0</v>
       </c>
       <c r="M264" t="n">
-        <v>432</v>
+        <v>36</v>
       </c>
       <c r="N264" t="n">
-        <v>9760.865567680499</v>
+        <v>44470</v>
       </c>
       <c r="O264" t="n">
-        <v>4216693.925237976</v>
+        <v>1600920</v>
       </c>
       <c r="P264" t="n">
-        <v>15900</v>
+        <v>71900</v>
       </c>
       <c r="Q264" t="n">
-        <v>6868800</v>
+        <v>2588400</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>C4958</t>
+          <t>C4959</t>
         </is>
       </c>
       <c r="B265" t="n">
@@ -12219,7 +12222,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>MUÑECA PATINADORA CONTROL REMOTO</t>
+          <t>MUÑECA POP ACCESORIOS C4959</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -12233,7 +12236,7 @@
         </is>
       </c>
       <c r="J265" t="n">
-        <v>36</v>
+        <v>684</v>
       </c>
       <c r="K265" t="n">
         <v>0</v>
@@ -12242,47 +12245,42 @@
         <v>0</v>
       </c>
       <c r="M265" t="n">
-        <v>36</v>
+        <v>684</v>
       </c>
       <c r="N265" t="n">
-        <v>45032.911392405</v>
+        <v>5215</v>
       </c>
       <c r="O265" t="n">
-        <v>1621184.81012658</v>
+        <v>3567060</v>
       </c>
       <c r="P265" t="n">
-        <v>71900</v>
+        <v>8900</v>
       </c>
       <c r="Q265" t="n">
-        <v>2588400</v>
+        <v>6087600</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>C4959</t>
+          <t>C502</t>
         </is>
       </c>
       <c r="B266" t="n">
-        <v>7700154271143</v>
+        <v>6952216485215</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>MUÑECA POP ACCESORIOS C4959</t>
-        </is>
-      </c>
-      <c r="E266" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>C502 MUNECA NANCY GRANDE</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J266" t="n">
-        <v>720</v>
+        <v>55</v>
       </c>
       <c r="K266" t="n">
         <v>0</v>
@@ -12291,42 +12289,47 @@
         <v>0</v>
       </c>
       <c r="M266" t="n">
-        <v>720</v>
+        <v>55</v>
       </c>
       <c r="N266" t="n">
-        <v>5227.7693437806</v>
+        <v>15423.36</v>
       </c>
       <c r="O266" t="n">
-        <v>3763993.927522032</v>
+        <v>848284.8</v>
       </c>
       <c r="P266" t="n">
-        <v>8900</v>
+        <v>24900</v>
       </c>
       <c r="Q266" t="n">
-        <v>6408000</v>
+        <v>1369500</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>C502</t>
+          <t>C5030</t>
         </is>
       </c>
       <c r="B267" t="n">
-        <v>6952216485215</v>
+        <v>6999899236062</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>C502 MUNECA NANCY GRANDE</t>
+          <t>INFLABLE DONA LLANTA C5030</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>INFLABLES</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J267" t="n">
-        <v>55</v>
+        <v>121</v>
       </c>
       <c r="K267" t="n">
         <v>0</v>
@@ -12335,33 +12338,33 @@
         <v>0</v>
       </c>
       <c r="M267" t="n">
-        <v>55</v>
+        <v>121</v>
       </c>
       <c r="N267" t="n">
-        <v>15646.886956522</v>
+        <v>2857.22</v>
       </c>
       <c r="O267" t="n">
-        <v>860578.78260871</v>
+        <v>345723.62</v>
       </c>
       <c r="P267" t="n">
-        <v>24900</v>
+        <v>4900</v>
       </c>
       <c r="Q267" t="n">
-        <v>1369500</v>
+        <v>592900</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>C5030</t>
+          <t>C5032</t>
         </is>
       </c>
       <c r="B268" t="n">
-        <v>6999899236062</v>
+        <v>6999899236154</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>INFLABLE DONA LLANTA C5030</t>
+          <t>INFLABLE TECHITO PIECITOS  FIGURAS STD C5032</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -12375,7 +12378,7 @@
         </is>
       </c>
       <c r="J268" t="n">
-        <v>121</v>
+        <v>534</v>
       </c>
       <c r="K268" t="n">
         <v>0</v>
@@ -12384,47 +12387,42 @@
         <v>0</v>
       </c>
       <c r="M268" t="n">
-        <v>121</v>
+        <v>534</v>
       </c>
       <c r="N268" t="n">
-        <v>2857.22</v>
+        <v>8945.379999999999</v>
       </c>
       <c r="O268" t="n">
-        <v>345723.62</v>
+        <v>4776832.92</v>
       </c>
       <c r="P268" t="n">
-        <v>4900</v>
+        <v>14900</v>
       </c>
       <c r="Q268" t="n">
-        <v>592900</v>
+        <v>7956600</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>C5032</t>
+          <t>C506</t>
         </is>
       </c>
       <c r="B269" t="n">
-        <v>6999899236154</v>
+        <v>6952365180054</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>INFLABLE TECHITO PIECITOS  FIGURAS STD C5032</t>
-        </is>
-      </c>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>INFLABLES</t>
+          <t>GLOBO BURBUJA 30</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J269" t="n">
-        <v>534</v>
+        <v>3650</v>
       </c>
       <c r="K269" t="n">
         <v>0</v>
@@ -12433,42 +12431,44 @@
         <v>0</v>
       </c>
       <c r="M269" t="n">
-        <v>534</v>
+        <v>3650</v>
       </c>
       <c r="N269" t="n">
-        <v>8945.379999999999</v>
+        <v>675.2255375485</v>
       </c>
       <c r="O269" t="n">
-        <v>4776832.92</v>
+        <v>2464573.212052025</v>
       </c>
       <c r="P269" t="n">
-        <v>14900</v>
+        <v>1300</v>
       </c>
       <c r="Q269" t="n">
-        <v>7956600</v>
+        <v>4745000</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>C506</t>
-        </is>
-      </c>
-      <c r="B270" t="n">
-        <v>6952365180054</v>
+          <t>C510-IO</t>
+        </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>GLOBO BURBUJA 30</t>
+          <t>GLOBO BURBUJA METALIZADO</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>GLOBOS</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J270" t="n">
-        <v>3650</v>
+        <v>3896</v>
       </c>
       <c r="K270" t="n">
         <v>0</v>
@@ -12477,44 +12477,42 @@
         <v>0</v>
       </c>
       <c r="M270" t="n">
-        <v>3650</v>
+        <v>3896</v>
       </c>
       <c r="N270" t="n">
-        <v>675.2255375485</v>
+        <v>960</v>
       </c>
       <c r="O270" t="n">
-        <v>2464573.212052025</v>
+        <v>3740160</v>
       </c>
       <c r="P270" t="n">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="Q270" t="n">
-        <v>4745000</v>
+        <v>4675200</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>C510-IO</t>
-        </is>
+          <t>C515</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>6953626330010</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>GLOBO BURBUJA METALIZADO</t>
-        </is>
-      </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>GLOBOS</t>
+          <t>GLOBO FIGURAS BURBUJA</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J271" t="n">
-        <v>3896</v>
+        <v>3800</v>
       </c>
       <c r="K271" t="n">
         <v>0</v>
@@ -12523,42 +12521,44 @@
         <v>0</v>
       </c>
       <c r="M271" t="n">
-        <v>3896</v>
+        <v>3800</v>
       </c>
       <c r="N271" t="n">
-        <v>960</v>
+        <v>583.7204926325001</v>
       </c>
       <c r="O271" t="n">
-        <v>3740160</v>
+        <v>2218137.8720035</v>
       </c>
       <c r="P271" t="n">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="Q271" t="n">
-        <v>4675200</v>
+        <v>2280000</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>C515</t>
-        </is>
-      </c>
-      <c r="B272" t="n">
-        <v>6953626330010</v>
+          <t>C5214</t>
+        </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>GLOBO FIGURAS BURBUJA</t>
+          <t>CUBO C5214</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J272" t="n">
-        <v>3800</v>
+        <v>1440</v>
       </c>
       <c r="K272" t="n">
         <v>0</v>
@@ -12567,44 +12567,42 @@
         <v>0</v>
       </c>
       <c r="M272" t="n">
-        <v>3800</v>
+        <v>1440</v>
       </c>
       <c r="N272" t="n">
-        <v>583.7204926325001</v>
+        <v>1690.8700093502</v>
       </c>
       <c r="O272" t="n">
-        <v>2218137.8720035</v>
+        <v>2434852.813464288</v>
       </c>
       <c r="P272" t="n">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="Q272" t="n">
-        <v>2280000</v>
+        <v>4320000</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>C5214</t>
-        </is>
+          <t>C523</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>6957430180212</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>CUBO C5214</t>
-        </is>
-      </c>
-      <c r="E273" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
+          <t>GLOBO NUMERO 16PLATEADO Y DORADO</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J273" t="n">
-        <v>1440</v>
+        <v>2556</v>
       </c>
       <c r="K273" t="n">
         <v>0</v>
@@ -12613,33 +12611,33 @@
         <v>0</v>
       </c>
       <c r="M273" t="n">
-        <v>1440</v>
+        <v>2556</v>
       </c>
       <c r="N273" t="n">
-        <v>1690.8700093371</v>
+        <v>481.48790873239</v>
       </c>
       <c r="O273" t="n">
-        <v>2434852.813445424</v>
+        <v>1230683.094719989</v>
       </c>
       <c r="P273" t="n">
-        <v>3000</v>
+        <v>650</v>
       </c>
       <c r="Q273" t="n">
-        <v>4320000</v>
+        <v>1661400</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>C523</t>
+          <t>C524</t>
         </is>
       </c>
       <c r="B274" t="n">
-        <v>6957430180212</v>
+        <v>6957430180229</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>GLOBO NUMERO 16PLATEADO Y DORADO</t>
+          <t>GLOBO NUMERO 30 PLATEADO Y DORADO</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -12648,7 +12646,7 @@
         </is>
       </c>
       <c r="J274" t="n">
-        <v>2556</v>
+        <v>614</v>
       </c>
       <c r="K274" t="n">
         <v>0</v>
@@ -12657,42 +12655,47 @@
         <v>0</v>
       </c>
       <c r="M274" t="n">
-        <v>2556</v>
+        <v>614</v>
       </c>
       <c r="N274" t="n">
-        <v>481.48790873239</v>
+        <v>872.15418687873</v>
       </c>
       <c r="O274" t="n">
-        <v>1230683.094719989</v>
+        <v>535502.6707435403</v>
       </c>
       <c r="P274" t="n">
-        <v>650</v>
+        <v>1200</v>
       </c>
       <c r="Q274" t="n">
-        <v>1661400</v>
+        <v>736800</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>C524</t>
+          <t>C5246/C5247</t>
         </is>
       </c>
       <c r="B275" t="n">
-        <v>6957430180229</v>
+        <v>6900077483239</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>GLOBO NUMERO 30 PLATEADO Y DORADO</t>
+          <t>MARIONETA DE DEDO ANIMALES STDS C5246/C5247</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J275" t="n">
-        <v>614</v>
+        <v>130</v>
       </c>
       <c r="K275" t="n">
         <v>0</v>
@@ -12701,47 +12704,42 @@
         <v>0</v>
       </c>
       <c r="M275" t="n">
-        <v>614</v>
+        <v>130</v>
       </c>
       <c r="N275" t="n">
-        <v>872.15418687873</v>
+        <v>8915.3355918367</v>
       </c>
       <c r="O275" t="n">
-        <v>535502.6707435403</v>
+        <v>1158993.626938771</v>
       </c>
       <c r="P275" t="n">
-        <v>1200</v>
+        <v>8900</v>
       </c>
       <c r="Q275" t="n">
-        <v>736800</v>
+        <v>1157000</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>C5246/C5247</t>
+          <t>C525</t>
         </is>
       </c>
       <c r="B276" t="n">
-        <v>6900077483239</v>
+        <v>6957430180236</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>MARIONETA DE DEDO ANIMALES STDS C5246/C5247</t>
-        </is>
-      </c>
-      <c r="E276" t="inlineStr">
-        <is>
-          <t>DIDACTICO</t>
+          <t>GLOBO NUMERO 16 COLORES Y PUNTOS</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J276" t="n">
-        <v>130</v>
+        <v>1436</v>
       </c>
       <c r="K276" t="n">
         <v>0</v>
@@ -12750,33 +12748,33 @@
         <v>0</v>
       </c>
       <c r="M276" t="n">
-        <v>130</v>
+        <v>1436</v>
       </c>
       <c r="N276" t="n">
-        <v>8702.219999999999</v>
+        <v>345.55838633169</v>
       </c>
       <c r="O276" t="n">
-        <v>1131288.6</v>
+        <v>496221.8427723068</v>
       </c>
       <c r="P276" t="n">
-        <v>8900</v>
+        <v>600</v>
       </c>
       <c r="Q276" t="n">
-        <v>1157000</v>
+        <v>861600</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>C525</t>
+          <t>C526</t>
         </is>
       </c>
       <c r="B277" t="n">
-        <v>6957430180236</v>
+        <v>6957430180243</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>GLOBO NUMERO 16 COLORES Y PUNTOS</t>
+          <t>GLOBO NUMERO 30 COLORES Y PUNTOS</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -12785,7 +12783,7 @@
         </is>
       </c>
       <c r="J277" t="n">
-        <v>1436</v>
+        <v>11416</v>
       </c>
       <c r="K277" t="n">
         <v>0</v>
@@ -12794,42 +12792,47 @@
         <v>0</v>
       </c>
       <c r="M277" t="n">
-        <v>1436</v>
+        <v>11416</v>
       </c>
       <c r="N277" t="n">
-        <v>345.55838633169</v>
+        <v>711.3366477489</v>
       </c>
       <c r="O277" t="n">
-        <v>496221.8427723068</v>
+        <v>8120619.170701442</v>
       </c>
       <c r="P277" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="Q277" t="n">
-        <v>861600</v>
+        <v>10274400</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>C526</t>
+          <t>C527-IO</t>
         </is>
       </c>
       <c r="B278" t="n">
-        <v>6957430180243</v>
+        <v>6957430180526</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>GLOBO NUMERO 30 COLORES Y PUNTOS</t>
+          <t>GLOBO FELIZ CUMPLEAÑOS LISTON</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>GLOBOS</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J278" t="n">
-        <v>11416</v>
+        <v>1242</v>
       </c>
       <c r="K278" t="n">
         <v>0</v>
@@ -12838,38 +12841,35 @@
         <v>0</v>
       </c>
       <c r="M278" t="n">
-        <v>11416</v>
+        <v>1242</v>
       </c>
       <c r="N278" t="n">
-        <v>711.3366477489</v>
+        <v>815.0599999999999</v>
       </c>
       <c r="O278" t="n">
-        <v>8120619.170701442</v>
+        <v>1012304.52</v>
       </c>
       <c r="P278" t="n">
         <v>900</v>
       </c>
       <c r="Q278" t="n">
-        <v>10274400</v>
+        <v>1117800</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>C527-IO</t>
-        </is>
-      </c>
-      <c r="B279" t="n">
-        <v>6957430180526</v>
+          <t>C541</t>
+        </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>GLOBO FELIZ CUMPLEAÑOS LISTON</t>
+          <t>GLOBO LLAMA PQÑO</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>GLOBOS</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -12878,7 +12878,7 @@
         </is>
       </c>
       <c r="J279" t="n">
-        <v>1242</v>
+        <v>2150</v>
       </c>
       <c r="K279" t="n">
         <v>0</v>
@@ -12887,30 +12887,30 @@
         <v>0</v>
       </c>
       <c r="M279" t="n">
-        <v>1242</v>
+        <v>2150</v>
       </c>
       <c r="N279" t="n">
-        <v>815.0599999999999</v>
+        <v>800</v>
       </c>
       <c r="O279" t="n">
-        <v>1012304.52</v>
+        <v>1720000</v>
       </c>
       <c r="P279" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="Q279" t="n">
-        <v>1117800</v>
+        <v>2150000</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>C541</t>
+          <t>C575-IO</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>GLOBO LLAMA PQÑO</t>
+          <t>GLOBO UNICORNIO PQÑO</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -12924,7 +12924,7 @@
         </is>
       </c>
       <c r="J280" t="n">
-        <v>2150</v>
+        <v>1001</v>
       </c>
       <c r="K280" t="n">
         <v>0</v>
@@ -12933,35 +12933,38 @@
         <v>0</v>
       </c>
       <c r="M280" t="n">
-        <v>2150</v>
+        <v>1001</v>
       </c>
       <c r="N280" t="n">
-        <v>800</v>
+        <v>320</v>
       </c>
       <c r="O280" t="n">
-        <v>1720000</v>
+        <v>320320</v>
       </c>
       <c r="P280" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="Q280" t="n">
-        <v>2150000</v>
+        <v>400400</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>C575-IO</t>
-        </is>
+          <t>C596-IO</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>8596162180268</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>GLOBO UNICORNIO PQÑO</t>
+          <t>GLOBO TE AMO</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>GLOBOS</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -12970,7 +12973,7 @@
         </is>
       </c>
       <c r="J281" t="n">
-        <v>1001</v>
+        <v>1455</v>
       </c>
       <c r="K281" t="n">
         <v>0</v>
@@ -12979,33 +12982,33 @@
         <v>0</v>
       </c>
       <c r="M281" t="n">
-        <v>1001</v>
+        <v>1455</v>
       </c>
       <c r="N281" t="n">
-        <v>320</v>
+        <v>1044.54</v>
       </c>
       <c r="O281" t="n">
-        <v>320320</v>
+        <v>1519805.7</v>
       </c>
       <c r="P281" t="n">
-        <v>400</v>
+        <v>1200</v>
       </c>
       <c r="Q281" t="n">
-        <v>400400</v>
+        <v>1746000</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>C596-IO</t>
+          <t>C60-IO</t>
         </is>
       </c>
       <c r="B282" t="n">
-        <v>8596162180268</v>
+        <v>6524521011245</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>GLOBO TE AMO</t>
+          <t>GLOBO TIKTOK BOUQUET</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -13019,7 +13022,7 @@
         </is>
       </c>
       <c r="J282" t="n">
-        <v>1455</v>
+        <v>740</v>
       </c>
       <c r="K282" t="n">
         <v>0</v>
@@ -13028,38 +13031,35 @@
         <v>0</v>
       </c>
       <c r="M282" t="n">
-        <v>1455</v>
+        <v>740</v>
       </c>
       <c r="N282" t="n">
-        <v>1044.54</v>
+        <v>1989.05</v>
       </c>
       <c r="O282" t="n">
-        <v>1519805.7</v>
+        <v>1471897</v>
       </c>
       <c r="P282" t="n">
-        <v>1200</v>
+        <v>3000</v>
       </c>
       <c r="Q282" t="n">
-        <v>1746000</v>
+        <v>2220000</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>C60-IO</t>
-        </is>
-      </c>
-      <c r="B283" t="n">
-        <v>6524521011245</v>
+          <t>C6074</t>
+        </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>GLOBO TIKTOK BOUQUET</t>
+          <t>FIGURAS ALIMENTOS DECORATIVOS C6074</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>GLOBOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -13068,7 +13068,7 @@
         </is>
       </c>
       <c r="J283" t="n">
-        <v>740</v>
+        <v>25</v>
       </c>
       <c r="K283" t="n">
         <v>0</v>
@@ -13077,44 +13077,42 @@
         <v>0</v>
       </c>
       <c r="M283" t="n">
-        <v>740</v>
+        <v>25</v>
       </c>
       <c r="N283" t="n">
-        <v>1989.05</v>
+        <v>9447.25</v>
       </c>
       <c r="O283" t="n">
-        <v>1471897</v>
+        <v>236181.25</v>
       </c>
       <c r="P283" t="n">
-        <v>3000</v>
+        <v>9900</v>
       </c>
       <c r="Q283" t="n">
-        <v>2220000</v>
+        <v>247500</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>C6074</t>
-        </is>
+          <t>C629</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>7791638082188</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>FIGURAS ALIMENTOS DECORATIVOS C6074</t>
-        </is>
-      </c>
-      <c r="E284" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
+          <t>BURBUJERO PITO STD</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J284" t="n">
-        <v>25</v>
+        <v>15264</v>
       </c>
       <c r="K284" t="n">
         <v>0</v>
@@ -13123,42 +13121,47 @@
         <v>0</v>
       </c>
       <c r="M284" t="n">
-        <v>25</v>
+        <v>15264</v>
       </c>
       <c r="N284" t="n">
-        <v>9447.25</v>
+        <v>703.7947715550901</v>
       </c>
       <c r="O284" t="n">
-        <v>236181.25</v>
+        <v>10742723.3930169</v>
       </c>
       <c r="P284" t="n">
-        <v>9900</v>
+        <v>900</v>
       </c>
       <c r="Q284" t="n">
-        <v>247500</v>
+        <v>13737600</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>C629</t>
+          <t>C6406</t>
         </is>
       </c>
       <c r="B285" t="n">
-        <v>7791638082188</v>
+        <v>6820212541115</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>BURBUJERO PITO STD</t>
+          <t>PAJAROS MUSICALES DECORATIVOS C6406</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J285" t="n">
-        <v>15264</v>
+        <v>52</v>
       </c>
       <c r="K285" t="n">
         <v>0</v>
@@ -13167,47 +13170,39 @@
         <v>0</v>
       </c>
       <c r="M285" t="n">
-        <v>15264</v>
+        <v>52</v>
       </c>
       <c r="N285" t="n">
-        <v>703.79479136392</v>
+        <v>14260.14</v>
       </c>
       <c r="O285" t="n">
-        <v>10742723.69537888</v>
+        <v>741527.28</v>
       </c>
       <c r="P285" t="n">
-        <v>900</v>
+        <v>15900</v>
       </c>
       <c r="Q285" t="n">
-        <v>13737600</v>
+        <v>826800</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>C6406</t>
-        </is>
-      </c>
-      <c r="B286" t="n">
-        <v>6820212541115</v>
+          <t>C642</t>
+        </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>PAJAROS MUSICALES DECORATIVOS C6406</t>
-        </is>
-      </c>
-      <c r="E286" t="inlineStr">
-        <is>
-          <t>MICELANEOS</t>
+          <t>LANZADOR AGUA</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J286" t="n">
-        <v>52</v>
+        <v>599</v>
       </c>
       <c r="K286" t="n">
         <v>0</v>
@@ -13216,39 +13211,44 @@
         <v>0</v>
       </c>
       <c r="M286" t="n">
-        <v>52</v>
+        <v>599</v>
       </c>
       <c r="N286" t="n">
-        <v>14260.14</v>
+        <v>2529.19</v>
       </c>
       <c r="O286" t="n">
-        <v>741527.28</v>
+        <v>1514984.81</v>
       </c>
       <c r="P286" t="n">
-        <v>15900</v>
+        <v>5100</v>
       </c>
       <c r="Q286" t="n">
-        <v>826800</v>
+        <v>3054900</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>C642</t>
+          <t>C671-LJ</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>LANZADOR AGUA</t>
+          <t>GLOBO UNICORNIO MEDIANO</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J287" t="n">
-        <v>599</v>
+        <v>1397</v>
       </c>
       <c r="K287" t="n">
         <v>0</v>
@@ -13257,35 +13257,38 @@
         <v>0</v>
       </c>
       <c r="M287" t="n">
-        <v>599</v>
+        <v>1397</v>
       </c>
       <c r="N287" t="n">
-        <v>2529.19</v>
+        <v>400</v>
       </c>
       <c r="O287" t="n">
-        <v>1514984.81</v>
+        <v>558800</v>
       </c>
       <c r="P287" t="n">
-        <v>5100</v>
+        <v>500</v>
       </c>
       <c r="Q287" t="n">
-        <v>3054900</v>
+        <v>698500</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>C671-LJ</t>
-        </is>
+          <t>C7005</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>6874123039124</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>GLOBO UNICORNIO MEDIANO</t>
+          <t>MAQUINA DE COSER C7005</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -13294,7 +13297,7 @@
         </is>
       </c>
       <c r="J288" t="n">
-        <v>1397</v>
+        <v>208</v>
       </c>
       <c r="K288" t="n">
         <v>0</v>
@@ -13303,38 +13306,38 @@
         <v>0</v>
       </c>
       <c r="M288" t="n">
-        <v>1397</v>
+        <v>208</v>
       </c>
       <c r="N288" t="n">
-        <v>400</v>
+        <v>6078.9925934066</v>
       </c>
       <c r="O288" t="n">
-        <v>558800</v>
+        <v>1264430.459428573</v>
       </c>
       <c r="P288" t="n">
-        <v>500</v>
+        <v>18500</v>
       </c>
       <c r="Q288" t="n">
-        <v>698500</v>
+        <v>3848000</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>C7005</t>
+          <t>C7009</t>
         </is>
       </c>
       <c r="B289" t="n">
-        <v>6874123039124</v>
+        <v>2024250256831</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>MAQUINA DE COSER C7005</t>
+          <t>LANZADORA DE AGUA  TUBO CON HELICE C7009</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>LANZADORES</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -13343,7 +13346,7 @@
         </is>
       </c>
       <c r="J289" t="n">
-        <v>208</v>
+        <v>12</v>
       </c>
       <c r="K289" t="n">
         <v>0</v>
@@ -13352,33 +13355,33 @@
         <v>0</v>
       </c>
       <c r="M289" t="n">
-        <v>208</v>
+        <v>12</v>
       </c>
       <c r="N289" t="n">
-        <v>6078.9925934066</v>
+        <v>5899.18</v>
       </c>
       <c r="O289" t="n">
-        <v>1264430.459428573</v>
+        <v>70790.16</v>
       </c>
       <c r="P289" t="n">
-        <v>18500</v>
+        <v>12500</v>
       </c>
       <c r="Q289" t="n">
-        <v>3848000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>C7009</t>
+          <t>C7038</t>
         </is>
       </c>
       <c r="B290" t="n">
-        <v>2024250256831</v>
+        <v>5132595141631</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>LANZADORA DE AGUA  TUBO CON HELICE C7009</t>
+          <t>LANZADORA DE AGUA GLOBO C7038</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -13392,7 +13395,7 @@
         </is>
       </c>
       <c r="J290" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="K290" t="n">
         <v>0</v>
@@ -13401,38 +13404,38 @@
         <v>0</v>
       </c>
       <c r="M290" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="N290" t="n">
-        <v>5899.18</v>
+        <v>18423.71</v>
       </c>
       <c r="O290" t="n">
-        <v>70790.16</v>
+        <v>423745.33</v>
       </c>
       <c r="P290" t="n">
-        <v>12500</v>
+        <v>10000</v>
       </c>
       <c r="Q290" t="n">
-        <v>150000</v>
+        <v>230000</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>C7038</t>
+          <t>C7039</t>
         </is>
       </c>
       <c r="B291" t="n">
-        <v>5132595141631</v>
+        <v>5132594521182</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>LANZADORA DE AGUA GLOBO C7038</t>
+          <t>LANZADOR AGUA GLOBO DELFIN C7039/M90-4</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>LANZADORES</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -13441,7 +13444,7 @@
         </is>
       </c>
       <c r="J291" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K291" t="n">
         <v>0</v>
@@ -13450,38 +13453,38 @@
         <v>0</v>
       </c>
       <c r="M291" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="N291" t="n">
-        <v>18423.71</v>
+        <v>10985.78</v>
       </c>
       <c r="O291" t="n">
-        <v>423745.33</v>
+        <v>219715.6</v>
       </c>
       <c r="P291" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="Q291" t="n">
-        <v>230000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>C7039</t>
+          <t>C7040</t>
         </is>
       </c>
       <c r="B292" t="n">
-        <v>5132594521182</v>
+        <v>6920373004365</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>LANZADOR AGUA GLOBO DELFIN C7039/M90-4</t>
+          <t>GARAJE EXIBICION CON LUZ C7040</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -13490,7 +13493,7 @@
         </is>
       </c>
       <c r="J292" t="n">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="K292" t="n">
         <v>0</v>
@@ -13499,38 +13502,38 @@
         <v>0</v>
       </c>
       <c r="M292" t="n">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="N292" t="n">
-        <v>10985.78</v>
+        <v>23452.77</v>
       </c>
       <c r="O292" t="n">
-        <v>219715.6</v>
+        <v>1102280.19</v>
       </c>
       <c r="P292" t="n">
-        <v>15000</v>
+        <v>39900</v>
       </c>
       <c r="Q292" t="n">
-        <v>300000</v>
+        <v>1875300</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>C7040</t>
+          <t>C7042</t>
         </is>
       </c>
       <c r="B293" t="n">
-        <v>6920373004365</v>
+        <v>2024081616255</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>GARAJE EXIBICION CON LUZ C7040</t>
+          <t>CANCHA BASKETBALL WIN24 C7042</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -13539,7 +13542,7 @@
         </is>
       </c>
       <c r="J293" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="K293" t="n">
         <v>0</v>
@@ -13548,38 +13551,35 @@
         <v>0</v>
       </c>
       <c r="M293" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="N293" t="n">
-        <v>23452.77</v>
+        <v>9694.41</v>
       </c>
       <c r="O293" t="n">
-        <v>1102280.19</v>
+        <v>96944.10000000001</v>
       </c>
       <c r="P293" t="n">
-        <v>39900</v>
+        <v>32500</v>
       </c>
       <c r="Q293" t="n">
-        <v>1875300</v>
+        <v>325000</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>C7042</t>
-        </is>
-      </c>
-      <c r="B294" t="n">
-        <v>2024081616255</v>
+          <t>C7080-BC</t>
+        </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>CANCHA BASKETBALL WIN24 C7042</t>
+          <t>ROBOT TRANSFORME STD C7080-BC</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MUÑECOS</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -13588,7 +13588,7 @@
         </is>
       </c>
       <c r="J294" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="K294" t="n">
         <v>0</v>
@@ -13597,35 +13597,38 @@
         <v>0</v>
       </c>
       <c r="M294" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="N294" t="n">
-        <v>9694.41</v>
+        <v>10556.12</v>
       </c>
       <c r="O294" t="n">
-        <v>96944.10000000001</v>
+        <v>411688.6800000001</v>
       </c>
       <c r="P294" t="n">
-        <v>32500</v>
+        <v>32900</v>
       </c>
       <c r="Q294" t="n">
-        <v>325000</v>
+        <v>1283100</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>C7080-BC</t>
-        </is>
+          <t>C7081</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>6301582313156</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>ROBOT TRANSFORME STD C7080-BC</t>
+          <t>LANZADORA DARDOS DE PILA C7081</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>MUÑECOS</t>
+          <t>LANZADORES</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -13634,7 +13637,7 @@
         </is>
       </c>
       <c r="J295" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="K295" t="n">
         <v>0</v>
@@ -13643,47 +13646,42 @@
         <v>0</v>
       </c>
       <c r="M295" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="N295" t="n">
-        <v>10556.12</v>
+        <v>22470.62</v>
       </c>
       <c r="O295" t="n">
-        <v>411688.6800000001</v>
+        <v>471883.02</v>
       </c>
       <c r="P295" t="n">
-        <v>32900</v>
+        <v>41900</v>
       </c>
       <c r="Q295" t="n">
-        <v>1283100</v>
+        <v>879900</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>C7081</t>
+          <t>C71</t>
         </is>
       </c>
       <c r="B296" t="n">
-        <v>6301582313156</v>
+        <v>5899989622205</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>LANZADORA DARDOS DE PILA C7081</t>
-        </is>
-      </c>
-      <c r="E296" t="inlineStr">
-        <is>
-          <t>LANZADORES</t>
+          <t>C71 INFLABLE PONY ROSADO-AZUL</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J296" t="n">
-        <v>21</v>
+        <v>392</v>
       </c>
       <c r="K296" t="n">
         <v>0</v>
@@ -13692,42 +13690,44 @@
         <v>0</v>
       </c>
       <c r="M296" t="n">
-        <v>21</v>
+        <v>392</v>
       </c>
       <c r="N296" t="n">
-        <v>22470.62</v>
+        <v>1669.6</v>
       </c>
       <c r="O296" t="n">
-        <v>471883.02</v>
+        <v>654483.2</v>
       </c>
       <c r="P296" t="n">
-        <v>41900</v>
+        <v>2900</v>
       </c>
       <c r="Q296" t="n">
-        <v>879900</v>
+        <v>1136800</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>C71</t>
-        </is>
-      </c>
-      <c r="B297" t="n">
-        <v>5899989622205</v>
+          <t>C7117</t>
+        </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>C71 INFLABLE PONY ROSADO-AZUL</t>
+          <t>BINGO LOTTO C7117</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>JUEGOS DE MESA</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J297" t="n">
-        <v>392</v>
+        <v>20</v>
       </c>
       <c r="K297" t="n">
         <v>0</v>
@@ -13736,35 +13736,35 @@
         <v>0</v>
       </c>
       <c r="M297" t="n">
-        <v>392</v>
+        <v>20</v>
       </c>
       <c r="N297" t="n">
-        <v>1669.6</v>
+        <v>5798.41</v>
       </c>
       <c r="O297" t="n">
-        <v>654483.2</v>
+        <v>115968.2</v>
       </c>
       <c r="P297" t="n">
-        <v>2900</v>
+        <v>14900</v>
       </c>
       <c r="Q297" t="n">
-        <v>1136800</v>
+        <v>298000</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>C7117</t>
+          <t>C7124</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>BINGO LOTTO C7117</t>
+          <t>TRAILER TRANFORME XQ05 C7124</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>JUEGOS DE MESA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -13773,7 +13773,7 @@
         </is>
       </c>
       <c r="J298" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K298" t="n">
         <v>0</v>
@@ -13782,35 +13782,35 @@
         <v>0</v>
       </c>
       <c r="M298" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="N298" t="n">
-        <v>5798.41</v>
+        <v>19587.53</v>
       </c>
       <c r="O298" t="n">
-        <v>115968.2</v>
+        <v>783501.2</v>
       </c>
       <c r="P298" t="n">
-        <v>14900</v>
+        <v>65000</v>
       </c>
       <c r="Q298" t="n">
-        <v>298000</v>
+        <v>2600000</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>C7124</t>
+          <t>C7132</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>TRAILER TRANFORME XQ05 C7124</t>
+          <t>SET PULSERAS Y CAUCHOS C7132</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -13819,7 +13819,7 @@
         </is>
       </c>
       <c r="J299" t="n">
-        <v>40</v>
+        <v>144</v>
       </c>
       <c r="K299" t="n">
         <v>0</v>
@@ -13828,30 +13828,33 @@
         <v>0</v>
       </c>
       <c r="M299" t="n">
-        <v>40</v>
+        <v>144</v>
       </c>
       <c r="N299" t="n">
-        <v>19587.53</v>
+        <v>3100.87</v>
       </c>
       <c r="O299" t="n">
-        <v>783501.2</v>
+        <v>446525.28</v>
       </c>
       <c r="P299" t="n">
-        <v>65000</v>
+        <v>9900</v>
       </c>
       <c r="Q299" t="n">
-        <v>2600000</v>
+        <v>1425600</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>C7132</t>
-        </is>
+          <t>C7147-A</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>6912209205022</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>SET PULSERAS Y CAUCHOS C7132</t>
+          <t>ANIMAL DINOSAURIO TRICERATOPS CONLUZ C7147-A</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -13865,7 +13868,7 @@
         </is>
       </c>
       <c r="J300" t="n">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="K300" t="n">
         <v>0</v>
@@ -13874,33 +13877,33 @@
         <v>0</v>
       </c>
       <c r="M300" t="n">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="N300" t="n">
-        <v>3100.87</v>
+        <v>10348.08</v>
       </c>
       <c r="O300" t="n">
-        <v>446525.28</v>
+        <v>413923.2</v>
       </c>
       <c r="P300" t="n">
-        <v>9900</v>
+        <v>16900</v>
       </c>
       <c r="Q300" t="n">
-        <v>1425600</v>
+        <v>676000</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>C7147-A</t>
+          <t>C7213</t>
         </is>
       </c>
       <c r="B301" t="n">
-        <v>6912209205022</v>
+        <v>6987540143012</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>ANIMAL DINOSAURIO TRICERATOPS CONLUZ C7147-A</t>
+          <t>PESCADO CON LUZ Y SONIDO C7213</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -13914,7 +13917,7 @@
         </is>
       </c>
       <c r="J301" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="K301" t="n">
         <v>0</v>
@@ -13923,33 +13926,33 @@
         <v>0</v>
       </c>
       <c r="M301" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="N301" t="n">
-        <v>10348.08</v>
+        <v>9746.8802061856</v>
       </c>
       <c r="O301" t="n">
-        <v>413923.2</v>
+        <v>467850.2498969088</v>
       </c>
       <c r="P301" t="n">
-        <v>16900</v>
+        <v>18500</v>
       </c>
       <c r="Q301" t="n">
-        <v>676000</v>
+        <v>888000</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>C7213</t>
+          <t>C7221</t>
         </is>
       </c>
       <c r="B302" t="n">
-        <v>6987540143012</v>
+        <v>7453100037446</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>PESCADO CON LUZ Y SONIDO C7213</t>
+          <t>RELOJ CON FICHAS ARMABLES  C7221</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -13963,7 +13966,7 @@
         </is>
       </c>
       <c r="J302" t="n">
-        <v>48</v>
+        <v>347</v>
       </c>
       <c r="K302" t="n">
         <v>0</v>
@@ -13972,33 +13975,33 @@
         <v>0</v>
       </c>
       <c r="M302" t="n">
-        <v>48</v>
+        <v>347</v>
       </c>
       <c r="N302" t="n">
-        <v>9746.8802020202</v>
+        <v>2672.89</v>
       </c>
       <c r="O302" t="n">
-        <v>467850.2496969696</v>
+        <v>927492.83</v>
       </c>
       <c r="P302" t="n">
-        <v>18500</v>
+        <v>10200</v>
       </c>
       <c r="Q302" t="n">
-        <v>888000</v>
+        <v>3539400</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>C7221</t>
+          <t>C7222</t>
         </is>
       </c>
       <c r="B303" t="n">
-        <v>7453100037446</v>
+        <v>7453100037453</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>RELOJ CON FICHAS ARMABLES  C7221</t>
+          <t>RELOJ DIDACTICO CARACOL C7222</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -14012,7 +14015,7 @@
         </is>
       </c>
       <c r="J303" t="n">
-        <v>347</v>
+        <v>230</v>
       </c>
       <c r="K303" t="n">
         <v>0</v>
@@ -14021,38 +14024,38 @@
         <v>0</v>
       </c>
       <c r="M303" t="n">
-        <v>347</v>
+        <v>230</v>
       </c>
       <c r="N303" t="n">
-        <v>2672.89</v>
+        <v>4795.69</v>
       </c>
       <c r="O303" t="n">
-        <v>927492.83</v>
+        <v>1103008.7</v>
       </c>
       <c r="P303" t="n">
         <v>10200</v>
       </c>
       <c r="Q303" t="n">
-        <v>3539400</v>
+        <v>2346000</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>C7222</t>
+          <t>C7294</t>
         </is>
       </c>
       <c r="B304" t="n">
-        <v>7453100037453</v>
+        <v>6895675680022</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>RELOJ DIDACTICO CARACOL C7222</t>
+          <t>JUEGO DEPORTIVO HOCHEY C7294</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -14061,7 +14064,7 @@
         </is>
       </c>
       <c r="J304" t="n">
-        <v>230</v>
+        <v>60</v>
       </c>
       <c r="K304" t="n">
         <v>0</v>
@@ -14070,38 +14073,38 @@
         <v>0</v>
       </c>
       <c r="M304" t="n">
-        <v>230</v>
+        <v>60</v>
       </c>
       <c r="N304" t="n">
-        <v>4795.69</v>
+        <v>4337.31</v>
       </c>
       <c r="O304" t="n">
-        <v>1103008.7</v>
+        <v>260238.6</v>
       </c>
       <c r="P304" t="n">
-        <v>10200</v>
+        <v>12900</v>
       </c>
       <c r="Q304" t="n">
-        <v>2346000</v>
+        <v>774000</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>C7246</t>
+          <t>C7325</t>
         </is>
       </c>
       <c r="B305" t="n">
-        <v>6902024622111</v>
+        <v>6974555555022</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>BLÍSTER SKATE X4 C7246</t>
+          <t>PISTA EN BLISTER C7325</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -14110,7 +14113,7 @@
         </is>
       </c>
       <c r="J305" t="n">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="K305" t="n">
         <v>0</v>
@@ -14119,38 +14122,35 @@
         <v>0</v>
       </c>
       <c r="M305" t="n">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="N305" t="n">
-        <v>2992.5733928571</v>
+        <v>3067.0906143345</v>
       </c>
       <c r="O305" t="n">
-        <v>38903.4541071423</v>
+        <v>138019.0776450525</v>
       </c>
       <c r="P305" t="n">
-        <v>6000</v>
+        <v>7200</v>
       </c>
       <c r="Q305" t="n">
-        <v>78000</v>
+        <v>324000</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>C7294</t>
-        </is>
-      </c>
-      <c r="B306" t="n">
-        <v>6895675680022</v>
+          <t>C736</t>
+        </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>JUEGO DEPORTIVO HOCHEY C7294</t>
+          <t>GLOBO CORAZON GDE MENSAJE</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -14159,7 +14159,7 @@
         </is>
       </c>
       <c r="J306" t="n">
-        <v>60</v>
+        <v>2700</v>
       </c>
       <c r="K306" t="n">
         <v>0</v>
@@ -14168,38 +14168,38 @@
         <v>0</v>
       </c>
       <c r="M306" t="n">
-        <v>60</v>
+        <v>2700</v>
       </c>
       <c r="N306" t="n">
-        <v>4337.31</v>
+        <v>640</v>
       </c>
       <c r="O306" t="n">
-        <v>260238.6</v>
+        <v>1728000</v>
       </c>
       <c r="P306" t="n">
-        <v>12900</v>
+        <v>800</v>
       </c>
       <c r="Q306" t="n">
-        <v>774000</v>
+        <v>2160000</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>C7325</t>
+          <t>C7365</t>
         </is>
       </c>
       <c r="B307" t="n">
-        <v>6974555555022</v>
+        <v>6920240750050</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>PISTA EN BLISTER C7325</t>
+          <t>DIDACTICO JIRAFA EN BOLSA C7365</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -14208,7 +14208,7 @@
         </is>
       </c>
       <c r="J307" t="n">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="K307" t="n">
         <v>0</v>
@@ -14217,35 +14217,38 @@
         <v>0</v>
       </c>
       <c r="M307" t="n">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="N307" t="n">
-        <v>3067.0906143345</v>
+        <v>4190.77</v>
       </c>
       <c r="O307" t="n">
-        <v>138019.0776450525</v>
+        <v>79624.63</v>
       </c>
       <c r="P307" t="n">
-        <v>7200</v>
+        <v>5900</v>
       </c>
       <c r="Q307" t="n">
-        <v>324000</v>
+        <v>112100</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>C736</t>
-        </is>
+          <t>C7366</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>6920240750098</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>GLOBO CORAZON GDE MENSAJE</t>
+          <t>TREN DIDACTICO EN BOLSA C7366</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -14254,7 +14257,7 @@
         </is>
       </c>
       <c r="J308" t="n">
-        <v>2700</v>
+        <v>104</v>
       </c>
       <c r="K308" t="n">
         <v>0</v>
@@ -14263,33 +14266,33 @@
         <v>0</v>
       </c>
       <c r="M308" t="n">
-        <v>2700</v>
+        <v>104</v>
       </c>
       <c r="N308" t="n">
-        <v>640</v>
+        <v>3499.72</v>
       </c>
       <c r="O308" t="n">
-        <v>1728000</v>
+        <v>363970.88</v>
       </c>
       <c r="P308" t="n">
-        <v>800</v>
+        <v>6900</v>
       </c>
       <c r="Q308" t="n">
-        <v>2160000</v>
+        <v>717600</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>C7365</t>
+          <t>C7368</t>
         </is>
       </c>
       <c r="B309" t="n">
-        <v>6920240750050</v>
+        <v>6920240750159</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>DIDACTICO JIRAFA EN BOLSA C7365</t>
+          <t>MOTO DIDACTICA EN BOLSA C736</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -14303,7 +14306,7 @@
         </is>
       </c>
       <c r="J309" t="n">
-        <v>19</v>
+        <v>158</v>
       </c>
       <c r="K309" t="n">
         <v>0</v>
@@ -14312,38 +14315,35 @@
         <v>0</v>
       </c>
       <c r="M309" t="n">
-        <v>19</v>
+        <v>158</v>
       </c>
       <c r="N309" t="n">
-        <v>4190.77</v>
+        <v>4593.1990728477</v>
       </c>
       <c r="O309" t="n">
-        <v>79624.63</v>
+        <v>725725.4535099367</v>
       </c>
       <c r="P309" t="n">
-        <v>5900</v>
+        <v>7500</v>
       </c>
       <c r="Q309" t="n">
-        <v>112100</v>
+        <v>1185000</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>C7366</t>
-        </is>
-      </c>
-      <c r="B310" t="n">
-        <v>6920240750098</v>
+          <t>C740-IO</t>
+        </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>TREN DIDACTICO EN BOLSA C7366</t>
+          <t>GLOBO UNICORNIO MED</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -14352,7 +14352,7 @@
         </is>
       </c>
       <c r="J310" t="n">
-        <v>104</v>
+        <v>1876</v>
       </c>
       <c r="K310" t="n">
         <v>0</v>
@@ -14361,33 +14361,33 @@
         <v>0</v>
       </c>
       <c r="M310" t="n">
-        <v>104</v>
+        <v>1876</v>
       </c>
       <c r="N310" t="n">
-        <v>3499.72</v>
+        <v>480</v>
       </c>
       <c r="O310" t="n">
-        <v>363970.88</v>
+        <v>900480</v>
       </c>
       <c r="P310" t="n">
-        <v>6900</v>
+        <v>600</v>
       </c>
       <c r="Q310" t="n">
-        <v>717600</v>
+        <v>1125600</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>C7368</t>
+          <t>C7413</t>
         </is>
       </c>
       <c r="B311" t="n">
-        <v>6920240750159</v>
+        <v>6921202412870</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>MOTO DIDACTICA EN BOLSA C736</t>
+          <t>DIDACTICO TORRE DE AROS C7413</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -14401,7 +14401,7 @@
         </is>
       </c>
       <c r="J311" t="n">
-        <v>158</v>
+        <v>120</v>
       </c>
       <c r="K311" t="n">
         <v>0</v>
@@ -14410,35 +14410,35 @@
         <v>0</v>
       </c>
       <c r="M311" t="n">
-        <v>158</v>
+        <v>120</v>
       </c>
       <c r="N311" t="n">
-        <v>4578.04</v>
+        <v>4159.0003007519</v>
       </c>
       <c r="O311" t="n">
-        <v>723330.3199999999</v>
+        <v>499080.036090228</v>
       </c>
       <c r="P311" t="n">
-        <v>7500</v>
+        <v>8900</v>
       </c>
       <c r="Q311" t="n">
-        <v>1185000</v>
+        <v>1068000</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>C740-IO</t>
+          <t>C744-IO</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>GLOBO UNICORNIO MED</t>
+          <t>GLOBO FELIZ CUMPLEAÑOS COLORES Y PUNTOS</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>GLOBOS</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -14447,7 +14447,7 @@
         </is>
       </c>
       <c r="J312" t="n">
-        <v>1876</v>
+        <v>478</v>
       </c>
       <c r="K312" t="n">
         <v>0</v>
@@ -14456,38 +14456,38 @@
         <v>0</v>
       </c>
       <c r="M312" t="n">
-        <v>1876</v>
+        <v>478</v>
       </c>
       <c r="N312" t="n">
-        <v>480</v>
+        <v>1554.12</v>
       </c>
       <c r="O312" t="n">
-        <v>900480</v>
+        <v>742869.36</v>
       </c>
       <c r="P312" t="n">
-        <v>600</v>
+        <v>1900</v>
       </c>
       <c r="Q312" t="n">
-        <v>1125600</v>
+        <v>908200</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>C7413</t>
+          <t>C7453</t>
         </is>
       </c>
       <c r="B313" t="n">
-        <v>6921202412870</v>
+        <v>6920247274535</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>DIDACTICO TORRE DE AROS C7413</t>
+          <t>JUEGO DE MESA BALONCESTO C7453</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -14496,7 +14496,7 @@
         </is>
       </c>
       <c r="J313" t="n">
-        <v>120</v>
+        <v>8</v>
       </c>
       <c r="K313" t="n">
         <v>0</v>
@@ -14505,35 +14505,35 @@
         <v>0</v>
       </c>
       <c r="M313" t="n">
-        <v>120</v>
+        <v>8</v>
       </c>
       <c r="N313" t="n">
-        <v>4159.0003007519</v>
+        <v>27938.1</v>
       </c>
       <c r="O313" t="n">
-        <v>499080.036090228</v>
+        <v>223504.8</v>
       </c>
       <c r="P313" t="n">
-        <v>8900</v>
+        <v>18000</v>
       </c>
       <c r="Q313" t="n">
-        <v>1068000</v>
+        <v>144000</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>C744-IO</t>
+          <t>C7462</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>GLOBO FELIZ CUMPLEAÑOS COLORES Y PUNTOS</t>
+          <t>SET DE BELLEZA ACCESORIOS PARA EL CABELLO C7462</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>GLOBOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -14542,7 +14542,7 @@
         </is>
       </c>
       <c r="J314" t="n">
-        <v>478</v>
+        <v>11</v>
       </c>
       <c r="K314" t="n">
         <v>0</v>
@@ -14551,33 +14551,33 @@
         <v>0</v>
       </c>
       <c r="M314" t="n">
-        <v>478</v>
+        <v>11</v>
       </c>
       <c r="N314" t="n">
-        <v>1554.12</v>
+        <v>14751.820327869</v>
       </c>
       <c r="O314" t="n">
-        <v>742869.36</v>
+        <v>162270.023606559</v>
       </c>
       <c r="P314" t="n">
-        <v>1900</v>
+        <v>37100</v>
       </c>
       <c r="Q314" t="n">
-        <v>908200</v>
+        <v>408100</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>C7453</t>
+          <t>C7467</t>
         </is>
       </c>
       <c r="B315" t="n">
-        <v>6920247274535</v>
+        <v>6920241023009</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>JUEGO DE MESA BALONCESTO C7453</t>
+          <t>ARCO Y FLECHA PARA NIÑAS C7467</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -14591,7 +14591,7 @@
         </is>
       </c>
       <c r="J315" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K315" t="n">
         <v>0</v>
@@ -14600,35 +14600,38 @@
         <v>0</v>
       </c>
       <c r="M315" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="N315" t="n">
-        <v>27938.1</v>
+        <v>15347.45</v>
       </c>
       <c r="O315" t="n">
-        <v>223504.8</v>
+        <v>230211.75</v>
       </c>
       <c r="P315" t="n">
-        <v>18000</v>
+        <v>23900</v>
       </c>
       <c r="Q315" t="n">
-        <v>144000</v>
+        <v>358500</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>C7462</t>
-        </is>
+          <t>C7488</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>6945158254520</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>SET DE BELLEZA ACCESORIOS PARA EL CABELLO C7462</t>
+          <t>SOPORTE CELULAR CON LUZ C7488</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -14637,7 +14640,7 @@
         </is>
       </c>
       <c r="J316" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="K316" t="n">
         <v>0</v>
@@ -14646,33 +14649,33 @@
         <v>0</v>
       </c>
       <c r="M316" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="N316" t="n">
-        <v>14751.820327869</v>
+        <v>8919.16</v>
       </c>
       <c r="O316" t="n">
-        <v>162270.023606559</v>
+        <v>258655.64</v>
       </c>
       <c r="P316" t="n">
-        <v>37100</v>
+        <v>10000</v>
       </c>
       <c r="Q316" t="n">
-        <v>408100</v>
+        <v>290000</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>C7467</t>
+          <t>C7513</t>
         </is>
       </c>
       <c r="B317" t="n">
-        <v>6920241023009</v>
+        <v>6905698382824</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>ARCO Y FLECHA PARA NIÑAS C7467</t>
+          <t>SONAJERO BOLA LUZ GDE C7513</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -14686,7 +14689,7 @@
         </is>
       </c>
       <c r="J317" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="K317" t="n">
         <v>0</v>
@@ -14695,47 +14698,42 @@
         <v>0</v>
       </c>
       <c r="M317" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="N317" t="n">
-        <v>15347.45</v>
+        <v>1024.29</v>
       </c>
       <c r="O317" t="n">
-        <v>230211.75</v>
+        <v>1024.29</v>
       </c>
       <c r="P317" t="n">
-        <v>23900</v>
+        <v>2900</v>
       </c>
       <c r="Q317" t="n">
-        <v>358500</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>C7488</t>
+          <t>C752</t>
         </is>
       </c>
       <c r="B318" t="n">
-        <v>6945158254520</v>
+        <v>8596162180497</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>SOPORTE CELULAR CON LUZ C7488</t>
-        </is>
-      </c>
-      <c r="E318" t="inlineStr">
-        <is>
-          <t>MICELANEOS</t>
+          <t>GLOBO UNICORNIO MED 4 PATAS</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J318" t="n">
-        <v>29</v>
+        <v>1398</v>
       </c>
       <c r="K318" t="n">
         <v>0</v>
@@ -14744,47 +14742,42 @@
         <v>0</v>
       </c>
       <c r="M318" t="n">
-        <v>29</v>
+        <v>1398</v>
       </c>
       <c r="N318" t="n">
-        <v>8919.16</v>
+        <v>1163.7447787403</v>
       </c>
       <c r="O318" t="n">
-        <v>258655.64</v>
+        <v>1626915.200678939</v>
       </c>
       <c r="P318" t="n">
-        <v>10000</v>
+        <v>1500</v>
       </c>
       <c r="Q318" t="n">
-        <v>290000</v>
+        <v>2097000</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>C7513</t>
+          <t>C753</t>
         </is>
       </c>
       <c r="B319" t="n">
-        <v>6905698382824</v>
+        <v>8596162180503</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>SONAJERO BOLA LUZ GDE C7513</t>
-        </is>
-      </c>
-      <c r="E319" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
+          <t>GLOBO UNICORNIO GDE 4 PATAS</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J319" t="n">
-        <v>1</v>
+        <v>277</v>
       </c>
       <c r="K319" t="n">
         <v>0</v>
@@ -14793,42 +14786,47 @@
         <v>0</v>
       </c>
       <c r="M319" t="n">
-        <v>1</v>
+        <v>277</v>
       </c>
       <c r="N319" t="n">
-        <v>1024.29</v>
+        <v>5113.4625508318</v>
       </c>
       <c r="O319" t="n">
-        <v>1024.29</v>
+        <v>1416429.126580409</v>
       </c>
       <c r="P319" t="n">
-        <v>2900</v>
+        <v>7000</v>
       </c>
       <c r="Q319" t="n">
-        <v>2900</v>
+        <v>1939000</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>C752</t>
+          <t>C7533</t>
         </is>
       </c>
       <c r="B320" t="n">
-        <v>8596162180497</v>
+        <v>6923669699979</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>GLOBO UNICORNIO MED 4 PATAS</t>
+          <t>REPUESTO BIOGEL NEON C7533</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J320" t="n">
-        <v>1398</v>
+        <v>12023</v>
       </c>
       <c r="K320" t="n">
         <v>0</v>
@@ -14837,42 +14835,47 @@
         <v>0</v>
       </c>
       <c r="M320" t="n">
-        <v>1398</v>
+        <v>12023</v>
       </c>
       <c r="N320" t="n">
-        <v>1163.7447787403</v>
+        <v>509.69</v>
       </c>
       <c r="O320" t="n">
-        <v>1626915.200678939</v>
+        <v>6128002.87</v>
       </c>
       <c r="P320" t="n">
-        <v>1500</v>
+        <v>750</v>
       </c>
       <c r="Q320" t="n">
-        <v>2097000</v>
+        <v>9017250</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>C753</t>
+          <t>C7534</t>
         </is>
       </c>
       <c r="B321" t="n">
-        <v>8596162180503</v>
+        <v>6951241752002</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>GLOBO UNICORNIO GDE 4 PATAS</t>
+          <t>GORRO PELUCHE LUZ C7534-A-B-C-D-E-F</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J321" t="n">
-        <v>277</v>
+        <v>499</v>
       </c>
       <c r="K321" t="n">
         <v>0</v>
@@ -14881,38 +14884,35 @@
         <v>0</v>
       </c>
       <c r="M321" t="n">
-        <v>277</v>
+        <v>499</v>
       </c>
       <c r="N321" t="n">
-        <v>5113.4625508318</v>
+        <v>7046.9398271765</v>
       </c>
       <c r="O321" t="n">
-        <v>1416429.126580409</v>
+        <v>3516422.973761074</v>
       </c>
       <c r="P321" t="n">
-        <v>7000</v>
+        <v>9900</v>
       </c>
       <c r="Q321" t="n">
-        <v>1939000</v>
+        <v>4940100</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>C7533</t>
-        </is>
-      </c>
-      <c r="B322" t="n">
-        <v>6923669699979</v>
+          <t>C7535</t>
+        </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>REPUESTO BIOGEL NEON C7533</t>
+          <t>CARRO METALICO X13 CON CAMION C7535</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -14921,7 +14921,7 @@
         </is>
       </c>
       <c r="J322" t="n">
-        <v>12023</v>
+        <v>30</v>
       </c>
       <c r="K322" t="n">
         <v>0</v>
@@ -14930,33 +14930,30 @@
         <v>0</v>
       </c>
       <c r="M322" t="n">
-        <v>12023</v>
+        <v>30</v>
       </c>
       <c r="N322" t="n">
-        <v>509.69</v>
+        <v>24338.47</v>
       </c>
       <c r="O322" t="n">
-        <v>6128002.87</v>
+        <v>730154.1000000001</v>
       </c>
       <c r="P322" t="n">
-        <v>750</v>
+        <v>27900</v>
       </c>
       <c r="Q322" t="n">
-        <v>9017250</v>
+        <v>837000</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>C7534</t>
-        </is>
-      </c>
-      <c r="B323" t="n">
-        <v>6951241752002</v>
+          <t>C7560</t>
+        </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>GORRO PELUCHE LUZ C7534-A-B-C-D-E-F</t>
+          <t>BARRA LUMINOSA 48CM C7560/211</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -14970,7 +14967,7 @@
         </is>
       </c>
       <c r="J323" t="n">
-        <v>499</v>
+        <v>188</v>
       </c>
       <c r="K323" t="n">
         <v>0</v>
@@ -14979,35 +14976,38 @@
         <v>0</v>
       </c>
       <c r="M323" t="n">
-        <v>499</v>
+        <v>188</v>
       </c>
       <c r="N323" t="n">
-        <v>7046.9398272138</v>
+        <v>796.3099999999999</v>
       </c>
       <c r="O323" t="n">
-        <v>3516422.973779686</v>
+        <v>149706.28</v>
       </c>
       <c r="P323" t="n">
-        <v>9900</v>
+        <v>2500</v>
       </c>
       <c r="Q323" t="n">
-        <v>4940100</v>
+        <v>470000</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>C7535</t>
-        </is>
+          <t>C7588</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>7588228020244</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>CARRO METALICO X13 CON CAMION C7535</t>
+          <t>SONAJERO LUZ PANDITA C7588</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -15016,7 +15016,7 @@
         </is>
       </c>
       <c r="J324" t="n">
-        <v>30</v>
+        <v>1429</v>
       </c>
       <c r="K324" t="n">
         <v>0</v>
@@ -15025,35 +15025,38 @@
         <v>0</v>
       </c>
       <c r="M324" t="n">
-        <v>30</v>
+        <v>1429</v>
       </c>
       <c r="N324" t="n">
-        <v>24338.47</v>
+        <v>641.78</v>
       </c>
       <c r="O324" t="n">
-        <v>730154.1000000001</v>
+        <v>917103.62</v>
       </c>
       <c r="P324" t="n">
-        <v>27900</v>
+        <v>2500</v>
       </c>
       <c r="Q324" t="n">
-        <v>837000</v>
+        <v>3572500</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>C7560</t>
-        </is>
+          <t>C7610</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>6999899236093</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>BARRA LUMINOSA 48CM C7560/211</t>
+          <t>BOTE TIMON PISCINA 80X60 C7610</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>INFLABLES</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -15062,7 +15065,7 @@
         </is>
       </c>
       <c r="J325" t="n">
-        <v>188</v>
+        <v>276</v>
       </c>
       <c r="K325" t="n">
         <v>0</v>
@@ -15071,38 +15074,38 @@
         <v>0</v>
       </c>
       <c r="M325" t="n">
-        <v>188</v>
+        <v>276</v>
       </c>
       <c r="N325" t="n">
-        <v>796.3099999999999</v>
+        <v>7811.9</v>
       </c>
       <c r="O325" t="n">
-        <v>149706.28</v>
+        <v>2156084.4</v>
       </c>
       <c r="P325" t="n">
-        <v>2500</v>
+        <v>13900</v>
       </c>
       <c r="Q325" t="n">
-        <v>470000</v>
+        <v>3836400</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>C7588</t>
+          <t>C7614-F</t>
         </is>
       </c>
       <c r="B326" t="n">
-        <v>7588228020244</v>
+        <v>6999899236130</v>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>SONAJERO LUZ PANDITA C7588</t>
+          <t>FLOTADOR DONA FLAMINGO C7614-F</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -15111,7 +15114,7 @@
         </is>
       </c>
       <c r="J326" t="n">
-        <v>1429</v>
+        <v>382</v>
       </c>
       <c r="K326" t="n">
         <v>0</v>
@@ -15120,47 +15123,42 @@
         <v>0</v>
       </c>
       <c r="M326" t="n">
-        <v>1429</v>
+        <v>382</v>
       </c>
       <c r="N326" t="n">
-        <v>641.78</v>
+        <v>3155</v>
       </c>
       <c r="O326" t="n">
-        <v>917103.62</v>
+        <v>1205210</v>
       </c>
       <c r="P326" t="n">
-        <v>2500</v>
+        <v>5900</v>
       </c>
       <c r="Q326" t="n">
-        <v>3572500</v>
+        <v>2253800</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>C7610</t>
+          <t>C784</t>
         </is>
       </c>
       <c r="B327" t="n">
-        <v>6999899236093</v>
+        <v>8913992935507</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>BOTE TIMON PISCINA 80X60 C7610</t>
-        </is>
-      </c>
-      <c r="E327" t="inlineStr">
-        <is>
-          <t>INFLABLES</t>
+          <t>GLOBO MENSAJE CUADRADO</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J327" t="n">
-        <v>276</v>
+        <v>1450</v>
       </c>
       <c r="K327" t="n">
         <v>0</v>
@@ -15169,47 +15167,42 @@
         <v>0</v>
       </c>
       <c r="M327" t="n">
-        <v>276</v>
+        <v>1450</v>
       </c>
       <c r="N327" t="n">
-        <v>7811.9</v>
+        <v>704.89694272446</v>
       </c>
       <c r="O327" t="n">
-        <v>2156084.4</v>
+        <v>1022100.566950467</v>
       </c>
       <c r="P327" t="n">
-        <v>13900</v>
+        <v>900</v>
       </c>
       <c r="Q327" t="n">
-        <v>3836400</v>
+        <v>1305000</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>C7614-F</t>
+          <t>C819</t>
         </is>
       </c>
       <c r="B328" t="n">
-        <v>6999899236130</v>
+        <v>2087202108190</v>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>FLOTADOR DONA FLAMINGO C7614-F</t>
-        </is>
-      </c>
-      <c r="E328" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>TROMPO EMOJI</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J328" t="n">
-        <v>382</v>
+        <v>468</v>
       </c>
       <c r="K328" t="n">
         <v>0</v>
@@ -15218,33 +15211,33 @@
         <v>0</v>
       </c>
       <c r="M328" t="n">
-        <v>382</v>
+        <v>468</v>
       </c>
       <c r="N328" t="n">
-        <v>3155</v>
+        <v>6761.25</v>
       </c>
       <c r="O328" t="n">
-        <v>1205210</v>
+        <v>3164265</v>
       </c>
       <c r="P328" t="n">
-        <v>5900</v>
+        <v>5200</v>
       </c>
       <c r="Q328" t="n">
-        <v>2253800</v>
+        <v>2433600</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>C784</t>
+          <t>C84</t>
         </is>
       </c>
       <c r="B329" t="n">
-        <v>8913992935507</v>
+        <v>2021010563031</v>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>GLOBO MENSAJE CUADRADO</t>
+          <t>LANZADOR DE AGUA</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -15253,7 +15246,7 @@
         </is>
       </c>
       <c r="J329" t="n">
-        <v>1450</v>
+        <v>212</v>
       </c>
       <c r="K329" t="n">
         <v>0</v>
@@ -15262,33 +15255,35 @@
         <v>0</v>
       </c>
       <c r="M329" t="n">
-        <v>1450</v>
+        <v>212</v>
       </c>
       <c r="N329" t="n">
-        <v>704.89694272446</v>
+        <v>1008.8125188917</v>
       </c>
       <c r="O329" t="n">
-        <v>1022100.566950467</v>
+        <v>213868.2540050404</v>
       </c>
       <c r="P329" t="n">
-        <v>900</v>
+        <v>1500</v>
       </c>
       <c r="Q329" t="n">
-        <v>1305000</v>
+        <v>318000</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>C819</t>
-        </is>
-      </c>
-      <c r="B330" t="n">
-        <v>2087202108190</v>
+          <t>C879</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>CG-2016-212</t>
+        </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>TROMPO EMOJI</t>
+          <t>VELA MARIPOSA</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -15297,7 +15292,7 @@
         </is>
       </c>
       <c r="J330" t="n">
-        <v>468</v>
+        <v>121</v>
       </c>
       <c r="K330" t="n">
         <v>0</v>
@@ -15306,42 +15301,49 @@
         <v>0</v>
       </c>
       <c r="M330" t="n">
-        <v>468</v>
+        <v>121</v>
       </c>
       <c r="N330" t="n">
-        <v>6761.25</v>
+        <v>1520</v>
       </c>
       <c r="O330" t="n">
-        <v>3164265</v>
+        <v>183920</v>
       </c>
       <c r="P330" t="n">
-        <v>5200</v>
+        <v>1900</v>
       </c>
       <c r="Q330" t="n">
-        <v>2433600</v>
+        <v>229900</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>C84</t>
-        </is>
-      </c>
-      <c r="B331" t="n">
-        <v>2021010563031</v>
+          <t>C880</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>cg2016213</t>
+        </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>LANZADOR DE AGUA</t>
+          <t>VELA FLOR</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>VELA</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J331" t="n">
-        <v>224</v>
+        <v>200</v>
       </c>
       <c r="K331" t="n">
         <v>0</v>
@@ -15350,35 +15352,30 @@
         <v>0</v>
       </c>
       <c r="M331" t="n">
-        <v>224</v>
+        <v>200</v>
       </c>
       <c r="N331" t="n">
-        <v>1008.8130317848</v>
+        <v>1520</v>
       </c>
       <c r="O331" t="n">
-        <v>225974.1191197952</v>
+        <v>304000</v>
       </c>
       <c r="P331" t="n">
-        <v>1500</v>
+        <v>1900</v>
       </c>
       <c r="Q331" t="n">
-        <v>336000</v>
+        <v>380000</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>C879</t>
-        </is>
-      </c>
-      <c r="B332" t="inlineStr">
-        <is>
-          <t>CG-2016-212</t>
+          <t>C888</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>VELA MARIPOSA</t>
+          <t>PELOTA CHILLON PUYAS SIN LUZ</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -15387,7 +15384,7 @@
         </is>
       </c>
       <c r="J332" t="n">
-        <v>121</v>
+        <v>169</v>
       </c>
       <c r="K332" t="n">
         <v>0</v>
@@ -15396,40 +15393,35 @@
         <v>0</v>
       </c>
       <c r="M332" t="n">
-        <v>121</v>
+        <v>169</v>
       </c>
       <c r="N332" t="n">
-        <v>1520</v>
+        <v>1213.6821400778</v>
       </c>
       <c r="O332" t="n">
-        <v>183920</v>
+        <v>205112.2816731482</v>
       </c>
       <c r="P332" t="n">
-        <v>1900</v>
+        <v>1500</v>
       </c>
       <c r="Q332" t="n">
-        <v>229900</v>
+        <v>253500</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>C880</t>
-        </is>
-      </c>
-      <c r="B333" t="inlineStr">
-        <is>
-          <t>cg2016213</t>
+          <t>FG037</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>VELA FLOR</t>
+          <t>SNORKEL 66046A</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>VELA</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -15438,7 +15430,7 @@
         </is>
       </c>
       <c r="J333" t="n">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="K333" t="n">
         <v>0</v>
@@ -15447,39 +15439,44 @@
         <v>0</v>
       </c>
       <c r="M333" t="n">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="N333" t="n">
-        <v>1520</v>
+        <v>13493.858292683</v>
       </c>
       <c r="O333" t="n">
-        <v>304000</v>
+        <v>2415400.634390257</v>
       </c>
       <c r="P333" t="n">
-        <v>1900</v>
+        <v>16900</v>
       </c>
       <c r="Q333" t="n">
-        <v>380000</v>
+        <v>3025100</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>C888</t>
+          <t>FG039</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>PELOTA CHILLON PUYAS SIN LUZ</t>
+          <t>GAFA DE NATACION BLISTER 2404-2</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J334" t="n">
-        <v>169</v>
+        <v>347</v>
       </c>
       <c r="K334" t="n">
         <v>0</v>
@@ -15488,35 +15485,40 @@
         <v>0</v>
       </c>
       <c r="M334" t="n">
-        <v>169</v>
+        <v>347</v>
       </c>
       <c r="N334" t="n">
-        <v>1213.6821400778</v>
+        <v>2655.5149832776</v>
       </c>
       <c r="O334" t="n">
-        <v>205112.2816731482</v>
+        <v>921463.6991973273</v>
       </c>
       <c r="P334" t="n">
-        <v>1500</v>
+        <v>3900</v>
       </c>
       <c r="Q334" t="n">
-        <v>253500</v>
+        <v>1353300</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>FG037</t>
+          <t>MG16332</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>MG16332</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>SNORKEL 66046A</t>
+          <t>LANZADOR  ARCO Y FLECA CON LASER MG16332</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -15525,7 +15527,7 @@
         </is>
       </c>
       <c r="J335" t="n">
-        <v>179</v>
+        <v>4</v>
       </c>
       <c r="K335" t="n">
         <v>0</v>
@@ -15534,35 +15536,35 @@
         <v>0</v>
       </c>
       <c r="M335" t="n">
-        <v>179</v>
+        <v>4</v>
       </c>
       <c r="N335" t="n">
-        <v>13493.858292683</v>
+        <v>8439.969999999999</v>
       </c>
       <c r="O335" t="n">
-        <v>2415400.634390257</v>
+        <v>33759.88</v>
       </c>
       <c r="P335" t="n">
-        <v>16900</v>
+        <v>29500</v>
       </c>
       <c r="Q335" t="n">
-        <v>3025100</v>
+        <v>118000</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>FG039</t>
+          <t>MG20430</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>GAFA DE NATACION BLISTER 2404-2</t>
+          <t>SET PLASTILINA CON MOLDES BARBERIA MALETA MG20430</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -15571,7 +15573,7 @@
         </is>
       </c>
       <c r="J336" t="n">
-        <v>347</v>
+        <v>18</v>
       </c>
       <c r="K336" t="n">
         <v>0</v>
@@ -15580,40 +15582,35 @@
         <v>0</v>
       </c>
       <c r="M336" t="n">
-        <v>347</v>
+        <v>18</v>
       </c>
       <c r="N336" t="n">
-        <v>2644.9</v>
+        <v>12189.831111111</v>
       </c>
       <c r="O336" t="n">
-        <v>917780.3</v>
+        <v>219416.959999998</v>
       </c>
       <c r="P336" t="n">
-        <v>3900</v>
+        <v>30900</v>
       </c>
       <c r="Q336" t="n">
-        <v>1353300</v>
+        <v>556200</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>MG16332</t>
-        </is>
-      </c>
-      <c r="B337" t="inlineStr">
-        <is>
-          <t>MG16332</t>
+          <t>MG40210</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>LANZADOR  ARCO Y FLECA CON LASER MG16332</t>
+          <t>SONAJERO OSO MG40210</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -15622,7 +15619,7 @@
         </is>
       </c>
       <c r="J337" t="n">
-        <v>4</v>
+        <v>363</v>
       </c>
       <c r="K337" t="n">
         <v>0</v>
@@ -15631,30 +15628,35 @@
         <v>0</v>
       </c>
       <c r="M337" t="n">
-        <v>4</v>
+        <v>363</v>
       </c>
       <c r="N337" t="n">
-        <v>8439.969999999999</v>
+        <v>571.87</v>
       </c>
       <c r="O337" t="n">
-        <v>33759.88</v>
+        <v>207588.81</v>
       </c>
       <c r="P337" t="n">
-        <v>29500</v>
+        <v>2500</v>
       </c>
       <c r="Q337" t="n">
-        <v>118000</v>
+        <v>907500</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>MG20430</t>
+          <t>MG40720</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>MG40720</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>SET PLASTILINA CON MOLDES BARBERIA MALETA MG20430</t>
+          <t>MAQUINA DE COSER MINI MG40720</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -15668,7 +15670,7 @@
         </is>
       </c>
       <c r="J338" t="n">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="K338" t="n">
         <v>0</v>
@@ -15677,166 +15679,18 @@
         <v>0</v>
       </c>
       <c r="M338" t="n">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="N338" t="n">
-        <v>12189.831111111</v>
+        <v>9917.040000000001</v>
       </c>
       <c r="O338" t="n">
-        <v>219416.959999998</v>
+        <v>634690.5600000001</v>
       </c>
       <c r="P338" t="n">
-        <v>30900</v>
+        <v>15900</v>
       </c>
       <c r="Q338" t="n">
-        <v>556200</v>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" t="inlineStr">
-        <is>
-          <t>MG30151</t>
-        </is>
-      </c>
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>MG30151</t>
-        </is>
-      </c>
-      <c r="C339" t="inlineStr">
-        <is>
-          <t>DIDACTICO PIANO MUSICAL CARRITO MG30151</t>
-        </is>
-      </c>
-      <c r="E339" t="inlineStr">
-        <is>
-          <t>DIDACTICO</t>
-        </is>
-      </c>
-      <c r="I339" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J339" t="n">
-        <v>48</v>
-      </c>
-      <c r="K339" t="n">
-        <v>0</v>
-      </c>
-      <c r="L339" t="n">
-        <v>0</v>
-      </c>
-      <c r="M339" t="n">
-        <v>48</v>
-      </c>
-      <c r="N339" t="n">
-        <v>15452.21</v>
-      </c>
-      <c r="O339" t="n">
-        <v>741706.08</v>
-      </c>
-      <c r="P339" t="n">
-        <v>36500</v>
-      </c>
-      <c r="Q339" t="n">
-        <v>1752000</v>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" t="inlineStr">
-        <is>
-          <t>MG40210</t>
-        </is>
-      </c>
-      <c r="C340" t="inlineStr">
-        <is>
-          <t>SONAJERO OSO MG40210</t>
-        </is>
-      </c>
-      <c r="E340" t="inlineStr">
-        <is>
-          <t>DIDACTICO</t>
-        </is>
-      </c>
-      <c r="I340" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J340" t="n">
-        <v>363</v>
-      </c>
-      <c r="K340" t="n">
-        <v>0</v>
-      </c>
-      <c r="L340" t="n">
-        <v>0</v>
-      </c>
-      <c r="M340" t="n">
-        <v>363</v>
-      </c>
-      <c r="N340" t="n">
-        <v>571.87</v>
-      </c>
-      <c r="O340" t="n">
-        <v>207588.81</v>
-      </c>
-      <c r="P340" t="n">
-        <v>2500</v>
-      </c>
-      <c r="Q340" t="n">
-        <v>907500</v>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" t="inlineStr">
-        <is>
-          <t>MG40720</t>
-        </is>
-      </c>
-      <c r="B341" t="inlineStr">
-        <is>
-          <t>MG40720</t>
-        </is>
-      </c>
-      <c r="C341" t="inlineStr">
-        <is>
-          <t>MAQUINA DE COSER MINI MG40720</t>
-        </is>
-      </c>
-      <c r="E341" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
-        </is>
-      </c>
-      <c r="I341" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J341" t="n">
-        <v>64</v>
-      </c>
-      <c r="K341" t="n">
-        <v>0</v>
-      </c>
-      <c r="L341" t="n">
-        <v>0</v>
-      </c>
-      <c r="M341" t="n">
-        <v>64</v>
-      </c>
-      <c r="N341" t="n">
-        <v>9917.040000000001</v>
-      </c>
-      <c r="O341" t="n">
-        <v>634690.5600000001</v>
-      </c>
-      <c r="P341" t="n">
-        <v>15900</v>
-      </c>
-      <c r="Q341" t="n">
         <v>1017600</v>
       </c>
     </row>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -798,10 +798,10 @@
         <v>1</v>
       </c>
       <c r="N10" t="n">
-        <v>4088.8962655602</v>
+        <v>4072</v>
       </c>
       <c r="O10" t="n">
-        <v>4088.8962655602</v>
+        <v>4072</v>
       </c>
       <c r="P10" t="n">
         <v>7500</v>
@@ -2365,10 +2365,10 @@
         <v>96</v>
       </c>
       <c r="N48" t="n">
-        <v>2644.1214388489</v>
+        <v>2570.16</v>
       </c>
       <c r="O48" t="n">
-        <v>253835.6581294944</v>
+        <v>246735.36</v>
       </c>
       <c r="P48" t="n">
         <v>4700</v>
@@ -2675,10 +2675,10 @@
         <v>40</v>
       </c>
       <c r="N55" t="n">
-        <v>10897.588251121</v>
+        <v>10752.93</v>
       </c>
       <c r="O55" t="n">
-        <v>435903.53004484</v>
+        <v>430117.2</v>
       </c>
       <c r="P55" t="n">
         <v>18400</v>
@@ -3748,10 +3748,10 @@
         <v>216</v>
       </c>
       <c r="N79" t="n">
-        <v>3594.2531182796</v>
+        <v>3594.2531034483</v>
       </c>
       <c r="O79" t="n">
-        <v>776358.6735483936</v>
+        <v>776358.6703448328</v>
       </c>
       <c r="P79" t="n">
         <v>6500</v>
@@ -5304,10 +5304,10 @@
         <v>2</v>
       </c>
       <c r="N113" t="n">
-        <v>17733.6</v>
+        <v>14778</v>
       </c>
       <c r="O113" t="n">
-        <v>35467.2</v>
+        <v>29556</v>
       </c>
       <c r="P113" t="n">
         <v>24900</v>
@@ -6414,10 +6414,10 @@
         <v>55</v>
       </c>
       <c r="N138" t="n">
-        <v>30262.214828189</v>
+        <v>30244.600034945</v>
       </c>
       <c r="O138" t="n">
-        <v>1664421.815550395</v>
+        <v>1663453.001921975</v>
       </c>
       <c r="P138" t="n">
         <v>48900</v>
@@ -6547,10 +6547,10 @@
         <v>94</v>
       </c>
       <c r="N141" t="n">
-        <v>61248.535714286</v>
+        <v>60174</v>
       </c>
       <c r="O141" t="n">
-        <v>5757362.357142884</v>
+        <v>5656356</v>
       </c>
       <c r="P141" t="n">
         <v>96900</v>
@@ -6864,10 +6864,10 @@
         <v>144</v>
       </c>
       <c r="N148" t="n">
-        <v>27233.355818182</v>
+        <v>27123.764828283</v>
       </c>
       <c r="O148" t="n">
-        <v>3921603.237818208</v>
+        <v>3905822.135272752</v>
       </c>
       <c r="P148" t="n">
         <v>44500</v>
@@ -7915,10 +7915,10 @@
         <v>160</v>
       </c>
       <c r="N171" t="n">
-        <v>16092.984749455</v>
+        <v>16058</v>
       </c>
       <c r="O171" t="n">
-        <v>2574877.5599128</v>
+        <v>2569280</v>
       </c>
       <c r="P171" t="n">
         <v>25900</v>
@@ -7961,10 +7961,10 @@
         <v>396</v>
       </c>
       <c r="N172" t="n">
-        <v>25576.890257559</v>
+        <v>25534</v>
       </c>
       <c r="O172" t="n">
-        <v>10128448.54199336</v>
+        <v>10111464</v>
       </c>
       <c r="P172" t="n">
         <v>40900</v>
@@ -8470,10 +8470,10 @@
         <v>210</v>
       </c>
       <c r="N183" t="n">
-        <v>10485.899280576</v>
+        <v>10411</v>
       </c>
       <c r="O183" t="n">
-        <v>2202038.84892096</v>
+        <v>2186310</v>
       </c>
       <c r="P183" t="n">
         <v>16900</v>
@@ -8746,10 +8746,10 @@
         <v>123</v>
       </c>
       <c r="N189" t="n">
-        <v>32566.857142857</v>
+        <v>32332</v>
       </c>
       <c r="O189" t="n">
-        <v>4005723.428571411</v>
+        <v>3976836</v>
       </c>
       <c r="P189" t="n">
         <v>55900</v>
@@ -9160,10 +9160,10 @@
         <v>12</v>
       </c>
       <c r="N198" t="n">
-        <v>23932.94</v>
+        <v>23376.36</v>
       </c>
       <c r="O198" t="n">
-        <v>287195.28</v>
+        <v>280516.32</v>
       </c>
       <c r="P198" t="n">
         <v>40900</v>
@@ -9206,10 +9206,10 @@
         <v>502</v>
       </c>
       <c r="N199" t="n">
-        <v>13233.257042254</v>
+        <v>13210</v>
       </c>
       <c r="O199" t="n">
-        <v>6643095.035211507</v>
+        <v>6631420</v>
       </c>
       <c r="P199" t="n">
         <v>23900</v>
@@ -9380,10 +9380,10 @@
         <v>51</v>
       </c>
       <c r="N203" t="n">
-        <v>36516.685818182</v>
+        <v>35864.602181818</v>
       </c>
       <c r="O203" t="n">
-        <v>1862350.976727282</v>
+        <v>1829094.711272718</v>
       </c>
       <c r="P203" t="n">
         <v>62900</v>
@@ -9564,10 +9564,10 @@
         <v>18</v>
       </c>
       <c r="N207" t="n">
-        <v>12498.870967742</v>
+        <v>11922</v>
       </c>
       <c r="O207" t="n">
-        <v>224979.677419356</v>
+        <v>214596</v>
       </c>
       <c r="P207" t="n">
         <v>19900</v>
@@ -9702,10 +9702,10 @@
         <v>443</v>
       </c>
       <c r="N210" t="n">
-        <v>6881.8463298379</v>
+        <v>6849.2</v>
       </c>
       <c r="O210" t="n">
-        <v>3048657.92411819</v>
+        <v>3034195.6</v>
       </c>
       <c r="P210" t="n">
         <v>11500</v>
@@ -10070,10 +10070,10 @@
         <v>1162</v>
       </c>
       <c r="N218" t="n">
-        <v>7639.2713286713</v>
+        <v>7635</v>
       </c>
       <c r="O218" t="n">
-        <v>8876833.283916051</v>
+        <v>8871870</v>
       </c>
       <c r="P218" t="n">
         <v>13900</v>
@@ -10392,10 +10392,10 @@
         <v>290</v>
       </c>
       <c r="N225" t="n">
-        <v>11478.737327189</v>
+        <v>11348</v>
       </c>
       <c r="O225" t="n">
-        <v>3328833.82488481</v>
+        <v>3290920</v>
       </c>
       <c r="P225" t="n">
         <v>19900</v>
@@ -11085,10 +11085,10 @@
         <v>78</v>
       </c>
       <c r="N240" t="n">
-        <v>14369.318181818</v>
+        <v>14050</v>
       </c>
       <c r="O240" t="n">
-        <v>1120806.818181804</v>
+        <v>1095900</v>
       </c>
       <c r="P240" t="n">
         <v>23900</v>
@@ -11131,10 +11131,10 @@
         <v>285</v>
       </c>
       <c r="N241" t="n">
-        <v>8721.3759213759</v>
+        <v>8700</v>
       </c>
       <c r="O241" t="n">
-        <v>2485592.137592132</v>
+        <v>2479500</v>
       </c>
       <c r="P241" t="n">
         <v>14900</v>
@@ -11453,10 +11453,10 @@
         <v>181</v>
       </c>
       <c r="N248" t="n">
-        <v>21884.258426966</v>
+        <v>21762</v>
       </c>
       <c r="O248" t="n">
-        <v>3961050.775280846</v>
+        <v>3938922</v>
       </c>
       <c r="P248" t="n">
         <v>35900</v>
@@ -11499,10 +11499,10 @@
         <v>934</v>
       </c>
       <c r="N249" t="n">
-        <v>3823.6153319644</v>
+        <v>3821</v>
       </c>
       <c r="O249" t="n">
-        <v>3571256.720054749</v>
+        <v>3568814</v>
       </c>
       <c r="P249" t="n">
         <v>5900</v>
@@ -11591,10 +11591,10 @@
         <v>8</v>
       </c>
       <c r="N251" t="n">
-        <v>50038.3125</v>
+        <v>48522</v>
       </c>
       <c r="O251" t="n">
-        <v>400306.5</v>
+        <v>388176</v>
       </c>
       <c r="P251" t="n">
         <v>77900</v>
@@ -12707,10 +12707,10 @@
         <v>130</v>
       </c>
       <c r="N275" t="n">
-        <v>8915.3355918367</v>
+        <v>8702.219999999999</v>
       </c>
       <c r="O275" t="n">
-        <v>1158993.626938771</v>
+        <v>1131288.6</v>
       </c>
       <c r="P275" t="n">
         <v>8900</v>
@@ -13124,10 +13124,10 @@
         <v>15264</v>
       </c>
       <c r="N284" t="n">
-        <v>703.7947715550901</v>
+        <v>704.67584580877</v>
       </c>
       <c r="O284" t="n">
-        <v>10742723.3930169</v>
+        <v>10756172.11042506</v>
       </c>
       <c r="P284" t="n">
         <v>900</v>
@@ -14318,10 +14318,10 @@
         <v>158</v>
       </c>
       <c r="N309" t="n">
-        <v>4593.1990728477</v>
+        <v>4578.04</v>
       </c>
       <c r="O309" t="n">
-        <v>725725.4535099367</v>
+        <v>723330.3199999999</v>
       </c>
       <c r="P309" t="n">
         <v>7500</v>
@@ -15488,10 +15488,10 @@
         <v>347</v>
       </c>
       <c r="N334" t="n">
-        <v>2655.5149832776</v>
+        <v>2644.9</v>
       </c>
       <c r="O334" t="n">
-        <v>921463.6991973273</v>
+        <v>917780.3</v>
       </c>
       <c r="P334" t="n">
         <v>3900</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q338"/>
+  <dimension ref="A1:Q336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-18</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-19</t>
         </is>
       </c>
     </row>
@@ -720,10 +720,10 @@
         <v>376</v>
       </c>
       <c r="N8" t="n">
-        <v>3376.7464140994</v>
+        <v>3376.7464051196</v>
       </c>
       <c r="O8" t="n">
-        <v>1269656.651701374</v>
+        <v>1269656.648324969</v>
       </c>
       <c r="P8" t="n">
         <v>4500</v>
@@ -1121,10 +1121,10 @@
         <v>36</v>
       </c>
       <c r="N18" t="n">
-        <v>12357.960425532</v>
+        <v>12357.960428571</v>
       </c>
       <c r="O18" t="n">
-        <v>444886.575319152</v>
+        <v>444886.575428556</v>
       </c>
       <c r="P18" t="n">
         <v>15900</v>
@@ -2027,10 +2027,10 @@
         <v>77</v>
       </c>
       <c r="N40" t="n">
-        <v>61666.874241573</v>
+        <v>61666.874364162</v>
       </c>
       <c r="O40" t="n">
-        <v>4748349.316601121</v>
+        <v>4748349.326040474</v>
       </c>
       <c r="P40" t="n">
         <v>98900</v>
@@ -2353,7 +2353,7 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -2362,19 +2362,19 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="N48" t="n">
         <v>2570.16</v>
       </c>
       <c r="O48" t="n">
-        <v>246735.36</v>
+        <v>123367.68</v>
       </c>
       <c r="P48" t="n">
         <v>4700</v>
       </c>
       <c r="Q48" t="n">
-        <v>451200</v>
+        <v>225600</v>
       </c>
     </row>
     <row r="49">
@@ -2411,10 +2411,10 @@
         <v>55</v>
       </c>
       <c r="N49" t="n">
-        <v>4878.2859393939</v>
+        <v>4878.2859756098</v>
       </c>
       <c r="O49" t="n">
-        <v>268305.7266666645</v>
+        <v>268305.728658539</v>
       </c>
       <c r="P49" t="n">
         <v>13500</v>
@@ -2675,10 +2675,10 @@
         <v>40</v>
       </c>
       <c r="N55" t="n">
-        <v>10752.93</v>
+        <v>10899.560863636</v>
       </c>
       <c r="O55" t="n">
-        <v>430117.2</v>
+        <v>435982.43454544</v>
       </c>
       <c r="P55" t="n">
         <v>18400</v>
@@ -2888,10 +2888,10 @@
         <v>248</v>
       </c>
       <c r="N60" t="n">
-        <v>13593.35</v>
+        <v>13609.886922141</v>
       </c>
       <c r="O60" t="n">
-        <v>3371150.8</v>
+        <v>3375251.956690968</v>
       </c>
       <c r="P60" t="n">
         <v>25500</v>
@@ -3065,10 +3065,10 @@
         <v>350</v>
       </c>
       <c r="N64" t="n">
-        <v>2582.25501002</v>
+        <v>2583.5545646704</v>
       </c>
       <c r="O64" t="n">
-        <v>903789.253507</v>
+        <v>904244.0976346399</v>
       </c>
       <c r="P64" t="n">
         <v>4500</v>
@@ -3111,10 +3111,10 @@
         <v>1232</v>
       </c>
       <c r="N65" t="n">
-        <v>5216.8959455416</v>
+        <v>5216.8959284856</v>
       </c>
       <c r="O65" t="n">
-        <v>6427215.804907251</v>
+        <v>6427215.783894259</v>
       </c>
       <c r="P65" t="n">
         <v>8500</v>
@@ -3157,10 +3157,10 @@
         <v>2592</v>
       </c>
       <c r="N66" t="n">
-        <v>3158.8608386776</v>
+        <v>3160.7464443118</v>
       </c>
       <c r="O66" t="n">
-        <v>8187767.293852339</v>
+        <v>8192654.783656185</v>
       </c>
       <c r="P66" t="n">
         <v>5600</v>
@@ -3341,10 +3341,10 @@
         <v>480</v>
       </c>
       <c r="N70" t="n">
-        <v>3795.7100076161</v>
+        <v>3795.7100076176</v>
       </c>
       <c r="O70" t="n">
-        <v>1821940.803655728</v>
+        <v>1821940.803656448</v>
       </c>
       <c r="P70" t="n">
         <v>6200</v>
@@ -3520,10 +3520,10 @@
         <v>346</v>
       </c>
       <c r="N74" t="n">
-        <v>4890.9300513149</v>
+        <v>4890.9300530504</v>
       </c>
       <c r="O74" t="n">
-        <v>1692261.797754955</v>
+        <v>1692261.798355438</v>
       </c>
       <c r="P74" t="n">
         <v>8200</v>
@@ -3748,10 +3748,10 @@
         <v>216</v>
       </c>
       <c r="N79" t="n">
-        <v>3594.2531034483</v>
+        <v>3594.2530785869</v>
       </c>
       <c r="O79" t="n">
-        <v>776358.6703448328</v>
+        <v>776358.6649747704</v>
       </c>
       <c r="P79" t="n">
         <v>6500</v>
@@ -4207,10 +4207,10 @@
         <v>336</v>
       </c>
       <c r="N89" t="n">
-        <v>12422.462946776</v>
+        <v>12422.462948052</v>
       </c>
       <c r="O89" t="n">
-        <v>4173947.550116736</v>
+        <v>4173947.550545472</v>
       </c>
       <c r="P89" t="n">
         <v>19900</v>
@@ -4299,10 +4299,10 @@
         <v>1800</v>
       </c>
       <c r="N91" t="n">
-        <v>3472.2761773616</v>
+        <v>3472.2761978447</v>
       </c>
       <c r="O91" t="n">
-        <v>6250097.11925088</v>
+        <v>6250097.15612046</v>
       </c>
       <c r="P91" t="n">
         <v>5900</v>
@@ -4389,10 +4389,10 @@
         <v>1356</v>
       </c>
       <c r="N93" t="n">
-        <v>4371.1712626125</v>
+        <v>4372.0654674395</v>
       </c>
       <c r="O93" t="n">
-        <v>5927308.23210255</v>
+        <v>5928520.773847962</v>
       </c>
       <c r="P93" t="n">
         <v>8900</v>
@@ -5753,10 +5753,10 @@
         <v>352</v>
       </c>
       <c r="N123" t="n">
-        <v>8794.48</v>
+        <v>8799.4655328798</v>
       </c>
       <c r="O123" t="n">
-        <v>3095656.96</v>
+        <v>3097411.86757369</v>
       </c>
       <c r="P123" t="n">
         <v>14500</v>
@@ -5835,10 +5835,10 @@
         <v>528</v>
       </c>
       <c r="N125" t="n">
-        <v>22485.695471698</v>
+        <v>22485.695454545</v>
       </c>
       <c r="O125" t="n">
-        <v>11872447.20905654</v>
+        <v>11872447.19999976</v>
       </c>
       <c r="P125" t="n">
         <v>36500</v>
@@ -6145,10 +6145,10 @@
         <v>18</v>
       </c>
       <c r="N132" t="n">
-        <v>56503</v>
+        <v>57801.91954023</v>
       </c>
       <c r="O132" t="n">
-        <v>1017054</v>
+        <v>1040434.55172414</v>
       </c>
       <c r="P132" t="n">
         <v>90500</v>
@@ -6286,10 +6286,10 @@
         <v>36</v>
       </c>
       <c r="N135" t="n">
-        <v>4285.1962793572</v>
+        <v>4285.1963341646</v>
       </c>
       <c r="O135" t="n">
-        <v>154267.0660568592</v>
+        <v>154267.0680299256</v>
       </c>
       <c r="P135" t="n">
         <v>6900</v>
@@ -6460,10 +6460,10 @@
         <v>948</v>
       </c>
       <c r="N139" t="n">
-        <v>4814.2679265446</v>
+        <v>4814.2679260066</v>
       </c>
       <c r="O139" t="n">
-        <v>4563925.994364281</v>
+        <v>4563925.993854256</v>
       </c>
       <c r="P139" t="n">
         <v>9900</v>
@@ -6772,10 +6772,10 @@
         <v>273</v>
       </c>
       <c r="N146" t="n">
-        <v>22730.48</v>
+        <v>22761.155411606</v>
       </c>
       <c r="O146" t="n">
-        <v>6205421.04</v>
+        <v>6213795.427368438</v>
       </c>
       <c r="P146" t="n">
         <v>36900</v>
@@ -7002,10 +7002,10 @@
         <v>148</v>
       </c>
       <c r="N151" t="n">
-        <v>5431.12</v>
+        <v>5455.0456387665</v>
       </c>
       <c r="O151" t="n">
-        <v>803805.76</v>
+        <v>807346.754537442</v>
       </c>
       <c r="P151" t="n">
         <v>8900</v>
@@ -7777,10 +7777,10 @@
         <v>680</v>
       </c>
       <c r="N168" t="n">
-        <v>1778.4728179471</v>
+        <v>1778.4728348758</v>
       </c>
       <c r="O168" t="n">
-        <v>1209361.516204028</v>
+        <v>1209361.527715544</v>
       </c>
       <c r="P168" t="n">
         <v>4900</v>
@@ -7869,10 +7869,10 @@
         <v>421</v>
       </c>
       <c r="N170" t="n">
-        <v>18016</v>
+        <v>18023.2064</v>
       </c>
       <c r="O170" t="n">
-        <v>7584736</v>
+        <v>7587769.8944</v>
       </c>
       <c r="P170" t="n">
         <v>29900</v>
@@ -8470,10 +8470,10 @@
         <v>210</v>
       </c>
       <c r="N183" t="n">
-        <v>10411</v>
+        <v>10448.584837545</v>
       </c>
       <c r="O183" t="n">
-        <v>2186310</v>
+        <v>2194202.81588445</v>
       </c>
       <c r="P183" t="n">
         <v>16900</v>
@@ -9194,7 +9194,7 @@
         </is>
       </c>
       <c r="J199" t="n">
-        <v>502</v>
+        <v>460</v>
       </c>
       <c r="K199" t="n">
         <v>0</v>
@@ -9203,19 +9203,19 @@
         <v>0</v>
       </c>
       <c r="M199" t="n">
-        <v>502</v>
+        <v>460</v>
       </c>
       <c r="N199" t="n">
         <v>13210</v>
       </c>
       <c r="O199" t="n">
-        <v>6631420</v>
+        <v>6076600</v>
       </c>
       <c r="P199" t="n">
         <v>23900</v>
       </c>
       <c r="Q199" t="n">
-        <v>11997800</v>
+        <v>10994000</v>
       </c>
     </row>
     <row r="200">
@@ -9298,10 +9298,10 @@
         <v>129</v>
       </c>
       <c r="N201" t="n">
-        <v>3903.7391411043</v>
+        <v>3903.7392422907</v>
       </c>
       <c r="O201" t="n">
-        <v>503582.3492024547</v>
+        <v>503582.3622555003</v>
       </c>
       <c r="P201" t="n">
         <v>7500</v>
@@ -9690,7 +9690,7 @@
         </is>
       </c>
       <c r="J210" t="n">
-        <v>443</v>
+        <v>307</v>
       </c>
       <c r="K210" t="n">
         <v>0</v>
@@ -9699,19 +9699,19 @@
         <v>0</v>
       </c>
       <c r="M210" t="n">
-        <v>443</v>
+        <v>307</v>
       </c>
       <c r="N210" t="n">
         <v>6849.2</v>
       </c>
       <c r="O210" t="n">
-        <v>3034195.6</v>
+        <v>2102704.4</v>
       </c>
       <c r="P210" t="n">
         <v>11500</v>
       </c>
       <c r="Q210" t="n">
-        <v>5094500</v>
+        <v>3530500</v>
       </c>
     </row>
     <row r="211">
@@ -9966,7 +9966,7 @@
         </is>
       </c>
       <c r="J216" t="n">
-        <v>153</v>
+        <v>105</v>
       </c>
       <c r="K216" t="n">
         <v>0</v>
@@ -9975,19 +9975,19 @@
         <v>0</v>
       </c>
       <c r="M216" t="n">
-        <v>153</v>
+        <v>105</v>
       </c>
       <c r="N216" t="n">
         <v>7562</v>
       </c>
       <c r="O216" t="n">
-        <v>1156986</v>
+        <v>794010</v>
       </c>
       <c r="P216" t="n">
         <v>12900</v>
       </c>
       <c r="Q216" t="n">
-        <v>1973700</v>
+        <v>1354500</v>
       </c>
     </row>
     <row r="217">
@@ -11008,12 +11008,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>C4600</t>
+          <t>C4601</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>SET PERRITO PATROL BUS C4600</t>
+          <t>SET PERRO PATROL C4601</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -11027,7 +11027,7 @@
         </is>
       </c>
       <c r="J239" t="n">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="K239" t="n">
         <v>0</v>
@@ -11036,30 +11036,30 @@
         <v>0</v>
       </c>
       <c r="M239" t="n">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="N239" t="n">
-        <v>16282</v>
+        <v>14050</v>
       </c>
       <c r="O239" t="n">
-        <v>732690</v>
+        <v>1095900</v>
       </c>
       <c r="P239" t="n">
-        <v>27900</v>
+        <v>23900</v>
       </c>
       <c r="Q239" t="n">
-        <v>1255500</v>
+        <v>1864200</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>C4601</t>
+          <t>C4602</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>SET PERRO PATROL C4601</t>
+          <t>AVION CON PISTA MODELOS STD C4602</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -11073,7 +11073,7 @@
         </is>
       </c>
       <c r="J240" t="n">
-        <v>78</v>
+        <v>285</v>
       </c>
       <c r="K240" t="n">
         <v>0</v>
@@ -11082,30 +11082,30 @@
         <v>0</v>
       </c>
       <c r="M240" t="n">
-        <v>78</v>
+        <v>285</v>
       </c>
       <c r="N240" t="n">
-        <v>14050</v>
+        <v>8700</v>
       </c>
       <c r="O240" t="n">
-        <v>1095900</v>
+        <v>2479500</v>
       </c>
       <c r="P240" t="n">
-        <v>23900</v>
+        <v>14900</v>
       </c>
       <c r="Q240" t="n">
-        <v>1864200</v>
+        <v>4246500</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>C4602</t>
+          <t>C4603</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>AVION CON PISTA MODELOS STD C4602</t>
+          <t>MAQUILLAJE BLISTER SENCILLO C4603</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -11119,7 +11119,7 @@
         </is>
       </c>
       <c r="J241" t="n">
-        <v>285</v>
+        <v>385</v>
       </c>
       <c r="K241" t="n">
         <v>0</v>
@@ -11128,30 +11128,30 @@
         <v>0</v>
       </c>
       <c r="M241" t="n">
-        <v>285</v>
+        <v>385</v>
       </c>
       <c r="N241" t="n">
-        <v>8700</v>
+        <v>3652.664695122</v>
       </c>
       <c r="O241" t="n">
-        <v>2479500</v>
+        <v>1406275.90762197</v>
       </c>
       <c r="P241" t="n">
-        <v>14900</v>
+        <v>7500</v>
       </c>
       <c r="Q241" t="n">
-        <v>4246500</v>
+        <v>2887500</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>C4603</t>
+          <t>C4604</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>MAQUILLAJE BLISTER SENCILLO C4603</t>
+          <t>MQUILLAJE BLISTER MODELOS STDS C4604</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -11165,7 +11165,7 @@
         </is>
       </c>
       <c r="J242" t="n">
-        <v>385</v>
+        <v>1709</v>
       </c>
       <c r="K242" t="n">
         <v>0</v>
@@ -11174,30 +11174,30 @@
         <v>0</v>
       </c>
       <c r="M242" t="n">
-        <v>385</v>
+        <v>1709</v>
       </c>
       <c r="N242" t="n">
-        <v>3639.35</v>
+        <v>1326</v>
       </c>
       <c r="O242" t="n">
-        <v>1401149.75</v>
+        <v>2266134</v>
       </c>
       <c r="P242" t="n">
-        <v>7500</v>
+        <v>2500</v>
       </c>
       <c r="Q242" t="n">
-        <v>2887500</v>
+        <v>4272500</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>C4604</t>
+          <t>C4605</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>MQUILLAJE BLISTER MODELOS STDS C4604</t>
+          <t>MAQUILLAJE BLISTER  CORAZON C4605</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -11211,7 +11211,7 @@
         </is>
       </c>
       <c r="J243" t="n">
-        <v>1709</v>
+        <v>176</v>
       </c>
       <c r="K243" t="n">
         <v>0</v>
@@ -11220,30 +11220,30 @@
         <v>0</v>
       </c>
       <c r="M243" t="n">
-        <v>1709</v>
+        <v>176</v>
       </c>
       <c r="N243" t="n">
-        <v>1326</v>
+        <v>5640</v>
       </c>
       <c r="O243" t="n">
-        <v>2266134</v>
+        <v>992640</v>
       </c>
       <c r="P243" t="n">
-        <v>2500</v>
+        <v>9900</v>
       </c>
       <c r="Q243" t="n">
-        <v>4272500</v>
+        <v>1742400</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>C4605</t>
+          <t>C4606</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>MAQUILLAJE BLISTER  CORAZON C4605</t>
+          <t>SONAJERO EN CAJA 6PCS C4606</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -11257,7 +11257,7 @@
         </is>
       </c>
       <c r="J244" t="n">
-        <v>176</v>
+        <v>279</v>
       </c>
       <c r="K244" t="n">
         <v>0</v>
@@ -11266,30 +11266,30 @@
         <v>0</v>
       </c>
       <c r="M244" t="n">
-        <v>176</v>
+        <v>279</v>
       </c>
       <c r="N244" t="n">
-        <v>5640</v>
+        <v>10713.21</v>
       </c>
       <c r="O244" t="n">
-        <v>992640</v>
+        <v>2988985.59</v>
       </c>
       <c r="P244" t="n">
-        <v>9900</v>
+        <v>20900</v>
       </c>
       <c r="Q244" t="n">
-        <v>1742400</v>
+        <v>5831100</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>C4606</t>
+          <t>C4607</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>SONAJERO EN CAJA 6PCS C4606</t>
+          <t>MAQUILLAJE SIRENA C4607</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -11303,7 +11303,7 @@
         </is>
       </c>
       <c r="J245" t="n">
-        <v>279</v>
+        <v>159</v>
       </c>
       <c r="K245" t="n">
         <v>0</v>
@@ -11312,30 +11312,30 @@
         <v>0</v>
       </c>
       <c r="M245" t="n">
-        <v>279</v>
+        <v>159</v>
       </c>
       <c r="N245" t="n">
-        <v>10713.21</v>
+        <v>10817</v>
       </c>
       <c r="O245" t="n">
-        <v>2988985.59</v>
+        <v>1719903</v>
       </c>
       <c r="P245" t="n">
-        <v>20900</v>
+        <v>17900</v>
       </c>
       <c r="Q245" t="n">
-        <v>5831100</v>
+        <v>2846100</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>C4607</t>
+          <t>C4609</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>MAQUILLAJE SIRENA C4607</t>
+          <t>MAQUILLAJE UNICORNIO C4609</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -11349,7 +11349,7 @@
         </is>
       </c>
       <c r="J246" t="n">
-        <v>159</v>
+        <v>79</v>
       </c>
       <c r="K246" t="n">
         <v>0</v>
@@ -11358,30 +11358,30 @@
         <v>0</v>
       </c>
       <c r="M246" t="n">
-        <v>159</v>
+        <v>79</v>
       </c>
       <c r="N246" t="n">
-        <v>10817</v>
+        <v>12489</v>
       </c>
       <c r="O246" t="n">
-        <v>1719903</v>
+        <v>986631</v>
       </c>
       <c r="P246" t="n">
-        <v>17900</v>
+        <v>20900</v>
       </c>
       <c r="Q246" t="n">
-        <v>2846100</v>
+        <v>1651100</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>C4609</t>
+          <t>C4612</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>MAQUILLAJE UNICORNIO C4609</t>
+          <t>CARRUAJE MUÑECA C4612</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -11395,7 +11395,7 @@
         </is>
       </c>
       <c r="J247" t="n">
-        <v>79</v>
+        <v>166</v>
       </c>
       <c r="K247" t="n">
         <v>0</v>
@@ -11404,30 +11404,30 @@
         <v>0</v>
       </c>
       <c r="M247" t="n">
-        <v>79</v>
+        <v>166</v>
       </c>
       <c r="N247" t="n">
-        <v>12489</v>
+        <v>21762</v>
       </c>
       <c r="O247" t="n">
-        <v>986631</v>
+        <v>3612492</v>
       </c>
       <c r="P247" t="n">
-        <v>20900</v>
+        <v>35900</v>
       </c>
       <c r="Q247" t="n">
-        <v>1651100</v>
+        <v>5959400</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>C4612</t>
+          <t>C4613</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>CARRUAJE MUÑECA C4612</t>
+          <t>DIDACTICOS ARMABLES STD C4613</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -11441,7 +11441,7 @@
         </is>
       </c>
       <c r="J248" t="n">
-        <v>181</v>
+        <v>934</v>
       </c>
       <c r="K248" t="n">
         <v>0</v>
@@ -11450,30 +11450,30 @@
         <v>0</v>
       </c>
       <c r="M248" t="n">
-        <v>181</v>
+        <v>934</v>
       </c>
       <c r="N248" t="n">
-        <v>21762</v>
+        <v>3821</v>
       </c>
       <c r="O248" t="n">
-        <v>3938922</v>
+        <v>3568814</v>
       </c>
       <c r="P248" t="n">
-        <v>35900</v>
+        <v>5900</v>
       </c>
       <c r="Q248" t="n">
-        <v>6497900</v>
+        <v>5510600</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>C4613</t>
+          <t>C4614</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>DIDACTICOS ARMABLES STD C4613</t>
+          <t>CASTILLO NIÑA C4614</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -11487,7 +11487,7 @@
         </is>
       </c>
       <c r="J249" t="n">
-        <v>934</v>
+        <v>144</v>
       </c>
       <c r="K249" t="n">
         <v>0</v>
@@ -11496,30 +11496,30 @@
         <v>0</v>
       </c>
       <c r="M249" t="n">
-        <v>934</v>
+        <v>144</v>
       </c>
       <c r="N249" t="n">
-        <v>3821</v>
+        <v>15472</v>
       </c>
       <c r="O249" t="n">
-        <v>3568814</v>
+        <v>2227968</v>
       </c>
       <c r="P249" t="n">
-        <v>5900</v>
+        <v>25900</v>
       </c>
       <c r="Q249" t="n">
-        <v>5510600</v>
+        <v>3729600</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>C4614</t>
+          <t>C4616</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>CASTILLO NIÑA C4614</t>
+          <t>CARRO TRANSFORME AMARILLO RECARGABLE C4616</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -11533,7 +11533,7 @@
         </is>
       </c>
       <c r="J250" t="n">
-        <v>144</v>
+        <v>8</v>
       </c>
       <c r="K250" t="n">
         <v>0</v>
@@ -11542,30 +11542,30 @@
         <v>0</v>
       </c>
       <c r="M250" t="n">
-        <v>144</v>
+        <v>8</v>
       </c>
       <c r="N250" t="n">
-        <v>15472</v>
+        <v>48522</v>
       </c>
       <c r="O250" t="n">
-        <v>2227968</v>
+        <v>388176</v>
       </c>
       <c r="P250" t="n">
-        <v>25900</v>
+        <v>77900</v>
       </c>
       <c r="Q250" t="n">
-        <v>3729600</v>
+        <v>623200</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>C4616</t>
+          <t>C4622</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>CARRO TRANSFORME AMARILLO RECARGABLE C4616</t>
+          <t>CARRO COLECCION X8 C4622</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -11579,7 +11579,7 @@
         </is>
       </c>
       <c r="J251" t="n">
-        <v>8</v>
+        <v>240</v>
       </c>
       <c r="K251" t="n">
         <v>0</v>
@@ -11588,30 +11588,30 @@
         <v>0</v>
       </c>
       <c r="M251" t="n">
-        <v>8</v>
+        <v>240</v>
       </c>
       <c r="N251" t="n">
-        <v>48522</v>
+        <v>5476</v>
       </c>
       <c r="O251" t="n">
-        <v>388176</v>
+        <v>1314240</v>
       </c>
       <c r="P251" t="n">
-        <v>77900</v>
+        <v>8900</v>
       </c>
       <c r="Q251" t="n">
-        <v>623200</v>
+        <v>2136000</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>C4622</t>
+          <t>C4629</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>CARRO COLECCION X8 C4622</t>
+          <t>COMPUTADOR USB CABLE C4629</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -11625,7 +11625,7 @@
         </is>
       </c>
       <c r="J252" t="n">
-        <v>240</v>
+        <v>36</v>
       </c>
       <c r="K252" t="n">
         <v>0</v>
@@ -11634,30 +11634,30 @@
         <v>0</v>
       </c>
       <c r="M252" t="n">
-        <v>240</v>
+        <v>36</v>
       </c>
       <c r="N252" t="n">
-        <v>5476</v>
+        <v>64612</v>
       </c>
       <c r="O252" t="n">
-        <v>1314240</v>
+        <v>2326032</v>
       </c>
       <c r="P252" t="n">
-        <v>8900</v>
+        <v>103900</v>
       </c>
       <c r="Q252" t="n">
-        <v>2136000</v>
+        <v>3740400</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>C4629</t>
+          <t>C4630</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>COMPUTADOR USB CABLE C4629</t>
+          <t>COMPUTADOR USB INGLES/ESPAÑOL C4630</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="J253" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="K253" t="n">
         <v>0</v>
@@ -11680,30 +11680,30 @@
         <v>0</v>
       </c>
       <c r="M253" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="N253" t="n">
-        <v>64612</v>
+        <v>38252</v>
       </c>
       <c r="O253" t="n">
-        <v>2326032</v>
+        <v>2142112</v>
       </c>
       <c r="P253" t="n">
-        <v>103900</v>
+        <v>61900</v>
       </c>
       <c r="Q253" t="n">
-        <v>3740400</v>
+        <v>3466400</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>C4630</t>
+          <t>C4631</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>COMPUTADOR USB INGLES/ESPAÑOL C4630</t>
+          <t>SQUISHY MOSTRICO STD C4631</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -11717,7 +11717,7 @@
         </is>
       </c>
       <c r="J254" t="n">
-        <v>56</v>
+        <v>864</v>
       </c>
       <c r="K254" t="n">
         <v>0</v>
@@ -11726,30 +11726,30 @@
         <v>0</v>
       </c>
       <c r="M254" t="n">
-        <v>56</v>
+        <v>864</v>
       </c>
       <c r="N254" t="n">
-        <v>38252</v>
+        <v>1516.0387397625</v>
       </c>
       <c r="O254" t="n">
-        <v>2142112</v>
+        <v>1309857.4711548</v>
       </c>
       <c r="P254" t="n">
-        <v>61900</v>
+        <v>2300</v>
       </c>
       <c r="Q254" t="n">
-        <v>3466400</v>
+        <v>1987200</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>C4631</t>
+          <t>C466-IO</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>SQUISHY MOSTRICO STD C4631</t>
+          <t>GLOBO FIGURAS TORNASOL Y MATE</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -11763,7 +11763,7 @@
         </is>
       </c>
       <c r="J255" t="n">
-        <v>864</v>
+        <v>1050</v>
       </c>
       <c r="K255" t="n">
         <v>0</v>
@@ -11772,30 +11772,30 @@
         <v>0</v>
       </c>
       <c r="M255" t="n">
-        <v>864</v>
+        <v>1050</v>
       </c>
       <c r="N255" t="n">
-        <v>1516.0387429797</v>
+        <v>356.78</v>
       </c>
       <c r="O255" t="n">
-        <v>1309857.473934461</v>
+        <v>374619</v>
       </c>
       <c r="P255" t="n">
-        <v>2300</v>
+        <v>300</v>
       </c>
       <c r="Q255" t="n">
-        <v>1987200</v>
+        <v>315000</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>C466-IO</t>
+          <t>C4728</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>GLOBO FIGURAS TORNASOL Y MATE</t>
+          <t>FLIOTADOR DONA DINOSAURIO #60 C4728</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -11809,7 +11809,7 @@
         </is>
       </c>
       <c r="J256" t="n">
-        <v>1050</v>
+        <v>550</v>
       </c>
       <c r="K256" t="n">
         <v>0</v>
@@ -11818,44 +11818,42 @@
         <v>0</v>
       </c>
       <c r="M256" t="n">
-        <v>1050</v>
+        <v>550</v>
       </c>
       <c r="N256" t="n">
-        <v>356.78</v>
+        <v>2454</v>
       </c>
       <c r="O256" t="n">
-        <v>374619</v>
+        <v>1349700</v>
       </c>
       <c r="P256" t="n">
-        <v>300</v>
+        <v>4200</v>
       </c>
       <c r="Q256" t="n">
-        <v>315000</v>
+        <v>2310000</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>C4728</t>
-        </is>
+          <t>C476</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>6932001041468</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>FLIOTADOR DONA DINOSAURIO #60 C4728</t>
-        </is>
-      </c>
-      <c r="E257" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>YENGA MADERA GRABDE</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J257" t="n">
-        <v>550</v>
+        <v>54</v>
       </c>
       <c r="K257" t="n">
         <v>0</v>
@@ -11864,42 +11862,44 @@
         <v>0</v>
       </c>
       <c r="M257" t="n">
-        <v>550</v>
+        <v>54</v>
       </c>
       <c r="N257" t="n">
-        <v>2454</v>
+        <v>5347.73</v>
       </c>
       <c r="O257" t="n">
-        <v>1349700</v>
+        <v>288777.42</v>
       </c>
       <c r="P257" t="n">
-        <v>4200</v>
+        <v>9500</v>
       </c>
       <c r="Q257" t="n">
-        <v>2310000</v>
+        <v>513000</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>C476</t>
-        </is>
-      </c>
-      <c r="B258" t="n">
-        <v>6932001041468</v>
+          <t>C4812</t>
+        </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>YENGA MADERA GRABDE</t>
+          <t>BURBUJERO DE ESPADA 44cm</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J258" t="n">
-        <v>54</v>
+        <v>4464</v>
       </c>
       <c r="K258" t="n">
         <v>0</v>
@@ -11908,30 +11908,30 @@
         <v>0</v>
       </c>
       <c r="M258" t="n">
-        <v>54</v>
+        <v>4464</v>
       </c>
       <c r="N258" t="n">
-        <v>5347.73</v>
+        <v>1801</v>
       </c>
       <c r="O258" t="n">
-        <v>288777.42</v>
+        <v>8039664</v>
       </c>
       <c r="P258" t="n">
-        <v>9500</v>
+        <v>2900</v>
       </c>
       <c r="Q258" t="n">
-        <v>513000</v>
+        <v>12945600</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>C4812</t>
+          <t>C494-IO</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>BURBUJERO DE ESPADA 44cm</t>
+          <t>GLOBO METALIZADO DULCES</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -11945,7 +11945,7 @@
         </is>
       </c>
       <c r="J259" t="n">
-        <v>4464</v>
+        <v>1352</v>
       </c>
       <c r="K259" t="n">
         <v>0</v>
@@ -11954,30 +11954,33 @@
         <v>0</v>
       </c>
       <c r="M259" t="n">
-        <v>4464</v>
+        <v>1352</v>
       </c>
       <c r="N259" t="n">
-        <v>1801</v>
+        <v>1200</v>
       </c>
       <c r="O259" t="n">
-        <v>8039664</v>
+        <v>1622400</v>
       </c>
       <c r="P259" t="n">
-        <v>2900</v>
+        <v>1500</v>
       </c>
       <c r="Q259" t="n">
-        <v>12945600</v>
+        <v>2028000</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>C494-IO</t>
-        </is>
+          <t>C4945</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>7700154271143</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>GLOBO METALIZADO DULCES</t>
+          <t>MUÑECA CON MASCOTA Y COCHE C4945</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -11991,7 +11994,7 @@
         </is>
       </c>
       <c r="J260" t="n">
-        <v>1352</v>
+        <v>432</v>
       </c>
       <c r="K260" t="n">
         <v>0</v>
@@ -12000,25 +12003,25 @@
         <v>0</v>
       </c>
       <c r="M260" t="n">
-        <v>1352</v>
+        <v>432</v>
       </c>
       <c r="N260" t="n">
-        <v>1200</v>
+        <v>11690</v>
       </c>
       <c r="O260" t="n">
-        <v>1622400</v>
+        <v>5050080</v>
       </c>
       <c r="P260" t="n">
-        <v>1500</v>
+        <v>18900</v>
       </c>
       <c r="Q260" t="n">
-        <v>2028000</v>
+        <v>8164800</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>C4945</t>
+          <t>C4946</t>
         </is>
       </c>
       <c r="B261" t="n">
@@ -12026,7 +12029,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>MUÑECA CON MASCOTA Y COCHE C4945</t>
+          <t>MUÑECA CON ODONTOLOGIA C4946</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -12040,7 +12043,7 @@
         </is>
       </c>
       <c r="J261" t="n">
-        <v>432</v>
+        <v>360</v>
       </c>
       <c r="K261" t="n">
         <v>0</v>
@@ -12049,25 +12052,25 @@
         <v>0</v>
       </c>
       <c r="M261" t="n">
-        <v>432</v>
+        <v>360</v>
       </c>
       <c r="N261" t="n">
-        <v>11690</v>
+        <v>13518</v>
       </c>
       <c r="O261" t="n">
-        <v>5050080</v>
+        <v>4866480</v>
       </c>
       <c r="P261" t="n">
-        <v>18900</v>
+        <v>21900</v>
       </c>
       <c r="Q261" t="n">
-        <v>8164800</v>
+        <v>7884000</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>C4946</t>
+          <t>C4947</t>
         </is>
       </c>
       <c r="B262" t="n">
@@ -12075,7 +12078,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>MUÑECA CON ODONTOLOGIA C4946</t>
+          <t>MUÑECA CON MASCOTAS   C4947</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -12089,7 +12092,7 @@
         </is>
       </c>
       <c r="J262" t="n">
-        <v>360</v>
+        <v>432</v>
       </c>
       <c r="K262" t="n">
         <v>0</v>
@@ -12098,25 +12101,25 @@
         <v>0</v>
       </c>
       <c r="M262" t="n">
-        <v>360</v>
+        <v>432</v>
       </c>
       <c r="N262" t="n">
-        <v>13518</v>
+        <v>9736</v>
       </c>
       <c r="O262" t="n">
-        <v>4866480</v>
+        <v>4205952</v>
       </c>
       <c r="P262" t="n">
-        <v>21900</v>
+        <v>15900</v>
       </c>
       <c r="Q262" t="n">
-        <v>7884000</v>
+        <v>6868800</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>C4947</t>
+          <t>C4958</t>
         </is>
       </c>
       <c r="B263" t="n">
@@ -12124,7 +12127,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>MUÑECA CON MASCOTAS   C4947</t>
+          <t>MUÑECA PATINADORA CONTROL REMOTO</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -12138,7 +12141,7 @@
         </is>
       </c>
       <c r="J263" t="n">
-        <v>432</v>
+        <v>24</v>
       </c>
       <c r="K263" t="n">
         <v>0</v>
@@ -12147,25 +12150,25 @@
         <v>0</v>
       </c>
       <c r="M263" t="n">
-        <v>432</v>
+        <v>24</v>
       </c>
       <c r="N263" t="n">
-        <v>9736</v>
+        <v>44470</v>
       </c>
       <c r="O263" t="n">
-        <v>4205952</v>
+        <v>1067280</v>
       </c>
       <c r="P263" t="n">
-        <v>15900</v>
+        <v>71900</v>
       </c>
       <c r="Q263" t="n">
-        <v>6868800</v>
+        <v>1725600</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>C4958</t>
+          <t>C4959</t>
         </is>
       </c>
       <c r="B264" t="n">
@@ -12173,7 +12176,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>MUÑECA PATINADORA CONTROL REMOTO</t>
+          <t>MUÑECA POP ACCESORIOS C4959</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -12187,7 +12190,7 @@
         </is>
       </c>
       <c r="J264" t="n">
-        <v>36</v>
+        <v>684</v>
       </c>
       <c r="K264" t="n">
         <v>0</v>
@@ -12196,47 +12199,42 @@
         <v>0</v>
       </c>
       <c r="M264" t="n">
-        <v>36</v>
+        <v>684</v>
       </c>
       <c r="N264" t="n">
-        <v>44470</v>
+        <v>5215</v>
       </c>
       <c r="O264" t="n">
-        <v>1600920</v>
+        <v>3567060</v>
       </c>
       <c r="P264" t="n">
-        <v>71900</v>
+        <v>8900</v>
       </c>
       <c r="Q264" t="n">
-        <v>2588400</v>
+        <v>6087600</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>C4959</t>
+          <t>C502</t>
         </is>
       </c>
       <c r="B265" t="n">
-        <v>7700154271143</v>
+        <v>6952216485215</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>MUÑECA POP ACCESORIOS C4959</t>
-        </is>
-      </c>
-      <c r="E265" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>C502 MUNECA NANCY GRANDE</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J265" t="n">
-        <v>684</v>
+        <v>55</v>
       </c>
       <c r="K265" t="n">
         <v>0</v>
@@ -12245,42 +12243,47 @@
         <v>0</v>
       </c>
       <c r="M265" t="n">
-        <v>684</v>
+        <v>55</v>
       </c>
       <c r="N265" t="n">
-        <v>5215</v>
+        <v>15423.36</v>
       </c>
       <c r="O265" t="n">
-        <v>3567060</v>
+        <v>848284.8</v>
       </c>
       <c r="P265" t="n">
-        <v>8900</v>
+        <v>24900</v>
       </c>
       <c r="Q265" t="n">
-        <v>6087600</v>
+        <v>1369500</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>C502</t>
+          <t>C5030</t>
         </is>
       </c>
       <c r="B266" t="n">
-        <v>6952216485215</v>
+        <v>6999899236062</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>C502 MUNECA NANCY GRANDE</t>
+          <t>INFLABLE DONA LLANTA C5030</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>INFLABLES</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J266" t="n">
-        <v>55</v>
+        <v>121</v>
       </c>
       <c r="K266" t="n">
         <v>0</v>
@@ -12289,33 +12292,33 @@
         <v>0</v>
       </c>
       <c r="M266" t="n">
-        <v>55</v>
+        <v>121</v>
       </c>
       <c r="N266" t="n">
-        <v>15423.36</v>
+        <v>2857.22</v>
       </c>
       <c r="O266" t="n">
-        <v>848284.8</v>
+        <v>345723.62</v>
       </c>
       <c r="P266" t="n">
-        <v>24900</v>
+        <v>4900</v>
       </c>
       <c r="Q266" t="n">
-        <v>1369500</v>
+        <v>592900</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>C5030</t>
+          <t>C5032</t>
         </is>
       </c>
       <c r="B267" t="n">
-        <v>6999899236062</v>
+        <v>6999899236154</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>INFLABLE DONA LLANTA C5030</t>
+          <t>INFLABLE TECHITO PIECITOS  FIGURAS STD C5032</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -12329,7 +12332,7 @@
         </is>
       </c>
       <c r="J267" t="n">
-        <v>121</v>
+        <v>534</v>
       </c>
       <c r="K267" t="n">
         <v>0</v>
@@ -12338,47 +12341,42 @@
         <v>0</v>
       </c>
       <c r="M267" t="n">
-        <v>121</v>
+        <v>534</v>
       </c>
       <c r="N267" t="n">
-        <v>2857.22</v>
+        <v>8945.379999999999</v>
       </c>
       <c r="O267" t="n">
-        <v>345723.62</v>
+        <v>4776832.92</v>
       </c>
       <c r="P267" t="n">
-        <v>4900</v>
+        <v>14900</v>
       </c>
       <c r="Q267" t="n">
-        <v>592900</v>
+        <v>7956600</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>C5032</t>
+          <t>C506</t>
         </is>
       </c>
       <c r="B268" t="n">
-        <v>6999899236154</v>
+        <v>6952365180054</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>INFLABLE TECHITO PIECITOS  FIGURAS STD C5032</t>
-        </is>
-      </c>
-      <c r="E268" t="inlineStr">
-        <is>
-          <t>INFLABLES</t>
+          <t>GLOBO BURBUJA 30</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J268" t="n">
-        <v>534</v>
+        <v>3650</v>
       </c>
       <c r="K268" t="n">
         <v>0</v>
@@ -12387,42 +12385,44 @@
         <v>0</v>
       </c>
       <c r="M268" t="n">
-        <v>534</v>
+        <v>3650</v>
       </c>
       <c r="N268" t="n">
-        <v>8945.379999999999</v>
+        <v>675.2255375485</v>
       </c>
       <c r="O268" t="n">
-        <v>4776832.92</v>
+        <v>2464573.212052025</v>
       </c>
       <c r="P268" t="n">
-        <v>14900</v>
+        <v>1300</v>
       </c>
       <c r="Q268" t="n">
-        <v>7956600</v>
+        <v>4745000</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>C506</t>
-        </is>
-      </c>
-      <c r="B269" t="n">
-        <v>6952365180054</v>
+          <t>C510-IO</t>
+        </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>GLOBO BURBUJA 30</t>
+          <t>GLOBO BURBUJA METALIZADO</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>GLOBOS</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J269" t="n">
-        <v>3650</v>
+        <v>3896</v>
       </c>
       <c r="K269" t="n">
         <v>0</v>
@@ -12431,44 +12431,42 @@
         <v>0</v>
       </c>
       <c r="M269" t="n">
-        <v>3650</v>
+        <v>3896</v>
       </c>
       <c r="N269" t="n">
-        <v>675.2255375485</v>
+        <v>960</v>
       </c>
       <c r="O269" t="n">
-        <v>2464573.212052025</v>
+        <v>3740160</v>
       </c>
       <c r="P269" t="n">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="Q269" t="n">
-        <v>4745000</v>
+        <v>4675200</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>C510-IO</t>
-        </is>
+          <t>C515</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>6953626330010</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>GLOBO BURBUJA METALIZADO</t>
-        </is>
-      </c>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>GLOBOS</t>
+          <t>GLOBO FIGURAS BURBUJA</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J270" t="n">
-        <v>3896</v>
+        <v>3800</v>
       </c>
       <c r="K270" t="n">
         <v>0</v>
@@ -12477,42 +12475,44 @@
         <v>0</v>
       </c>
       <c r="M270" t="n">
-        <v>3896</v>
+        <v>3800</v>
       </c>
       <c r="N270" t="n">
-        <v>960</v>
+        <v>583.7204926325001</v>
       </c>
       <c r="O270" t="n">
-        <v>3740160</v>
+        <v>2218137.8720035</v>
       </c>
       <c r="P270" t="n">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="Q270" t="n">
-        <v>4675200</v>
+        <v>2280000</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>C515</t>
-        </is>
-      </c>
-      <c r="B271" t="n">
-        <v>6953626330010</v>
+          <t>C5214</t>
+        </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>GLOBO FIGURAS BURBUJA</t>
+          <t>CUBO C5214</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J271" t="n">
-        <v>3800</v>
+        <v>1440</v>
       </c>
       <c r="K271" t="n">
         <v>0</v>
@@ -12521,44 +12521,42 @@
         <v>0</v>
       </c>
       <c r="M271" t="n">
-        <v>3800</v>
+        <v>1440</v>
       </c>
       <c r="N271" t="n">
-        <v>583.7204926325001</v>
+        <v>1690.8700093809</v>
       </c>
       <c r="O271" t="n">
-        <v>2218137.8720035</v>
+        <v>2434852.813508496</v>
       </c>
       <c r="P271" t="n">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="Q271" t="n">
-        <v>2280000</v>
+        <v>4320000</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>C5214</t>
-        </is>
+          <t>C523</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>6957430180212</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>CUBO C5214</t>
-        </is>
-      </c>
-      <c r="E272" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
+          <t>GLOBO NUMERO 16PLATEADO Y DORADO</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J272" t="n">
-        <v>1440</v>
+        <v>2556</v>
       </c>
       <c r="K272" t="n">
         <v>0</v>
@@ -12567,33 +12565,33 @@
         <v>0</v>
       </c>
       <c r="M272" t="n">
-        <v>1440</v>
+        <v>2556</v>
       </c>
       <c r="N272" t="n">
-        <v>1690.8700093502</v>
+        <v>481.48790873239</v>
       </c>
       <c r="O272" t="n">
-        <v>2434852.813464288</v>
+        <v>1230683.094719989</v>
       </c>
       <c r="P272" t="n">
-        <v>3000</v>
+        <v>650</v>
       </c>
       <c r="Q272" t="n">
-        <v>4320000</v>
+        <v>1661400</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>C523</t>
+          <t>C524</t>
         </is>
       </c>
       <c r="B273" t="n">
-        <v>6957430180212</v>
+        <v>6957430180229</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>GLOBO NUMERO 16PLATEADO Y DORADO</t>
+          <t>GLOBO NUMERO 30 PLATEADO Y DORADO</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -12602,7 +12600,7 @@
         </is>
       </c>
       <c r="J273" t="n">
-        <v>2556</v>
+        <v>614</v>
       </c>
       <c r="K273" t="n">
         <v>0</v>
@@ -12611,42 +12609,47 @@
         <v>0</v>
       </c>
       <c r="M273" t="n">
-        <v>2556</v>
+        <v>614</v>
       </c>
       <c r="N273" t="n">
-        <v>481.48790873239</v>
+        <v>872.15418687873</v>
       </c>
       <c r="O273" t="n">
-        <v>1230683.094719989</v>
+        <v>535502.6707435403</v>
       </c>
       <c r="P273" t="n">
-        <v>650</v>
+        <v>1200</v>
       </c>
       <c r="Q273" t="n">
-        <v>1661400</v>
+        <v>736800</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>C524</t>
+          <t>C5246/C5247</t>
         </is>
       </c>
       <c r="B274" t="n">
-        <v>6957430180229</v>
+        <v>6900077483239</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>GLOBO NUMERO 30 PLATEADO Y DORADO</t>
+          <t>MARIONETA DE DEDO ANIMALES STDS C5246/C5247</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J274" t="n">
-        <v>614</v>
+        <v>130</v>
       </c>
       <c r="K274" t="n">
         <v>0</v>
@@ -12655,47 +12658,42 @@
         <v>0</v>
       </c>
       <c r="M274" t="n">
-        <v>614</v>
+        <v>130</v>
       </c>
       <c r="N274" t="n">
-        <v>872.15418687873</v>
+        <v>8702.219999999999</v>
       </c>
       <c r="O274" t="n">
-        <v>535502.6707435403</v>
+        <v>1131288.6</v>
       </c>
       <c r="P274" t="n">
-        <v>1200</v>
+        <v>8900</v>
       </c>
       <c r="Q274" t="n">
-        <v>736800</v>
+        <v>1157000</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>C5246/C5247</t>
+          <t>C525</t>
         </is>
       </c>
       <c r="B275" t="n">
-        <v>6900077483239</v>
+        <v>6957430180236</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>MARIONETA DE DEDO ANIMALES STDS C5246/C5247</t>
-        </is>
-      </c>
-      <c r="E275" t="inlineStr">
-        <is>
-          <t>DIDACTICO</t>
+          <t>GLOBO NUMERO 16 COLORES Y PUNTOS</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J275" t="n">
-        <v>130</v>
+        <v>1436</v>
       </c>
       <c r="K275" t="n">
         <v>0</v>
@@ -12704,33 +12702,33 @@
         <v>0</v>
       </c>
       <c r="M275" t="n">
-        <v>130</v>
+        <v>1436</v>
       </c>
       <c r="N275" t="n">
-        <v>8702.219999999999</v>
+        <v>345.63428985635</v>
       </c>
       <c r="O275" t="n">
-        <v>1131288.6</v>
+        <v>496330.8402337186</v>
       </c>
       <c r="P275" t="n">
-        <v>8900</v>
+        <v>600</v>
       </c>
       <c r="Q275" t="n">
-        <v>1157000</v>
+        <v>861600</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>C525</t>
+          <t>C526</t>
         </is>
       </c>
       <c r="B276" t="n">
-        <v>6957430180236</v>
+        <v>6957430180243</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>GLOBO NUMERO 16 COLORES Y PUNTOS</t>
+          <t>GLOBO NUMERO 30 COLORES Y PUNTOS</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -12739,7 +12737,7 @@
         </is>
       </c>
       <c r="J276" t="n">
-        <v>1436</v>
+        <v>11416</v>
       </c>
       <c r="K276" t="n">
         <v>0</v>
@@ -12748,42 +12746,47 @@
         <v>0</v>
       </c>
       <c r="M276" t="n">
-        <v>1436</v>
+        <v>11416</v>
       </c>
       <c r="N276" t="n">
-        <v>345.55838633169</v>
+        <v>711.87861852814</v>
       </c>
       <c r="O276" t="n">
-        <v>496221.8427723068</v>
+        <v>8126806.309117246</v>
       </c>
       <c r="P276" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="Q276" t="n">
-        <v>861600</v>
+        <v>10274400</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>C526</t>
+          <t>C527-IO</t>
         </is>
       </c>
       <c r="B277" t="n">
-        <v>6957430180243</v>
+        <v>6957430180526</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>GLOBO NUMERO 30 COLORES Y PUNTOS</t>
+          <t>GLOBO FELIZ CUMPLEAÑOS LISTON</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>GLOBOS</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J277" t="n">
-        <v>11416</v>
+        <v>1242</v>
       </c>
       <c r="K277" t="n">
         <v>0</v>
@@ -12792,38 +12795,35 @@
         <v>0</v>
       </c>
       <c r="M277" t="n">
-        <v>11416</v>
+        <v>1242</v>
       </c>
       <c r="N277" t="n">
-        <v>711.3366477489</v>
+        <v>815.0599999999999</v>
       </c>
       <c r="O277" t="n">
-        <v>8120619.170701442</v>
+        <v>1012304.52</v>
       </c>
       <c r="P277" t="n">
         <v>900</v>
       </c>
       <c r="Q277" t="n">
-        <v>10274400</v>
+        <v>1117800</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>C527-IO</t>
-        </is>
-      </c>
-      <c r="B278" t="n">
-        <v>6957430180526</v>
+          <t>C541</t>
+        </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>GLOBO FELIZ CUMPLEAÑOS LISTON</t>
+          <t>GLOBO LLAMA PQÑO</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>GLOBOS</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -12832,7 +12832,7 @@
         </is>
       </c>
       <c r="J278" t="n">
-        <v>1242</v>
+        <v>2150</v>
       </c>
       <c r="K278" t="n">
         <v>0</v>
@@ -12841,30 +12841,30 @@
         <v>0</v>
       </c>
       <c r="M278" t="n">
-        <v>1242</v>
+        <v>2150</v>
       </c>
       <c r="N278" t="n">
-        <v>815.0599999999999</v>
+        <v>800</v>
       </c>
       <c r="O278" t="n">
-        <v>1012304.52</v>
+        <v>1720000</v>
       </c>
       <c r="P278" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="Q278" t="n">
-        <v>1117800</v>
+        <v>2150000</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>C541</t>
+          <t>C575-IO</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>GLOBO LLAMA PQÑO</t>
+          <t>GLOBO UNICORNIO PQÑO</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -12878,7 +12878,7 @@
         </is>
       </c>
       <c r="J279" t="n">
-        <v>2150</v>
+        <v>1001</v>
       </c>
       <c r="K279" t="n">
         <v>0</v>
@@ -12887,35 +12887,38 @@
         <v>0</v>
       </c>
       <c r="M279" t="n">
-        <v>2150</v>
+        <v>1001</v>
       </c>
       <c r="N279" t="n">
-        <v>800</v>
+        <v>320</v>
       </c>
       <c r="O279" t="n">
-        <v>1720000</v>
+        <v>320320</v>
       </c>
       <c r="P279" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="Q279" t="n">
-        <v>2150000</v>
+        <v>400400</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>C575-IO</t>
-        </is>
+          <t>C596-IO</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>8596162180268</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>GLOBO UNICORNIO PQÑO</t>
+          <t>GLOBO TE AMO</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>GLOBOS</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -12924,7 +12927,7 @@
         </is>
       </c>
       <c r="J280" t="n">
-        <v>1001</v>
+        <v>1455</v>
       </c>
       <c r="K280" t="n">
         <v>0</v>
@@ -12933,33 +12936,33 @@
         <v>0</v>
       </c>
       <c r="M280" t="n">
-        <v>1001</v>
+        <v>1455</v>
       </c>
       <c r="N280" t="n">
-        <v>320</v>
+        <v>1044.54</v>
       </c>
       <c r="O280" t="n">
-        <v>320320</v>
+        <v>1519805.7</v>
       </c>
       <c r="P280" t="n">
-        <v>400</v>
+        <v>1200</v>
       </c>
       <c r="Q280" t="n">
-        <v>400400</v>
+        <v>1746000</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>C596-IO</t>
+          <t>C60-IO</t>
         </is>
       </c>
       <c r="B281" t="n">
-        <v>8596162180268</v>
+        <v>6524521011245</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>GLOBO TE AMO</t>
+          <t>GLOBO TIKTOK BOUQUET</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -12973,7 +12976,7 @@
         </is>
       </c>
       <c r="J281" t="n">
-        <v>1455</v>
+        <v>740</v>
       </c>
       <c r="K281" t="n">
         <v>0</v>
@@ -12982,38 +12985,35 @@
         <v>0</v>
       </c>
       <c r="M281" t="n">
-        <v>1455</v>
+        <v>740</v>
       </c>
       <c r="N281" t="n">
-        <v>1044.54</v>
+        <v>1989.05</v>
       </c>
       <c r="O281" t="n">
-        <v>1519805.7</v>
+        <v>1471897</v>
       </c>
       <c r="P281" t="n">
-        <v>1200</v>
+        <v>3000</v>
       </c>
       <c r="Q281" t="n">
-        <v>1746000</v>
+        <v>2220000</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>C60-IO</t>
-        </is>
-      </c>
-      <c r="B282" t="n">
-        <v>6524521011245</v>
+          <t>C6074</t>
+        </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>GLOBO TIKTOK BOUQUET</t>
+          <t>FIGURAS ALIMENTOS DECORATIVOS C6074</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>GLOBOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -13022,7 +13022,7 @@
         </is>
       </c>
       <c r="J282" t="n">
-        <v>740</v>
+        <v>25</v>
       </c>
       <c r="K282" t="n">
         <v>0</v>
@@ -13031,44 +13031,42 @@
         <v>0</v>
       </c>
       <c r="M282" t="n">
-        <v>740</v>
+        <v>25</v>
       </c>
       <c r="N282" t="n">
-        <v>1989.05</v>
+        <v>9447.25</v>
       </c>
       <c r="O282" t="n">
-        <v>1471897</v>
+        <v>236181.25</v>
       </c>
       <c r="P282" t="n">
-        <v>3000</v>
+        <v>9900</v>
       </c>
       <c r="Q282" t="n">
-        <v>2220000</v>
+        <v>247500</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>C6074</t>
-        </is>
+          <t>C629</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>7791638082188</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>FIGURAS ALIMENTOS DECORATIVOS C6074</t>
-        </is>
-      </c>
-      <c r="E283" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
+          <t>BURBUJERO PITO STD</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J283" t="n">
-        <v>25</v>
+        <v>15264</v>
       </c>
       <c r="K283" t="n">
         <v>0</v>
@@ -13077,42 +13075,47 @@
         <v>0</v>
       </c>
       <c r="M283" t="n">
-        <v>25</v>
+        <v>15264</v>
       </c>
       <c r="N283" t="n">
-        <v>9447.25</v>
+        <v>703.7947515264</v>
       </c>
       <c r="O283" t="n">
-        <v>236181.25</v>
+        <v>10742723.08729897</v>
       </c>
       <c r="P283" t="n">
-        <v>9900</v>
+        <v>900</v>
       </c>
       <c r="Q283" t="n">
-        <v>247500</v>
+        <v>13737600</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>C629</t>
+          <t>C6406</t>
         </is>
       </c>
       <c r="B284" t="n">
-        <v>7791638082188</v>
+        <v>6820212541115</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>BURBUJERO PITO STD</t>
+          <t>PAJAROS MUSICALES DECORATIVOS C6406</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J284" t="n">
-        <v>15264</v>
+        <v>52</v>
       </c>
       <c r="K284" t="n">
         <v>0</v>
@@ -13121,47 +13124,39 @@
         <v>0</v>
       </c>
       <c r="M284" t="n">
-        <v>15264</v>
+        <v>52</v>
       </c>
       <c r="N284" t="n">
-        <v>704.67584580877</v>
+        <v>14260.14</v>
       </c>
       <c r="O284" t="n">
-        <v>10756172.11042506</v>
+        <v>741527.28</v>
       </c>
       <c r="P284" t="n">
-        <v>900</v>
+        <v>15900</v>
       </c>
       <c r="Q284" t="n">
-        <v>13737600</v>
+        <v>826800</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>C6406</t>
-        </is>
-      </c>
-      <c r="B285" t="n">
-        <v>6820212541115</v>
+          <t>C642</t>
+        </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>PAJAROS MUSICALES DECORATIVOS C6406</t>
-        </is>
-      </c>
-      <c r="E285" t="inlineStr">
-        <is>
-          <t>MICELANEOS</t>
+          <t>LANZADOR AGUA</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J285" t="n">
-        <v>52</v>
+        <v>599</v>
       </c>
       <c r="K285" t="n">
         <v>0</v>
@@ -13170,39 +13165,44 @@
         <v>0</v>
       </c>
       <c r="M285" t="n">
-        <v>52</v>
+        <v>599</v>
       </c>
       <c r="N285" t="n">
-        <v>14260.14</v>
+        <v>2529.19</v>
       </c>
       <c r="O285" t="n">
-        <v>741527.28</v>
+        <v>1514984.81</v>
       </c>
       <c r="P285" t="n">
-        <v>15900</v>
+        <v>5100</v>
       </c>
       <c r="Q285" t="n">
-        <v>826800</v>
+        <v>3054900</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>C642</t>
+          <t>C671-LJ</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>LANZADOR AGUA</t>
+          <t>GLOBO UNICORNIO MEDIANO</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J286" t="n">
-        <v>599</v>
+        <v>1397</v>
       </c>
       <c r="K286" t="n">
         <v>0</v>
@@ -13211,35 +13211,38 @@
         <v>0</v>
       </c>
       <c r="M286" t="n">
-        <v>599</v>
+        <v>1397</v>
       </c>
       <c r="N286" t="n">
-        <v>2529.19</v>
+        <v>400</v>
       </c>
       <c r="O286" t="n">
-        <v>1514984.81</v>
+        <v>558800</v>
       </c>
       <c r="P286" t="n">
-        <v>5100</v>
+        <v>500</v>
       </c>
       <c r="Q286" t="n">
-        <v>3054900</v>
+        <v>698500</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>C671-LJ</t>
-        </is>
+          <t>C7005</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>6874123039124</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>GLOBO UNICORNIO MEDIANO</t>
+          <t>MAQUINA DE COSER C7005</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -13248,7 +13251,7 @@
         </is>
       </c>
       <c r="J287" t="n">
-        <v>1397</v>
+        <v>208</v>
       </c>
       <c r="K287" t="n">
         <v>0</v>
@@ -13257,38 +13260,38 @@
         <v>0</v>
       </c>
       <c r="M287" t="n">
-        <v>1397</v>
+        <v>208</v>
       </c>
       <c r="N287" t="n">
-        <v>400</v>
+        <v>6078.9925962596</v>
       </c>
       <c r="O287" t="n">
-        <v>558800</v>
+        <v>1264430.460021997</v>
       </c>
       <c r="P287" t="n">
-        <v>500</v>
+        <v>18500</v>
       </c>
       <c r="Q287" t="n">
-        <v>698500</v>
+        <v>3848000</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>C7005</t>
+          <t>C7009</t>
         </is>
       </c>
       <c r="B288" t="n">
-        <v>6874123039124</v>
+        <v>2024250256831</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>MAQUINA DE COSER C7005</t>
+          <t>LANZADORA DE AGUA  TUBO CON HELICE C7009</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>LANZADORES</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -13297,7 +13300,7 @@
         </is>
       </c>
       <c r="J288" t="n">
-        <v>208</v>
+        <v>12</v>
       </c>
       <c r="K288" t="n">
         <v>0</v>
@@ -13306,33 +13309,33 @@
         <v>0</v>
       </c>
       <c r="M288" t="n">
-        <v>208</v>
+        <v>12</v>
       </c>
       <c r="N288" t="n">
-        <v>6078.9925934066</v>
+        <v>5899.18</v>
       </c>
       <c r="O288" t="n">
-        <v>1264430.459428573</v>
+        <v>70790.16</v>
       </c>
       <c r="P288" t="n">
-        <v>18500</v>
+        <v>12500</v>
       </c>
       <c r="Q288" t="n">
-        <v>3848000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>C7009</t>
+          <t>C7038</t>
         </is>
       </c>
       <c r="B289" t="n">
-        <v>2024250256831</v>
+        <v>5132595141631</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>LANZADORA DE AGUA  TUBO CON HELICE C7009</t>
+          <t>LANZADORA DE AGUA GLOBO C7038</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -13346,7 +13349,7 @@
         </is>
       </c>
       <c r="J289" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="K289" t="n">
         <v>0</v>
@@ -13355,38 +13358,38 @@
         <v>0</v>
       </c>
       <c r="M289" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="N289" t="n">
-        <v>5899.18</v>
+        <v>18423.71</v>
       </c>
       <c r="O289" t="n">
-        <v>70790.16</v>
+        <v>423745.33</v>
       </c>
       <c r="P289" t="n">
-        <v>12500</v>
+        <v>10000</v>
       </c>
       <c r="Q289" t="n">
-        <v>150000</v>
+        <v>230000</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>C7038</t>
+          <t>C7039</t>
         </is>
       </c>
       <c r="B290" t="n">
-        <v>5132595141631</v>
+        <v>5132594521182</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>LANZADORA DE AGUA GLOBO C7038</t>
+          <t>LANZADOR AGUA GLOBO DELFIN C7039/M90-4</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>LANZADORES</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -13395,7 +13398,7 @@
         </is>
       </c>
       <c r="J290" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K290" t="n">
         <v>0</v>
@@ -13404,38 +13407,38 @@
         <v>0</v>
       </c>
       <c r="M290" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="N290" t="n">
-        <v>18423.71</v>
+        <v>10985.78</v>
       </c>
       <c r="O290" t="n">
-        <v>423745.33</v>
+        <v>219715.6</v>
       </c>
       <c r="P290" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="Q290" t="n">
-        <v>230000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>C7039</t>
+          <t>C7040</t>
         </is>
       </c>
       <c r="B291" t="n">
-        <v>5132594521182</v>
+        <v>6920373004365</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>LANZADOR AGUA GLOBO DELFIN C7039/M90-4</t>
+          <t>GARAJE EXIBICION CON LUZ C7040</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -13444,7 +13447,7 @@
         </is>
       </c>
       <c r="J291" t="n">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="K291" t="n">
         <v>0</v>
@@ -13453,38 +13456,38 @@
         <v>0</v>
       </c>
       <c r="M291" t="n">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="N291" t="n">
-        <v>10985.78</v>
+        <v>23452.77</v>
       </c>
       <c r="O291" t="n">
-        <v>219715.6</v>
+        <v>1102280.19</v>
       </c>
       <c r="P291" t="n">
-        <v>15000</v>
+        <v>39900</v>
       </c>
       <c r="Q291" t="n">
-        <v>300000</v>
+        <v>1875300</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>C7040</t>
+          <t>C7042</t>
         </is>
       </c>
       <c r="B292" t="n">
-        <v>6920373004365</v>
+        <v>2024081616255</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>GARAJE EXIBICION CON LUZ C7040</t>
+          <t>CANCHA BASKETBALL WIN24 C7042</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -13493,7 +13496,7 @@
         </is>
       </c>
       <c r="J292" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="K292" t="n">
         <v>0</v>
@@ -13502,38 +13505,35 @@
         <v>0</v>
       </c>
       <c r="M292" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="N292" t="n">
-        <v>23452.77</v>
+        <v>9694.41</v>
       </c>
       <c r="O292" t="n">
-        <v>1102280.19</v>
+        <v>96944.10000000001</v>
       </c>
       <c r="P292" t="n">
-        <v>39900</v>
+        <v>32500</v>
       </c>
       <c r="Q292" t="n">
-        <v>1875300</v>
+        <v>325000</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>C7042</t>
-        </is>
-      </c>
-      <c r="B293" t="n">
-        <v>2024081616255</v>
+          <t>C7080-BC</t>
+        </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>CANCHA BASKETBALL WIN24 C7042</t>
+          <t>ROBOT TRANSFORME STD C7080-BC</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MUÑECOS</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -13542,7 +13542,7 @@
         </is>
       </c>
       <c r="J293" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="K293" t="n">
         <v>0</v>
@@ -13551,35 +13551,38 @@
         <v>0</v>
       </c>
       <c r="M293" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="N293" t="n">
-        <v>9694.41</v>
+        <v>10556.12</v>
       </c>
       <c r="O293" t="n">
-        <v>96944.10000000001</v>
+        <v>411688.6800000001</v>
       </c>
       <c r="P293" t="n">
-        <v>32500</v>
+        <v>32900</v>
       </c>
       <c r="Q293" t="n">
-        <v>325000</v>
+        <v>1283100</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>C7080-BC</t>
-        </is>
+          <t>C7081</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>6301582313156</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>ROBOT TRANSFORME STD C7080-BC</t>
+          <t>LANZADORA DARDOS DE PILA C7081</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>MUÑECOS</t>
+          <t>LANZADORES</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -13588,7 +13591,7 @@
         </is>
       </c>
       <c r="J294" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="K294" t="n">
         <v>0</v>
@@ -13597,47 +13600,42 @@
         <v>0</v>
       </c>
       <c r="M294" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="N294" t="n">
-        <v>10556.12</v>
+        <v>22470.62</v>
       </c>
       <c r="O294" t="n">
-        <v>411688.6800000001</v>
+        <v>471883.02</v>
       </c>
       <c r="P294" t="n">
-        <v>32900</v>
+        <v>41900</v>
       </c>
       <c r="Q294" t="n">
-        <v>1283100</v>
+        <v>879900</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>C7081</t>
+          <t>C71</t>
         </is>
       </c>
       <c r="B295" t="n">
-        <v>6301582313156</v>
+        <v>5899989622205</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>LANZADORA DARDOS DE PILA C7081</t>
-        </is>
-      </c>
-      <c r="E295" t="inlineStr">
-        <is>
-          <t>LANZADORES</t>
+          <t>C71 INFLABLE PONY ROSADO-AZUL</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J295" t="n">
-        <v>21</v>
+        <v>392</v>
       </c>
       <c r="K295" t="n">
         <v>0</v>
@@ -13646,42 +13644,44 @@
         <v>0</v>
       </c>
       <c r="M295" t="n">
-        <v>21</v>
+        <v>392</v>
       </c>
       <c r="N295" t="n">
-        <v>22470.62</v>
+        <v>1669.6</v>
       </c>
       <c r="O295" t="n">
-        <v>471883.02</v>
+        <v>654483.2</v>
       </c>
       <c r="P295" t="n">
-        <v>41900</v>
+        <v>2900</v>
       </c>
       <c r="Q295" t="n">
-        <v>879900</v>
+        <v>1136800</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>C71</t>
-        </is>
-      </c>
-      <c r="B296" t="n">
-        <v>5899989622205</v>
+          <t>C7117</t>
+        </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>C71 INFLABLE PONY ROSADO-AZUL</t>
+          <t>BINGO LOTTO C7117</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>JUEGOS DE MESA</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J296" t="n">
-        <v>392</v>
+        <v>20</v>
       </c>
       <c r="K296" t="n">
         <v>0</v>
@@ -13690,35 +13690,35 @@
         <v>0</v>
       </c>
       <c r="M296" t="n">
-        <v>392</v>
+        <v>20</v>
       </c>
       <c r="N296" t="n">
-        <v>1669.6</v>
+        <v>5798.41</v>
       </c>
       <c r="O296" t="n">
-        <v>654483.2</v>
+        <v>115968.2</v>
       </c>
       <c r="P296" t="n">
-        <v>2900</v>
+        <v>14900</v>
       </c>
       <c r="Q296" t="n">
-        <v>1136800</v>
+        <v>298000</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>C7117</t>
+          <t>C7124</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>BINGO LOTTO C7117</t>
+          <t>TRAILER TRANFORME XQ05 C7124</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>JUEGOS DE MESA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -13727,7 +13727,7 @@
         </is>
       </c>
       <c r="J297" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K297" t="n">
         <v>0</v>
@@ -13736,35 +13736,35 @@
         <v>0</v>
       </c>
       <c r="M297" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="N297" t="n">
-        <v>5798.41</v>
+        <v>19587.53</v>
       </c>
       <c r="O297" t="n">
-        <v>115968.2</v>
+        <v>783501.2</v>
       </c>
       <c r="P297" t="n">
-        <v>14900</v>
+        <v>65000</v>
       </c>
       <c r="Q297" t="n">
-        <v>298000</v>
+        <v>2600000</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>C7124</t>
+          <t>C7132</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>TRAILER TRANFORME XQ05 C7124</t>
+          <t>SET PULSERAS Y CAUCHOS C7132</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -13773,7 +13773,7 @@
         </is>
       </c>
       <c r="J298" t="n">
-        <v>40</v>
+        <v>144</v>
       </c>
       <c r="K298" t="n">
         <v>0</v>
@@ -13782,30 +13782,33 @@
         <v>0</v>
       </c>
       <c r="M298" t="n">
-        <v>40</v>
+        <v>144</v>
       </c>
       <c r="N298" t="n">
-        <v>19587.53</v>
+        <v>3100.87</v>
       </c>
       <c r="O298" t="n">
-        <v>783501.2</v>
+        <v>446525.28</v>
       </c>
       <c r="P298" t="n">
-        <v>65000</v>
+        <v>9900</v>
       </c>
       <c r="Q298" t="n">
-        <v>2600000</v>
+        <v>1425600</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>C7132</t>
-        </is>
+          <t>C7147-A</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>6912209205022</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>SET PULSERAS Y CAUCHOS C7132</t>
+          <t>ANIMAL DINOSAURIO TRICERATOPS CONLUZ C7147-A</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -13819,7 +13822,7 @@
         </is>
       </c>
       <c r="J299" t="n">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="K299" t="n">
         <v>0</v>
@@ -13828,33 +13831,33 @@
         <v>0</v>
       </c>
       <c r="M299" t="n">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="N299" t="n">
-        <v>3100.87</v>
+        <v>10348.08</v>
       </c>
       <c r="O299" t="n">
-        <v>446525.28</v>
+        <v>413923.2</v>
       </c>
       <c r="P299" t="n">
-        <v>9900</v>
+        <v>16900</v>
       </c>
       <c r="Q299" t="n">
-        <v>1425600</v>
+        <v>676000</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>C7147-A</t>
+          <t>C7213</t>
         </is>
       </c>
       <c r="B300" t="n">
-        <v>6912209205022</v>
+        <v>6987540143012</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>ANIMAL DINOSAURIO TRICERATOPS CONLUZ C7147-A</t>
+          <t>PESCADO CON LUZ Y SONIDO C7213</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -13868,7 +13871,7 @@
         </is>
       </c>
       <c r="J300" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="K300" t="n">
         <v>0</v>
@@ -13877,33 +13880,33 @@
         <v>0</v>
       </c>
       <c r="M300" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="N300" t="n">
-        <v>10348.08</v>
+        <v>9746.8802061856</v>
       </c>
       <c r="O300" t="n">
-        <v>413923.2</v>
+        <v>467850.2498969088</v>
       </c>
       <c r="P300" t="n">
-        <v>16900</v>
+        <v>18500</v>
       </c>
       <c r="Q300" t="n">
-        <v>676000</v>
+        <v>888000</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>C7213</t>
+          <t>C7221</t>
         </is>
       </c>
       <c r="B301" t="n">
-        <v>6987540143012</v>
+        <v>7453100037446</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>PESCADO CON LUZ Y SONIDO C7213</t>
+          <t>RELOJ CON FICHAS ARMABLES  C7221</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -13917,7 +13920,7 @@
         </is>
       </c>
       <c r="J301" t="n">
-        <v>48</v>
+        <v>347</v>
       </c>
       <c r="K301" t="n">
         <v>0</v>
@@ -13926,33 +13929,33 @@
         <v>0</v>
       </c>
       <c r="M301" t="n">
-        <v>48</v>
+        <v>347</v>
       </c>
       <c r="N301" t="n">
-        <v>9746.8802061856</v>
+        <v>2672.89</v>
       </c>
       <c r="O301" t="n">
-        <v>467850.2498969088</v>
+        <v>927492.83</v>
       </c>
       <c r="P301" t="n">
-        <v>18500</v>
+        <v>10200</v>
       </c>
       <c r="Q301" t="n">
-        <v>888000</v>
+        <v>3539400</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>C7221</t>
+          <t>C7222</t>
         </is>
       </c>
       <c r="B302" t="n">
-        <v>7453100037446</v>
+        <v>7453100037453</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>RELOJ CON FICHAS ARMABLES  C7221</t>
+          <t>RELOJ DIDACTICO CARACOL C7222</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -13966,7 +13969,7 @@
         </is>
       </c>
       <c r="J302" t="n">
-        <v>347</v>
+        <v>230</v>
       </c>
       <c r="K302" t="n">
         <v>0</v>
@@ -13975,38 +13978,38 @@
         <v>0</v>
       </c>
       <c r="M302" t="n">
-        <v>347</v>
+        <v>230</v>
       </c>
       <c r="N302" t="n">
-        <v>2672.89</v>
+        <v>4795.69</v>
       </c>
       <c r="O302" t="n">
-        <v>927492.83</v>
+        <v>1103008.7</v>
       </c>
       <c r="P302" t="n">
         <v>10200</v>
       </c>
       <c r="Q302" t="n">
-        <v>3539400</v>
+        <v>2346000</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>C7222</t>
+          <t>C7294</t>
         </is>
       </c>
       <c r="B303" t="n">
-        <v>7453100037453</v>
+        <v>6895675680022</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>RELOJ DIDACTICO CARACOL C7222</t>
+          <t>JUEGO DEPORTIVO HOCHEY C7294</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -14015,7 +14018,7 @@
         </is>
       </c>
       <c r="J303" t="n">
-        <v>230</v>
+        <v>60</v>
       </c>
       <c r="K303" t="n">
         <v>0</v>
@@ -14024,38 +14027,38 @@
         <v>0</v>
       </c>
       <c r="M303" t="n">
-        <v>230</v>
+        <v>60</v>
       </c>
       <c r="N303" t="n">
-        <v>4795.69</v>
+        <v>4337.31</v>
       </c>
       <c r="O303" t="n">
-        <v>1103008.7</v>
+        <v>260238.6</v>
       </c>
       <c r="P303" t="n">
-        <v>10200</v>
+        <v>12900</v>
       </c>
       <c r="Q303" t="n">
-        <v>2346000</v>
+        <v>774000</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>C7294</t>
+          <t>C7325</t>
         </is>
       </c>
       <c r="B304" t="n">
-        <v>6895675680022</v>
+        <v>6974555555022</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>JUEGO DEPORTIVO HOCHEY C7294</t>
+          <t>PISTA EN BLISTER C7325</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -14064,7 +14067,7 @@
         </is>
       </c>
       <c r="J304" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="K304" t="n">
         <v>0</v>
@@ -14073,38 +14076,35 @@
         <v>0</v>
       </c>
       <c r="M304" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="N304" t="n">
-        <v>4337.31</v>
+        <v>3067.0906143345</v>
       </c>
       <c r="O304" t="n">
-        <v>260238.6</v>
+        <v>138019.0776450525</v>
       </c>
       <c r="P304" t="n">
-        <v>12900</v>
+        <v>7200</v>
       </c>
       <c r="Q304" t="n">
-        <v>774000</v>
+        <v>324000</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>C7325</t>
-        </is>
-      </c>
-      <c r="B305" t="n">
-        <v>6974555555022</v>
+          <t>C736</t>
+        </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>PISTA EN BLISTER C7325</t>
+          <t>GLOBO CORAZON GDE MENSAJE</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -14113,7 +14113,7 @@
         </is>
       </c>
       <c r="J305" t="n">
-        <v>45</v>
+        <v>2700</v>
       </c>
       <c r="K305" t="n">
         <v>0</v>
@@ -14122,35 +14122,38 @@
         <v>0</v>
       </c>
       <c r="M305" t="n">
-        <v>45</v>
+        <v>2700</v>
       </c>
       <c r="N305" t="n">
-        <v>3067.0906143345</v>
+        <v>640</v>
       </c>
       <c r="O305" t="n">
-        <v>138019.0776450525</v>
+        <v>1728000</v>
       </c>
       <c r="P305" t="n">
-        <v>7200</v>
+        <v>800</v>
       </c>
       <c r="Q305" t="n">
-        <v>324000</v>
+        <v>2160000</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>C736</t>
-        </is>
+          <t>C7365</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>6920240750050</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>GLOBO CORAZON GDE MENSAJE</t>
+          <t>DIDACTICO JIRAFA EN BOLSA C7365</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -14159,7 +14162,7 @@
         </is>
       </c>
       <c r="J306" t="n">
-        <v>2700</v>
+        <v>19</v>
       </c>
       <c r="K306" t="n">
         <v>0</v>
@@ -14168,33 +14171,33 @@
         <v>0</v>
       </c>
       <c r="M306" t="n">
-        <v>2700</v>
+        <v>19</v>
       </c>
       <c r="N306" t="n">
-        <v>640</v>
+        <v>4234.4238541667</v>
       </c>
       <c r="O306" t="n">
-        <v>1728000</v>
+        <v>80454.0532291673</v>
       </c>
       <c r="P306" t="n">
-        <v>800</v>
+        <v>5900</v>
       </c>
       <c r="Q306" t="n">
-        <v>2160000</v>
+        <v>112100</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>C7365</t>
+          <t>C7366</t>
         </is>
       </c>
       <c r="B307" t="n">
-        <v>6920240750050</v>
+        <v>6920240750098</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>DIDACTICO JIRAFA EN BOLSA C7365</t>
+          <t>TREN DIDACTICO EN BOLSA C7366</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -14208,7 +14211,7 @@
         </is>
       </c>
       <c r="J307" t="n">
-        <v>19</v>
+        <v>104</v>
       </c>
       <c r="K307" t="n">
         <v>0</v>
@@ -14217,33 +14220,33 @@
         <v>0</v>
       </c>
       <c r="M307" t="n">
-        <v>19</v>
+        <v>104</v>
       </c>
       <c r="N307" t="n">
-        <v>4190.77</v>
+        <v>3503.9263942308</v>
       </c>
       <c r="O307" t="n">
-        <v>79624.63</v>
+        <v>364408.3450000032</v>
       </c>
       <c r="P307" t="n">
-        <v>5900</v>
+        <v>6900</v>
       </c>
       <c r="Q307" t="n">
-        <v>112100</v>
+        <v>717600</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>C7366</t>
+          <t>C7368</t>
         </is>
       </c>
       <c r="B308" t="n">
-        <v>6920240750098</v>
+        <v>6920240750159</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>TREN DIDACTICO EN BOLSA C7366</t>
+          <t>MOTO DIDACTICA EN BOLSA C736</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -14257,7 +14260,7 @@
         </is>
       </c>
       <c r="J308" t="n">
-        <v>104</v>
+        <v>158</v>
       </c>
       <c r="K308" t="n">
         <v>0</v>
@@ -14266,38 +14269,35 @@
         <v>0</v>
       </c>
       <c r="M308" t="n">
-        <v>104</v>
+        <v>158</v>
       </c>
       <c r="N308" t="n">
-        <v>3499.72</v>
+        <v>4593.2494352159</v>
       </c>
       <c r="O308" t="n">
-        <v>363970.88</v>
+        <v>725733.4107641123</v>
       </c>
       <c r="P308" t="n">
-        <v>6900</v>
+        <v>7500</v>
       </c>
       <c r="Q308" t="n">
-        <v>717600</v>
+        <v>1185000</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>C7368</t>
-        </is>
-      </c>
-      <c r="B309" t="n">
-        <v>6920240750159</v>
+          <t>C740-IO</t>
+        </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>MOTO DIDACTICA EN BOLSA C736</t>
+          <t>GLOBO UNICORNIO MED</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -14306,7 +14306,7 @@
         </is>
       </c>
       <c r="J309" t="n">
-        <v>158</v>
+        <v>1876</v>
       </c>
       <c r="K309" t="n">
         <v>0</v>
@@ -14315,35 +14315,38 @@
         <v>0</v>
       </c>
       <c r="M309" t="n">
-        <v>158</v>
+        <v>1876</v>
       </c>
       <c r="N309" t="n">
-        <v>4578.04</v>
+        <v>480</v>
       </c>
       <c r="O309" t="n">
-        <v>723330.3199999999</v>
+        <v>900480</v>
       </c>
       <c r="P309" t="n">
-        <v>7500</v>
+        <v>600</v>
       </c>
       <c r="Q309" t="n">
-        <v>1185000</v>
+        <v>1125600</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>C740-IO</t>
-        </is>
+          <t>C7413</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>6921202412870</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>GLOBO UNICORNIO MED</t>
+          <t>DIDACTICO TORRE DE AROS C7413</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -14352,7 +14355,7 @@
         </is>
       </c>
       <c r="J310" t="n">
-        <v>1876</v>
+        <v>120</v>
       </c>
       <c r="K310" t="n">
         <v>0</v>
@@ -14361,38 +14364,35 @@
         <v>0</v>
       </c>
       <c r="M310" t="n">
-        <v>1876</v>
+        <v>120</v>
       </c>
       <c r="N310" t="n">
-        <v>480</v>
+        <v>4159.0003007519</v>
       </c>
       <c r="O310" t="n">
-        <v>900480</v>
+        <v>499080.036090228</v>
       </c>
       <c r="P310" t="n">
-        <v>600</v>
+        <v>8900</v>
       </c>
       <c r="Q310" t="n">
-        <v>1125600</v>
+        <v>1068000</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>C7413</t>
-        </is>
-      </c>
-      <c r="B311" t="n">
-        <v>6921202412870</v>
+          <t>C744-IO</t>
+        </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>DIDACTICO TORRE DE AROS C7413</t>
+          <t>GLOBO FELIZ CUMPLEAÑOS COLORES Y PUNTOS</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>GLOBOS</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -14401,7 +14401,7 @@
         </is>
       </c>
       <c r="J311" t="n">
-        <v>120</v>
+        <v>478</v>
       </c>
       <c r="K311" t="n">
         <v>0</v>
@@ -14410,35 +14410,35 @@
         <v>0</v>
       </c>
       <c r="M311" t="n">
-        <v>120</v>
+        <v>478</v>
       </c>
       <c r="N311" t="n">
-        <v>4159.0003007519</v>
+        <v>1554.12</v>
       </c>
       <c r="O311" t="n">
-        <v>499080.036090228</v>
+        <v>742869.36</v>
       </c>
       <c r="P311" t="n">
-        <v>8900</v>
+        <v>1900</v>
       </c>
       <c r="Q311" t="n">
-        <v>1068000</v>
+        <v>908200</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>C744-IO</t>
+          <t>C7462</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>GLOBO FELIZ CUMPLEAÑOS COLORES Y PUNTOS</t>
+          <t>SET DE BELLEZA ACCESORIOS PARA EL CABELLO C7462</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>GLOBOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -14447,7 +14447,7 @@
         </is>
       </c>
       <c r="J312" t="n">
-        <v>478</v>
+        <v>11</v>
       </c>
       <c r="K312" t="n">
         <v>0</v>
@@ -14456,33 +14456,33 @@
         <v>0</v>
       </c>
       <c r="M312" t="n">
-        <v>478</v>
+        <v>11</v>
       </c>
       <c r="N312" t="n">
-        <v>1554.12</v>
+        <v>14751.820327869</v>
       </c>
       <c r="O312" t="n">
-        <v>742869.36</v>
+        <v>162270.023606559</v>
       </c>
       <c r="P312" t="n">
-        <v>1900</v>
+        <v>37100</v>
       </c>
       <c r="Q312" t="n">
-        <v>908200</v>
+        <v>408100</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>C7453</t>
+          <t>C7467</t>
         </is>
       </c>
       <c r="B313" t="n">
-        <v>6920247274535</v>
+        <v>6920241023009</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>JUEGO DE MESA BALONCESTO C7453</t>
+          <t>ARCO Y FLECHA PARA NIÑAS C7467</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -14496,7 +14496,7 @@
         </is>
       </c>
       <c r="J313" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K313" t="n">
         <v>0</v>
@@ -14505,35 +14505,38 @@
         <v>0</v>
       </c>
       <c r="M313" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="N313" t="n">
-        <v>27938.1</v>
+        <v>15347.45</v>
       </c>
       <c r="O313" t="n">
-        <v>223504.8</v>
+        <v>230211.75</v>
       </c>
       <c r="P313" t="n">
-        <v>18000</v>
+        <v>23900</v>
       </c>
       <c r="Q313" t="n">
-        <v>144000</v>
+        <v>358500</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>C7462</t>
-        </is>
+          <t>C7488</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>6945158254520</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>SET DE BELLEZA ACCESORIOS PARA EL CABELLO C7462</t>
+          <t>SOPORTE CELULAR CON LUZ C7488</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -14542,7 +14545,7 @@
         </is>
       </c>
       <c r="J314" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="K314" t="n">
         <v>0</v>
@@ -14551,33 +14554,33 @@
         <v>0</v>
       </c>
       <c r="M314" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="N314" t="n">
-        <v>14751.820327869</v>
+        <v>8919.16</v>
       </c>
       <c r="O314" t="n">
-        <v>162270.023606559</v>
+        <v>258655.64</v>
       </c>
       <c r="P314" t="n">
-        <v>37100</v>
+        <v>10000</v>
       </c>
       <c r="Q314" t="n">
-        <v>408100</v>
+        <v>290000</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>C7467</t>
+          <t>C7513</t>
         </is>
       </c>
       <c r="B315" t="n">
-        <v>6920241023009</v>
+        <v>6905698382824</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>ARCO Y FLECHA PARA NIÑAS C7467</t>
+          <t>SONAJERO BOLA LUZ GDE C7513</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -14591,7 +14594,7 @@
         </is>
       </c>
       <c r="J315" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="K315" t="n">
         <v>0</v>
@@ -14600,47 +14603,42 @@
         <v>0</v>
       </c>
       <c r="M315" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="N315" t="n">
-        <v>15347.45</v>
+        <v>1024.29</v>
       </c>
       <c r="O315" t="n">
-        <v>230211.75</v>
+        <v>1024.29</v>
       </c>
       <c r="P315" t="n">
-        <v>23900</v>
+        <v>2900</v>
       </c>
       <c r="Q315" t="n">
-        <v>358500</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>C7488</t>
+          <t>C752</t>
         </is>
       </c>
       <c r="B316" t="n">
-        <v>6945158254520</v>
+        <v>8596162180497</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>SOPORTE CELULAR CON LUZ C7488</t>
-        </is>
-      </c>
-      <c r="E316" t="inlineStr">
-        <is>
-          <t>MICELANEOS</t>
+          <t>GLOBO UNICORNIO MED 4 PATAS</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J316" t="n">
-        <v>29</v>
+        <v>1398</v>
       </c>
       <c r="K316" t="n">
         <v>0</v>
@@ -14649,47 +14647,42 @@
         <v>0</v>
       </c>
       <c r="M316" t="n">
-        <v>29</v>
+        <v>1398</v>
       </c>
       <c r="N316" t="n">
-        <v>8919.16</v>
+        <v>1163.7447787403</v>
       </c>
       <c r="O316" t="n">
-        <v>258655.64</v>
+        <v>1626915.200678939</v>
       </c>
       <c r="P316" t="n">
-        <v>10000</v>
+        <v>1500</v>
       </c>
       <c r="Q316" t="n">
-        <v>290000</v>
+        <v>2097000</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>C7513</t>
+          <t>C753</t>
         </is>
       </c>
       <c r="B317" t="n">
-        <v>6905698382824</v>
+        <v>8596162180503</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>SONAJERO BOLA LUZ GDE C7513</t>
-        </is>
-      </c>
-      <c r="E317" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
+          <t>GLOBO UNICORNIO GDE 4 PATAS</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J317" t="n">
-        <v>1</v>
+        <v>277</v>
       </c>
       <c r="K317" t="n">
         <v>0</v>
@@ -14698,42 +14691,47 @@
         <v>0</v>
       </c>
       <c r="M317" t="n">
-        <v>1</v>
+        <v>277</v>
       </c>
       <c r="N317" t="n">
-        <v>1024.29</v>
+        <v>5113.4625508318</v>
       </c>
       <c r="O317" t="n">
-        <v>1024.29</v>
+        <v>1416429.126580409</v>
       </c>
       <c r="P317" t="n">
-        <v>2900</v>
+        <v>7000</v>
       </c>
       <c r="Q317" t="n">
-        <v>2900</v>
+        <v>1939000</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>C752</t>
+          <t>C7533</t>
         </is>
       </c>
       <c r="B318" t="n">
-        <v>8596162180497</v>
+        <v>6923669699979</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>GLOBO UNICORNIO MED 4 PATAS</t>
+          <t>REPUESTO BIOGEL NEON C7533</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J318" t="n">
-        <v>1398</v>
+        <v>12023</v>
       </c>
       <c r="K318" t="n">
         <v>0</v>
@@ -14742,42 +14740,47 @@
         <v>0</v>
       </c>
       <c r="M318" t="n">
-        <v>1398</v>
+        <v>12023</v>
       </c>
       <c r="N318" t="n">
-        <v>1163.7447787403</v>
+        <v>509.69</v>
       </c>
       <c r="O318" t="n">
-        <v>1626915.200678939</v>
+        <v>6128002.87</v>
       </c>
       <c r="P318" t="n">
-        <v>1500</v>
+        <v>750</v>
       </c>
       <c r="Q318" t="n">
-        <v>2097000</v>
+        <v>9017250</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>C753</t>
+          <t>C7534</t>
         </is>
       </c>
       <c r="B319" t="n">
-        <v>8596162180503</v>
+        <v>6951241752002</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>GLOBO UNICORNIO GDE 4 PATAS</t>
+          <t>GORRO PELUCHE LUZ C7534-A-B-C-D-E-F</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J319" t="n">
-        <v>277</v>
+        <v>499</v>
       </c>
       <c r="K319" t="n">
         <v>0</v>
@@ -14786,38 +14789,35 @@
         <v>0</v>
       </c>
       <c r="M319" t="n">
-        <v>277</v>
+        <v>499</v>
       </c>
       <c r="N319" t="n">
-        <v>5113.4625508318</v>
+        <v>7056.0857581657</v>
       </c>
       <c r="O319" t="n">
-        <v>1416429.126580409</v>
+        <v>3520986.793324684</v>
       </c>
       <c r="P319" t="n">
-        <v>7000</v>
+        <v>9900</v>
       </c>
       <c r="Q319" t="n">
-        <v>1939000</v>
+        <v>4940100</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>C7533</t>
-        </is>
-      </c>
-      <c r="B320" t="n">
-        <v>6923669699979</v>
+          <t>C7535</t>
+        </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>REPUESTO BIOGEL NEON C7533</t>
+          <t>CARRO METALICO X13 CON CAMION C7535</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -14826,7 +14826,7 @@
         </is>
       </c>
       <c r="J320" t="n">
-        <v>12023</v>
+        <v>30</v>
       </c>
       <c r="K320" t="n">
         <v>0</v>
@@ -14835,33 +14835,30 @@
         <v>0</v>
       </c>
       <c r="M320" t="n">
-        <v>12023</v>
+        <v>30</v>
       </c>
       <c r="N320" t="n">
-        <v>509.69</v>
+        <v>24338.47</v>
       </c>
       <c r="O320" t="n">
-        <v>6128002.87</v>
+        <v>730154.1000000001</v>
       </c>
       <c r="P320" t="n">
-        <v>750</v>
+        <v>27900</v>
       </c>
       <c r="Q320" t="n">
-        <v>9017250</v>
+        <v>837000</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>C7534</t>
-        </is>
-      </c>
-      <c r="B321" t="n">
-        <v>6951241752002</v>
+          <t>C7560</t>
+        </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>GORRO PELUCHE LUZ C7534-A-B-C-D-E-F</t>
+          <t>BARRA LUMINOSA 48CM C7560/211</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -14875,7 +14872,7 @@
         </is>
       </c>
       <c r="J321" t="n">
-        <v>499</v>
+        <v>188</v>
       </c>
       <c r="K321" t="n">
         <v>0</v>
@@ -14884,35 +14881,38 @@
         <v>0</v>
       </c>
       <c r="M321" t="n">
-        <v>499</v>
+        <v>188</v>
       </c>
       <c r="N321" t="n">
-        <v>7046.9398271765</v>
+        <v>796.3099999999999</v>
       </c>
       <c r="O321" t="n">
-        <v>3516422.973761074</v>
+        <v>149706.28</v>
       </c>
       <c r="P321" t="n">
-        <v>9900</v>
+        <v>2500</v>
       </c>
       <c r="Q321" t="n">
-        <v>4940100</v>
+        <v>470000</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>C7535</t>
-        </is>
+          <t>C7588</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>7588228020244</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>CARRO METALICO X13 CON CAMION C7535</t>
+          <t>SONAJERO LUZ PANDITA C7588</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -14921,7 +14921,7 @@
         </is>
       </c>
       <c r="J322" t="n">
-        <v>30</v>
+        <v>1429</v>
       </c>
       <c r="K322" t="n">
         <v>0</v>
@@ -14930,35 +14930,38 @@
         <v>0</v>
       </c>
       <c r="M322" t="n">
-        <v>30</v>
+        <v>1429</v>
       </c>
       <c r="N322" t="n">
-        <v>24338.47</v>
+        <v>641.78</v>
       </c>
       <c r="O322" t="n">
-        <v>730154.1000000001</v>
+        <v>917103.62</v>
       </c>
       <c r="P322" t="n">
-        <v>27900</v>
+        <v>2500</v>
       </c>
       <c r="Q322" t="n">
-        <v>837000</v>
+        <v>3572500</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>C7560</t>
-        </is>
+          <t>C7610</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>6999899236093</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>BARRA LUMINOSA 48CM C7560/211</t>
+          <t>BOTE TIMON PISCINA 80X60 C7610</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>INFLABLES</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -14967,7 +14970,7 @@
         </is>
       </c>
       <c r="J323" t="n">
-        <v>188</v>
+        <v>276</v>
       </c>
       <c r="K323" t="n">
         <v>0</v>
@@ -14976,38 +14979,38 @@
         <v>0</v>
       </c>
       <c r="M323" t="n">
-        <v>188</v>
+        <v>276</v>
       </c>
       <c r="N323" t="n">
-        <v>796.3099999999999</v>
+        <v>7811.9</v>
       </c>
       <c r="O323" t="n">
-        <v>149706.28</v>
+        <v>2156084.4</v>
       </c>
       <c r="P323" t="n">
-        <v>2500</v>
+        <v>13900</v>
       </c>
       <c r="Q323" t="n">
-        <v>470000</v>
+        <v>3836400</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>C7588</t>
+          <t>C7614-F</t>
         </is>
       </c>
       <c r="B324" t="n">
-        <v>7588228020244</v>
+        <v>6999899236130</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>SONAJERO LUZ PANDITA C7588</t>
+          <t>FLOTADOR DONA FLAMINGO C7614-F</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -15016,7 +15019,7 @@
         </is>
       </c>
       <c r="J324" t="n">
-        <v>1429</v>
+        <v>382</v>
       </c>
       <c r="K324" t="n">
         <v>0</v>
@@ -15025,47 +15028,42 @@
         <v>0</v>
       </c>
       <c r="M324" t="n">
-        <v>1429</v>
+        <v>382</v>
       </c>
       <c r="N324" t="n">
-        <v>641.78</v>
+        <v>3155</v>
       </c>
       <c r="O324" t="n">
-        <v>917103.62</v>
+        <v>1205210</v>
       </c>
       <c r="P324" t="n">
-        <v>2500</v>
+        <v>5900</v>
       </c>
       <c r="Q324" t="n">
-        <v>3572500</v>
+        <v>2253800</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>C7610</t>
+          <t>C784</t>
         </is>
       </c>
       <c r="B325" t="n">
-        <v>6999899236093</v>
+        <v>8913992935507</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>BOTE TIMON PISCINA 80X60 C7610</t>
-        </is>
-      </c>
-      <c r="E325" t="inlineStr">
-        <is>
-          <t>INFLABLES</t>
+          <t>GLOBO MENSAJE CUADRADO</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J325" t="n">
-        <v>276</v>
+        <v>1450</v>
       </c>
       <c r="K325" t="n">
         <v>0</v>
@@ -15074,47 +15072,42 @@
         <v>0</v>
       </c>
       <c r="M325" t="n">
-        <v>276</v>
+        <v>1450</v>
       </c>
       <c r="N325" t="n">
-        <v>7811.9</v>
+        <v>704.89694272446</v>
       </c>
       <c r="O325" t="n">
-        <v>2156084.4</v>
+        <v>1022100.566950467</v>
       </c>
       <c r="P325" t="n">
-        <v>13900</v>
+        <v>900</v>
       </c>
       <c r="Q325" t="n">
-        <v>3836400</v>
+        <v>1305000</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>C7614-F</t>
+          <t>C819</t>
         </is>
       </c>
       <c r="B326" t="n">
-        <v>6999899236130</v>
+        <v>2087202108190</v>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>FLOTADOR DONA FLAMINGO C7614-F</t>
-        </is>
-      </c>
-      <c r="E326" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>TROMPO EMOJI</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J326" t="n">
-        <v>382</v>
+        <v>468</v>
       </c>
       <c r="K326" t="n">
         <v>0</v>
@@ -15123,33 +15116,33 @@
         <v>0</v>
       </c>
       <c r="M326" t="n">
-        <v>382</v>
+        <v>468</v>
       </c>
       <c r="N326" t="n">
-        <v>3155</v>
+        <v>6761.25</v>
       </c>
       <c r="O326" t="n">
-        <v>1205210</v>
+        <v>3164265</v>
       </c>
       <c r="P326" t="n">
-        <v>5900</v>
+        <v>5200</v>
       </c>
       <c r="Q326" t="n">
-        <v>2253800</v>
+        <v>2433600</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>C784</t>
+          <t>C84</t>
         </is>
       </c>
       <c r="B327" t="n">
-        <v>8913992935507</v>
+        <v>2021010563031</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>GLOBO MENSAJE CUADRADO</t>
+          <t>LANZADOR DE AGUA</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -15158,7 +15151,7 @@
         </is>
       </c>
       <c r="J327" t="n">
-        <v>1450</v>
+        <v>212</v>
       </c>
       <c r="K327" t="n">
         <v>0</v>
@@ -15167,33 +15160,35 @@
         <v>0</v>
       </c>
       <c r="M327" t="n">
-        <v>1450</v>
+        <v>212</v>
       </c>
       <c r="N327" t="n">
-        <v>704.89694272446</v>
+        <v>1008.8125188917</v>
       </c>
       <c r="O327" t="n">
-        <v>1022100.566950467</v>
+        <v>213868.2540050404</v>
       </c>
       <c r="P327" t="n">
-        <v>900</v>
+        <v>1500</v>
       </c>
       <c r="Q327" t="n">
-        <v>1305000</v>
+        <v>318000</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>C819</t>
-        </is>
-      </c>
-      <c r="B328" t="n">
-        <v>2087202108190</v>
+          <t>C879</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>CG-2016-212</t>
+        </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>TROMPO EMOJI</t>
+          <t>VELA MARIPOSA</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -15202,7 +15197,7 @@
         </is>
       </c>
       <c r="J328" t="n">
-        <v>468</v>
+        <v>121</v>
       </c>
       <c r="K328" t="n">
         <v>0</v>
@@ -15211,42 +15206,49 @@
         <v>0</v>
       </c>
       <c r="M328" t="n">
-        <v>468</v>
+        <v>121</v>
       </c>
       <c r="N328" t="n">
-        <v>6761.25</v>
+        <v>1520</v>
       </c>
       <c r="O328" t="n">
-        <v>3164265</v>
+        <v>183920</v>
       </c>
       <c r="P328" t="n">
-        <v>5200</v>
+        <v>1900</v>
       </c>
       <c r="Q328" t="n">
-        <v>2433600</v>
+        <v>229900</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>C84</t>
-        </is>
-      </c>
-      <c r="B329" t="n">
-        <v>2021010563031</v>
+          <t>C880</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>cg2016213</t>
+        </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>LANZADOR DE AGUA</t>
+          <t>VELA FLOR</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>VELA</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J329" t="n">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="K329" t="n">
         <v>0</v>
@@ -15255,35 +15257,30 @@
         <v>0</v>
       </c>
       <c r="M329" t="n">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="N329" t="n">
-        <v>1008.8125188917</v>
+        <v>1520</v>
       </c>
       <c r="O329" t="n">
-        <v>213868.2540050404</v>
+        <v>304000</v>
       </c>
       <c r="P329" t="n">
-        <v>1500</v>
+        <v>1900</v>
       </c>
       <c r="Q329" t="n">
-        <v>318000</v>
+        <v>380000</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>C879</t>
-        </is>
-      </c>
-      <c r="B330" t="inlineStr">
-        <is>
-          <t>CG-2016-212</t>
+          <t>C888</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>VELA MARIPOSA</t>
+          <t>PELOTA CHILLON PUYAS SIN LUZ</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -15292,7 +15289,7 @@
         </is>
       </c>
       <c r="J330" t="n">
-        <v>121</v>
+        <v>169</v>
       </c>
       <c r="K330" t="n">
         <v>0</v>
@@ -15301,40 +15298,35 @@
         <v>0</v>
       </c>
       <c r="M330" t="n">
-        <v>121</v>
+        <v>169</v>
       </c>
       <c r="N330" t="n">
-        <v>1520</v>
+        <v>1213.6821400778</v>
       </c>
       <c r="O330" t="n">
-        <v>183920</v>
+        <v>205112.2816731482</v>
       </c>
       <c r="P330" t="n">
-        <v>1900</v>
+        <v>1500</v>
       </c>
       <c r="Q330" t="n">
-        <v>229900</v>
+        <v>253500</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>C880</t>
-        </is>
-      </c>
-      <c r="B331" t="inlineStr">
-        <is>
-          <t>cg2016213</t>
+          <t>FG037</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>VELA FLOR</t>
+          <t>SNORKEL 66046A</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>VELA</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
@@ -15343,7 +15335,7 @@
         </is>
       </c>
       <c r="J331" t="n">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="K331" t="n">
         <v>0</v>
@@ -15352,39 +15344,44 @@
         <v>0</v>
       </c>
       <c r="M331" t="n">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="N331" t="n">
-        <v>1520</v>
+        <v>13493.858292683</v>
       </c>
       <c r="O331" t="n">
-        <v>304000</v>
+        <v>2415400.634390257</v>
       </c>
       <c r="P331" t="n">
-        <v>1900</v>
+        <v>16900</v>
       </c>
       <c r="Q331" t="n">
-        <v>380000</v>
+        <v>3025100</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>C888</t>
+          <t>FG039</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>PELOTA CHILLON PUYAS SIN LUZ</t>
+          <t>GAFA DE NATACION BLISTER 2404-2</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J332" t="n">
-        <v>169</v>
+        <v>347</v>
       </c>
       <c r="K332" t="n">
         <v>0</v>
@@ -15393,35 +15390,40 @@
         <v>0</v>
       </c>
       <c r="M332" t="n">
-        <v>169</v>
+        <v>347</v>
       </c>
       <c r="N332" t="n">
-        <v>1213.6821400778</v>
+        <v>2644.9</v>
       </c>
       <c r="O332" t="n">
-        <v>205112.2816731482</v>
+        <v>917780.3</v>
       </c>
       <c r="P332" t="n">
-        <v>1500</v>
+        <v>3900</v>
       </c>
       <c r="Q332" t="n">
-        <v>253500</v>
+        <v>1353300</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>FG037</t>
+          <t>MG16332</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>MG16332</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>SNORKEL 66046A</t>
+          <t>LANZADOR  ARCO Y FLECA CON LASER MG16332</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -15430,7 +15432,7 @@
         </is>
       </c>
       <c r="J333" t="n">
-        <v>179</v>
+        <v>4</v>
       </c>
       <c r="K333" t="n">
         <v>0</v>
@@ -15439,35 +15441,35 @@
         <v>0</v>
       </c>
       <c r="M333" t="n">
-        <v>179</v>
+        <v>4</v>
       </c>
       <c r="N333" t="n">
-        <v>13493.858292683</v>
+        <v>8439.969999999999</v>
       </c>
       <c r="O333" t="n">
-        <v>2415400.634390257</v>
+        <v>33759.88</v>
       </c>
       <c r="P333" t="n">
-        <v>16900</v>
+        <v>29500</v>
       </c>
       <c r="Q333" t="n">
-        <v>3025100</v>
+        <v>118000</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>FG039</t>
+          <t>MG20430</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>GAFA DE NATACION BLISTER 2404-2</t>
+          <t>SET PLASTILINA CON MOLDES BARBERIA MALETA MG20430</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -15476,7 +15478,7 @@
         </is>
       </c>
       <c r="J334" t="n">
-        <v>347</v>
+        <v>18</v>
       </c>
       <c r="K334" t="n">
         <v>0</v>
@@ -15485,40 +15487,35 @@
         <v>0</v>
       </c>
       <c r="M334" t="n">
-        <v>347</v>
+        <v>18</v>
       </c>
       <c r="N334" t="n">
-        <v>2644.9</v>
+        <v>12189.831111111</v>
       </c>
       <c r="O334" t="n">
-        <v>917780.3</v>
+        <v>219416.959999998</v>
       </c>
       <c r="P334" t="n">
-        <v>3900</v>
+        <v>30900</v>
       </c>
       <c r="Q334" t="n">
-        <v>1353300</v>
+        <v>556200</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>MG16332</t>
-        </is>
-      </c>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>MG16332</t>
+          <t>MG40210</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>LANZADOR  ARCO Y FLECA CON LASER MG16332</t>
+          <t>SONAJERO OSO MG40210</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -15527,7 +15524,7 @@
         </is>
       </c>
       <c r="J335" t="n">
-        <v>4</v>
+        <v>363</v>
       </c>
       <c r="K335" t="n">
         <v>0</v>
@@ -15536,30 +15533,35 @@
         <v>0</v>
       </c>
       <c r="M335" t="n">
-        <v>4</v>
+        <v>363</v>
       </c>
       <c r="N335" t="n">
-        <v>8439.969999999999</v>
+        <v>571.87</v>
       </c>
       <c r="O335" t="n">
-        <v>33759.88</v>
+        <v>207588.81</v>
       </c>
       <c r="P335" t="n">
-        <v>29500</v>
+        <v>2500</v>
       </c>
       <c r="Q335" t="n">
-        <v>118000</v>
+        <v>907500</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>MG20430</t>
+          <t>MG40720</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>MG40720</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>SET PLASTILINA CON MOLDES BARBERIA MALETA MG20430</t>
+          <t>MAQUINA DE COSER MINI MG40720</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -15573,7 +15575,7 @@
         </is>
       </c>
       <c r="J336" t="n">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="K336" t="n">
         <v>0</v>
@@ -15582,115 +15584,18 @@
         <v>0</v>
       </c>
       <c r="M336" t="n">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="N336" t="n">
-        <v>12189.831111111</v>
+        <v>9917.040000000001</v>
       </c>
       <c r="O336" t="n">
-        <v>219416.959999998</v>
+        <v>634690.5600000001</v>
       </c>
       <c r="P336" t="n">
-        <v>30900</v>
+        <v>15900</v>
       </c>
       <c r="Q336" t="n">
-        <v>556200</v>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" t="inlineStr">
-        <is>
-          <t>MG40210</t>
-        </is>
-      </c>
-      <c r="C337" t="inlineStr">
-        <is>
-          <t>SONAJERO OSO MG40210</t>
-        </is>
-      </c>
-      <c r="E337" t="inlineStr">
-        <is>
-          <t>DIDACTICO</t>
-        </is>
-      </c>
-      <c r="I337" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J337" t="n">
-        <v>363</v>
-      </c>
-      <c r="K337" t="n">
-        <v>0</v>
-      </c>
-      <c r="L337" t="n">
-        <v>0</v>
-      </c>
-      <c r="M337" t="n">
-        <v>363</v>
-      </c>
-      <c r="N337" t="n">
-        <v>571.87</v>
-      </c>
-      <c r="O337" t="n">
-        <v>207588.81</v>
-      </c>
-      <c r="P337" t="n">
-        <v>2500</v>
-      </c>
-      <c r="Q337" t="n">
-        <v>907500</v>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" t="inlineStr">
-        <is>
-          <t>MG40720</t>
-        </is>
-      </c>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>MG40720</t>
-        </is>
-      </c>
-      <c r="C338" t="inlineStr">
-        <is>
-          <t>MAQUINA DE COSER MINI MG40720</t>
-        </is>
-      </c>
-      <c r="E338" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
-        </is>
-      </c>
-      <c r="I338" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J338" t="n">
-        <v>64</v>
-      </c>
-      <c r="K338" t="n">
-        <v>0</v>
-      </c>
-      <c r="L338" t="n">
-        <v>0</v>
-      </c>
-      <c r="M338" t="n">
-        <v>64</v>
-      </c>
-      <c r="N338" t="n">
-        <v>9917.040000000001</v>
-      </c>
-      <c r="O338" t="n">
-        <v>634690.5600000001</v>
-      </c>
-      <c r="P338" t="n">
-        <v>15900</v>
-      </c>
-      <c r="Q338" t="n">
         <v>1017600</v>
       </c>
     </row>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -2675,10 +2675,10 @@
         <v>40</v>
       </c>
       <c r="N55" t="n">
-        <v>10899.560863636</v>
+        <v>10752.93</v>
       </c>
       <c r="O55" t="n">
-        <v>435982.43454544</v>
+        <v>430117.2</v>
       </c>
       <c r="P55" t="n">
         <v>18400</v>
@@ -2888,10 +2888,10 @@
         <v>248</v>
       </c>
       <c r="N60" t="n">
-        <v>13609.886922141</v>
+        <v>13593.35</v>
       </c>
       <c r="O60" t="n">
-        <v>3375251.956690968</v>
+        <v>3371150.8</v>
       </c>
       <c r="P60" t="n">
         <v>25500</v>
@@ -3065,10 +3065,10 @@
         <v>350</v>
       </c>
       <c r="N64" t="n">
-        <v>2583.5545646704</v>
+        <v>2582.2549874182</v>
       </c>
       <c r="O64" t="n">
-        <v>904244.0976346399</v>
+        <v>903789.24559637</v>
       </c>
       <c r="P64" t="n">
         <v>4500</v>
@@ -3157,10 +3157,10 @@
         <v>2592</v>
       </c>
       <c r="N66" t="n">
-        <v>3160.7464443118</v>
+        <v>3158.8608391782</v>
       </c>
       <c r="O66" t="n">
-        <v>8192654.783656185</v>
+        <v>8187767.295149894</v>
       </c>
       <c r="P66" t="n">
         <v>5600</v>
@@ -4389,10 +4389,10 @@
         <v>1356</v>
       </c>
       <c r="N93" t="n">
-        <v>4372.0654674395</v>
+        <v>4371.1712628708</v>
       </c>
       <c r="O93" t="n">
-        <v>5928520.773847962</v>
+        <v>5927308.232452805</v>
       </c>
       <c r="P93" t="n">
         <v>8900</v>
@@ -5753,10 +5753,10 @@
         <v>352</v>
       </c>
       <c r="N123" t="n">
-        <v>8799.4655328798</v>
+        <v>8794.48</v>
       </c>
       <c r="O123" t="n">
-        <v>3097411.86757369</v>
+        <v>3095656.96</v>
       </c>
       <c r="P123" t="n">
         <v>14500</v>
@@ -6145,10 +6145,10 @@
         <v>18</v>
       </c>
       <c r="N132" t="n">
-        <v>57801.91954023</v>
+        <v>56503</v>
       </c>
       <c r="O132" t="n">
-        <v>1040434.55172414</v>
+        <v>1017054</v>
       </c>
       <c r="P132" t="n">
         <v>90500</v>
@@ -6772,10 +6772,10 @@
         <v>273</v>
       </c>
       <c r="N146" t="n">
-        <v>22761.155411606</v>
+        <v>22730.48</v>
       </c>
       <c r="O146" t="n">
-        <v>6213795.427368438</v>
+        <v>6205421.04</v>
       </c>
       <c r="P146" t="n">
         <v>36900</v>
@@ -7002,10 +7002,10 @@
         <v>148</v>
       </c>
       <c r="N151" t="n">
-        <v>5455.0456387665</v>
+        <v>5431.12</v>
       </c>
       <c r="O151" t="n">
-        <v>807346.754537442</v>
+        <v>803805.76</v>
       </c>
       <c r="P151" t="n">
         <v>8900</v>
@@ -7869,10 +7869,10 @@
         <v>421</v>
       </c>
       <c r="N170" t="n">
-        <v>18023.2064</v>
+        <v>18016</v>
       </c>
       <c r="O170" t="n">
-        <v>7587769.8944</v>
+        <v>7584736</v>
       </c>
       <c r="P170" t="n">
         <v>29900</v>
@@ -8470,10 +8470,10 @@
         <v>210</v>
       </c>
       <c r="N183" t="n">
-        <v>10448.584837545</v>
+        <v>10411</v>
       </c>
       <c r="O183" t="n">
-        <v>2194202.81588445</v>
+        <v>2186310</v>
       </c>
       <c r="P183" t="n">
         <v>16900</v>
@@ -11131,10 +11131,10 @@
         <v>385</v>
       </c>
       <c r="N241" t="n">
-        <v>3652.664695122</v>
+        <v>3639.35</v>
       </c>
       <c r="O241" t="n">
-        <v>1406275.90762197</v>
+        <v>1401149.75</v>
       </c>
       <c r="P241" t="n">
         <v>7500</v>
@@ -12705,10 +12705,10 @@
         <v>1436</v>
       </c>
       <c r="N275" t="n">
-        <v>345.63428985635</v>
+        <v>345.55838597724</v>
       </c>
       <c r="O275" t="n">
-        <v>496330.8402337186</v>
+        <v>496221.8422633166</v>
       </c>
       <c r="P275" t="n">
         <v>600</v>
@@ -12749,10 +12749,10 @@
         <v>11416</v>
       </c>
       <c r="N276" t="n">
-        <v>711.87861852814</v>
+        <v>711.33664519481</v>
       </c>
       <c r="O276" t="n">
-        <v>8126806.309117246</v>
+        <v>8120619.141543951</v>
       </c>
       <c r="P276" t="n">
         <v>900</v>
@@ -14174,10 +14174,10 @@
         <v>19</v>
       </c>
       <c r="N306" t="n">
-        <v>4234.4238541667</v>
+        <v>4190.77</v>
       </c>
       <c r="O306" t="n">
-        <v>80454.0532291673</v>
+        <v>79624.63</v>
       </c>
       <c r="P306" t="n">
         <v>5900</v>
@@ -14223,10 +14223,10 @@
         <v>104</v>
       </c>
       <c r="N307" t="n">
-        <v>3503.9263942308</v>
+        <v>3499.72</v>
       </c>
       <c r="O307" t="n">
-        <v>364408.3450000032</v>
+        <v>363970.88</v>
       </c>
       <c r="P307" t="n">
         <v>6900</v>
@@ -14272,10 +14272,10 @@
         <v>158</v>
       </c>
       <c r="N308" t="n">
-        <v>4593.2494352159</v>
+        <v>4578.04</v>
       </c>
       <c r="O308" t="n">
-        <v>725733.4107641123</v>
+        <v>723330.3199999999</v>
       </c>
       <c r="P308" t="n">
         <v>7500</v>
@@ -14792,10 +14792,10 @@
         <v>499</v>
       </c>
       <c r="N319" t="n">
-        <v>7056.0857581657</v>
+        <v>7046.9398269522</v>
       </c>
       <c r="O319" t="n">
-        <v>3520986.793324684</v>
+        <v>3516422.973649148</v>
       </c>
       <c r="P319" t="n">
         <v>9900</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-19</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-20</t>
         </is>
       </c>
     </row>
@@ -1199,10 +1199,10 @@
         <v>180</v>
       </c>
       <c r="N20" t="n">
-        <v>3926.8370787689</v>
+        <v>3926.8370772443</v>
       </c>
       <c r="O20" t="n">
-        <v>706830.6741784021</v>
+        <v>706830.673903974</v>
       </c>
       <c r="P20" t="n">
         <v>4800</v>
@@ -1433,10 +1433,10 @@
         <v>118</v>
       </c>
       <c r="N26" t="n">
-        <v>3910.6279357798</v>
+        <v>3910.6279310345</v>
       </c>
       <c r="O26" t="n">
-        <v>461454.0964220164</v>
+        <v>461454.095862071</v>
       </c>
       <c r="P26" t="n">
         <v>9100</v>
@@ -3065,10 +3065,10 @@
         <v>350</v>
       </c>
       <c r="N64" t="n">
-        <v>2582.2549874182</v>
+        <v>2582.2549620637</v>
       </c>
       <c r="O64" t="n">
-        <v>903789.24559637</v>
+        <v>903789.2367222951</v>
       </c>
       <c r="P64" t="n">
         <v>4500</v>
@@ -3111,10 +3111,10 @@
         <v>1232</v>
       </c>
       <c r="N65" t="n">
-        <v>5216.8959284856</v>
+        <v>5216.8958877086</v>
       </c>
       <c r="O65" t="n">
-        <v>6427215.783894259</v>
+        <v>6427215.733656995</v>
       </c>
       <c r="P65" t="n">
         <v>8500</v>
@@ -3520,10 +3520,10 @@
         <v>346</v>
       </c>
       <c r="N74" t="n">
-        <v>4890.9300530504</v>
+        <v>4890.9300534045</v>
       </c>
       <c r="O74" t="n">
-        <v>1692261.798355438</v>
+        <v>1692261.798477957</v>
       </c>
       <c r="P74" t="n">
         <v>8200</v>
@@ -3748,10 +3748,10 @@
         <v>216</v>
       </c>
       <c r="N79" t="n">
-        <v>3594.2530785869</v>
+        <v>3594.2530181818</v>
       </c>
       <c r="O79" t="n">
-        <v>776358.6649747704</v>
+        <v>776358.6519272688</v>
       </c>
       <c r="P79" t="n">
         <v>6500</v>
@@ -3930,10 +3930,10 @@
         <v>3200</v>
       </c>
       <c r="N83" t="n">
-        <v>616.01871807046</v>
+        <v>616.01871794872</v>
       </c>
       <c r="O83" t="n">
-        <v>1971259.897825472</v>
+        <v>1971259.897435904</v>
       </c>
       <c r="P83" t="n">
         <v>800</v>
@@ -4207,10 +4207,10 @@
         <v>336</v>
       </c>
       <c r="N89" t="n">
-        <v>12422.462948052</v>
+        <v>12422.462959583</v>
       </c>
       <c r="O89" t="n">
-        <v>4173947.550545472</v>
+        <v>4173947.554419888</v>
       </c>
       <c r="P89" t="n">
         <v>19900</v>
@@ -4299,10 +4299,10 @@
         <v>1800</v>
       </c>
       <c r="N91" t="n">
-        <v>3472.2761978447</v>
+        <v>3472.2762167406</v>
       </c>
       <c r="O91" t="n">
-        <v>6250097.15612046</v>
+        <v>6250097.19013308</v>
       </c>
       <c r="P91" t="n">
         <v>5900</v>
@@ -4389,10 +4389,10 @@
         <v>1356</v>
       </c>
       <c r="N93" t="n">
-        <v>4371.1712628708</v>
+        <v>4371.1712629569</v>
       </c>
       <c r="O93" t="n">
-        <v>5927308.232452805</v>
+        <v>5927308.232569557</v>
       </c>
       <c r="P93" t="n">
         <v>8900</v>
@@ -5794,10 +5794,10 @@
         <v>432</v>
       </c>
       <c r="N124" t="n">
-        <v>2029.8741413584</v>
+        <v>2029.8741689828</v>
       </c>
       <c r="O124" t="n">
-        <v>876905.6290668289</v>
+        <v>876905.6410005696</v>
       </c>
       <c r="P124" t="n">
         <v>3600</v>
@@ -6007,10 +6007,10 @@
         <v>310</v>
       </c>
       <c r="N129" t="n">
-        <v>2680.7396939413</v>
+        <v>2680.7396933667</v>
       </c>
       <c r="O129" t="n">
-        <v>831029.3051218031</v>
+        <v>831029.304943677</v>
       </c>
       <c r="P129" t="n">
         <v>4900</v>
@@ -6286,10 +6286,10 @@
         <v>36</v>
       </c>
       <c r="N135" t="n">
-        <v>4285.1963341646</v>
+        <v>4285.1963420724</v>
       </c>
       <c r="O135" t="n">
-        <v>154267.0680299256</v>
+        <v>154267.0683146064</v>
       </c>
       <c r="P135" t="n">
         <v>6900</v>
@@ -6460,10 +6460,10 @@
         <v>948</v>
       </c>
       <c r="N139" t="n">
-        <v>4814.2679260066</v>
+        <v>4814.2679256837</v>
       </c>
       <c r="O139" t="n">
-        <v>4563925.993854256</v>
+        <v>4563925.993548147</v>
       </c>
       <c r="P139" t="n">
         <v>9900</v>
@@ -7777,10 +7777,10 @@
         <v>680</v>
       </c>
       <c r="N168" t="n">
-        <v>1778.4728348758</v>
+        <v>1778.4728413344</v>
       </c>
       <c r="O168" t="n">
-        <v>1209361.527715544</v>
+        <v>1209361.532107392</v>
       </c>
       <c r="P168" t="n">
         <v>4900</v>
@@ -9298,10 +9298,10 @@
         <v>129</v>
       </c>
       <c r="N201" t="n">
-        <v>3903.7392422907</v>
+        <v>3903.7394479074</v>
       </c>
       <c r="O201" t="n">
-        <v>503582.3622555003</v>
+        <v>503582.3887800546</v>
       </c>
       <c r="P201" t="n">
         <v>7500</v>
@@ -9656,10 +9656,10 @@
         <v>144</v>
       </c>
       <c r="N209" t="n">
-        <v>5869.1725284974</v>
+        <v>5869.172402529</v>
       </c>
       <c r="O209" t="n">
-        <v>845160.8441036256</v>
+        <v>845160.825964176</v>
       </c>
       <c r="P209" t="n">
         <v>9500</v>
@@ -10438,10 +10438,10 @@
         <v>192</v>
       </c>
       <c r="N226" t="n">
-        <v>17075.989518828</v>
+        <v>17075.989518156</v>
       </c>
       <c r="O226" t="n">
-        <v>3278589.987614976</v>
+        <v>3278589.987485952</v>
       </c>
       <c r="P226" t="n">
         <v>27500</v>
@@ -11729,10 +11729,10 @@
         <v>864</v>
       </c>
       <c r="N254" t="n">
-        <v>1516.0387397625</v>
+        <v>1516.0387386003</v>
       </c>
       <c r="O254" t="n">
-        <v>1309857.4711548</v>
+        <v>1309857.470150659</v>
       </c>
       <c r="P254" t="n">
         <v>2300</v>
@@ -11994,7 +11994,7 @@
         </is>
       </c>
       <c r="J260" t="n">
-        <v>432</v>
+        <v>402</v>
       </c>
       <c r="K260" t="n">
         <v>0</v>
@@ -12003,19 +12003,19 @@
         <v>0</v>
       </c>
       <c r="M260" t="n">
-        <v>432</v>
+        <v>402</v>
       </c>
       <c r="N260" t="n">
         <v>11690</v>
       </c>
       <c r="O260" t="n">
-        <v>5050080</v>
+        <v>4699380</v>
       </c>
       <c r="P260" t="n">
         <v>18900</v>
       </c>
       <c r="Q260" t="n">
-        <v>8164800</v>
+        <v>7597800</v>
       </c>
     </row>
     <row r="261">
@@ -12092,7 +12092,7 @@
         </is>
       </c>
       <c r="J262" t="n">
-        <v>432</v>
+        <v>396</v>
       </c>
       <c r="K262" t="n">
         <v>0</v>
@@ -12101,19 +12101,19 @@
         <v>0</v>
       </c>
       <c r="M262" t="n">
-        <v>432</v>
+        <v>396</v>
       </c>
       <c r="N262" t="n">
         <v>9736</v>
       </c>
       <c r="O262" t="n">
-        <v>4205952</v>
+        <v>3855456</v>
       </c>
       <c r="P262" t="n">
         <v>15900</v>
       </c>
       <c r="Q262" t="n">
-        <v>6868800</v>
+        <v>6296400</v>
       </c>
     </row>
     <row r="263">
@@ -12524,10 +12524,10 @@
         <v>1440</v>
       </c>
       <c r="N271" t="n">
-        <v>1690.8700093809</v>
+        <v>1690.8700094029</v>
       </c>
       <c r="O271" t="n">
-        <v>2434852.813508496</v>
+        <v>2434852.813540176</v>
       </c>
       <c r="P271" t="n">
         <v>3000</v>
@@ -12705,10 +12705,10 @@
         <v>1436</v>
       </c>
       <c r="N275" t="n">
-        <v>345.55838597724</v>
+        <v>345.55838583542</v>
       </c>
       <c r="O275" t="n">
-        <v>496221.8422633166</v>
+        <v>496221.8420596631</v>
       </c>
       <c r="P275" t="n">
         <v>600</v>
@@ -12749,10 +12749,10 @@
         <v>11416</v>
       </c>
       <c r="N276" t="n">
-        <v>711.33664519481</v>
+        <v>711.33664496242</v>
       </c>
       <c r="O276" t="n">
-        <v>8120619.141543951</v>
+        <v>8120619.138890986</v>
       </c>
       <c r="P276" t="n">
         <v>900</v>
@@ -13078,10 +13078,10 @@
         <v>15264</v>
       </c>
       <c r="N283" t="n">
-        <v>703.7947515264</v>
+        <v>703.7947376286299</v>
       </c>
       <c r="O283" t="n">
-        <v>10742723.08729897</v>
+        <v>10742722.87516341</v>
       </c>
       <c r="P283" t="n">
         <v>900</v>
@@ -13263,10 +13263,10 @@
         <v>208</v>
       </c>
       <c r="N287" t="n">
-        <v>6078.9925962596</v>
+        <v>6078.9926048565</v>
       </c>
       <c r="O287" t="n">
-        <v>1264430.460021997</v>
+        <v>1264430.461810152</v>
       </c>
       <c r="P287" t="n">
         <v>18500</v>
@@ -14459,10 +14459,10 @@
         <v>11</v>
       </c>
       <c r="N312" t="n">
-        <v>14751.820327869</v>
+        <v>14751.820338983</v>
       </c>
       <c r="O312" t="n">
-        <v>162270.023606559</v>
+        <v>162270.023728813</v>
       </c>
       <c r="P312" t="n">
         <v>37100</v>
@@ -14792,10 +14792,10 @@
         <v>499</v>
       </c>
       <c r="N319" t="n">
-        <v>7046.9398269522</v>
+        <v>7046.9398267273</v>
       </c>
       <c r="O319" t="n">
-        <v>3516422.973649148</v>
+        <v>3516422.973536923</v>
       </c>
       <c r="P319" t="n">
         <v>9900</v>
@@ -15075,10 +15075,10 @@
         <v>1450</v>
       </c>
       <c r="N325" t="n">
-        <v>704.89694272446</v>
+        <v>704.89696969697</v>
       </c>
       <c r="O325" t="n">
-        <v>1022100.566950467</v>
+        <v>1022100.606060607</v>
       </c>
       <c r="P325" t="n">
         <v>900</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-20</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-21</t>
         </is>
       </c>
     </row>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -1480,10 +1480,10 @@
         <v>20</v>
       </c>
       <c r="N27" t="n">
-        <v>9392.0756666667</v>
+        <v>9392.075964912299</v>
       </c>
       <c r="O27" t="n">
-        <v>187841.513333334</v>
+        <v>187841.519298246</v>
       </c>
       <c r="P27" t="n">
         <v>18500</v>
@@ -3065,10 +3065,10 @@
         <v>350</v>
       </c>
       <c r="N64" t="n">
-        <v>2582.2549620637</v>
+        <v>2582.2549607893</v>
       </c>
       <c r="O64" t="n">
-        <v>903789.2367222951</v>
+        <v>903789.2362762551</v>
       </c>
       <c r="P64" t="n">
         <v>4500</v>
@@ -3111,10 +3111,10 @@
         <v>1232</v>
       </c>
       <c r="N65" t="n">
-        <v>5216.8958877086</v>
+        <v>5216.8958858357</v>
       </c>
       <c r="O65" t="n">
-        <v>6427215.733656995</v>
+        <v>6427215.731349583</v>
       </c>
       <c r="P65" t="n">
         <v>8500</v>
@@ -3157,10 +3157,10 @@
         <v>2592</v>
       </c>
       <c r="N66" t="n">
-        <v>3158.8608391782</v>
+        <v>3158.86083922</v>
       </c>
       <c r="O66" t="n">
-        <v>8187767.295149894</v>
+        <v>8187767.29525824</v>
       </c>
       <c r="P66" t="n">
         <v>5600</v>
@@ -3341,10 +3341,10 @@
         <v>480</v>
       </c>
       <c r="N70" t="n">
-        <v>3795.7100076176</v>
+        <v>3795.7100076234</v>
       </c>
       <c r="O70" t="n">
-        <v>1821940.803656448</v>
+        <v>1821940.803659232</v>
       </c>
       <c r="P70" t="n">
         <v>6200</v>
@@ -3520,10 +3520,10 @@
         <v>346</v>
       </c>
       <c r="N74" t="n">
-        <v>4890.9300534045</v>
+        <v>4890.9300534402</v>
       </c>
       <c r="O74" t="n">
-        <v>1692261.798477957</v>
+        <v>1692261.798490309</v>
       </c>
       <c r="P74" t="n">
         <v>8200</v>
@@ -3748,10 +3748,10 @@
         <v>216</v>
       </c>
       <c r="N79" t="n">
-        <v>3594.2530181818</v>
+        <v>3594.2529978118</v>
       </c>
       <c r="O79" t="n">
-        <v>776358.6519272688</v>
+        <v>776358.6475273488</v>
       </c>
       <c r="P79" t="n">
         <v>6500</v>
@@ -4299,10 +4299,10 @@
         <v>1800</v>
       </c>
       <c r="N91" t="n">
-        <v>3472.2762167406</v>
+        <v>3472.276224504</v>
       </c>
       <c r="O91" t="n">
-        <v>6250097.19013308</v>
+        <v>6250097.2041072</v>
       </c>
       <c r="P91" t="n">
         <v>5900</v>
@@ -4389,10 +4389,10 @@
         <v>1356</v>
       </c>
       <c r="N93" t="n">
-        <v>4371.1712629569</v>
+        <v>4371.7675214841</v>
       </c>
       <c r="O93" t="n">
-        <v>5927308.232569557</v>
+        <v>5928116.75913244</v>
       </c>
       <c r="P93" t="n">
         <v>8900</v>
@@ -4438,10 +4438,10 @@
         <v>2144</v>
       </c>
       <c r="N94" t="n">
-        <v>4648.6</v>
+        <v>4649.4131187686</v>
       </c>
       <c r="O94" t="n">
-        <v>9966598.4</v>
+        <v>9968341.726639878</v>
       </c>
       <c r="P94" t="n">
         <v>8900</v>
@@ -5960,22 +5960,22 @@
         <v>0</v>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M128" t="n">
-        <v>180</v>
+        <v>156</v>
       </c>
       <c r="N128" t="n">
-        <v>24538.02</v>
+        <v>25442.647465438</v>
       </c>
       <c r="O128" t="n">
-        <v>4416843.6</v>
+        <v>3969053.004608328</v>
       </c>
       <c r="P128" t="n">
         <v>52900</v>
       </c>
       <c r="Q128" t="n">
-        <v>9522000</v>
+        <v>8252400</v>
       </c>
     </row>
     <row r="129">
@@ -6286,10 +6286,10 @@
         <v>36</v>
       </c>
       <c r="N135" t="n">
-        <v>4285.1963420724</v>
+        <v>4285.1963819095</v>
       </c>
       <c r="O135" t="n">
-        <v>154267.0683146064</v>
+        <v>154267.069748742</v>
       </c>
       <c r="P135" t="n">
         <v>6900</v>
@@ -6956,10 +6956,10 @@
         <v>221</v>
       </c>
       <c r="N150" t="n">
-        <v>8332.779612403099</v>
+        <v>8332.7796073298</v>
       </c>
       <c r="O150" t="n">
-        <v>1841544.294341085</v>
+        <v>1841544.293219886</v>
       </c>
       <c r="P150" t="n">
         <v>14900</v>
@@ -7777,10 +7777,10 @@
         <v>680</v>
       </c>
       <c r="N168" t="n">
-        <v>1778.4728413344</v>
+        <v>1778.4728487518</v>
       </c>
       <c r="O168" t="n">
-        <v>1209361.532107392</v>
+        <v>1209361.537151224</v>
       </c>
       <c r="P168" t="n">
         <v>4900</v>
@@ -9114,10 +9114,10 @@
         <v>252</v>
       </c>
       <c r="N197" t="n">
-        <v>6414</v>
+        <v>6426.9445005045</v>
       </c>
       <c r="O197" t="n">
-        <v>1616328</v>
+        <v>1619590.014127134</v>
       </c>
       <c r="P197" t="n">
         <v>10900</v>
@@ -9298,10 +9298,10 @@
         <v>129</v>
       </c>
       <c r="N201" t="n">
-        <v>3903.7394479074</v>
+        <v>3903.7394652406</v>
       </c>
       <c r="O201" t="n">
-        <v>503582.3887800546</v>
+        <v>503582.3910160374</v>
       </c>
       <c r="P201" t="n">
         <v>7500</v>
@@ -9794,10 +9794,10 @@
         <v>456</v>
       </c>
       <c r="N212" t="n">
-        <v>6645</v>
+        <v>6648.7102177554</v>
       </c>
       <c r="O212" t="n">
-        <v>3030120</v>
+        <v>3031811.859296462</v>
       </c>
       <c r="P212" t="n">
         <v>10900</v>
@@ -13078,10 +13078,10 @@
         <v>15264</v>
       </c>
       <c r="N283" t="n">
-        <v>703.7947376286299</v>
+        <v>703.79473431536</v>
       </c>
       <c r="O283" t="n">
-        <v>10742722.87516341</v>
+        <v>10742722.82458965</v>
       </c>
       <c r="P283" t="n">
         <v>900</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q336"/>
+  <dimension ref="A1:Q332"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-21</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-22</t>
         </is>
       </c>
     </row>
@@ -1777,10 +1777,10 @@
         <v>36</v>
       </c>
       <c r="N34" t="n">
-        <v>200072.20240385</v>
+        <v>200072.2037234</v>
       </c>
       <c r="O34" t="n">
-        <v>7202599.2865386</v>
+        <v>7202599.334042399</v>
       </c>
       <c r="P34" t="n">
         <v>312000</v>
@@ -1824,10 +1824,10 @@
         <v>4</v>
       </c>
       <c r="N35" t="n">
-        <v>344599.17844444</v>
+        <v>344599.17815789</v>
       </c>
       <c r="O35" t="n">
-        <v>1378396.71377776</v>
+        <v>1378396.71263156</v>
       </c>
       <c r="P35" t="n">
         <v>532900</v>
@@ -3111,10 +3111,10 @@
         <v>1232</v>
       </c>
       <c r="N65" t="n">
-        <v>5216.8958858357</v>
+        <v>5216.8958827104</v>
       </c>
       <c r="O65" t="n">
-        <v>6427215.731349583</v>
+        <v>6427215.727499212</v>
       </c>
       <c r="P65" t="n">
         <v>8500</v>
@@ -3157,10 +3157,10 @@
         <v>2592</v>
       </c>
       <c r="N66" t="n">
-        <v>3158.86083922</v>
+        <v>3158.8608398885</v>
       </c>
       <c r="O66" t="n">
-        <v>8187767.29525824</v>
+        <v>8187767.296990992</v>
       </c>
       <c r="P66" t="n">
         <v>5600</v>
@@ -3341,10 +3341,10 @@
         <v>480</v>
       </c>
       <c r="N70" t="n">
-        <v>3795.7100076234</v>
+        <v>3795.7100076292</v>
       </c>
       <c r="O70" t="n">
-        <v>1821940.803659232</v>
+        <v>1821940.803662016</v>
       </c>
       <c r="P70" t="n">
         <v>6200</v>
@@ -3748,10 +3748,10 @@
         <v>216</v>
       </c>
       <c r="N79" t="n">
-        <v>3594.2529978118</v>
+        <v>3594.2529721816</v>
       </c>
       <c r="O79" t="n">
-        <v>776358.6475273488</v>
+        <v>776358.6419912255</v>
       </c>
       <c r="P79" t="n">
         <v>6500</v>
@@ -4299,10 +4299,10 @@
         <v>1800</v>
       </c>
       <c r="N91" t="n">
-        <v>3472.276224504</v>
+        <v>3472.2762270961</v>
       </c>
       <c r="O91" t="n">
-        <v>6250097.2041072</v>
+        <v>6250097.20877298</v>
       </c>
       <c r="P91" t="n">
         <v>5900</v>
@@ -4389,10 +4389,10 @@
         <v>1356</v>
       </c>
       <c r="N93" t="n">
-        <v>4371.7675214841</v>
+        <v>4371.1712631292</v>
       </c>
       <c r="O93" t="n">
-        <v>5928116.75913244</v>
+        <v>5927308.232803196</v>
       </c>
       <c r="P93" t="n">
         <v>8900</v>
@@ -4438,10 +4438,10 @@
         <v>2144</v>
       </c>
       <c r="N94" t="n">
-        <v>4649.4131187686</v>
+        <v>4648.6</v>
       </c>
       <c r="O94" t="n">
-        <v>9968341.726639878</v>
+        <v>9966598.4</v>
       </c>
       <c r="P94" t="n">
         <v>8900</v>
@@ -5666,10 +5666,10 @@
         <v>480</v>
       </c>
       <c r="N121" t="n">
-        <v>4196.872541806</v>
+        <v>4196.8725453531</v>
       </c>
       <c r="O121" t="n">
-        <v>2014498.82006688</v>
+        <v>2014498.821769488</v>
       </c>
       <c r="P121" t="n">
         <v>5900</v>
@@ -5835,10 +5835,10 @@
         <v>528</v>
       </c>
       <c r="N125" t="n">
-        <v>22485.695454545</v>
+        <v>22485.695448799</v>
       </c>
       <c r="O125" t="n">
-        <v>11872447.19999976</v>
+        <v>11872447.19696587</v>
       </c>
       <c r="P125" t="n">
         <v>36500</v>
@@ -5954,22 +5954,22 @@
         </is>
       </c>
       <c r="J128" t="n">
-        <v>180</v>
+        <v>156</v>
       </c>
       <c r="K128" t="n">
         <v>0</v>
       </c>
       <c r="L128" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
         <v>156</v>
       </c>
       <c r="N128" t="n">
-        <v>25442.647465438</v>
+        <v>24538.02</v>
       </c>
       <c r="O128" t="n">
-        <v>3969053.004608328</v>
+        <v>3827931.12</v>
       </c>
       <c r="P128" t="n">
         <v>52900</v>
@@ -6286,10 +6286,10 @@
         <v>36</v>
       </c>
       <c r="N135" t="n">
-        <v>4285.1963819095</v>
+        <v>4285.1964141414</v>
       </c>
       <c r="O135" t="n">
-        <v>154267.069748742</v>
+        <v>154267.0709090904</v>
       </c>
       <c r="P135" t="n">
         <v>6900</v>
@@ -7397,7 +7397,7 @@
         </is>
       </c>
       <c r="J160" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="K160" t="n">
         <v>0</v>
@@ -7406,19 +7406,19 @@
         <v>0</v>
       </c>
       <c r="M160" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="N160" t="n">
         <v>38449</v>
       </c>
       <c r="O160" t="n">
-        <v>1153470</v>
+        <v>692082</v>
       </c>
       <c r="P160" t="n">
         <v>62900</v>
       </c>
       <c r="Q160" t="n">
-        <v>1887000</v>
+        <v>1132200</v>
       </c>
     </row>
     <row r="161">
@@ -7654,12 +7654,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>C4289</t>
+          <t>C4294</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>FICHAS DE ARMAR C4289</t>
+          <t>FICHAS DE ARMAR C4294</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -7673,7 +7673,7 @@
         </is>
       </c>
       <c r="J166" t="n">
-        <v>11</v>
+        <v>128</v>
       </c>
       <c r="K166" t="n">
         <v>0</v>
@@ -7682,30 +7682,30 @@
         <v>0</v>
       </c>
       <c r="M166" t="n">
-        <v>11</v>
+        <v>128</v>
       </c>
       <c r="N166" t="n">
-        <v>23521.623</v>
+        <v>3486</v>
       </c>
       <c r="O166" t="n">
-        <v>258737.853</v>
+        <v>446208</v>
       </c>
       <c r="P166" t="n">
-        <v>39000</v>
+        <v>6900</v>
       </c>
       <c r="Q166" t="n">
-        <v>429000</v>
+        <v>883200</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>C4294</t>
+          <t>C4295</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>FICHAS DE ARMAR C4294</t>
+          <t>FICHAS DE ARMAR C4295</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -7719,7 +7719,7 @@
         </is>
       </c>
       <c r="J167" t="n">
-        <v>128</v>
+        <v>680</v>
       </c>
       <c r="K167" t="n">
         <v>0</v>
@@ -7728,30 +7728,30 @@
         <v>0</v>
       </c>
       <c r="M167" t="n">
-        <v>128</v>
+        <v>680</v>
       </c>
       <c r="N167" t="n">
-        <v>3486</v>
+        <v>1778.4728562081</v>
       </c>
       <c r="O167" t="n">
-        <v>446208</v>
+        <v>1209361.542221508</v>
       </c>
       <c r="P167" t="n">
-        <v>6900</v>
+        <v>4900</v>
       </c>
       <c r="Q167" t="n">
-        <v>883200</v>
+        <v>3332000</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>C4295</t>
+          <t>C4302</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>FICHAS DE ARMAR C4295</t>
+          <t>MUÑECA GRANDE CON VESTIDO Y SOMBRERO EN BOLSA C4302</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -7765,7 +7765,7 @@
         </is>
       </c>
       <c r="J168" t="n">
-        <v>680</v>
+        <v>192</v>
       </c>
       <c r="K168" t="n">
         <v>0</v>
@@ -7774,30 +7774,30 @@
         <v>0</v>
       </c>
       <c r="M168" t="n">
-        <v>680</v>
+        <v>192</v>
       </c>
       <c r="N168" t="n">
-        <v>1778.4728487518</v>
+        <v>22739</v>
       </c>
       <c r="O168" t="n">
-        <v>1209361.537151224</v>
+        <v>4365888</v>
       </c>
       <c r="P168" t="n">
-        <v>4900</v>
+        <v>36900</v>
       </c>
       <c r="Q168" t="n">
-        <v>3332000</v>
+        <v>7084800</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>C4302</t>
+          <t>C4303</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>MUÑECA GRANDE CON VESTIDO Y SOMBRERO EN BOLSA C4302</t>
+          <t>BEBE CON PIJAMA MED BOLSA PVC C4303</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -7811,7 +7811,7 @@
         </is>
       </c>
       <c r="J169" t="n">
-        <v>192</v>
+        <v>421</v>
       </c>
       <c r="K169" t="n">
         <v>0</v>
@@ -7820,30 +7820,30 @@
         <v>0</v>
       </c>
       <c r="M169" t="n">
-        <v>192</v>
+        <v>421</v>
       </c>
       <c r="N169" t="n">
-        <v>22739</v>
+        <v>18016</v>
       </c>
       <c r="O169" t="n">
-        <v>4365888</v>
+        <v>7584736</v>
       </c>
       <c r="P169" t="n">
-        <v>36900</v>
+        <v>29900</v>
       </c>
       <c r="Q169" t="n">
-        <v>7084800</v>
+        <v>12587900</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>C4303</t>
+          <t>C4304</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>BEBE CON PIJAMA MED BOLSA PVC C4303</t>
+          <t>MUÑECA BEBE CON CHUPO EN BOLSA C4304</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -7857,7 +7857,7 @@
         </is>
       </c>
       <c r="J170" t="n">
-        <v>421</v>
+        <v>160</v>
       </c>
       <c r="K170" t="n">
         <v>0</v>
@@ -7866,30 +7866,30 @@
         <v>0</v>
       </c>
       <c r="M170" t="n">
-        <v>421</v>
+        <v>160</v>
       </c>
       <c r="N170" t="n">
-        <v>18016</v>
+        <v>16058</v>
       </c>
       <c r="O170" t="n">
-        <v>7584736</v>
+        <v>2569280</v>
       </c>
       <c r="P170" t="n">
-        <v>29900</v>
+        <v>25900</v>
       </c>
       <c r="Q170" t="n">
-        <v>12587900</v>
+        <v>4144000</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>C4304</t>
+          <t>C4305</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>MUÑECA BEBE CON CHUPO EN BOLSA C4304</t>
+          <t>MUÑECA BEBE GRANDE CON PIJAMA EN BOLSA C4305</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -7903,7 +7903,7 @@
         </is>
       </c>
       <c r="J171" t="n">
-        <v>160</v>
+        <v>396</v>
       </c>
       <c r="K171" t="n">
         <v>0</v>
@@ -7912,30 +7912,30 @@
         <v>0</v>
       </c>
       <c r="M171" t="n">
-        <v>160</v>
+        <v>396</v>
       </c>
       <c r="N171" t="n">
-        <v>16058</v>
+        <v>25534</v>
       </c>
       <c r="O171" t="n">
-        <v>2569280</v>
+        <v>10111464</v>
       </c>
       <c r="P171" t="n">
-        <v>25900</v>
+        <v>40900</v>
       </c>
       <c r="Q171" t="n">
-        <v>4144000</v>
+        <v>16196400</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>C4305</t>
+          <t>C4310</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>MUÑECA BEBE GRANDE CON PIJAMA EN BOLSA C4305</t>
+          <t>MUÑECA CON CARRO HUMO RECARGABLE C4310</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -7949,7 +7949,7 @@
         </is>
       </c>
       <c r="J172" t="n">
-        <v>396</v>
+        <v>100</v>
       </c>
       <c r="K172" t="n">
         <v>0</v>
@@ -7958,30 +7958,30 @@
         <v>0</v>
       </c>
       <c r="M172" t="n">
-        <v>396</v>
+        <v>100</v>
       </c>
       <c r="N172" t="n">
-        <v>25534</v>
+        <v>72889</v>
       </c>
       <c r="O172" t="n">
-        <v>10111464</v>
+        <v>7288900</v>
       </c>
       <c r="P172" t="n">
-        <v>40900</v>
+        <v>117500</v>
       </c>
       <c r="Q172" t="n">
-        <v>16196400</v>
+        <v>11750000</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>C4310</t>
+          <t>C4386</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>MUÑECA CON CARRO HUMO RECARGABLE C4310</t>
+          <t>MALETA VIAJERA HERRAMIENTAS</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -7995,7 +7995,7 @@
         </is>
       </c>
       <c r="J173" t="n">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="K173" t="n">
         <v>0</v>
@@ -8004,30 +8004,30 @@
         <v>0</v>
       </c>
       <c r="M173" t="n">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="N173" t="n">
-        <v>72889</v>
+        <v>44055</v>
       </c>
       <c r="O173" t="n">
-        <v>7288900</v>
+        <v>3171960</v>
       </c>
       <c r="P173" t="n">
-        <v>117500</v>
+        <v>70900</v>
       </c>
       <c r="Q173" t="n">
-        <v>11750000</v>
+        <v>5104800</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>C4386</t>
+          <t>C4387</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>MALETA VIAJERA HERRAMIENTAS</t>
+          <t>MAQUILLAJE DONNA C4387</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -8041,7 +8041,7 @@
         </is>
       </c>
       <c r="J174" t="n">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="K174" t="n">
         <v>0</v>
@@ -8050,35 +8050,38 @@
         <v>0</v>
       </c>
       <c r="M174" t="n">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="N174" t="n">
-        <v>44055</v>
+        <v>4917</v>
       </c>
       <c r="O174" t="n">
-        <v>3171960</v>
+        <v>472032</v>
       </c>
       <c r="P174" t="n">
-        <v>70900</v>
+        <v>8600</v>
       </c>
       <c r="Q174" t="n">
-        <v>5104800</v>
+        <v>825600</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>C4387</t>
-        </is>
+          <t>C439</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>6914919077302</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>MAQUILLAJE DONNA C4387</t>
+          <t>globo burbuja 10</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>GLOBOS</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -8087,7 +8090,7 @@
         </is>
       </c>
       <c r="J175" t="n">
-        <v>96</v>
+        <v>38365</v>
       </c>
       <c r="K175" t="n">
         <v>0</v>
@@ -8096,38 +8099,35 @@
         <v>0</v>
       </c>
       <c r="M175" t="n">
-        <v>96</v>
+        <v>38365</v>
       </c>
       <c r="N175" t="n">
-        <v>4917</v>
+        <v>239.91</v>
       </c>
       <c r="O175" t="n">
-        <v>472032</v>
+        <v>9204147.15</v>
       </c>
       <c r="P175" t="n">
-        <v>8600</v>
+        <v>300</v>
       </c>
       <c r="Q175" t="n">
-        <v>825600</v>
+        <v>11509500</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>C439</t>
-        </is>
-      </c>
-      <c r="B176" t="n">
-        <v>6914919077302</v>
+          <t>C4393</t>
+        </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>globo burbuja 10</t>
+          <t>MESA DE BILLAR C4393</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>GLOBOS</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -8136,7 +8136,7 @@
         </is>
       </c>
       <c r="J176" t="n">
-        <v>38365</v>
+        <v>84</v>
       </c>
       <c r="K176" t="n">
         <v>0</v>
@@ -8145,30 +8145,30 @@
         <v>0</v>
       </c>
       <c r="M176" t="n">
-        <v>38365</v>
+        <v>84</v>
       </c>
       <c r="N176" t="n">
-        <v>239.91</v>
+        <v>32295</v>
       </c>
       <c r="O176" t="n">
-        <v>9204147.15</v>
+        <v>2712780</v>
       </c>
       <c r="P176" t="n">
-        <v>300</v>
+        <v>51900</v>
       </c>
       <c r="Q176" t="n">
-        <v>11509500</v>
+        <v>4359600</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>C4393</t>
+          <t>C4406</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>MESA DE BILLAR C4393</t>
+          <t>LANZADORA AUTOMATICA</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -8182,7 +8182,7 @@
         </is>
       </c>
       <c r="J177" t="n">
-        <v>84</v>
+        <v>14</v>
       </c>
       <c r="K177" t="n">
         <v>0</v>
@@ -8191,30 +8191,30 @@
         <v>0</v>
       </c>
       <c r="M177" t="n">
-        <v>84</v>
+        <v>14</v>
       </c>
       <c r="N177" t="n">
-        <v>32295</v>
+        <v>55898</v>
       </c>
       <c r="O177" t="n">
-        <v>2712780</v>
+        <v>782572</v>
       </c>
       <c r="P177" t="n">
-        <v>51900</v>
+        <v>89900</v>
       </c>
       <c r="Q177" t="n">
-        <v>4359600</v>
+        <v>1258600</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>C4406</t>
+          <t>C4408</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>LANZADORA AUTOMATICA</t>
+          <t>CANCHA DE FUTBOL BOLSA PVC C4408</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -8228,7 +8228,7 @@
         </is>
       </c>
       <c r="J178" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="K178" t="n">
         <v>0</v>
@@ -8237,30 +8237,30 @@
         <v>0</v>
       </c>
       <c r="M178" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="N178" t="n">
-        <v>55898</v>
+        <v>11857</v>
       </c>
       <c r="O178" t="n">
-        <v>782572</v>
+        <v>355710</v>
       </c>
       <c r="P178" t="n">
-        <v>89900</v>
+        <v>19900</v>
       </c>
       <c r="Q178" t="n">
-        <v>1258600</v>
+        <v>597000</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>C4408</t>
+          <t>C4410</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>CANCHA DE FUTBOL BOLSA PVC C4408</t>
+          <t>PIANO MUSICAL CONEJO MED C4410</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -8274,7 +8274,7 @@
         </is>
       </c>
       <c r="J179" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="K179" t="n">
         <v>0</v>
@@ -8283,30 +8283,30 @@
         <v>0</v>
       </c>
       <c r="M179" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="N179" t="n">
-        <v>11857</v>
+        <v>7713</v>
       </c>
       <c r="O179" t="n">
-        <v>355710</v>
+        <v>431928</v>
       </c>
       <c r="P179" t="n">
-        <v>19900</v>
+        <v>12500</v>
       </c>
       <c r="Q179" t="n">
-        <v>597000</v>
+        <v>700000</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>C4410</t>
+          <t>C4415</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>PIANO MUSICAL CONEJO MED C4410</t>
+          <t>MOVIL BEBES LUZ-SONIDOS</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -8320,7 +8320,7 @@
         </is>
       </c>
       <c r="J180" t="n">
-        <v>96</v>
+        <v>12</v>
       </c>
       <c r="K180" t="n">
         <v>0</v>
@@ -8329,30 +8329,30 @@
         <v>0</v>
       </c>
       <c r="M180" t="n">
-        <v>96</v>
+        <v>12</v>
       </c>
       <c r="N180" t="n">
-        <v>7713</v>
+        <v>28116</v>
       </c>
       <c r="O180" t="n">
-        <v>740448</v>
+        <v>337392</v>
       </c>
       <c r="P180" t="n">
-        <v>12500</v>
+        <v>45900</v>
       </c>
       <c r="Q180" t="n">
-        <v>1200000</v>
+        <v>550800</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>C4415</t>
+          <t>C4416</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>MOVIL BEBES LUZ-SONIDOS</t>
+          <t>AJEDREZ MAGNETICO  C4416</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="J181" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K181" t="n">
         <v>0</v>
@@ -8375,30 +8375,30 @@
         <v>0</v>
       </c>
       <c r="M181" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="N181" t="n">
-        <v>28116</v>
+        <v>24847</v>
       </c>
       <c r="O181" t="n">
-        <v>337392</v>
+        <v>894492</v>
       </c>
       <c r="P181" t="n">
-        <v>45900</v>
+        <v>39900</v>
       </c>
       <c r="Q181" t="n">
-        <v>550800</v>
+        <v>1436400</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>C4416</t>
+          <t>C4433</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>AJEDREZ MAGNETICO  C4416</t>
+          <t>AVION LUCES SONIDOS</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -8412,7 +8412,7 @@
         </is>
       </c>
       <c r="J182" t="n">
-        <v>36</v>
+        <v>210</v>
       </c>
       <c r="K182" t="n">
         <v>0</v>
@@ -8421,30 +8421,30 @@
         <v>0</v>
       </c>
       <c r="M182" t="n">
-        <v>36</v>
+        <v>210</v>
       </c>
       <c r="N182" t="n">
-        <v>24847</v>
+        <v>10411</v>
       </c>
       <c r="O182" t="n">
-        <v>894492</v>
+        <v>2186310</v>
       </c>
       <c r="P182" t="n">
-        <v>39900</v>
+        <v>16900</v>
       </c>
       <c r="Q182" t="n">
-        <v>1436400</v>
+        <v>3549000</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>C4433</t>
+          <t>C4443</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>AVION LUCES SONIDOS</t>
+          <t>CARRITO BURBUJERO DINOSAURIO C4443</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -8458,7 +8458,7 @@
         </is>
       </c>
       <c r="J183" t="n">
-        <v>210</v>
+        <v>36</v>
       </c>
       <c r="K183" t="n">
         <v>0</v>
@@ -8467,30 +8467,30 @@
         <v>0</v>
       </c>
       <c r="M183" t="n">
-        <v>210</v>
+        <v>36</v>
       </c>
       <c r="N183" t="n">
-        <v>10411</v>
+        <v>17644.653275862</v>
       </c>
       <c r="O183" t="n">
-        <v>2186310</v>
+        <v>635207.517931032</v>
       </c>
       <c r="P183" t="n">
-        <v>16900</v>
+        <v>28200</v>
       </c>
       <c r="Q183" t="n">
-        <v>3549000</v>
+        <v>1015200</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>C4441</t>
+          <t>C446-IO</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>PIANO MUSICAL PERRO C4441</t>
+          <t>GLOBO UNICORNIO PQÑO 4PATAS</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -8504,7 +8504,7 @@
         </is>
       </c>
       <c r="J184" t="n">
-        <v>12</v>
+        <v>2200</v>
       </c>
       <c r="K184" t="n">
         <v>0</v>
@@ -8513,30 +8513,30 @@
         <v>0</v>
       </c>
       <c r="M184" t="n">
-        <v>12</v>
+        <v>2200</v>
       </c>
       <c r="N184" t="n">
-        <v>13019</v>
+        <v>880</v>
       </c>
       <c r="O184" t="n">
-        <v>156228</v>
+        <v>1936000</v>
       </c>
       <c r="P184" t="n">
-        <v>20900</v>
+        <v>1100</v>
       </c>
       <c r="Q184" t="n">
-        <v>250800</v>
+        <v>2420000</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>C4443</t>
+          <t>C4466</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>CARRITO BURBUJERO DINOSAURIO C4443</t>
+          <t>MAQUINA DE SLIME C4466</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -8550,7 +8550,7 @@
         </is>
       </c>
       <c r="J185" t="n">
-        <v>36</v>
+        <v>136</v>
       </c>
       <c r="K185" t="n">
         <v>0</v>
@@ -8559,30 +8559,30 @@
         <v>0</v>
       </c>
       <c r="M185" t="n">
-        <v>36</v>
+        <v>136</v>
       </c>
       <c r="N185" t="n">
-        <v>17644.653275862</v>
+        <v>21676</v>
       </c>
       <c r="O185" t="n">
-        <v>635207.517931032</v>
+        <v>2947936</v>
       </c>
       <c r="P185" t="n">
-        <v>28200</v>
+        <v>34900</v>
       </c>
       <c r="Q185" t="n">
-        <v>1015200</v>
+        <v>4746400</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>C446-IO</t>
+          <t>C4468</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>GLOBO UNICORNIO PQÑO 4PATAS</t>
+          <t>MAQUINA PARA HACER PULSERAS C4468</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -8596,7 +8596,7 @@
         </is>
       </c>
       <c r="J186" t="n">
-        <v>2200</v>
+        <v>103</v>
       </c>
       <c r="K186" t="n">
         <v>0</v>
@@ -8605,30 +8605,30 @@
         <v>0</v>
       </c>
       <c r="M186" t="n">
-        <v>2200</v>
+        <v>103</v>
       </c>
       <c r="N186" t="n">
-        <v>880</v>
+        <v>9384</v>
       </c>
       <c r="O186" t="n">
-        <v>1936000</v>
+        <v>966552</v>
       </c>
       <c r="P186" t="n">
-        <v>1100</v>
+        <v>15900</v>
       </c>
       <c r="Q186" t="n">
-        <v>2420000</v>
+        <v>1637700</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>C4466</t>
+          <t>C4475</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>MAQUINA DE SLIME C4466</t>
+          <t>LANZADORAS BIOGEL MODELOS STD C4475</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -8642,7 +8642,7 @@
         </is>
       </c>
       <c r="J187" t="n">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="K187" t="n">
         <v>0</v>
@@ -8651,30 +8651,30 @@
         <v>0</v>
       </c>
       <c r="M187" t="n">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="N187" t="n">
-        <v>21676</v>
+        <v>32332</v>
       </c>
       <c r="O187" t="n">
-        <v>2947936</v>
+        <v>3976836</v>
       </c>
       <c r="P187" t="n">
-        <v>34900</v>
+        <v>55900</v>
       </c>
       <c r="Q187" t="n">
-        <v>4746400</v>
+        <v>6875700</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>C4468</t>
+          <t>C4485</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>MAQUINA PARA HACER PULSERAS C4468</t>
+          <t>LANZADORA AGUA BIOGEL C4485</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -8688,7 +8688,7 @@
         </is>
       </c>
       <c r="J188" t="n">
-        <v>103</v>
+        <v>20</v>
       </c>
       <c r="K188" t="n">
         <v>0</v>
@@ -8697,30 +8697,30 @@
         <v>0</v>
       </c>
       <c r="M188" t="n">
-        <v>103</v>
+        <v>20</v>
       </c>
       <c r="N188" t="n">
-        <v>9384</v>
+        <v>34912</v>
       </c>
       <c r="O188" t="n">
-        <v>966552</v>
+        <v>698240</v>
       </c>
       <c r="P188" t="n">
-        <v>15900</v>
+        <v>56900</v>
       </c>
       <c r="Q188" t="n">
-        <v>1637700</v>
+        <v>1138000</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>C4475</t>
+          <t>C4486</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>LANZADORAS BIOGEL MODELOS STD C4475</t>
+          <t>CHILLONES DINOSAURIOS C4486</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -8734,7 +8734,7 @@
         </is>
       </c>
       <c r="J189" t="n">
-        <v>123</v>
+        <v>175</v>
       </c>
       <c r="K189" t="n">
         <v>0</v>
@@ -8743,30 +8743,30 @@
         <v>0</v>
       </c>
       <c r="M189" t="n">
-        <v>123</v>
+        <v>175</v>
       </c>
       <c r="N189" t="n">
-        <v>32332</v>
+        <v>3519</v>
       </c>
       <c r="O189" t="n">
-        <v>3976836</v>
+        <v>615825</v>
       </c>
       <c r="P189" t="n">
-        <v>55900</v>
+        <v>5900</v>
       </c>
       <c r="Q189" t="n">
-        <v>6875700</v>
+        <v>1032500</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>C4485</t>
+          <t>C4487</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>LANZADORA AGUA BIOGEL C4485</t>
+          <t>JUEGO DOMINO TREN C4487</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -8792,27 +8792,27 @@
         <v>20</v>
       </c>
       <c r="N190" t="n">
-        <v>34912</v>
+        <v>15760</v>
       </c>
       <c r="O190" t="n">
-        <v>698240</v>
+        <v>315200</v>
       </c>
       <c r="P190" t="n">
-        <v>56900</v>
+        <v>25000</v>
       </c>
       <c r="Q190" t="n">
-        <v>1138000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>C4486</t>
+          <t>C4488</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>CHILLONES DINOSAURIOS C4486</t>
+          <t>RANITA LUZ Y SONIDO C4488</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -8826,7 +8826,7 @@
         </is>
       </c>
       <c r="J191" t="n">
-        <v>175</v>
+        <v>124</v>
       </c>
       <c r="K191" t="n">
         <v>0</v>
@@ -8835,30 +8835,30 @@
         <v>0</v>
       </c>
       <c r="M191" t="n">
-        <v>175</v>
+        <v>124</v>
       </c>
       <c r="N191" t="n">
-        <v>3519</v>
+        <v>9003</v>
       </c>
       <c r="O191" t="n">
-        <v>615825</v>
+        <v>1116372</v>
       </c>
       <c r="P191" t="n">
-        <v>5900</v>
+        <v>14900</v>
       </c>
       <c r="Q191" t="n">
-        <v>1032500</v>
+        <v>1847600</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>C4487</t>
+          <t>C4489</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>JUEGO DOMINO TREN C4487</t>
+          <t>PATO LUZ Y SONIDO C4489</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -8872,7 +8872,7 @@
         </is>
       </c>
       <c r="J192" t="n">
-        <v>20</v>
+        <v>216</v>
       </c>
       <c r="K192" t="n">
         <v>0</v>
@@ -8881,30 +8881,30 @@
         <v>0</v>
       </c>
       <c r="M192" t="n">
-        <v>20</v>
+        <v>216</v>
       </c>
       <c r="N192" t="n">
-        <v>15760</v>
+        <v>9178</v>
       </c>
       <c r="O192" t="n">
-        <v>315200</v>
+        <v>1982448</v>
       </c>
       <c r="P192" t="n">
-        <v>25000</v>
+        <v>14900</v>
       </c>
       <c r="Q192" t="n">
-        <v>500000</v>
+        <v>3218400</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>C4488</t>
+          <t>C4493</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>RANITA LUZ Y SONIDO C4488</t>
+          <t>ARCO STD NIÑO Y NIÑA LASER C4493</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -8918,7 +8918,7 @@
         </is>
       </c>
       <c r="J193" t="n">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="K193" t="n">
         <v>0</v>
@@ -8927,30 +8927,30 @@
         <v>0</v>
       </c>
       <c r="M193" t="n">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="N193" t="n">
-        <v>9003</v>
+        <v>13922</v>
       </c>
       <c r="O193" t="n">
-        <v>1116372</v>
+        <v>2046534</v>
       </c>
       <c r="P193" t="n">
-        <v>14900</v>
+        <v>22900</v>
       </c>
       <c r="Q193" t="n">
-        <v>1847600</v>
+        <v>3366300</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>C4489</t>
+          <t>C4497</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>PATO LUZ Y SONIDO C4489</t>
+          <t>JUEGO D MESA 2EN 1 C4497</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -8964,7 +8964,7 @@
         </is>
       </c>
       <c r="J194" t="n">
-        <v>216</v>
+        <v>24</v>
       </c>
       <c r="K194" t="n">
         <v>0</v>
@@ -8973,30 +8973,30 @@
         <v>0</v>
       </c>
       <c r="M194" t="n">
-        <v>216</v>
+        <v>24</v>
       </c>
       <c r="N194" t="n">
-        <v>9178</v>
+        <v>25076</v>
       </c>
       <c r="O194" t="n">
-        <v>1982448</v>
+        <v>601824</v>
       </c>
       <c r="P194" t="n">
-        <v>14900</v>
+        <v>40900</v>
       </c>
       <c r="Q194" t="n">
-        <v>3218400</v>
+        <v>981600</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>C4493</t>
+          <t>C4499</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>ARCO STD NIÑO Y NIÑA LASER C4493</t>
+          <t>PIANO ELEFANTE PQÑ C4499</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -9010,7 +9010,7 @@
         </is>
       </c>
       <c r="J195" t="n">
-        <v>147</v>
+        <v>234</v>
       </c>
       <c r="K195" t="n">
         <v>0</v>
@@ -9019,30 +9019,30 @@
         <v>0</v>
       </c>
       <c r="M195" t="n">
-        <v>147</v>
+        <v>234</v>
       </c>
       <c r="N195" t="n">
-        <v>13922</v>
+        <v>6414</v>
       </c>
       <c r="O195" t="n">
-        <v>2046534</v>
+        <v>1500876</v>
       </c>
       <c r="P195" t="n">
-        <v>22900</v>
+        <v>10900</v>
       </c>
       <c r="Q195" t="n">
-        <v>3366300</v>
+        <v>2550600</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>C4497</t>
+          <t>C4504</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>JUEGO D MESA 2EN 1 C4497</t>
+          <t>CASTILLO ACCESORIOS STD C4504</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -9056,7 +9056,7 @@
         </is>
       </c>
       <c r="J196" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="K196" t="n">
         <v>0</v>
@@ -9065,30 +9065,30 @@
         <v>0</v>
       </c>
       <c r="M196" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="N196" t="n">
-        <v>25076</v>
+        <v>23376.36</v>
       </c>
       <c r="O196" t="n">
-        <v>601824</v>
+        <v>280516.32</v>
       </c>
       <c r="P196" t="n">
         <v>40900</v>
       </c>
       <c r="Q196" t="n">
-        <v>981600</v>
+        <v>490800</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>C4499</t>
+          <t>C4505</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>PIANO ELEFANTE PQÑ C4499</t>
+          <t>PESCADITO Y TIBURON  LUZ Y SONIDO C4505</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -9102,7 +9102,7 @@
         </is>
       </c>
       <c r="J197" t="n">
-        <v>252</v>
+        <v>460</v>
       </c>
       <c r="K197" t="n">
         <v>0</v>
@@ -9111,30 +9111,30 @@
         <v>0</v>
       </c>
       <c r="M197" t="n">
-        <v>252</v>
+        <v>460</v>
       </c>
       <c r="N197" t="n">
-        <v>6426.9445005045</v>
+        <v>13210</v>
       </c>
       <c r="O197" t="n">
-        <v>1619590.014127134</v>
+        <v>6076600</v>
       </c>
       <c r="P197" t="n">
-        <v>10900</v>
+        <v>23900</v>
       </c>
       <c r="Q197" t="n">
-        <v>2746800</v>
+        <v>10994000</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>C4504</t>
+          <t>C4510</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>CASTILLO ACCESORIOS STD C4504</t>
+          <t>TOCADOR CASTILLO MUSICA Y LUZ C4510</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -9148,7 +9148,7 @@
         </is>
       </c>
       <c r="J198" t="n">
-        <v>12</v>
+        <v>144</v>
       </c>
       <c r="K198" t="n">
         <v>0</v>
@@ -9157,30 +9157,30 @@
         <v>0</v>
       </c>
       <c r="M198" t="n">
-        <v>12</v>
+        <v>144</v>
       </c>
       <c r="N198" t="n">
-        <v>23376.36</v>
+        <v>52443</v>
       </c>
       <c r="O198" t="n">
-        <v>280516.32</v>
+        <v>7551792</v>
       </c>
       <c r="P198" t="n">
-        <v>40900</v>
+        <v>83900</v>
       </c>
       <c r="Q198" t="n">
-        <v>490800</v>
+        <v>12081600</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>C4505</t>
+          <t>C4511</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>PESCADITO Y TIBURON  LUZ Y SONIDO C4505</t>
+          <t>BURBUJERO MODELOS STDS C4511</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -9194,7 +9194,7 @@
         </is>
       </c>
       <c r="J199" t="n">
-        <v>460</v>
+        <v>129</v>
       </c>
       <c r="K199" t="n">
         <v>0</v>
@@ -9203,35 +9203,30 @@
         <v>0</v>
       </c>
       <c r="M199" t="n">
-        <v>460</v>
+        <v>129</v>
       </c>
       <c r="N199" t="n">
-        <v>13210</v>
+        <v>3903.7395348837</v>
       </c>
       <c r="O199" t="n">
-        <v>6076600</v>
+        <v>503582.3999999973</v>
       </c>
       <c r="P199" t="n">
-        <v>23900</v>
+        <v>7500</v>
       </c>
       <c r="Q199" t="n">
-        <v>10994000</v>
+        <v>967500</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>C4510</t>
+          <t>C4512</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>TOCADOR CASTILLO MUSICA Y LUZ C4510</t>
-        </is>
-      </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>MAQUILLAJE ESTUCHE UNICORNIO C4512</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -9240,7 +9235,7 @@
         </is>
       </c>
       <c r="J200" t="n">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="K200" t="n">
         <v>0</v>
@@ -9249,35 +9244,30 @@
         <v>0</v>
       </c>
       <c r="M200" t="n">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="N200" t="n">
-        <v>52443</v>
+        <v>20726</v>
       </c>
       <c r="O200" t="n">
-        <v>7551792</v>
+        <v>829040</v>
       </c>
       <c r="P200" t="n">
-        <v>83900</v>
+        <v>33900</v>
       </c>
       <c r="Q200" t="n">
-        <v>12081600</v>
+        <v>1356000</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>C4511</t>
+          <t>C4513</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>BURBUJERO MODELOS STDS C4511</t>
-        </is>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>ESTUCHE MAQUILLAJE UNICORNIO CON BALACA C4513</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -9286,7 +9276,7 @@
         </is>
       </c>
       <c r="J201" t="n">
-        <v>129</v>
+        <v>35</v>
       </c>
       <c r="K201" t="n">
         <v>0</v>
@@ -9295,30 +9285,35 @@
         <v>0</v>
       </c>
       <c r="M201" t="n">
-        <v>129</v>
+        <v>35</v>
       </c>
       <c r="N201" t="n">
-        <v>3903.7394652406</v>
+        <v>35864.602181818</v>
       </c>
       <c r="O201" t="n">
-        <v>503582.3910160374</v>
+        <v>1255261.07636363</v>
       </c>
       <c r="P201" t="n">
-        <v>7500</v>
+        <v>62900</v>
       </c>
       <c r="Q201" t="n">
-        <v>967500</v>
+        <v>2201500</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>C4512</t>
+          <t>C4514</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>MAQUILLAJE ESTUCHE UNICORNIO C4512</t>
+          <t>ESTUCHE MAQUILLAJE PARA UÑAS C4514</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -9327,7 +9322,7 @@
         </is>
       </c>
       <c r="J202" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="K202" t="n">
         <v>0</v>
@@ -9336,30 +9331,35 @@
         <v>0</v>
       </c>
       <c r="M202" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N202" t="n">
-        <v>20726</v>
+        <v>20731</v>
       </c>
       <c r="O202" t="n">
-        <v>829040</v>
+        <v>953626</v>
       </c>
       <c r="P202" t="n">
         <v>33900</v>
       </c>
       <c r="Q202" t="n">
-        <v>1356000</v>
+        <v>1559400</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>C4513</t>
+          <t>C4521</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>ESTUCHE MAQUILLAJE UNICORNIO CON BALACA C4513</t>
+          <t>JUEGO DE AJEDREZ 3EN1</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -9368,7 +9368,7 @@
         </is>
       </c>
       <c r="J203" t="n">
-        <v>51</v>
+        <v>118</v>
       </c>
       <c r="K203" t="n">
         <v>0</v>
@@ -9377,30 +9377,30 @@
         <v>0</v>
       </c>
       <c r="M203" t="n">
-        <v>51</v>
+        <v>118</v>
       </c>
       <c r="N203" t="n">
-        <v>35864.602181818</v>
+        <v>4202</v>
       </c>
       <c r="O203" t="n">
-        <v>1829094.711272718</v>
+        <v>495836</v>
       </c>
       <c r="P203" t="n">
-        <v>62900</v>
+        <v>7900</v>
       </c>
       <c r="Q203" t="n">
-        <v>3207900</v>
+        <v>932200</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>C4514</t>
+          <t>C4523</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>ESTUCHE MAQUILLAJE PARA UÑAS C4514</t>
+          <t>PIANO TAPETE MUSICAL C4523</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="J204" t="n">
-        <v>46</v>
+        <v>144</v>
       </c>
       <c r="K204" t="n">
         <v>0</v>
@@ -9423,30 +9423,30 @@
         <v>0</v>
       </c>
       <c r="M204" t="n">
-        <v>46</v>
+        <v>144</v>
       </c>
       <c r="N204" t="n">
-        <v>20731</v>
+        <v>16469</v>
       </c>
       <c r="O204" t="n">
-        <v>953626</v>
+        <v>2371536</v>
       </c>
       <c r="P204" t="n">
-        <v>33900</v>
+        <v>26900</v>
       </c>
       <c r="Q204" t="n">
-        <v>1559400</v>
+        <v>3873600</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>C4521</t>
+          <t>C4525</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>JUEGO DE AJEDREZ 3EN1</t>
+          <t>LANZADORA CATAPULTA C4525</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -9460,7 +9460,7 @@
         </is>
       </c>
       <c r="J205" t="n">
-        <v>118</v>
+        <v>18</v>
       </c>
       <c r="K205" t="n">
         <v>0</v>
@@ -9469,30 +9469,30 @@
         <v>0</v>
       </c>
       <c r="M205" t="n">
-        <v>118</v>
+        <v>18</v>
       </c>
       <c r="N205" t="n">
-        <v>4202</v>
+        <v>11922</v>
       </c>
       <c r="O205" t="n">
-        <v>495836</v>
+        <v>214596</v>
       </c>
       <c r="P205" t="n">
-        <v>7900</v>
+        <v>19900</v>
       </c>
       <c r="Q205" t="n">
-        <v>932200</v>
+        <v>358200</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>C4523</t>
+          <t>C4527</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>PIANO TAPETE MUSICAL C4523</t>
+          <t>MINI PIANO C4527</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -9506,7 +9506,7 @@
         </is>
       </c>
       <c r="J206" t="n">
-        <v>144</v>
+        <v>108</v>
       </c>
       <c r="K206" t="n">
         <v>0</v>
@@ -9515,30 +9515,30 @@
         <v>0</v>
       </c>
       <c r="M206" t="n">
-        <v>144</v>
+        <v>108</v>
       </c>
       <c r="N206" t="n">
-        <v>16469</v>
+        <v>12556</v>
       </c>
       <c r="O206" t="n">
-        <v>2371536</v>
+        <v>1356048</v>
       </c>
       <c r="P206" t="n">
-        <v>26900</v>
+        <v>21900</v>
       </c>
       <c r="Q206" t="n">
-        <v>3873600</v>
+        <v>2365200</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>C4525</t>
+          <t>C4530</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>LANZADORA CATAPULTA C4525</t>
+          <t>CARRO FORMULAY DINO BURBUJERA C4530</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -9552,7 +9552,7 @@
         </is>
       </c>
       <c r="J207" t="n">
-        <v>18</v>
+        <v>144</v>
       </c>
       <c r="K207" t="n">
         <v>0</v>
@@ -9561,30 +9561,30 @@
         <v>0</v>
       </c>
       <c r="M207" t="n">
-        <v>18</v>
+        <v>144</v>
       </c>
       <c r="N207" t="n">
-        <v>11922</v>
+        <v>5869.1723864836</v>
       </c>
       <c r="O207" t="n">
-        <v>214596</v>
+        <v>845160.8236536385</v>
       </c>
       <c r="P207" t="n">
-        <v>19900</v>
+        <v>9500</v>
       </c>
       <c r="Q207" t="n">
-        <v>358200</v>
+        <v>1368000</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>C4527</t>
+          <t>C4531</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>MINI PIANO C4527</t>
+          <t>CARROS RETRO/GRUA STD BOLSA PVC C4531</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -9598,7 +9598,7 @@
         </is>
       </c>
       <c r="J208" t="n">
-        <v>108</v>
+        <v>307</v>
       </c>
       <c r="K208" t="n">
         <v>0</v>
@@ -9607,30 +9607,30 @@
         <v>0</v>
       </c>
       <c r="M208" t="n">
-        <v>108</v>
+        <v>307</v>
       </c>
       <c r="N208" t="n">
-        <v>12556</v>
+        <v>6849.2</v>
       </c>
       <c r="O208" t="n">
-        <v>1356048</v>
+        <v>2102704.4</v>
       </c>
       <c r="P208" t="n">
-        <v>21900</v>
+        <v>11500</v>
       </c>
       <c r="Q208" t="n">
-        <v>2365200</v>
+        <v>3530500</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>C4530</t>
+          <t>C4534</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>CARRO FORMULAY DINO BURBUJERA C4530</t>
+          <t>CARROS RETROS STD CAJA X 12 C4534</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -9644,7 +9644,7 @@
         </is>
       </c>
       <c r="J209" t="n">
-        <v>144</v>
+        <v>702</v>
       </c>
       <c r="K209" t="n">
         <v>0</v>
@@ -9653,30 +9653,30 @@
         <v>0</v>
       </c>
       <c r="M209" t="n">
-        <v>144</v>
+        <v>702</v>
       </c>
       <c r="N209" t="n">
-        <v>5869.172402529</v>
+        <v>5772</v>
       </c>
       <c r="O209" t="n">
-        <v>845160.825964176</v>
+        <v>4051944</v>
       </c>
       <c r="P209" t="n">
-        <v>9500</v>
+        <v>9900</v>
       </c>
       <c r="Q209" t="n">
-        <v>1368000</v>
+        <v>6949800</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>C4531</t>
+          <t>C4541</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>CARROS RETRO/GRUA STD BOLSA PVC C4531</t>
+          <t>LANZADORADARDOS MED C4541</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -9690,7 +9690,7 @@
         </is>
       </c>
       <c r="J210" t="n">
-        <v>307</v>
+        <v>456</v>
       </c>
       <c r="K210" t="n">
         <v>0</v>
@@ -9699,30 +9699,30 @@
         <v>0</v>
       </c>
       <c r="M210" t="n">
-        <v>307</v>
+        <v>456</v>
       </c>
       <c r="N210" t="n">
-        <v>6849.2</v>
+        <v>6645</v>
       </c>
       <c r="O210" t="n">
-        <v>2102704.4</v>
+        <v>3030120</v>
       </c>
       <c r="P210" t="n">
-        <v>11500</v>
+        <v>10900</v>
       </c>
       <c r="Q210" t="n">
-        <v>3530500</v>
+        <v>4970400</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>C4534</t>
+          <t>C4542</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>CARROS RETROS STD CAJA X 12 C4534</t>
+          <t>LANZDORA DE DARDOS Y BIOGEL C4542</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -9736,7 +9736,7 @@
         </is>
       </c>
       <c r="J211" t="n">
-        <v>702</v>
+        <v>256</v>
       </c>
       <c r="K211" t="n">
         <v>0</v>
@@ -9745,30 +9745,30 @@
         <v>0</v>
       </c>
       <c r="M211" t="n">
-        <v>702</v>
+        <v>256</v>
       </c>
       <c r="N211" t="n">
-        <v>5772</v>
+        <v>13098</v>
       </c>
       <c r="O211" t="n">
-        <v>4051944</v>
+        <v>3353088</v>
       </c>
       <c r="P211" t="n">
-        <v>9900</v>
+        <v>21200</v>
       </c>
       <c r="Q211" t="n">
-        <v>6949800</v>
+        <v>5427200</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>C4541</t>
+          <t>C4545</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>LANZADORADARDOS MED C4541</t>
+          <t>TAPETE PIANO PARA BEBE C4545</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -9782,7 +9782,7 @@
         </is>
       </c>
       <c r="J212" t="n">
-        <v>456</v>
+        <v>132</v>
       </c>
       <c r="K212" t="n">
         <v>0</v>
@@ -9791,30 +9791,30 @@
         <v>0</v>
       </c>
       <c r="M212" t="n">
-        <v>456</v>
+        <v>132</v>
       </c>
       <c r="N212" t="n">
-        <v>6648.7102177554</v>
+        <v>27186</v>
       </c>
       <c r="O212" t="n">
-        <v>3031811.859296462</v>
+        <v>3588552</v>
       </c>
       <c r="P212" t="n">
-        <v>10900</v>
+        <v>43900</v>
       </c>
       <c r="Q212" t="n">
-        <v>4970400</v>
+        <v>5794800</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>C4542</t>
+          <t>C4547</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>LANZDORA DE DARDOS Y BIOGEL C4542</t>
+          <t>CASA VILLA ACCESORIOS C4547</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -9828,7 +9828,7 @@
         </is>
       </c>
       <c r="J213" t="n">
-        <v>256</v>
+        <v>84</v>
       </c>
       <c r="K213" t="n">
         <v>0</v>
@@ -9837,30 +9837,30 @@
         <v>0</v>
       </c>
       <c r="M213" t="n">
-        <v>256</v>
+        <v>84</v>
       </c>
       <c r="N213" t="n">
-        <v>13098</v>
+        <v>72535</v>
       </c>
       <c r="O213" t="n">
-        <v>3353088</v>
+        <v>6092940</v>
       </c>
       <c r="P213" t="n">
-        <v>21200</v>
+        <v>116900</v>
       </c>
       <c r="Q213" t="n">
-        <v>5427200</v>
+        <v>9819600</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>C4545</t>
+          <t>C4548</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>TAPETE PIANO PARA BEBE C4545</t>
+          <t>CARRO DIDACTICO X4 BEBE</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -9874,7 +9874,7 @@
         </is>
       </c>
       <c r="J214" t="n">
-        <v>132</v>
+        <v>105</v>
       </c>
       <c r="K214" t="n">
         <v>0</v>
@@ -9883,30 +9883,30 @@
         <v>0</v>
       </c>
       <c r="M214" t="n">
-        <v>132</v>
+        <v>105</v>
       </c>
       <c r="N214" t="n">
-        <v>27186</v>
+        <v>7562</v>
       </c>
       <c r="O214" t="n">
-        <v>3588552</v>
+        <v>794010</v>
       </c>
       <c r="P214" t="n">
-        <v>43900</v>
+        <v>12900</v>
       </c>
       <c r="Q214" t="n">
-        <v>5794800</v>
+        <v>1354500</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>C4547</t>
+          <t>C4550</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>CASA VILLA ACCESORIOS C4547</t>
+          <t>HELICOPTERO  FASHION C4550</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -9920,7 +9920,7 @@
         </is>
       </c>
       <c r="J215" t="n">
-        <v>84</v>
+        <v>245</v>
       </c>
       <c r="K215" t="n">
         <v>0</v>
@@ -9929,30 +9929,30 @@
         <v>0</v>
       </c>
       <c r="M215" t="n">
-        <v>84</v>
+        <v>245</v>
       </c>
       <c r="N215" t="n">
-        <v>72535</v>
+        <v>13565</v>
       </c>
       <c r="O215" t="n">
-        <v>6092940</v>
+        <v>3323425</v>
       </c>
       <c r="P215" t="n">
-        <v>116900</v>
+        <v>22500</v>
       </c>
       <c r="Q215" t="n">
-        <v>9819600</v>
+        <v>5512500</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>C4548</t>
+          <t>C4551</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>CARRO DIDACTICO X4 BEBE</t>
+          <t>PRINCESS EN CASTILLO Y CARRUAJE C4551</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -9966,7 +9966,7 @@
         </is>
       </c>
       <c r="J216" t="n">
-        <v>105</v>
+        <v>1162</v>
       </c>
       <c r="K216" t="n">
         <v>0</v>
@@ -9975,30 +9975,30 @@
         <v>0</v>
       </c>
       <c r="M216" t="n">
-        <v>105</v>
+        <v>1162</v>
       </c>
       <c r="N216" t="n">
-        <v>7562</v>
+        <v>7635</v>
       </c>
       <c r="O216" t="n">
-        <v>794010</v>
+        <v>8871870</v>
       </c>
       <c r="P216" t="n">
-        <v>12900</v>
+        <v>13900</v>
       </c>
       <c r="Q216" t="n">
-        <v>1354500</v>
+        <v>16151800</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>C4550</t>
+          <t>C4555</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>HELICOPTERO  FASHION C4550</t>
+          <t>SONAJERO EN BOLSA 5 PCS C4555</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -10012,7 +10012,7 @@
         </is>
       </c>
       <c r="J217" t="n">
-        <v>245</v>
+        <v>336</v>
       </c>
       <c r="K217" t="n">
         <v>0</v>
@@ -10021,30 +10021,30 @@
         <v>0</v>
       </c>
       <c r="M217" t="n">
-        <v>245</v>
+        <v>336</v>
       </c>
       <c r="N217" t="n">
-        <v>13565</v>
+        <v>5438</v>
       </c>
       <c r="O217" t="n">
-        <v>3323425</v>
+        <v>1827168</v>
       </c>
       <c r="P217" t="n">
-        <v>22500</v>
+        <v>8900</v>
       </c>
       <c r="Q217" t="n">
-        <v>5512500</v>
+        <v>2990400</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>C4551</t>
+          <t>C4556</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>PRINCESS EN CASTILLO Y CARRUAJE C4551</t>
+          <t>SONAJERO EN CAJA 8PCS C4556</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -10058,7 +10058,7 @@
         </is>
       </c>
       <c r="J218" t="n">
-        <v>1162</v>
+        <v>48</v>
       </c>
       <c r="K218" t="n">
         <v>0</v>
@@ -10067,30 +10067,30 @@
         <v>0</v>
       </c>
       <c r="M218" t="n">
-        <v>1162</v>
+        <v>48</v>
       </c>
       <c r="N218" t="n">
-        <v>7635</v>
+        <v>16086</v>
       </c>
       <c r="O218" t="n">
-        <v>8871870</v>
+        <v>772128</v>
       </c>
       <c r="P218" t="n">
-        <v>13900</v>
+        <v>25900</v>
       </c>
       <c r="Q218" t="n">
-        <v>16151800</v>
+        <v>1243200</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>C4555</t>
+          <t>C4557</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>SONAJERO EN BOLSA 5 PCS C4555</t>
+          <t>JUEGO DE UÑAS Y MAQUILLAJE C4557</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -10104,7 +10104,7 @@
         </is>
       </c>
       <c r="J219" t="n">
-        <v>336</v>
+        <v>560</v>
       </c>
       <c r="K219" t="n">
         <v>0</v>
@@ -10113,30 +10113,30 @@
         <v>0</v>
       </c>
       <c r="M219" t="n">
-        <v>336</v>
+        <v>560</v>
       </c>
       <c r="N219" t="n">
-        <v>5438</v>
+        <v>8806</v>
       </c>
       <c r="O219" t="n">
-        <v>1827168</v>
+        <v>4931360</v>
       </c>
       <c r="P219" t="n">
-        <v>8900</v>
+        <v>14900</v>
       </c>
       <c r="Q219" t="n">
-        <v>2990400</v>
+        <v>8344000</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>C4556</t>
+          <t>C4559</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>SONAJERO EN CAJA 8PCS C4556</t>
+          <t>PIANO DIDACTICO 3en1 C4559</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -10150,7 +10150,7 @@
         </is>
       </c>
       <c r="J220" t="n">
-        <v>48</v>
+        <v>180</v>
       </c>
       <c r="K220" t="n">
         <v>0</v>
@@ -10159,30 +10159,30 @@
         <v>0</v>
       </c>
       <c r="M220" t="n">
-        <v>48</v>
+        <v>180</v>
       </c>
       <c r="N220" t="n">
-        <v>16086</v>
+        <v>19008</v>
       </c>
       <c r="O220" t="n">
-        <v>772128</v>
+        <v>3421440</v>
       </c>
       <c r="P220" t="n">
-        <v>25900</v>
+        <v>30900</v>
       </c>
       <c r="Q220" t="n">
-        <v>1243200</v>
+        <v>5562000</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>C4557</t>
+          <t>C4560</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>JUEGO DE UÑAS Y MAQUILLAJE C4557</t>
+          <t>PIANO TAPETE C4560</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -10196,7 +10196,7 @@
         </is>
       </c>
       <c r="J221" t="n">
-        <v>560</v>
+        <v>460</v>
       </c>
       <c r="K221" t="n">
         <v>0</v>
@@ -10205,30 +10205,30 @@
         <v>0</v>
       </c>
       <c r="M221" t="n">
-        <v>560</v>
+        <v>460</v>
       </c>
       <c r="N221" t="n">
-        <v>8806</v>
+        <v>11302</v>
       </c>
       <c r="O221" t="n">
-        <v>4931360</v>
+        <v>5198920</v>
       </c>
       <c r="P221" t="n">
-        <v>14900</v>
+        <v>18900</v>
       </c>
       <c r="Q221" t="n">
-        <v>8344000</v>
+        <v>8694000</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>C4559</t>
+          <t>C4561</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>PIANO DIDACTICO 3en1 C4559</t>
+          <t>ABECEDARIO INGLES MUSICAL C4561</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -10254,27 +10254,27 @@
         <v>180</v>
       </c>
       <c r="N222" t="n">
-        <v>19008</v>
+        <v>17992</v>
       </c>
       <c r="O222" t="n">
-        <v>3421440</v>
+        <v>3238560</v>
       </c>
       <c r="P222" t="n">
-        <v>30900</v>
+        <v>28900</v>
       </c>
       <c r="Q222" t="n">
-        <v>5562000</v>
+        <v>5202000</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>C4560</t>
+          <t>C4566</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>PIANO TAPETE C4560</t>
+          <t>CARRO MINI CONTROL MODELOS STDS C4566</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -10288,7 +10288,7 @@
         </is>
       </c>
       <c r="J223" t="n">
-        <v>460</v>
+        <v>290</v>
       </c>
       <c r="K223" t="n">
         <v>0</v>
@@ -10297,30 +10297,30 @@
         <v>0</v>
       </c>
       <c r="M223" t="n">
-        <v>460</v>
+        <v>290</v>
       </c>
       <c r="N223" t="n">
-        <v>11302</v>
+        <v>11348</v>
       </c>
       <c r="O223" t="n">
-        <v>5198920</v>
+        <v>3290920</v>
       </c>
       <c r="P223" t="n">
-        <v>18900</v>
+        <v>19900</v>
       </c>
       <c r="Q223" t="n">
-        <v>8694000</v>
+        <v>5771000</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>C4561</t>
+          <t>C4567</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>ABECEDARIO INGLES MUSICAL C4561</t>
+          <t>JUEGO MESA FORMA DE ANIMALES C4567</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -10334,7 +10334,7 @@
         </is>
       </c>
       <c r="J224" t="n">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="K224" t="n">
         <v>0</v>
@@ -10343,30 +10343,30 @@
         <v>0</v>
       </c>
       <c r="M224" t="n">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="N224" t="n">
-        <v>17992</v>
+        <v>17075.989518156</v>
       </c>
       <c r="O224" t="n">
-        <v>3238560</v>
+        <v>3278589.987485952</v>
       </c>
       <c r="P224" t="n">
-        <v>28900</v>
+        <v>27500</v>
       </c>
       <c r="Q224" t="n">
-        <v>5202000</v>
+        <v>5280000</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>C4566</t>
+          <t>C4570</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>CARRO MINI CONTROL MODELOS STDS C4566</t>
+          <t>CUBO MAGICO C4570 EQY766</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -10380,7 +10380,7 @@
         </is>
       </c>
       <c r="J225" t="n">
-        <v>290</v>
+        <v>60</v>
       </c>
       <c r="K225" t="n">
         <v>0</v>
@@ -10389,30 +10389,30 @@
         <v>0</v>
       </c>
       <c r="M225" t="n">
-        <v>290</v>
+        <v>60</v>
       </c>
       <c r="N225" t="n">
-        <v>11348</v>
+        <v>10398</v>
       </c>
       <c r="O225" t="n">
-        <v>3290920</v>
+        <v>623880</v>
       </c>
       <c r="P225" t="n">
-        <v>19900</v>
+        <v>16900</v>
       </c>
       <c r="Q225" t="n">
-        <v>5771000</v>
+        <v>1014000</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>C4567</t>
+          <t>C4572</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>JUEGO MESA FORMA DE ANIMALES C4567</t>
+          <t>CUBO MAGICO C4572 EQY10130</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -10426,7 +10426,7 @@
         </is>
       </c>
       <c r="J226" t="n">
-        <v>192</v>
+        <v>108</v>
       </c>
       <c r="K226" t="n">
         <v>0</v>
@@ -10435,30 +10435,30 @@
         <v>0</v>
       </c>
       <c r="M226" t="n">
-        <v>192</v>
+        <v>108</v>
       </c>
       <c r="N226" t="n">
-        <v>17075.989518156</v>
+        <v>4518</v>
       </c>
       <c r="O226" t="n">
-        <v>3278589.987485952</v>
+        <v>487944</v>
       </c>
       <c r="P226" t="n">
-        <v>27500</v>
+        <v>7900</v>
       </c>
       <c r="Q226" t="n">
-        <v>5280000</v>
+        <v>853200</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>C4570</t>
+          <t>C4577</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>CUBO MAGICO C4570 EQY766</t>
+          <t>PISTA DINOSAURIO C4577</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -10472,7 +10472,7 @@
         </is>
       </c>
       <c r="J227" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="K227" t="n">
         <v>0</v>
@@ -10481,30 +10481,30 @@
         <v>0</v>
       </c>
       <c r="M227" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="N227" t="n">
-        <v>10398</v>
+        <v>21346</v>
       </c>
       <c r="O227" t="n">
-        <v>623880</v>
+        <v>1430182</v>
       </c>
       <c r="P227" t="n">
-        <v>16900</v>
+        <v>34900</v>
       </c>
       <c r="Q227" t="n">
-        <v>1014000</v>
+        <v>2338300</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>C4572</t>
+          <t>C4578</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>CUBO MAGICO C4572 EQY10130</t>
+          <t>LANZADORA DE AGUA BOLSA PVC C4578</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -10518,7 +10518,7 @@
         </is>
       </c>
       <c r="J228" t="n">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="K228" t="n">
         <v>0</v>
@@ -10527,30 +10527,30 @@
         <v>0</v>
       </c>
       <c r="M228" t="n">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="N228" t="n">
-        <v>4518</v>
+        <v>18001</v>
       </c>
       <c r="O228" t="n">
-        <v>487944</v>
+        <v>1512084</v>
       </c>
       <c r="P228" t="n">
-        <v>7900</v>
+        <v>28900</v>
       </c>
       <c r="Q228" t="n">
-        <v>853200</v>
+        <v>2427600</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>C4577</t>
+          <t>C4579</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>PISTA DINOSAURIO C4577</t>
+          <t>LANZADORA DE AGUA C4579</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -10564,7 +10564,7 @@
         </is>
       </c>
       <c r="J229" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K229" t="n">
         <v>0</v>
@@ -10573,30 +10573,33 @@
         <v>0</v>
       </c>
       <c r="M229" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="N229" t="n">
-        <v>21346</v>
+        <v>10219</v>
       </c>
       <c r="O229" t="n">
-        <v>1430182</v>
+        <v>694892</v>
       </c>
       <c r="P229" t="n">
-        <v>34900</v>
+        <v>16900</v>
       </c>
       <c r="Q229" t="n">
-        <v>2338300</v>
+        <v>1149200</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>C4578</t>
-        </is>
+          <t>C458</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>6920190230459</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>LANZADORA DE AGUA BOLSA PVC C4578</t>
+          <t>BURRO SENCILLO SONIDO</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -10606,11 +10609,11 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J230" t="n">
-        <v>84</v>
+        <v>420</v>
       </c>
       <c r="K230" t="n">
         <v>0</v>
@@ -10619,30 +10622,30 @@
         <v>0</v>
       </c>
       <c r="M230" t="n">
-        <v>84</v>
+        <v>420</v>
       </c>
       <c r="N230" t="n">
-        <v>18001</v>
+        <v>10755</v>
       </c>
       <c r="O230" t="n">
-        <v>1512084</v>
+        <v>4517100</v>
       </c>
       <c r="P230" t="n">
-        <v>28900</v>
+        <v>17900</v>
       </c>
       <c r="Q230" t="n">
-        <v>2427600</v>
+        <v>7518000</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>C4579</t>
+          <t>C4581</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>LANZADORA DE AGUA C4579</t>
+          <t>ESPADA BURBUJERA C4581</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -10656,7 +10659,7 @@
         </is>
       </c>
       <c r="J231" t="n">
-        <v>68</v>
+        <v>106</v>
       </c>
       <c r="K231" t="n">
         <v>0</v>
@@ -10665,33 +10668,30 @@
         <v>0</v>
       </c>
       <c r="M231" t="n">
-        <v>68</v>
+        <v>106</v>
       </c>
       <c r="N231" t="n">
-        <v>10219</v>
+        <v>17168</v>
       </c>
       <c r="O231" t="n">
-        <v>694892</v>
+        <v>1819808</v>
       </c>
       <c r="P231" t="n">
-        <v>16900</v>
+        <v>27900</v>
       </c>
       <c r="Q231" t="n">
-        <v>1149200</v>
+        <v>2957400</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>C458</t>
-        </is>
-      </c>
-      <c r="B232" t="n">
-        <v>6920190230459</v>
+          <t>C4584</t>
+        </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>BURRO SENCILLO SONIDO</t>
+          <t>LANZADORA DARDOS C4584</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -10701,11 +10701,11 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J232" t="n">
-        <v>420</v>
+        <v>132</v>
       </c>
       <c r="K232" t="n">
         <v>0</v>
@@ -10714,30 +10714,30 @@
         <v>0</v>
       </c>
       <c r="M232" t="n">
-        <v>420</v>
+        <v>132</v>
       </c>
       <c r="N232" t="n">
-        <v>10755</v>
+        <v>27254</v>
       </c>
       <c r="O232" t="n">
-        <v>4517100</v>
+        <v>3597528</v>
       </c>
       <c r="P232" t="n">
-        <v>17900</v>
+        <v>43900</v>
       </c>
       <c r="Q232" t="n">
-        <v>7518000</v>
+        <v>5794800</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>C4581</t>
+          <t>C4596</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>ESPADA BURBUJERA C4581</t>
+          <t>JUEGO ANTIESTRES C4596</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -10751,7 +10751,7 @@
         </is>
       </c>
       <c r="J233" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="K233" t="n">
         <v>0</v>
@@ -10760,30 +10760,30 @@
         <v>0</v>
       </c>
       <c r="M233" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="N233" t="n">
-        <v>17168</v>
+        <v>4303</v>
       </c>
       <c r="O233" t="n">
-        <v>1819808</v>
+        <v>464724</v>
       </c>
       <c r="P233" t="n">
-        <v>27900</v>
+        <v>7900</v>
       </c>
       <c r="Q233" t="n">
-        <v>2957400</v>
+        <v>853200</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>C4582</t>
+          <t>C4599</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>MUÑECA CHICHI SONIDOS C4582</t>
+          <t>VARA HELICE DINOSAURIO C4599</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -10797,7 +10797,7 @@
         </is>
       </c>
       <c r="J234" t="n">
-        <v>30</v>
+        <v>720</v>
       </c>
       <c r="K234" t="n">
         <v>0</v>
@@ -10806,30 +10806,30 @@
         <v>0</v>
       </c>
       <c r="M234" t="n">
-        <v>30</v>
+        <v>720</v>
       </c>
       <c r="N234" t="n">
-        <v>20014</v>
+        <v>5588</v>
       </c>
       <c r="O234" t="n">
-        <v>600420</v>
+        <v>4023360</v>
       </c>
       <c r="P234" t="n">
-        <v>33900</v>
+        <v>9500</v>
       </c>
       <c r="Q234" t="n">
-        <v>1017000</v>
+        <v>6840000</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>C4584</t>
+          <t>C4601</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>LANZADORA DARDOS C4584</t>
+          <t>SET PERRO PATROL C4601</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -10843,7 +10843,7 @@
         </is>
       </c>
       <c r="J235" t="n">
-        <v>132</v>
+        <v>60</v>
       </c>
       <c r="K235" t="n">
         <v>0</v>
@@ -10852,30 +10852,30 @@
         <v>0</v>
       </c>
       <c r="M235" t="n">
-        <v>132</v>
+        <v>60</v>
       </c>
       <c r="N235" t="n">
-        <v>27254</v>
+        <v>14050</v>
       </c>
       <c r="O235" t="n">
-        <v>3597528</v>
+        <v>843000</v>
       </c>
       <c r="P235" t="n">
-        <v>43900</v>
+        <v>23900</v>
       </c>
       <c r="Q235" t="n">
-        <v>5794800</v>
+        <v>1434000</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>C4586</t>
+          <t>C4602</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>DINOSAURIO CONTROL REMOTO HUMO C4586</t>
+          <t>AVION CON PISTA MODELOS STD C4602</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -10889,7 +10889,7 @@
         </is>
       </c>
       <c r="J236" t="n">
-        <v>3</v>
+        <v>285</v>
       </c>
       <c r="K236" t="n">
         <v>0</v>
@@ -10898,30 +10898,30 @@
         <v>0</v>
       </c>
       <c r="M236" t="n">
-        <v>3</v>
+        <v>285</v>
       </c>
       <c r="N236" t="n">
-        <v>52755</v>
+        <v>8700</v>
       </c>
       <c r="O236" t="n">
-        <v>158265</v>
+        <v>2479500</v>
       </c>
       <c r="P236" t="n">
-        <v>85900</v>
+        <v>14900</v>
       </c>
       <c r="Q236" t="n">
-        <v>257700</v>
+        <v>4246500</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>C4596</t>
+          <t>C4603</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>JUEGO ANTIESTRES C4596</t>
+          <t>MAQUILLAJE BLISTER SENCILLO C4603</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -10935,7 +10935,7 @@
         </is>
       </c>
       <c r="J237" t="n">
-        <v>108</v>
+        <v>385</v>
       </c>
       <c r="K237" t="n">
         <v>0</v>
@@ -10944,30 +10944,30 @@
         <v>0</v>
       </c>
       <c r="M237" t="n">
-        <v>108</v>
+        <v>385</v>
       </c>
       <c r="N237" t="n">
-        <v>4303</v>
+        <v>3639.35</v>
       </c>
       <c r="O237" t="n">
-        <v>464724</v>
+        <v>1401149.75</v>
       </c>
       <c r="P237" t="n">
-        <v>7900</v>
+        <v>7500</v>
       </c>
       <c r="Q237" t="n">
-        <v>853200</v>
+        <v>2887500</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>C4599</t>
+          <t>C4604</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>VARA HELICE DINOSAURIO C4599</t>
+          <t>MQUILLAJE BLISTER MODELOS STDS C4604</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -10981,7 +10981,7 @@
         </is>
       </c>
       <c r="J238" t="n">
-        <v>720</v>
+        <v>1709</v>
       </c>
       <c r="K238" t="n">
         <v>0</v>
@@ -10990,30 +10990,30 @@
         <v>0</v>
       </c>
       <c r="M238" t="n">
-        <v>720</v>
+        <v>1709</v>
       </c>
       <c r="N238" t="n">
-        <v>5588</v>
+        <v>1326</v>
       </c>
       <c r="O238" t="n">
-        <v>4023360</v>
+        <v>2266134</v>
       </c>
       <c r="P238" t="n">
-        <v>9500</v>
+        <v>2500</v>
       </c>
       <c r="Q238" t="n">
-        <v>6840000</v>
+        <v>4272500</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>C4601</t>
+          <t>C4605</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>SET PERRO PATROL C4601</t>
+          <t>MAQUILLAJE BLISTER  CORAZON C4605</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -11027,7 +11027,7 @@
         </is>
       </c>
       <c r="J239" t="n">
-        <v>78</v>
+        <v>176</v>
       </c>
       <c r="K239" t="n">
         <v>0</v>
@@ -11036,30 +11036,30 @@
         <v>0</v>
       </c>
       <c r="M239" t="n">
-        <v>78</v>
+        <v>176</v>
       </c>
       <c r="N239" t="n">
-        <v>14050</v>
+        <v>5640</v>
       </c>
       <c r="O239" t="n">
-        <v>1095900</v>
+        <v>992640</v>
       </c>
       <c r="P239" t="n">
-        <v>23900</v>
+        <v>9900</v>
       </c>
       <c r="Q239" t="n">
-        <v>1864200</v>
+        <v>1742400</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>C4602</t>
+          <t>C4606</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>AVION CON PISTA MODELOS STD C4602</t>
+          <t>SONAJERO EN CAJA 6PCS C4606</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -11073,7 +11073,7 @@
         </is>
       </c>
       <c r="J240" t="n">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="K240" t="n">
         <v>0</v>
@@ -11082,30 +11082,30 @@
         <v>0</v>
       </c>
       <c r="M240" t="n">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="N240" t="n">
-        <v>8700</v>
+        <v>10713.21</v>
       </c>
       <c r="O240" t="n">
-        <v>2479500</v>
+        <v>2988985.59</v>
       </c>
       <c r="P240" t="n">
-        <v>14900</v>
+        <v>20900</v>
       </c>
       <c r="Q240" t="n">
-        <v>4246500</v>
+        <v>5831100</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>C4603</t>
+          <t>C4607</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>MAQUILLAJE BLISTER SENCILLO C4603</t>
+          <t>MAQUILLAJE SIRENA C4607</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -11119,7 +11119,7 @@
         </is>
       </c>
       <c r="J241" t="n">
-        <v>385</v>
+        <v>159</v>
       </c>
       <c r="K241" t="n">
         <v>0</v>
@@ -11128,30 +11128,30 @@
         <v>0</v>
       </c>
       <c r="M241" t="n">
-        <v>385</v>
+        <v>159</v>
       </c>
       <c r="N241" t="n">
-        <v>3639.35</v>
+        <v>10817</v>
       </c>
       <c r="O241" t="n">
-        <v>1401149.75</v>
+        <v>1719903</v>
       </c>
       <c r="P241" t="n">
-        <v>7500</v>
+        <v>17900</v>
       </c>
       <c r="Q241" t="n">
-        <v>2887500</v>
+        <v>2846100</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>C4604</t>
+          <t>C4609</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>MQUILLAJE BLISTER MODELOS STDS C4604</t>
+          <t>MAQUILLAJE UNICORNIO C4609</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -11165,7 +11165,7 @@
         </is>
       </c>
       <c r="J242" t="n">
-        <v>1709</v>
+        <v>79</v>
       </c>
       <c r="K242" t="n">
         <v>0</v>
@@ -11174,30 +11174,30 @@
         <v>0</v>
       </c>
       <c r="M242" t="n">
-        <v>1709</v>
+        <v>79</v>
       </c>
       <c r="N242" t="n">
-        <v>1326</v>
+        <v>12489</v>
       </c>
       <c r="O242" t="n">
-        <v>2266134</v>
+        <v>986631</v>
       </c>
       <c r="P242" t="n">
-        <v>2500</v>
+        <v>20900</v>
       </c>
       <c r="Q242" t="n">
-        <v>4272500</v>
+        <v>1651100</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>C4605</t>
+          <t>C4612</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>MAQUILLAJE BLISTER  CORAZON C4605</t>
+          <t>CARRUAJE MUÑECA C4612</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -11211,7 +11211,7 @@
         </is>
       </c>
       <c r="J243" t="n">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="K243" t="n">
         <v>0</v>
@@ -11220,30 +11220,30 @@
         <v>0</v>
       </c>
       <c r="M243" t="n">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="N243" t="n">
-        <v>5640</v>
+        <v>21762</v>
       </c>
       <c r="O243" t="n">
-        <v>992640</v>
+        <v>3612492</v>
       </c>
       <c r="P243" t="n">
-        <v>9900</v>
+        <v>35900</v>
       </c>
       <c r="Q243" t="n">
-        <v>1742400</v>
+        <v>5959400</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>C4606</t>
+          <t>C4613</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>SONAJERO EN CAJA 6PCS C4606</t>
+          <t>DIDACTICOS ARMABLES STD C4613</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -11257,7 +11257,7 @@
         </is>
       </c>
       <c r="J244" t="n">
-        <v>279</v>
+        <v>934</v>
       </c>
       <c r="K244" t="n">
         <v>0</v>
@@ -11266,30 +11266,30 @@
         <v>0</v>
       </c>
       <c r="M244" t="n">
-        <v>279</v>
+        <v>934</v>
       </c>
       <c r="N244" t="n">
-        <v>10713.21</v>
+        <v>3821</v>
       </c>
       <c r="O244" t="n">
-        <v>2988985.59</v>
+        <v>3568814</v>
       </c>
       <c r="P244" t="n">
-        <v>20900</v>
+        <v>5900</v>
       </c>
       <c r="Q244" t="n">
-        <v>5831100</v>
+        <v>5510600</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>C4607</t>
+          <t>C4614</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>MAQUILLAJE SIRENA C4607</t>
+          <t>CASTILLO NIÑA C4614</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -11303,7 +11303,7 @@
         </is>
       </c>
       <c r="J245" t="n">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="K245" t="n">
         <v>0</v>
@@ -11312,30 +11312,30 @@
         <v>0</v>
       </c>
       <c r="M245" t="n">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="N245" t="n">
-        <v>10817</v>
+        <v>15472</v>
       </c>
       <c r="O245" t="n">
-        <v>1719903</v>
+        <v>2227968</v>
       </c>
       <c r="P245" t="n">
-        <v>17900</v>
+        <v>25900</v>
       </c>
       <c r="Q245" t="n">
-        <v>2846100</v>
+        <v>3729600</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>C4609</t>
+          <t>C4616</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>MAQUILLAJE UNICORNIO C4609</t>
+          <t>CARRO TRANSFORME AMARILLO RECARGABLE C4616</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -11349,7 +11349,7 @@
         </is>
       </c>
       <c r="J246" t="n">
-        <v>79</v>
+        <v>8</v>
       </c>
       <c r="K246" t="n">
         <v>0</v>
@@ -11358,30 +11358,30 @@
         <v>0</v>
       </c>
       <c r="M246" t="n">
-        <v>79</v>
+        <v>8</v>
       </c>
       <c r="N246" t="n">
-        <v>12489</v>
+        <v>48522</v>
       </c>
       <c r="O246" t="n">
-        <v>986631</v>
+        <v>388176</v>
       </c>
       <c r="P246" t="n">
-        <v>20900</v>
+        <v>77900</v>
       </c>
       <c r="Q246" t="n">
-        <v>1651100</v>
+        <v>623200</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>C4612</t>
+          <t>C4622</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>CARRUAJE MUÑECA C4612</t>
+          <t>CARRO COLECCION X8 C4622</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -11395,7 +11395,7 @@
         </is>
       </c>
       <c r="J247" t="n">
-        <v>166</v>
+        <v>240</v>
       </c>
       <c r="K247" t="n">
         <v>0</v>
@@ -11404,30 +11404,30 @@
         <v>0</v>
       </c>
       <c r="M247" t="n">
-        <v>166</v>
+        <v>240</v>
       </c>
       <c r="N247" t="n">
-        <v>21762</v>
+        <v>5476</v>
       </c>
       <c r="O247" t="n">
-        <v>3612492</v>
+        <v>1314240</v>
       </c>
       <c r="P247" t="n">
-        <v>35900</v>
+        <v>8900</v>
       </c>
       <c r="Q247" t="n">
-        <v>5959400</v>
+        <v>2136000</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>C4613</t>
+          <t>C4629</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>DIDACTICOS ARMABLES STD C4613</t>
+          <t>COMPUTADOR USB CABLE C4629</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -11441,7 +11441,7 @@
         </is>
       </c>
       <c r="J248" t="n">
-        <v>934</v>
+        <v>36</v>
       </c>
       <c r="K248" t="n">
         <v>0</v>
@@ -11450,30 +11450,30 @@
         <v>0</v>
       </c>
       <c r="M248" t="n">
-        <v>934</v>
+        <v>36</v>
       </c>
       <c r="N248" t="n">
-        <v>3821</v>
+        <v>64612</v>
       </c>
       <c r="O248" t="n">
-        <v>3568814</v>
+        <v>2326032</v>
       </c>
       <c r="P248" t="n">
-        <v>5900</v>
+        <v>103900</v>
       </c>
       <c r="Q248" t="n">
-        <v>5510600</v>
+        <v>3740400</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>C4614</t>
+          <t>C4630</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>CASTILLO NIÑA C4614</t>
+          <t>COMPUTADOR USB INGLES/ESPAÑOL C4630</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -11487,7 +11487,7 @@
         </is>
       </c>
       <c r="J249" t="n">
-        <v>144</v>
+        <v>56</v>
       </c>
       <c r="K249" t="n">
         <v>0</v>
@@ -11496,30 +11496,30 @@
         <v>0</v>
       </c>
       <c r="M249" t="n">
-        <v>144</v>
+        <v>56</v>
       </c>
       <c r="N249" t="n">
-        <v>15472</v>
+        <v>38252</v>
       </c>
       <c r="O249" t="n">
-        <v>2227968</v>
+        <v>2142112</v>
       </c>
       <c r="P249" t="n">
-        <v>25900</v>
+        <v>61900</v>
       </c>
       <c r="Q249" t="n">
-        <v>3729600</v>
+        <v>3466400</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>C4616</t>
+          <t>C4631</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>CARRO TRANSFORME AMARILLO RECARGABLE C4616</t>
+          <t>SQUISHY MOSTRICO STD C4631</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -11533,7 +11533,7 @@
         </is>
       </c>
       <c r="J250" t="n">
-        <v>8</v>
+        <v>864</v>
       </c>
       <c r="K250" t="n">
         <v>0</v>
@@ -11542,30 +11542,30 @@
         <v>0</v>
       </c>
       <c r="M250" t="n">
-        <v>8</v>
+        <v>864</v>
       </c>
       <c r="N250" t="n">
-        <v>48522</v>
+        <v>1516.0387367881</v>
       </c>
       <c r="O250" t="n">
-        <v>388176</v>
+        <v>1309857.468584918</v>
       </c>
       <c r="P250" t="n">
-        <v>77900</v>
+        <v>2300</v>
       </c>
       <c r="Q250" t="n">
-        <v>623200</v>
+        <v>1987200</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>C4622</t>
+          <t>C466-IO</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>CARRO COLECCION X8 C4622</t>
+          <t>GLOBO FIGURAS TORNASOL Y MATE</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -11579,7 +11579,7 @@
         </is>
       </c>
       <c r="J251" t="n">
-        <v>240</v>
+        <v>1050</v>
       </c>
       <c r="K251" t="n">
         <v>0</v>
@@ -11588,30 +11588,30 @@
         <v>0</v>
       </c>
       <c r="M251" t="n">
-        <v>240</v>
+        <v>1050</v>
       </c>
       <c r="N251" t="n">
-        <v>5476</v>
+        <v>356.78</v>
       </c>
       <c r="O251" t="n">
-        <v>1314240</v>
+        <v>374619</v>
       </c>
       <c r="P251" t="n">
-        <v>8900</v>
+        <v>300</v>
       </c>
       <c r="Q251" t="n">
-        <v>2136000</v>
+        <v>315000</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>C4629</t>
+          <t>C4728</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>COMPUTADOR USB CABLE C4629</t>
+          <t>FLIOTADOR DONA DINOSAURIO #60 C4728</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -11625,7 +11625,7 @@
         </is>
       </c>
       <c r="J252" t="n">
-        <v>36</v>
+        <v>550</v>
       </c>
       <c r="K252" t="n">
         <v>0</v>
@@ -11634,44 +11634,42 @@
         <v>0</v>
       </c>
       <c r="M252" t="n">
-        <v>36</v>
+        <v>550</v>
       </c>
       <c r="N252" t="n">
-        <v>64612</v>
+        <v>2454</v>
       </c>
       <c r="O252" t="n">
-        <v>2326032</v>
+        <v>1349700</v>
       </c>
       <c r="P252" t="n">
-        <v>103900</v>
+        <v>4200</v>
       </c>
       <c r="Q252" t="n">
-        <v>3740400</v>
+        <v>2310000</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>C4630</t>
-        </is>
+          <t>C476</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>6932001041468</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>COMPUTADOR USB INGLES/ESPAÑOL C4630</t>
-        </is>
-      </c>
-      <c r="E253" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>YENGA MADERA GRABDE</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J253" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K253" t="n">
         <v>0</v>
@@ -11680,30 +11678,30 @@
         <v>0</v>
       </c>
       <c r="M253" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="N253" t="n">
-        <v>38252</v>
+        <v>5347.73</v>
       </c>
       <c r="O253" t="n">
-        <v>2142112</v>
+        <v>288777.42</v>
       </c>
       <c r="P253" t="n">
-        <v>61900</v>
+        <v>9500</v>
       </c>
       <c r="Q253" t="n">
-        <v>3466400</v>
+        <v>513000</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>C4631</t>
+          <t>C4812</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>SQUISHY MOSTRICO STD C4631</t>
+          <t>BURBUJERO DE ESPADA 44cm</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -11717,7 +11715,7 @@
         </is>
       </c>
       <c r="J254" t="n">
-        <v>864</v>
+        <v>4464</v>
       </c>
       <c r="K254" t="n">
         <v>0</v>
@@ -11726,30 +11724,30 @@
         <v>0</v>
       </c>
       <c r="M254" t="n">
-        <v>864</v>
+        <v>4464</v>
       </c>
       <c r="N254" t="n">
-        <v>1516.0387386003</v>
+        <v>1801</v>
       </c>
       <c r="O254" t="n">
-        <v>1309857.470150659</v>
+        <v>8039664</v>
       </c>
       <c r="P254" t="n">
-        <v>2300</v>
+        <v>2900</v>
       </c>
       <c r="Q254" t="n">
-        <v>1987200</v>
+        <v>12945600</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>C466-IO</t>
+          <t>C494-IO</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>GLOBO FIGURAS TORNASOL Y MATE</t>
+          <t>GLOBO METALIZADO DULCES</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -11763,7 +11761,7 @@
         </is>
       </c>
       <c r="J255" t="n">
-        <v>1050</v>
+        <v>1352</v>
       </c>
       <c r="K255" t="n">
         <v>0</v>
@@ -11772,30 +11770,33 @@
         <v>0</v>
       </c>
       <c r="M255" t="n">
-        <v>1050</v>
+        <v>1352</v>
       </c>
       <c r="N255" t="n">
-        <v>356.78</v>
+        <v>1200</v>
       </c>
       <c r="O255" t="n">
-        <v>374619</v>
+        <v>1622400</v>
       </c>
       <c r="P255" t="n">
-        <v>300</v>
+        <v>1500</v>
       </c>
       <c r="Q255" t="n">
-        <v>315000</v>
+        <v>2028000</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>C4728</t>
-        </is>
+          <t>C4945</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>7700154271143</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>FLIOTADOR DONA DINOSAURIO #60 C4728</t>
+          <t>MUÑECA CON MASCOTA Y COCHE C4945</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -11809,7 +11810,7 @@
         </is>
       </c>
       <c r="J256" t="n">
-        <v>550</v>
+        <v>402</v>
       </c>
       <c r="K256" t="n">
         <v>0</v>
@@ -11818,42 +11819,47 @@
         <v>0</v>
       </c>
       <c r="M256" t="n">
-        <v>550</v>
+        <v>402</v>
       </c>
       <c r="N256" t="n">
-        <v>2454</v>
+        <v>11690</v>
       </c>
       <c r="O256" t="n">
-        <v>1349700</v>
+        <v>4699380</v>
       </c>
       <c r="P256" t="n">
-        <v>4200</v>
+        <v>18900</v>
       </c>
       <c r="Q256" t="n">
-        <v>2310000</v>
+        <v>7597800</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>C476</t>
+          <t>C4946</t>
         </is>
       </c>
       <c r="B257" t="n">
-        <v>6932001041468</v>
+        <v>7700154271143</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>YENGA MADERA GRABDE</t>
+          <t>MUÑECA CON ODONTOLOGIA C4946</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J257" t="n">
-        <v>54</v>
+        <v>360</v>
       </c>
       <c r="K257" t="n">
         <v>0</v>
@@ -11862,30 +11868,33 @@
         <v>0</v>
       </c>
       <c r="M257" t="n">
-        <v>54</v>
+        <v>360</v>
       </c>
       <c r="N257" t="n">
-        <v>5347.73</v>
+        <v>13518</v>
       </c>
       <c r="O257" t="n">
-        <v>288777.42</v>
+        <v>4866480</v>
       </c>
       <c r="P257" t="n">
-        <v>9500</v>
+        <v>21900</v>
       </c>
       <c r="Q257" t="n">
-        <v>513000</v>
+        <v>7884000</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>C4812</t>
-        </is>
+          <t>C4947</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>7700154271143</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>BURBUJERO DE ESPADA 44cm</t>
+          <t>MUÑECA CON MASCOTAS   C4947</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -11899,7 +11908,7 @@
         </is>
       </c>
       <c r="J258" t="n">
-        <v>4464</v>
+        <v>396</v>
       </c>
       <c r="K258" t="n">
         <v>0</v>
@@ -11908,30 +11917,33 @@
         <v>0</v>
       </c>
       <c r="M258" t="n">
-        <v>4464</v>
+        <v>396</v>
       </c>
       <c r="N258" t="n">
-        <v>1801</v>
+        <v>9736</v>
       </c>
       <c r="O258" t="n">
-        <v>8039664</v>
+        <v>3855456</v>
       </c>
       <c r="P258" t="n">
-        <v>2900</v>
+        <v>15900</v>
       </c>
       <c r="Q258" t="n">
-        <v>12945600</v>
+        <v>6296400</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>C494-IO</t>
-        </is>
+          <t>C4958</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>7700154271143</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>GLOBO METALIZADO DULCES</t>
+          <t>MUÑECA PATINADORA CONTROL REMOTO</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -11945,7 +11957,7 @@
         </is>
       </c>
       <c r="J259" t="n">
-        <v>1352</v>
+        <v>24</v>
       </c>
       <c r="K259" t="n">
         <v>0</v>
@@ -11954,25 +11966,25 @@
         <v>0</v>
       </c>
       <c r="M259" t="n">
-        <v>1352</v>
+        <v>24</v>
       </c>
       <c r="N259" t="n">
-        <v>1200</v>
+        <v>44470</v>
       </c>
       <c r="O259" t="n">
-        <v>1622400</v>
+        <v>1067280</v>
       </c>
       <c r="P259" t="n">
-        <v>1500</v>
+        <v>71900</v>
       </c>
       <c r="Q259" t="n">
-        <v>2028000</v>
+        <v>1725600</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>C4945</t>
+          <t>C4959</t>
         </is>
       </c>
       <c r="B260" t="n">
@@ -11980,7 +11992,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>MUÑECA CON MASCOTA Y COCHE C4945</t>
+          <t>MUÑECA POP ACCESORIOS C4959</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -11994,7 +12006,7 @@
         </is>
       </c>
       <c r="J260" t="n">
-        <v>402</v>
+        <v>634</v>
       </c>
       <c r="K260" t="n">
         <v>0</v>
@@ -12003,47 +12015,42 @@
         <v>0</v>
       </c>
       <c r="M260" t="n">
-        <v>402</v>
+        <v>634</v>
       </c>
       <c r="N260" t="n">
-        <v>11690</v>
+        <v>5215</v>
       </c>
       <c r="O260" t="n">
-        <v>4699380</v>
+        <v>3306310</v>
       </c>
       <c r="P260" t="n">
-        <v>18900</v>
+        <v>8900</v>
       </c>
       <c r="Q260" t="n">
-        <v>7597800</v>
+        <v>5642600</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>C4946</t>
+          <t>C502</t>
         </is>
       </c>
       <c r="B261" t="n">
-        <v>7700154271143</v>
+        <v>6952216485215</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>MUÑECA CON ODONTOLOGIA C4946</t>
-        </is>
-      </c>
-      <c r="E261" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>C502 MUNECA NANCY GRANDE</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J261" t="n">
-        <v>360</v>
+        <v>55</v>
       </c>
       <c r="K261" t="n">
         <v>0</v>
@@ -12052,38 +12059,38 @@
         <v>0</v>
       </c>
       <c r="M261" t="n">
-        <v>360</v>
+        <v>55</v>
       </c>
       <c r="N261" t="n">
-        <v>13518</v>
+        <v>15423.36</v>
       </c>
       <c r="O261" t="n">
-        <v>4866480</v>
+        <v>848284.8</v>
       </c>
       <c r="P261" t="n">
-        <v>21900</v>
+        <v>24900</v>
       </c>
       <c r="Q261" t="n">
-        <v>7884000</v>
+        <v>1369500</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>C4947</t>
+          <t>C5030</t>
         </is>
       </c>
       <c r="B262" t="n">
-        <v>7700154271143</v>
+        <v>6999899236062</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>MUÑECA CON MASCOTAS   C4947</t>
+          <t>INFLABLE DONA LLANTA C5030</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>INFLABLES</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -12092,7 +12099,7 @@
         </is>
       </c>
       <c r="J262" t="n">
-        <v>396</v>
+        <v>121</v>
       </c>
       <c r="K262" t="n">
         <v>0</v>
@@ -12101,38 +12108,38 @@
         <v>0</v>
       </c>
       <c r="M262" t="n">
-        <v>396</v>
+        <v>121</v>
       </c>
       <c r="N262" t="n">
-        <v>9736</v>
+        <v>2857.22</v>
       </c>
       <c r="O262" t="n">
-        <v>3855456</v>
+        <v>345723.62</v>
       </c>
       <c r="P262" t="n">
-        <v>15900</v>
+        <v>4900</v>
       </c>
       <c r="Q262" t="n">
-        <v>6296400</v>
+        <v>592900</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>C4958</t>
+          <t>C5032</t>
         </is>
       </c>
       <c r="B263" t="n">
-        <v>7700154271143</v>
+        <v>6999899236154</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>MUÑECA PATINADORA CONTROL REMOTO</t>
+          <t>INFLABLE TECHITO PIECITOS  FIGURAS STD C5032</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>INFLABLES</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -12141,7 +12148,7 @@
         </is>
       </c>
       <c r="J263" t="n">
-        <v>24</v>
+        <v>534</v>
       </c>
       <c r="K263" t="n">
         <v>0</v>
@@ -12150,47 +12157,42 @@
         <v>0</v>
       </c>
       <c r="M263" t="n">
-        <v>24</v>
+        <v>534</v>
       </c>
       <c r="N263" t="n">
-        <v>44470</v>
+        <v>8945.379999999999</v>
       </c>
       <c r="O263" t="n">
-        <v>1067280</v>
+        <v>4776832.92</v>
       </c>
       <c r="P263" t="n">
-        <v>71900</v>
+        <v>14900</v>
       </c>
       <c r="Q263" t="n">
-        <v>1725600</v>
+        <v>7956600</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>C4959</t>
+          <t>C506</t>
         </is>
       </c>
       <c r="B264" t="n">
-        <v>7700154271143</v>
+        <v>6952365180054</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>MUÑECA POP ACCESORIOS C4959</t>
-        </is>
-      </c>
-      <c r="E264" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>GLOBO BURBUJA 30</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J264" t="n">
-        <v>684</v>
+        <v>3650</v>
       </c>
       <c r="K264" t="n">
         <v>0</v>
@@ -12199,42 +12201,44 @@
         <v>0</v>
       </c>
       <c r="M264" t="n">
-        <v>684</v>
+        <v>3650</v>
       </c>
       <c r="N264" t="n">
-        <v>5215</v>
+        <v>675.2255375485</v>
       </c>
       <c r="O264" t="n">
-        <v>3567060</v>
+        <v>2464573.212052025</v>
       </c>
       <c r="P264" t="n">
-        <v>8900</v>
+        <v>1300</v>
       </c>
       <c r="Q264" t="n">
-        <v>6087600</v>
+        <v>4745000</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>C502</t>
-        </is>
-      </c>
-      <c r="B265" t="n">
-        <v>6952216485215</v>
+          <t>C510-IO</t>
+        </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>C502 MUNECA NANCY GRANDE</t>
+          <t>GLOBO BURBUJA METALIZADO</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>GLOBOS</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J265" t="n">
-        <v>55</v>
+        <v>3896</v>
       </c>
       <c r="K265" t="n">
         <v>0</v>
@@ -12243,47 +12247,42 @@
         <v>0</v>
       </c>
       <c r="M265" t="n">
-        <v>55</v>
+        <v>3896</v>
       </c>
       <c r="N265" t="n">
-        <v>15423.36</v>
+        <v>960</v>
       </c>
       <c r="O265" t="n">
-        <v>848284.8</v>
+        <v>3740160</v>
       </c>
       <c r="P265" t="n">
-        <v>24900</v>
+        <v>1200</v>
       </c>
       <c r="Q265" t="n">
-        <v>1369500</v>
+        <v>4675200</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>C5030</t>
+          <t>C515</t>
         </is>
       </c>
       <c r="B266" t="n">
-        <v>6999899236062</v>
+        <v>6953626330010</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>INFLABLE DONA LLANTA C5030</t>
-        </is>
-      </c>
-      <c r="E266" t="inlineStr">
-        <is>
-          <t>INFLABLES</t>
+          <t>GLOBO FIGURAS BURBUJA</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J266" t="n">
-        <v>121</v>
+        <v>3800</v>
       </c>
       <c r="K266" t="n">
         <v>0</v>
@@ -12292,38 +12291,35 @@
         <v>0</v>
       </c>
       <c r="M266" t="n">
-        <v>121</v>
+        <v>3800</v>
       </c>
       <c r="N266" t="n">
-        <v>2857.22</v>
+        <v>583.7204926325001</v>
       </c>
       <c r="O266" t="n">
-        <v>345723.62</v>
+        <v>2218137.8720035</v>
       </c>
       <c r="P266" t="n">
-        <v>4900</v>
+        <v>600</v>
       </c>
       <c r="Q266" t="n">
-        <v>592900</v>
+        <v>2280000</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>C5032</t>
-        </is>
-      </c>
-      <c r="B267" t="n">
-        <v>6999899236154</v>
+          <t>C5214</t>
+        </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>INFLABLE TECHITO PIECITOS  FIGURAS STD C5032</t>
+          <t>CUBO C5214</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>INFLABLES</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -12332,7 +12328,7 @@
         </is>
       </c>
       <c r="J267" t="n">
-        <v>534</v>
+        <v>1440</v>
       </c>
       <c r="K267" t="n">
         <v>0</v>
@@ -12341,33 +12337,33 @@
         <v>0</v>
       </c>
       <c r="M267" t="n">
-        <v>534</v>
+        <v>1440</v>
       </c>
       <c r="N267" t="n">
-        <v>8945.379999999999</v>
+        <v>1690.8700094251</v>
       </c>
       <c r="O267" t="n">
-        <v>4776832.92</v>
+        <v>2434852.813572144</v>
       </c>
       <c r="P267" t="n">
-        <v>14900</v>
+        <v>3000</v>
       </c>
       <c r="Q267" t="n">
-        <v>7956600</v>
+        <v>4320000</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>C506</t>
+          <t>C523</t>
         </is>
       </c>
       <c r="B268" t="n">
-        <v>6952365180054</v>
+        <v>6957430180212</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>GLOBO BURBUJA 30</t>
+          <t>GLOBO NUMERO 16PLATEADO Y DORADO</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -12376,7 +12372,7 @@
         </is>
       </c>
       <c r="J268" t="n">
-        <v>3650</v>
+        <v>2556</v>
       </c>
       <c r="K268" t="n">
         <v>0</v>
@@ -12385,44 +12381,42 @@
         <v>0</v>
       </c>
       <c r="M268" t="n">
-        <v>3650</v>
+        <v>2556</v>
       </c>
       <c r="N268" t="n">
-        <v>675.2255375485</v>
+        <v>481.48790873239</v>
       </c>
       <c r="O268" t="n">
-        <v>2464573.212052025</v>
+        <v>1230683.094719989</v>
       </c>
       <c r="P268" t="n">
-        <v>1300</v>
+        <v>650</v>
       </c>
       <c r="Q268" t="n">
-        <v>4745000</v>
+        <v>1661400</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>C510-IO</t>
-        </is>
+          <t>C524</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>6957430180229</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>GLOBO BURBUJA METALIZADO</t>
-        </is>
-      </c>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>GLOBOS</t>
+          <t>GLOBO NUMERO 30 PLATEADO Y DORADO</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J269" t="n">
-        <v>3896</v>
+        <v>614</v>
       </c>
       <c r="K269" t="n">
         <v>0</v>
@@ -12431,42 +12425,47 @@
         <v>0</v>
       </c>
       <c r="M269" t="n">
-        <v>3896</v>
+        <v>614</v>
       </c>
       <c r="N269" t="n">
-        <v>960</v>
+        <v>872.15418687873</v>
       </c>
       <c r="O269" t="n">
-        <v>3740160</v>
+        <v>535502.6707435403</v>
       </c>
       <c r="P269" t="n">
         <v>1200</v>
       </c>
       <c r="Q269" t="n">
-        <v>4675200</v>
+        <v>736800</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>C515</t>
+          <t>C5246/C5247</t>
         </is>
       </c>
       <c r="B270" t="n">
-        <v>6953626330010</v>
+        <v>6900077483239</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>GLOBO FIGURAS BURBUJA</t>
+          <t>MARIONETA DE DEDO ANIMALES STDS C5246/C5247</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J270" t="n">
-        <v>3800</v>
+        <v>130</v>
       </c>
       <c r="K270" t="n">
         <v>0</v>
@@ -12475,44 +12474,42 @@
         <v>0</v>
       </c>
       <c r="M270" t="n">
-        <v>3800</v>
+        <v>130</v>
       </c>
       <c r="N270" t="n">
-        <v>583.7204926325001</v>
+        <v>8702.219999999999</v>
       </c>
       <c r="O270" t="n">
-        <v>2218137.8720035</v>
+        <v>1131288.6</v>
       </c>
       <c r="P270" t="n">
-        <v>600</v>
+        <v>8900</v>
       </c>
       <c r="Q270" t="n">
-        <v>2280000</v>
+        <v>1157000</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>C5214</t>
-        </is>
+          <t>C525</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>6957430180236</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>CUBO C5214</t>
-        </is>
-      </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
+          <t>GLOBO NUMERO 16 COLORES Y PUNTOS</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J271" t="n">
-        <v>1440</v>
+        <v>1436</v>
       </c>
       <c r="K271" t="n">
         <v>0</v>
@@ -12521,33 +12518,33 @@
         <v>0</v>
       </c>
       <c r="M271" t="n">
-        <v>1440</v>
+        <v>1436</v>
       </c>
       <c r="N271" t="n">
-        <v>1690.8700094029</v>
+        <v>345.55838583542</v>
       </c>
       <c r="O271" t="n">
-        <v>2434852.813540176</v>
+        <v>496221.8420596631</v>
       </c>
       <c r="P271" t="n">
-        <v>3000</v>
+        <v>600</v>
       </c>
       <c r="Q271" t="n">
-        <v>4320000</v>
+        <v>861600</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>C523</t>
+          <t>C526</t>
         </is>
       </c>
       <c r="B272" t="n">
-        <v>6957430180212</v>
+        <v>6957430180243</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>GLOBO NUMERO 16PLATEADO Y DORADO</t>
+          <t>GLOBO NUMERO 30 COLORES Y PUNTOS</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -12556,7 +12553,7 @@
         </is>
       </c>
       <c r="J272" t="n">
-        <v>2556</v>
+        <v>11416</v>
       </c>
       <c r="K272" t="n">
         <v>0</v>
@@ -12565,42 +12562,47 @@
         <v>0</v>
       </c>
       <c r="M272" t="n">
-        <v>2556</v>
+        <v>11416</v>
       </c>
       <c r="N272" t="n">
-        <v>481.48790873239</v>
+        <v>711.33664496242</v>
       </c>
       <c r="O272" t="n">
-        <v>1230683.094719989</v>
+        <v>8120619.138890986</v>
       </c>
       <c r="P272" t="n">
-        <v>650</v>
+        <v>900</v>
       </c>
       <c r="Q272" t="n">
-        <v>1661400</v>
+        <v>10274400</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>C524</t>
+          <t>C527-IO</t>
         </is>
       </c>
       <c r="B273" t="n">
-        <v>6957430180229</v>
+        <v>6957430180526</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>GLOBO NUMERO 30 PLATEADO Y DORADO</t>
+          <t>GLOBO FELIZ CUMPLEAÑOS LISTON</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>GLOBOS</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J273" t="n">
-        <v>614</v>
+        <v>1242</v>
       </c>
       <c r="K273" t="n">
         <v>0</v>
@@ -12609,38 +12611,35 @@
         <v>0</v>
       </c>
       <c r="M273" t="n">
-        <v>614</v>
+        <v>1242</v>
       </c>
       <c r="N273" t="n">
-        <v>872.15418687873</v>
+        <v>815.0599999999999</v>
       </c>
       <c r="O273" t="n">
-        <v>535502.6707435403</v>
+        <v>1012304.52</v>
       </c>
       <c r="P273" t="n">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="Q273" t="n">
-        <v>736800</v>
+        <v>1117800</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>C5246/C5247</t>
-        </is>
-      </c>
-      <c r="B274" t="n">
-        <v>6900077483239</v>
+          <t>C541</t>
+        </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>MARIONETA DE DEDO ANIMALES STDS C5246/C5247</t>
+          <t>GLOBO LLAMA PQÑO</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -12649,7 +12648,7 @@
         </is>
       </c>
       <c r="J274" t="n">
-        <v>130</v>
+        <v>2150</v>
       </c>
       <c r="K274" t="n">
         <v>0</v>
@@ -12658,42 +12657,44 @@
         <v>0</v>
       </c>
       <c r="M274" t="n">
-        <v>130</v>
+        <v>2150</v>
       </c>
       <c r="N274" t="n">
-        <v>8702.219999999999</v>
+        <v>800</v>
       </c>
       <c r="O274" t="n">
-        <v>1131288.6</v>
+        <v>1720000</v>
       </c>
       <c r="P274" t="n">
-        <v>8900</v>
+        <v>1000</v>
       </c>
       <c r="Q274" t="n">
-        <v>1157000</v>
+        <v>2150000</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>C525</t>
-        </is>
-      </c>
-      <c r="B275" t="n">
-        <v>6957430180236</v>
+          <t>C575-IO</t>
+        </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>GLOBO NUMERO 16 COLORES Y PUNTOS</t>
+          <t>GLOBO UNICORNIO PQÑO</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J275" t="n">
-        <v>1436</v>
+        <v>1001</v>
       </c>
       <c r="K275" t="n">
         <v>0</v>
@@ -12702,42 +12703,47 @@
         <v>0</v>
       </c>
       <c r="M275" t="n">
-        <v>1436</v>
+        <v>1001</v>
       </c>
       <c r="N275" t="n">
-        <v>345.55838583542</v>
+        <v>320</v>
       </c>
       <c r="O275" t="n">
-        <v>496221.8420596631</v>
+        <v>320320</v>
       </c>
       <c r="P275" t="n">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="Q275" t="n">
-        <v>861600</v>
+        <v>400400</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>C526</t>
+          <t>C596-IO</t>
         </is>
       </c>
       <c r="B276" t="n">
-        <v>6957430180243</v>
+        <v>8596162180268</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>GLOBO NUMERO 30 COLORES Y PUNTOS</t>
+          <t>GLOBO TE AMO</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>GLOBOS</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J276" t="n">
-        <v>11416</v>
+        <v>1455</v>
       </c>
       <c r="K276" t="n">
         <v>0</v>
@@ -12746,33 +12752,33 @@
         <v>0</v>
       </c>
       <c r="M276" t="n">
-        <v>11416</v>
+        <v>1455</v>
       </c>
       <c r="N276" t="n">
-        <v>711.33664496242</v>
+        <v>1044.54</v>
       </c>
       <c r="O276" t="n">
-        <v>8120619.138890986</v>
+        <v>1519805.7</v>
       </c>
       <c r="P276" t="n">
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="Q276" t="n">
-        <v>10274400</v>
+        <v>1746000</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>C527-IO</t>
+          <t>C60-IO</t>
         </is>
       </c>
       <c r="B277" t="n">
-        <v>6957430180526</v>
+        <v>6524521011245</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>GLOBO FELIZ CUMPLEAÑOS LISTON</t>
+          <t>GLOBO TIKTOK BOUQUET</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -12786,7 +12792,7 @@
         </is>
       </c>
       <c r="J277" t="n">
-        <v>1242</v>
+        <v>740</v>
       </c>
       <c r="K277" t="n">
         <v>0</v>
@@ -12795,35 +12801,35 @@
         <v>0</v>
       </c>
       <c r="M277" t="n">
-        <v>1242</v>
+        <v>740</v>
       </c>
       <c r="N277" t="n">
-        <v>815.0599999999999</v>
+        <v>1989.05</v>
       </c>
       <c r="O277" t="n">
-        <v>1012304.52</v>
+        <v>1471897</v>
       </c>
       <c r="P277" t="n">
-        <v>900</v>
+        <v>3000</v>
       </c>
       <c r="Q277" t="n">
-        <v>1117800</v>
+        <v>2220000</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>C541</t>
+          <t>C6074</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>GLOBO LLAMA PQÑO</t>
+          <t>FIGURAS ALIMENTOS DECORATIVOS C6074</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -12832,7 +12838,7 @@
         </is>
       </c>
       <c r="J278" t="n">
-        <v>2150</v>
+        <v>25</v>
       </c>
       <c r="K278" t="n">
         <v>0</v>
@@ -12841,44 +12847,42 @@
         <v>0</v>
       </c>
       <c r="M278" t="n">
-        <v>2150</v>
+        <v>25</v>
       </c>
       <c r="N278" t="n">
-        <v>800</v>
+        <v>9447.25</v>
       </c>
       <c r="O278" t="n">
-        <v>1720000</v>
+        <v>236181.25</v>
       </c>
       <c r="P278" t="n">
-        <v>1000</v>
+        <v>9900</v>
       </c>
       <c r="Q278" t="n">
-        <v>2150000</v>
+        <v>247500</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>C575-IO</t>
-        </is>
+          <t>C629</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>7791638082188</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>GLOBO UNICORNIO PQÑO</t>
-        </is>
-      </c>
-      <c r="E279" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>BURBUJERO PITO STD</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J279" t="n">
-        <v>1001</v>
+        <v>15264</v>
       </c>
       <c r="K279" t="n">
         <v>0</v>
@@ -12887,38 +12891,38 @@
         <v>0</v>
       </c>
       <c r="M279" t="n">
-        <v>1001</v>
+        <v>15264</v>
       </c>
       <c r="N279" t="n">
-        <v>320</v>
+        <v>703.79472483574</v>
       </c>
       <c r="O279" t="n">
-        <v>320320</v>
+        <v>10742722.67989274</v>
       </c>
       <c r="P279" t="n">
-        <v>400</v>
+        <v>900</v>
       </c>
       <c r="Q279" t="n">
-        <v>400400</v>
+        <v>13737600</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>C596-IO</t>
+          <t>C6406</t>
         </is>
       </c>
       <c r="B280" t="n">
-        <v>8596162180268</v>
+        <v>6820212541115</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>GLOBO TE AMO</t>
+          <t>PAJAROS MUSICALES DECORATIVOS C6406</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>GLOBOS</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -12927,7 +12931,7 @@
         </is>
       </c>
       <c r="J280" t="n">
-        <v>1455</v>
+        <v>52</v>
       </c>
       <c r="K280" t="n">
         <v>0</v>
@@ -12936,47 +12940,39 @@
         <v>0</v>
       </c>
       <c r="M280" t="n">
-        <v>1455</v>
+        <v>52</v>
       </c>
       <c r="N280" t="n">
-        <v>1044.54</v>
+        <v>14260.14</v>
       </c>
       <c r="O280" t="n">
-        <v>1519805.7</v>
+        <v>741527.28</v>
       </c>
       <c r="P280" t="n">
-        <v>1200</v>
+        <v>15900</v>
       </c>
       <c r="Q280" t="n">
-        <v>1746000</v>
+        <v>826800</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>C60-IO</t>
-        </is>
-      </c>
-      <c r="B281" t="n">
-        <v>6524521011245</v>
+          <t>C642</t>
+        </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>GLOBO TIKTOK BOUQUET</t>
-        </is>
-      </c>
-      <c r="E281" t="inlineStr">
-        <is>
-          <t>GLOBOS</t>
+          <t>LANZADOR AGUA</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J281" t="n">
-        <v>740</v>
+        <v>599</v>
       </c>
       <c r="K281" t="n">
         <v>0</v>
@@ -12985,35 +12981,35 @@
         <v>0</v>
       </c>
       <c r="M281" t="n">
-        <v>740</v>
+        <v>599</v>
       </c>
       <c r="N281" t="n">
-        <v>1989.05</v>
+        <v>2529.19</v>
       </c>
       <c r="O281" t="n">
-        <v>1471897</v>
+        <v>1514984.81</v>
       </c>
       <c r="P281" t="n">
-        <v>3000</v>
+        <v>5100</v>
       </c>
       <c r="Q281" t="n">
-        <v>2220000</v>
+        <v>3054900</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>C6074</t>
+          <t>C671-LJ</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>FIGURAS ALIMENTOS DECORATIVOS C6074</t>
+          <t>GLOBO UNICORNIO MEDIANO</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -13022,7 +13018,7 @@
         </is>
       </c>
       <c r="J282" t="n">
-        <v>25</v>
+        <v>1397</v>
       </c>
       <c r="K282" t="n">
         <v>0</v>
@@ -13031,42 +13027,47 @@
         <v>0</v>
       </c>
       <c r="M282" t="n">
-        <v>25</v>
+        <v>1397</v>
       </c>
       <c r="N282" t="n">
-        <v>9447.25</v>
+        <v>400</v>
       </c>
       <c r="O282" t="n">
-        <v>236181.25</v>
+        <v>558800</v>
       </c>
       <c r="P282" t="n">
-        <v>9900</v>
+        <v>500</v>
       </c>
       <c r="Q282" t="n">
-        <v>247500</v>
+        <v>698500</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>C629</t>
+          <t>C7005</t>
         </is>
       </c>
       <c r="B283" t="n">
-        <v>7791638082188</v>
+        <v>6874123039124</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>BURBUJERO PITO STD</t>
+          <t>MAQUINA DE COSER C7005</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J283" t="n">
-        <v>15264</v>
+        <v>208</v>
       </c>
       <c r="K283" t="n">
         <v>0</v>
@@ -13075,38 +13076,38 @@
         <v>0</v>
       </c>
       <c r="M283" t="n">
-        <v>15264</v>
+        <v>208</v>
       </c>
       <c r="N283" t="n">
-        <v>703.79473431536</v>
+        <v>6078.9926048565</v>
       </c>
       <c r="O283" t="n">
-        <v>10742722.82458965</v>
+        <v>1264430.461810152</v>
       </c>
       <c r="P283" t="n">
-        <v>900</v>
+        <v>18500</v>
       </c>
       <c r="Q283" t="n">
-        <v>13737600</v>
+        <v>3848000</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>C6406</t>
+          <t>C7009</t>
         </is>
       </c>
       <c r="B284" t="n">
-        <v>6820212541115</v>
+        <v>2024250256831</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>PAJAROS MUSICALES DECORATIVOS C6406</t>
+          <t>LANZADORA DE AGUA  TUBO CON HELICE C7009</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>LANZADORES</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -13115,7 +13116,7 @@
         </is>
       </c>
       <c r="J284" t="n">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="K284" t="n">
         <v>0</v>
@@ -13124,39 +13125,47 @@
         <v>0</v>
       </c>
       <c r="M284" t="n">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="N284" t="n">
-        <v>14260.14</v>
+        <v>5899.18</v>
       </c>
       <c r="O284" t="n">
-        <v>741527.28</v>
+        <v>70790.16</v>
       </c>
       <c r="P284" t="n">
-        <v>15900</v>
+        <v>12500</v>
       </c>
       <c r="Q284" t="n">
-        <v>826800</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>C642</t>
-        </is>
+          <t>C7038</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>5132595141631</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>LANZADOR AGUA</t>
+          <t>LANZADORA DE AGUA GLOBO C7038</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>LANZADORES</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J285" t="n">
-        <v>599</v>
+        <v>23</v>
       </c>
       <c r="K285" t="n">
         <v>0</v>
@@ -13165,35 +13174,38 @@
         <v>0</v>
       </c>
       <c r="M285" t="n">
-        <v>599</v>
+        <v>23</v>
       </c>
       <c r="N285" t="n">
-        <v>2529.19</v>
+        <v>18423.71</v>
       </c>
       <c r="O285" t="n">
-        <v>1514984.81</v>
+        <v>423745.33</v>
       </c>
       <c r="P285" t="n">
-        <v>5100</v>
+        <v>10000</v>
       </c>
       <c r="Q285" t="n">
-        <v>3054900</v>
+        <v>230000</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>C671-LJ</t>
-        </is>
+          <t>C7039</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>5132594521182</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>GLOBO UNICORNIO MEDIANO</t>
+          <t>LANZADOR AGUA GLOBO DELFIN C7039/M90-4</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -13202,7 +13214,7 @@
         </is>
       </c>
       <c r="J286" t="n">
-        <v>1397</v>
+        <v>20</v>
       </c>
       <c r="K286" t="n">
         <v>0</v>
@@ -13211,38 +13223,38 @@
         <v>0</v>
       </c>
       <c r="M286" t="n">
-        <v>1397</v>
+        <v>20</v>
       </c>
       <c r="N286" t="n">
-        <v>400</v>
+        <v>10985.78</v>
       </c>
       <c r="O286" t="n">
-        <v>558800</v>
+        <v>219715.6</v>
       </c>
       <c r="P286" t="n">
-        <v>500</v>
+        <v>15000</v>
       </c>
       <c r="Q286" t="n">
-        <v>698500</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>C7005</t>
+          <t>C7040</t>
         </is>
       </c>
       <c r="B287" t="n">
-        <v>6874123039124</v>
+        <v>6920373004365</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>MAQUINA DE COSER C7005</t>
+          <t>GARAJE EXIBICION CON LUZ C7040</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -13251,7 +13263,7 @@
         </is>
       </c>
       <c r="J287" t="n">
-        <v>208</v>
+        <v>47</v>
       </c>
       <c r="K287" t="n">
         <v>0</v>
@@ -13260,38 +13272,38 @@
         <v>0</v>
       </c>
       <c r="M287" t="n">
-        <v>208</v>
+        <v>47</v>
       </c>
       <c r="N287" t="n">
-        <v>6078.9926048565</v>
+        <v>23452.77</v>
       </c>
       <c r="O287" t="n">
-        <v>1264430.461810152</v>
+        <v>1102280.19</v>
       </c>
       <c r="P287" t="n">
-        <v>18500</v>
+        <v>39900</v>
       </c>
       <c r="Q287" t="n">
-        <v>3848000</v>
+        <v>1875300</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>C7009</t>
+          <t>C7042</t>
         </is>
       </c>
       <c r="B288" t="n">
-        <v>2024250256831</v>
+        <v>2024081616255</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>LANZADORA DE AGUA  TUBO CON HELICE C7009</t>
+          <t>CANCHA BASKETBALL WIN24 C7042</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>LANZADORES</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -13300,7 +13312,7 @@
         </is>
       </c>
       <c r="J288" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K288" t="n">
         <v>0</v>
@@ -13309,38 +13321,35 @@
         <v>0</v>
       </c>
       <c r="M288" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N288" t="n">
-        <v>5899.18</v>
+        <v>9694.41</v>
       </c>
       <c r="O288" t="n">
-        <v>70790.16</v>
+        <v>96944.10000000001</v>
       </c>
       <c r="P288" t="n">
-        <v>12500</v>
+        <v>32500</v>
       </c>
       <c r="Q288" t="n">
-        <v>150000</v>
+        <v>325000</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>C7038</t>
-        </is>
-      </c>
-      <c r="B289" t="n">
-        <v>5132595141631</v>
+          <t>C7080-BC</t>
+        </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>LANZADORA DE AGUA GLOBO C7038</t>
+          <t>ROBOT TRANSFORME STD C7080-BC</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>LANZADORES</t>
+          <t>MUÑECOS</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -13349,7 +13358,7 @@
         </is>
       </c>
       <c r="J289" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="K289" t="n">
         <v>0</v>
@@ -13358,38 +13367,38 @@
         <v>0</v>
       </c>
       <c r="M289" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="N289" t="n">
-        <v>18423.71</v>
+        <v>10556.12</v>
       </c>
       <c r="O289" t="n">
-        <v>423745.33</v>
+        <v>411688.6800000001</v>
       </c>
       <c r="P289" t="n">
-        <v>10000</v>
+        <v>32900</v>
       </c>
       <c r="Q289" t="n">
-        <v>230000</v>
+        <v>1283100</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>C7039</t>
+          <t>C7081</t>
         </is>
       </c>
       <c r="B290" t="n">
-        <v>5132594521182</v>
+        <v>6301582313156</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>LANZADOR AGUA GLOBO DELFIN C7039/M90-4</t>
+          <t>LANZADORA DARDOS DE PILA C7081</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>LANZADORES</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -13398,7 +13407,7 @@
         </is>
       </c>
       <c r="J290" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K290" t="n">
         <v>0</v>
@@ -13407,47 +13416,42 @@
         <v>0</v>
       </c>
       <c r="M290" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N290" t="n">
-        <v>10985.78</v>
+        <v>22470.62</v>
       </c>
       <c r="O290" t="n">
-        <v>219715.6</v>
+        <v>471883.02</v>
       </c>
       <c r="P290" t="n">
-        <v>15000</v>
+        <v>41900</v>
       </c>
       <c r="Q290" t="n">
-        <v>300000</v>
+        <v>879900</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>C7040</t>
+          <t>C71</t>
         </is>
       </c>
       <c r="B291" t="n">
-        <v>6920373004365</v>
+        <v>5899989622205</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>GARAJE EXIBICION CON LUZ C7040</t>
-        </is>
-      </c>
-      <c r="E291" t="inlineStr">
-        <is>
-          <t>MICELANEOS</t>
+          <t>C71 INFLABLE PONY ROSADO-AZUL</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J291" t="n">
-        <v>47</v>
+        <v>392</v>
       </c>
       <c r="K291" t="n">
         <v>0</v>
@@ -13456,38 +13460,35 @@
         <v>0</v>
       </c>
       <c r="M291" t="n">
-        <v>47</v>
+        <v>392</v>
       </c>
       <c r="N291" t="n">
-        <v>23452.77</v>
+        <v>1669.6</v>
       </c>
       <c r="O291" t="n">
-        <v>1102280.19</v>
+        <v>654483.2</v>
       </c>
       <c r="P291" t="n">
-        <v>39900</v>
+        <v>2900</v>
       </c>
       <c r="Q291" t="n">
-        <v>1875300</v>
+        <v>1136800</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>C7042</t>
-        </is>
-      </c>
-      <c r="B292" t="n">
-        <v>2024081616255</v>
+          <t>C7117</t>
+        </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>CANCHA BASKETBALL WIN24 C7042</t>
+          <t>BINGO LOTTO C7117</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUEGOS DE MESA</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -13496,7 +13497,7 @@
         </is>
       </c>
       <c r="J292" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K292" t="n">
         <v>0</v>
@@ -13505,35 +13506,35 @@
         <v>0</v>
       </c>
       <c r="M292" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="N292" t="n">
-        <v>9694.41</v>
+        <v>5798.41</v>
       </c>
       <c r="O292" t="n">
-        <v>96944.10000000001</v>
+        <v>115968.2</v>
       </c>
       <c r="P292" t="n">
-        <v>32500</v>
+        <v>14900</v>
       </c>
       <c r="Q292" t="n">
-        <v>325000</v>
+        <v>298000</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>C7080-BC</t>
+          <t>C7124</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>ROBOT TRANSFORME STD C7080-BC</t>
+          <t>TRAILER TRANFORME XQ05 C7124</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>MUÑECOS</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -13542,7 +13543,7 @@
         </is>
       </c>
       <c r="J293" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K293" t="n">
         <v>0</v>
@@ -13551,38 +13552,35 @@
         <v>0</v>
       </c>
       <c r="M293" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N293" t="n">
-        <v>10556.12</v>
+        <v>19587.53</v>
       </c>
       <c r="O293" t="n">
-        <v>411688.6800000001</v>
+        <v>783501.2</v>
       </c>
       <c r="P293" t="n">
-        <v>32900</v>
+        <v>65000</v>
       </c>
       <c r="Q293" t="n">
-        <v>1283100</v>
+        <v>2600000</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>C7081</t>
-        </is>
-      </c>
-      <c r="B294" t="n">
-        <v>6301582313156</v>
+          <t>C7132</t>
+        </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>LANZADORA DARDOS DE PILA C7081</t>
+          <t>SET PULSERAS Y CAUCHOS C7132</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>LANZADORES</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -13591,7 +13589,7 @@
         </is>
       </c>
       <c r="J294" t="n">
-        <v>21</v>
+        <v>144</v>
       </c>
       <c r="K294" t="n">
         <v>0</v>
@@ -13600,42 +13598,47 @@
         <v>0</v>
       </c>
       <c r="M294" t="n">
-        <v>21</v>
+        <v>144</v>
       </c>
       <c r="N294" t="n">
-        <v>22470.62</v>
+        <v>3100.87</v>
       </c>
       <c r="O294" t="n">
-        <v>471883.02</v>
+        <v>446525.28</v>
       </c>
       <c r="P294" t="n">
-        <v>41900</v>
+        <v>9900</v>
       </c>
       <c r="Q294" t="n">
-        <v>879900</v>
+        <v>1425600</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>C71</t>
+          <t>C7147-A</t>
         </is>
       </c>
       <c r="B295" t="n">
-        <v>5899989622205</v>
+        <v>6912209205022</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>C71 INFLABLE PONY ROSADO-AZUL</t>
+          <t>ANIMAL DINOSAURIO TRICERATOPS CONLUZ C7147-A</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J295" t="n">
-        <v>392</v>
+        <v>40</v>
       </c>
       <c r="K295" t="n">
         <v>0</v>
@@ -13644,35 +13647,38 @@
         <v>0</v>
       </c>
       <c r="M295" t="n">
-        <v>392</v>
+        <v>40</v>
       </c>
       <c r="N295" t="n">
-        <v>1669.6</v>
+        <v>10348.08</v>
       </c>
       <c r="O295" t="n">
-        <v>654483.2</v>
+        <v>413923.2</v>
       </c>
       <c r="P295" t="n">
-        <v>2900</v>
+        <v>16900</v>
       </c>
       <c r="Q295" t="n">
-        <v>1136800</v>
+        <v>676000</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>C7117</t>
-        </is>
+          <t>C7213</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>6987540143012</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>BINGO LOTTO C7117</t>
+          <t>PESCADO CON LUZ Y SONIDO C7213</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>JUEGOS DE MESA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -13681,7 +13687,7 @@
         </is>
       </c>
       <c r="J296" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="K296" t="n">
         <v>0</v>
@@ -13690,35 +13696,38 @@
         <v>0</v>
       </c>
       <c r="M296" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="N296" t="n">
-        <v>5798.41</v>
+        <v>9746.8802061856</v>
       </c>
       <c r="O296" t="n">
-        <v>115968.2</v>
+        <v>467850.2498969088</v>
       </c>
       <c r="P296" t="n">
-        <v>14900</v>
+        <v>18500</v>
       </c>
       <c r="Q296" t="n">
-        <v>298000</v>
+        <v>888000</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>C7124</t>
-        </is>
+          <t>C7221</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>7453100037446</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>TRAILER TRANFORME XQ05 C7124</t>
+          <t>RELOJ CON FICHAS ARMABLES  C7221</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -13727,7 +13736,7 @@
         </is>
       </c>
       <c r="J297" t="n">
-        <v>40</v>
+        <v>347</v>
       </c>
       <c r="K297" t="n">
         <v>0</v>
@@ -13736,30 +13745,33 @@
         <v>0</v>
       </c>
       <c r="M297" t="n">
-        <v>40</v>
+        <v>347</v>
       </c>
       <c r="N297" t="n">
-        <v>19587.53</v>
+        <v>2672.89</v>
       </c>
       <c r="O297" t="n">
-        <v>783501.2</v>
+        <v>927492.83</v>
       </c>
       <c r="P297" t="n">
-        <v>65000</v>
+        <v>10200</v>
       </c>
       <c r="Q297" t="n">
-        <v>2600000</v>
+        <v>3539400</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>C7132</t>
-        </is>
+          <t>C7222</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>7453100037453</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>SET PULSERAS Y CAUCHOS C7132</t>
+          <t>RELOJ DIDACTICO CARACOL C7222</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -13773,7 +13785,7 @@
         </is>
       </c>
       <c r="J298" t="n">
-        <v>144</v>
+        <v>230</v>
       </c>
       <c r="K298" t="n">
         <v>0</v>
@@ -13782,38 +13794,38 @@
         <v>0</v>
       </c>
       <c r="M298" t="n">
-        <v>144</v>
+        <v>230</v>
       </c>
       <c r="N298" t="n">
-        <v>3100.87</v>
+        <v>4795.69</v>
       </c>
       <c r="O298" t="n">
-        <v>446525.28</v>
+        <v>1103008.7</v>
       </c>
       <c r="P298" t="n">
-        <v>9900</v>
+        <v>10200</v>
       </c>
       <c r="Q298" t="n">
-        <v>1425600</v>
+        <v>2346000</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>C7147-A</t>
+          <t>C7294</t>
         </is>
       </c>
       <c r="B299" t="n">
-        <v>6912209205022</v>
+        <v>6895675680022</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>ANIMAL DINOSAURIO TRICERATOPS CONLUZ C7147-A</t>
+          <t>JUEGO DEPORTIVO HOCHEY C7294</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -13822,7 +13834,7 @@
         </is>
       </c>
       <c r="J299" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="K299" t="n">
         <v>0</v>
@@ -13831,38 +13843,38 @@
         <v>0</v>
       </c>
       <c r="M299" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="N299" t="n">
-        <v>10348.08</v>
+        <v>4337.31</v>
       </c>
       <c r="O299" t="n">
-        <v>413923.2</v>
+        <v>260238.6</v>
       </c>
       <c r="P299" t="n">
-        <v>16900</v>
+        <v>12900</v>
       </c>
       <c r="Q299" t="n">
-        <v>676000</v>
+        <v>774000</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>C7213</t>
+          <t>C7325</t>
         </is>
       </c>
       <c r="B300" t="n">
-        <v>6987540143012</v>
+        <v>6974555555022</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>PESCADO CON LUZ Y SONIDO C7213</t>
+          <t>PISTA EN BLISTER C7325</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -13871,7 +13883,7 @@
         </is>
       </c>
       <c r="J300" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="K300" t="n">
         <v>0</v>
@@ -13880,38 +13892,35 @@
         <v>0</v>
       </c>
       <c r="M300" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="N300" t="n">
-        <v>9746.8802061856</v>
+        <v>3067.0906164384</v>
       </c>
       <c r="O300" t="n">
-        <v>467850.2498969088</v>
+        <v>138019.077739728</v>
       </c>
       <c r="P300" t="n">
-        <v>18500</v>
+        <v>7200</v>
       </c>
       <c r="Q300" t="n">
-        <v>888000</v>
+        <v>324000</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>C7221</t>
-        </is>
-      </c>
-      <c r="B301" t="n">
-        <v>7453100037446</v>
+          <t>C736</t>
+        </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>RELOJ CON FICHAS ARMABLES  C7221</t>
+          <t>GLOBO CORAZON GDE MENSAJE</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -13920,7 +13929,7 @@
         </is>
       </c>
       <c r="J301" t="n">
-        <v>347</v>
+        <v>2700</v>
       </c>
       <c r="K301" t="n">
         <v>0</v>
@@ -13929,38 +13938,38 @@
         <v>0</v>
       </c>
       <c r="M301" t="n">
-        <v>347</v>
+        <v>2700</v>
       </c>
       <c r="N301" t="n">
-        <v>2672.89</v>
+        <v>640</v>
       </c>
       <c r="O301" t="n">
-        <v>927492.83</v>
+        <v>1728000</v>
       </c>
       <c r="P301" t="n">
-        <v>10200</v>
+        <v>800</v>
       </c>
       <c r="Q301" t="n">
-        <v>3539400</v>
+        <v>2160000</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>C7222</t>
+          <t>C7365</t>
         </is>
       </c>
       <c r="B302" t="n">
-        <v>7453100037453</v>
+        <v>6920240750050</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>RELOJ DIDACTICO CARACOL C7222</t>
+          <t>DIDACTICO JIRAFA EN BOLSA C7365</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -13969,7 +13978,7 @@
         </is>
       </c>
       <c r="J302" t="n">
-        <v>230</v>
+        <v>19</v>
       </c>
       <c r="K302" t="n">
         <v>0</v>
@@ -13978,38 +13987,38 @@
         <v>0</v>
       </c>
       <c r="M302" t="n">
-        <v>230</v>
+        <v>19</v>
       </c>
       <c r="N302" t="n">
-        <v>4795.69</v>
+        <v>4190.77</v>
       </c>
       <c r="O302" t="n">
-        <v>1103008.7</v>
+        <v>79624.63</v>
       </c>
       <c r="P302" t="n">
-        <v>10200</v>
+        <v>5900</v>
       </c>
       <c r="Q302" t="n">
-        <v>2346000</v>
+        <v>112100</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>C7294</t>
+          <t>C7366</t>
         </is>
       </c>
       <c r="B303" t="n">
-        <v>6895675680022</v>
+        <v>6920240750098</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>JUEGO DEPORTIVO HOCHEY C7294</t>
+          <t>TREN DIDACTICO EN BOLSA C7366</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -14018,7 +14027,7 @@
         </is>
       </c>
       <c r="J303" t="n">
-        <v>60</v>
+        <v>104</v>
       </c>
       <c r="K303" t="n">
         <v>0</v>
@@ -14027,38 +14036,38 @@
         <v>0</v>
       </c>
       <c r="M303" t="n">
-        <v>60</v>
+        <v>104</v>
       </c>
       <c r="N303" t="n">
-        <v>4337.31</v>
+        <v>3499.72</v>
       </c>
       <c r="O303" t="n">
-        <v>260238.6</v>
+        <v>363970.88</v>
       </c>
       <c r="P303" t="n">
-        <v>12900</v>
+        <v>6900</v>
       </c>
       <c r="Q303" t="n">
-        <v>774000</v>
+        <v>717600</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>C7325</t>
+          <t>C7368</t>
         </is>
       </c>
       <c r="B304" t="n">
-        <v>6974555555022</v>
+        <v>6920240750159</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>PISTA EN BLISTER C7325</t>
+          <t>MOTO DIDACTICA EN BOLSA C736</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -14067,7 +14076,7 @@
         </is>
       </c>
       <c r="J304" t="n">
-        <v>45</v>
+        <v>158</v>
       </c>
       <c r="K304" t="n">
         <v>0</v>
@@ -14076,30 +14085,30 @@
         <v>0</v>
       </c>
       <c r="M304" t="n">
-        <v>45</v>
+        <v>158</v>
       </c>
       <c r="N304" t="n">
-        <v>3067.0906143345</v>
+        <v>4578.04</v>
       </c>
       <c r="O304" t="n">
-        <v>138019.0776450525</v>
+        <v>723330.3199999999</v>
       </c>
       <c r="P304" t="n">
-        <v>7200</v>
+        <v>7500</v>
       </c>
       <c r="Q304" t="n">
-        <v>324000</v>
+        <v>1185000</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>C736</t>
+          <t>C740-IO</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>GLOBO CORAZON GDE MENSAJE</t>
+          <t>GLOBO UNICORNIO MED</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -14113,7 +14122,7 @@
         </is>
       </c>
       <c r="J305" t="n">
-        <v>2700</v>
+        <v>1876</v>
       </c>
       <c r="K305" t="n">
         <v>0</v>
@@ -14122,33 +14131,33 @@
         <v>0</v>
       </c>
       <c r="M305" t="n">
-        <v>2700</v>
+        <v>1876</v>
       </c>
       <c r="N305" t="n">
-        <v>640</v>
+        <v>480</v>
       </c>
       <c r="O305" t="n">
-        <v>1728000</v>
+        <v>900480</v>
       </c>
       <c r="P305" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="Q305" t="n">
-        <v>2160000</v>
+        <v>1125600</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>C7365</t>
+          <t>C7413</t>
         </is>
       </c>
       <c r="B306" t="n">
-        <v>6920240750050</v>
+        <v>6921202412870</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>DIDACTICO JIRAFA EN BOLSA C7365</t>
+          <t>DIDACTICO TORRE DE AROS C7413</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -14162,7 +14171,7 @@
         </is>
       </c>
       <c r="J306" t="n">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="K306" t="n">
         <v>0</v>
@@ -14171,38 +14180,35 @@
         <v>0</v>
       </c>
       <c r="M306" t="n">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="N306" t="n">
-        <v>4190.77</v>
+        <v>4159.0003007519</v>
       </c>
       <c r="O306" t="n">
-        <v>79624.63</v>
+        <v>499080.036090228</v>
       </c>
       <c r="P306" t="n">
-        <v>5900</v>
+        <v>8900</v>
       </c>
       <c r="Q306" t="n">
-        <v>112100</v>
+        <v>1068000</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>C7366</t>
-        </is>
-      </c>
-      <c r="B307" t="n">
-        <v>6920240750098</v>
+          <t>C744-IO</t>
+        </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>TREN DIDACTICO EN BOLSA C7366</t>
+          <t>GLOBO FELIZ CUMPLEAÑOS COLORES Y PUNTOS</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>GLOBOS</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -14211,7 +14217,7 @@
         </is>
       </c>
       <c r="J307" t="n">
-        <v>104</v>
+        <v>478</v>
       </c>
       <c r="K307" t="n">
         <v>0</v>
@@ -14220,38 +14226,35 @@
         <v>0</v>
       </c>
       <c r="M307" t="n">
-        <v>104</v>
+        <v>478</v>
       </c>
       <c r="N307" t="n">
-        <v>3499.72</v>
+        <v>1554.12</v>
       </c>
       <c r="O307" t="n">
-        <v>363970.88</v>
+        <v>742869.36</v>
       </c>
       <c r="P307" t="n">
-        <v>6900</v>
+        <v>1900</v>
       </c>
       <c r="Q307" t="n">
-        <v>717600</v>
+        <v>908200</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>C7368</t>
-        </is>
-      </c>
-      <c r="B308" t="n">
-        <v>6920240750159</v>
+          <t>C7462</t>
+        </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>MOTO DIDACTICA EN BOLSA C736</t>
+          <t>SET DE BELLEZA ACCESORIOS PARA EL CABELLO C7462</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -14260,7 +14263,7 @@
         </is>
       </c>
       <c r="J308" t="n">
-        <v>158</v>
+        <v>11</v>
       </c>
       <c r="K308" t="n">
         <v>0</v>
@@ -14269,35 +14272,38 @@
         <v>0</v>
       </c>
       <c r="M308" t="n">
-        <v>158</v>
+        <v>11</v>
       </c>
       <c r="N308" t="n">
-        <v>4578.04</v>
+        <v>14751.820338983</v>
       </c>
       <c r="O308" t="n">
-        <v>723330.3199999999</v>
+        <v>162270.023728813</v>
       </c>
       <c r="P308" t="n">
-        <v>7500</v>
+        <v>37100</v>
       </c>
       <c r="Q308" t="n">
-        <v>1185000</v>
+        <v>408100</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>C740-IO</t>
-        </is>
+          <t>C7467</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>6920241023009</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>GLOBO UNICORNIO MED</t>
+          <t>ARCO Y FLECHA PARA NIÑAS C7467</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -14306,7 +14312,7 @@
         </is>
       </c>
       <c r="J309" t="n">
-        <v>1876</v>
+        <v>15</v>
       </c>
       <c r="K309" t="n">
         <v>0</v>
@@ -14315,38 +14321,38 @@
         <v>0</v>
       </c>
       <c r="M309" t="n">
-        <v>1876</v>
+        <v>15</v>
       </c>
       <c r="N309" t="n">
-        <v>480</v>
+        <v>15347.45</v>
       </c>
       <c r="O309" t="n">
-        <v>900480</v>
+        <v>230211.75</v>
       </c>
       <c r="P309" t="n">
-        <v>600</v>
+        <v>23900</v>
       </c>
       <c r="Q309" t="n">
-        <v>1125600</v>
+        <v>358500</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>C7413</t>
+          <t>C7488</t>
         </is>
       </c>
       <c r="B310" t="n">
-        <v>6921202412870</v>
+        <v>6945158254520</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>DIDACTICO TORRE DE AROS C7413</t>
+          <t>SOPORTE CELULAR CON LUZ C7488</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -14355,7 +14361,7 @@
         </is>
       </c>
       <c r="J310" t="n">
-        <v>120</v>
+        <v>29</v>
       </c>
       <c r="K310" t="n">
         <v>0</v>
@@ -14364,35 +14370,38 @@
         <v>0</v>
       </c>
       <c r="M310" t="n">
-        <v>120</v>
+        <v>29</v>
       </c>
       <c r="N310" t="n">
-        <v>4159.0003007519</v>
+        <v>8919.16</v>
       </c>
       <c r="O310" t="n">
-        <v>499080.036090228</v>
+        <v>258655.64</v>
       </c>
       <c r="P310" t="n">
-        <v>8900</v>
+        <v>10000</v>
       </c>
       <c r="Q310" t="n">
-        <v>1068000</v>
+        <v>290000</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>C744-IO</t>
-        </is>
+          <t>C7513</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>6905698382824</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>GLOBO FELIZ CUMPLEAÑOS COLORES Y PUNTOS</t>
+          <t>SONAJERO BOLA LUZ GDE C7513</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>GLOBOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -14401,7 +14410,7 @@
         </is>
       </c>
       <c r="J311" t="n">
-        <v>478</v>
+        <v>1</v>
       </c>
       <c r="K311" t="n">
         <v>0</v>
@@ -14410,44 +14419,42 @@
         <v>0</v>
       </c>
       <c r="M311" t="n">
-        <v>478</v>
+        <v>1</v>
       </c>
       <c r="N311" t="n">
-        <v>1554.12</v>
+        <v>1024.29</v>
       </c>
       <c r="O311" t="n">
-        <v>742869.36</v>
+        <v>1024.29</v>
       </c>
       <c r="P311" t="n">
-        <v>1900</v>
+        <v>2900</v>
       </c>
       <c r="Q311" t="n">
-        <v>908200</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>C7462</t>
-        </is>
+          <t>C752</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>8596162180497</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>SET DE BELLEZA ACCESORIOS PARA EL CABELLO C7462</t>
-        </is>
-      </c>
-      <c r="E312" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
+          <t>GLOBO UNICORNIO MED 4 PATAS</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J312" t="n">
-        <v>11</v>
+        <v>1398</v>
       </c>
       <c r="K312" t="n">
         <v>0</v>
@@ -14456,47 +14463,42 @@
         <v>0</v>
       </c>
       <c r="M312" t="n">
-        <v>11</v>
+        <v>1398</v>
       </c>
       <c r="N312" t="n">
-        <v>14751.820338983</v>
+        <v>1163.7447787403</v>
       </c>
       <c r="O312" t="n">
-        <v>162270.023728813</v>
+        <v>1626915.200678939</v>
       </c>
       <c r="P312" t="n">
-        <v>37100</v>
+        <v>1500</v>
       </c>
       <c r="Q312" t="n">
-        <v>408100</v>
+        <v>2097000</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>C7467</t>
+          <t>C753</t>
         </is>
       </c>
       <c r="B313" t="n">
-        <v>6920241023009</v>
+        <v>8596162180503</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>ARCO Y FLECHA PARA NIÑAS C7467</t>
-        </is>
-      </c>
-      <c r="E313" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
+          <t>GLOBO UNICORNIO GDE 4 PATAS</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J313" t="n">
-        <v>15</v>
+        <v>277</v>
       </c>
       <c r="K313" t="n">
         <v>0</v>
@@ -14505,38 +14507,38 @@
         <v>0</v>
       </c>
       <c r="M313" t="n">
-        <v>15</v>
+        <v>277</v>
       </c>
       <c r="N313" t="n">
-        <v>15347.45</v>
+        <v>5113.4625508318</v>
       </c>
       <c r="O313" t="n">
-        <v>230211.75</v>
+        <v>1416429.126580409</v>
       </c>
       <c r="P313" t="n">
-        <v>23900</v>
+        <v>7000</v>
       </c>
       <c r="Q313" t="n">
-        <v>358500</v>
+        <v>1939000</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>C7488</t>
+          <t>C7533</t>
         </is>
       </c>
       <c r="B314" t="n">
-        <v>6945158254520</v>
+        <v>6923669699979</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>SOPORTE CELULAR CON LUZ C7488</t>
+          <t>REPUESTO BIOGEL NEON C7533</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -14545,7 +14547,7 @@
         </is>
       </c>
       <c r="J314" t="n">
-        <v>29</v>
+        <v>12023</v>
       </c>
       <c r="K314" t="n">
         <v>0</v>
@@ -14554,33 +14556,33 @@
         <v>0</v>
       </c>
       <c r="M314" t="n">
-        <v>29</v>
+        <v>12023</v>
       </c>
       <c r="N314" t="n">
-        <v>8919.16</v>
+        <v>509.69</v>
       </c>
       <c r="O314" t="n">
-        <v>258655.64</v>
+        <v>6128002.87</v>
       </c>
       <c r="P314" t="n">
-        <v>10000</v>
+        <v>750</v>
       </c>
       <c r="Q314" t="n">
-        <v>290000</v>
+        <v>9017250</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>C7513</t>
+          <t>C7534</t>
         </is>
       </c>
       <c r="B315" t="n">
-        <v>6905698382824</v>
+        <v>6951241752002</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>SONAJERO BOLA LUZ GDE C7513</t>
+          <t>GORRO PELUCHE LUZ C7534-A-B-C-D-E-F</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -14594,7 +14596,7 @@
         </is>
       </c>
       <c r="J315" t="n">
-        <v>1</v>
+        <v>499</v>
       </c>
       <c r="K315" t="n">
         <v>0</v>
@@ -14603,42 +14605,44 @@
         <v>0</v>
       </c>
       <c r="M315" t="n">
-        <v>1</v>
+        <v>499</v>
       </c>
       <c r="N315" t="n">
-        <v>1024.29</v>
+        <v>7046.9398265771</v>
       </c>
       <c r="O315" t="n">
-        <v>1024.29</v>
+        <v>3516422.973461973</v>
       </c>
       <c r="P315" t="n">
-        <v>2900</v>
+        <v>9900</v>
       </c>
       <c r="Q315" t="n">
-        <v>2900</v>
+        <v>4940100</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>C752</t>
-        </is>
-      </c>
-      <c r="B316" t="n">
-        <v>8596162180497</v>
+          <t>C7535</t>
+        </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>GLOBO UNICORNIO MED 4 PATAS</t>
+          <t>CARRO METALICO X13 CON CAMION C7535</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J316" t="n">
-        <v>1398</v>
+        <v>30</v>
       </c>
       <c r="K316" t="n">
         <v>0</v>
@@ -14647,42 +14651,44 @@
         <v>0</v>
       </c>
       <c r="M316" t="n">
-        <v>1398</v>
+        <v>30</v>
       </c>
       <c r="N316" t="n">
-        <v>1163.7447787403</v>
+        <v>24338.47</v>
       </c>
       <c r="O316" t="n">
-        <v>1626915.200678939</v>
+        <v>730154.1000000001</v>
       </c>
       <c r="P316" t="n">
-        <v>1500</v>
+        <v>27900</v>
       </c>
       <c r="Q316" t="n">
-        <v>2097000</v>
+        <v>837000</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>C753</t>
-        </is>
-      </c>
-      <c r="B317" t="n">
-        <v>8596162180503</v>
+          <t>C7560</t>
+        </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>GLOBO UNICORNIO GDE 4 PATAS</t>
+          <t>BARRA LUMINOSA 48CM C7560/211</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J317" t="n">
-        <v>277</v>
+        <v>188</v>
       </c>
       <c r="K317" t="n">
         <v>0</v>
@@ -14691,33 +14697,33 @@
         <v>0</v>
       </c>
       <c r="M317" t="n">
-        <v>277</v>
+        <v>188</v>
       </c>
       <c r="N317" t="n">
-        <v>5113.4625508318</v>
+        <v>796.3099999999999</v>
       </c>
       <c r="O317" t="n">
-        <v>1416429.126580409</v>
+        <v>149706.28</v>
       </c>
       <c r="P317" t="n">
-        <v>7000</v>
+        <v>2500</v>
       </c>
       <c r="Q317" t="n">
-        <v>1939000</v>
+        <v>470000</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>C7533</t>
+          <t>C7588</t>
         </is>
       </c>
       <c r="B318" t="n">
-        <v>6923669699979</v>
+        <v>7588228020244</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>REPUESTO BIOGEL NEON C7533</t>
+          <t>SONAJERO LUZ PANDITA C7588</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -14731,7 +14737,7 @@
         </is>
       </c>
       <c r="J318" t="n">
-        <v>12023</v>
+        <v>1429</v>
       </c>
       <c r="K318" t="n">
         <v>0</v>
@@ -14740,38 +14746,38 @@
         <v>0</v>
       </c>
       <c r="M318" t="n">
-        <v>12023</v>
+        <v>1429</v>
       </c>
       <c r="N318" t="n">
-        <v>509.69</v>
+        <v>641.78</v>
       </c>
       <c r="O318" t="n">
-        <v>6128002.87</v>
+        <v>917103.62</v>
       </c>
       <c r="P318" t="n">
-        <v>750</v>
+        <v>2500</v>
       </c>
       <c r="Q318" t="n">
-        <v>9017250</v>
+        <v>3572500</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>C7534</t>
+          <t>C7610</t>
         </is>
       </c>
       <c r="B319" t="n">
-        <v>6951241752002</v>
+        <v>6999899236093</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>GORRO PELUCHE LUZ C7534-A-B-C-D-E-F</t>
+          <t>BOTE TIMON PISCINA 80X60 C7610</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>INFLABLES</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -14780,7 +14786,7 @@
         </is>
       </c>
       <c r="J319" t="n">
-        <v>499</v>
+        <v>276</v>
       </c>
       <c r="K319" t="n">
         <v>0</v>
@@ -14789,35 +14795,38 @@
         <v>0</v>
       </c>
       <c r="M319" t="n">
-        <v>499</v>
+        <v>276</v>
       </c>
       <c r="N319" t="n">
-        <v>7046.9398267273</v>
+        <v>7811.9</v>
       </c>
       <c r="O319" t="n">
-        <v>3516422.973536923</v>
+        <v>2156084.4</v>
       </c>
       <c r="P319" t="n">
-        <v>9900</v>
+        <v>13900</v>
       </c>
       <c r="Q319" t="n">
-        <v>4940100</v>
+        <v>3836400</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>C7535</t>
-        </is>
+          <t>C7614-F</t>
+        </is>
+      </c>
+      <c r="B320" t="n">
+        <v>6999899236130</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>CARRO METALICO X13 CON CAMION C7535</t>
+          <t>FLOTADOR DONA FLAMINGO C7614-F</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -14826,7 +14835,7 @@
         </is>
       </c>
       <c r="J320" t="n">
-        <v>30</v>
+        <v>382</v>
       </c>
       <c r="K320" t="n">
         <v>0</v>
@@ -14835,44 +14844,42 @@
         <v>0</v>
       </c>
       <c r="M320" t="n">
-        <v>30</v>
+        <v>382</v>
       </c>
       <c r="N320" t="n">
-        <v>24338.47</v>
+        <v>3155</v>
       </c>
       <c r="O320" t="n">
-        <v>730154.1000000001</v>
+        <v>1205210</v>
       </c>
       <c r="P320" t="n">
-        <v>27900</v>
+        <v>5900</v>
       </c>
       <c r="Q320" t="n">
-        <v>837000</v>
+        <v>2253800</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>C7560</t>
-        </is>
+          <t>C784</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>8913992935507</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>BARRA LUMINOSA 48CM C7560/211</t>
-        </is>
-      </c>
-      <c r="E321" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
+          <t>GLOBO MENSAJE CUADRADO</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J321" t="n">
-        <v>188</v>
+        <v>1450</v>
       </c>
       <c r="K321" t="n">
         <v>0</v>
@@ -14881,47 +14888,42 @@
         <v>0</v>
       </c>
       <c r="M321" t="n">
-        <v>188</v>
+        <v>1450</v>
       </c>
       <c r="N321" t="n">
-        <v>796.3099999999999</v>
+        <v>704.89696969697</v>
       </c>
       <c r="O321" t="n">
-        <v>149706.28</v>
+        <v>1022100.606060607</v>
       </c>
       <c r="P321" t="n">
-        <v>2500</v>
+        <v>900</v>
       </c>
       <c r="Q321" t="n">
-        <v>470000</v>
+        <v>1305000</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>C7588</t>
+          <t>C819</t>
         </is>
       </c>
       <c r="B322" t="n">
-        <v>7588228020244</v>
+        <v>2087202108190</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>SONAJERO LUZ PANDITA C7588</t>
-        </is>
-      </c>
-      <c r="E322" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
+          <t>TROMPO EMOJI</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J322" t="n">
-        <v>1429</v>
+        <v>468</v>
       </c>
       <c r="K322" t="n">
         <v>0</v>
@@ -14930,47 +14932,42 @@
         <v>0</v>
       </c>
       <c r="M322" t="n">
-        <v>1429</v>
+        <v>468</v>
       </c>
       <c r="N322" t="n">
-        <v>641.78</v>
+        <v>6761.25</v>
       </c>
       <c r="O322" t="n">
-        <v>917103.62</v>
+        <v>3164265</v>
       </c>
       <c r="P322" t="n">
-        <v>2500</v>
+        <v>5200</v>
       </c>
       <c r="Q322" t="n">
-        <v>3572500</v>
+        <v>2433600</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>C7610</t>
+          <t>C84</t>
         </is>
       </c>
       <c r="B323" t="n">
-        <v>6999899236093</v>
+        <v>2021010563031</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>BOTE TIMON PISCINA 80X60 C7610</t>
-        </is>
-      </c>
-      <c r="E323" t="inlineStr">
-        <is>
-          <t>INFLABLES</t>
+          <t>LANZADOR DE AGUA</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J323" t="n">
-        <v>276</v>
+        <v>212</v>
       </c>
       <c r="K323" t="n">
         <v>0</v>
@@ -14979,47 +14976,44 @@
         <v>0</v>
       </c>
       <c r="M323" t="n">
-        <v>276</v>
+        <v>212</v>
       </c>
       <c r="N323" t="n">
-        <v>7811.9</v>
+        <v>1008.8125188917</v>
       </c>
       <c r="O323" t="n">
-        <v>2156084.4</v>
+        <v>213868.2540050404</v>
       </c>
       <c r="P323" t="n">
-        <v>13900</v>
+        <v>1500</v>
       </c>
       <c r="Q323" t="n">
-        <v>3836400</v>
+        <v>318000</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>C7614-F</t>
-        </is>
-      </c>
-      <c r="B324" t="n">
-        <v>6999899236130</v>
+          <t>C879</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>CG-2016-212</t>
+        </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>FLOTADOR DONA FLAMINGO C7614-F</t>
-        </is>
-      </c>
-      <c r="E324" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>VELA MARIPOSA</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J324" t="n">
-        <v>382</v>
+        <v>121</v>
       </c>
       <c r="K324" t="n">
         <v>0</v>
@@ -15028,42 +15022,49 @@
         <v>0</v>
       </c>
       <c r="M324" t="n">
-        <v>382</v>
+        <v>121</v>
       </c>
       <c r="N324" t="n">
-        <v>3155</v>
+        <v>1520</v>
       </c>
       <c r="O324" t="n">
-        <v>1205210</v>
+        <v>183920</v>
       </c>
       <c r="P324" t="n">
-        <v>5900</v>
+        <v>1900</v>
       </c>
       <c r="Q324" t="n">
-        <v>2253800</v>
+        <v>229900</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>C784</t>
-        </is>
-      </c>
-      <c r="B325" t="n">
-        <v>8913992935507</v>
+          <t>C880</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>cg2016213</t>
+        </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>GLOBO MENSAJE CUADRADO</t>
+          <t>VELA FLOR</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>VELA</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J325" t="n">
-        <v>1450</v>
+        <v>200</v>
       </c>
       <c r="K325" t="n">
         <v>0</v>
@@ -15072,33 +15073,30 @@
         <v>0</v>
       </c>
       <c r="M325" t="n">
-        <v>1450</v>
+        <v>200</v>
       </c>
       <c r="N325" t="n">
-        <v>704.89696969697</v>
+        <v>1520</v>
       </c>
       <c r="O325" t="n">
-        <v>1022100.606060607</v>
+        <v>304000</v>
       </c>
       <c r="P325" t="n">
-        <v>900</v>
+        <v>1900</v>
       </c>
       <c r="Q325" t="n">
-        <v>1305000</v>
+        <v>380000</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>C819</t>
-        </is>
-      </c>
-      <c r="B326" t="n">
-        <v>2087202108190</v>
+          <t>C888</t>
+        </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>TROMPO EMOJI</t>
+          <t>PELOTA CHILLON PUYAS SIN LUZ</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -15107,7 +15105,7 @@
         </is>
       </c>
       <c r="J326" t="n">
-        <v>468</v>
+        <v>169</v>
       </c>
       <c r="K326" t="n">
         <v>0</v>
@@ -15116,42 +15114,44 @@
         <v>0</v>
       </c>
       <c r="M326" t="n">
-        <v>468</v>
+        <v>169</v>
       </c>
       <c r="N326" t="n">
-        <v>6761.25</v>
+        <v>1213.6821400778</v>
       </c>
       <c r="O326" t="n">
-        <v>3164265</v>
+        <v>205112.2816731482</v>
       </c>
       <c r="P326" t="n">
-        <v>5200</v>
+        <v>1500</v>
       </c>
       <c r="Q326" t="n">
-        <v>2433600</v>
+        <v>253500</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>C84</t>
-        </is>
-      </c>
-      <c r="B327" t="n">
-        <v>2021010563031</v>
+          <t>FG037</t>
+        </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>LANZADOR DE AGUA</t>
+          <t>SNORKEL 66046A</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J327" t="n">
-        <v>212</v>
+        <v>179</v>
       </c>
       <c r="K327" t="n">
         <v>0</v>
@@ -15160,44 +15160,44 @@
         <v>0</v>
       </c>
       <c r="M327" t="n">
-        <v>212</v>
+        <v>179</v>
       </c>
       <c r="N327" t="n">
-        <v>1008.8125188917</v>
+        <v>13493.858292683</v>
       </c>
       <c r="O327" t="n">
-        <v>213868.2540050404</v>
+        <v>2415400.634390257</v>
       </c>
       <c r="P327" t="n">
-        <v>1500</v>
+        <v>16900</v>
       </c>
       <c r="Q327" t="n">
-        <v>318000</v>
+        <v>3025100</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>C879</t>
-        </is>
-      </c>
-      <c r="B328" t="inlineStr">
-        <is>
-          <t>CG-2016-212</t>
+          <t>FG039</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>VELA MARIPOSA</t>
+          <t>GAFA DE NATACION BLISTER 2404-2</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J328" t="n">
-        <v>121</v>
+        <v>347</v>
       </c>
       <c r="K328" t="n">
         <v>0</v>
@@ -15206,40 +15206,40 @@
         <v>0</v>
       </c>
       <c r="M328" t="n">
-        <v>121</v>
+        <v>347</v>
       </c>
       <c r="N328" t="n">
-        <v>1520</v>
+        <v>2644.9</v>
       </c>
       <c r="O328" t="n">
-        <v>183920</v>
+        <v>917780.3</v>
       </c>
       <c r="P328" t="n">
-        <v>1900</v>
+        <v>3900</v>
       </c>
       <c r="Q328" t="n">
-        <v>229900</v>
+        <v>1353300</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>C880</t>
+          <t>MG16332</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>cg2016213</t>
+          <t>MG16332</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>VELA FLOR</t>
+          <t>LANZADOR  ARCO Y FLECA CON LASER MG16332</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>VELA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -15248,7 +15248,7 @@
         </is>
       </c>
       <c r="J329" t="n">
-        <v>200</v>
+        <v>4</v>
       </c>
       <c r="K329" t="n">
         <v>0</v>
@@ -15257,39 +15257,44 @@
         <v>0</v>
       </c>
       <c r="M329" t="n">
-        <v>200</v>
+        <v>4</v>
       </c>
       <c r="N329" t="n">
-        <v>1520</v>
+        <v>8439.969999999999</v>
       </c>
       <c r="O329" t="n">
-        <v>304000</v>
+        <v>33759.88</v>
       </c>
       <c r="P329" t="n">
-        <v>1900</v>
+        <v>29500</v>
       </c>
       <c r="Q329" t="n">
-        <v>380000</v>
+        <v>118000</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>C888</t>
+          <t>MG20430</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>PELOTA CHILLON PUYAS SIN LUZ</t>
+          <t>SET PLASTILINA CON MOLDES BARBERIA MALETA MG20430</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J330" t="n">
-        <v>169</v>
+        <v>18</v>
       </c>
       <c r="K330" t="n">
         <v>0</v>
@@ -15298,35 +15303,35 @@
         <v>0</v>
       </c>
       <c r="M330" t="n">
-        <v>169</v>
+        <v>18</v>
       </c>
       <c r="N330" t="n">
-        <v>1213.6821400778</v>
+        <v>12189.831111111</v>
       </c>
       <c r="O330" t="n">
-        <v>205112.2816731482</v>
+        <v>219416.959999998</v>
       </c>
       <c r="P330" t="n">
-        <v>1500</v>
+        <v>30900</v>
       </c>
       <c r="Q330" t="n">
-        <v>253500</v>
+        <v>556200</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>FG037</t>
+          <t>MG40210</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>SNORKEL 66046A</t>
+          <t>SONAJERO OSO MG40210</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
@@ -15335,7 +15340,7 @@
         </is>
       </c>
       <c r="J331" t="n">
-        <v>179</v>
+        <v>363</v>
       </c>
       <c r="K331" t="n">
         <v>0</v>
@@ -15344,35 +15349,40 @@
         <v>0</v>
       </c>
       <c r="M331" t="n">
-        <v>179</v>
+        <v>363</v>
       </c>
       <c r="N331" t="n">
-        <v>13493.858292683</v>
+        <v>571.87</v>
       </c>
       <c r="O331" t="n">
-        <v>2415400.634390257</v>
+        <v>207588.81</v>
       </c>
       <c r="P331" t="n">
-        <v>16900</v>
+        <v>2500</v>
       </c>
       <c r="Q331" t="n">
-        <v>3025100</v>
+        <v>907500</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>FG039</t>
+          <t>MG40720</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>MG40720</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>GAFA DE NATACION BLISTER 2404-2</t>
+          <t>MAQUINA DE COSER MINI MG40720</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -15381,7 +15391,7 @@
         </is>
       </c>
       <c r="J332" t="n">
-        <v>347</v>
+        <v>64</v>
       </c>
       <c r="K332" t="n">
         <v>0</v>
@@ -15390,212 +15400,18 @@
         <v>0</v>
       </c>
       <c r="M332" t="n">
-        <v>347</v>
+        <v>64</v>
       </c>
       <c r="N332" t="n">
-        <v>2644.9</v>
+        <v>9917.040000000001</v>
       </c>
       <c r="O332" t="n">
-        <v>917780.3</v>
+        <v>634690.5600000001</v>
       </c>
       <c r="P332" t="n">
-        <v>3900</v>
+        <v>15900</v>
       </c>
       <c r="Q332" t="n">
-        <v>1353300</v>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" t="inlineStr">
-        <is>
-          <t>MG16332</t>
-        </is>
-      </c>
-      <c r="B333" t="inlineStr">
-        <is>
-          <t>MG16332</t>
-        </is>
-      </c>
-      <c r="C333" t="inlineStr">
-        <is>
-          <t>LANZADOR  ARCO Y FLECA CON LASER MG16332</t>
-        </is>
-      </c>
-      <c r="E333" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
-        </is>
-      </c>
-      <c r="I333" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J333" t="n">
-        <v>4</v>
-      </c>
-      <c r="K333" t="n">
-        <v>0</v>
-      </c>
-      <c r="L333" t="n">
-        <v>0</v>
-      </c>
-      <c r="M333" t="n">
-        <v>4</v>
-      </c>
-      <c r="N333" t="n">
-        <v>8439.969999999999</v>
-      </c>
-      <c r="O333" t="n">
-        <v>33759.88</v>
-      </c>
-      <c r="P333" t="n">
-        <v>29500</v>
-      </c>
-      <c r="Q333" t="n">
-        <v>118000</v>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" t="inlineStr">
-        <is>
-          <t>MG20430</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>SET PLASTILINA CON MOLDES BARBERIA MALETA MG20430</t>
-        </is>
-      </c>
-      <c r="E334" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
-        </is>
-      </c>
-      <c r="I334" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J334" t="n">
-        <v>18</v>
-      </c>
-      <c r="K334" t="n">
-        <v>0</v>
-      </c>
-      <c r="L334" t="n">
-        <v>0</v>
-      </c>
-      <c r="M334" t="n">
-        <v>18</v>
-      </c>
-      <c r="N334" t="n">
-        <v>12189.831111111</v>
-      </c>
-      <c r="O334" t="n">
-        <v>219416.959999998</v>
-      </c>
-      <c r="P334" t="n">
-        <v>30900</v>
-      </c>
-      <c r="Q334" t="n">
-        <v>556200</v>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="inlineStr">
-        <is>
-          <t>MG40210</t>
-        </is>
-      </c>
-      <c r="C335" t="inlineStr">
-        <is>
-          <t>SONAJERO OSO MG40210</t>
-        </is>
-      </c>
-      <c r="E335" t="inlineStr">
-        <is>
-          <t>DIDACTICO</t>
-        </is>
-      </c>
-      <c r="I335" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J335" t="n">
-        <v>363</v>
-      </c>
-      <c r="K335" t="n">
-        <v>0</v>
-      </c>
-      <c r="L335" t="n">
-        <v>0</v>
-      </c>
-      <c r="M335" t="n">
-        <v>363</v>
-      </c>
-      <c r="N335" t="n">
-        <v>571.87</v>
-      </c>
-      <c r="O335" t="n">
-        <v>207588.81</v>
-      </c>
-      <c r="P335" t="n">
-        <v>2500</v>
-      </c>
-      <c r="Q335" t="n">
-        <v>907500</v>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" t="inlineStr">
-        <is>
-          <t>MG40720</t>
-        </is>
-      </c>
-      <c r="B336" t="inlineStr">
-        <is>
-          <t>MG40720</t>
-        </is>
-      </c>
-      <c r="C336" t="inlineStr">
-        <is>
-          <t>MAQUINA DE COSER MINI MG40720</t>
-        </is>
-      </c>
-      <c r="E336" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
-        </is>
-      </c>
-      <c r="I336" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J336" t="n">
-        <v>64</v>
-      </c>
-      <c r="K336" t="n">
-        <v>0</v>
-      </c>
-      <c r="L336" t="n">
-        <v>0</v>
-      </c>
-      <c r="M336" t="n">
-        <v>64</v>
-      </c>
-      <c r="N336" t="n">
-        <v>9917.040000000001</v>
-      </c>
-      <c r="O336" t="n">
-        <v>634690.5600000001</v>
-      </c>
-      <c r="P336" t="n">
-        <v>15900</v>
-      </c>
-      <c r="Q336" t="n">
         <v>1017600</v>
       </c>
     </row>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -4207,10 +4207,10 @@
         <v>336</v>
       </c>
       <c r="N89" t="n">
-        <v>12422.462959583</v>
+        <v>12422.46296087</v>
       </c>
       <c r="O89" t="n">
-        <v>4173947.554419888</v>
+        <v>4173947.55485232</v>
       </c>
       <c r="P89" t="n">
         <v>19900</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-22</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-23</t>
         </is>
       </c>
     </row>
@@ -720,10 +720,10 @@
         <v>376</v>
       </c>
       <c r="N8" t="n">
-        <v>3376.7464051196</v>
+        <v>3376.7464001115</v>
       </c>
       <c r="O8" t="n">
-        <v>1269656.648324969</v>
+        <v>1269656.646441924</v>
       </c>
       <c r="P8" t="n">
         <v>4500</v>
@@ -1480,10 +1480,10 @@
         <v>20</v>
       </c>
       <c r="N27" t="n">
-        <v>9392.075964912299</v>
+        <v>9392.0766666667</v>
       </c>
       <c r="O27" t="n">
-        <v>187841.519298246</v>
+        <v>187841.533333334</v>
       </c>
       <c r="P27" t="n">
         <v>18500</v>
@@ -1824,10 +1824,10 @@
         <v>4</v>
       </c>
       <c r="N35" t="n">
-        <v>344599.17815789</v>
+        <v>344599.17805556</v>
       </c>
       <c r="O35" t="n">
-        <v>1378396.71263156</v>
+        <v>1378396.71222224</v>
       </c>
       <c r="P35" t="n">
         <v>532900</v>
@@ -2027,10 +2027,10 @@
         <v>77</v>
       </c>
       <c r="N40" t="n">
-        <v>61666.874364162</v>
+        <v>61666.874376812</v>
       </c>
       <c r="O40" t="n">
-        <v>4748349.326040474</v>
+        <v>4748349.327014524</v>
       </c>
       <c r="P40" t="n">
         <v>98900</v>
@@ -3065,10 +3065,10 @@
         <v>350</v>
       </c>
       <c r="N64" t="n">
-        <v>2582.2549607893</v>
+        <v>2582.2549274255</v>
       </c>
       <c r="O64" t="n">
-        <v>903789.2362762551</v>
+        <v>903789.2245989249</v>
       </c>
       <c r="P64" t="n">
         <v>4500</v>
@@ -3111,10 +3111,10 @@
         <v>1232</v>
       </c>
       <c r="N65" t="n">
-        <v>5216.8958827104</v>
+        <v>5216.8958543674</v>
       </c>
       <c r="O65" t="n">
-        <v>6427215.727499212</v>
+        <v>6427215.692580637</v>
       </c>
       <c r="P65" t="n">
         <v>8500</v>
@@ -3157,10 +3157,10 @@
         <v>2592</v>
       </c>
       <c r="N66" t="n">
-        <v>3158.8608398885</v>
+        <v>3158.8608400976</v>
       </c>
       <c r="O66" t="n">
-        <v>8187767.296990992</v>
+        <v>8187767.297532979</v>
       </c>
       <c r="P66" t="n">
         <v>5600</v>
@@ -3520,10 +3520,10 @@
         <v>346</v>
       </c>
       <c r="N74" t="n">
-        <v>4890.9300534402</v>
+        <v>4890.9300535117</v>
       </c>
       <c r="O74" t="n">
-        <v>1692261.798490309</v>
+        <v>1692261.798515048</v>
       </c>
       <c r="P74" t="n">
         <v>8200</v>
@@ -3748,10 +3748,10 @@
         <v>216</v>
       </c>
       <c r="N79" t="n">
-        <v>3594.2529721816</v>
+        <v>3594.2529307806</v>
       </c>
       <c r="O79" t="n">
-        <v>776358.6419912255</v>
+        <v>776358.6330486096</v>
       </c>
       <c r="P79" t="n">
         <v>6500</v>
@@ -4207,10 +4207,10 @@
         <v>336</v>
       </c>
       <c r="N89" t="n">
-        <v>12422.46296087</v>
+        <v>12422.462986842</v>
       </c>
       <c r="O89" t="n">
-        <v>4173947.55485232</v>
+        <v>4173947.563578912</v>
       </c>
       <c r="P89" t="n">
         <v>19900</v>
@@ -4287,7 +4287,7 @@
         </is>
       </c>
       <c r="J91" t="n">
-        <v>1800</v>
+        <v>1728</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
@@ -4296,19 +4296,19 @@
         <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>1800</v>
+        <v>1728</v>
       </c>
       <c r="N91" t="n">
-        <v>3472.2762270961</v>
+        <v>3472.2762824732</v>
       </c>
       <c r="O91" t="n">
-        <v>6250097.20877298</v>
+        <v>6000093.41611369</v>
       </c>
       <c r="P91" t="n">
         <v>5900</v>
       </c>
       <c r="Q91" t="n">
-        <v>10620000</v>
+        <v>10195200</v>
       </c>
     </row>
     <row r="92">
@@ -5479,7 +5479,7 @@
         </is>
       </c>
       <c r="J117" t="n">
-        <v>193</v>
+        <v>163</v>
       </c>
       <c r="K117" t="n">
         <v>0</v>
@@ -5488,19 +5488,19 @@
         <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>193</v>
+        <v>163</v>
       </c>
       <c r="N117" t="n">
         <v>7028</v>
       </c>
       <c r="O117" t="n">
-        <v>1356404</v>
+        <v>1145564</v>
       </c>
       <c r="P117" t="n">
         <v>15900</v>
       </c>
       <c r="Q117" t="n">
-        <v>3068700</v>
+        <v>2591700</v>
       </c>
     </row>
     <row r="118">
@@ -5794,10 +5794,10 @@
         <v>432</v>
       </c>
       <c r="N124" t="n">
-        <v>2029.8741689828</v>
+        <v>2029.8741829336</v>
       </c>
       <c r="O124" t="n">
-        <v>876905.6410005696</v>
+        <v>876905.6470273152</v>
       </c>
       <c r="P124" t="n">
         <v>3600</v>
@@ -5835,10 +5835,10 @@
         <v>528</v>
       </c>
       <c r="N125" t="n">
-        <v>22485.695448799</v>
+        <v>22485.695419847</v>
       </c>
       <c r="O125" t="n">
-        <v>11872447.19696587</v>
+        <v>11872447.18167922</v>
       </c>
       <c r="P125" t="n">
         <v>36500</v>
@@ -6191,10 +6191,10 @@
         <v>799</v>
       </c>
       <c r="N133" t="n">
-        <v>998.76126436782</v>
+        <v>998.76126783754</v>
       </c>
       <c r="O133" t="n">
-        <v>798010.2502298881</v>
+        <v>798010.2530021945</v>
       </c>
       <c r="P133" t="n">
         <v>1600</v>
@@ -6225,7 +6225,7 @@
         </is>
       </c>
       <c r="J134" t="n">
-        <v>960</v>
+        <v>900</v>
       </c>
       <c r="K134" t="n">
         <v>0</v>
@@ -6234,19 +6234,19 @@
         <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>960</v>
+        <v>900</v>
       </c>
       <c r="N134" t="n">
         <v>6207.9882238578</v>
       </c>
       <c r="O134" t="n">
-        <v>5959668.694903488</v>
+        <v>5587189.40147202</v>
       </c>
       <c r="P134" t="n">
         <v>9900</v>
       </c>
       <c r="Q134" t="n">
-        <v>9504000</v>
+        <v>8910000</v>
       </c>
     </row>
     <row r="135">
@@ -6760,7 +6760,7 @@
         </is>
       </c>
       <c r="J146" t="n">
-        <v>273</v>
+        <v>243</v>
       </c>
       <c r="K146" t="n">
         <v>0</v>
@@ -6769,19 +6769,19 @@
         <v>0</v>
       </c>
       <c r="M146" t="n">
-        <v>273</v>
+        <v>243</v>
       </c>
       <c r="N146" t="n">
         <v>22730.48</v>
       </c>
       <c r="O146" t="n">
-        <v>6205421.04</v>
+        <v>5523506.64</v>
       </c>
       <c r="P146" t="n">
         <v>36900</v>
       </c>
       <c r="Q146" t="n">
-        <v>10073700</v>
+        <v>8966700</v>
       </c>
     </row>
     <row r="147">
@@ -6864,10 +6864,10 @@
         <v>144</v>
       </c>
       <c r="N148" t="n">
-        <v>27123.764828283</v>
+        <v>27123.764699793</v>
       </c>
       <c r="O148" t="n">
-        <v>3905822.135272752</v>
+        <v>3905822.116770192</v>
       </c>
       <c r="P148" t="n">
         <v>44500</v>
@@ -7731,10 +7731,10 @@
         <v>680</v>
       </c>
       <c r="N167" t="n">
-        <v>1778.4728562081</v>
+        <v>1778.4728585462</v>
       </c>
       <c r="O167" t="n">
-        <v>1209361.542221508</v>
+        <v>1209361.543811416</v>
       </c>
       <c r="P167" t="n">
         <v>4900</v>
@@ -8412,7 +8412,7 @@
         </is>
       </c>
       <c r="J182" t="n">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="K182" t="n">
         <v>0</v>
@@ -8421,19 +8421,19 @@
         <v>0</v>
       </c>
       <c r="M182" t="n">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="N182" t="n">
         <v>10411</v>
       </c>
       <c r="O182" t="n">
-        <v>2186310</v>
+        <v>1873980</v>
       </c>
       <c r="P182" t="n">
         <v>16900</v>
       </c>
       <c r="Q182" t="n">
-        <v>3549000</v>
+        <v>3042000</v>
       </c>
     </row>
     <row r="183">
@@ -9206,10 +9206,10 @@
         <v>129</v>
       </c>
       <c r="N199" t="n">
-        <v>3903.7395348837</v>
+        <v>3903.7398185118</v>
       </c>
       <c r="O199" t="n">
-        <v>503582.3999999973</v>
+        <v>503582.4365880222</v>
       </c>
       <c r="P199" t="n">
         <v>7500</v>
@@ -9564,10 +9564,10 @@
         <v>144</v>
       </c>
       <c r="N207" t="n">
-        <v>5869.1723864836</v>
+        <v>5869.1723297872</v>
       </c>
       <c r="O207" t="n">
-        <v>845160.8236536385</v>
+        <v>845160.8154893569</v>
       </c>
       <c r="P207" t="n">
         <v>9500</v>
@@ -11545,10 +11545,10 @@
         <v>864</v>
       </c>
       <c r="N250" t="n">
-        <v>1516.0387367881</v>
+        <v>1516.0387356204</v>
       </c>
       <c r="O250" t="n">
-        <v>1309857.468584918</v>
+        <v>1309857.467576026</v>
       </c>
       <c r="P250" t="n">
         <v>2300</v>
@@ -11859,7 +11859,7 @@
         </is>
       </c>
       <c r="J257" t="n">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="K257" t="n">
         <v>0</v>
@@ -11868,19 +11868,19 @@
         <v>0</v>
       </c>
       <c r="M257" t="n">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="N257" t="n">
         <v>13518</v>
       </c>
       <c r="O257" t="n">
-        <v>4866480</v>
+        <v>4704264</v>
       </c>
       <c r="P257" t="n">
         <v>21900</v>
       </c>
       <c r="Q257" t="n">
-        <v>7884000</v>
+        <v>7621200</v>
       </c>
     </row>
     <row r="258">
@@ -12340,10 +12340,10 @@
         <v>1440</v>
       </c>
       <c r="N267" t="n">
-        <v>1690.8700094251</v>
+        <v>1690.8700094518</v>
       </c>
       <c r="O267" t="n">
-        <v>2434852.813572144</v>
+        <v>2434852.813610592</v>
       </c>
       <c r="P267" t="n">
         <v>3000</v>
@@ -12894,10 +12894,10 @@
         <v>15264</v>
       </c>
       <c r="N279" t="n">
-        <v>703.79472483574</v>
+        <v>703.79470242023</v>
       </c>
       <c r="O279" t="n">
-        <v>10742722.67989274</v>
+        <v>10742722.33774239</v>
       </c>
       <c r="P279" t="n">
         <v>900</v>
@@ -14967,7 +14967,7 @@
         </is>
       </c>
       <c r="J323" t="n">
-        <v>212</v>
+        <v>188</v>
       </c>
       <c r="K323" t="n">
         <v>0</v>
@@ -14976,19 +14976,19 @@
         <v>0</v>
       </c>
       <c r="M323" t="n">
-        <v>212</v>
+        <v>188</v>
       </c>
       <c r="N323" t="n">
-        <v>1008.8125188917</v>
+        <v>1008.8113941019</v>
       </c>
       <c r="O323" t="n">
-        <v>213868.2540050404</v>
+        <v>189656.5420911572</v>
       </c>
       <c r="P323" t="n">
         <v>1500</v>
       </c>
       <c r="Q323" t="n">
-        <v>318000</v>
+        <v>282000</v>
       </c>
     </row>
     <row r="324">

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -3748,10 +3748,10 @@
         <v>216</v>
       </c>
       <c r="N79" t="n">
-        <v>3594.2529307806</v>
+        <v>3594.2529255711</v>
       </c>
       <c r="O79" t="n">
-        <v>776358.6330486096</v>
+        <v>776358.6319233576</v>
       </c>
       <c r="P79" t="n">
         <v>6500</v>
@@ -4207,10 +4207,10 @@
         <v>336</v>
       </c>
       <c r="N89" t="n">
-        <v>12422.462986842</v>
+        <v>12422.462990777</v>
       </c>
       <c r="O89" t="n">
-        <v>4173947.563578912</v>
+        <v>4173947.564901072</v>
       </c>
       <c r="P89" t="n">
         <v>19900</v>
@@ -6286,10 +6286,10 @@
         <v>36</v>
       </c>
       <c r="N135" t="n">
-        <v>4285.1964141414</v>
+        <v>4285.1964303797</v>
       </c>
       <c r="O135" t="n">
-        <v>154267.0709090904</v>
+        <v>154267.0714936692</v>
       </c>
       <c r="P135" t="n">
         <v>6900</v>
@@ -11545,10 +11545,10 @@
         <v>864</v>
       </c>
       <c r="N250" t="n">
-        <v>1516.0387356204</v>
+        <v>1516.0387309278</v>
       </c>
       <c r="O250" t="n">
-        <v>1309857.467576026</v>
+        <v>1309857.463521619</v>
       </c>
       <c r="P250" t="n">
         <v>2300</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q332"/>
+  <dimension ref="A1:Q331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-23</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-24</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>376</v>
+        <v>298</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -717,19 +717,19 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>376</v>
+        <v>298</v>
       </c>
       <c r="N8" t="n">
         <v>3376.7464001115</v>
       </c>
       <c r="O8" t="n">
-        <v>1269656.646441924</v>
+        <v>1006270.427233227</v>
       </c>
       <c r="P8" t="n">
         <v>4500</v>
       </c>
       <c r="Q8" t="n">
-        <v>1692000</v>
+        <v>1341000</v>
       </c>
     </row>
     <row r="9">
@@ -3065,10 +3065,10 @@
         <v>350</v>
       </c>
       <c r="N64" t="n">
-        <v>2582.2549274255</v>
+        <v>2582.2549040675</v>
       </c>
       <c r="O64" t="n">
-        <v>903789.2245989249</v>
+        <v>903789.216423625</v>
       </c>
       <c r="P64" t="n">
         <v>4500</v>
@@ -3111,10 +3111,10 @@
         <v>1232</v>
       </c>
       <c r="N65" t="n">
-        <v>5216.8958543674</v>
+        <v>5216.8958410068</v>
       </c>
       <c r="O65" t="n">
-        <v>6427215.692580637</v>
+        <v>6427215.676120377</v>
       </c>
       <c r="P65" t="n">
         <v>8500</v>
@@ -3157,10 +3157,10 @@
         <v>2592</v>
       </c>
       <c r="N66" t="n">
-        <v>3158.8608400976</v>
+        <v>3158.8608413965</v>
       </c>
       <c r="O66" t="n">
-        <v>8187767.297532979</v>
+        <v>8187767.300899727</v>
       </c>
       <c r="P66" t="n">
         <v>5600</v>
@@ -3203,10 +3203,10 @@
         <v>58</v>
       </c>
       <c r="N67" t="n">
-        <v>3841.6251265823</v>
+        <v>3841.6251483051</v>
       </c>
       <c r="O67" t="n">
-        <v>222814.2573417734</v>
+        <v>222814.2586016958</v>
       </c>
       <c r="P67" t="n">
         <v>6900</v>
@@ -3341,10 +3341,10 @@
         <v>480</v>
       </c>
       <c r="N70" t="n">
-        <v>3795.7100076292</v>
+        <v>3795.7100076321</v>
       </c>
       <c r="O70" t="n">
-        <v>1821940.803662016</v>
+        <v>1821940.803663408</v>
       </c>
       <c r="P70" t="n">
         <v>6200</v>
@@ -3520,10 +3520,10 @@
         <v>346</v>
       </c>
       <c r="N74" t="n">
-        <v>4890.9300535117</v>
+        <v>4890.9300537634</v>
       </c>
       <c r="O74" t="n">
-        <v>1692261.798515048</v>
+        <v>1692261.798602136</v>
       </c>
       <c r="P74" t="n">
         <v>8200</v>
@@ -3748,10 +3748,10 @@
         <v>216</v>
       </c>
       <c r="N79" t="n">
-        <v>3594.2529255711</v>
+        <v>3594.252920354</v>
       </c>
       <c r="O79" t="n">
-        <v>776358.6319233576</v>
+        <v>776358.6307964639</v>
       </c>
       <c r="P79" t="n">
         <v>6500</v>
@@ -3782,7 +3782,7 @@
         </is>
       </c>
       <c r="J80" t="n">
-        <v>424</v>
+        <v>384</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
@@ -3791,19 +3791,19 @@
         <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>424</v>
+        <v>384</v>
       </c>
       <c r="N80" t="n">
         <v>4891</v>
       </c>
       <c r="O80" t="n">
-        <v>2073784</v>
+        <v>1878144</v>
       </c>
       <c r="P80" t="n">
         <v>8200</v>
       </c>
       <c r="Q80" t="n">
-        <v>3476800</v>
+        <v>3148800</v>
       </c>
     </row>
     <row r="81">
@@ -4207,10 +4207,10 @@
         <v>336</v>
       </c>
       <c r="N89" t="n">
-        <v>12422.462990777</v>
+        <v>12422.462992091</v>
       </c>
       <c r="O89" t="n">
-        <v>4173947.564901072</v>
+        <v>4173947.565342576</v>
       </c>
       <c r="P89" t="n">
         <v>19900</v>
@@ -4299,10 +4299,10 @@
         <v>1728</v>
       </c>
       <c r="N91" t="n">
-        <v>3472.2762824732</v>
+        <v>3472.2762877567</v>
       </c>
       <c r="O91" t="n">
-        <v>6000093.41611369</v>
+        <v>6000093.425243578</v>
       </c>
       <c r="P91" t="n">
         <v>5900</v>
@@ -4389,10 +4389,10 @@
         <v>1356</v>
       </c>
       <c r="N93" t="n">
-        <v>4371.1712631292</v>
+        <v>4371.1712633877</v>
       </c>
       <c r="O93" t="n">
-        <v>5927308.232803196</v>
+        <v>5927308.23315372</v>
       </c>
       <c r="P93" t="n">
         <v>8900</v>
@@ -5835,10 +5835,10 @@
         <v>528</v>
       </c>
       <c r="N125" t="n">
-        <v>22485.695419847</v>
+        <v>22485.695402299</v>
       </c>
       <c r="O125" t="n">
-        <v>11872447.18167922</v>
+        <v>11872447.17241387</v>
       </c>
       <c r="P125" t="n">
         <v>36500</v>
@@ -6237,10 +6237,10 @@
         <v>900</v>
       </c>
       <c r="N134" t="n">
-        <v>6207.9882238578</v>
+        <v>6207.9882231175</v>
       </c>
       <c r="O134" t="n">
-        <v>5587189.40147202</v>
+        <v>5587189.40080575</v>
       </c>
       <c r="P134" t="n">
         <v>9900</v>
@@ -6460,10 +6460,10 @@
         <v>948</v>
       </c>
       <c r="N139" t="n">
-        <v>4814.2679256837</v>
+        <v>4814.2679250376</v>
       </c>
       <c r="O139" t="n">
-        <v>4563925.993548147</v>
+        <v>4563925.992935645</v>
       </c>
       <c r="P139" t="n">
         <v>9900</v>
@@ -6956,10 +6956,10 @@
         <v>221</v>
       </c>
       <c r="N150" t="n">
-        <v>8332.7796073298</v>
+        <v>8332.7796062992</v>
       </c>
       <c r="O150" t="n">
-        <v>1841544.293219886</v>
+        <v>1841544.292992123</v>
       </c>
       <c r="P150" t="n">
         <v>14900</v>
@@ -7731,10 +7731,10 @@
         <v>680</v>
       </c>
       <c r="N167" t="n">
-        <v>1778.4728585462</v>
+        <v>1778.4728622951</v>
       </c>
       <c r="O167" t="n">
-        <v>1209361.543811416</v>
+        <v>1209361.546360668</v>
       </c>
       <c r="P167" t="n">
         <v>4900</v>
@@ -8945,12 +8945,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>C4497</t>
+          <t>C4499</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>JUEGO D MESA 2EN 1 C4497</t>
+          <t>PIANO ELEFANTE PQÑ C4499</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -8964,7 +8964,7 @@
         </is>
       </c>
       <c r="J194" t="n">
-        <v>24</v>
+        <v>234</v>
       </c>
       <c r="K194" t="n">
         <v>0</v>
@@ -8973,30 +8973,30 @@
         <v>0</v>
       </c>
       <c r="M194" t="n">
-        <v>24</v>
+        <v>234</v>
       </c>
       <c r="N194" t="n">
-        <v>25076</v>
+        <v>6414</v>
       </c>
       <c r="O194" t="n">
-        <v>601824</v>
+        <v>1500876</v>
       </c>
       <c r="P194" t="n">
-        <v>40900</v>
+        <v>10900</v>
       </c>
       <c r="Q194" t="n">
-        <v>981600</v>
+        <v>2550600</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>C4499</t>
+          <t>C4504</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>PIANO ELEFANTE PQÑ C4499</t>
+          <t>CASTILLO ACCESORIOS STD C4504</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -9010,7 +9010,7 @@
         </is>
       </c>
       <c r="J195" t="n">
-        <v>234</v>
+        <v>12</v>
       </c>
       <c r="K195" t="n">
         <v>0</v>
@@ -9019,30 +9019,30 @@
         <v>0</v>
       </c>
       <c r="M195" t="n">
-        <v>234</v>
+        <v>12</v>
       </c>
       <c r="N195" t="n">
-        <v>6414</v>
+        <v>23376.36</v>
       </c>
       <c r="O195" t="n">
-        <v>1500876</v>
+        <v>280516.32</v>
       </c>
       <c r="P195" t="n">
-        <v>10900</v>
+        <v>40900</v>
       </c>
       <c r="Q195" t="n">
-        <v>2550600</v>
+        <v>490800</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>C4504</t>
+          <t>C4505</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>CASTILLO ACCESORIOS STD C4504</t>
+          <t>PESCADITO Y TIBURON  LUZ Y SONIDO C4505</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -9056,7 +9056,7 @@
         </is>
       </c>
       <c r="J196" t="n">
-        <v>12</v>
+        <v>460</v>
       </c>
       <c r="K196" t="n">
         <v>0</v>
@@ -9065,30 +9065,30 @@
         <v>0</v>
       </c>
       <c r="M196" t="n">
-        <v>12</v>
+        <v>460</v>
       </c>
       <c r="N196" t="n">
-        <v>23376.36</v>
+        <v>13210</v>
       </c>
       <c r="O196" t="n">
-        <v>280516.32</v>
+        <v>6076600</v>
       </c>
       <c r="P196" t="n">
-        <v>40900</v>
+        <v>23900</v>
       </c>
       <c r="Q196" t="n">
-        <v>490800</v>
+        <v>10994000</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>C4505</t>
+          <t>C4510</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>PESCADITO Y TIBURON  LUZ Y SONIDO C4505</t>
+          <t>TOCADOR CASTILLO MUSICA Y LUZ C4510</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -9102,7 +9102,7 @@
         </is>
       </c>
       <c r="J197" t="n">
-        <v>460</v>
+        <v>144</v>
       </c>
       <c r="K197" t="n">
         <v>0</v>
@@ -9111,30 +9111,30 @@
         <v>0</v>
       </c>
       <c r="M197" t="n">
-        <v>460</v>
+        <v>144</v>
       </c>
       <c r="N197" t="n">
-        <v>13210</v>
+        <v>52443</v>
       </c>
       <c r="O197" t="n">
-        <v>6076600</v>
+        <v>7551792</v>
       </c>
       <c r="P197" t="n">
-        <v>23900</v>
+        <v>83900</v>
       </c>
       <c r="Q197" t="n">
-        <v>10994000</v>
+        <v>12081600</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>C4510</t>
+          <t>C4511</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>TOCADOR CASTILLO MUSICA Y LUZ C4510</t>
+          <t>BURBUJERO MODELOS STDS C4511</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -9148,7 +9148,7 @@
         </is>
       </c>
       <c r="J198" t="n">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="K198" t="n">
         <v>0</v>
@@ -9157,35 +9157,30 @@
         <v>0</v>
       </c>
       <c r="M198" t="n">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="N198" t="n">
-        <v>52443</v>
+        <v>3903.7398185118</v>
       </c>
       <c r="O198" t="n">
-        <v>7551792</v>
+        <v>503582.4365880222</v>
       </c>
       <c r="P198" t="n">
-        <v>83900</v>
+        <v>7500</v>
       </c>
       <c r="Q198" t="n">
-        <v>12081600</v>
+        <v>967500</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>C4511</t>
+          <t>C4512</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>BURBUJERO MODELOS STDS C4511</t>
-        </is>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>MAQUILLAJE ESTUCHE UNICORNIO C4512</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -9194,7 +9189,7 @@
         </is>
       </c>
       <c r="J199" t="n">
-        <v>129</v>
+        <v>40</v>
       </c>
       <c r="K199" t="n">
         <v>0</v>
@@ -9203,30 +9198,30 @@
         <v>0</v>
       </c>
       <c r="M199" t="n">
-        <v>129</v>
+        <v>40</v>
       </c>
       <c r="N199" t="n">
-        <v>3903.7398185118</v>
+        <v>20726</v>
       </c>
       <c r="O199" t="n">
-        <v>503582.4365880222</v>
+        <v>829040</v>
       </c>
       <c r="P199" t="n">
-        <v>7500</v>
+        <v>33900</v>
       </c>
       <c r="Q199" t="n">
-        <v>967500</v>
+        <v>1356000</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>C4512</t>
+          <t>C4513</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>MAQUILLAJE ESTUCHE UNICORNIO C4512</t>
+          <t>ESTUCHE MAQUILLAJE UNICORNIO CON BALACA C4513</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -9235,7 +9230,7 @@
         </is>
       </c>
       <c r="J200" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="K200" t="n">
         <v>0</v>
@@ -9244,30 +9239,35 @@
         <v>0</v>
       </c>
       <c r="M200" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="N200" t="n">
-        <v>20726</v>
+        <v>35864.602181818</v>
       </c>
       <c r="O200" t="n">
-        <v>829040</v>
+        <v>1255261.07636363</v>
       </c>
       <c r="P200" t="n">
-        <v>33900</v>
+        <v>62900</v>
       </c>
       <c r="Q200" t="n">
-        <v>1356000</v>
+        <v>2201500</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>C4513</t>
+          <t>C4514</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>ESTUCHE MAQUILLAJE UNICORNIO CON BALACA C4513</t>
+          <t>ESTUCHE MAQUILLAJE PARA UÑAS C4514</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -9276,7 +9276,7 @@
         </is>
       </c>
       <c r="J201" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="K201" t="n">
         <v>0</v>
@@ -9285,30 +9285,30 @@
         <v>0</v>
       </c>
       <c r="M201" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="N201" t="n">
-        <v>35864.602181818</v>
+        <v>20731</v>
       </c>
       <c r="O201" t="n">
-        <v>1255261.07636363</v>
+        <v>953626</v>
       </c>
       <c r="P201" t="n">
-        <v>62900</v>
+        <v>33900</v>
       </c>
       <c r="Q201" t="n">
-        <v>2201500</v>
+        <v>1559400</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>C4514</t>
+          <t>C4521</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>ESTUCHE MAQUILLAJE PARA UÑAS C4514</t>
+          <t>JUEGO DE AJEDREZ 3EN1</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -9322,7 +9322,7 @@
         </is>
       </c>
       <c r="J202" t="n">
-        <v>46</v>
+        <v>118</v>
       </c>
       <c r="K202" t="n">
         <v>0</v>
@@ -9331,30 +9331,30 @@
         <v>0</v>
       </c>
       <c r="M202" t="n">
-        <v>46</v>
+        <v>118</v>
       </c>
       <c r="N202" t="n">
-        <v>20731</v>
+        <v>4202</v>
       </c>
       <c r="O202" t="n">
-        <v>953626</v>
+        <v>495836</v>
       </c>
       <c r="P202" t="n">
-        <v>33900</v>
+        <v>7900</v>
       </c>
       <c r="Q202" t="n">
-        <v>1559400</v>
+        <v>932200</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>C4521</t>
+          <t>C4523</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>JUEGO DE AJEDREZ 3EN1</t>
+          <t>PIANO TAPETE MUSICAL C4523</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -9368,7 +9368,7 @@
         </is>
       </c>
       <c r="J203" t="n">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="K203" t="n">
         <v>0</v>
@@ -9377,30 +9377,30 @@
         <v>0</v>
       </c>
       <c r="M203" t="n">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="N203" t="n">
-        <v>4202</v>
+        <v>16469</v>
       </c>
       <c r="O203" t="n">
-        <v>495836</v>
+        <v>2371536</v>
       </c>
       <c r="P203" t="n">
-        <v>7900</v>
+        <v>26900</v>
       </c>
       <c r="Q203" t="n">
-        <v>932200</v>
+        <v>3873600</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>C4523</t>
+          <t>C4525</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>PIANO TAPETE MUSICAL C4523</t>
+          <t>LANZADORA CATAPULTA C4525</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="J204" t="n">
-        <v>144</v>
+        <v>18</v>
       </c>
       <c r="K204" t="n">
         <v>0</v>
@@ -9423,30 +9423,30 @@
         <v>0</v>
       </c>
       <c r="M204" t="n">
-        <v>144</v>
+        <v>18</v>
       </c>
       <c r="N204" t="n">
-        <v>16469</v>
+        <v>11922</v>
       </c>
       <c r="O204" t="n">
-        <v>2371536</v>
+        <v>214596</v>
       </c>
       <c r="P204" t="n">
-        <v>26900</v>
+        <v>19900</v>
       </c>
       <c r="Q204" t="n">
-        <v>3873600</v>
+        <v>358200</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>C4525</t>
+          <t>C4527</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>LANZADORA CATAPULTA C4525</t>
+          <t>MINI PIANO C4527</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -9460,7 +9460,7 @@
         </is>
       </c>
       <c r="J205" t="n">
-        <v>18</v>
+        <v>108</v>
       </c>
       <c r="K205" t="n">
         <v>0</v>
@@ -9469,30 +9469,30 @@
         <v>0</v>
       </c>
       <c r="M205" t="n">
-        <v>18</v>
+        <v>108</v>
       </c>
       <c r="N205" t="n">
-        <v>11922</v>
+        <v>12556</v>
       </c>
       <c r="O205" t="n">
-        <v>214596</v>
+        <v>1356048</v>
       </c>
       <c r="P205" t="n">
-        <v>19900</v>
+        <v>21900</v>
       </c>
       <c r="Q205" t="n">
-        <v>358200</v>
+        <v>2365200</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>C4527</t>
+          <t>C4530</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>MINI PIANO C4527</t>
+          <t>CARRO FORMULAY DINO BURBUJERA C4530</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -9506,7 +9506,7 @@
         </is>
       </c>
       <c r="J206" t="n">
-        <v>108</v>
+        <v>144</v>
       </c>
       <c r="K206" t="n">
         <v>0</v>
@@ -9515,30 +9515,30 @@
         <v>0</v>
       </c>
       <c r="M206" t="n">
-        <v>108</v>
+        <v>144</v>
       </c>
       <c r="N206" t="n">
-        <v>12556</v>
+        <v>5869.1723297872</v>
       </c>
       <c r="O206" t="n">
-        <v>1356048</v>
+        <v>845160.8154893569</v>
       </c>
       <c r="P206" t="n">
-        <v>21900</v>
+        <v>9500</v>
       </c>
       <c r="Q206" t="n">
-        <v>2365200</v>
+        <v>1368000</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>C4530</t>
+          <t>C4531</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>CARRO FORMULAY DINO BURBUJERA C4530</t>
+          <t>CARROS RETRO/GRUA STD BOLSA PVC C4531</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -9552,7 +9552,7 @@
         </is>
       </c>
       <c r="J207" t="n">
-        <v>144</v>
+        <v>307</v>
       </c>
       <c r="K207" t="n">
         <v>0</v>
@@ -9561,30 +9561,30 @@
         <v>0</v>
       </c>
       <c r="M207" t="n">
-        <v>144</v>
+        <v>307</v>
       </c>
       <c r="N207" t="n">
-        <v>5869.1723297872</v>
+        <v>6849.2</v>
       </c>
       <c r="O207" t="n">
-        <v>845160.8154893569</v>
+        <v>2102704.4</v>
       </c>
       <c r="P207" t="n">
-        <v>9500</v>
+        <v>11500</v>
       </c>
       <c r="Q207" t="n">
-        <v>1368000</v>
+        <v>3530500</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>C4531</t>
+          <t>C4534</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>CARROS RETRO/GRUA STD BOLSA PVC C4531</t>
+          <t>CARROS RETROS STD CAJA X 12 C4534</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -9598,7 +9598,7 @@
         </is>
       </c>
       <c r="J208" t="n">
-        <v>307</v>
+        <v>702</v>
       </c>
       <c r="K208" t="n">
         <v>0</v>
@@ -9607,30 +9607,30 @@
         <v>0</v>
       </c>
       <c r="M208" t="n">
-        <v>307</v>
+        <v>702</v>
       </c>
       <c r="N208" t="n">
-        <v>6849.2</v>
+        <v>5772</v>
       </c>
       <c r="O208" t="n">
-        <v>2102704.4</v>
+        <v>4051944</v>
       </c>
       <c r="P208" t="n">
-        <v>11500</v>
+        <v>9900</v>
       </c>
       <c r="Q208" t="n">
-        <v>3530500</v>
+        <v>6949800</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>C4534</t>
+          <t>C4541</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>CARROS RETROS STD CAJA X 12 C4534</t>
+          <t>LANZADORADARDOS MED C4541</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -9644,7 +9644,7 @@
         </is>
       </c>
       <c r="J209" t="n">
-        <v>702</v>
+        <v>456</v>
       </c>
       <c r="K209" t="n">
         <v>0</v>
@@ -9653,30 +9653,30 @@
         <v>0</v>
       </c>
       <c r="M209" t="n">
-        <v>702</v>
+        <v>456</v>
       </c>
       <c r="N209" t="n">
-        <v>5772</v>
+        <v>6645</v>
       </c>
       <c r="O209" t="n">
-        <v>4051944</v>
+        <v>3030120</v>
       </c>
       <c r="P209" t="n">
-        <v>9900</v>
+        <v>10900</v>
       </c>
       <c r="Q209" t="n">
-        <v>6949800</v>
+        <v>4970400</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>C4541</t>
+          <t>C4542</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>LANZADORADARDOS MED C4541</t>
+          <t>LANZDORA DE DARDOS Y BIOGEL C4542</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -9690,7 +9690,7 @@
         </is>
       </c>
       <c r="J210" t="n">
-        <v>456</v>
+        <v>256</v>
       </c>
       <c r="K210" t="n">
         <v>0</v>
@@ -9699,30 +9699,30 @@
         <v>0</v>
       </c>
       <c r="M210" t="n">
-        <v>456</v>
+        <v>256</v>
       </c>
       <c r="N210" t="n">
-        <v>6645</v>
+        <v>13098</v>
       </c>
       <c r="O210" t="n">
-        <v>3030120</v>
+        <v>3353088</v>
       </c>
       <c r="P210" t="n">
-        <v>10900</v>
+        <v>21200</v>
       </c>
       <c r="Q210" t="n">
-        <v>4970400</v>
+        <v>5427200</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>C4542</t>
+          <t>C4545</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>LANZDORA DE DARDOS Y BIOGEL C4542</t>
+          <t>TAPETE PIANO PARA BEBE C4545</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -9736,7 +9736,7 @@
         </is>
       </c>
       <c r="J211" t="n">
-        <v>256</v>
+        <v>132</v>
       </c>
       <c r="K211" t="n">
         <v>0</v>
@@ -9745,30 +9745,30 @@
         <v>0</v>
       </c>
       <c r="M211" t="n">
-        <v>256</v>
+        <v>132</v>
       </c>
       <c r="N211" t="n">
-        <v>13098</v>
+        <v>27186</v>
       </c>
       <c r="O211" t="n">
-        <v>3353088</v>
+        <v>3588552</v>
       </c>
       <c r="P211" t="n">
-        <v>21200</v>
+        <v>43900</v>
       </c>
       <c r="Q211" t="n">
-        <v>5427200</v>
+        <v>5794800</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>C4545</t>
+          <t>C4547</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>TAPETE PIANO PARA BEBE C4545</t>
+          <t>CASA VILLA ACCESORIOS C4547</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -9782,7 +9782,7 @@
         </is>
       </c>
       <c r="J212" t="n">
-        <v>132</v>
+        <v>84</v>
       </c>
       <c r="K212" t="n">
         <v>0</v>
@@ -9791,30 +9791,30 @@
         <v>0</v>
       </c>
       <c r="M212" t="n">
-        <v>132</v>
+        <v>84</v>
       </c>
       <c r="N212" t="n">
-        <v>27186</v>
+        <v>72535</v>
       </c>
       <c r="O212" t="n">
-        <v>3588552</v>
+        <v>6092940</v>
       </c>
       <c r="P212" t="n">
-        <v>43900</v>
+        <v>116900</v>
       </c>
       <c r="Q212" t="n">
-        <v>5794800</v>
+        <v>9819600</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>C4547</t>
+          <t>C4548</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>CASA VILLA ACCESORIOS C4547</t>
+          <t>CARRO DIDACTICO X4 BEBE</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -9828,7 +9828,7 @@
         </is>
       </c>
       <c r="J213" t="n">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="K213" t="n">
         <v>0</v>
@@ -9837,30 +9837,30 @@
         <v>0</v>
       </c>
       <c r="M213" t="n">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="N213" t="n">
-        <v>72535</v>
+        <v>7562</v>
       </c>
       <c r="O213" t="n">
-        <v>6092940</v>
+        <v>794010</v>
       </c>
       <c r="P213" t="n">
-        <v>116900</v>
+        <v>12900</v>
       </c>
       <c r="Q213" t="n">
-        <v>9819600</v>
+        <v>1354500</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>C4548</t>
+          <t>C4550</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>CARRO DIDACTICO X4 BEBE</t>
+          <t>HELICOPTERO  FASHION C4550</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -9874,7 +9874,7 @@
         </is>
       </c>
       <c r="J214" t="n">
-        <v>105</v>
+        <v>245</v>
       </c>
       <c r="K214" t="n">
         <v>0</v>
@@ -9883,30 +9883,30 @@
         <v>0</v>
       </c>
       <c r="M214" t="n">
-        <v>105</v>
+        <v>245</v>
       </c>
       <c r="N214" t="n">
-        <v>7562</v>
+        <v>13565</v>
       </c>
       <c r="O214" t="n">
-        <v>794010</v>
+        <v>3323425</v>
       </c>
       <c r="P214" t="n">
-        <v>12900</v>
+        <v>22500</v>
       </c>
       <c r="Q214" t="n">
-        <v>1354500</v>
+        <v>5512500</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>C4550</t>
+          <t>C4551</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>HELICOPTERO  FASHION C4550</t>
+          <t>PRINCESS EN CASTILLO Y CARRUAJE C4551</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -9920,7 +9920,7 @@
         </is>
       </c>
       <c r="J215" t="n">
-        <v>245</v>
+        <v>1162</v>
       </c>
       <c r="K215" t="n">
         <v>0</v>
@@ -9929,30 +9929,30 @@
         <v>0</v>
       </c>
       <c r="M215" t="n">
-        <v>245</v>
+        <v>1162</v>
       </c>
       <c r="N215" t="n">
-        <v>13565</v>
+        <v>7635</v>
       </c>
       <c r="O215" t="n">
-        <v>3323425</v>
+        <v>8871870</v>
       </c>
       <c r="P215" t="n">
-        <v>22500</v>
+        <v>13900</v>
       </c>
       <c r="Q215" t="n">
-        <v>5512500</v>
+        <v>16151800</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>C4551</t>
+          <t>C4555</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>PRINCESS EN CASTILLO Y CARRUAJE C4551</t>
+          <t>SONAJERO EN BOLSA 5 PCS C4555</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -9966,7 +9966,7 @@
         </is>
       </c>
       <c r="J216" t="n">
-        <v>1162</v>
+        <v>336</v>
       </c>
       <c r="K216" t="n">
         <v>0</v>
@@ -9975,30 +9975,30 @@
         <v>0</v>
       </c>
       <c r="M216" t="n">
-        <v>1162</v>
+        <v>336</v>
       </c>
       <c r="N216" t="n">
-        <v>7635</v>
+        <v>5438</v>
       </c>
       <c r="O216" t="n">
-        <v>8871870</v>
+        <v>1827168</v>
       </c>
       <c r="P216" t="n">
-        <v>13900</v>
+        <v>8900</v>
       </c>
       <c r="Q216" t="n">
-        <v>16151800</v>
+        <v>2990400</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>C4555</t>
+          <t>C4556</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>SONAJERO EN BOLSA 5 PCS C4555</t>
+          <t>SONAJERO EN CAJA 8PCS C4556</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -10012,7 +10012,7 @@
         </is>
       </c>
       <c r="J217" t="n">
-        <v>336</v>
+        <v>48</v>
       </c>
       <c r="K217" t="n">
         <v>0</v>
@@ -10021,30 +10021,30 @@
         <v>0</v>
       </c>
       <c r="M217" t="n">
-        <v>336</v>
+        <v>48</v>
       </c>
       <c r="N217" t="n">
-        <v>5438</v>
+        <v>16086</v>
       </c>
       <c r="O217" t="n">
-        <v>1827168</v>
+        <v>772128</v>
       </c>
       <c r="P217" t="n">
-        <v>8900</v>
+        <v>25900</v>
       </c>
       <c r="Q217" t="n">
-        <v>2990400</v>
+        <v>1243200</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>C4556</t>
+          <t>C4557</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>SONAJERO EN CAJA 8PCS C4556</t>
+          <t>JUEGO DE UÑAS Y MAQUILLAJE C4557</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -10058,7 +10058,7 @@
         </is>
       </c>
       <c r="J218" t="n">
-        <v>48</v>
+        <v>560</v>
       </c>
       <c r="K218" t="n">
         <v>0</v>
@@ -10067,30 +10067,30 @@
         <v>0</v>
       </c>
       <c r="M218" t="n">
-        <v>48</v>
+        <v>560</v>
       </c>
       <c r="N218" t="n">
-        <v>16086</v>
+        <v>8806</v>
       </c>
       <c r="O218" t="n">
-        <v>772128</v>
+        <v>4931360</v>
       </c>
       <c r="P218" t="n">
-        <v>25900</v>
+        <v>14900</v>
       </c>
       <c r="Q218" t="n">
-        <v>1243200</v>
+        <v>8344000</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>C4557</t>
+          <t>C4559</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>JUEGO DE UÑAS Y MAQUILLAJE C4557</t>
+          <t>PIANO DIDACTICO 3en1 C4559</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -10104,7 +10104,7 @@
         </is>
       </c>
       <c r="J219" t="n">
-        <v>560</v>
+        <v>180</v>
       </c>
       <c r="K219" t="n">
         <v>0</v>
@@ -10113,30 +10113,30 @@
         <v>0</v>
       </c>
       <c r="M219" t="n">
-        <v>560</v>
+        <v>180</v>
       </c>
       <c r="N219" t="n">
-        <v>8806</v>
+        <v>19008</v>
       </c>
       <c r="O219" t="n">
-        <v>4931360</v>
+        <v>3421440</v>
       </c>
       <c r="P219" t="n">
-        <v>14900</v>
+        <v>30900</v>
       </c>
       <c r="Q219" t="n">
-        <v>8344000</v>
+        <v>5562000</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>C4559</t>
+          <t>C4560</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>PIANO DIDACTICO 3en1 C4559</t>
+          <t>PIANO TAPETE C4560</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -10150,7 +10150,7 @@
         </is>
       </c>
       <c r="J220" t="n">
-        <v>180</v>
+        <v>460</v>
       </c>
       <c r="K220" t="n">
         <v>0</v>
@@ -10159,30 +10159,30 @@
         <v>0</v>
       </c>
       <c r="M220" t="n">
-        <v>180</v>
+        <v>460</v>
       </c>
       <c r="N220" t="n">
-        <v>19008</v>
+        <v>11302</v>
       </c>
       <c r="O220" t="n">
-        <v>3421440</v>
+        <v>5198920</v>
       </c>
       <c r="P220" t="n">
-        <v>30900</v>
+        <v>18900</v>
       </c>
       <c r="Q220" t="n">
-        <v>5562000</v>
+        <v>8694000</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>C4560</t>
+          <t>C4561</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>PIANO TAPETE C4560</t>
+          <t>ABECEDARIO INGLES MUSICAL C4561</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -10196,7 +10196,7 @@
         </is>
       </c>
       <c r="J221" t="n">
-        <v>460</v>
+        <v>180</v>
       </c>
       <c r="K221" t="n">
         <v>0</v>
@@ -10205,30 +10205,30 @@
         <v>0</v>
       </c>
       <c r="M221" t="n">
-        <v>460</v>
+        <v>180</v>
       </c>
       <c r="N221" t="n">
-        <v>11302</v>
+        <v>17992</v>
       </c>
       <c r="O221" t="n">
-        <v>5198920</v>
+        <v>3238560</v>
       </c>
       <c r="P221" t="n">
-        <v>18900</v>
+        <v>28900</v>
       </c>
       <c r="Q221" t="n">
-        <v>8694000</v>
+        <v>5202000</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>C4561</t>
+          <t>C4566</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>ABECEDARIO INGLES MUSICAL C4561</t>
+          <t>CARRO MINI CONTROL MODELOS STDS C4566</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -10242,7 +10242,7 @@
         </is>
       </c>
       <c r="J222" t="n">
-        <v>180</v>
+        <v>290</v>
       </c>
       <c r="K222" t="n">
         <v>0</v>
@@ -10251,30 +10251,30 @@
         <v>0</v>
       </c>
       <c r="M222" t="n">
-        <v>180</v>
+        <v>290</v>
       </c>
       <c r="N222" t="n">
-        <v>17992</v>
+        <v>11348</v>
       </c>
       <c r="O222" t="n">
-        <v>3238560</v>
+        <v>3290920</v>
       </c>
       <c r="P222" t="n">
-        <v>28900</v>
+        <v>19900</v>
       </c>
       <c r="Q222" t="n">
-        <v>5202000</v>
+        <v>5771000</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>C4566</t>
+          <t>C4567</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>CARRO MINI CONTROL MODELOS STDS C4566</t>
+          <t>JUEGO MESA FORMA DE ANIMALES C4567</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -10288,7 +10288,7 @@
         </is>
       </c>
       <c r="J223" t="n">
-        <v>290</v>
+        <v>192</v>
       </c>
       <c r="K223" t="n">
         <v>0</v>
@@ -10297,30 +10297,30 @@
         <v>0</v>
       </c>
       <c r="M223" t="n">
-        <v>290</v>
+        <v>192</v>
       </c>
       <c r="N223" t="n">
-        <v>11348</v>
+        <v>17075.98951782</v>
       </c>
       <c r="O223" t="n">
-        <v>3290920</v>
+        <v>3278589.98742144</v>
       </c>
       <c r="P223" t="n">
-        <v>19900</v>
+        <v>27500</v>
       </c>
       <c r="Q223" t="n">
-        <v>5771000</v>
+        <v>5280000</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>C4567</t>
+          <t>C4570</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>JUEGO MESA FORMA DE ANIMALES C4567</t>
+          <t>CUBO MAGICO C4570 EQY766</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -10334,7 +10334,7 @@
         </is>
       </c>
       <c r="J224" t="n">
-        <v>192</v>
+        <v>60</v>
       </c>
       <c r="K224" t="n">
         <v>0</v>
@@ -10343,30 +10343,30 @@
         <v>0</v>
       </c>
       <c r="M224" t="n">
-        <v>192</v>
+        <v>60</v>
       </c>
       <c r="N224" t="n">
-        <v>17075.989518156</v>
+        <v>10398</v>
       </c>
       <c r="O224" t="n">
-        <v>3278589.987485952</v>
+        <v>623880</v>
       </c>
       <c r="P224" t="n">
-        <v>27500</v>
+        <v>16900</v>
       </c>
       <c r="Q224" t="n">
-        <v>5280000</v>
+        <v>1014000</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>C4570</t>
+          <t>C4572</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>CUBO MAGICO C4570 EQY766</t>
+          <t>CUBO MAGICO C4572 EQY10130</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -10380,7 +10380,7 @@
         </is>
       </c>
       <c r="J225" t="n">
-        <v>60</v>
+        <v>108</v>
       </c>
       <c r="K225" t="n">
         <v>0</v>
@@ -10389,30 +10389,30 @@
         <v>0</v>
       </c>
       <c r="M225" t="n">
-        <v>60</v>
+        <v>108</v>
       </c>
       <c r="N225" t="n">
-        <v>10398</v>
+        <v>4518</v>
       </c>
       <c r="O225" t="n">
-        <v>623880</v>
+        <v>487944</v>
       </c>
       <c r="P225" t="n">
-        <v>16900</v>
+        <v>7900</v>
       </c>
       <c r="Q225" t="n">
-        <v>1014000</v>
+        <v>853200</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>C4572</t>
+          <t>C4577</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>CUBO MAGICO C4572 EQY10130</t>
+          <t>PISTA DINOSAURIO C4577</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -10426,7 +10426,7 @@
         </is>
       </c>
       <c r="J226" t="n">
-        <v>108</v>
+        <v>67</v>
       </c>
       <c r="K226" t="n">
         <v>0</v>
@@ -10435,30 +10435,30 @@
         <v>0</v>
       </c>
       <c r="M226" t="n">
-        <v>108</v>
+        <v>67</v>
       </c>
       <c r="N226" t="n">
-        <v>4518</v>
+        <v>21346</v>
       </c>
       <c r="O226" t="n">
-        <v>487944</v>
+        <v>1430182</v>
       </c>
       <c r="P226" t="n">
-        <v>7900</v>
+        <v>34900</v>
       </c>
       <c r="Q226" t="n">
-        <v>853200</v>
+        <v>2338300</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>C4577</t>
+          <t>C4578</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>PISTA DINOSAURIO C4577</t>
+          <t>LANZADORA DE AGUA BOLSA PVC C4578</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -10472,7 +10472,7 @@
         </is>
       </c>
       <c r="J227" t="n">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="K227" t="n">
         <v>0</v>
@@ -10481,30 +10481,30 @@
         <v>0</v>
       </c>
       <c r="M227" t="n">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="N227" t="n">
-        <v>21346</v>
+        <v>18001</v>
       </c>
       <c r="O227" t="n">
-        <v>1430182</v>
+        <v>1512084</v>
       </c>
       <c r="P227" t="n">
-        <v>34900</v>
+        <v>28900</v>
       </c>
       <c r="Q227" t="n">
-        <v>2338300</v>
+        <v>2427600</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>C4578</t>
+          <t>C4579</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>LANZADORA DE AGUA BOLSA PVC C4578</t>
+          <t>LANZADORA DE AGUA C4579</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -10518,7 +10518,7 @@
         </is>
       </c>
       <c r="J228" t="n">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="K228" t="n">
         <v>0</v>
@@ -10527,30 +10527,33 @@
         <v>0</v>
       </c>
       <c r="M228" t="n">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="N228" t="n">
-        <v>18001</v>
+        <v>10219</v>
       </c>
       <c r="O228" t="n">
-        <v>1512084</v>
+        <v>694892</v>
       </c>
       <c r="P228" t="n">
-        <v>28900</v>
+        <v>16900</v>
       </c>
       <c r="Q228" t="n">
-        <v>2427600</v>
+        <v>1149200</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>C4579</t>
-        </is>
+          <t>C458</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>6920190230459</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>LANZADORA DE AGUA C4579</t>
+          <t>BURRO SENCILLO SONIDO</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -10560,11 +10563,11 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J229" t="n">
-        <v>68</v>
+        <v>420</v>
       </c>
       <c r="K229" t="n">
         <v>0</v>
@@ -10573,33 +10576,30 @@
         <v>0</v>
       </c>
       <c r="M229" t="n">
-        <v>68</v>
+        <v>420</v>
       </c>
       <c r="N229" t="n">
-        <v>10219</v>
+        <v>10755</v>
       </c>
       <c r="O229" t="n">
-        <v>694892</v>
+        <v>4517100</v>
       </c>
       <c r="P229" t="n">
-        <v>16900</v>
+        <v>17900</v>
       </c>
       <c r="Q229" t="n">
-        <v>1149200</v>
+        <v>7518000</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>C458</t>
-        </is>
-      </c>
-      <c r="B230" t="n">
-        <v>6920190230459</v>
+          <t>C4581</t>
+        </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>BURRO SENCILLO SONIDO</t>
+          <t>ESPADA BURBUJERA C4581</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -10609,11 +10609,11 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J230" t="n">
-        <v>420</v>
+        <v>106</v>
       </c>
       <c r="K230" t="n">
         <v>0</v>
@@ -10622,30 +10622,30 @@
         <v>0</v>
       </c>
       <c r="M230" t="n">
-        <v>420</v>
+        <v>106</v>
       </c>
       <c r="N230" t="n">
-        <v>10755</v>
+        <v>17168</v>
       </c>
       <c r="O230" t="n">
-        <v>4517100</v>
+        <v>1819808</v>
       </c>
       <c r="P230" t="n">
-        <v>17900</v>
+        <v>27900</v>
       </c>
       <c r="Q230" t="n">
-        <v>7518000</v>
+        <v>2957400</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>C4581</t>
+          <t>C4584</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>ESPADA BURBUJERA C4581</t>
+          <t>LANZADORA DARDOS C4584</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -10659,7 +10659,7 @@
         </is>
       </c>
       <c r="J231" t="n">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="K231" t="n">
         <v>0</v>
@@ -10668,30 +10668,30 @@
         <v>0</v>
       </c>
       <c r="M231" t="n">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="N231" t="n">
-        <v>17168</v>
+        <v>27254</v>
       </c>
       <c r="O231" t="n">
-        <v>1819808</v>
+        <v>3597528</v>
       </c>
       <c r="P231" t="n">
-        <v>27900</v>
+        <v>43900</v>
       </c>
       <c r="Q231" t="n">
-        <v>2957400</v>
+        <v>5794800</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>C4584</t>
+          <t>C4596</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>LANZADORA DARDOS C4584</t>
+          <t>JUEGO ANTIESTRES C4596</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -10705,7 +10705,7 @@
         </is>
       </c>
       <c r="J232" t="n">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="K232" t="n">
         <v>0</v>
@@ -10714,30 +10714,30 @@
         <v>0</v>
       </c>
       <c r="M232" t="n">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="N232" t="n">
-        <v>27254</v>
+        <v>4303</v>
       </c>
       <c r="O232" t="n">
-        <v>3597528</v>
+        <v>464724</v>
       </c>
       <c r="P232" t="n">
-        <v>43900</v>
+        <v>7900</v>
       </c>
       <c r="Q232" t="n">
-        <v>5794800</v>
+        <v>853200</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>C4596</t>
+          <t>C4599</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>JUEGO ANTIESTRES C4596</t>
+          <t>VARA HELICE DINOSAURIO C4599</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -10751,7 +10751,7 @@
         </is>
       </c>
       <c r="J233" t="n">
-        <v>108</v>
+        <v>720</v>
       </c>
       <c r="K233" t="n">
         <v>0</v>
@@ -10760,30 +10760,30 @@
         <v>0</v>
       </c>
       <c r="M233" t="n">
-        <v>108</v>
+        <v>720</v>
       </c>
       <c r="N233" t="n">
-        <v>4303</v>
+        <v>5588</v>
       </c>
       <c r="O233" t="n">
-        <v>464724</v>
+        <v>4023360</v>
       </c>
       <c r="P233" t="n">
-        <v>7900</v>
+        <v>9500</v>
       </c>
       <c r="Q233" t="n">
-        <v>853200</v>
+        <v>6840000</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>C4599</t>
+          <t>C4601</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>VARA HELICE DINOSAURIO C4599</t>
+          <t>SET PERRO PATROL C4601</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -10797,7 +10797,7 @@
         </is>
       </c>
       <c r="J234" t="n">
-        <v>720</v>
+        <v>60</v>
       </c>
       <c r="K234" t="n">
         <v>0</v>
@@ -10806,30 +10806,30 @@
         <v>0</v>
       </c>
       <c r="M234" t="n">
-        <v>720</v>
+        <v>60</v>
       </c>
       <c r="N234" t="n">
-        <v>5588</v>
+        <v>14050</v>
       </c>
       <c r="O234" t="n">
-        <v>4023360</v>
+        <v>843000</v>
       </c>
       <c r="P234" t="n">
-        <v>9500</v>
+        <v>23900</v>
       </c>
       <c r="Q234" t="n">
-        <v>6840000</v>
+        <v>1434000</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>C4601</t>
+          <t>C4602</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>SET PERRO PATROL C4601</t>
+          <t>AVION CON PISTA MODELOS STD C4602</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -10843,7 +10843,7 @@
         </is>
       </c>
       <c r="J235" t="n">
-        <v>60</v>
+        <v>285</v>
       </c>
       <c r="K235" t="n">
         <v>0</v>
@@ -10852,30 +10852,30 @@
         <v>0</v>
       </c>
       <c r="M235" t="n">
-        <v>60</v>
+        <v>285</v>
       </c>
       <c r="N235" t="n">
-        <v>14050</v>
+        <v>8700</v>
       </c>
       <c r="O235" t="n">
-        <v>843000</v>
+        <v>2479500</v>
       </c>
       <c r="P235" t="n">
-        <v>23900</v>
+        <v>14900</v>
       </c>
       <c r="Q235" t="n">
-        <v>1434000</v>
+        <v>4246500</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>C4602</t>
+          <t>C4603</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>AVION CON PISTA MODELOS STD C4602</t>
+          <t>MAQUILLAJE BLISTER SENCILLO C4603</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -10889,7 +10889,7 @@
         </is>
       </c>
       <c r="J236" t="n">
-        <v>285</v>
+        <v>385</v>
       </c>
       <c r="K236" t="n">
         <v>0</v>
@@ -10898,30 +10898,30 @@
         <v>0</v>
       </c>
       <c r="M236" t="n">
-        <v>285</v>
+        <v>385</v>
       </c>
       <c r="N236" t="n">
-        <v>8700</v>
+        <v>3639.35</v>
       </c>
       <c r="O236" t="n">
-        <v>2479500</v>
+        <v>1401149.75</v>
       </c>
       <c r="P236" t="n">
-        <v>14900</v>
+        <v>7500</v>
       </c>
       <c r="Q236" t="n">
-        <v>4246500</v>
+        <v>2887500</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>C4603</t>
+          <t>C4604</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>MAQUILLAJE BLISTER SENCILLO C4603</t>
+          <t>MQUILLAJE BLISTER MODELOS STDS C4604</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -10935,7 +10935,7 @@
         </is>
       </c>
       <c r="J237" t="n">
-        <v>385</v>
+        <v>1709</v>
       </c>
       <c r="K237" t="n">
         <v>0</v>
@@ -10944,30 +10944,30 @@
         <v>0</v>
       </c>
       <c r="M237" t="n">
-        <v>385</v>
+        <v>1709</v>
       </c>
       <c r="N237" t="n">
-        <v>3639.35</v>
+        <v>1326</v>
       </c>
       <c r="O237" t="n">
-        <v>1401149.75</v>
+        <v>2266134</v>
       </c>
       <c r="P237" t="n">
-        <v>7500</v>
+        <v>2500</v>
       </c>
       <c r="Q237" t="n">
-        <v>2887500</v>
+        <v>4272500</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>C4604</t>
+          <t>C4605</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>MQUILLAJE BLISTER MODELOS STDS C4604</t>
+          <t>MAQUILLAJE BLISTER  CORAZON C4605</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -10981,7 +10981,7 @@
         </is>
       </c>
       <c r="J238" t="n">
-        <v>1709</v>
+        <v>176</v>
       </c>
       <c r="K238" t="n">
         <v>0</v>
@@ -10990,30 +10990,30 @@
         <v>0</v>
       </c>
       <c r="M238" t="n">
-        <v>1709</v>
+        <v>176</v>
       </c>
       <c r="N238" t="n">
-        <v>1326</v>
+        <v>5640</v>
       </c>
       <c r="O238" t="n">
-        <v>2266134</v>
+        <v>992640</v>
       </c>
       <c r="P238" t="n">
-        <v>2500</v>
+        <v>9900</v>
       </c>
       <c r="Q238" t="n">
-        <v>4272500</v>
+        <v>1742400</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>C4605</t>
+          <t>C4606</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>MAQUILLAJE BLISTER  CORAZON C4605</t>
+          <t>SONAJERO EN CAJA 6PCS C4606</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -11027,7 +11027,7 @@
         </is>
       </c>
       <c r="J239" t="n">
-        <v>176</v>
+        <v>279</v>
       </c>
       <c r="K239" t="n">
         <v>0</v>
@@ -11036,30 +11036,30 @@
         <v>0</v>
       </c>
       <c r="M239" t="n">
-        <v>176</v>
+        <v>279</v>
       </c>
       <c r="N239" t="n">
-        <v>5640</v>
+        <v>10713.21</v>
       </c>
       <c r="O239" t="n">
-        <v>992640</v>
+        <v>2988985.59</v>
       </c>
       <c r="P239" t="n">
-        <v>9900</v>
+        <v>20900</v>
       </c>
       <c r="Q239" t="n">
-        <v>1742400</v>
+        <v>5831100</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>C4606</t>
+          <t>C4607</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>SONAJERO EN CAJA 6PCS C4606</t>
+          <t>MAQUILLAJE SIRENA C4607</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -11073,7 +11073,7 @@
         </is>
       </c>
       <c r="J240" t="n">
-        <v>279</v>
+        <v>159</v>
       </c>
       <c r="K240" t="n">
         <v>0</v>
@@ -11082,30 +11082,30 @@
         <v>0</v>
       </c>
       <c r="M240" t="n">
-        <v>279</v>
+        <v>159</v>
       </c>
       <c r="N240" t="n">
-        <v>10713.21</v>
+        <v>10817</v>
       </c>
       <c r="O240" t="n">
-        <v>2988985.59</v>
+        <v>1719903</v>
       </c>
       <c r="P240" t="n">
-        <v>20900</v>
+        <v>17900</v>
       </c>
       <c r="Q240" t="n">
-        <v>5831100</v>
+        <v>2846100</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>C4607</t>
+          <t>C4609</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>MAQUILLAJE SIRENA C4607</t>
+          <t>MAQUILLAJE UNICORNIO C4609</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -11119,7 +11119,7 @@
         </is>
       </c>
       <c r="J241" t="n">
-        <v>159</v>
+        <v>79</v>
       </c>
       <c r="K241" t="n">
         <v>0</v>
@@ -11128,30 +11128,30 @@
         <v>0</v>
       </c>
       <c r="M241" t="n">
-        <v>159</v>
+        <v>79</v>
       </c>
       <c r="N241" t="n">
-        <v>10817</v>
+        <v>12489</v>
       </c>
       <c r="O241" t="n">
-        <v>1719903</v>
+        <v>986631</v>
       </c>
       <c r="P241" t="n">
-        <v>17900</v>
+        <v>20900</v>
       </c>
       <c r="Q241" t="n">
-        <v>2846100</v>
+        <v>1651100</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>C4609</t>
+          <t>C4612</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>MAQUILLAJE UNICORNIO C4609</t>
+          <t>CARRUAJE MUÑECA C4612</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -11165,7 +11165,7 @@
         </is>
       </c>
       <c r="J242" t="n">
-        <v>79</v>
+        <v>166</v>
       </c>
       <c r="K242" t="n">
         <v>0</v>
@@ -11174,30 +11174,30 @@
         <v>0</v>
       </c>
       <c r="M242" t="n">
-        <v>79</v>
+        <v>166</v>
       </c>
       <c r="N242" t="n">
-        <v>12489</v>
+        <v>21762</v>
       </c>
       <c r="O242" t="n">
-        <v>986631</v>
+        <v>3612492</v>
       </c>
       <c r="P242" t="n">
-        <v>20900</v>
+        <v>35900</v>
       </c>
       <c r="Q242" t="n">
-        <v>1651100</v>
+        <v>5959400</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>C4612</t>
+          <t>C4613</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>CARRUAJE MUÑECA C4612</t>
+          <t>DIDACTICOS ARMABLES STD C4613</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -11211,7 +11211,7 @@
         </is>
       </c>
       <c r="J243" t="n">
-        <v>166</v>
+        <v>934</v>
       </c>
       <c r="K243" t="n">
         <v>0</v>
@@ -11220,30 +11220,30 @@
         <v>0</v>
       </c>
       <c r="M243" t="n">
-        <v>166</v>
+        <v>934</v>
       </c>
       <c r="N243" t="n">
-        <v>21762</v>
+        <v>3821</v>
       </c>
       <c r="O243" t="n">
-        <v>3612492</v>
+        <v>3568814</v>
       </c>
       <c r="P243" t="n">
-        <v>35900</v>
+        <v>5900</v>
       </c>
       <c r="Q243" t="n">
-        <v>5959400</v>
+        <v>5510600</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>C4613</t>
+          <t>C4614</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>DIDACTICOS ARMABLES STD C4613</t>
+          <t>CASTILLO NIÑA C4614</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -11257,7 +11257,7 @@
         </is>
       </c>
       <c r="J244" t="n">
-        <v>934</v>
+        <v>144</v>
       </c>
       <c r="K244" t="n">
         <v>0</v>
@@ -11266,30 +11266,30 @@
         <v>0</v>
       </c>
       <c r="M244" t="n">
-        <v>934</v>
+        <v>144</v>
       </c>
       <c r="N244" t="n">
-        <v>3821</v>
+        <v>15472</v>
       </c>
       <c r="O244" t="n">
-        <v>3568814</v>
+        <v>2227968</v>
       </c>
       <c r="P244" t="n">
-        <v>5900</v>
+        <v>25900</v>
       </c>
       <c r="Q244" t="n">
-        <v>5510600</v>
+        <v>3729600</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>C4614</t>
+          <t>C4616</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>CASTILLO NIÑA C4614</t>
+          <t>CARRO TRANSFORME AMARILLO RECARGABLE C4616</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -11303,7 +11303,7 @@
         </is>
       </c>
       <c r="J245" t="n">
-        <v>144</v>
+        <v>8</v>
       </c>
       <c r="K245" t="n">
         <v>0</v>
@@ -11312,30 +11312,30 @@
         <v>0</v>
       </c>
       <c r="M245" t="n">
-        <v>144</v>
+        <v>8</v>
       </c>
       <c r="N245" t="n">
-        <v>15472</v>
+        <v>48522</v>
       </c>
       <c r="O245" t="n">
-        <v>2227968</v>
+        <v>388176</v>
       </c>
       <c r="P245" t="n">
-        <v>25900</v>
+        <v>77900</v>
       </c>
       <c r="Q245" t="n">
-        <v>3729600</v>
+        <v>623200</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>C4616</t>
+          <t>C4622</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>CARRO TRANSFORME AMARILLO RECARGABLE C4616</t>
+          <t>CARRO COLECCION X8 C4622</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -11349,7 +11349,7 @@
         </is>
       </c>
       <c r="J246" t="n">
-        <v>8</v>
+        <v>240</v>
       </c>
       <c r="K246" t="n">
         <v>0</v>
@@ -11358,30 +11358,30 @@
         <v>0</v>
       </c>
       <c r="M246" t="n">
-        <v>8</v>
+        <v>240</v>
       </c>
       <c r="N246" t="n">
-        <v>48522</v>
+        <v>5476</v>
       </c>
       <c r="O246" t="n">
-        <v>388176</v>
+        <v>1314240</v>
       </c>
       <c r="P246" t="n">
-        <v>77900</v>
+        <v>8900</v>
       </c>
       <c r="Q246" t="n">
-        <v>623200</v>
+        <v>2136000</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>C4622</t>
+          <t>C4629</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>CARRO COLECCION X8 C4622</t>
+          <t>COMPUTADOR USB CABLE C4629</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -11395,7 +11395,7 @@
         </is>
       </c>
       <c r="J247" t="n">
-        <v>240</v>
+        <v>36</v>
       </c>
       <c r="K247" t="n">
         <v>0</v>
@@ -11404,30 +11404,30 @@
         <v>0</v>
       </c>
       <c r="M247" t="n">
-        <v>240</v>
+        <v>36</v>
       </c>
       <c r="N247" t="n">
-        <v>5476</v>
+        <v>64612</v>
       </c>
       <c r="O247" t="n">
-        <v>1314240</v>
+        <v>2326032</v>
       </c>
       <c r="P247" t="n">
-        <v>8900</v>
+        <v>103900</v>
       </c>
       <c r="Q247" t="n">
-        <v>2136000</v>
+        <v>3740400</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>C4629</t>
+          <t>C4630</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>COMPUTADOR USB CABLE C4629</t>
+          <t>COMPUTADOR USB INGLES/ESPAÑOL C4630</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -11441,7 +11441,7 @@
         </is>
       </c>
       <c r="J248" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="K248" t="n">
         <v>0</v>
@@ -11450,30 +11450,30 @@
         <v>0</v>
       </c>
       <c r="M248" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="N248" t="n">
-        <v>64612</v>
+        <v>38252</v>
       </c>
       <c r="O248" t="n">
-        <v>2326032</v>
+        <v>2142112</v>
       </c>
       <c r="P248" t="n">
-        <v>103900</v>
+        <v>61900</v>
       </c>
       <c r="Q248" t="n">
-        <v>3740400</v>
+        <v>3466400</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>C4630</t>
+          <t>C4631</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>COMPUTADOR USB INGLES/ESPAÑOL C4630</t>
+          <t>SQUISHY MOSTRICO STD C4631</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -11487,7 +11487,7 @@
         </is>
       </c>
       <c r="J249" t="n">
-        <v>56</v>
+        <v>864</v>
       </c>
       <c r="K249" t="n">
         <v>0</v>
@@ -11496,30 +11496,30 @@
         <v>0</v>
       </c>
       <c r="M249" t="n">
-        <v>56</v>
+        <v>864</v>
       </c>
       <c r="N249" t="n">
-        <v>38252</v>
+        <v>1516.0387272539</v>
       </c>
       <c r="O249" t="n">
-        <v>2142112</v>
+        <v>1309857.46034737</v>
       </c>
       <c r="P249" t="n">
-        <v>61900</v>
+        <v>2300</v>
       </c>
       <c r="Q249" t="n">
-        <v>3466400</v>
+        <v>1987200</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>C4631</t>
+          <t>C466-IO</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>SQUISHY MOSTRICO STD C4631</t>
+          <t>GLOBO FIGURAS TORNASOL Y MATE</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -11533,7 +11533,7 @@
         </is>
       </c>
       <c r="J250" t="n">
-        <v>864</v>
+        <v>1050</v>
       </c>
       <c r="K250" t="n">
         <v>0</v>
@@ -11542,30 +11542,30 @@
         <v>0</v>
       </c>
       <c r="M250" t="n">
-        <v>864</v>
+        <v>1050</v>
       </c>
       <c r="N250" t="n">
-        <v>1516.0387309278</v>
+        <v>356.78</v>
       </c>
       <c r="O250" t="n">
-        <v>1309857.463521619</v>
+        <v>374619</v>
       </c>
       <c r="P250" t="n">
-        <v>2300</v>
+        <v>300</v>
       </c>
       <c r="Q250" t="n">
-        <v>1987200</v>
+        <v>315000</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>C466-IO</t>
+          <t>C4728</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>GLOBO FIGURAS TORNASOL Y MATE</t>
+          <t>FLIOTADOR DONA DINOSAURIO #60 C4728</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -11579,7 +11579,7 @@
         </is>
       </c>
       <c r="J251" t="n">
-        <v>1050</v>
+        <v>550</v>
       </c>
       <c r="K251" t="n">
         <v>0</v>
@@ -11588,44 +11588,42 @@
         <v>0</v>
       </c>
       <c r="M251" t="n">
-        <v>1050</v>
+        <v>550</v>
       </c>
       <c r="N251" t="n">
-        <v>356.78</v>
+        <v>2454</v>
       </c>
       <c r="O251" t="n">
-        <v>374619</v>
+        <v>1349700</v>
       </c>
       <c r="P251" t="n">
-        <v>300</v>
+        <v>4200</v>
       </c>
       <c r="Q251" t="n">
-        <v>315000</v>
+        <v>2310000</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>C4728</t>
-        </is>
+          <t>C476</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>6932001041468</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>FLIOTADOR DONA DINOSAURIO #60 C4728</t>
-        </is>
-      </c>
-      <c r="E252" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>YENGA MADERA GRABDE</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J252" t="n">
-        <v>550</v>
+        <v>54</v>
       </c>
       <c r="K252" t="n">
         <v>0</v>
@@ -11634,42 +11632,44 @@
         <v>0</v>
       </c>
       <c r="M252" t="n">
-        <v>550</v>
+        <v>54</v>
       </c>
       <c r="N252" t="n">
-        <v>2454</v>
+        <v>5347.73</v>
       </c>
       <c r="O252" t="n">
-        <v>1349700</v>
+        <v>288777.42</v>
       </c>
       <c r="P252" t="n">
-        <v>4200</v>
+        <v>9500</v>
       </c>
       <c r="Q252" t="n">
-        <v>2310000</v>
+        <v>513000</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>C476</t>
-        </is>
-      </c>
-      <c r="B253" t="n">
-        <v>6932001041468</v>
+          <t>C4812</t>
+        </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>YENGA MADERA GRABDE</t>
+          <t>BURBUJERO DE ESPADA 44cm</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J253" t="n">
-        <v>54</v>
+        <v>4464</v>
       </c>
       <c r="K253" t="n">
         <v>0</v>
@@ -11678,30 +11678,30 @@
         <v>0</v>
       </c>
       <c r="M253" t="n">
-        <v>54</v>
+        <v>4464</v>
       </c>
       <c r="N253" t="n">
-        <v>5347.73</v>
+        <v>1801</v>
       </c>
       <c r="O253" t="n">
-        <v>288777.42</v>
+        <v>8039664</v>
       </c>
       <c r="P253" t="n">
-        <v>9500</v>
+        <v>2900</v>
       </c>
       <c r="Q253" t="n">
-        <v>513000</v>
+        <v>12945600</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>C4812</t>
+          <t>C494-IO</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>BURBUJERO DE ESPADA 44cm</t>
+          <t>GLOBO METALIZADO DULCES</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -11715,7 +11715,7 @@
         </is>
       </c>
       <c r="J254" t="n">
-        <v>4464</v>
+        <v>1352</v>
       </c>
       <c r="K254" t="n">
         <v>0</v>
@@ -11724,30 +11724,33 @@
         <v>0</v>
       </c>
       <c r="M254" t="n">
-        <v>4464</v>
+        <v>1352</v>
       </c>
       <c r="N254" t="n">
-        <v>1801</v>
+        <v>1200</v>
       </c>
       <c r="O254" t="n">
-        <v>8039664</v>
+        <v>1622400</v>
       </c>
       <c r="P254" t="n">
-        <v>2900</v>
+        <v>1500</v>
       </c>
       <c r="Q254" t="n">
-        <v>12945600</v>
+        <v>2028000</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>C494-IO</t>
-        </is>
+          <t>C4945</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>7700154271143</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>GLOBO METALIZADO DULCES</t>
+          <t>MUÑECA CON MASCOTA Y COCHE C4945</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -11761,7 +11764,7 @@
         </is>
       </c>
       <c r="J255" t="n">
-        <v>1352</v>
+        <v>402</v>
       </c>
       <c r="K255" t="n">
         <v>0</v>
@@ -11770,25 +11773,25 @@
         <v>0</v>
       </c>
       <c r="M255" t="n">
-        <v>1352</v>
+        <v>402</v>
       </c>
       <c r="N255" t="n">
-        <v>1200</v>
+        <v>11690</v>
       </c>
       <c r="O255" t="n">
-        <v>1622400</v>
+        <v>4699380</v>
       </c>
       <c r="P255" t="n">
-        <v>1500</v>
+        <v>18900</v>
       </c>
       <c r="Q255" t="n">
-        <v>2028000</v>
+        <v>7597800</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>C4945</t>
+          <t>C4946</t>
         </is>
       </c>
       <c r="B256" t="n">
@@ -11796,7 +11799,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>MUÑECA CON MASCOTA Y COCHE C4945</t>
+          <t>MUÑECA CON ODONTOLOGIA C4946</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -11810,7 +11813,7 @@
         </is>
       </c>
       <c r="J256" t="n">
-        <v>402</v>
+        <v>348</v>
       </c>
       <c r="K256" t="n">
         <v>0</v>
@@ -11819,25 +11822,25 @@
         <v>0</v>
       </c>
       <c r="M256" t="n">
-        <v>402</v>
+        <v>348</v>
       </c>
       <c r="N256" t="n">
-        <v>11690</v>
+        <v>13518</v>
       </c>
       <c r="O256" t="n">
-        <v>4699380</v>
+        <v>4704264</v>
       </c>
       <c r="P256" t="n">
-        <v>18900</v>
+        <v>21900</v>
       </c>
       <c r="Q256" t="n">
-        <v>7597800</v>
+        <v>7621200</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>C4946</t>
+          <t>C4947</t>
         </is>
       </c>
       <c r="B257" t="n">
@@ -11845,7 +11848,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>MUÑECA CON ODONTOLOGIA C4946</t>
+          <t>MUÑECA CON MASCOTAS   C4947</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -11859,7 +11862,7 @@
         </is>
       </c>
       <c r="J257" t="n">
-        <v>348</v>
+        <v>396</v>
       </c>
       <c r="K257" t="n">
         <v>0</v>
@@ -11868,25 +11871,25 @@
         <v>0</v>
       </c>
       <c r="M257" t="n">
-        <v>348</v>
+        <v>396</v>
       </c>
       <c r="N257" t="n">
-        <v>13518</v>
+        <v>9736</v>
       </c>
       <c r="O257" t="n">
-        <v>4704264</v>
+        <v>3855456</v>
       </c>
       <c r="P257" t="n">
-        <v>21900</v>
+        <v>15900</v>
       </c>
       <c r="Q257" t="n">
-        <v>7621200</v>
+        <v>6296400</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>C4947</t>
+          <t>C4958</t>
         </is>
       </c>
       <c r="B258" t="n">
@@ -11894,7 +11897,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>MUÑECA CON MASCOTAS   C4947</t>
+          <t>MUÑECA PATINADORA CONTROL REMOTO</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -11908,7 +11911,7 @@
         </is>
       </c>
       <c r="J258" t="n">
-        <v>396</v>
+        <v>24</v>
       </c>
       <c r="K258" t="n">
         <v>0</v>
@@ -11917,25 +11920,25 @@
         <v>0</v>
       </c>
       <c r="M258" t="n">
-        <v>396</v>
+        <v>24</v>
       </c>
       <c r="N258" t="n">
-        <v>9736</v>
+        <v>44470</v>
       </c>
       <c r="O258" t="n">
-        <v>3855456</v>
+        <v>1067280</v>
       </c>
       <c r="P258" t="n">
-        <v>15900</v>
+        <v>71900</v>
       </c>
       <c r="Q258" t="n">
-        <v>6296400</v>
+        <v>1725600</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>C4958</t>
+          <t>C4959</t>
         </is>
       </c>
       <c r="B259" t="n">
@@ -11943,7 +11946,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>MUÑECA PATINADORA CONTROL REMOTO</t>
+          <t>MUÑECA POP ACCESORIOS C4959</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -11957,7 +11960,7 @@
         </is>
       </c>
       <c r="J259" t="n">
-        <v>24</v>
+        <v>634</v>
       </c>
       <c r="K259" t="n">
         <v>0</v>
@@ -11966,47 +11969,42 @@
         <v>0</v>
       </c>
       <c r="M259" t="n">
-        <v>24</v>
+        <v>634</v>
       </c>
       <c r="N259" t="n">
-        <v>44470</v>
+        <v>5215</v>
       </c>
       <c r="O259" t="n">
-        <v>1067280</v>
+        <v>3306310</v>
       </c>
       <c r="P259" t="n">
-        <v>71900</v>
+        <v>8900</v>
       </c>
       <c r="Q259" t="n">
-        <v>1725600</v>
+        <v>5642600</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>C4959</t>
+          <t>C502</t>
         </is>
       </c>
       <c r="B260" t="n">
-        <v>7700154271143</v>
+        <v>6952216485215</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>MUÑECA POP ACCESORIOS C4959</t>
-        </is>
-      </c>
-      <c r="E260" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>C502 MUNECA NANCY GRANDE</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J260" t="n">
-        <v>634</v>
+        <v>55</v>
       </c>
       <c r="K260" t="n">
         <v>0</v>
@@ -12015,42 +12013,47 @@
         <v>0</v>
       </c>
       <c r="M260" t="n">
-        <v>634</v>
+        <v>55</v>
       </c>
       <c r="N260" t="n">
-        <v>5215</v>
+        <v>15423.36</v>
       </c>
       <c r="O260" t="n">
-        <v>3306310</v>
+        <v>848284.8</v>
       </c>
       <c r="P260" t="n">
-        <v>8900</v>
+        <v>24900</v>
       </c>
       <c r="Q260" t="n">
-        <v>5642600</v>
+        <v>1369500</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>C502</t>
+          <t>C5030</t>
         </is>
       </c>
       <c r="B261" t="n">
-        <v>6952216485215</v>
+        <v>6999899236062</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>C502 MUNECA NANCY GRANDE</t>
+          <t>INFLABLE DONA LLANTA C5030</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>INFLABLES</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J261" t="n">
-        <v>55</v>
+        <v>121</v>
       </c>
       <c r="K261" t="n">
         <v>0</v>
@@ -12059,33 +12062,33 @@
         <v>0</v>
       </c>
       <c r="M261" t="n">
-        <v>55</v>
+        <v>121</v>
       </c>
       <c r="N261" t="n">
-        <v>15423.36</v>
+        <v>2857.22</v>
       </c>
       <c r="O261" t="n">
-        <v>848284.8</v>
+        <v>345723.62</v>
       </c>
       <c r="P261" t="n">
-        <v>24900</v>
+        <v>4900</v>
       </c>
       <c r="Q261" t="n">
-        <v>1369500</v>
+        <v>592900</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>C5030</t>
+          <t>C5032</t>
         </is>
       </c>
       <c r="B262" t="n">
-        <v>6999899236062</v>
+        <v>6999899236154</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>INFLABLE DONA LLANTA C5030</t>
+          <t>INFLABLE TECHITO PIECITOS  FIGURAS STD C5032</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -12099,7 +12102,7 @@
         </is>
       </c>
       <c r="J262" t="n">
-        <v>121</v>
+        <v>534</v>
       </c>
       <c r="K262" t="n">
         <v>0</v>
@@ -12108,47 +12111,42 @@
         <v>0</v>
       </c>
       <c r="M262" t="n">
-        <v>121</v>
+        <v>534</v>
       </c>
       <c r="N262" t="n">
-        <v>2857.22</v>
+        <v>8945.379999999999</v>
       </c>
       <c r="O262" t="n">
-        <v>345723.62</v>
+        <v>4776832.92</v>
       </c>
       <c r="P262" t="n">
-        <v>4900</v>
+        <v>14900</v>
       </c>
       <c r="Q262" t="n">
-        <v>592900</v>
+        <v>7956600</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>C5032</t>
+          <t>C506</t>
         </is>
       </c>
       <c r="B263" t="n">
-        <v>6999899236154</v>
+        <v>6952365180054</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>INFLABLE TECHITO PIECITOS  FIGURAS STD C5032</t>
-        </is>
-      </c>
-      <c r="E263" t="inlineStr">
-        <is>
-          <t>INFLABLES</t>
+          <t>GLOBO BURBUJA 30</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J263" t="n">
-        <v>534</v>
+        <v>3650</v>
       </c>
       <c r="K263" t="n">
         <v>0</v>
@@ -12157,42 +12155,44 @@
         <v>0</v>
       </c>
       <c r="M263" t="n">
-        <v>534</v>
+        <v>3650</v>
       </c>
       <c r="N263" t="n">
-        <v>8945.379999999999</v>
+        <v>675.2255375485</v>
       </c>
       <c r="O263" t="n">
-        <v>4776832.92</v>
+        <v>2464573.212052025</v>
       </c>
       <c r="P263" t="n">
-        <v>14900</v>
+        <v>1300</v>
       </c>
       <c r="Q263" t="n">
-        <v>7956600</v>
+        <v>4745000</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>C506</t>
-        </is>
-      </c>
-      <c r="B264" t="n">
-        <v>6952365180054</v>
+          <t>C510-IO</t>
+        </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>GLOBO BURBUJA 30</t>
+          <t>GLOBO BURBUJA METALIZADO</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>GLOBOS</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J264" t="n">
-        <v>3650</v>
+        <v>3896</v>
       </c>
       <c r="K264" t="n">
         <v>0</v>
@@ -12201,44 +12201,42 @@
         <v>0</v>
       </c>
       <c r="M264" t="n">
-        <v>3650</v>
+        <v>3896</v>
       </c>
       <c r="N264" t="n">
-        <v>675.2255375485</v>
+        <v>960</v>
       </c>
       <c r="O264" t="n">
-        <v>2464573.212052025</v>
+        <v>3740160</v>
       </c>
       <c r="P264" t="n">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="Q264" t="n">
-        <v>4745000</v>
+        <v>4675200</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>C510-IO</t>
-        </is>
+          <t>C515</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>6953626330010</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>GLOBO BURBUJA METALIZADO</t>
-        </is>
-      </c>
-      <c r="E265" t="inlineStr">
-        <is>
-          <t>GLOBOS</t>
+          <t>GLOBO FIGURAS BURBUJA</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J265" t="n">
-        <v>3896</v>
+        <v>3800</v>
       </c>
       <c r="K265" t="n">
         <v>0</v>
@@ -12247,42 +12245,44 @@
         <v>0</v>
       </c>
       <c r="M265" t="n">
-        <v>3896</v>
+        <v>3800</v>
       </c>
       <c r="N265" t="n">
-        <v>960</v>
+        <v>583.7204926325001</v>
       </c>
       <c r="O265" t="n">
-        <v>3740160</v>
+        <v>2218137.8720035</v>
       </c>
       <c r="P265" t="n">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="Q265" t="n">
-        <v>4675200</v>
+        <v>2280000</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>C515</t>
-        </is>
-      </c>
-      <c r="B266" t="n">
-        <v>6953626330010</v>
+          <t>C5214</t>
+        </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>GLOBO FIGURAS BURBUJA</t>
+          <t>CUBO C5214</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J266" t="n">
-        <v>3800</v>
+        <v>1440</v>
       </c>
       <c r="K266" t="n">
         <v>0</v>
@@ -12291,44 +12291,42 @@
         <v>0</v>
       </c>
       <c r="M266" t="n">
-        <v>3800</v>
+        <v>1440</v>
       </c>
       <c r="N266" t="n">
-        <v>583.7204926325001</v>
+        <v>1690.8700095238</v>
       </c>
       <c r="O266" t="n">
-        <v>2218137.8720035</v>
+        <v>2434852.813714272</v>
       </c>
       <c r="P266" t="n">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="Q266" t="n">
-        <v>2280000</v>
+        <v>4320000</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>C5214</t>
-        </is>
+          <t>C523</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>6957430180212</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>CUBO C5214</t>
-        </is>
-      </c>
-      <c r="E267" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
+          <t>GLOBO NUMERO 16PLATEADO Y DORADO</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J267" t="n">
-        <v>1440</v>
+        <v>2556</v>
       </c>
       <c r="K267" t="n">
         <v>0</v>
@@ -12337,33 +12335,33 @@
         <v>0</v>
       </c>
       <c r="M267" t="n">
-        <v>1440</v>
+        <v>2556</v>
       </c>
       <c r="N267" t="n">
-        <v>1690.8700094518</v>
+        <v>481.48790873239</v>
       </c>
       <c r="O267" t="n">
-        <v>2434852.813610592</v>
+        <v>1230683.094719989</v>
       </c>
       <c r="P267" t="n">
-        <v>3000</v>
+        <v>650</v>
       </c>
       <c r="Q267" t="n">
-        <v>4320000</v>
+        <v>1661400</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>C523</t>
+          <t>C524</t>
         </is>
       </c>
       <c r="B268" t="n">
-        <v>6957430180212</v>
+        <v>6957430180229</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>GLOBO NUMERO 16PLATEADO Y DORADO</t>
+          <t>GLOBO NUMERO 30 PLATEADO Y DORADO</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -12372,7 +12370,7 @@
         </is>
       </c>
       <c r="J268" t="n">
-        <v>2556</v>
+        <v>614</v>
       </c>
       <c r="K268" t="n">
         <v>0</v>
@@ -12381,42 +12379,47 @@
         <v>0</v>
       </c>
       <c r="M268" t="n">
-        <v>2556</v>
+        <v>614</v>
       </c>
       <c r="N268" t="n">
-        <v>481.48790873239</v>
+        <v>872.15418687873</v>
       </c>
       <c r="O268" t="n">
-        <v>1230683.094719989</v>
+        <v>535502.6707435403</v>
       </c>
       <c r="P268" t="n">
-        <v>650</v>
+        <v>1200</v>
       </c>
       <c r="Q268" t="n">
-        <v>1661400</v>
+        <v>736800</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>C524</t>
+          <t>C5246/C5247</t>
         </is>
       </c>
       <c r="B269" t="n">
-        <v>6957430180229</v>
+        <v>6900077483239</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>GLOBO NUMERO 30 PLATEADO Y DORADO</t>
+          <t>MARIONETA DE DEDO ANIMALES STDS C5246/C5247</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J269" t="n">
-        <v>614</v>
+        <v>130</v>
       </c>
       <c r="K269" t="n">
         <v>0</v>
@@ -12425,47 +12428,42 @@
         <v>0</v>
       </c>
       <c r="M269" t="n">
-        <v>614</v>
+        <v>130</v>
       </c>
       <c r="N269" t="n">
-        <v>872.15418687873</v>
+        <v>8702.219999999999</v>
       </c>
       <c r="O269" t="n">
-        <v>535502.6707435403</v>
+        <v>1131288.6</v>
       </c>
       <c r="P269" t="n">
-        <v>1200</v>
+        <v>8900</v>
       </c>
       <c r="Q269" t="n">
-        <v>736800</v>
+        <v>1157000</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>C5246/C5247</t>
+          <t>C525</t>
         </is>
       </c>
       <c r="B270" t="n">
-        <v>6900077483239</v>
+        <v>6957430180236</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>MARIONETA DE DEDO ANIMALES STDS C5246/C5247</t>
-        </is>
-      </c>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>DIDACTICO</t>
+          <t>GLOBO NUMERO 16 COLORES Y PUNTOS</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J270" t="n">
-        <v>130</v>
+        <v>1436</v>
       </c>
       <c r="K270" t="n">
         <v>0</v>
@@ -12474,33 +12472,33 @@
         <v>0</v>
       </c>
       <c r="M270" t="n">
-        <v>130</v>
+        <v>1436</v>
       </c>
       <c r="N270" t="n">
-        <v>8702.219999999999</v>
+        <v>345.55838583542</v>
       </c>
       <c r="O270" t="n">
-        <v>1131288.6</v>
+        <v>496221.8420596631</v>
       </c>
       <c r="P270" t="n">
-        <v>8900</v>
+        <v>600</v>
       </c>
       <c r="Q270" t="n">
-        <v>1157000</v>
+        <v>861600</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>C525</t>
+          <t>C526</t>
         </is>
       </c>
       <c r="B271" t="n">
-        <v>6957430180236</v>
+        <v>6957430180243</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>GLOBO NUMERO 16 COLORES Y PUNTOS</t>
+          <t>GLOBO NUMERO 30 COLORES Y PUNTOS</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -12509,7 +12507,7 @@
         </is>
       </c>
       <c r="J271" t="n">
-        <v>1436</v>
+        <v>11416</v>
       </c>
       <c r="K271" t="n">
         <v>0</v>
@@ -12518,42 +12516,47 @@
         <v>0</v>
       </c>
       <c r="M271" t="n">
-        <v>1436</v>
+        <v>11416</v>
       </c>
       <c r="N271" t="n">
-        <v>345.55838583542</v>
+        <v>711.33664496242</v>
       </c>
       <c r="O271" t="n">
-        <v>496221.8420596631</v>
+        <v>8120619.138890986</v>
       </c>
       <c r="P271" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="Q271" t="n">
-        <v>861600</v>
+        <v>10274400</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>C526</t>
+          <t>C527-IO</t>
         </is>
       </c>
       <c r="B272" t="n">
-        <v>6957430180243</v>
+        <v>6957430180526</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>GLOBO NUMERO 30 COLORES Y PUNTOS</t>
+          <t>GLOBO FELIZ CUMPLEAÑOS LISTON</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>GLOBOS</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J272" t="n">
-        <v>11416</v>
+        <v>1242</v>
       </c>
       <c r="K272" t="n">
         <v>0</v>
@@ -12562,38 +12565,35 @@
         <v>0</v>
       </c>
       <c r="M272" t="n">
-        <v>11416</v>
+        <v>1242</v>
       </c>
       <c r="N272" t="n">
-        <v>711.33664496242</v>
+        <v>815.0599999999999</v>
       </c>
       <c r="O272" t="n">
-        <v>8120619.138890986</v>
+        <v>1012304.52</v>
       </c>
       <c r="P272" t="n">
         <v>900</v>
       </c>
       <c r="Q272" t="n">
-        <v>10274400</v>
+        <v>1117800</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>C527-IO</t>
-        </is>
-      </c>
-      <c r="B273" t="n">
-        <v>6957430180526</v>
+          <t>C541</t>
+        </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>GLOBO FELIZ CUMPLEAÑOS LISTON</t>
+          <t>GLOBO LLAMA PQÑO</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>GLOBOS</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -12602,7 +12602,7 @@
         </is>
       </c>
       <c r="J273" t="n">
-        <v>1242</v>
+        <v>2150</v>
       </c>
       <c r="K273" t="n">
         <v>0</v>
@@ -12611,30 +12611,30 @@
         <v>0</v>
       </c>
       <c r="M273" t="n">
-        <v>1242</v>
+        <v>2150</v>
       </c>
       <c r="N273" t="n">
-        <v>815.0599999999999</v>
+        <v>800</v>
       </c>
       <c r="O273" t="n">
-        <v>1012304.52</v>
+        <v>1720000</v>
       </c>
       <c r="P273" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="Q273" t="n">
-        <v>1117800</v>
+        <v>2150000</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>C541</t>
+          <t>C575-IO</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>GLOBO LLAMA PQÑO</t>
+          <t>GLOBO UNICORNIO PQÑO</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -12648,7 +12648,7 @@
         </is>
       </c>
       <c r="J274" t="n">
-        <v>2150</v>
+        <v>1001</v>
       </c>
       <c r="K274" t="n">
         <v>0</v>
@@ -12657,35 +12657,38 @@
         <v>0</v>
       </c>
       <c r="M274" t="n">
-        <v>2150</v>
+        <v>1001</v>
       </c>
       <c r="N274" t="n">
-        <v>800</v>
+        <v>320</v>
       </c>
       <c r="O274" t="n">
-        <v>1720000</v>
+        <v>320320</v>
       </c>
       <c r="P274" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="Q274" t="n">
-        <v>2150000</v>
+        <v>400400</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>C575-IO</t>
-        </is>
+          <t>C596-IO</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>8596162180268</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>GLOBO UNICORNIO PQÑO</t>
+          <t>GLOBO TE AMO</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>GLOBOS</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -12694,7 +12697,7 @@
         </is>
       </c>
       <c r="J275" t="n">
-        <v>1001</v>
+        <v>1455</v>
       </c>
       <c r="K275" t="n">
         <v>0</v>
@@ -12703,33 +12706,33 @@
         <v>0</v>
       </c>
       <c r="M275" t="n">
-        <v>1001</v>
+        <v>1455</v>
       </c>
       <c r="N275" t="n">
-        <v>320</v>
+        <v>1044.54</v>
       </c>
       <c r="O275" t="n">
-        <v>320320</v>
+        <v>1519805.7</v>
       </c>
       <c r="P275" t="n">
-        <v>400</v>
+        <v>1200</v>
       </c>
       <c r="Q275" t="n">
-        <v>400400</v>
+        <v>1746000</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>C596-IO</t>
+          <t>C60-IO</t>
         </is>
       </c>
       <c r="B276" t="n">
-        <v>8596162180268</v>
+        <v>6524521011245</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>GLOBO TE AMO</t>
+          <t>GLOBO TIKTOK BOUQUET</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -12743,7 +12746,7 @@
         </is>
       </c>
       <c r="J276" t="n">
-        <v>1455</v>
+        <v>740</v>
       </c>
       <c r="K276" t="n">
         <v>0</v>
@@ -12752,38 +12755,35 @@
         <v>0</v>
       </c>
       <c r="M276" t="n">
-        <v>1455</v>
+        <v>740</v>
       </c>
       <c r="N276" t="n">
-        <v>1044.54</v>
+        <v>1989.05</v>
       </c>
       <c r="O276" t="n">
-        <v>1519805.7</v>
+        <v>1471897</v>
       </c>
       <c r="P276" t="n">
-        <v>1200</v>
+        <v>3000</v>
       </c>
       <c r="Q276" t="n">
-        <v>1746000</v>
+        <v>2220000</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>C60-IO</t>
-        </is>
-      </c>
-      <c r="B277" t="n">
-        <v>6524521011245</v>
+          <t>C6074</t>
+        </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>GLOBO TIKTOK BOUQUET</t>
+          <t>FIGURAS ALIMENTOS DECORATIVOS C6074</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>GLOBOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -12792,7 +12792,7 @@
         </is>
       </c>
       <c r="J277" t="n">
-        <v>740</v>
+        <v>25</v>
       </c>
       <c r="K277" t="n">
         <v>0</v>
@@ -12801,44 +12801,42 @@
         <v>0</v>
       </c>
       <c r="M277" t="n">
-        <v>740</v>
+        <v>25</v>
       </c>
       <c r="N277" t="n">
-        <v>1989.05</v>
+        <v>9447.25</v>
       </c>
       <c r="O277" t="n">
-        <v>1471897</v>
+        <v>236181.25</v>
       </c>
       <c r="P277" t="n">
-        <v>3000</v>
+        <v>9900</v>
       </c>
       <c r="Q277" t="n">
-        <v>2220000</v>
+        <v>247500</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>C6074</t>
-        </is>
+          <t>C629</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>7791638082188</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>FIGURAS ALIMENTOS DECORATIVOS C6074</t>
-        </is>
-      </c>
-      <c r="E278" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
+          <t>BURBUJERO PITO STD</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J278" t="n">
-        <v>25</v>
+        <v>15264</v>
       </c>
       <c r="K278" t="n">
         <v>0</v>
@@ -12847,42 +12845,47 @@
         <v>0</v>
       </c>
       <c r="M278" t="n">
-        <v>25</v>
+        <v>15264</v>
       </c>
       <c r="N278" t="n">
-        <v>9447.25</v>
+        <v>703.79469605084</v>
       </c>
       <c r="O278" t="n">
-        <v>236181.25</v>
+        <v>10742722.24052002</v>
       </c>
       <c r="P278" t="n">
-        <v>9900</v>
+        <v>900</v>
       </c>
       <c r="Q278" t="n">
-        <v>247500</v>
+        <v>13737600</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>C629</t>
+          <t>C6406</t>
         </is>
       </c>
       <c r="B279" t="n">
-        <v>7791638082188</v>
+        <v>6820212541115</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>BURBUJERO PITO STD</t>
+          <t>PAJAROS MUSICALES DECORATIVOS C6406</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J279" t="n">
-        <v>15264</v>
+        <v>52</v>
       </c>
       <c r="K279" t="n">
         <v>0</v>
@@ -12891,47 +12894,39 @@
         <v>0</v>
       </c>
       <c r="M279" t="n">
-        <v>15264</v>
+        <v>52</v>
       </c>
       <c r="N279" t="n">
-        <v>703.79470242023</v>
+        <v>14260.14</v>
       </c>
       <c r="O279" t="n">
-        <v>10742722.33774239</v>
+        <v>741527.28</v>
       </c>
       <c r="P279" t="n">
-        <v>900</v>
+        <v>15900</v>
       </c>
       <c r="Q279" t="n">
-        <v>13737600</v>
+        <v>826800</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>C6406</t>
-        </is>
-      </c>
-      <c r="B280" t="n">
-        <v>6820212541115</v>
+          <t>C642</t>
+        </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>PAJAROS MUSICALES DECORATIVOS C6406</t>
-        </is>
-      </c>
-      <c r="E280" t="inlineStr">
-        <is>
-          <t>MICELANEOS</t>
+          <t>LANZADOR AGUA</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J280" t="n">
-        <v>52</v>
+        <v>599</v>
       </c>
       <c r="K280" t="n">
         <v>0</v>
@@ -12940,39 +12935,44 @@
         <v>0</v>
       </c>
       <c r="M280" t="n">
-        <v>52</v>
+        <v>599</v>
       </c>
       <c r="N280" t="n">
-        <v>14260.14</v>
+        <v>2529.19</v>
       </c>
       <c r="O280" t="n">
-        <v>741527.28</v>
+        <v>1514984.81</v>
       </c>
       <c r="P280" t="n">
-        <v>15900</v>
+        <v>5100</v>
       </c>
       <c r="Q280" t="n">
-        <v>826800</v>
+        <v>3054900</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>C642</t>
+          <t>C671-LJ</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>LANZADOR AGUA</t>
+          <t>GLOBO UNICORNIO MEDIANO</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J281" t="n">
-        <v>599</v>
+        <v>1397</v>
       </c>
       <c r="K281" t="n">
         <v>0</v>
@@ -12981,35 +12981,38 @@
         <v>0</v>
       </c>
       <c r="M281" t="n">
-        <v>599</v>
+        <v>1397</v>
       </c>
       <c r="N281" t="n">
-        <v>2529.19</v>
+        <v>400</v>
       </c>
       <c r="O281" t="n">
-        <v>1514984.81</v>
+        <v>558800</v>
       </c>
       <c r="P281" t="n">
-        <v>5100</v>
+        <v>500</v>
       </c>
       <c r="Q281" t="n">
-        <v>3054900</v>
+        <v>698500</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>C671-LJ</t>
-        </is>
+          <t>C7005</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>6874123039124</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>GLOBO UNICORNIO MEDIANO</t>
+          <t>MAQUINA DE COSER C7005</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -13018,7 +13021,7 @@
         </is>
       </c>
       <c r="J282" t="n">
-        <v>1397</v>
+        <v>208</v>
       </c>
       <c r="K282" t="n">
         <v>0</v>
@@ -13027,38 +13030,38 @@
         <v>0</v>
       </c>
       <c r="M282" t="n">
-        <v>1397</v>
+        <v>208</v>
       </c>
       <c r="N282" t="n">
-        <v>400</v>
+        <v>6078.9926048565</v>
       </c>
       <c r="O282" t="n">
-        <v>558800</v>
+        <v>1264430.461810152</v>
       </c>
       <c r="P282" t="n">
-        <v>500</v>
+        <v>18500</v>
       </c>
       <c r="Q282" t="n">
-        <v>698500</v>
+        <v>3848000</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>C7005</t>
+          <t>C7009</t>
         </is>
       </c>
       <c r="B283" t="n">
-        <v>6874123039124</v>
+        <v>2024250256831</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>MAQUINA DE COSER C7005</t>
+          <t>LANZADORA DE AGUA  TUBO CON HELICE C7009</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>LANZADORES</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -13067,7 +13070,7 @@
         </is>
       </c>
       <c r="J283" t="n">
-        <v>208</v>
+        <v>12</v>
       </c>
       <c r="K283" t="n">
         <v>0</v>
@@ -13076,33 +13079,33 @@
         <v>0</v>
       </c>
       <c r="M283" t="n">
-        <v>208</v>
+        <v>12</v>
       </c>
       <c r="N283" t="n">
-        <v>6078.9926048565</v>
+        <v>5899.18</v>
       </c>
       <c r="O283" t="n">
-        <v>1264430.461810152</v>
+        <v>70790.16</v>
       </c>
       <c r="P283" t="n">
-        <v>18500</v>
+        <v>12500</v>
       </c>
       <c r="Q283" t="n">
-        <v>3848000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>C7009</t>
+          <t>C7038</t>
         </is>
       </c>
       <c r="B284" t="n">
-        <v>2024250256831</v>
+        <v>5132595141631</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>LANZADORA DE AGUA  TUBO CON HELICE C7009</t>
+          <t>LANZADORA DE AGUA GLOBO C7038</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -13116,7 +13119,7 @@
         </is>
       </c>
       <c r="J284" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="K284" t="n">
         <v>0</v>
@@ -13125,38 +13128,38 @@
         <v>0</v>
       </c>
       <c r="M284" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="N284" t="n">
-        <v>5899.18</v>
+        <v>18423.71</v>
       </c>
       <c r="O284" t="n">
-        <v>70790.16</v>
+        <v>423745.33</v>
       </c>
       <c r="P284" t="n">
-        <v>12500</v>
+        <v>10000</v>
       </c>
       <c r="Q284" t="n">
-        <v>150000</v>
+        <v>230000</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>C7038</t>
+          <t>C7039</t>
         </is>
       </c>
       <c r="B285" t="n">
-        <v>5132595141631</v>
+        <v>5132594521182</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>LANZADORA DE AGUA GLOBO C7038</t>
+          <t>LANZADOR AGUA GLOBO DELFIN C7039/M90-4</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>LANZADORES</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -13165,7 +13168,7 @@
         </is>
       </c>
       <c r="J285" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K285" t="n">
         <v>0</v>
@@ -13174,38 +13177,38 @@
         <v>0</v>
       </c>
       <c r="M285" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="N285" t="n">
-        <v>18423.71</v>
+        <v>10985.78</v>
       </c>
       <c r="O285" t="n">
-        <v>423745.33</v>
+        <v>219715.6</v>
       </c>
       <c r="P285" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="Q285" t="n">
-        <v>230000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>C7039</t>
+          <t>C7040</t>
         </is>
       </c>
       <c r="B286" t="n">
-        <v>5132594521182</v>
+        <v>6920373004365</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>LANZADOR AGUA GLOBO DELFIN C7039/M90-4</t>
+          <t>GARAJE EXIBICION CON LUZ C7040</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -13214,7 +13217,7 @@
         </is>
       </c>
       <c r="J286" t="n">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="K286" t="n">
         <v>0</v>
@@ -13223,38 +13226,38 @@
         <v>0</v>
       </c>
       <c r="M286" t="n">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="N286" t="n">
-        <v>10985.78</v>
+        <v>23452.77</v>
       </c>
       <c r="O286" t="n">
-        <v>219715.6</v>
+        <v>1102280.19</v>
       </c>
       <c r="P286" t="n">
-        <v>15000</v>
+        <v>39900</v>
       </c>
       <c r="Q286" t="n">
-        <v>300000</v>
+        <v>1875300</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>C7040</t>
+          <t>C7042</t>
         </is>
       </c>
       <c r="B287" t="n">
-        <v>6920373004365</v>
+        <v>2024081616255</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>GARAJE EXIBICION CON LUZ C7040</t>
+          <t>CANCHA BASKETBALL WIN24 C7042</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -13263,7 +13266,7 @@
         </is>
       </c>
       <c r="J287" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="K287" t="n">
         <v>0</v>
@@ -13272,38 +13275,35 @@
         <v>0</v>
       </c>
       <c r="M287" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="N287" t="n">
-        <v>23452.77</v>
+        <v>9694.41</v>
       </c>
       <c r="O287" t="n">
-        <v>1102280.19</v>
+        <v>96944.10000000001</v>
       </c>
       <c r="P287" t="n">
-        <v>39900</v>
+        <v>32500</v>
       </c>
       <c r="Q287" t="n">
-        <v>1875300</v>
+        <v>325000</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>C7042</t>
-        </is>
-      </c>
-      <c r="B288" t="n">
-        <v>2024081616255</v>
+          <t>C7080-BC</t>
+        </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>CANCHA BASKETBALL WIN24 C7042</t>
+          <t>ROBOT TRANSFORME STD C7080-BC</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MUÑECOS</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -13312,7 +13312,7 @@
         </is>
       </c>
       <c r="J288" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="K288" t="n">
         <v>0</v>
@@ -13321,35 +13321,38 @@
         <v>0</v>
       </c>
       <c r="M288" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="N288" t="n">
-        <v>9694.41</v>
+        <v>10556.12</v>
       </c>
       <c r="O288" t="n">
-        <v>96944.10000000001</v>
+        <v>411688.6800000001</v>
       </c>
       <c r="P288" t="n">
-        <v>32500</v>
+        <v>32900</v>
       </c>
       <c r="Q288" t="n">
-        <v>325000</v>
+        <v>1283100</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>C7080-BC</t>
-        </is>
+          <t>C7081</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>6301582313156</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>ROBOT TRANSFORME STD C7080-BC</t>
+          <t>LANZADORA DARDOS DE PILA C7081</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>MUÑECOS</t>
+          <t>LANZADORES</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -13358,7 +13361,7 @@
         </is>
       </c>
       <c r="J289" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="K289" t="n">
         <v>0</v>
@@ -13367,47 +13370,42 @@
         <v>0</v>
       </c>
       <c r="M289" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="N289" t="n">
-        <v>10556.12</v>
+        <v>22470.62</v>
       </c>
       <c r="O289" t="n">
-        <v>411688.6800000001</v>
+        <v>471883.02</v>
       </c>
       <c r="P289" t="n">
-        <v>32900</v>
+        <v>41900</v>
       </c>
       <c r="Q289" t="n">
-        <v>1283100</v>
+        <v>879900</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>C7081</t>
+          <t>C71</t>
         </is>
       </c>
       <c r="B290" t="n">
-        <v>6301582313156</v>
+        <v>5899989622205</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>LANZADORA DARDOS DE PILA C7081</t>
-        </is>
-      </c>
-      <c r="E290" t="inlineStr">
-        <is>
-          <t>LANZADORES</t>
+          <t>C71 INFLABLE PONY ROSADO-AZUL</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J290" t="n">
-        <v>21</v>
+        <v>392</v>
       </c>
       <c r="K290" t="n">
         <v>0</v>
@@ -13416,42 +13414,44 @@
         <v>0</v>
       </c>
       <c r="M290" t="n">
-        <v>21</v>
+        <v>392</v>
       </c>
       <c r="N290" t="n">
-        <v>22470.62</v>
+        <v>1669.6</v>
       </c>
       <c r="O290" t="n">
-        <v>471883.02</v>
+        <v>654483.2</v>
       </c>
       <c r="P290" t="n">
-        <v>41900</v>
+        <v>2900</v>
       </c>
       <c r="Q290" t="n">
-        <v>879900</v>
+        <v>1136800</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>C71</t>
-        </is>
-      </c>
-      <c r="B291" t="n">
-        <v>5899989622205</v>
+          <t>C7117</t>
+        </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>C71 INFLABLE PONY ROSADO-AZUL</t>
+          <t>BINGO LOTTO C7117</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>JUEGOS DE MESA</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J291" t="n">
-        <v>392</v>
+        <v>17</v>
       </c>
       <c r="K291" t="n">
         <v>0</v>
@@ -13460,35 +13460,35 @@
         <v>0</v>
       </c>
       <c r="M291" t="n">
-        <v>392</v>
+        <v>17</v>
       </c>
       <c r="N291" t="n">
-        <v>1669.6</v>
+        <v>5798.41</v>
       </c>
       <c r="O291" t="n">
-        <v>654483.2</v>
+        <v>98572.97</v>
       </c>
       <c r="P291" t="n">
-        <v>2900</v>
+        <v>14900</v>
       </c>
       <c r="Q291" t="n">
-        <v>1136800</v>
+        <v>253300</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>C7117</t>
+          <t>C7124</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>BINGO LOTTO C7117</t>
+          <t>TRAILER TRANFORME XQ05 C7124</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>JUEGOS DE MESA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -13497,7 +13497,7 @@
         </is>
       </c>
       <c r="J292" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K292" t="n">
         <v>0</v>
@@ -13506,35 +13506,35 @@
         <v>0</v>
       </c>
       <c r="M292" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="N292" t="n">
-        <v>5798.41</v>
+        <v>19587.53</v>
       </c>
       <c r="O292" t="n">
-        <v>115968.2</v>
+        <v>783501.2</v>
       </c>
       <c r="P292" t="n">
-        <v>14900</v>
+        <v>65000</v>
       </c>
       <c r="Q292" t="n">
-        <v>298000</v>
+        <v>2600000</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>C7124</t>
+          <t>C7132</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>TRAILER TRANFORME XQ05 C7124</t>
+          <t>SET PULSERAS Y CAUCHOS C7132</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -13543,7 +13543,7 @@
         </is>
       </c>
       <c r="J293" t="n">
-        <v>40</v>
+        <v>144</v>
       </c>
       <c r="K293" t="n">
         <v>0</v>
@@ -13552,30 +13552,33 @@
         <v>0</v>
       </c>
       <c r="M293" t="n">
-        <v>40</v>
+        <v>144</v>
       </c>
       <c r="N293" t="n">
-        <v>19587.53</v>
+        <v>3100.87</v>
       </c>
       <c r="O293" t="n">
-        <v>783501.2</v>
+        <v>446525.28</v>
       </c>
       <c r="P293" t="n">
-        <v>65000</v>
+        <v>9900</v>
       </c>
       <c r="Q293" t="n">
-        <v>2600000</v>
+        <v>1425600</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>C7132</t>
-        </is>
+          <t>C7147-A</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>6912209205022</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>SET PULSERAS Y CAUCHOS C7132</t>
+          <t>ANIMAL DINOSAURIO TRICERATOPS CONLUZ C7147-A</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -13589,7 +13592,7 @@
         </is>
       </c>
       <c r="J294" t="n">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="K294" t="n">
         <v>0</v>
@@ -13598,33 +13601,33 @@
         <v>0</v>
       </c>
       <c r="M294" t="n">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="N294" t="n">
-        <v>3100.87</v>
+        <v>10348.08</v>
       </c>
       <c r="O294" t="n">
-        <v>446525.28</v>
+        <v>413923.2</v>
       </c>
       <c r="P294" t="n">
-        <v>9900</v>
+        <v>16900</v>
       </c>
       <c r="Q294" t="n">
-        <v>1425600</v>
+        <v>676000</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>C7147-A</t>
+          <t>C7213</t>
         </is>
       </c>
       <c r="B295" t="n">
-        <v>6912209205022</v>
+        <v>6987540143012</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>ANIMAL DINOSAURIO TRICERATOPS CONLUZ C7147-A</t>
+          <t>PESCADO CON LUZ Y SONIDO C7213</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -13638,7 +13641,7 @@
         </is>
       </c>
       <c r="J295" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="K295" t="n">
         <v>0</v>
@@ -13647,33 +13650,33 @@
         <v>0</v>
       </c>
       <c r="M295" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="N295" t="n">
-        <v>10348.08</v>
+        <v>9746.8802061856</v>
       </c>
       <c r="O295" t="n">
-        <v>413923.2</v>
+        <v>467850.2498969088</v>
       </c>
       <c r="P295" t="n">
-        <v>16900</v>
+        <v>18500</v>
       </c>
       <c r="Q295" t="n">
-        <v>676000</v>
+        <v>888000</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>C7213</t>
+          <t>C7221</t>
         </is>
       </c>
       <c r="B296" t="n">
-        <v>6987540143012</v>
+        <v>7453100037446</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>PESCADO CON LUZ Y SONIDO C7213</t>
+          <t>RELOJ CON FICHAS ARMABLES  C7221</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -13687,7 +13690,7 @@
         </is>
       </c>
       <c r="J296" t="n">
-        <v>48</v>
+        <v>347</v>
       </c>
       <c r="K296" t="n">
         <v>0</v>
@@ -13696,33 +13699,33 @@
         <v>0</v>
       </c>
       <c r="M296" t="n">
-        <v>48</v>
+        <v>347</v>
       </c>
       <c r="N296" t="n">
-        <v>9746.8802061856</v>
+        <v>2672.89</v>
       </c>
       <c r="O296" t="n">
-        <v>467850.2498969088</v>
+        <v>927492.83</v>
       </c>
       <c r="P296" t="n">
-        <v>18500</v>
+        <v>10200</v>
       </c>
       <c r="Q296" t="n">
-        <v>888000</v>
+        <v>3539400</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>C7221</t>
+          <t>C7222</t>
         </is>
       </c>
       <c r="B297" t="n">
-        <v>7453100037446</v>
+        <v>7453100037453</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>RELOJ CON FICHAS ARMABLES  C7221</t>
+          <t>RELOJ DIDACTICO CARACOL C7222</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -13736,7 +13739,7 @@
         </is>
       </c>
       <c r="J297" t="n">
-        <v>347</v>
+        <v>230</v>
       </c>
       <c r="K297" t="n">
         <v>0</v>
@@ -13745,38 +13748,38 @@
         <v>0</v>
       </c>
       <c r="M297" t="n">
-        <v>347</v>
+        <v>230</v>
       </c>
       <c r="N297" t="n">
-        <v>2672.89</v>
+        <v>4795.69</v>
       </c>
       <c r="O297" t="n">
-        <v>927492.83</v>
+        <v>1103008.7</v>
       </c>
       <c r="P297" t="n">
         <v>10200</v>
       </c>
       <c r="Q297" t="n">
-        <v>3539400</v>
+        <v>2346000</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>C7222</t>
+          <t>C7294</t>
         </is>
       </c>
       <c r="B298" t="n">
-        <v>7453100037453</v>
+        <v>6895675680022</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>RELOJ DIDACTICO CARACOL C7222</t>
+          <t>JUEGO DEPORTIVO HOCHEY C7294</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -13785,7 +13788,7 @@
         </is>
       </c>
       <c r="J298" t="n">
-        <v>230</v>
+        <v>60</v>
       </c>
       <c r="K298" t="n">
         <v>0</v>
@@ -13794,38 +13797,38 @@
         <v>0</v>
       </c>
       <c r="M298" t="n">
-        <v>230</v>
+        <v>60</v>
       </c>
       <c r="N298" t="n">
-        <v>4795.69</v>
+        <v>4337.31</v>
       </c>
       <c r="O298" t="n">
-        <v>1103008.7</v>
+        <v>260238.6</v>
       </c>
       <c r="P298" t="n">
-        <v>10200</v>
+        <v>12900</v>
       </c>
       <c r="Q298" t="n">
-        <v>2346000</v>
+        <v>774000</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>C7294</t>
+          <t>C7325</t>
         </is>
       </c>
       <c r="B299" t="n">
-        <v>6895675680022</v>
+        <v>6974555555022</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>JUEGO DEPORTIVO HOCHEY C7294</t>
+          <t>PISTA EN BLISTER C7325</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -13834,7 +13837,7 @@
         </is>
       </c>
       <c r="J299" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="K299" t="n">
         <v>0</v>
@@ -13843,38 +13846,35 @@
         <v>0</v>
       </c>
       <c r="M299" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="N299" t="n">
-        <v>4337.31</v>
+        <v>3067.0906185567</v>
       </c>
       <c r="O299" t="n">
-        <v>260238.6</v>
+        <v>138019.0778350515</v>
       </c>
       <c r="P299" t="n">
-        <v>12900</v>
+        <v>7200</v>
       </c>
       <c r="Q299" t="n">
-        <v>774000</v>
+        <v>324000</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>C7325</t>
-        </is>
-      </c>
-      <c r="B300" t="n">
-        <v>6974555555022</v>
+          <t>C736</t>
+        </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>PISTA EN BLISTER C7325</t>
+          <t>GLOBO CORAZON GDE MENSAJE</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -13883,7 +13883,7 @@
         </is>
       </c>
       <c r="J300" t="n">
-        <v>45</v>
+        <v>2700</v>
       </c>
       <c r="K300" t="n">
         <v>0</v>
@@ -13892,35 +13892,38 @@
         <v>0</v>
       </c>
       <c r="M300" t="n">
-        <v>45</v>
+        <v>2700</v>
       </c>
       <c r="N300" t="n">
-        <v>3067.0906164384</v>
+        <v>640</v>
       </c>
       <c r="O300" t="n">
-        <v>138019.077739728</v>
+        <v>1728000</v>
       </c>
       <c r="P300" t="n">
-        <v>7200</v>
+        <v>800</v>
       </c>
       <c r="Q300" t="n">
-        <v>324000</v>
+        <v>2160000</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>C736</t>
-        </is>
+          <t>C7365</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>6920240750050</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>GLOBO CORAZON GDE MENSAJE</t>
+          <t>DIDACTICO JIRAFA EN BOLSA C7365</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -13929,7 +13932,7 @@
         </is>
       </c>
       <c r="J301" t="n">
-        <v>2700</v>
+        <v>19</v>
       </c>
       <c r="K301" t="n">
         <v>0</v>
@@ -13938,33 +13941,33 @@
         <v>0</v>
       </c>
       <c r="M301" t="n">
-        <v>2700</v>
+        <v>19</v>
       </c>
       <c r="N301" t="n">
-        <v>640</v>
+        <v>4190.77</v>
       </c>
       <c r="O301" t="n">
-        <v>1728000</v>
+        <v>79624.63</v>
       </c>
       <c r="P301" t="n">
-        <v>800</v>
+        <v>5900</v>
       </c>
       <c r="Q301" t="n">
-        <v>2160000</v>
+        <v>112100</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>C7365</t>
+          <t>C7366</t>
         </is>
       </c>
       <c r="B302" t="n">
-        <v>6920240750050</v>
+        <v>6920240750098</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>DIDACTICO JIRAFA EN BOLSA C7365</t>
+          <t>TREN DIDACTICO EN BOLSA C7366</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -13978,7 +13981,7 @@
         </is>
       </c>
       <c r="J302" t="n">
-        <v>19</v>
+        <v>104</v>
       </c>
       <c r="K302" t="n">
         <v>0</v>
@@ -13987,33 +13990,33 @@
         <v>0</v>
       </c>
       <c r="M302" t="n">
-        <v>19</v>
+        <v>104</v>
       </c>
       <c r="N302" t="n">
-        <v>4190.77</v>
+        <v>3499.72</v>
       </c>
       <c r="O302" t="n">
-        <v>79624.63</v>
+        <v>363970.88</v>
       </c>
       <c r="P302" t="n">
-        <v>5900</v>
+        <v>6900</v>
       </c>
       <c r="Q302" t="n">
-        <v>112100</v>
+        <v>717600</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>C7366</t>
+          <t>C7368</t>
         </is>
       </c>
       <c r="B303" t="n">
-        <v>6920240750098</v>
+        <v>6920240750159</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>TREN DIDACTICO EN BOLSA C7366</t>
+          <t>MOTO DIDACTICA EN BOLSA C736</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -14027,7 +14030,7 @@
         </is>
       </c>
       <c r="J303" t="n">
-        <v>104</v>
+        <v>158</v>
       </c>
       <c r="K303" t="n">
         <v>0</v>
@@ -14036,38 +14039,35 @@
         <v>0</v>
       </c>
       <c r="M303" t="n">
-        <v>104</v>
+        <v>158</v>
       </c>
       <c r="N303" t="n">
-        <v>3499.72</v>
+        <v>4578.04</v>
       </c>
       <c r="O303" t="n">
-        <v>363970.88</v>
+        <v>723330.3199999999</v>
       </c>
       <c r="P303" t="n">
-        <v>6900</v>
+        <v>7500</v>
       </c>
       <c r="Q303" t="n">
-        <v>717600</v>
+        <v>1185000</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>C7368</t>
-        </is>
-      </c>
-      <c r="B304" t="n">
-        <v>6920240750159</v>
+          <t>C740-IO</t>
+        </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>MOTO DIDACTICA EN BOLSA C736</t>
+          <t>GLOBO UNICORNIO MED</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -14076,7 +14076,7 @@
         </is>
       </c>
       <c r="J304" t="n">
-        <v>158</v>
+        <v>1876</v>
       </c>
       <c r="K304" t="n">
         <v>0</v>
@@ -14085,35 +14085,38 @@
         <v>0</v>
       </c>
       <c r="M304" t="n">
-        <v>158</v>
+        <v>1876</v>
       </c>
       <c r="N304" t="n">
-        <v>4578.04</v>
+        <v>480</v>
       </c>
       <c r="O304" t="n">
-        <v>723330.3199999999</v>
+        <v>900480</v>
       </c>
       <c r="P304" t="n">
-        <v>7500</v>
+        <v>600</v>
       </c>
       <c r="Q304" t="n">
-        <v>1185000</v>
+        <v>1125600</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>C740-IO</t>
-        </is>
+          <t>C7413</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>6921202412870</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>GLOBO UNICORNIO MED</t>
+          <t>DIDACTICO TORRE DE AROS C7413</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -14122,7 +14125,7 @@
         </is>
       </c>
       <c r="J305" t="n">
-        <v>1876</v>
+        <v>120</v>
       </c>
       <c r="K305" t="n">
         <v>0</v>
@@ -14131,38 +14134,35 @@
         <v>0</v>
       </c>
       <c r="M305" t="n">
-        <v>1876</v>
+        <v>120</v>
       </c>
       <c r="N305" t="n">
-        <v>480</v>
+        <v>4159.0003007519</v>
       </c>
       <c r="O305" t="n">
-        <v>900480</v>
+        <v>499080.036090228</v>
       </c>
       <c r="P305" t="n">
-        <v>600</v>
+        <v>8900</v>
       </c>
       <c r="Q305" t="n">
-        <v>1125600</v>
+        <v>1068000</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>C7413</t>
-        </is>
-      </c>
-      <c r="B306" t="n">
-        <v>6921202412870</v>
+          <t>C744-IO</t>
+        </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>DIDACTICO TORRE DE AROS C7413</t>
+          <t>GLOBO FELIZ CUMPLEAÑOS COLORES Y PUNTOS</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>GLOBOS</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -14171,7 +14171,7 @@
         </is>
       </c>
       <c r="J306" t="n">
-        <v>120</v>
+        <v>478</v>
       </c>
       <c r="K306" t="n">
         <v>0</v>
@@ -14180,35 +14180,35 @@
         <v>0</v>
       </c>
       <c r="M306" t="n">
-        <v>120</v>
+        <v>478</v>
       </c>
       <c r="N306" t="n">
-        <v>4159.0003007519</v>
+        <v>1554.12</v>
       </c>
       <c r="O306" t="n">
-        <v>499080.036090228</v>
+        <v>742869.36</v>
       </c>
       <c r="P306" t="n">
-        <v>8900</v>
+        <v>1900</v>
       </c>
       <c r="Q306" t="n">
-        <v>1068000</v>
+        <v>908200</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>C744-IO</t>
+          <t>C7462</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>GLOBO FELIZ CUMPLEAÑOS COLORES Y PUNTOS</t>
+          <t>SET DE BELLEZA ACCESORIOS PARA EL CABELLO C7462</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>GLOBOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -14217,7 +14217,7 @@
         </is>
       </c>
       <c r="J307" t="n">
-        <v>478</v>
+        <v>11</v>
       </c>
       <c r="K307" t="n">
         <v>0</v>
@@ -14226,30 +14226,33 @@
         <v>0</v>
       </c>
       <c r="M307" t="n">
-        <v>478</v>
+        <v>11</v>
       </c>
       <c r="N307" t="n">
-        <v>1554.12</v>
+        <v>14751.820338983</v>
       </c>
       <c r="O307" t="n">
-        <v>742869.36</v>
+        <v>162270.023728813</v>
       </c>
       <c r="P307" t="n">
-        <v>1900</v>
+        <v>37100</v>
       </c>
       <c r="Q307" t="n">
-        <v>908200</v>
+        <v>408100</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>C7462</t>
-        </is>
+          <t>C7467</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>6920241023009</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>SET DE BELLEZA ACCESORIOS PARA EL CABELLO C7462</t>
+          <t>ARCO Y FLECHA PARA NIÑAS C7467</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -14263,7 +14266,7 @@
         </is>
       </c>
       <c r="J308" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K308" t="n">
         <v>0</v>
@@ -14272,38 +14275,38 @@
         <v>0</v>
       </c>
       <c r="M308" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="N308" t="n">
-        <v>14751.820338983</v>
+        <v>15347.45</v>
       </c>
       <c r="O308" t="n">
-        <v>162270.023728813</v>
+        <v>230211.75</v>
       </c>
       <c r="P308" t="n">
-        <v>37100</v>
+        <v>23900</v>
       </c>
       <c r="Q308" t="n">
-        <v>408100</v>
+        <v>358500</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>C7467</t>
+          <t>C7488</t>
         </is>
       </c>
       <c r="B309" t="n">
-        <v>6920241023009</v>
+        <v>6945158254520</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>ARCO Y FLECHA PARA NIÑAS C7467</t>
+          <t>SOPORTE CELULAR CON LUZ C7488</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -14312,7 +14315,7 @@
         </is>
       </c>
       <c r="J309" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="K309" t="n">
         <v>0</v>
@@ -14321,38 +14324,38 @@
         <v>0</v>
       </c>
       <c r="M309" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="N309" t="n">
-        <v>15347.45</v>
+        <v>8919.16</v>
       </c>
       <c r="O309" t="n">
-        <v>230211.75</v>
+        <v>258655.64</v>
       </c>
       <c r="P309" t="n">
-        <v>23900</v>
+        <v>10000</v>
       </c>
       <c r="Q309" t="n">
-        <v>358500</v>
+        <v>290000</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>C7488</t>
+          <t>C7513</t>
         </is>
       </c>
       <c r="B310" t="n">
-        <v>6945158254520</v>
+        <v>6905698382824</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>SOPORTE CELULAR CON LUZ C7488</t>
+          <t>SONAJERO BOLA LUZ GDE C7513</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -14361,7 +14364,7 @@
         </is>
       </c>
       <c r="J310" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="K310" t="n">
         <v>0</v>
@@ -14370,47 +14373,42 @@
         <v>0</v>
       </c>
       <c r="M310" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="N310" t="n">
-        <v>8919.16</v>
+        <v>1024.29</v>
       </c>
       <c r="O310" t="n">
-        <v>258655.64</v>
+        <v>1024.29</v>
       </c>
       <c r="P310" t="n">
-        <v>10000</v>
+        <v>2900</v>
       </c>
       <c r="Q310" t="n">
-        <v>290000</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>C7513</t>
+          <t>C752</t>
         </is>
       </c>
       <c r="B311" t="n">
-        <v>6905698382824</v>
+        <v>8596162180497</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>SONAJERO BOLA LUZ GDE C7513</t>
-        </is>
-      </c>
-      <c r="E311" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
+          <t>GLOBO UNICORNIO MED 4 PATAS</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J311" t="n">
-        <v>1</v>
+        <v>1398</v>
       </c>
       <c r="K311" t="n">
         <v>0</v>
@@ -14419,33 +14417,33 @@
         <v>0</v>
       </c>
       <c r="M311" t="n">
-        <v>1</v>
+        <v>1398</v>
       </c>
       <c r="N311" t="n">
-        <v>1024.29</v>
+        <v>1163.7447787403</v>
       </c>
       <c r="O311" t="n">
-        <v>1024.29</v>
+        <v>1626915.200678939</v>
       </c>
       <c r="P311" t="n">
-        <v>2900</v>
+        <v>1500</v>
       </c>
       <c r="Q311" t="n">
-        <v>2900</v>
+        <v>2097000</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>C752</t>
+          <t>C753</t>
         </is>
       </c>
       <c r="B312" t="n">
-        <v>8596162180497</v>
+        <v>8596162180503</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>GLOBO UNICORNIO MED 4 PATAS</t>
+          <t>GLOBO UNICORNIO GDE 4 PATAS</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -14454,7 +14452,7 @@
         </is>
       </c>
       <c r="J312" t="n">
-        <v>1398</v>
+        <v>277</v>
       </c>
       <c r="K312" t="n">
         <v>0</v>
@@ -14463,42 +14461,47 @@
         <v>0</v>
       </c>
       <c r="M312" t="n">
-        <v>1398</v>
+        <v>277</v>
       </c>
       <c r="N312" t="n">
-        <v>1163.7447787403</v>
+        <v>5113.4625508318</v>
       </c>
       <c r="O312" t="n">
-        <v>1626915.200678939</v>
+        <v>1416429.126580409</v>
       </c>
       <c r="P312" t="n">
-        <v>1500</v>
+        <v>7000</v>
       </c>
       <c r="Q312" t="n">
-        <v>2097000</v>
+        <v>1939000</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>C753</t>
+          <t>C7533</t>
         </is>
       </c>
       <c r="B313" t="n">
-        <v>8596162180503</v>
+        <v>6923669699979</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>GLOBO UNICORNIO GDE 4 PATAS</t>
+          <t>REPUESTO BIOGEL NEON C7533</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J313" t="n">
-        <v>277</v>
+        <v>12023</v>
       </c>
       <c r="K313" t="n">
         <v>0</v>
@@ -14507,33 +14510,33 @@
         <v>0</v>
       </c>
       <c r="M313" t="n">
-        <v>277</v>
+        <v>12023</v>
       </c>
       <c r="N313" t="n">
-        <v>5113.4625508318</v>
+        <v>509.69</v>
       </c>
       <c r="O313" t="n">
-        <v>1416429.126580409</v>
+        <v>6128002.87</v>
       </c>
       <c r="P313" t="n">
-        <v>7000</v>
+        <v>750</v>
       </c>
       <c r="Q313" t="n">
-        <v>1939000</v>
+        <v>9017250</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>C7533</t>
+          <t>C7534</t>
         </is>
       </c>
       <c r="B314" t="n">
-        <v>6923669699979</v>
+        <v>6951241752002</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>REPUESTO BIOGEL NEON C7533</t>
+          <t>GORRO PELUCHE LUZ C7534-A-B-C-D-E-F</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -14547,7 +14550,7 @@
         </is>
       </c>
       <c r="J314" t="n">
-        <v>12023</v>
+        <v>499</v>
       </c>
       <c r="K314" t="n">
         <v>0</v>
@@ -14556,38 +14559,35 @@
         <v>0</v>
       </c>
       <c r="M314" t="n">
-        <v>12023</v>
+        <v>499</v>
       </c>
       <c r="N314" t="n">
-        <v>509.69</v>
+        <v>7046.9398265771</v>
       </c>
       <c r="O314" t="n">
-        <v>6128002.87</v>
+        <v>3516422.973461973</v>
       </c>
       <c r="P314" t="n">
-        <v>750</v>
+        <v>9900</v>
       </c>
       <c r="Q314" t="n">
-        <v>9017250</v>
+        <v>4940100</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>C7534</t>
-        </is>
-      </c>
-      <c r="B315" t="n">
-        <v>6951241752002</v>
+          <t>C7535</t>
+        </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>GORRO PELUCHE LUZ C7534-A-B-C-D-E-F</t>
+          <t>CARRO METALICO X13 CON CAMION C7535</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -14596,7 +14596,7 @@
         </is>
       </c>
       <c r="J315" t="n">
-        <v>499</v>
+        <v>30</v>
       </c>
       <c r="K315" t="n">
         <v>0</v>
@@ -14605,35 +14605,35 @@
         <v>0</v>
       </c>
       <c r="M315" t="n">
-        <v>499</v>
+        <v>30</v>
       </c>
       <c r="N315" t="n">
-        <v>7046.9398265771</v>
+        <v>24338.47</v>
       </c>
       <c r="O315" t="n">
-        <v>3516422.973461973</v>
+        <v>730154.1000000001</v>
       </c>
       <c r="P315" t="n">
-        <v>9900</v>
+        <v>27900</v>
       </c>
       <c r="Q315" t="n">
-        <v>4940100</v>
+        <v>837000</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>C7535</t>
+          <t>C7560</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>CARRO METALICO X13 CON CAMION C7535</t>
+          <t>BARRA LUMINOSA 48CM C7560/211</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -14642,7 +14642,7 @@
         </is>
       </c>
       <c r="J316" t="n">
-        <v>30</v>
+        <v>188</v>
       </c>
       <c r="K316" t="n">
         <v>0</v>
@@ -14651,30 +14651,33 @@
         <v>0</v>
       </c>
       <c r="M316" t="n">
-        <v>30</v>
+        <v>188</v>
       </c>
       <c r="N316" t="n">
-        <v>24338.47</v>
+        <v>796.3099999999999</v>
       </c>
       <c r="O316" t="n">
-        <v>730154.1000000001</v>
+        <v>149706.28</v>
       </c>
       <c r="P316" t="n">
-        <v>27900</v>
+        <v>2500</v>
       </c>
       <c r="Q316" t="n">
-        <v>837000</v>
+        <v>470000</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>C7560</t>
-        </is>
+          <t>C7588</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>7588228020244</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>BARRA LUMINOSA 48CM C7560/211</t>
+          <t>SONAJERO LUZ PANDITA C7588</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -14688,7 +14691,7 @@
         </is>
       </c>
       <c r="J317" t="n">
-        <v>188</v>
+        <v>1429</v>
       </c>
       <c r="K317" t="n">
         <v>0</v>
@@ -14697,38 +14700,38 @@
         <v>0</v>
       </c>
       <c r="M317" t="n">
-        <v>188</v>
+        <v>1429</v>
       </c>
       <c r="N317" t="n">
-        <v>796.3099999999999</v>
+        <v>641.78</v>
       </c>
       <c r="O317" t="n">
-        <v>149706.28</v>
+        <v>917103.62</v>
       </c>
       <c r="P317" t="n">
         <v>2500</v>
       </c>
       <c r="Q317" t="n">
-        <v>470000</v>
+        <v>3572500</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>C7588</t>
+          <t>C7610</t>
         </is>
       </c>
       <c r="B318" t="n">
-        <v>7588228020244</v>
+        <v>6999899236093</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>SONAJERO LUZ PANDITA C7588</t>
+          <t>BOTE TIMON PISCINA 80X60 C7610</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>INFLABLES</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -14737,7 +14740,7 @@
         </is>
       </c>
       <c r="J318" t="n">
-        <v>1429</v>
+        <v>276</v>
       </c>
       <c r="K318" t="n">
         <v>0</v>
@@ -14746,38 +14749,38 @@
         <v>0</v>
       </c>
       <c r="M318" t="n">
-        <v>1429</v>
+        <v>276</v>
       </c>
       <c r="N318" t="n">
-        <v>641.78</v>
+        <v>7811.9</v>
       </c>
       <c r="O318" t="n">
-        <v>917103.62</v>
+        <v>2156084.4</v>
       </c>
       <c r="P318" t="n">
-        <v>2500</v>
+        <v>13900</v>
       </c>
       <c r="Q318" t="n">
-        <v>3572500</v>
+        <v>3836400</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>C7610</t>
+          <t>C7614-F</t>
         </is>
       </c>
       <c r="B319" t="n">
-        <v>6999899236093</v>
+        <v>6999899236130</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>BOTE TIMON PISCINA 80X60 C7610</t>
+          <t>FLOTADOR DONA FLAMINGO C7614-F</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>INFLABLES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -14786,7 +14789,7 @@
         </is>
       </c>
       <c r="J319" t="n">
-        <v>276</v>
+        <v>382</v>
       </c>
       <c r="K319" t="n">
         <v>0</v>
@@ -14795,47 +14798,42 @@
         <v>0</v>
       </c>
       <c r="M319" t="n">
-        <v>276</v>
+        <v>382</v>
       </c>
       <c r="N319" t="n">
-        <v>7811.9</v>
+        <v>3155</v>
       </c>
       <c r="O319" t="n">
-        <v>2156084.4</v>
+        <v>1205210</v>
       </c>
       <c r="P319" t="n">
-        <v>13900</v>
+        <v>5900</v>
       </c>
       <c r="Q319" t="n">
-        <v>3836400</v>
+        <v>2253800</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>C7614-F</t>
+          <t>C784</t>
         </is>
       </c>
       <c r="B320" t="n">
-        <v>6999899236130</v>
+        <v>8913992935507</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>FLOTADOR DONA FLAMINGO C7614-F</t>
-        </is>
-      </c>
-      <c r="E320" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>GLOBO MENSAJE CUADRADO</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J320" t="n">
-        <v>382</v>
+        <v>1450</v>
       </c>
       <c r="K320" t="n">
         <v>0</v>
@@ -14844,33 +14842,33 @@
         <v>0</v>
       </c>
       <c r="M320" t="n">
-        <v>382</v>
+        <v>1450</v>
       </c>
       <c r="N320" t="n">
-        <v>3155</v>
+        <v>704.89696969697</v>
       </c>
       <c r="O320" t="n">
-        <v>1205210</v>
+        <v>1022100.606060607</v>
       </c>
       <c r="P320" t="n">
-        <v>5900</v>
+        <v>900</v>
       </c>
       <c r="Q320" t="n">
-        <v>2253800</v>
+        <v>1305000</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>C784</t>
+          <t>C819</t>
         </is>
       </c>
       <c r="B321" t="n">
-        <v>8913992935507</v>
+        <v>2087202108190</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>GLOBO MENSAJE CUADRADO</t>
+          <t>TROMPO EMOJI</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -14879,7 +14877,7 @@
         </is>
       </c>
       <c r="J321" t="n">
-        <v>1450</v>
+        <v>468</v>
       </c>
       <c r="K321" t="n">
         <v>0</v>
@@ -14888,33 +14886,33 @@
         <v>0</v>
       </c>
       <c r="M321" t="n">
-        <v>1450</v>
+        <v>468</v>
       </c>
       <c r="N321" t="n">
-        <v>704.89696969697</v>
+        <v>6761.25</v>
       </c>
       <c r="O321" t="n">
-        <v>1022100.606060607</v>
+        <v>3164265</v>
       </c>
       <c r="P321" t="n">
-        <v>900</v>
+        <v>5200</v>
       </c>
       <c r="Q321" t="n">
-        <v>1305000</v>
+        <v>2433600</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>C819</t>
+          <t>C84</t>
         </is>
       </c>
       <c r="B322" t="n">
-        <v>2087202108190</v>
+        <v>2021010563031</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>TROMPO EMOJI</t>
+          <t>LANZADOR DE AGUA</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -14923,7 +14921,7 @@
         </is>
       </c>
       <c r="J322" t="n">
-        <v>468</v>
+        <v>188</v>
       </c>
       <c r="K322" t="n">
         <v>0</v>
@@ -14932,33 +14930,35 @@
         <v>0</v>
       </c>
       <c r="M322" t="n">
-        <v>468</v>
+        <v>188</v>
       </c>
       <c r="N322" t="n">
-        <v>6761.25</v>
+        <v>1008.8113941019</v>
       </c>
       <c r="O322" t="n">
-        <v>3164265</v>
+        <v>189656.5420911572</v>
       </c>
       <c r="P322" t="n">
-        <v>5200</v>
+        <v>1500</v>
       </c>
       <c r="Q322" t="n">
-        <v>2433600</v>
+        <v>282000</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>C84</t>
-        </is>
-      </c>
-      <c r="B323" t="n">
-        <v>2021010563031</v>
+          <t>C879</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>CG-2016-212</t>
+        </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>LANZADOR DE AGUA</t>
+          <t>VELA MARIPOSA</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -14967,7 +14967,7 @@
         </is>
       </c>
       <c r="J323" t="n">
-        <v>188</v>
+        <v>121</v>
       </c>
       <c r="K323" t="n">
         <v>0</v>
@@ -14976,44 +14976,49 @@
         <v>0</v>
       </c>
       <c r="M323" t="n">
-        <v>188</v>
+        <v>121</v>
       </c>
       <c r="N323" t="n">
-        <v>1008.8113941019</v>
+        <v>1520</v>
       </c>
       <c r="O323" t="n">
-        <v>189656.5420911572</v>
+        <v>183920</v>
       </c>
       <c r="P323" t="n">
-        <v>1500</v>
+        <v>1900</v>
       </c>
       <c r="Q323" t="n">
-        <v>282000</v>
+        <v>229900</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>C879</t>
+          <t>C880</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>CG-2016-212</t>
+          <t>cg2016213</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>VELA MARIPOSA</t>
+          <t>VELA FLOR</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>VELA</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J324" t="n">
-        <v>121</v>
+        <v>200</v>
       </c>
       <c r="K324" t="n">
         <v>0</v>
@@ -15022,49 +15027,39 @@
         <v>0</v>
       </c>
       <c r="M324" t="n">
-        <v>121</v>
+        <v>200</v>
       </c>
       <c r="N324" t="n">
         <v>1520</v>
       </c>
       <c r="O324" t="n">
-        <v>183920</v>
+        <v>304000</v>
       </c>
       <c r="P324" t="n">
         <v>1900</v>
       </c>
       <c r="Q324" t="n">
-        <v>229900</v>
+        <v>380000</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>C880</t>
-        </is>
-      </c>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>cg2016213</t>
+          <t>C888</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>VELA FLOR</t>
-        </is>
-      </c>
-      <c r="E325" t="inlineStr">
-        <is>
-          <t>VELA</t>
+          <t>PELOTA CHILLON PUYAS SIN LUZ</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J325" t="n">
-        <v>200</v>
+        <v>169</v>
       </c>
       <c r="K325" t="n">
         <v>0</v>
@@ -15073,39 +15068,44 @@
         <v>0</v>
       </c>
       <c r="M325" t="n">
-        <v>200</v>
+        <v>169</v>
       </c>
       <c r="N325" t="n">
-        <v>1520</v>
+        <v>1213.6821400778</v>
       </c>
       <c r="O325" t="n">
-        <v>304000</v>
+        <v>205112.2816731482</v>
       </c>
       <c r="P325" t="n">
-        <v>1900</v>
+        <v>1500</v>
       </c>
       <c r="Q325" t="n">
-        <v>380000</v>
+        <v>253500</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>C888</t>
+          <t>FG037</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>PELOTA CHILLON PUYAS SIN LUZ</t>
+          <t>SNORKEL 66046A</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J326" t="n">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="K326" t="n">
         <v>0</v>
@@ -15114,30 +15114,30 @@
         <v>0</v>
       </c>
       <c r="M326" t="n">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="N326" t="n">
-        <v>1213.6821400778</v>
+        <v>13493.858292683</v>
       </c>
       <c r="O326" t="n">
-        <v>205112.2816731482</v>
+        <v>2415400.634390257</v>
       </c>
       <c r="P326" t="n">
-        <v>1500</v>
+        <v>16900</v>
       </c>
       <c r="Q326" t="n">
-        <v>253500</v>
+        <v>3025100</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>FG037</t>
+          <t>FG039</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>SNORKEL 66046A</t>
+          <t>GAFA DE NATACION BLISTER 2404-2</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -15151,7 +15151,7 @@
         </is>
       </c>
       <c r="J327" t="n">
-        <v>179</v>
+        <v>347</v>
       </c>
       <c r="K327" t="n">
         <v>0</v>
@@ -15160,35 +15160,40 @@
         <v>0</v>
       </c>
       <c r="M327" t="n">
-        <v>179</v>
+        <v>347</v>
       </c>
       <c r="N327" t="n">
-        <v>13493.858292683</v>
+        <v>2644.9</v>
       </c>
       <c r="O327" t="n">
-        <v>2415400.634390257</v>
+        <v>917780.3</v>
       </c>
       <c r="P327" t="n">
-        <v>16900</v>
+        <v>3900</v>
       </c>
       <c r="Q327" t="n">
-        <v>3025100</v>
+        <v>1353300</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>FG039</t>
+          <t>MG16332</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>MG16332</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>GAFA DE NATACION BLISTER 2404-2</t>
+          <t>LANZADOR  ARCO Y FLECA CON LASER MG16332</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -15197,7 +15202,7 @@
         </is>
       </c>
       <c r="J328" t="n">
-        <v>347</v>
+        <v>4</v>
       </c>
       <c r="K328" t="n">
         <v>0</v>
@@ -15206,35 +15211,30 @@
         <v>0</v>
       </c>
       <c r="M328" t="n">
-        <v>347</v>
+        <v>4</v>
       </c>
       <c r="N328" t="n">
-        <v>2644.9</v>
+        <v>8439.969999999999</v>
       </c>
       <c r="O328" t="n">
-        <v>917780.3</v>
+        <v>33759.88</v>
       </c>
       <c r="P328" t="n">
-        <v>3900</v>
+        <v>29500</v>
       </c>
       <c r="Q328" t="n">
-        <v>1353300</v>
+        <v>118000</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>MG16332</t>
-        </is>
-      </c>
-      <c r="B329" t="inlineStr">
-        <is>
-          <t>MG16332</t>
+          <t>MG20430</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>LANZADOR  ARCO Y FLECA CON LASER MG16332</t>
+          <t>SET PLASTILINA CON MOLDES BARBERIA MALETA MG20430</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -15248,7 +15248,7 @@
         </is>
       </c>
       <c r="J329" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="K329" t="n">
         <v>0</v>
@@ -15257,35 +15257,35 @@
         <v>0</v>
       </c>
       <c r="M329" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="N329" t="n">
-        <v>8439.969999999999</v>
+        <v>12189.831111111</v>
       </c>
       <c r="O329" t="n">
-        <v>33759.88</v>
+        <v>219416.959999998</v>
       </c>
       <c r="P329" t="n">
-        <v>29500</v>
+        <v>30900</v>
       </c>
       <c r="Q329" t="n">
-        <v>118000</v>
+        <v>556200</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>MG20430</t>
+          <t>MG40210</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>SET PLASTILINA CON MOLDES BARBERIA MALETA MG20430</t>
+          <t>SONAJERO OSO MG40210</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -15294,7 +15294,7 @@
         </is>
       </c>
       <c r="J330" t="n">
-        <v>18</v>
+        <v>263</v>
       </c>
       <c r="K330" t="n">
         <v>0</v>
@@ -15303,35 +15303,40 @@
         <v>0</v>
       </c>
       <c r="M330" t="n">
-        <v>18</v>
+        <v>263</v>
       </c>
       <c r="N330" t="n">
-        <v>12189.831111111</v>
+        <v>571.87</v>
       </c>
       <c r="O330" t="n">
-        <v>219416.959999998</v>
+        <v>150401.81</v>
       </c>
       <c r="P330" t="n">
-        <v>30900</v>
+        <v>2500</v>
       </c>
       <c r="Q330" t="n">
-        <v>556200</v>
+        <v>657500</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>MG40210</t>
+          <t>MG40720</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>MG40720</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>SONAJERO OSO MG40210</t>
+          <t>MAQUINA DE COSER MINI MG40720</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
@@ -15340,7 +15345,7 @@
         </is>
       </c>
       <c r="J331" t="n">
-        <v>363</v>
+        <v>64</v>
       </c>
       <c r="K331" t="n">
         <v>0</v>
@@ -15349,69 +15354,18 @@
         <v>0</v>
       </c>
       <c r="M331" t="n">
-        <v>363</v>
+        <v>64</v>
       </c>
       <c r="N331" t="n">
-        <v>571.87</v>
+        <v>9917.040000000001</v>
       </c>
       <c r="O331" t="n">
-        <v>207588.81</v>
+        <v>634690.5600000001</v>
       </c>
       <c r="P331" t="n">
-        <v>2500</v>
+        <v>15900</v>
       </c>
       <c r="Q331" t="n">
-        <v>907500</v>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" t="inlineStr">
-        <is>
-          <t>MG40720</t>
-        </is>
-      </c>
-      <c r="B332" t="inlineStr">
-        <is>
-          <t>MG40720</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>MAQUINA DE COSER MINI MG40720</t>
-        </is>
-      </c>
-      <c r="E332" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
-        </is>
-      </c>
-      <c r="I332" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J332" t="n">
-        <v>64</v>
-      </c>
-      <c r="K332" t="n">
-        <v>0</v>
-      </c>
-      <c r="L332" t="n">
-        <v>0</v>
-      </c>
-      <c r="M332" t="n">
-        <v>64</v>
-      </c>
-      <c r="N332" t="n">
-        <v>9917.040000000001</v>
-      </c>
-      <c r="O332" t="n">
-        <v>634690.5600000001</v>
-      </c>
-      <c r="P332" t="n">
-        <v>15900</v>
-      </c>
-      <c r="Q332" t="n">
         <v>1017600</v>
       </c>
     </row>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -3341,10 +3341,10 @@
         <v>480</v>
       </c>
       <c r="N70" t="n">
-        <v>3795.7100076321</v>
+        <v>3795.710007638</v>
       </c>
       <c r="O70" t="n">
-        <v>1821940.803663408</v>
+        <v>1821940.80366624</v>
       </c>
       <c r="P70" t="n">
         <v>6200</v>
@@ -3520,10 +3520,10 @@
         <v>346</v>
       </c>
       <c r="N74" t="n">
-        <v>4890.9300537634</v>
+        <v>4890.9300539811</v>
       </c>
       <c r="O74" t="n">
-        <v>1692261.798602136</v>
+        <v>1692261.798677461</v>
       </c>
       <c r="P74" t="n">
         <v>8200</v>
@@ -3794,10 +3794,10 @@
         <v>384</v>
       </c>
       <c r="N80" t="n">
-        <v>4891</v>
+        <v>4906.5393169182</v>
       </c>
       <c r="O80" t="n">
-        <v>1878144</v>
+        <v>1884111.097696589</v>
       </c>
       <c r="P80" t="n">
         <v>8200</v>
@@ -4299,10 +4299,10 @@
         <v>1728</v>
       </c>
       <c r="N91" t="n">
-        <v>3472.2762877567</v>
+        <v>3472.2762983503</v>
       </c>
       <c r="O91" t="n">
-        <v>6000093.425243578</v>
+        <v>6000093.443549318</v>
       </c>
       <c r="P91" t="n">
         <v>5900</v>
@@ -4389,10 +4389,10 @@
         <v>1356</v>
       </c>
       <c r="N93" t="n">
-        <v>4371.1712633877</v>
+        <v>4371.171263905</v>
       </c>
       <c r="O93" t="n">
-        <v>5927308.23315372</v>
+        <v>5927308.23385518</v>
       </c>
       <c r="P93" t="n">
         <v>8900</v>
@@ -6237,10 +6237,10 @@
         <v>900</v>
       </c>
       <c r="N134" t="n">
-        <v>6207.9882231175</v>
+        <v>6213.167301168</v>
       </c>
       <c r="O134" t="n">
-        <v>5587189.40080575</v>
+        <v>5591850.571051201</v>
       </c>
       <c r="P134" t="n">
         <v>9900</v>
@@ -6501,10 +6501,10 @@
         <v>1228</v>
       </c>
       <c r="N140" t="n">
-        <v>3591.13</v>
+        <v>3594.9639466192</v>
       </c>
       <c r="O140" t="n">
-        <v>4409907.640000001</v>
+        <v>4414615.726448378</v>
       </c>
       <c r="P140" t="n">
         <v>6300</v>
@@ -9564,10 +9564,10 @@
         <v>307</v>
       </c>
       <c r="N207" t="n">
-        <v>6849.2</v>
+        <v>6862.329456869</v>
       </c>
       <c r="O207" t="n">
-        <v>2102704.4</v>
+        <v>2106735.143258783</v>
       </c>
       <c r="P207" t="n">
         <v>11500</v>
@@ -11499,10 +11499,10 @@
         <v>864</v>
       </c>
       <c r="N249" t="n">
-        <v>1516.0387272539</v>
+        <v>1516.0387269907</v>
       </c>
       <c r="O249" t="n">
-        <v>1309857.46034737</v>
+        <v>1309857.460119965</v>
       </c>
       <c r="P249" t="n">
         <v>2300</v>
@@ -12848,10 +12848,10 @@
         <v>15264</v>
       </c>
       <c r="N278" t="n">
-        <v>703.79469605084</v>
+        <v>703.79468467395</v>
       </c>
       <c r="O278" t="n">
-        <v>10742722.24052002</v>
+        <v>10742722.06686317</v>
       </c>
       <c r="P278" t="n">
         <v>900</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q331"/>
+  <dimension ref="A1:Q330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-24</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-25</t>
         </is>
       </c>
     </row>
@@ -720,10 +720,10 @@
         <v>298</v>
       </c>
       <c r="N8" t="n">
-        <v>3376.7464001115</v>
+        <v>3376.746386014</v>
       </c>
       <c r="O8" t="n">
-        <v>1006270.427233227</v>
+        <v>1006270.423032172</v>
       </c>
       <c r="P8" t="n">
         <v>4500</v>
@@ -1199,10 +1199,10 @@
         <v>180</v>
       </c>
       <c r="N20" t="n">
-        <v>3926.8370772443</v>
+        <v>3926.8370726607</v>
       </c>
       <c r="O20" t="n">
-        <v>706830.673903974</v>
+        <v>706830.673078926</v>
       </c>
       <c r="P20" t="n">
         <v>4800</v>
@@ -1277,10 +1277,10 @@
         <v>52</v>
       </c>
       <c r="N22" t="n">
-        <v>2681</v>
+        <v>2785.6243902439</v>
       </c>
       <c r="O22" t="n">
-        <v>139412</v>
+        <v>144852.4682926828</v>
       </c>
       <c r="P22" t="n">
         <v>3500</v>
@@ -2319,10 +2319,10 @@
         <v>120</v>
       </c>
       <c r="N47" t="n">
-        <v>2572.67</v>
+        <v>2584.1380683507</v>
       </c>
       <c r="O47" t="n">
-        <v>308720.4</v>
+        <v>310096.568202084</v>
       </c>
       <c r="P47" t="n">
         <v>4700</v>
@@ -3065,10 +3065,10 @@
         <v>350</v>
       </c>
       <c r="N64" t="n">
-        <v>2582.2549040675</v>
+        <v>2582.2548633316</v>
       </c>
       <c r="O64" t="n">
-        <v>903789.216423625</v>
+        <v>903789.20216606</v>
       </c>
       <c r="P64" t="n">
         <v>4500</v>
@@ -3099,7 +3099,7 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>1232</v>
+        <v>1122</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
@@ -3108,19 +3108,19 @@
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>1232</v>
+        <v>1122</v>
       </c>
       <c r="N65" t="n">
-        <v>5216.8958410068</v>
+        <v>5216.8958275597</v>
       </c>
       <c r="O65" t="n">
-        <v>6427215.676120377</v>
+        <v>5853357.118521983</v>
       </c>
       <c r="P65" t="n">
         <v>8500</v>
       </c>
       <c r="Q65" t="n">
-        <v>10472000</v>
+        <v>9537000</v>
       </c>
     </row>
     <row r="66">
@@ -3520,10 +3520,10 @@
         <v>346</v>
       </c>
       <c r="N74" t="n">
-        <v>4890.9300539811</v>
+        <v>4890.9300540176</v>
       </c>
       <c r="O74" t="n">
-        <v>1692261.798677461</v>
+        <v>1692261.798690089</v>
       </c>
       <c r="P74" t="n">
         <v>8200</v>
@@ -3549,7 +3549,7 @@
         </is>
       </c>
       <c r="J75" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
@@ -3558,19 +3558,19 @@
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="N75" t="n">
         <v>180</v>
       </c>
       <c r="O75" t="n">
-        <v>45000</v>
+        <v>90000</v>
       </c>
       <c r="P75" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="Q75" t="n">
-        <v>55000</v>
+        <v>115000</v>
       </c>
     </row>
     <row r="76">
@@ -3653,10 +3653,10 @@
         <v>246</v>
       </c>
       <c r="N77" t="n">
-        <v>7041</v>
+        <v>7063.376059322</v>
       </c>
       <c r="O77" t="n">
-        <v>1732086</v>
+        <v>1737590.510593212</v>
       </c>
       <c r="P77" t="n">
         <v>11500</v>
@@ -3748,10 +3748,10 @@
         <v>216</v>
       </c>
       <c r="N79" t="n">
-        <v>3594.252920354</v>
+        <v>3594.2528730512</v>
       </c>
       <c r="O79" t="n">
-        <v>776358.6307964639</v>
+        <v>776358.6205790592</v>
       </c>
       <c r="P79" t="n">
         <v>6500</v>
@@ -3794,10 +3794,10 @@
         <v>384</v>
       </c>
       <c r="N80" t="n">
-        <v>4906.5393169182</v>
+        <v>4891</v>
       </c>
       <c r="O80" t="n">
-        <v>1884111.097696589</v>
+        <v>1878144</v>
       </c>
       <c r="P80" t="n">
         <v>8200</v>
@@ -3886,10 +3886,10 @@
         <v>316</v>
       </c>
       <c r="N82" t="n">
-        <v>14822.378819914</v>
+        <v>14822.378817006</v>
       </c>
       <c r="O82" t="n">
-        <v>4683871.707092824</v>
+        <v>4683871.706173896</v>
       </c>
       <c r="P82" t="n">
         <v>24900</v>
@@ -3974,10 +3974,10 @@
         <v>2346</v>
       </c>
       <c r="N84" t="n">
-        <v>2090.85</v>
+        <v>2093.3158067369</v>
       </c>
       <c r="O84" t="n">
-        <v>4905134.1</v>
+        <v>4910918.882604768</v>
       </c>
       <c r="P84" t="n">
         <v>2900</v>
@@ -4207,10 +4207,10 @@
         <v>336</v>
       </c>
       <c r="N89" t="n">
-        <v>12422.462992091</v>
+        <v>12422.463</v>
       </c>
       <c r="O89" t="n">
-        <v>4173947.565342576</v>
+        <v>4173947.568</v>
       </c>
       <c r="P89" t="n">
         <v>19900</v>
@@ -4287,7 +4287,7 @@
         </is>
       </c>
       <c r="J91" t="n">
-        <v>1728</v>
+        <v>1584</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
@@ -4296,19 +4296,19 @@
         <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>1728</v>
+        <v>1584</v>
       </c>
       <c r="N91" t="n">
-        <v>3472.2762983503</v>
+        <v>3472.276319645</v>
       </c>
       <c r="O91" t="n">
-        <v>6000093.443549318</v>
+        <v>5500085.69031768</v>
       </c>
       <c r="P91" t="n">
         <v>5900</v>
       </c>
       <c r="Q91" t="n">
-        <v>10195200</v>
+        <v>9345600</v>
       </c>
     </row>
     <row r="92">
@@ -4389,10 +4389,10 @@
         <v>1356</v>
       </c>
       <c r="N93" t="n">
-        <v>4371.171263905</v>
+        <v>4371.1712639913</v>
       </c>
       <c r="O93" t="n">
-        <v>5927308.23385518</v>
+        <v>5927308.233972203</v>
       </c>
       <c r="P93" t="n">
         <v>8900</v>
@@ -4660,10 +4660,10 @@
         <v>401</v>
       </c>
       <c r="N99" t="n">
-        <v>9414.309999999999</v>
+        <v>9677.770167910399</v>
       </c>
       <c r="O99" t="n">
-        <v>3775138.31</v>
+        <v>3880785.83733207</v>
       </c>
       <c r="P99" t="n">
         <v>16900</v>
@@ -6007,10 +6007,10 @@
         <v>310</v>
       </c>
       <c r="N129" t="n">
-        <v>2680.7396933667</v>
+        <v>2680.7396931747</v>
       </c>
       <c r="O129" t="n">
-        <v>831029.304943677</v>
+        <v>831029.3048841569</v>
       </c>
       <c r="P129" t="n">
         <v>4900</v>
@@ -6237,10 +6237,10 @@
         <v>900</v>
       </c>
       <c r="N134" t="n">
-        <v>6213.167301168</v>
+        <v>6207.988218663</v>
       </c>
       <c r="O134" t="n">
-        <v>5591850.571051201</v>
+        <v>5587189.396796701</v>
       </c>
       <c r="P134" t="n">
         <v>9900</v>
@@ -6286,10 +6286,10 @@
         <v>36</v>
       </c>
       <c r="N135" t="n">
-        <v>4285.1964303797</v>
+        <v>4285.1964713376</v>
       </c>
       <c r="O135" t="n">
-        <v>154267.0714936692</v>
+        <v>154267.0729681536</v>
       </c>
       <c r="P135" t="n">
         <v>6900</v>
@@ -6460,10 +6460,10 @@
         <v>948</v>
       </c>
       <c r="N139" t="n">
-        <v>4814.2679250376</v>
+        <v>4814.2679247144</v>
       </c>
       <c r="O139" t="n">
-        <v>4563925.992935645</v>
+        <v>4563925.992629251</v>
       </c>
       <c r="P139" t="n">
         <v>9900</v>
@@ -6501,10 +6501,10 @@
         <v>1228</v>
       </c>
       <c r="N140" t="n">
-        <v>3594.9639466192</v>
+        <v>3591.13</v>
       </c>
       <c r="O140" t="n">
-        <v>4414615.726448378</v>
+        <v>4409907.640000001</v>
       </c>
       <c r="P140" t="n">
         <v>6300</v>
@@ -7455,10 +7455,10 @@
         <v>48</v>
       </c>
       <c r="N161" t="n">
-        <v>18536</v>
+        <v>18873.018181818</v>
       </c>
       <c r="O161" t="n">
-        <v>889728</v>
+        <v>905904.872727264</v>
       </c>
       <c r="P161" t="n">
         <v>30900</v>
@@ -7731,10 +7731,10 @@
         <v>680</v>
       </c>
       <c r="N167" t="n">
-        <v>1778.4728622951</v>
+        <v>1778.4728660538</v>
       </c>
       <c r="O167" t="n">
-        <v>1209361.546360668</v>
+        <v>1209361.548916584</v>
       </c>
       <c r="P167" t="n">
         <v>4900</v>
@@ -8424,10 +8424,10 @@
         <v>180</v>
       </c>
       <c r="N182" t="n">
-        <v>10411</v>
+        <v>10448.721014493</v>
       </c>
       <c r="O182" t="n">
-        <v>1873980</v>
+        <v>1880769.78260874</v>
       </c>
       <c r="P182" t="n">
         <v>16900</v>
@@ -8470,10 +8470,10 @@
         <v>36</v>
       </c>
       <c r="N183" t="n">
-        <v>17644.653275862</v>
+        <v>17644.653392857</v>
       </c>
       <c r="O183" t="n">
-        <v>635207.517931032</v>
+        <v>635207.522142852</v>
       </c>
       <c r="P183" t="n">
         <v>28200</v>
@@ -9160,10 +9160,10 @@
         <v>129</v>
       </c>
       <c r="N198" t="n">
-        <v>3903.7398185118</v>
+        <v>3903.7398545455</v>
       </c>
       <c r="O198" t="n">
-        <v>503582.4365880222</v>
+        <v>503582.4412363695</v>
       </c>
       <c r="P198" t="n">
         <v>7500</v>
@@ -9518,10 +9518,10 @@
         <v>144</v>
       </c>
       <c r="N206" t="n">
-        <v>5869.1723297872</v>
+        <v>5869.1723216187</v>
       </c>
       <c r="O206" t="n">
-        <v>845160.8154893569</v>
+        <v>845160.8143130929</v>
       </c>
       <c r="P206" t="n">
         <v>9500</v>
@@ -9564,10 +9564,10 @@
         <v>307</v>
       </c>
       <c r="N207" t="n">
-        <v>6862.329456869</v>
+        <v>6849.2</v>
       </c>
       <c r="O207" t="n">
-        <v>2106735.143258783</v>
+        <v>2102704.4</v>
       </c>
       <c r="P207" t="n">
         <v>11500</v>
@@ -9656,10 +9656,10 @@
         <v>456</v>
       </c>
       <c r="N209" t="n">
-        <v>6645</v>
+        <v>6650.5777839955</v>
       </c>
       <c r="O209" t="n">
-        <v>3030120</v>
+        <v>3032663.469501948</v>
       </c>
       <c r="P209" t="n">
         <v>10900</v>
@@ -10242,7 +10242,7 @@
         </is>
       </c>
       <c r="J222" t="n">
-        <v>290</v>
+        <v>250</v>
       </c>
       <c r="K222" t="n">
         <v>0</v>
@@ -10251,19 +10251,19 @@
         <v>0</v>
       </c>
       <c r="M222" t="n">
-        <v>290</v>
+        <v>250</v>
       </c>
       <c r="N222" t="n">
         <v>11348</v>
       </c>
       <c r="O222" t="n">
-        <v>3290920</v>
+        <v>2837000</v>
       </c>
       <c r="P222" t="n">
         <v>19900</v>
       </c>
       <c r="Q222" t="n">
-        <v>5771000</v>
+        <v>4975000</v>
       </c>
     </row>
     <row r="223">
@@ -10300,10 +10300,10 @@
         <v>192</v>
       </c>
       <c r="N223" t="n">
-        <v>17075.98951782</v>
+        <v>17075.989516129</v>
       </c>
       <c r="O223" t="n">
-        <v>3278589.98742144</v>
+        <v>3278589.987096768</v>
       </c>
       <c r="P223" t="n">
         <v>27500</v>
@@ -10484,10 +10484,10 @@
         <v>84</v>
       </c>
       <c r="N227" t="n">
-        <v>18001</v>
+        <v>18170.288401254</v>
       </c>
       <c r="O227" t="n">
-        <v>1512084</v>
+        <v>1526304.225705336</v>
       </c>
       <c r="P227" t="n">
         <v>28900</v>
@@ -11039,10 +11039,10 @@
         <v>279</v>
       </c>
       <c r="N239" t="n">
-        <v>10713.21</v>
+        <v>10795.831156812</v>
       </c>
       <c r="O239" t="n">
-        <v>2988985.59</v>
+        <v>3012036.892750548</v>
       </c>
       <c r="P239" t="n">
         <v>20900</v>
@@ -11499,10 +11499,10 @@
         <v>864</v>
       </c>
       <c r="N249" t="n">
-        <v>1516.0387269907</v>
+        <v>1516.0387131507</v>
       </c>
       <c r="O249" t="n">
-        <v>1309857.460119965</v>
+        <v>1309857.448162205</v>
       </c>
       <c r="P249" t="n">
         <v>2300</v>
@@ -12294,10 +12294,10 @@
         <v>1440</v>
       </c>
       <c r="N266" t="n">
-        <v>1690.8700095238</v>
+        <v>1690.8700095877</v>
       </c>
       <c r="O266" t="n">
-        <v>2434852.813714272</v>
+        <v>2434852.813806288</v>
       </c>
       <c r="P266" t="n">
         <v>3000</v>
@@ -12338,10 +12338,10 @@
         <v>2556</v>
       </c>
       <c r="N267" t="n">
-        <v>481.48790873239</v>
+        <v>481.48790068997</v>
       </c>
       <c r="O267" t="n">
-        <v>1230683.094719989</v>
+        <v>1230683.074163563</v>
       </c>
       <c r="P267" t="n">
         <v>650</v>
@@ -12382,10 +12382,10 @@
         <v>614</v>
       </c>
       <c r="N268" t="n">
-        <v>872.15418687873</v>
+        <v>872.15420863309</v>
       </c>
       <c r="O268" t="n">
-        <v>535502.6707435403</v>
+        <v>535502.6841007172</v>
       </c>
       <c r="P268" t="n">
         <v>1200</v>
@@ -12836,7 +12836,7 @@
         </is>
       </c>
       <c r="J278" t="n">
-        <v>15264</v>
+        <v>14112</v>
       </c>
       <c r="K278" t="n">
         <v>0</v>
@@ -12845,19 +12845,19 @@
         <v>0</v>
       </c>
       <c r="M278" t="n">
-        <v>15264</v>
+        <v>14112</v>
       </c>
       <c r="N278" t="n">
-        <v>703.79468467395</v>
+        <v>703.79465893216</v>
       </c>
       <c r="O278" t="n">
-        <v>10742722.06686317</v>
+        <v>9931950.226850642</v>
       </c>
       <c r="P278" t="n">
         <v>900</v>
       </c>
       <c r="Q278" t="n">
-        <v>13737600</v>
+        <v>12700800</v>
       </c>
     </row>
     <row r="279">
@@ -13339,29 +13339,24 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>C7081</t>
+          <t>C71</t>
         </is>
       </c>
       <c r="B289" t="n">
-        <v>6301582313156</v>
+        <v>5899989622205</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>LANZADORA DARDOS DE PILA C7081</t>
-        </is>
-      </c>
-      <c r="E289" t="inlineStr">
-        <is>
-          <t>LANZADORES</t>
+          <t>C71 INFLABLE PONY ROSADO-AZUL</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J289" t="n">
-        <v>21</v>
+        <v>392</v>
       </c>
       <c r="K289" t="n">
         <v>0</v>
@@ -13370,42 +13365,44 @@
         <v>0</v>
       </c>
       <c r="M289" t="n">
-        <v>21</v>
+        <v>392</v>
       </c>
       <c r="N289" t="n">
-        <v>22470.62</v>
+        <v>1669.6</v>
       </c>
       <c r="O289" t="n">
-        <v>471883.02</v>
+        <v>654483.2</v>
       </c>
       <c r="P289" t="n">
-        <v>41900</v>
+        <v>2900</v>
       </c>
       <c r="Q289" t="n">
-        <v>879900</v>
+        <v>1136800</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>C71</t>
-        </is>
-      </c>
-      <c r="B290" t="n">
-        <v>5899989622205</v>
+          <t>C7117</t>
+        </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>C71 INFLABLE PONY ROSADO-AZUL</t>
+          <t>BINGO LOTTO C7117</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>JUEGOS DE MESA</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J290" t="n">
-        <v>392</v>
+        <v>17</v>
       </c>
       <c r="K290" t="n">
         <v>0</v>
@@ -13414,35 +13411,35 @@
         <v>0</v>
       </c>
       <c r="M290" t="n">
-        <v>392</v>
+        <v>17</v>
       </c>
       <c r="N290" t="n">
-        <v>1669.6</v>
+        <v>5798.41</v>
       </c>
       <c r="O290" t="n">
-        <v>654483.2</v>
+        <v>98572.97</v>
       </c>
       <c r="P290" t="n">
-        <v>2900</v>
+        <v>14900</v>
       </c>
       <c r="Q290" t="n">
-        <v>1136800</v>
+        <v>253300</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>C7117</t>
+          <t>C7124</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>BINGO LOTTO C7117</t>
+          <t>TRAILER TRANFORME XQ05 C7124</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>JUEGOS DE MESA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -13451,7 +13448,7 @@
         </is>
       </c>
       <c r="J291" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="K291" t="n">
         <v>0</v>
@@ -13460,35 +13457,35 @@
         <v>0</v>
       </c>
       <c r="M291" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="N291" t="n">
-        <v>5798.41</v>
+        <v>19587.53</v>
       </c>
       <c r="O291" t="n">
-        <v>98572.97</v>
+        <v>783501.2</v>
       </c>
       <c r="P291" t="n">
-        <v>14900</v>
+        <v>65000</v>
       </c>
       <c r="Q291" t="n">
-        <v>253300</v>
+        <v>2600000</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>C7124</t>
+          <t>C7132</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>TRAILER TRANFORME XQ05 C7124</t>
+          <t>SET PULSERAS Y CAUCHOS C7132</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -13497,7 +13494,7 @@
         </is>
       </c>
       <c r="J292" t="n">
-        <v>40</v>
+        <v>144</v>
       </c>
       <c r="K292" t="n">
         <v>0</v>
@@ -13506,30 +13503,33 @@
         <v>0</v>
       </c>
       <c r="M292" t="n">
-        <v>40</v>
+        <v>144</v>
       </c>
       <c r="N292" t="n">
-        <v>19587.53</v>
+        <v>3100.87</v>
       </c>
       <c r="O292" t="n">
-        <v>783501.2</v>
+        <v>446525.28</v>
       </c>
       <c r="P292" t="n">
-        <v>65000</v>
+        <v>9900</v>
       </c>
       <c r="Q292" t="n">
-        <v>2600000</v>
+        <v>1425600</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>C7132</t>
-        </is>
+          <t>C7147-A</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>6912209205022</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>SET PULSERAS Y CAUCHOS C7132</t>
+          <t>ANIMAL DINOSAURIO TRICERATOPS CONLUZ C7147-A</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -13543,7 +13543,7 @@
         </is>
       </c>
       <c r="J293" t="n">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="K293" t="n">
         <v>0</v>
@@ -13552,33 +13552,33 @@
         <v>0</v>
       </c>
       <c r="M293" t="n">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="N293" t="n">
-        <v>3100.87</v>
+        <v>10348.08</v>
       </c>
       <c r="O293" t="n">
-        <v>446525.28</v>
+        <v>413923.2</v>
       </c>
       <c r="P293" t="n">
-        <v>9900</v>
+        <v>16900</v>
       </c>
       <c r="Q293" t="n">
-        <v>1425600</v>
+        <v>676000</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>C7147-A</t>
+          <t>C7213</t>
         </is>
       </c>
       <c r="B294" t="n">
-        <v>6912209205022</v>
+        <v>6987540143012</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>ANIMAL DINOSAURIO TRICERATOPS CONLUZ C7147-A</t>
+          <t>PESCADO CON LUZ Y SONIDO C7213</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -13592,7 +13592,7 @@
         </is>
       </c>
       <c r="J294" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="K294" t="n">
         <v>0</v>
@@ -13601,33 +13601,33 @@
         <v>0</v>
       </c>
       <c r="M294" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="N294" t="n">
-        <v>10348.08</v>
+        <v>9746.8802061856</v>
       </c>
       <c r="O294" t="n">
-        <v>413923.2</v>
+        <v>467850.2498969088</v>
       </c>
       <c r="P294" t="n">
-        <v>16900</v>
+        <v>18500</v>
       </c>
       <c r="Q294" t="n">
-        <v>676000</v>
+        <v>888000</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>C7213</t>
+          <t>C7221</t>
         </is>
       </c>
       <c r="B295" t="n">
-        <v>6987540143012</v>
+        <v>7453100037446</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>PESCADO CON LUZ Y SONIDO C7213</t>
+          <t>RELOJ CON FICHAS ARMABLES  C7221</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -13641,7 +13641,7 @@
         </is>
       </c>
       <c r="J295" t="n">
-        <v>48</v>
+        <v>347</v>
       </c>
       <c r="K295" t="n">
         <v>0</v>
@@ -13650,33 +13650,33 @@
         <v>0</v>
       </c>
       <c r="M295" t="n">
-        <v>48</v>
+        <v>347</v>
       </c>
       <c r="N295" t="n">
-        <v>9746.8802061856</v>
+        <v>2672.89</v>
       </c>
       <c r="O295" t="n">
-        <v>467850.2498969088</v>
+        <v>927492.83</v>
       </c>
       <c r="P295" t="n">
-        <v>18500</v>
+        <v>10200</v>
       </c>
       <c r="Q295" t="n">
-        <v>888000</v>
+        <v>3539400</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>C7221</t>
+          <t>C7222</t>
         </is>
       </c>
       <c r="B296" t="n">
-        <v>7453100037446</v>
+        <v>7453100037453</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>RELOJ CON FICHAS ARMABLES  C7221</t>
+          <t>RELOJ DIDACTICO CARACOL C7222</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -13690,7 +13690,7 @@
         </is>
       </c>
       <c r="J296" t="n">
-        <v>347</v>
+        <v>230</v>
       </c>
       <c r="K296" t="n">
         <v>0</v>
@@ -13699,38 +13699,38 @@
         <v>0</v>
       </c>
       <c r="M296" t="n">
-        <v>347</v>
+        <v>230</v>
       </c>
       <c r="N296" t="n">
-        <v>2672.89</v>
+        <v>4795.69</v>
       </c>
       <c r="O296" t="n">
-        <v>927492.83</v>
+        <v>1103008.7</v>
       </c>
       <c r="P296" t="n">
         <v>10200</v>
       </c>
       <c r="Q296" t="n">
-        <v>3539400</v>
+        <v>2346000</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>C7222</t>
+          <t>C7294</t>
         </is>
       </c>
       <c r="B297" t="n">
-        <v>7453100037453</v>
+        <v>6895675680022</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>RELOJ DIDACTICO CARACOL C7222</t>
+          <t>JUEGO DEPORTIVO HOCHEY C7294</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -13739,7 +13739,7 @@
         </is>
       </c>
       <c r="J297" t="n">
-        <v>230</v>
+        <v>60</v>
       </c>
       <c r="K297" t="n">
         <v>0</v>
@@ -13748,38 +13748,38 @@
         <v>0</v>
       </c>
       <c r="M297" t="n">
-        <v>230</v>
+        <v>60</v>
       </c>
       <c r="N297" t="n">
-        <v>4795.69</v>
+        <v>4337.31</v>
       </c>
       <c r="O297" t="n">
-        <v>1103008.7</v>
+        <v>260238.6</v>
       </c>
       <c r="P297" t="n">
-        <v>10200</v>
+        <v>12900</v>
       </c>
       <c r="Q297" t="n">
-        <v>2346000</v>
+        <v>774000</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>C7294</t>
+          <t>C7325</t>
         </is>
       </c>
       <c r="B298" t="n">
-        <v>6895675680022</v>
+        <v>6974555555022</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>JUEGO DEPORTIVO HOCHEY C7294</t>
+          <t>PISTA EN BLISTER C7325</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -13788,7 +13788,7 @@
         </is>
       </c>
       <c r="J298" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="K298" t="n">
         <v>0</v>
@@ -13797,38 +13797,35 @@
         <v>0</v>
       </c>
       <c r="M298" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="N298" t="n">
-        <v>4337.31</v>
+        <v>3099.0394791667</v>
       </c>
       <c r="O298" t="n">
-        <v>260238.6</v>
+        <v>139456.7765625015</v>
       </c>
       <c r="P298" t="n">
-        <v>12900</v>
+        <v>7200</v>
       </c>
       <c r="Q298" t="n">
-        <v>774000</v>
+        <v>324000</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>C7325</t>
-        </is>
-      </c>
-      <c r="B299" t="n">
-        <v>6974555555022</v>
+          <t>C736</t>
+        </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>PISTA EN BLISTER C7325</t>
+          <t>GLOBO CORAZON GDE MENSAJE</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -13837,7 +13834,7 @@
         </is>
       </c>
       <c r="J299" t="n">
-        <v>45</v>
+        <v>2700</v>
       </c>
       <c r="K299" t="n">
         <v>0</v>
@@ -13846,35 +13843,38 @@
         <v>0</v>
       </c>
       <c r="M299" t="n">
-        <v>45</v>
+        <v>2700</v>
       </c>
       <c r="N299" t="n">
-        <v>3067.0906185567</v>
+        <v>640</v>
       </c>
       <c r="O299" t="n">
-        <v>138019.0778350515</v>
+        <v>1728000</v>
       </c>
       <c r="P299" t="n">
-        <v>7200</v>
+        <v>800</v>
       </c>
       <c r="Q299" t="n">
-        <v>324000</v>
+        <v>2160000</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>C736</t>
-        </is>
+          <t>C7365</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>6920240750050</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>GLOBO CORAZON GDE MENSAJE</t>
+          <t>DIDACTICO JIRAFA EN BOLSA C7365</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -13883,7 +13883,7 @@
         </is>
       </c>
       <c r="J300" t="n">
-        <v>2700</v>
+        <v>19</v>
       </c>
       <c r="K300" t="n">
         <v>0</v>
@@ -13892,33 +13892,33 @@
         <v>0</v>
       </c>
       <c r="M300" t="n">
-        <v>2700</v>
+        <v>19</v>
       </c>
       <c r="N300" t="n">
-        <v>640</v>
+        <v>4234.8833684211</v>
       </c>
       <c r="O300" t="n">
-        <v>1728000</v>
+        <v>80462.7840000009</v>
       </c>
       <c r="P300" t="n">
-        <v>800</v>
+        <v>5900</v>
       </c>
       <c r="Q300" t="n">
-        <v>2160000</v>
+        <v>112100</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>C7365</t>
+          <t>C7366</t>
         </is>
       </c>
       <c r="B301" t="n">
-        <v>6920240750050</v>
+        <v>6920240750098</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>DIDACTICO JIRAFA EN BOLSA C7365</t>
+          <t>TREN DIDACTICO EN BOLSA C7366</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -13932,7 +13932,7 @@
         </is>
       </c>
       <c r="J301" t="n">
-        <v>19</v>
+        <v>104</v>
       </c>
       <c r="K301" t="n">
         <v>0</v>
@@ -13941,33 +13941,33 @@
         <v>0</v>
       </c>
       <c r="M301" t="n">
-        <v>19</v>
+        <v>104</v>
       </c>
       <c r="N301" t="n">
-        <v>4190.77</v>
+        <v>3499.72</v>
       </c>
       <c r="O301" t="n">
-        <v>79624.63</v>
+        <v>363970.88</v>
       </c>
       <c r="P301" t="n">
-        <v>5900</v>
+        <v>6900</v>
       </c>
       <c r="Q301" t="n">
-        <v>112100</v>
+        <v>717600</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>C7366</t>
+          <t>C7368</t>
         </is>
       </c>
       <c r="B302" t="n">
-        <v>6920240750098</v>
+        <v>6920240750159</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>TREN DIDACTICO EN BOLSA C7366</t>
+          <t>MOTO DIDACTICA EN BOLSA C736</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -13981,7 +13981,7 @@
         </is>
       </c>
       <c r="J302" t="n">
-        <v>104</v>
+        <v>158</v>
       </c>
       <c r="K302" t="n">
         <v>0</v>
@@ -13990,38 +13990,35 @@
         <v>0</v>
       </c>
       <c r="M302" t="n">
-        <v>104</v>
+        <v>158</v>
       </c>
       <c r="N302" t="n">
-        <v>3499.72</v>
+        <v>4578.04</v>
       </c>
       <c r="O302" t="n">
-        <v>363970.88</v>
+        <v>723330.3199999999</v>
       </c>
       <c r="P302" t="n">
-        <v>6900</v>
+        <v>7500</v>
       </c>
       <c r="Q302" t="n">
-        <v>717600</v>
+        <v>1185000</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>C7368</t>
-        </is>
-      </c>
-      <c r="B303" t="n">
-        <v>6920240750159</v>
+          <t>C740-IO</t>
+        </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>MOTO DIDACTICA EN BOLSA C736</t>
+          <t>GLOBO UNICORNIO MED</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -14030,7 +14027,7 @@
         </is>
       </c>
       <c r="J303" t="n">
-        <v>158</v>
+        <v>1876</v>
       </c>
       <c r="K303" t="n">
         <v>0</v>
@@ -14039,35 +14036,38 @@
         <v>0</v>
       </c>
       <c r="M303" t="n">
-        <v>158</v>
+        <v>1876</v>
       </c>
       <c r="N303" t="n">
-        <v>4578.04</v>
+        <v>480</v>
       </c>
       <c r="O303" t="n">
-        <v>723330.3199999999</v>
+        <v>900480</v>
       </c>
       <c r="P303" t="n">
-        <v>7500</v>
+        <v>600</v>
       </c>
       <c r="Q303" t="n">
-        <v>1185000</v>
+        <v>1125600</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>C740-IO</t>
-        </is>
+          <t>C7413</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>6921202412870</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>GLOBO UNICORNIO MED</t>
+          <t>DIDACTICO TORRE DE AROS C7413</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -14076,7 +14076,7 @@
         </is>
       </c>
       <c r="J304" t="n">
-        <v>1876</v>
+        <v>120</v>
       </c>
       <c r="K304" t="n">
         <v>0</v>
@@ -14085,38 +14085,35 @@
         <v>0</v>
       </c>
       <c r="M304" t="n">
-        <v>1876</v>
+        <v>120</v>
       </c>
       <c r="N304" t="n">
-        <v>480</v>
+        <v>4159.0003007519</v>
       </c>
       <c r="O304" t="n">
-        <v>900480</v>
+        <v>499080.036090228</v>
       </c>
       <c r="P304" t="n">
-        <v>600</v>
+        <v>8900</v>
       </c>
       <c r="Q304" t="n">
-        <v>1125600</v>
+        <v>1068000</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>C7413</t>
-        </is>
-      </c>
-      <c r="B305" t="n">
-        <v>6921202412870</v>
+          <t>C744-IO</t>
+        </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>DIDACTICO TORRE DE AROS C7413</t>
+          <t>GLOBO FELIZ CUMPLEAÑOS COLORES Y PUNTOS</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>GLOBOS</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -14125,7 +14122,7 @@
         </is>
       </c>
       <c r="J305" t="n">
-        <v>120</v>
+        <v>478</v>
       </c>
       <c r="K305" t="n">
         <v>0</v>
@@ -14134,35 +14131,35 @@
         <v>0</v>
       </c>
       <c r="M305" t="n">
-        <v>120</v>
+        <v>478</v>
       </c>
       <c r="N305" t="n">
-        <v>4159.0003007519</v>
+        <v>1554.12</v>
       </c>
       <c r="O305" t="n">
-        <v>499080.036090228</v>
+        <v>742869.36</v>
       </c>
       <c r="P305" t="n">
-        <v>8900</v>
+        <v>1900</v>
       </c>
       <c r="Q305" t="n">
-        <v>1068000</v>
+        <v>908200</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>C744-IO</t>
+          <t>C7462</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>GLOBO FELIZ CUMPLEAÑOS COLORES Y PUNTOS</t>
+          <t>SET DE BELLEZA ACCESORIOS PARA EL CABELLO C7462</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>GLOBOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -14171,7 +14168,7 @@
         </is>
       </c>
       <c r="J306" t="n">
-        <v>478</v>
+        <v>11</v>
       </c>
       <c r="K306" t="n">
         <v>0</v>
@@ -14180,30 +14177,33 @@
         <v>0</v>
       </c>
       <c r="M306" t="n">
-        <v>478</v>
+        <v>11</v>
       </c>
       <c r="N306" t="n">
-        <v>1554.12</v>
+        <v>14751.820338983</v>
       </c>
       <c r="O306" t="n">
-        <v>742869.36</v>
+        <v>162270.023728813</v>
       </c>
       <c r="P306" t="n">
-        <v>1900</v>
+        <v>37100</v>
       </c>
       <c r="Q306" t="n">
-        <v>908200</v>
+        <v>408100</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>C7462</t>
-        </is>
+          <t>C7467</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>6920241023009</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>SET DE BELLEZA ACCESORIOS PARA EL CABELLO C7462</t>
+          <t>ARCO Y FLECHA PARA NIÑAS C7467</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -14217,7 +14217,7 @@
         </is>
       </c>
       <c r="J307" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K307" t="n">
         <v>0</v>
@@ -14226,38 +14226,38 @@
         <v>0</v>
       </c>
       <c r="M307" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="N307" t="n">
-        <v>14751.820338983</v>
+        <v>15347.45</v>
       </c>
       <c r="O307" t="n">
-        <v>162270.023728813</v>
+        <v>230211.75</v>
       </c>
       <c r="P307" t="n">
-        <v>37100</v>
+        <v>23900</v>
       </c>
       <c r="Q307" t="n">
-        <v>408100</v>
+        <v>358500</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>C7467</t>
+          <t>C7488</t>
         </is>
       </c>
       <c r="B308" t="n">
-        <v>6920241023009</v>
+        <v>6945158254520</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>ARCO Y FLECHA PARA NIÑAS C7467</t>
+          <t>SOPORTE CELULAR CON LUZ C7488</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -14266,7 +14266,7 @@
         </is>
       </c>
       <c r="J308" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="K308" t="n">
         <v>0</v>
@@ -14275,38 +14275,38 @@
         <v>0</v>
       </c>
       <c r="M308" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="N308" t="n">
-        <v>15347.45</v>
+        <v>8919.16</v>
       </c>
       <c r="O308" t="n">
-        <v>230211.75</v>
+        <v>258655.64</v>
       </c>
       <c r="P308" t="n">
-        <v>23900</v>
+        <v>10000</v>
       </c>
       <c r="Q308" t="n">
-        <v>358500</v>
+        <v>290000</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>C7488</t>
+          <t>C7513</t>
         </is>
       </c>
       <c r="B309" t="n">
-        <v>6945158254520</v>
+        <v>6905698382824</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>SOPORTE CELULAR CON LUZ C7488</t>
+          <t>SONAJERO BOLA LUZ GDE C7513</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -14315,7 +14315,7 @@
         </is>
       </c>
       <c r="J309" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="K309" t="n">
         <v>0</v>
@@ -14324,47 +14324,42 @@
         <v>0</v>
       </c>
       <c r="M309" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="N309" t="n">
-        <v>8919.16</v>
+        <v>1024.29</v>
       </c>
       <c r="O309" t="n">
-        <v>258655.64</v>
+        <v>1024.29</v>
       </c>
       <c r="P309" t="n">
-        <v>10000</v>
+        <v>2900</v>
       </c>
       <c r="Q309" t="n">
-        <v>290000</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>C7513</t>
+          <t>C752</t>
         </is>
       </c>
       <c r="B310" t="n">
-        <v>6905698382824</v>
+        <v>8596162180497</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>SONAJERO BOLA LUZ GDE C7513</t>
-        </is>
-      </c>
-      <c r="E310" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
+          <t>GLOBO UNICORNIO MED 4 PATAS</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J310" t="n">
-        <v>1</v>
+        <v>1398</v>
       </c>
       <c r="K310" t="n">
         <v>0</v>
@@ -14373,33 +14368,33 @@
         <v>0</v>
       </c>
       <c r="M310" t="n">
-        <v>1</v>
+        <v>1398</v>
       </c>
       <c r="N310" t="n">
-        <v>1024.29</v>
+        <v>1163.7447787403</v>
       </c>
       <c r="O310" t="n">
-        <v>1024.29</v>
+        <v>1626915.200678939</v>
       </c>
       <c r="P310" t="n">
-        <v>2900</v>
+        <v>1500</v>
       </c>
       <c r="Q310" t="n">
-        <v>2900</v>
+        <v>2097000</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>C752</t>
+          <t>C753</t>
         </is>
       </c>
       <c r="B311" t="n">
-        <v>8596162180497</v>
+        <v>8596162180503</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>GLOBO UNICORNIO MED 4 PATAS</t>
+          <t>GLOBO UNICORNIO GDE 4 PATAS</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -14408,7 +14403,7 @@
         </is>
       </c>
       <c r="J311" t="n">
-        <v>1398</v>
+        <v>277</v>
       </c>
       <c r="K311" t="n">
         <v>0</v>
@@ -14417,42 +14412,47 @@
         <v>0</v>
       </c>
       <c r="M311" t="n">
-        <v>1398</v>
+        <v>277</v>
       </c>
       <c r="N311" t="n">
-        <v>1163.7447787403</v>
+        <v>5113.4625508318</v>
       </c>
       <c r="O311" t="n">
-        <v>1626915.200678939</v>
+        <v>1416429.126580409</v>
       </c>
       <c r="P311" t="n">
-        <v>1500</v>
+        <v>7000</v>
       </c>
       <c r="Q311" t="n">
-        <v>2097000</v>
+        <v>1939000</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>C753</t>
+          <t>C7533</t>
         </is>
       </c>
       <c r="B312" t="n">
-        <v>8596162180503</v>
+        <v>6923669699979</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>GLOBO UNICORNIO GDE 4 PATAS</t>
+          <t>REPUESTO BIOGEL NEON C7533</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J312" t="n">
-        <v>277</v>
+        <v>12023</v>
       </c>
       <c r="K312" t="n">
         <v>0</v>
@@ -14461,33 +14461,33 @@
         <v>0</v>
       </c>
       <c r="M312" t="n">
-        <v>277</v>
+        <v>12023</v>
       </c>
       <c r="N312" t="n">
-        <v>5113.4625508318</v>
+        <v>509.69</v>
       </c>
       <c r="O312" t="n">
-        <v>1416429.126580409</v>
+        <v>6128002.87</v>
       </c>
       <c r="P312" t="n">
-        <v>7000</v>
+        <v>750</v>
       </c>
       <c r="Q312" t="n">
-        <v>1939000</v>
+        <v>9017250</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>C7533</t>
+          <t>C7534</t>
         </is>
       </c>
       <c r="B313" t="n">
-        <v>6923669699979</v>
+        <v>6951241752002</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>REPUESTO BIOGEL NEON C7533</t>
+          <t>GORRO PELUCHE LUZ C7534-A-B-C-D-E-F</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -14501,7 +14501,7 @@
         </is>
       </c>
       <c r="J313" t="n">
-        <v>12023</v>
+        <v>499</v>
       </c>
       <c r="K313" t="n">
         <v>0</v>
@@ -14510,38 +14510,35 @@
         <v>0</v>
       </c>
       <c r="M313" t="n">
-        <v>12023</v>
+        <v>499</v>
       </c>
       <c r="N313" t="n">
-        <v>509.69</v>
+        <v>7046.9398263889</v>
       </c>
       <c r="O313" t="n">
-        <v>6128002.87</v>
+        <v>3516422.973368061</v>
       </c>
       <c r="P313" t="n">
-        <v>750</v>
+        <v>9900</v>
       </c>
       <c r="Q313" t="n">
-        <v>9017250</v>
+        <v>4940100</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>C7534</t>
-        </is>
-      </c>
-      <c r="B314" t="n">
-        <v>6951241752002</v>
+          <t>C7535</t>
+        </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>GORRO PELUCHE LUZ C7534-A-B-C-D-E-F</t>
+          <t>CARRO METALICO X13 CON CAMION C7535</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -14550,7 +14547,7 @@
         </is>
       </c>
       <c r="J314" t="n">
-        <v>499</v>
+        <v>30</v>
       </c>
       <c r="K314" t="n">
         <v>0</v>
@@ -14559,35 +14556,35 @@
         <v>0</v>
       </c>
       <c r="M314" t="n">
-        <v>499</v>
+        <v>30</v>
       </c>
       <c r="N314" t="n">
-        <v>7046.9398265771</v>
+        <v>24338.47</v>
       </c>
       <c r="O314" t="n">
-        <v>3516422.973461973</v>
+        <v>730154.1000000001</v>
       </c>
       <c r="P314" t="n">
-        <v>9900</v>
+        <v>27900</v>
       </c>
       <c r="Q314" t="n">
-        <v>4940100</v>
+        <v>837000</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>C7535</t>
+          <t>C7560</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>CARRO METALICO X13 CON CAMION C7535</t>
+          <t>BARRA LUMINOSA 48CM C7560/211</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -14596,7 +14593,7 @@
         </is>
       </c>
       <c r="J315" t="n">
-        <v>30</v>
+        <v>188</v>
       </c>
       <c r="K315" t="n">
         <v>0</v>
@@ -14605,30 +14602,33 @@
         <v>0</v>
       </c>
       <c r="M315" t="n">
-        <v>30</v>
+        <v>188</v>
       </c>
       <c r="N315" t="n">
-        <v>24338.47</v>
+        <v>796.3099999999999</v>
       </c>
       <c r="O315" t="n">
-        <v>730154.1000000001</v>
+        <v>149706.28</v>
       </c>
       <c r="P315" t="n">
-        <v>27900</v>
+        <v>2500</v>
       </c>
       <c r="Q315" t="n">
-        <v>837000</v>
+        <v>470000</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>C7560</t>
-        </is>
+          <t>C7588</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>7588228020244</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>BARRA LUMINOSA 48CM C7560/211</t>
+          <t>SONAJERO LUZ PANDITA C7588</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -14642,7 +14642,7 @@
         </is>
       </c>
       <c r="J316" t="n">
-        <v>188</v>
+        <v>1429</v>
       </c>
       <c r="K316" t="n">
         <v>0</v>
@@ -14651,38 +14651,38 @@
         <v>0</v>
       </c>
       <c r="M316" t="n">
-        <v>188</v>
+        <v>1429</v>
       </c>
       <c r="N316" t="n">
-        <v>796.3099999999999</v>
+        <v>641.78</v>
       </c>
       <c r="O316" t="n">
-        <v>149706.28</v>
+        <v>917103.62</v>
       </c>
       <c r="P316" t="n">
         <v>2500</v>
       </c>
       <c r="Q316" t="n">
-        <v>470000</v>
+        <v>3572500</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>C7588</t>
+          <t>C7610</t>
         </is>
       </c>
       <c r="B317" t="n">
-        <v>7588228020244</v>
+        <v>6999899236093</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>SONAJERO LUZ PANDITA C7588</t>
+          <t>BOTE TIMON PISCINA 80X60 C7610</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>INFLABLES</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -14691,7 +14691,7 @@
         </is>
       </c>
       <c r="J317" t="n">
-        <v>1429</v>
+        <v>276</v>
       </c>
       <c r="K317" t="n">
         <v>0</v>
@@ -14700,38 +14700,38 @@
         <v>0</v>
       </c>
       <c r="M317" t="n">
-        <v>1429</v>
+        <v>276</v>
       </c>
       <c r="N317" t="n">
-        <v>641.78</v>
+        <v>7811.9</v>
       </c>
       <c r="O317" t="n">
-        <v>917103.62</v>
+        <v>2156084.4</v>
       </c>
       <c r="P317" t="n">
-        <v>2500</v>
+        <v>13900</v>
       </c>
       <c r="Q317" t="n">
-        <v>3572500</v>
+        <v>3836400</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>C7610</t>
+          <t>C7614-F</t>
         </is>
       </c>
       <c r="B318" t="n">
-        <v>6999899236093</v>
+        <v>6999899236130</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>BOTE TIMON PISCINA 80X60 C7610</t>
+          <t>FLOTADOR DONA FLAMINGO C7614-F</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>INFLABLES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -14740,7 +14740,7 @@
         </is>
       </c>
       <c r="J318" t="n">
-        <v>276</v>
+        <v>382</v>
       </c>
       <c r="K318" t="n">
         <v>0</v>
@@ -14749,47 +14749,42 @@
         <v>0</v>
       </c>
       <c r="M318" t="n">
-        <v>276</v>
+        <v>382</v>
       </c>
       <c r="N318" t="n">
-        <v>7811.9</v>
+        <v>3155</v>
       </c>
       <c r="O318" t="n">
-        <v>2156084.4</v>
+        <v>1205210</v>
       </c>
       <c r="P318" t="n">
-        <v>13900</v>
+        <v>5900</v>
       </c>
       <c r="Q318" t="n">
-        <v>3836400</v>
+        <v>2253800</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>C7614-F</t>
+          <t>C784</t>
         </is>
       </c>
       <c r="B319" t="n">
-        <v>6999899236130</v>
+        <v>8913992935507</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>FLOTADOR DONA FLAMINGO C7614-F</t>
-        </is>
-      </c>
-      <c r="E319" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>GLOBO MENSAJE CUADRADO</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J319" t="n">
-        <v>382</v>
+        <v>1450</v>
       </c>
       <c r="K319" t="n">
         <v>0</v>
@@ -14798,33 +14793,33 @@
         <v>0</v>
       </c>
       <c r="M319" t="n">
-        <v>382</v>
+        <v>1450</v>
       </c>
       <c r="N319" t="n">
-        <v>3155</v>
+        <v>704.89696969697</v>
       </c>
       <c r="O319" t="n">
-        <v>1205210</v>
+        <v>1022100.606060607</v>
       </c>
       <c r="P319" t="n">
-        <v>5900</v>
+        <v>900</v>
       </c>
       <c r="Q319" t="n">
-        <v>2253800</v>
+        <v>1305000</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>C784</t>
+          <t>C819</t>
         </is>
       </c>
       <c r="B320" t="n">
-        <v>8913992935507</v>
+        <v>2087202108190</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>GLOBO MENSAJE CUADRADO</t>
+          <t>TROMPO EMOJI</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -14833,7 +14828,7 @@
         </is>
       </c>
       <c r="J320" t="n">
-        <v>1450</v>
+        <v>468</v>
       </c>
       <c r="K320" t="n">
         <v>0</v>
@@ -14842,33 +14837,33 @@
         <v>0</v>
       </c>
       <c r="M320" t="n">
-        <v>1450</v>
+        <v>468</v>
       </c>
       <c r="N320" t="n">
-        <v>704.89696969697</v>
+        <v>6761.25</v>
       </c>
       <c r="O320" t="n">
-        <v>1022100.606060607</v>
+        <v>3164265</v>
       </c>
       <c r="P320" t="n">
-        <v>900</v>
+        <v>5200</v>
       </c>
       <c r="Q320" t="n">
-        <v>1305000</v>
+        <v>2433600</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>C819</t>
+          <t>C84</t>
         </is>
       </c>
       <c r="B321" t="n">
-        <v>2087202108190</v>
+        <v>2021010563031</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>TROMPO EMOJI</t>
+          <t>LANZADOR DE AGUA</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -14877,7 +14872,7 @@
         </is>
       </c>
       <c r="J321" t="n">
-        <v>468</v>
+        <v>188</v>
       </c>
       <c r="K321" t="n">
         <v>0</v>
@@ -14886,33 +14881,35 @@
         <v>0</v>
       </c>
       <c r="M321" t="n">
-        <v>468</v>
+        <v>188</v>
       </c>
       <c r="N321" t="n">
-        <v>6761.25</v>
+        <v>1008.8113941019</v>
       </c>
       <c r="O321" t="n">
-        <v>3164265</v>
+        <v>189656.5420911572</v>
       </c>
       <c r="P321" t="n">
-        <v>5200</v>
+        <v>1500</v>
       </c>
       <c r="Q321" t="n">
-        <v>2433600</v>
+        <v>282000</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>C84</t>
-        </is>
-      </c>
-      <c r="B322" t="n">
-        <v>2021010563031</v>
+          <t>C879</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>CG-2016-212</t>
+        </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>LANZADOR DE AGUA</t>
+          <t>VELA MARIPOSA</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -14921,7 +14918,7 @@
         </is>
       </c>
       <c r="J322" t="n">
-        <v>188</v>
+        <v>121</v>
       </c>
       <c r="K322" t="n">
         <v>0</v>
@@ -14930,44 +14927,49 @@
         <v>0</v>
       </c>
       <c r="M322" t="n">
-        <v>188</v>
+        <v>121</v>
       </c>
       <c r="N322" t="n">
-        <v>1008.8113941019</v>
+        <v>1520</v>
       </c>
       <c r="O322" t="n">
-        <v>189656.5420911572</v>
+        <v>183920</v>
       </c>
       <c r="P322" t="n">
-        <v>1500</v>
+        <v>1900</v>
       </c>
       <c r="Q322" t="n">
-        <v>282000</v>
+        <v>229900</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>C879</t>
+          <t>C880</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>CG-2016-212</t>
+          <t>cg2016213</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>VELA MARIPOSA</t>
+          <t>VELA FLOR</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>VELA</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J323" t="n">
-        <v>121</v>
+        <v>200</v>
       </c>
       <c r="K323" t="n">
         <v>0</v>
@@ -14976,49 +14978,39 @@
         <v>0</v>
       </c>
       <c r="M323" t="n">
-        <v>121</v>
+        <v>200</v>
       </c>
       <c r="N323" t="n">
         <v>1520</v>
       </c>
       <c r="O323" t="n">
-        <v>183920</v>
+        <v>304000</v>
       </c>
       <c r="P323" t="n">
         <v>1900</v>
       </c>
       <c r="Q323" t="n">
-        <v>229900</v>
+        <v>380000</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>C880</t>
-        </is>
-      </c>
-      <c r="B324" t="inlineStr">
-        <is>
-          <t>cg2016213</t>
+          <t>C888</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>VELA FLOR</t>
-        </is>
-      </c>
-      <c r="E324" t="inlineStr">
-        <is>
-          <t>VELA</t>
+          <t>PELOTA CHILLON PUYAS SIN LUZ</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J324" t="n">
-        <v>200</v>
+        <v>169</v>
       </c>
       <c r="K324" t="n">
         <v>0</v>
@@ -15027,39 +15019,44 @@
         <v>0</v>
       </c>
       <c r="M324" t="n">
-        <v>200</v>
+        <v>169</v>
       </c>
       <c r="N324" t="n">
-        <v>1520</v>
+        <v>1213.6821400778</v>
       </c>
       <c r="O324" t="n">
-        <v>304000</v>
+        <v>205112.2816731482</v>
       </c>
       <c r="P324" t="n">
-        <v>1900</v>
+        <v>1500</v>
       </c>
       <c r="Q324" t="n">
-        <v>380000</v>
+        <v>253500</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>C888</t>
+          <t>FG037</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>PELOTA CHILLON PUYAS SIN LUZ</t>
+          <t>SNORKEL 66046A</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J325" t="n">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="K325" t="n">
         <v>0</v>
@@ -15068,30 +15065,30 @@
         <v>0</v>
       </c>
       <c r="M325" t="n">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="N325" t="n">
-        <v>1213.6821400778</v>
+        <v>13493.858292683</v>
       </c>
       <c r="O325" t="n">
-        <v>205112.2816731482</v>
+        <v>2415400.634390257</v>
       </c>
       <c r="P325" t="n">
-        <v>1500</v>
+        <v>16900</v>
       </c>
       <c r="Q325" t="n">
-        <v>253500</v>
+        <v>3025100</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>FG037</t>
+          <t>FG039</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>SNORKEL 66046A</t>
+          <t>GAFA DE NATACION BLISTER 2404-2</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -15105,7 +15102,7 @@
         </is>
       </c>
       <c r="J326" t="n">
-        <v>179</v>
+        <v>347</v>
       </c>
       <c r="K326" t="n">
         <v>0</v>
@@ -15114,35 +15111,40 @@
         <v>0</v>
       </c>
       <c r="M326" t="n">
-        <v>179</v>
+        <v>347</v>
       </c>
       <c r="N326" t="n">
-        <v>13493.858292683</v>
+        <v>2644.9</v>
       </c>
       <c r="O326" t="n">
-        <v>2415400.634390257</v>
+        <v>917780.3</v>
       </c>
       <c r="P326" t="n">
-        <v>16900</v>
+        <v>3900</v>
       </c>
       <c r="Q326" t="n">
-        <v>3025100</v>
+        <v>1353300</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>FG039</t>
+          <t>MG16332</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>MG16332</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>GAFA DE NATACION BLISTER 2404-2</t>
+          <t>LANZADOR  ARCO Y FLECA CON LASER MG16332</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -15151,7 +15153,7 @@
         </is>
       </c>
       <c r="J327" t="n">
-        <v>347</v>
+        <v>4</v>
       </c>
       <c r="K327" t="n">
         <v>0</v>
@@ -15160,35 +15162,30 @@
         <v>0</v>
       </c>
       <c r="M327" t="n">
-        <v>347</v>
+        <v>4</v>
       </c>
       <c r="N327" t="n">
-        <v>2644.9</v>
+        <v>8439.969999999999</v>
       </c>
       <c r="O327" t="n">
-        <v>917780.3</v>
+        <v>33759.88</v>
       </c>
       <c r="P327" t="n">
-        <v>3900</v>
+        <v>29500</v>
       </c>
       <c r="Q327" t="n">
-        <v>1353300</v>
+        <v>118000</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>MG16332</t>
-        </is>
-      </c>
-      <c r="B328" t="inlineStr">
-        <is>
-          <t>MG16332</t>
+          <t>MG20430</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>LANZADOR  ARCO Y FLECA CON LASER MG16332</t>
+          <t>SET PLASTILINA CON MOLDES BARBERIA MALETA MG20430</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -15202,7 +15199,7 @@
         </is>
       </c>
       <c r="J328" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="K328" t="n">
         <v>0</v>
@@ -15211,35 +15208,35 @@
         <v>0</v>
       </c>
       <c r="M328" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="N328" t="n">
-        <v>8439.969999999999</v>
+        <v>12189.831111111</v>
       </c>
       <c r="O328" t="n">
-        <v>33759.88</v>
+        <v>219416.959999998</v>
       </c>
       <c r="P328" t="n">
-        <v>29500</v>
+        <v>30900</v>
       </c>
       <c r="Q328" t="n">
-        <v>118000</v>
+        <v>556200</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>MG20430</t>
+          <t>MG40210</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>SET PLASTILINA CON MOLDES BARBERIA MALETA MG20430</t>
+          <t>SONAJERO OSO MG40210</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -15248,7 +15245,7 @@
         </is>
       </c>
       <c r="J329" t="n">
-        <v>18</v>
+        <v>263</v>
       </c>
       <c r="K329" t="n">
         <v>0</v>
@@ -15257,35 +15254,40 @@
         <v>0</v>
       </c>
       <c r="M329" t="n">
-        <v>18</v>
+        <v>263</v>
       </c>
       <c r="N329" t="n">
-        <v>12189.831111111</v>
+        <v>571.87</v>
       </c>
       <c r="O329" t="n">
-        <v>219416.959999998</v>
+        <v>150401.81</v>
       </c>
       <c r="P329" t="n">
-        <v>30900</v>
+        <v>2500</v>
       </c>
       <c r="Q329" t="n">
-        <v>556200</v>
+        <v>657500</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>MG40210</t>
+          <t>MG40720</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>MG40720</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>SONAJERO OSO MG40210</t>
+          <t>MAQUINA DE COSER MINI MG40720</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -15294,7 +15296,7 @@
         </is>
       </c>
       <c r="J330" t="n">
-        <v>263</v>
+        <v>64</v>
       </c>
       <c r="K330" t="n">
         <v>0</v>
@@ -15303,69 +15305,18 @@
         <v>0</v>
       </c>
       <c r="M330" t="n">
-        <v>263</v>
+        <v>64</v>
       </c>
       <c r="N330" t="n">
-        <v>571.87</v>
+        <v>9917.040000000001</v>
       </c>
       <c r="O330" t="n">
-        <v>150401.81</v>
+        <v>634690.5600000001</v>
       </c>
       <c r="P330" t="n">
-        <v>2500</v>
+        <v>15900</v>
       </c>
       <c r="Q330" t="n">
-        <v>657500</v>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" t="inlineStr">
-        <is>
-          <t>MG40720</t>
-        </is>
-      </c>
-      <c r="B331" t="inlineStr">
-        <is>
-          <t>MG40720</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>MAQUINA DE COSER MINI MG40720</t>
-        </is>
-      </c>
-      <c r="E331" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
-        </is>
-      </c>
-      <c r="I331" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J331" t="n">
-        <v>64</v>
-      </c>
-      <c r="K331" t="n">
-        <v>0</v>
-      </c>
-      <c r="L331" t="n">
-        <v>0</v>
-      </c>
-      <c r="M331" t="n">
-        <v>64</v>
-      </c>
-      <c r="N331" t="n">
-        <v>9917.040000000001</v>
-      </c>
-      <c r="O331" t="n">
-        <v>634690.5600000001</v>
-      </c>
-      <c r="P331" t="n">
-        <v>15900</v>
-      </c>
-      <c r="Q331" t="n">
         <v>1017600</v>
       </c>
     </row>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -1121,10 +1121,10 @@
         <v>36</v>
       </c>
       <c r="N18" t="n">
-        <v>12357.960428571</v>
+        <v>12357.960431655</v>
       </c>
       <c r="O18" t="n">
-        <v>444886.575428556</v>
+        <v>444886.57553958</v>
       </c>
       <c r="P18" t="n">
         <v>15900</v>
@@ -1277,10 +1277,10 @@
         <v>52</v>
       </c>
       <c r="N22" t="n">
-        <v>2785.6243902439</v>
+        <v>2681</v>
       </c>
       <c r="O22" t="n">
-        <v>144852.4682926828</v>
+        <v>139412</v>
       </c>
       <c r="P22" t="n">
         <v>3500</v>
@@ -2319,10 +2319,10 @@
         <v>120</v>
       </c>
       <c r="N47" t="n">
-        <v>2584.1380683507</v>
+        <v>2572.67</v>
       </c>
       <c r="O47" t="n">
-        <v>310096.568202084</v>
+        <v>308720.4</v>
       </c>
       <c r="P47" t="n">
         <v>4700</v>
@@ -3065,10 +3065,10 @@
         <v>350</v>
       </c>
       <c r="N64" t="n">
-        <v>2582.2548633316</v>
+        <v>2582.2548540429</v>
       </c>
       <c r="O64" t="n">
-        <v>903789.20216606</v>
+        <v>903789.1989150151</v>
       </c>
       <c r="P64" t="n">
         <v>4500</v>
@@ -3520,10 +3520,10 @@
         <v>346</v>
       </c>
       <c r="N74" t="n">
-        <v>4890.9300540176</v>
+        <v>4890.9300540541</v>
       </c>
       <c r="O74" t="n">
-        <v>1692261.798690089</v>
+        <v>1692261.798702718</v>
       </c>
       <c r="P74" t="n">
         <v>8200</v>
@@ -3653,10 +3653,10 @@
         <v>246</v>
       </c>
       <c r="N77" t="n">
-        <v>7063.376059322</v>
+        <v>7041</v>
       </c>
       <c r="O77" t="n">
-        <v>1737590.510593212</v>
+        <v>1732086</v>
       </c>
       <c r="P77" t="n">
         <v>11500</v>
@@ -3748,10 +3748,10 @@
         <v>216</v>
       </c>
       <c r="N79" t="n">
-        <v>3594.2528730512</v>
+        <v>3594.2528624535</v>
       </c>
       <c r="O79" t="n">
-        <v>776358.6205790592</v>
+        <v>776358.618289956</v>
       </c>
       <c r="P79" t="n">
         <v>6500</v>
@@ -3974,10 +3974,10 @@
         <v>2346</v>
       </c>
       <c r="N84" t="n">
-        <v>2093.3158067369</v>
+        <v>2090.85</v>
       </c>
       <c r="O84" t="n">
-        <v>4910918.882604768</v>
+        <v>4905134.1</v>
       </c>
       <c r="P84" t="n">
         <v>2900</v>
@@ -4299,10 +4299,10 @@
         <v>1584</v>
       </c>
       <c r="N91" t="n">
-        <v>3472.276319645</v>
+        <v>3472.276322317</v>
       </c>
       <c r="O91" t="n">
-        <v>5500085.69031768</v>
+        <v>5500085.694550128</v>
       </c>
       <c r="P91" t="n">
         <v>5900</v>
@@ -4660,10 +4660,10 @@
         <v>401</v>
       </c>
       <c r="N99" t="n">
-        <v>9677.770167910399</v>
+        <v>9414.309999999999</v>
       </c>
       <c r="O99" t="n">
-        <v>3880785.83733207</v>
+        <v>3775138.31</v>
       </c>
       <c r="P99" t="n">
         <v>16900</v>
@@ -6237,10 +6237,10 @@
         <v>900</v>
       </c>
       <c r="N134" t="n">
-        <v>6207.988218663</v>
+        <v>6207.9882181666</v>
       </c>
       <c r="O134" t="n">
-        <v>5587189.396796701</v>
+        <v>5587189.39634994</v>
       </c>
       <c r="P134" t="n">
         <v>9900</v>
@@ -6460,10 +6460,10 @@
         <v>948</v>
       </c>
       <c r="N139" t="n">
-        <v>4814.2679247144</v>
+        <v>4814.2679243911</v>
       </c>
       <c r="O139" t="n">
-        <v>4563925.992629251</v>
+        <v>4563925.992322762</v>
       </c>
       <c r="P139" t="n">
         <v>9900</v>
@@ -7455,10 +7455,10 @@
         <v>48</v>
       </c>
       <c r="N161" t="n">
-        <v>18873.018181818</v>
+        <v>18536</v>
       </c>
       <c r="O161" t="n">
-        <v>905904.872727264</v>
+        <v>889728</v>
       </c>
       <c r="P161" t="n">
         <v>30900</v>
@@ -8424,10 +8424,10 @@
         <v>180</v>
       </c>
       <c r="N182" t="n">
-        <v>10448.721014493</v>
+        <v>10411</v>
       </c>
       <c r="O182" t="n">
-        <v>1880769.78260874</v>
+        <v>1873980</v>
       </c>
       <c r="P182" t="n">
         <v>16900</v>
@@ -9656,10 +9656,10 @@
         <v>456</v>
       </c>
       <c r="N209" t="n">
-        <v>6650.5777839955</v>
+        <v>6645</v>
       </c>
       <c r="O209" t="n">
-        <v>3032663.469501948</v>
+        <v>3030120</v>
       </c>
       <c r="P209" t="n">
         <v>10900</v>
@@ -10484,10 +10484,10 @@
         <v>84</v>
       </c>
       <c r="N227" t="n">
-        <v>18170.288401254</v>
+        <v>18001</v>
       </c>
       <c r="O227" t="n">
-        <v>1526304.225705336</v>
+        <v>1512084</v>
       </c>
       <c r="P227" t="n">
         <v>28900</v>
@@ -11039,10 +11039,10 @@
         <v>279</v>
       </c>
       <c r="N239" t="n">
-        <v>10795.831156812</v>
+        <v>10713.21</v>
       </c>
       <c r="O239" t="n">
-        <v>3012036.892750548</v>
+        <v>2988985.59</v>
       </c>
       <c r="P239" t="n">
         <v>20900</v>
@@ -11499,10 +11499,10 @@
         <v>864</v>
       </c>
       <c r="N249" t="n">
-        <v>1516.0387131507</v>
+        <v>1516.0387126124</v>
       </c>
       <c r="O249" t="n">
-        <v>1309857.448162205</v>
+        <v>1309857.447697114</v>
       </c>
       <c r="P249" t="n">
         <v>2300</v>
@@ -12848,10 +12848,10 @@
         <v>14112</v>
       </c>
       <c r="N278" t="n">
-        <v>703.79465893216</v>
+        <v>703.79465786602</v>
       </c>
       <c r="O278" t="n">
-        <v>9931950.226850642</v>
+        <v>9931950.211805275</v>
       </c>
       <c r="P278" t="n">
         <v>900</v>
@@ -13800,10 +13800,10 @@
         <v>45</v>
       </c>
       <c r="N298" t="n">
-        <v>3099.0394791667</v>
+        <v>3067.090625</v>
       </c>
       <c r="O298" t="n">
-        <v>139456.7765625015</v>
+        <v>138019.078125</v>
       </c>
       <c r="P298" t="n">
         <v>7200</v>
@@ -13895,10 +13895,10 @@
         <v>19</v>
       </c>
       <c r="N300" t="n">
-        <v>4234.8833684211</v>
+        <v>4190.77</v>
       </c>
       <c r="O300" t="n">
-        <v>80462.7840000009</v>
+        <v>79624.63</v>
       </c>
       <c r="P300" t="n">
         <v>5900</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-25</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-26</t>
         </is>
       </c>
     </row>
@@ -720,10 +720,10 @@
         <v>298</v>
       </c>
       <c r="N8" t="n">
-        <v>3376.746386014</v>
+        <v>3376.7463829787</v>
       </c>
       <c r="O8" t="n">
-        <v>1006270.423032172</v>
+        <v>1006270.422127653</v>
       </c>
       <c r="P8" t="n">
         <v>4500</v>
@@ -1199,10 +1199,10 @@
         <v>180</v>
       </c>
       <c r="N20" t="n">
-        <v>3926.8370726607</v>
+        <v>3926.8370711297</v>
       </c>
       <c r="O20" t="n">
-        <v>706830.673078926</v>
+        <v>706830.672803346</v>
       </c>
       <c r="P20" t="n">
         <v>4800</v>
@@ -1688,10 +1688,10 @@
         <v>4</v>
       </c>
       <c r="N32" t="n">
-        <v>62349.638888889</v>
+        <v>62349.636470588</v>
       </c>
       <c r="O32" t="n">
-        <v>249398.555555556</v>
+        <v>249398.545882352</v>
       </c>
       <c r="P32" t="n">
         <v>109900</v>
@@ -3065,10 +3065,10 @@
         <v>350</v>
       </c>
       <c r="N64" t="n">
-        <v>2582.2548540429</v>
+        <v>2582.2548393782</v>
       </c>
       <c r="O64" t="n">
-        <v>903789.1989150151</v>
+        <v>903789.19378237</v>
       </c>
       <c r="P64" t="n">
         <v>4500</v>
@@ -3157,10 +3157,10 @@
         <v>2592</v>
       </c>
       <c r="N66" t="n">
-        <v>3158.8608413965</v>
+        <v>3158.8608416484</v>
       </c>
       <c r="O66" t="n">
-        <v>8187767.300899727</v>
+        <v>8187767.301552652</v>
       </c>
       <c r="P66" t="n">
         <v>5600</v>
@@ -3520,10 +3520,10 @@
         <v>346</v>
       </c>
       <c r="N74" t="n">
-        <v>4890.9300540541</v>
+        <v>4890.9300548321</v>
       </c>
       <c r="O74" t="n">
-        <v>1692261.798702718</v>
+        <v>1692261.798971907</v>
       </c>
       <c r="P74" t="n">
         <v>8200</v>
@@ -3748,10 +3748,10 @@
         <v>216</v>
       </c>
       <c r="N79" t="n">
-        <v>3594.2528624535</v>
+        <v>3594.2528571429</v>
       </c>
       <c r="O79" t="n">
-        <v>776358.618289956</v>
+        <v>776358.6171428665</v>
       </c>
       <c r="P79" t="n">
         <v>6500</v>
@@ -4389,10 +4389,10 @@
         <v>1356</v>
       </c>
       <c r="N93" t="n">
-        <v>4371.1712639913</v>
+        <v>4371.1712646818</v>
       </c>
       <c r="O93" t="n">
-        <v>5927308.233972203</v>
+        <v>5927308.23490852</v>
       </c>
       <c r="P93" t="n">
         <v>8900</v>
@@ -6237,10 +6237,10 @@
         <v>900</v>
       </c>
       <c r="N134" t="n">
-        <v>6207.9882181666</v>
+        <v>6207.9882044083</v>
       </c>
       <c r="O134" t="n">
-        <v>5587189.39634994</v>
+        <v>5587189.383967469</v>
       </c>
       <c r="P134" t="n">
         <v>9900</v>
@@ -6286,10 +6286,10 @@
         <v>36</v>
       </c>
       <c r="N135" t="n">
-        <v>4285.1964713376</v>
+        <v>4285.196521181</v>
       </c>
       <c r="O135" t="n">
-        <v>154267.0729681536</v>
+        <v>154267.074762516</v>
       </c>
       <c r="P135" t="n">
         <v>6900</v>
@@ -6460,10 +6460,10 @@
         <v>948</v>
       </c>
       <c r="N139" t="n">
-        <v>4814.2679243911</v>
+        <v>4814.2679220172</v>
       </c>
       <c r="O139" t="n">
-        <v>4563925.992322762</v>
+        <v>4563925.990072306</v>
       </c>
       <c r="P139" t="n">
         <v>9900</v>
@@ -6535,7 +6535,7 @@
         </is>
       </c>
       <c r="J141" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K141" t="n">
         <v>0</v>
@@ -6544,19 +6544,19 @@
         <v>0</v>
       </c>
       <c r="M141" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="N141" t="n">
         <v>60174</v>
       </c>
       <c r="O141" t="n">
-        <v>5656356</v>
+        <v>5596182</v>
       </c>
       <c r="P141" t="n">
         <v>96900</v>
       </c>
       <c r="Q141" t="n">
-        <v>9108600</v>
+        <v>9011700</v>
       </c>
     </row>
     <row r="142">
@@ -9518,10 +9518,10 @@
         <v>144</v>
       </c>
       <c r="N206" t="n">
-        <v>5869.1723216187</v>
+        <v>5869.1723052295</v>
       </c>
       <c r="O206" t="n">
-        <v>845160.8143130929</v>
+        <v>845160.811953048</v>
       </c>
       <c r="P206" t="n">
         <v>9500</v>
@@ -10300,10 +10300,10 @@
         <v>192</v>
       </c>
       <c r="N223" t="n">
-        <v>17075.989516129</v>
+        <v>17075.989515789</v>
       </c>
       <c r="O223" t="n">
-        <v>3278589.987096768</v>
+        <v>3278589.987031488</v>
       </c>
       <c r="P223" t="n">
         <v>27500</v>
@@ -11499,10 +11499,10 @@
         <v>864</v>
       </c>
       <c r="N249" t="n">
-        <v>1516.0387126124</v>
+        <v>1516.0387122084</v>
       </c>
       <c r="O249" t="n">
-        <v>1309857.447697114</v>
+        <v>1309857.447348058</v>
       </c>
       <c r="P249" t="n">
         <v>2300</v>
@@ -11960,7 +11960,7 @@
         </is>
       </c>
       <c r="J259" t="n">
-        <v>634</v>
+        <v>604</v>
       </c>
       <c r="K259" t="n">
         <v>0</v>
@@ -11969,19 +11969,19 @@
         <v>0</v>
       </c>
       <c r="M259" t="n">
-        <v>634</v>
+        <v>604</v>
       </c>
       <c r="N259" t="n">
         <v>5215</v>
       </c>
       <c r="O259" t="n">
-        <v>3306310</v>
+        <v>3149860</v>
       </c>
       <c r="P259" t="n">
         <v>8900</v>
       </c>
       <c r="Q259" t="n">
-        <v>5642600</v>
+        <v>5375600</v>
       </c>
     </row>
     <row r="260">
@@ -12848,10 +12848,10 @@
         <v>14112</v>
       </c>
       <c r="N278" t="n">
-        <v>703.79465786602</v>
+        <v>703.79463731331</v>
       </c>
       <c r="O278" t="n">
-        <v>9931950.211805275</v>
+        <v>9931949.92176543</v>
       </c>
       <c r="P278" t="n">
         <v>900</v>
@@ -13033,10 +13033,10 @@
         <v>208</v>
       </c>
       <c r="N282" t="n">
-        <v>6078.9926048565</v>
+        <v>6078.992616408</v>
       </c>
       <c r="O282" t="n">
-        <v>1264430.461810152</v>
+        <v>1264430.464212864</v>
       </c>
       <c r="P282" t="n">
         <v>18500</v>
@@ -14088,10 +14088,10 @@
         <v>120</v>
       </c>
       <c r="N304" t="n">
-        <v>4159.0003007519</v>
+        <v>4159.0003030303</v>
       </c>
       <c r="O304" t="n">
-        <v>499080.036090228</v>
+        <v>499080.036363636</v>
       </c>
       <c r="P304" t="n">
         <v>8900</v>
@@ -14513,10 +14513,10 @@
         <v>499</v>
       </c>
       <c r="N313" t="n">
-        <v>7046.9398263889</v>
+        <v>7046.9398263512</v>
       </c>
       <c r="O313" t="n">
-        <v>3516422.973368061</v>
+        <v>3516422.973349249</v>
       </c>
       <c r="P313" t="n">
         <v>9900</v>
@@ -15068,10 +15068,10 @@
         <v>179</v>
       </c>
       <c r="N325" t="n">
-        <v>13493.858292683</v>
+        <v>13493.858287462</v>
       </c>
       <c r="O325" t="n">
-        <v>2415400.634390257</v>
+        <v>2415400.633455698</v>
       </c>
       <c r="P325" t="n">
         <v>16900</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -10579,10 +10579,10 @@
         <v>420</v>
       </c>
       <c r="N229" t="n">
-        <v>10755</v>
+        <v>10795.738636364</v>
       </c>
       <c r="O229" t="n">
-        <v>4517100</v>
+        <v>4534210.22727288</v>
       </c>
       <c r="P229" t="n">
         <v>17900</v>
@@ -12848,10 +12848,10 @@
         <v>14112</v>
       </c>
       <c r="N278" t="n">
-        <v>703.79463731331</v>
+        <v>703.79463559345</v>
       </c>
       <c r="O278" t="n">
-        <v>9931949.92176543</v>
+        <v>9931949.897494767</v>
       </c>
       <c r="P278" t="n">
         <v>900</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-27</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-28</t>
         </is>
       </c>
     </row>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -550,22 +550,22 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M4" t="n">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="N4" t="n">
-        <v>27000</v>
+        <v>27065.693430657</v>
       </c>
       <c r="O4" t="n">
-        <v>8910000</v>
+        <v>8850481.751824839</v>
       </c>
       <c r="P4" t="n">
         <v>20000</v>
       </c>
       <c r="Q4" t="n">
-        <v>6600000</v>
+        <v>6540000</v>
       </c>
     </row>
     <row r="5">
@@ -642,10 +642,10 @@
         <v>275</v>
       </c>
       <c r="N6" t="n">
-        <v>27000</v>
+        <v>27109.756097561</v>
       </c>
       <c r="O6" t="n">
-        <v>7425000</v>
+        <v>7455182.926829275</v>
       </c>
       <c r="P6" t="n">
         <v>20000</v>
@@ -965,10 +965,10 @@
         <v>130</v>
       </c>
       <c r="N14" t="n">
-        <v>27000</v>
+        <v>27267.326732673</v>
       </c>
       <c r="O14" t="n">
-        <v>3510000</v>
+        <v>3544752.47524749</v>
       </c>
       <c r="P14" t="n">
         <v>20000</v>
@@ -1004,10 +1004,10 @@
         <v>172</v>
       </c>
       <c r="N15" t="n">
-        <v>27000</v>
+        <v>27151.898734177</v>
       </c>
       <c r="O15" t="n">
-        <v>4644000</v>
+        <v>4670126.582278444</v>
       </c>
       <c r="P15" t="n">
         <v>20000</v>
@@ -1199,10 +1199,10 @@
         <v>180</v>
       </c>
       <c r="N20" t="n">
-        <v>3926.8370711297</v>
+        <v>3926.837066527</v>
       </c>
       <c r="O20" t="n">
-        <v>706830.672803346</v>
+        <v>706830.67197486</v>
       </c>
       <c r="P20" t="n">
         <v>4800</v>
@@ -1871,10 +1871,10 @@
         <v>62</v>
       </c>
       <c r="N36" t="n">
-        <v>27000</v>
+        <v>27352.173913043</v>
       </c>
       <c r="O36" t="n">
-        <v>1674000</v>
+        <v>1695834.782608666</v>
       </c>
       <c r="P36" t="n">
         <v>20000</v>
@@ -3065,10 +3065,10 @@
         <v>350</v>
       </c>
       <c r="N64" t="n">
-        <v>2582.2548125</v>
+        <v>2582.2547989556</v>
       </c>
       <c r="O64" t="n">
-        <v>903789.184375</v>
+        <v>903789.17963446</v>
       </c>
       <c r="P64" t="n">
         <v>4500</v>
@@ -3105,22 +3105,22 @@
         <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M65" t="n">
-        <v>1122</v>
+        <v>1102</v>
       </c>
       <c r="N65" t="n">
         <v>5216.895823058</v>
       </c>
       <c r="O65" t="n">
-        <v>5853357.113471076</v>
+        <v>5749019.197009916</v>
       </c>
       <c r="P65" t="n">
         <v>8500</v>
       </c>
       <c r="Q65" t="n">
-        <v>9537000</v>
+        <v>9367000</v>
       </c>
     </row>
     <row r="66">
@@ -3376,22 +3376,22 @@
         <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M71" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N71" t="n">
         <v>2612.77</v>
       </c>
       <c r="O71" t="n">
-        <v>261277</v>
+        <v>253438.69</v>
       </c>
       <c r="P71" t="n">
         <v>4900</v>
       </c>
       <c r="Q71" t="n">
-        <v>490000</v>
+        <v>475300</v>
       </c>
     </row>
     <row r="72">
@@ -3474,10 +3474,10 @@
         <v>296</v>
       </c>
       <c r="N73" t="n">
-        <v>4890.9300552868</v>
+        <v>4890.930055517</v>
       </c>
       <c r="O73" t="n">
-        <v>1447715.296364893</v>
+        <v>1447715.296433032</v>
       </c>
       <c r="P73" t="n">
         <v>8200</v>
@@ -3840,10 +3840,10 @@
         <v>291</v>
       </c>
       <c r="N81" t="n">
-        <v>14822.378817006</v>
+        <v>14822.378814083</v>
       </c>
       <c r="O81" t="n">
-        <v>4313312.235748746</v>
+        <v>4313312.234898153</v>
       </c>
       <c r="P81" t="n">
         <v>24900</v>
@@ -4161,10 +4161,10 @@
         <v>336</v>
       </c>
       <c r="N88" t="n">
-        <v>12422.463007951</v>
+        <v>12422.463013274</v>
       </c>
       <c r="O88" t="n">
-        <v>4173947.570671536</v>
+        <v>4173947.572460064</v>
       </c>
       <c r="P88" t="n">
         <v>19900</v>
@@ -4253,10 +4253,10 @@
         <v>1584</v>
       </c>
       <c r="N90" t="n">
-        <v>3472.2763500602</v>
+        <v>3472.2763717066</v>
       </c>
       <c r="O90" t="n">
-        <v>5500085.738495356</v>
+        <v>5500085.772783254</v>
       </c>
       <c r="P90" t="n">
         <v>5900</v>
@@ -4343,10 +4343,10 @@
         <v>1356</v>
       </c>
       <c r="N92" t="n">
-        <v>4371.1729689003</v>
+        <v>4371.1729703288</v>
       </c>
       <c r="O92" t="n">
-        <v>5927310.545828806</v>
+        <v>5927310.547765853</v>
       </c>
       <c r="P92" t="n">
         <v>8900</v>
@@ -5748,10 +5748,10 @@
         <v>432</v>
       </c>
       <c r="N123" t="n">
-        <v>2029.8742253521</v>
+        <v>2029.8742541123</v>
       </c>
       <c r="O123" t="n">
-        <v>876905.6653521071</v>
+        <v>876905.6777765136</v>
       </c>
       <c r="P123" t="n">
         <v>3600</v>
@@ -5961,10 +5961,10 @@
         <v>310</v>
       </c>
       <c r="N128" t="n">
-        <v>2680.7396931747</v>
+        <v>2680.7396929825</v>
       </c>
       <c r="O128" t="n">
-        <v>831029.3048841569</v>
+        <v>831029.304824575</v>
       </c>
       <c r="P128" t="n">
         <v>4900</v>
@@ -6053,10 +6053,10 @@
         <v>192</v>
       </c>
       <c r="N130" t="n">
-        <v>30611</v>
+        <v>30745.062773723</v>
       </c>
       <c r="O130" t="n">
-        <v>5877312</v>
+        <v>5903052.052554816</v>
       </c>
       <c r="P130" t="n">
         <v>38900</v>
@@ -6185,22 +6185,22 @@
         <v>0</v>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M133" t="n">
-        <v>900</v>
+        <v>850</v>
       </c>
       <c r="N133" t="n">
-        <v>6207.9882021366</v>
+        <v>6207.9882013781</v>
       </c>
       <c r="O133" t="n">
-        <v>5587189.38192294</v>
+        <v>5276789.971171385</v>
       </c>
       <c r="P133" t="n">
         <v>9900</v>
       </c>
       <c r="Q133" t="n">
-        <v>8910000</v>
+        <v>8415000</v>
       </c>
     </row>
     <row r="134">
@@ -6240,10 +6240,10 @@
         <v>36</v>
       </c>
       <c r="N134" t="n">
-        <v>4285.1965633075</v>
+        <v>4285.1966145833</v>
       </c>
       <c r="O134" t="n">
-        <v>154267.07627907</v>
+        <v>154267.0781249988</v>
       </c>
       <c r="P134" t="n">
         <v>6900</v>
@@ -6414,10 +6414,10 @@
         <v>908</v>
       </c>
       <c r="N138" t="n">
-        <v>4814.2633769677</v>
+        <v>4814.2633736737</v>
       </c>
       <c r="O138" t="n">
-        <v>4371351.146286672</v>
+        <v>4371351.143295719</v>
       </c>
       <c r="P138" t="n">
         <v>9900</v>
@@ -6818,10 +6818,10 @@
         <v>144</v>
       </c>
       <c r="N147" t="n">
-        <v>27123.764688797</v>
+        <v>27123.764610526</v>
       </c>
       <c r="O147" t="n">
-        <v>3905822.115186768</v>
+        <v>3905822.103915744</v>
       </c>
       <c r="P147" t="n">
         <v>44500</v>
@@ -6910,10 +6910,10 @@
         <v>221</v>
       </c>
       <c r="N149" t="n">
-        <v>8332.7796042216</v>
+        <v>8332.7795967742</v>
       </c>
       <c r="O149" t="n">
-        <v>1841544.292532973</v>
+        <v>1841544.290887098</v>
       </c>
       <c r="P149" t="n">
         <v>14900</v>
@@ -7002,10 +7002,10 @@
         <v>144</v>
       </c>
       <c r="N151" t="n">
-        <v>26854</v>
+        <v>27080.935211268</v>
       </c>
       <c r="O151" t="n">
-        <v>3866976</v>
+        <v>3899654.670422592</v>
       </c>
       <c r="P151" t="n">
         <v>43900</v>
@@ -7644,10 +7644,10 @@
         <v>680</v>
       </c>
       <c r="N165" t="n">
-        <v>1778.4728840436</v>
+        <v>1778.4728878597</v>
       </c>
       <c r="O165" t="n">
-        <v>1209361.561149648</v>
+        <v>1209361.563744596</v>
       </c>
       <c r="P165" t="n">
         <v>4900</v>
@@ -7690,10 +7690,10 @@
         <v>192</v>
       </c>
       <c r="N166" t="n">
-        <v>22739</v>
+        <v>22935.194995686</v>
       </c>
       <c r="O166" t="n">
-        <v>4365888</v>
+        <v>4403557.439171712</v>
       </c>
       <c r="P166" t="n">
         <v>36900</v>
@@ -7782,10 +7782,10 @@
         <v>160</v>
       </c>
       <c r="N168" t="n">
-        <v>16058</v>
+        <v>16177.301634473</v>
       </c>
       <c r="O168" t="n">
-        <v>2569280</v>
+        <v>2588368.26151568</v>
       </c>
       <c r="P168" t="n">
         <v>25900</v>
@@ -8153,10 +8153,10 @@
         <v>30</v>
       </c>
       <c r="N176" t="n">
-        <v>11857</v>
+        <v>12344.273972603</v>
       </c>
       <c r="O176" t="n">
-        <v>355710</v>
+        <v>370328.21917809</v>
       </c>
       <c r="P176" t="n">
         <v>19900</v>
@@ -8245,10 +8245,10 @@
         <v>12</v>
       </c>
       <c r="N178" t="n">
-        <v>28116</v>
+        <v>28661.941747573</v>
       </c>
       <c r="O178" t="n">
-        <v>337392</v>
+        <v>343943.300970876</v>
       </c>
       <c r="P178" t="n">
         <v>45900</v>
@@ -8653,22 +8653,22 @@
         <v>0</v>
       </c>
       <c r="L187" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M187" t="n">
-        <v>175</v>
+        <v>75</v>
       </c>
       <c r="N187" t="n">
-        <v>3519</v>
+        <v>4129.9375</v>
       </c>
       <c r="O187" t="n">
-        <v>615825</v>
+        <v>309745.3125</v>
       </c>
       <c r="P187" t="n">
         <v>5900</v>
       </c>
       <c r="Q187" t="n">
-        <v>1032500</v>
+        <v>442500</v>
       </c>
     </row>
     <row r="188">
@@ -9114,10 +9114,10 @@
         <v>40</v>
       </c>
       <c r="N197" t="n">
-        <v>20726</v>
+        <v>21286.162162162</v>
       </c>
       <c r="O197" t="n">
-        <v>829040</v>
+        <v>851446.48648648</v>
       </c>
       <c r="P197" t="n">
         <v>33900</v>
@@ -9201,10 +9201,10 @@
         <v>46</v>
       </c>
       <c r="N199" t="n">
-        <v>20731</v>
+        <v>21767.55</v>
       </c>
       <c r="O199" t="n">
-        <v>953626</v>
+        <v>1001307.3</v>
       </c>
       <c r="P199" t="n">
         <v>33900</v>
@@ -9799,10 +9799,10 @@
         <v>245</v>
       </c>
       <c r="N212" t="n">
-        <v>13565</v>
+        <v>13585.998452012</v>
       </c>
       <c r="O212" t="n">
-        <v>3323425</v>
+        <v>3328569.62074294</v>
       </c>
       <c r="P212" t="n">
         <v>22500</v>
@@ -9937,10 +9937,10 @@
         <v>48</v>
       </c>
       <c r="N215" t="n">
-        <v>16086</v>
+        <v>16443.466666667</v>
       </c>
       <c r="O215" t="n">
-        <v>772128</v>
+        <v>789286.400000016</v>
       </c>
       <c r="P215" t="n">
         <v>25900</v>
@@ -10029,10 +10029,10 @@
         <v>180</v>
       </c>
       <c r="N217" t="n">
-        <v>19008</v>
+        <v>19059.165545087</v>
       </c>
       <c r="O217" t="n">
-        <v>3421440</v>
+        <v>3430649.79811566</v>
       </c>
       <c r="P217" t="n">
         <v>30900</v>
@@ -10121,10 +10121,10 @@
         <v>180</v>
       </c>
       <c r="N219" t="n">
-        <v>17992</v>
+        <v>18038.854166667</v>
       </c>
       <c r="O219" t="n">
-        <v>3238560</v>
+        <v>3246993.75000006</v>
       </c>
       <c r="P219" t="n">
         <v>28900</v>
@@ -10213,10 +10213,10 @@
         <v>192</v>
       </c>
       <c r="N221" t="n">
-        <v>17075.989515789</v>
+        <v>17112.014810127</v>
       </c>
       <c r="O221" t="n">
-        <v>3278589.987031488</v>
+        <v>3285506.843544384</v>
       </c>
       <c r="P221" t="n">
         <v>27500</v>
@@ -10998,10 +10998,10 @@
         <v>159</v>
       </c>
       <c r="N238" t="n">
-        <v>10817</v>
+        <v>10997.283333333</v>
       </c>
       <c r="O238" t="n">
-        <v>1719903</v>
+        <v>1748568.049999947</v>
       </c>
       <c r="P238" t="n">
         <v>17900</v>
@@ -11044,10 +11044,10 @@
         <v>79</v>
       </c>
       <c r="N239" t="n">
-        <v>12489</v>
+        <v>12769.651685393</v>
       </c>
       <c r="O239" t="n">
-        <v>986631</v>
+        <v>1008802.483146047</v>
       </c>
       <c r="P239" t="n">
         <v>20900</v>
@@ -11182,10 +11182,10 @@
         <v>144</v>
       </c>
       <c r="N242" t="n">
-        <v>15472</v>
+        <v>15602.016806723</v>
       </c>
       <c r="O242" t="n">
-        <v>2227968</v>
+        <v>2246690.420168112</v>
       </c>
       <c r="P242" t="n">
         <v>25900</v>
@@ -11588,22 +11588,22 @@
         <v>0</v>
       </c>
       <c r="L251" t="n">
-        <v>0</v>
+        <v>432</v>
       </c>
       <c r="M251" t="n">
-        <v>4464</v>
+        <v>4032</v>
       </c>
       <c r="N251" t="n">
         <v>1801</v>
       </c>
       <c r="O251" t="n">
-        <v>8039664</v>
+        <v>7261632</v>
       </c>
       <c r="P251" t="n">
         <v>2900</v>
       </c>
       <c r="Q251" t="n">
-        <v>12945600</v>
+        <v>11692800</v>
       </c>
     </row>
     <row r="252">
@@ -11732,22 +11732,22 @@
         <v>0</v>
       </c>
       <c r="L254" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M254" t="n">
-        <v>348</v>
+        <v>276</v>
       </c>
       <c r="N254" t="n">
         <v>13518</v>
       </c>
       <c r="O254" t="n">
-        <v>4704264</v>
+        <v>3730968</v>
       </c>
       <c r="P254" t="n">
         <v>21900</v>
       </c>
       <c r="Q254" t="n">
-        <v>7621200</v>
+        <v>6044400</v>
       </c>
     </row>
     <row r="255">
@@ -12207,10 +12207,10 @@
         <v>1440</v>
       </c>
       <c r="N264" t="n">
-        <v>1690.8700095969</v>
+        <v>1690.8700097561</v>
       </c>
       <c r="O264" t="n">
-        <v>2434852.813819536</v>
+        <v>2434852.814048784</v>
       </c>
       <c r="P264" t="n">
         <v>3000</v>
@@ -12761,10 +12761,10 @@
         <v>14112</v>
       </c>
       <c r="N276" t="n">
-        <v>703.79459507493</v>
+        <v>703.79459259958</v>
       </c>
       <c r="O276" t="n">
-        <v>9931949.325697413</v>
+        <v>9931949.290765272</v>
       </c>
       <c r="P276" t="n">
         <v>900</v>
@@ -13713,10 +13713,10 @@
         <v>45</v>
       </c>
       <c r="N296" t="n">
-        <v>3067.0906293706</v>
+        <v>3099.6039575972</v>
       </c>
       <c r="O296" t="n">
-        <v>138019.078321677</v>
+        <v>139482.178091874</v>
       </c>
       <c r="P296" t="n">
         <v>7200</v>
@@ -14093,10 +14093,10 @@
         <v>11</v>
       </c>
       <c r="N304" t="n">
-        <v>14751.820338983</v>
+        <v>15571.365925926</v>
       </c>
       <c r="O304" t="n">
-        <v>162270.023728813</v>
+        <v>171285.025185186</v>
       </c>
       <c r="P304" t="n">
         <v>37100</v>
@@ -14142,10 +14142,10 @@
         <v>15</v>
       </c>
       <c r="N305" t="n">
-        <v>15347.45</v>
+        <v>15516.103296703</v>
       </c>
       <c r="O305" t="n">
-        <v>230211.75</v>
+        <v>232741.549450545</v>
       </c>
       <c r="P305" t="n">
         <v>23900</v>
@@ -14472,10 +14472,10 @@
         <v>30</v>
       </c>
       <c r="N312" t="n">
-        <v>24338.47</v>
+        <v>24856.309787234</v>
       </c>
       <c r="O312" t="n">
-        <v>730154.1000000001</v>
+        <v>745689.29361702</v>
       </c>
       <c r="P312" t="n">
         <v>27900</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q328"/>
+  <dimension ref="A1:Q327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-28</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-29</t>
         </is>
       </c>
     </row>
@@ -544,22 +544,22 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>327</v>
       </c>
       <c r="N4" t="n">
-        <v>27065.693430657</v>
+        <v>27000</v>
       </c>
       <c r="O4" t="n">
-        <v>8850481.751824839</v>
+        <v>8829000</v>
       </c>
       <c r="P4" t="n">
         <v>20000</v>
@@ -720,10 +720,10 @@
         <v>298</v>
       </c>
       <c r="N8" t="n">
-        <v>3376.7463799384</v>
+        <v>3376.7463585118</v>
       </c>
       <c r="O8" t="n">
-        <v>1006270.421221643</v>
+        <v>1006270.414836516</v>
       </c>
       <c r="P8" t="n">
         <v>4500</v>
@@ -965,10 +965,10 @@
         <v>130</v>
       </c>
       <c r="N14" t="n">
-        <v>27267.326732673</v>
+        <v>27000</v>
       </c>
       <c r="O14" t="n">
-        <v>3544752.47524749</v>
+        <v>3510000</v>
       </c>
       <c r="P14" t="n">
         <v>20000</v>
@@ -1004,10 +1004,10 @@
         <v>172</v>
       </c>
       <c r="N15" t="n">
-        <v>27151.898734177</v>
+        <v>27000</v>
       </c>
       <c r="O15" t="n">
-        <v>4670126.582278444</v>
+        <v>4644000</v>
       </c>
       <c r="P15" t="n">
         <v>20000</v>
@@ -1199,10 +1199,10 @@
         <v>180</v>
       </c>
       <c r="N20" t="n">
-        <v>3926.837066527</v>
+        <v>3926.837057278</v>
       </c>
       <c r="O20" t="n">
-        <v>706830.67197486</v>
+        <v>706830.67031004</v>
       </c>
       <c r="P20" t="n">
         <v>4800</v>
@@ -1735,10 +1735,10 @@
         <v>65</v>
       </c>
       <c r="N33" t="n">
-        <v>141416.88465116</v>
+        <v>141416.88463576</v>
       </c>
       <c r="O33" t="n">
-        <v>9192097.502325401</v>
+        <v>9192097.5013244</v>
       </c>
       <c r="P33" t="n">
         <v>251900</v>
@@ -1871,10 +1871,10 @@
         <v>62</v>
       </c>
       <c r="N36" t="n">
-        <v>27352.173913043</v>
+        <v>27000</v>
       </c>
       <c r="O36" t="n">
-        <v>1695834.782608666</v>
+        <v>1674000</v>
       </c>
       <c r="P36" t="n">
         <v>20000</v>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -1946,19 +1946,19 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="N38" t="n">
         <v>26280.41</v>
       </c>
       <c r="O38" t="n">
-        <v>1261459.68</v>
+        <v>946094.76</v>
       </c>
       <c r="P38" t="n">
         <v>46500</v>
       </c>
       <c r="Q38" t="n">
-        <v>2232000</v>
+        <v>1674000</v>
       </c>
     </row>
     <row r="39">
@@ -2015,7 +2015,7 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -2024,19 +2024,19 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="N40" t="n">
-        <v>61666.874389535</v>
+        <v>61666.874467456</v>
       </c>
       <c r="O40" t="n">
-        <v>4748349.327994195</v>
+        <v>4378348.087189376</v>
       </c>
       <c r="P40" t="n">
         <v>98900</v>
       </c>
       <c r="Q40" t="n">
-        <v>7615300</v>
+        <v>7021900</v>
       </c>
     </row>
     <row r="41">
@@ -3065,10 +3065,10 @@
         <v>350</v>
       </c>
       <c r="N64" t="n">
-        <v>2582.2547989556</v>
+        <v>2582.25476203</v>
       </c>
       <c r="O64" t="n">
-        <v>903789.17963446</v>
+        <v>903789.1667105</v>
       </c>
       <c r="P64" t="n">
         <v>4500</v>
@@ -3099,22 +3099,22 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>1122</v>
+        <v>1102</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
         <v>1102</v>
       </c>
       <c r="N65" t="n">
-        <v>5216.895823058</v>
+        <v>5216.8958101422</v>
       </c>
       <c r="O65" t="n">
-        <v>5749019.197009916</v>
+        <v>5749019.182776704</v>
       </c>
       <c r="P65" t="n">
         <v>8500</v>
@@ -3157,10 +3157,10 @@
         <v>2592</v>
       </c>
       <c r="N66" t="n">
-        <v>3158.8608423208</v>
+        <v>3158.8608436687</v>
       </c>
       <c r="O66" t="n">
-        <v>8187767.303295515</v>
+        <v>8187767.306789271</v>
       </c>
       <c r="P66" t="n">
         <v>5600</v>
@@ -3370,13 +3370,13 @@
         </is>
       </c>
       <c r="J71" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
         <v>97</v>
@@ -3474,10 +3474,10 @@
         <v>296</v>
       </c>
       <c r="N73" t="n">
-        <v>4890.930055517</v>
+        <v>4890.9300565371</v>
       </c>
       <c r="O73" t="n">
-        <v>1447715.296433032</v>
+        <v>1447715.296734982</v>
       </c>
       <c r="P73" t="n">
         <v>8200</v>
@@ -4161,10 +4161,10 @@
         <v>336</v>
       </c>
       <c r="N88" t="n">
-        <v>12422.463013274</v>
+        <v>12422.46300928</v>
       </c>
       <c r="O88" t="n">
-        <v>4173947.572460064</v>
+        <v>4173947.57111808</v>
       </c>
       <c r="P88" t="n">
         <v>19900</v>
@@ -4253,10 +4253,10 @@
         <v>1584</v>
       </c>
       <c r="N90" t="n">
-        <v>3472.2763717066</v>
+        <v>3472.2763744227</v>
       </c>
       <c r="O90" t="n">
-        <v>5500085.772783254</v>
+        <v>5500085.777085557</v>
       </c>
       <c r="P90" t="n">
         <v>5900</v>
@@ -4343,10 +4343,10 @@
         <v>1356</v>
       </c>
       <c r="N92" t="n">
-        <v>4371.1729703288</v>
+        <v>4371.1729731899</v>
       </c>
       <c r="O92" t="n">
-        <v>5927310.547765853</v>
+        <v>5927310.551645505</v>
       </c>
       <c r="P92" t="n">
         <v>8900</v>
@@ -5789,10 +5789,10 @@
         <v>528</v>
       </c>
       <c r="N124" t="n">
-        <v>22485.695396419</v>
+        <v>22485.695378691</v>
       </c>
       <c r="O124" t="n">
-        <v>11872447.16930923</v>
+        <v>11872447.15994885</v>
       </c>
       <c r="P124" t="n">
         <v>36500</v>
@@ -6179,22 +6179,22 @@
         </is>
       </c>
       <c r="J133" t="n">
-        <v>900</v>
+        <v>850</v>
       </c>
       <c r="K133" t="n">
         <v>0</v>
       </c>
       <c r="L133" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
         <v>850</v>
       </c>
       <c r="N133" t="n">
-        <v>6207.9882013781</v>
+        <v>6207.9882003658</v>
       </c>
       <c r="O133" t="n">
-        <v>5276789.971171385</v>
+        <v>5276789.97031093</v>
       </c>
       <c r="P133" t="n">
         <v>9900</v>
@@ -6368,10 +6368,10 @@
         <v>55</v>
       </c>
       <c r="N137" t="n">
-        <v>30244.600034965</v>
+        <v>30244.600034985</v>
       </c>
       <c r="O137" t="n">
-        <v>1663453.001923075</v>
+        <v>1663453.001924175</v>
       </c>
       <c r="P137" t="n">
         <v>48900</v>
@@ -6414,10 +6414,10 @@
         <v>908</v>
       </c>
       <c r="N138" t="n">
-        <v>4814.2633736737</v>
+        <v>4814.2633472037</v>
       </c>
       <c r="O138" t="n">
-        <v>4371351.143295719</v>
+        <v>4371351.119260959</v>
       </c>
       <c r="P138" t="n">
         <v>9900</v>
@@ -6461,10 +6461,10 @@
         <v>4180075.32</v>
       </c>
       <c r="P139" t="n">
-        <v>6300</v>
+        <v>6900</v>
       </c>
       <c r="Q139" t="n">
-        <v>7333200</v>
+        <v>8031600</v>
       </c>
     </row>
     <row r="140">
@@ -7356,7 +7356,7 @@
         </is>
       </c>
       <c r="J159" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="K159" t="n">
         <v>0</v>
@@ -7365,19 +7365,19 @@
         <v>0</v>
       </c>
       <c r="M159" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="N159" t="n">
         <v>18536</v>
       </c>
       <c r="O159" t="n">
-        <v>889728</v>
+        <v>778512</v>
       </c>
       <c r="P159" t="n">
         <v>30900</v>
       </c>
       <c r="Q159" t="n">
-        <v>1483200</v>
+        <v>1297800</v>
       </c>
     </row>
     <row r="160">
@@ -7644,10 +7644,10 @@
         <v>680</v>
       </c>
       <c r="N165" t="n">
-        <v>1778.4728878597</v>
+        <v>1778.4728955224</v>
       </c>
       <c r="O165" t="n">
-        <v>1209361.563744596</v>
+        <v>1209361.568955232</v>
       </c>
       <c r="P165" t="n">
         <v>4900</v>
@@ -7782,10 +7782,10 @@
         <v>160</v>
       </c>
       <c r="N168" t="n">
-        <v>16177.301634473</v>
+        <v>16058</v>
       </c>
       <c r="O168" t="n">
-        <v>2588368.26151568</v>
+        <v>2569280</v>
       </c>
       <c r="P168" t="n">
         <v>25900</v>
@@ -8647,22 +8647,22 @@
         </is>
       </c>
       <c r="J187" t="n">
-        <v>175</v>
+        <v>75</v>
       </c>
       <c r="K187" t="n">
         <v>0</v>
       </c>
       <c r="L187" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M187" t="n">
         <v>75</v>
       </c>
       <c r="N187" t="n">
-        <v>4129.9375</v>
+        <v>3519</v>
       </c>
       <c r="O187" t="n">
-        <v>309745.3125</v>
+        <v>263925</v>
       </c>
       <c r="P187" t="n">
         <v>5900</v>
@@ -9073,10 +9073,10 @@
         <v>129</v>
       </c>
       <c r="N196" t="n">
-        <v>3903.7399452055</v>
+        <v>3903.7403351955</v>
       </c>
       <c r="O196" t="n">
-        <v>503582.4529315095</v>
+        <v>503582.5032402195</v>
       </c>
       <c r="P196" t="n">
         <v>7500</v>
@@ -10998,10 +10998,10 @@
         <v>159</v>
       </c>
       <c r="N238" t="n">
-        <v>10997.283333333</v>
+        <v>10817</v>
       </c>
       <c r="O238" t="n">
-        <v>1748568.049999947</v>
+        <v>1719903</v>
       </c>
       <c r="P238" t="n">
         <v>17900</v>
@@ -11412,10 +11412,10 @@
         <v>864</v>
       </c>
       <c r="N247" t="n">
-        <v>1516.0387067969</v>
+        <v>1516.0386973545</v>
       </c>
       <c r="O247" t="n">
-        <v>1309857.442672522</v>
+        <v>1309857.434514288</v>
       </c>
       <c r="P247" t="n">
         <v>2300</v>
@@ -11582,13 +11582,13 @@
         </is>
       </c>
       <c r="J251" t="n">
-        <v>4464</v>
+        <v>4032</v>
       </c>
       <c r="K251" t="n">
         <v>0</v>
       </c>
       <c r="L251" t="n">
-        <v>432</v>
+        <v>0</v>
       </c>
       <c r="M251" t="n">
         <v>4032</v>
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="J254" t="n">
-        <v>348</v>
+        <v>276</v>
       </c>
       <c r="K254" t="n">
         <v>0</v>
       </c>
       <c r="L254" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="M254" t="n">
         <v>276</v>
@@ -11917,7 +11917,7 @@
         </is>
       </c>
       <c r="J258" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="K258" t="n">
         <v>0</v>
@@ -11926,19 +11926,19 @@
         <v>0</v>
       </c>
       <c r="M258" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="N258" t="n">
         <v>15423.36</v>
       </c>
       <c r="O258" t="n">
-        <v>848284.8</v>
+        <v>663204.48</v>
       </c>
       <c r="P258" t="n">
         <v>24900</v>
       </c>
       <c r="Q258" t="n">
-        <v>1369500</v>
+        <v>1070700</v>
       </c>
     </row>
     <row r="259">
@@ -12207,10 +12207,10 @@
         <v>1440</v>
       </c>
       <c r="N264" t="n">
-        <v>1690.8700097561</v>
+        <v>1690.8700097895</v>
       </c>
       <c r="O264" t="n">
-        <v>2434852.814048784</v>
+        <v>2434852.81409688</v>
       </c>
       <c r="P264" t="n">
         <v>3000</v>
@@ -12761,10 +12761,10 @@
         <v>14112</v>
       </c>
       <c r="N276" t="n">
-        <v>703.79459259958</v>
+        <v>703.79458866348</v>
       </c>
       <c r="O276" t="n">
-        <v>9931949.290765272</v>
+        <v>9931949.23521903</v>
       </c>
       <c r="P276" t="n">
         <v>900</v>
@@ -13679,20 +13679,17 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>C7325</t>
-        </is>
-      </c>
-      <c r="B296" t="n">
-        <v>6974555555022</v>
+          <t>C736</t>
+        </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>PISTA EN BLISTER C7325</t>
+          <t>GLOBO CORAZON GDE MENSAJE</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -13701,7 +13698,7 @@
         </is>
       </c>
       <c r="J296" t="n">
-        <v>45</v>
+        <v>2700</v>
       </c>
       <c r="K296" t="n">
         <v>0</v>
@@ -13710,35 +13707,38 @@
         <v>0</v>
       </c>
       <c r="M296" t="n">
-        <v>45</v>
+        <v>2700</v>
       </c>
       <c r="N296" t="n">
-        <v>3099.6039575972</v>
+        <v>640</v>
       </c>
       <c r="O296" t="n">
-        <v>139482.178091874</v>
+        <v>1728000</v>
       </c>
       <c r="P296" t="n">
-        <v>7200</v>
+        <v>800</v>
       </c>
       <c r="Q296" t="n">
-        <v>324000</v>
+        <v>2160000</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>C736</t>
-        </is>
+          <t>C7365</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>6920240750050</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>GLOBO CORAZON GDE MENSAJE</t>
+          <t>DIDACTICO JIRAFA EN BOLSA C7365</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -13747,7 +13747,7 @@
         </is>
       </c>
       <c r="J297" t="n">
-        <v>2700</v>
+        <v>19</v>
       </c>
       <c r="K297" t="n">
         <v>0</v>
@@ -13756,33 +13756,33 @@
         <v>0</v>
       </c>
       <c r="M297" t="n">
-        <v>2700</v>
+        <v>19</v>
       </c>
       <c r="N297" t="n">
-        <v>640</v>
+        <v>4190.77</v>
       </c>
       <c r="O297" t="n">
-        <v>1728000</v>
+        <v>79624.63</v>
       </c>
       <c r="P297" t="n">
-        <v>800</v>
+        <v>5900</v>
       </c>
       <c r="Q297" t="n">
-        <v>2160000</v>
+        <v>112100</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>C7365</t>
+          <t>C7366</t>
         </is>
       </c>
       <c r="B298" t="n">
-        <v>6920240750050</v>
+        <v>6920240750098</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>DIDACTICO JIRAFA EN BOLSA C7365</t>
+          <t>TREN DIDACTICO EN BOLSA C7366</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -13796,7 +13796,7 @@
         </is>
       </c>
       <c r="J298" t="n">
-        <v>19</v>
+        <v>104</v>
       </c>
       <c r="K298" t="n">
         <v>0</v>
@@ -13805,33 +13805,33 @@
         <v>0</v>
       </c>
       <c r="M298" t="n">
-        <v>19</v>
+        <v>104</v>
       </c>
       <c r="N298" t="n">
-        <v>4190.77</v>
+        <v>3499.72</v>
       </c>
       <c r="O298" t="n">
-        <v>79624.63</v>
+        <v>363970.88</v>
       </c>
       <c r="P298" t="n">
-        <v>5900</v>
+        <v>6900</v>
       </c>
       <c r="Q298" t="n">
-        <v>112100</v>
+        <v>717600</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>C7366</t>
+          <t>C7368</t>
         </is>
       </c>
       <c r="B299" t="n">
-        <v>6920240750098</v>
+        <v>6920240750159</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>TREN DIDACTICO EN BOLSA C7366</t>
+          <t>MOTO DIDACTICA EN BOLSA C736</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -13845,7 +13845,7 @@
         </is>
       </c>
       <c r="J299" t="n">
-        <v>104</v>
+        <v>158</v>
       </c>
       <c r="K299" t="n">
         <v>0</v>
@@ -13854,38 +13854,35 @@
         <v>0</v>
       </c>
       <c r="M299" t="n">
-        <v>104</v>
+        <v>158</v>
       </c>
       <c r="N299" t="n">
-        <v>3499.72</v>
+        <v>4578.04</v>
       </c>
       <c r="O299" t="n">
-        <v>363970.88</v>
+        <v>723330.3199999999</v>
       </c>
       <c r="P299" t="n">
-        <v>6900</v>
+        <v>7500</v>
       </c>
       <c r="Q299" t="n">
-        <v>717600</v>
+        <v>1185000</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>C7368</t>
-        </is>
-      </c>
-      <c r="B300" t="n">
-        <v>6920240750159</v>
+          <t>C740-IO</t>
+        </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>MOTO DIDACTICA EN BOLSA C736</t>
+          <t>GLOBO UNICORNIO MED</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -13894,7 +13891,7 @@
         </is>
       </c>
       <c r="J300" t="n">
-        <v>158</v>
+        <v>1876</v>
       </c>
       <c r="K300" t="n">
         <v>0</v>
@@ -13903,35 +13900,38 @@
         <v>0</v>
       </c>
       <c r="M300" t="n">
-        <v>158</v>
+        <v>1876</v>
       </c>
       <c r="N300" t="n">
-        <v>4578.04</v>
+        <v>480</v>
       </c>
       <c r="O300" t="n">
-        <v>723330.3199999999</v>
+        <v>900480</v>
       </c>
       <c r="P300" t="n">
-        <v>7500</v>
+        <v>600</v>
       </c>
       <c r="Q300" t="n">
-        <v>1185000</v>
+        <v>1125600</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>C740-IO</t>
-        </is>
+          <t>C7413</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>6921202412870</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>GLOBO UNICORNIO MED</t>
+          <t>DIDACTICO TORRE DE AROS C7413</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -13940,7 +13940,7 @@
         </is>
       </c>
       <c r="J301" t="n">
-        <v>1876</v>
+        <v>120</v>
       </c>
       <c r="K301" t="n">
         <v>0</v>
@@ -13949,38 +13949,35 @@
         <v>0</v>
       </c>
       <c r="M301" t="n">
-        <v>1876</v>
+        <v>120</v>
       </c>
       <c r="N301" t="n">
-        <v>480</v>
+        <v>4159.0003030303</v>
       </c>
       <c r="O301" t="n">
-        <v>900480</v>
+        <v>499080.036363636</v>
       </c>
       <c r="P301" t="n">
-        <v>600</v>
+        <v>8900</v>
       </c>
       <c r="Q301" t="n">
-        <v>1125600</v>
+        <v>1068000</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>C7413</t>
-        </is>
-      </c>
-      <c r="B302" t="n">
-        <v>6921202412870</v>
+          <t>C744-IO</t>
+        </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>DIDACTICO TORRE DE AROS C7413</t>
+          <t>GLOBO FELIZ CUMPLEAÑOS COLORES Y PUNTOS</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>GLOBOS</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -13989,7 +13986,7 @@
         </is>
       </c>
       <c r="J302" t="n">
-        <v>120</v>
+        <v>478</v>
       </c>
       <c r="K302" t="n">
         <v>0</v>
@@ -13998,35 +13995,35 @@
         <v>0</v>
       </c>
       <c r="M302" t="n">
-        <v>120</v>
+        <v>478</v>
       </c>
       <c r="N302" t="n">
-        <v>4159.0003030303</v>
+        <v>1554.12</v>
       </c>
       <c r="O302" t="n">
-        <v>499080.036363636</v>
+        <v>742869.36</v>
       </c>
       <c r="P302" t="n">
-        <v>8900</v>
+        <v>1900</v>
       </c>
       <c r="Q302" t="n">
-        <v>1068000</v>
+        <v>908200</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>C744-IO</t>
+          <t>C7462</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>GLOBO FELIZ CUMPLEAÑOS COLORES Y PUNTOS</t>
+          <t>SET DE BELLEZA ACCESORIOS PARA EL CABELLO C7462</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>GLOBOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -14035,7 +14032,7 @@
         </is>
       </c>
       <c r="J303" t="n">
-        <v>478</v>
+        <v>11</v>
       </c>
       <c r="K303" t="n">
         <v>0</v>
@@ -14044,30 +14041,33 @@
         <v>0</v>
       </c>
       <c r="M303" t="n">
-        <v>478</v>
+        <v>11</v>
       </c>
       <c r="N303" t="n">
-        <v>1554.12</v>
+        <v>14751.820377358</v>
       </c>
       <c r="O303" t="n">
-        <v>742869.36</v>
+        <v>162270.024150938</v>
       </c>
       <c r="P303" t="n">
-        <v>1900</v>
+        <v>37100</v>
       </c>
       <c r="Q303" t="n">
-        <v>908200</v>
+        <v>408100</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>C7462</t>
-        </is>
+          <t>C7467</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>6920241023009</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>SET DE BELLEZA ACCESORIOS PARA EL CABELLO C7462</t>
+          <t>ARCO Y FLECHA PARA NIÑAS C7467</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -14081,7 +14081,7 @@
         </is>
       </c>
       <c r="J304" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K304" t="n">
         <v>0</v>
@@ -14090,38 +14090,38 @@
         <v>0</v>
       </c>
       <c r="M304" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="N304" t="n">
-        <v>15571.365925926</v>
+        <v>15347.45</v>
       </c>
       <c r="O304" t="n">
-        <v>171285.025185186</v>
+        <v>230211.75</v>
       </c>
       <c r="P304" t="n">
-        <v>37100</v>
+        <v>23900</v>
       </c>
       <c r="Q304" t="n">
-        <v>408100</v>
+        <v>358500</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>C7467</t>
+          <t>C7488</t>
         </is>
       </c>
       <c r="B305" t="n">
-        <v>6920241023009</v>
+        <v>6945158254520</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>ARCO Y FLECHA PARA NIÑAS C7467</t>
+          <t>SOPORTE CELULAR CON LUZ C7488</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -14130,7 +14130,7 @@
         </is>
       </c>
       <c r="J305" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="K305" t="n">
         <v>0</v>
@@ -14139,38 +14139,38 @@
         <v>0</v>
       </c>
       <c r="M305" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="N305" t="n">
-        <v>15516.103296703</v>
+        <v>8919.16</v>
       </c>
       <c r="O305" t="n">
-        <v>232741.549450545</v>
+        <v>258655.64</v>
       </c>
       <c r="P305" t="n">
-        <v>23900</v>
+        <v>10000</v>
       </c>
       <c r="Q305" t="n">
-        <v>358500</v>
+        <v>290000</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>C7488</t>
+          <t>C7513</t>
         </is>
       </c>
       <c r="B306" t="n">
-        <v>6945158254520</v>
+        <v>6905698382824</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>SOPORTE CELULAR CON LUZ C7488</t>
+          <t>SONAJERO BOLA LUZ GDE C7513</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -14179,7 +14179,7 @@
         </is>
       </c>
       <c r="J306" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="K306" t="n">
         <v>0</v>
@@ -14188,47 +14188,42 @@
         <v>0</v>
       </c>
       <c r="M306" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="N306" t="n">
-        <v>8919.16</v>
+        <v>1024.29</v>
       </c>
       <c r="O306" t="n">
-        <v>258655.64</v>
+        <v>1024.29</v>
       </c>
       <c r="P306" t="n">
-        <v>10000</v>
+        <v>2900</v>
       </c>
       <c r="Q306" t="n">
-        <v>290000</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>C7513</t>
+          <t>C752</t>
         </is>
       </c>
       <c r="B307" t="n">
-        <v>6905698382824</v>
+        <v>8596162180497</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>SONAJERO BOLA LUZ GDE C7513</t>
-        </is>
-      </c>
-      <c r="E307" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
+          <t>GLOBO UNICORNIO MED 4 PATAS</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J307" t="n">
-        <v>1</v>
+        <v>1398</v>
       </c>
       <c r="K307" t="n">
         <v>0</v>
@@ -14237,33 +14232,33 @@
         <v>0</v>
       </c>
       <c r="M307" t="n">
-        <v>1</v>
+        <v>1398</v>
       </c>
       <c r="N307" t="n">
-        <v>1024.29</v>
+        <v>1163.7447787403</v>
       </c>
       <c r="O307" t="n">
-        <v>1024.29</v>
+        <v>1626915.200678939</v>
       </c>
       <c r="P307" t="n">
-        <v>2900</v>
+        <v>1500</v>
       </c>
       <c r="Q307" t="n">
-        <v>2900</v>
+        <v>2097000</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>C752</t>
+          <t>C753</t>
         </is>
       </c>
       <c r="B308" t="n">
-        <v>8596162180497</v>
+        <v>8596162180503</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>GLOBO UNICORNIO MED 4 PATAS</t>
+          <t>GLOBO UNICORNIO GDE 4 PATAS</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -14272,7 +14267,7 @@
         </is>
       </c>
       <c r="J308" t="n">
-        <v>1398</v>
+        <v>277</v>
       </c>
       <c r="K308" t="n">
         <v>0</v>
@@ -14281,42 +14276,47 @@
         <v>0</v>
       </c>
       <c r="M308" t="n">
-        <v>1398</v>
+        <v>277</v>
       </c>
       <c r="N308" t="n">
-        <v>1163.7447787403</v>
+        <v>5113.4625508318</v>
       </c>
       <c r="O308" t="n">
-        <v>1626915.200678939</v>
+        <v>1416429.126580409</v>
       </c>
       <c r="P308" t="n">
-        <v>1500</v>
+        <v>7000</v>
       </c>
       <c r="Q308" t="n">
-        <v>2097000</v>
+        <v>1939000</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>C753</t>
+          <t>C7533</t>
         </is>
       </c>
       <c r="B309" t="n">
-        <v>8596162180503</v>
+        <v>6923669699979</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>GLOBO UNICORNIO GDE 4 PATAS</t>
+          <t>REPUESTO BIOGEL NEON C7533</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J309" t="n">
-        <v>277</v>
+        <v>12023</v>
       </c>
       <c r="K309" t="n">
         <v>0</v>
@@ -14325,33 +14325,33 @@
         <v>0</v>
       </c>
       <c r="M309" t="n">
-        <v>277</v>
+        <v>12023</v>
       </c>
       <c r="N309" t="n">
-        <v>5113.4625508318</v>
+        <v>509.69</v>
       </c>
       <c r="O309" t="n">
-        <v>1416429.126580409</v>
+        <v>6128002.87</v>
       </c>
       <c r="P309" t="n">
-        <v>7000</v>
+        <v>750</v>
       </c>
       <c r="Q309" t="n">
-        <v>1939000</v>
+        <v>9017250</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>C7533</t>
+          <t>C7534</t>
         </is>
       </c>
       <c r="B310" t="n">
-        <v>6923669699979</v>
+        <v>6951241752002</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>REPUESTO BIOGEL NEON C7533</t>
+          <t>GORRO PELUCHE LUZ C7534-A-B-C-D-E-F</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -14365,7 +14365,7 @@
         </is>
       </c>
       <c r="J310" t="n">
-        <v>12023</v>
+        <v>499</v>
       </c>
       <c r="K310" t="n">
         <v>0</v>
@@ -14374,38 +14374,35 @@
         <v>0</v>
       </c>
       <c r="M310" t="n">
-        <v>12023</v>
+        <v>499</v>
       </c>
       <c r="N310" t="n">
-        <v>509.69</v>
+        <v>7046.9398262758</v>
       </c>
       <c r="O310" t="n">
-        <v>6128002.87</v>
+        <v>3516422.973311624</v>
       </c>
       <c r="P310" t="n">
-        <v>750</v>
+        <v>9900</v>
       </c>
       <c r="Q310" t="n">
-        <v>9017250</v>
+        <v>4940100</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>C7534</t>
-        </is>
-      </c>
-      <c r="B311" t="n">
-        <v>6951241752002</v>
+          <t>C7535</t>
+        </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>GORRO PELUCHE LUZ C7534-A-B-C-D-E-F</t>
+          <t>CARRO METALICO X13 CON CAMION C7535</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -14414,7 +14411,7 @@
         </is>
       </c>
       <c r="J311" t="n">
-        <v>499</v>
+        <v>30</v>
       </c>
       <c r="K311" t="n">
         <v>0</v>
@@ -14423,35 +14420,35 @@
         <v>0</v>
       </c>
       <c r="M311" t="n">
-        <v>499</v>
+        <v>30</v>
       </c>
       <c r="N311" t="n">
-        <v>7046.9398262758</v>
+        <v>24338.47</v>
       </c>
       <c r="O311" t="n">
-        <v>3516422.973311624</v>
+        <v>730154.1000000001</v>
       </c>
       <c r="P311" t="n">
-        <v>9900</v>
+        <v>27900</v>
       </c>
       <c r="Q311" t="n">
-        <v>4940100</v>
+        <v>837000</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>C7535</t>
+          <t>C7560</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>CARRO METALICO X13 CON CAMION C7535</t>
+          <t>BARRA LUMINOSA 48CM C7560/211</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -14460,7 +14457,7 @@
         </is>
       </c>
       <c r="J312" t="n">
-        <v>30</v>
+        <v>188</v>
       </c>
       <c r="K312" t="n">
         <v>0</v>
@@ -14469,30 +14466,33 @@
         <v>0</v>
       </c>
       <c r="M312" t="n">
-        <v>30</v>
+        <v>188</v>
       </c>
       <c r="N312" t="n">
-        <v>24856.309787234</v>
+        <v>796.3099999999999</v>
       </c>
       <c r="O312" t="n">
-        <v>745689.29361702</v>
+        <v>149706.28</v>
       </c>
       <c r="P312" t="n">
-        <v>27900</v>
+        <v>2500</v>
       </c>
       <c r="Q312" t="n">
-        <v>837000</v>
+        <v>470000</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>C7560</t>
-        </is>
+          <t>C7588</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>7588228020244</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>BARRA LUMINOSA 48CM C7560/211</t>
+          <t>SONAJERO LUZ PANDITA C7588</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -14506,7 +14506,7 @@
         </is>
       </c>
       <c r="J313" t="n">
-        <v>188</v>
+        <v>1429</v>
       </c>
       <c r="K313" t="n">
         <v>0</v>
@@ -14515,38 +14515,38 @@
         <v>0</v>
       </c>
       <c r="M313" t="n">
-        <v>188</v>
+        <v>1429</v>
       </c>
       <c r="N313" t="n">
-        <v>796.3099999999999</v>
+        <v>641.78</v>
       </c>
       <c r="O313" t="n">
-        <v>149706.28</v>
+        <v>917103.62</v>
       </c>
       <c r="P313" t="n">
         <v>2500</v>
       </c>
       <c r="Q313" t="n">
-        <v>470000</v>
+        <v>3572500</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>C7588</t>
+          <t>C7610</t>
         </is>
       </c>
       <c r="B314" t="n">
-        <v>7588228020244</v>
+        <v>6999899236093</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>SONAJERO LUZ PANDITA C7588</t>
+          <t>BOTE TIMON PISCINA 80X60 C7610</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>INFLABLES</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -14555,7 +14555,7 @@
         </is>
       </c>
       <c r="J314" t="n">
-        <v>1429</v>
+        <v>276</v>
       </c>
       <c r="K314" t="n">
         <v>0</v>
@@ -14564,38 +14564,38 @@
         <v>0</v>
       </c>
       <c r="M314" t="n">
-        <v>1429</v>
+        <v>276</v>
       </c>
       <c r="N314" t="n">
-        <v>641.78</v>
+        <v>7811.9</v>
       </c>
       <c r="O314" t="n">
-        <v>917103.62</v>
+        <v>2156084.4</v>
       </c>
       <c r="P314" t="n">
-        <v>2500</v>
+        <v>13900</v>
       </c>
       <c r="Q314" t="n">
-        <v>3572500</v>
+        <v>3836400</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>C7610</t>
+          <t>C7614-F</t>
         </is>
       </c>
       <c r="B315" t="n">
-        <v>6999899236093</v>
+        <v>6999899236130</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>BOTE TIMON PISCINA 80X60 C7610</t>
+          <t>FLOTADOR DONA FLAMINGO C7614-F</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>INFLABLES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -14604,7 +14604,7 @@
         </is>
       </c>
       <c r="J315" t="n">
-        <v>276</v>
+        <v>382</v>
       </c>
       <c r="K315" t="n">
         <v>0</v>
@@ -14613,47 +14613,42 @@
         <v>0</v>
       </c>
       <c r="M315" t="n">
-        <v>276</v>
+        <v>382</v>
       </c>
       <c r="N315" t="n">
-        <v>7811.9</v>
+        <v>3155</v>
       </c>
       <c r="O315" t="n">
-        <v>2156084.4</v>
+        <v>1205210</v>
       </c>
       <c r="P315" t="n">
-        <v>13900</v>
+        <v>5900</v>
       </c>
       <c r="Q315" t="n">
-        <v>3836400</v>
+        <v>2253800</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>C7614-F</t>
+          <t>C784</t>
         </is>
       </c>
       <c r="B316" t="n">
-        <v>6999899236130</v>
+        <v>8913992935507</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>FLOTADOR DONA FLAMINGO C7614-F</t>
-        </is>
-      </c>
-      <c r="E316" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>GLOBO MENSAJE CUADRADO</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J316" t="n">
-        <v>382</v>
+        <v>1450</v>
       </c>
       <c r="K316" t="n">
         <v>0</v>
@@ -14662,33 +14657,33 @@
         <v>0</v>
       </c>
       <c r="M316" t="n">
-        <v>382</v>
+        <v>1450</v>
       </c>
       <c r="N316" t="n">
-        <v>3155</v>
+        <v>704.89696969697</v>
       </c>
       <c r="O316" t="n">
-        <v>1205210</v>
+        <v>1022100.606060607</v>
       </c>
       <c r="P316" t="n">
-        <v>5900</v>
+        <v>900</v>
       </c>
       <c r="Q316" t="n">
-        <v>2253800</v>
+        <v>1305000</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>C784</t>
+          <t>C819</t>
         </is>
       </c>
       <c r="B317" t="n">
-        <v>8913992935507</v>
+        <v>2087202108190</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>GLOBO MENSAJE CUADRADO</t>
+          <t>TROMPO EMOJI</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -14697,7 +14692,7 @@
         </is>
       </c>
       <c r="J317" t="n">
-        <v>1450</v>
+        <v>468</v>
       </c>
       <c r="K317" t="n">
         <v>0</v>
@@ -14706,33 +14701,33 @@
         <v>0</v>
       </c>
       <c r="M317" t="n">
-        <v>1450</v>
+        <v>468</v>
       </c>
       <c r="N317" t="n">
-        <v>704.89696969697</v>
+        <v>6761.25</v>
       </c>
       <c r="O317" t="n">
-        <v>1022100.606060607</v>
+        <v>3164265</v>
       </c>
       <c r="P317" t="n">
-        <v>900</v>
+        <v>5200</v>
       </c>
       <c r="Q317" t="n">
-        <v>1305000</v>
+        <v>2433600</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>C819</t>
+          <t>C84</t>
         </is>
       </c>
       <c r="B318" t="n">
-        <v>2087202108190</v>
+        <v>2021010563031</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>TROMPO EMOJI</t>
+          <t>LANZADOR DE AGUA</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -14741,7 +14736,7 @@
         </is>
       </c>
       <c r="J318" t="n">
-        <v>468</v>
+        <v>182</v>
       </c>
       <c r="K318" t="n">
         <v>0</v>
@@ -14750,33 +14745,35 @@
         <v>0</v>
       </c>
       <c r="M318" t="n">
-        <v>468</v>
+        <v>182</v>
       </c>
       <c r="N318" t="n">
-        <v>6761.25</v>
+        <v>1008.8110899183</v>
       </c>
       <c r="O318" t="n">
-        <v>3164265</v>
+        <v>183603.6183651306</v>
       </c>
       <c r="P318" t="n">
-        <v>5200</v>
+        <v>1500</v>
       </c>
       <c r="Q318" t="n">
-        <v>2433600</v>
+        <v>273000</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>C84</t>
-        </is>
-      </c>
-      <c r="B319" t="n">
-        <v>2021010563031</v>
+          <t>C879</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>CG-2016-212</t>
+        </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>LANZADOR DE AGUA</t>
+          <t>VELA MARIPOSA</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -14785,7 +14782,7 @@
         </is>
       </c>
       <c r="J319" t="n">
-        <v>182</v>
+        <v>121</v>
       </c>
       <c r="K319" t="n">
         <v>0</v>
@@ -14794,44 +14791,49 @@
         <v>0</v>
       </c>
       <c r="M319" t="n">
-        <v>182</v>
+        <v>121</v>
       </c>
       <c r="N319" t="n">
-        <v>1008.8110899183</v>
+        <v>1520</v>
       </c>
       <c r="O319" t="n">
-        <v>183603.6183651306</v>
+        <v>183920</v>
       </c>
       <c r="P319" t="n">
-        <v>1500</v>
+        <v>1900</v>
       </c>
       <c r="Q319" t="n">
-        <v>273000</v>
+        <v>229900</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>C879</t>
+          <t>C880</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>CG-2016-212</t>
+          <t>cg2016213</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>VELA MARIPOSA</t>
+          <t>VELA FLOR</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>VELA</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J320" t="n">
-        <v>121</v>
+        <v>200</v>
       </c>
       <c r="K320" t="n">
         <v>0</v>
@@ -14840,49 +14842,39 @@
         <v>0</v>
       </c>
       <c r="M320" t="n">
-        <v>121</v>
+        <v>200</v>
       </c>
       <c r="N320" t="n">
         <v>1520</v>
       </c>
       <c r="O320" t="n">
-        <v>183920</v>
+        <v>304000</v>
       </c>
       <c r="P320" t="n">
         <v>1900</v>
       </c>
       <c r="Q320" t="n">
-        <v>229900</v>
+        <v>380000</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>C880</t>
-        </is>
-      </c>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>cg2016213</t>
+          <t>C888</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>VELA FLOR</t>
-        </is>
-      </c>
-      <c r="E321" t="inlineStr">
-        <is>
-          <t>VELA</t>
+          <t>PELOTA CHILLON PUYAS SIN LUZ</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J321" t="n">
-        <v>200</v>
+        <v>169</v>
       </c>
       <c r="K321" t="n">
         <v>0</v>
@@ -14891,39 +14883,44 @@
         <v>0</v>
       </c>
       <c r="M321" t="n">
-        <v>200</v>
+        <v>169</v>
       </c>
       <c r="N321" t="n">
-        <v>1520</v>
+        <v>1213.6821400778</v>
       </c>
       <c r="O321" t="n">
-        <v>304000</v>
+        <v>205112.2816731482</v>
       </c>
       <c r="P321" t="n">
-        <v>1900</v>
+        <v>1500</v>
       </c>
       <c r="Q321" t="n">
-        <v>380000</v>
+        <v>253500</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>C888</t>
+          <t>FG037</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>PELOTA CHILLON PUYAS SIN LUZ</t>
+          <t>SNORKEL 66046A</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J322" t="n">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="K322" t="n">
         <v>0</v>
@@ -14932,30 +14929,30 @@
         <v>0</v>
       </c>
       <c r="M322" t="n">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="N322" t="n">
-        <v>1213.6821400778</v>
+        <v>13493.858287462</v>
       </c>
       <c r="O322" t="n">
-        <v>205112.2816731482</v>
+        <v>2415400.633455698</v>
       </c>
       <c r="P322" t="n">
-        <v>1500</v>
+        <v>16900</v>
       </c>
       <c r="Q322" t="n">
-        <v>253500</v>
+        <v>3025100</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>FG037</t>
+          <t>FG039</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>SNORKEL 66046A</t>
+          <t>GAFA DE NATACION BLISTER 2404-2</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -14969,7 +14966,7 @@
         </is>
       </c>
       <c r="J323" t="n">
-        <v>179</v>
+        <v>347</v>
       </c>
       <c r="K323" t="n">
         <v>0</v>
@@ -14978,35 +14975,40 @@
         <v>0</v>
       </c>
       <c r="M323" t="n">
-        <v>179</v>
+        <v>347</v>
       </c>
       <c r="N323" t="n">
-        <v>13493.858287462</v>
+        <v>2644.9</v>
       </c>
       <c r="O323" t="n">
-        <v>2415400.633455698</v>
+        <v>917780.3</v>
       </c>
       <c r="P323" t="n">
-        <v>16900</v>
+        <v>3900</v>
       </c>
       <c r="Q323" t="n">
-        <v>3025100</v>
+        <v>1353300</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>FG039</t>
+          <t>MG16332</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>MG16332</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>GAFA DE NATACION BLISTER 2404-2</t>
+          <t>LANZADOR  ARCO Y FLECA CON LASER MG16332</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -15015,7 +15017,7 @@
         </is>
       </c>
       <c r="J324" t="n">
-        <v>347</v>
+        <v>4</v>
       </c>
       <c r="K324" t="n">
         <v>0</v>
@@ -15024,35 +15026,30 @@
         <v>0</v>
       </c>
       <c r="M324" t="n">
-        <v>347</v>
+        <v>4</v>
       </c>
       <c r="N324" t="n">
-        <v>2644.9</v>
+        <v>8439.969999999999</v>
       </c>
       <c r="O324" t="n">
-        <v>917780.3</v>
+        <v>33759.88</v>
       </c>
       <c r="P324" t="n">
-        <v>3900</v>
+        <v>29500</v>
       </c>
       <c r="Q324" t="n">
-        <v>1353300</v>
+        <v>118000</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>MG16332</t>
-        </is>
-      </c>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>MG16332</t>
+          <t>MG20430</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>LANZADOR  ARCO Y FLECA CON LASER MG16332</t>
+          <t>SET PLASTILINA CON MOLDES BARBERIA MALETA MG20430</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -15066,7 +15063,7 @@
         </is>
       </c>
       <c r="J325" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="K325" t="n">
         <v>0</v>
@@ -15075,35 +15072,35 @@
         <v>0</v>
       </c>
       <c r="M325" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="N325" t="n">
-        <v>8439.969999999999</v>
+        <v>12189.831111111</v>
       </c>
       <c r="O325" t="n">
-        <v>33759.88</v>
+        <v>219416.959999998</v>
       </c>
       <c r="P325" t="n">
-        <v>29500</v>
+        <v>30900</v>
       </c>
       <c r="Q325" t="n">
-        <v>118000</v>
+        <v>556200</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>MG20430</t>
+          <t>MG40210</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>SET PLASTILINA CON MOLDES BARBERIA MALETA MG20430</t>
+          <t>SONAJERO OSO MG40210</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -15112,7 +15109,7 @@
         </is>
       </c>
       <c r="J326" t="n">
-        <v>18</v>
+        <v>263</v>
       </c>
       <c r="K326" t="n">
         <v>0</v>
@@ -15121,35 +15118,40 @@
         <v>0</v>
       </c>
       <c r="M326" t="n">
-        <v>18</v>
+        <v>263</v>
       </c>
       <c r="N326" t="n">
-        <v>12189.831111111</v>
+        <v>571.87</v>
       </c>
       <c r="O326" t="n">
-        <v>219416.959999998</v>
+        <v>150401.81</v>
       </c>
       <c r="P326" t="n">
-        <v>30900</v>
+        <v>2500</v>
       </c>
       <c r="Q326" t="n">
-        <v>556200</v>
+        <v>657500</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>MG40210</t>
+          <t>MG40720</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>MG40720</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>SONAJERO OSO MG40210</t>
+          <t>MAQUINA DE COSER MINI MG40720</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -15158,7 +15160,7 @@
         </is>
       </c>
       <c r="J327" t="n">
-        <v>263</v>
+        <v>64</v>
       </c>
       <c r="K327" t="n">
         <v>0</v>
@@ -15167,69 +15169,18 @@
         <v>0</v>
       </c>
       <c r="M327" t="n">
-        <v>263</v>
+        <v>64</v>
       </c>
       <c r="N327" t="n">
-        <v>571.87</v>
+        <v>9917.040000000001</v>
       </c>
       <c r="O327" t="n">
-        <v>150401.81</v>
+        <v>634690.5600000001</v>
       </c>
       <c r="P327" t="n">
-        <v>2500</v>
+        <v>15900</v>
       </c>
       <c r="Q327" t="n">
-        <v>657500</v>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" t="inlineStr">
-        <is>
-          <t>MG40720</t>
-        </is>
-      </c>
-      <c r="B328" t="inlineStr">
-        <is>
-          <t>MG40720</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>MAQUINA DE COSER MINI MG40720</t>
-        </is>
-      </c>
-      <c r="E328" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
-        </is>
-      </c>
-      <c r="I328" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J328" t="n">
-        <v>64</v>
-      </c>
-      <c r="K328" t="n">
-        <v>0</v>
-      </c>
-      <c r="L328" t="n">
-        <v>0</v>
-      </c>
-      <c r="M328" t="n">
-        <v>64</v>
-      </c>
-      <c r="N328" t="n">
-        <v>9917.040000000001</v>
-      </c>
-      <c r="O328" t="n">
-        <v>634690.5600000001</v>
-      </c>
-      <c r="P328" t="n">
-        <v>15900</v>
-      </c>
-      <c r="Q328" t="n">
         <v>1017600</v>
       </c>
     </row>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -642,10 +642,10 @@
         <v>275</v>
       </c>
       <c r="N6" t="n">
-        <v>27109.756097561</v>
+        <v>27000</v>
       </c>
       <c r="O6" t="n">
-        <v>7455182.926829275</v>
+        <v>7425000</v>
       </c>
       <c r="P6" t="n">
         <v>20000</v>
@@ -3065,10 +3065,10 @@
         <v>350</v>
       </c>
       <c r="N64" t="n">
-        <v>2582.25476203</v>
+        <v>2586.3633253779</v>
       </c>
       <c r="O64" t="n">
-        <v>903789.1667105</v>
+        <v>905227.163882265</v>
       </c>
       <c r="P64" t="n">
         <v>4500</v>
@@ -4253,10 +4253,10 @@
         <v>1584</v>
       </c>
       <c r="N90" t="n">
-        <v>3472.2763744227</v>
+        <v>3472.276379862</v>
       </c>
       <c r="O90" t="n">
-        <v>5500085.777085557</v>
+        <v>5500085.785701408</v>
       </c>
       <c r="P90" t="n">
         <v>5900</v>
@@ -5748,10 +5748,10 @@
         <v>432</v>
       </c>
       <c r="N123" t="n">
-        <v>2029.8742541123</v>
+        <v>2029.8742613636</v>
       </c>
       <c r="O123" t="n">
-        <v>876905.6777765136</v>
+        <v>876905.6809090752</v>
       </c>
       <c r="P123" t="n">
         <v>3600</v>
@@ -6053,10 +6053,10 @@
         <v>192</v>
       </c>
       <c r="N130" t="n">
-        <v>30745.062773723</v>
+        <v>30611</v>
       </c>
       <c r="O130" t="n">
-        <v>5903052.052554816</v>
+        <v>5877312</v>
       </c>
       <c r="P130" t="n">
         <v>38900</v>
@@ -6191,10 +6191,10 @@
         <v>850</v>
       </c>
       <c r="N133" t="n">
-        <v>6207.9882003658</v>
+        <v>6207.9882013781</v>
       </c>
       <c r="O133" t="n">
-        <v>5276789.97031093</v>
+        <v>5276789.971171385</v>
       </c>
       <c r="P133" t="n">
         <v>9900</v>
@@ -6414,10 +6414,10 @@
         <v>908</v>
       </c>
       <c r="N138" t="n">
-        <v>4814.2633472037</v>
+        <v>4814.2633516301</v>
       </c>
       <c r="O138" t="n">
-        <v>4371351.119260959</v>
+        <v>4371351.123280131</v>
       </c>
       <c r="P138" t="n">
         <v>9900</v>
@@ -6818,10 +6818,10 @@
         <v>144</v>
       </c>
       <c r="N147" t="n">
-        <v>27123.764610526</v>
+        <v>27123.764587738</v>
       </c>
       <c r="O147" t="n">
-        <v>3905822.103915744</v>
+        <v>3905822.100634272</v>
       </c>
       <c r="P147" t="n">
         <v>44500</v>
@@ -7002,10 +7002,10 @@
         <v>144</v>
       </c>
       <c r="N151" t="n">
-        <v>27080.935211268</v>
+        <v>26854</v>
       </c>
       <c r="O151" t="n">
-        <v>3899654.670422592</v>
+        <v>3866976</v>
       </c>
       <c r="P151" t="n">
         <v>43900</v>
@@ -7690,10 +7690,10 @@
         <v>192</v>
       </c>
       <c r="N166" t="n">
-        <v>22935.194995686</v>
+        <v>22739</v>
       </c>
       <c r="O166" t="n">
-        <v>4403557.439171712</v>
+        <v>4365888</v>
       </c>
       <c r="P166" t="n">
         <v>36900</v>
@@ -8153,10 +8153,10 @@
         <v>30</v>
       </c>
       <c r="N176" t="n">
-        <v>12344.273972603</v>
+        <v>11857</v>
       </c>
       <c r="O176" t="n">
-        <v>370328.21917809</v>
+        <v>355710</v>
       </c>
       <c r="P176" t="n">
         <v>19900</v>
@@ -8245,10 +8245,10 @@
         <v>12</v>
       </c>
       <c r="N178" t="n">
-        <v>28661.941747573</v>
+        <v>28116</v>
       </c>
       <c r="O178" t="n">
-        <v>343943.300970876</v>
+        <v>337392</v>
       </c>
       <c r="P178" t="n">
         <v>45900</v>
@@ -8337,10 +8337,10 @@
         <v>180</v>
       </c>
       <c r="N180" t="n">
-        <v>10411</v>
+        <v>10642.355555556</v>
       </c>
       <c r="O180" t="n">
-        <v>1873980</v>
+        <v>1915624.00000008</v>
       </c>
       <c r="P180" t="n">
         <v>16900</v>
@@ -9114,10 +9114,10 @@
         <v>40</v>
       </c>
       <c r="N197" t="n">
-        <v>21286.162162162</v>
+        <v>20726</v>
       </c>
       <c r="O197" t="n">
-        <v>851446.48648648</v>
+        <v>829040</v>
       </c>
       <c r="P197" t="n">
         <v>33900</v>
@@ -9201,10 +9201,10 @@
         <v>46</v>
       </c>
       <c r="N199" t="n">
-        <v>21767.55</v>
+        <v>20731</v>
       </c>
       <c r="O199" t="n">
-        <v>1001307.3</v>
+        <v>953626</v>
       </c>
       <c r="P199" t="n">
         <v>33900</v>
@@ -9799,10 +9799,10 @@
         <v>245</v>
       </c>
       <c r="N212" t="n">
-        <v>13585.998452012</v>
+        <v>13565</v>
       </c>
       <c r="O212" t="n">
-        <v>3328569.62074294</v>
+        <v>3323425</v>
       </c>
       <c r="P212" t="n">
         <v>22500</v>
@@ -9937,10 +9937,10 @@
         <v>48</v>
       </c>
       <c r="N215" t="n">
-        <v>16443.466666667</v>
+        <v>16086</v>
       </c>
       <c r="O215" t="n">
-        <v>789286.400000016</v>
+        <v>772128</v>
       </c>
       <c r="P215" t="n">
         <v>25900</v>
@@ -10029,10 +10029,10 @@
         <v>180</v>
       </c>
       <c r="N217" t="n">
-        <v>19059.165545087</v>
+        <v>19008</v>
       </c>
       <c r="O217" t="n">
-        <v>3430649.79811566</v>
+        <v>3421440</v>
       </c>
       <c r="P217" t="n">
         <v>30900</v>
@@ -10121,10 +10121,10 @@
         <v>180</v>
       </c>
       <c r="N219" t="n">
-        <v>18038.854166667</v>
+        <v>17992</v>
       </c>
       <c r="O219" t="n">
-        <v>3246993.75000006</v>
+        <v>3238560</v>
       </c>
       <c r="P219" t="n">
         <v>28900</v>
@@ -10213,10 +10213,10 @@
         <v>192</v>
       </c>
       <c r="N221" t="n">
-        <v>17112.014810127</v>
+        <v>17075.989514768</v>
       </c>
       <c r="O221" t="n">
-        <v>3285506.843544384</v>
+        <v>3278589.986835456</v>
       </c>
       <c r="P221" t="n">
         <v>27500</v>
@@ -11044,10 +11044,10 @@
         <v>79</v>
       </c>
       <c r="N239" t="n">
-        <v>12769.651685393</v>
+        <v>12489</v>
       </c>
       <c r="O239" t="n">
-        <v>1008802.483146047</v>
+        <v>986631</v>
       </c>
       <c r="P239" t="n">
         <v>20900</v>
@@ -11182,10 +11182,10 @@
         <v>144</v>
       </c>
       <c r="N242" t="n">
-        <v>15602.016806723</v>
+        <v>15472</v>
       </c>
       <c r="O242" t="n">
-        <v>2246690.420168112</v>
+        <v>2227968</v>
       </c>
       <c r="P242" t="n">
         <v>25900</v>
@@ -11412,10 +11412,10 @@
         <v>864</v>
       </c>
       <c r="N247" t="n">
-        <v>1516.0386973545</v>
+        <v>1516.0386990066</v>
       </c>
       <c r="O247" t="n">
-        <v>1309857.434514288</v>
+        <v>1309857.435941702</v>
       </c>
       <c r="P247" t="n">
         <v>2300</v>
@@ -12027,10 +12027,10 @@
         <v>534</v>
       </c>
       <c r="N260" t="n">
-        <v>8945.379999999999</v>
+        <v>8949.4124778362</v>
       </c>
       <c r="O260" t="n">
-        <v>4776832.92</v>
+        <v>4778986.263164531</v>
       </c>
       <c r="P260" t="n">
         <v>14900</v>
@@ -12761,10 +12761,10 @@
         <v>14112</v>
       </c>
       <c r="N276" t="n">
-        <v>703.79458866348</v>
+        <v>703.7945904135599</v>
       </c>
       <c r="O276" t="n">
-        <v>9931949.23521903</v>
+        <v>9931949.259916158</v>
       </c>
       <c r="P276" t="n">
         <v>900</v>
@@ -13517,10 +13517,10 @@
         <v>48</v>
       </c>
       <c r="N292" t="n">
-        <v>9746.8802061856</v>
+        <v>9746.8802105263</v>
       </c>
       <c r="O292" t="n">
-        <v>467850.2498969088</v>
+        <v>467850.2501052624</v>
       </c>
       <c r="P292" t="n">
         <v>18500</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q327"/>
+  <dimension ref="A1:Q326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-29</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-30</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -600,19 +600,19 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>74676.625625</v>
+        <v>74676.599</v>
       </c>
       <c r="O5" t="n">
-        <v>746766.25625</v>
+        <v>298706.396</v>
       </c>
       <c r="P5" t="n">
         <v>144900</v>
       </c>
       <c r="Q5" t="n">
-        <v>1449000</v>
+        <v>579600</v>
       </c>
     </row>
     <row r="6">
@@ -759,10 +759,10 @@
         <v>96</v>
       </c>
       <c r="N9" t="n">
-        <v>5758.9597772829</v>
+        <v>5758.9597767857</v>
       </c>
       <c r="O9" t="n">
-        <v>552860.1386191584</v>
+        <v>552860.1385714272</v>
       </c>
       <c r="P9" t="n">
         <v>16900</v>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>172</v>
+        <v>148</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1001,19 +1001,19 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>172</v>
+        <v>148</v>
       </c>
       <c r="N15" t="n">
         <v>27000</v>
       </c>
       <c r="O15" t="n">
-        <v>4644000</v>
+        <v>3996000</v>
       </c>
       <c r="P15" t="n">
         <v>20000</v>
       </c>
       <c r="Q15" t="n">
-        <v>3440000</v>
+        <v>2960000</v>
       </c>
     </row>
     <row r="16">
@@ -1433,10 +1433,10 @@
         <v>118</v>
       </c>
       <c r="N26" t="n">
-        <v>3910.6279262673</v>
+        <v>3910.6278971963</v>
       </c>
       <c r="O26" t="n">
-        <v>461454.0952995414</v>
+        <v>461454.0918691634</v>
       </c>
       <c r="P26" t="n">
         <v>9100</v>
@@ -1735,10 +1735,10 @@
         <v>65</v>
       </c>
       <c r="N33" t="n">
-        <v>141416.88463576</v>
+        <v>141416.88465116</v>
       </c>
       <c r="O33" t="n">
-        <v>9192097.5013244</v>
+        <v>9192097.502325401</v>
       </c>
       <c r="P33" t="n">
         <v>251900</v>
@@ -1824,10 +1824,10 @@
         <v>4</v>
       </c>
       <c r="N35" t="n">
-        <v>344599.17805556</v>
+        <v>344599.178</v>
       </c>
       <c r="O35" t="n">
-        <v>1378396.71222224</v>
+        <v>1378396.712</v>
       </c>
       <c r="P35" t="n">
         <v>532900</v>
@@ -3065,10 +3065,10 @@
         <v>350</v>
       </c>
       <c r="N64" t="n">
-        <v>2586.3633253779</v>
+        <v>2582.2547091633</v>
       </c>
       <c r="O64" t="n">
-        <v>905227.163882265</v>
+        <v>903789.1482071551</v>
       </c>
       <c r="P64" t="n">
         <v>4500</v>
@@ -3111,10 +3111,10 @@
         <v>1102</v>
       </c>
       <c r="N65" t="n">
-        <v>5216.8958101422</v>
+        <v>5216.8958023544</v>
       </c>
       <c r="O65" t="n">
-        <v>5749019.182776704</v>
+        <v>5749019.174194549</v>
       </c>
       <c r="P65" t="n">
         <v>8500</v>
@@ -3157,10 +3157,10 @@
         <v>2592</v>
       </c>
       <c r="N66" t="n">
-        <v>3158.8608436687</v>
+        <v>3158.8608437109</v>
       </c>
       <c r="O66" t="n">
-        <v>8187767.306789271</v>
+        <v>8187767.306898654</v>
       </c>
       <c r="P66" t="n">
         <v>5600</v>
@@ -3295,10 +3295,10 @@
         <v>480</v>
       </c>
       <c r="N69" t="n">
-        <v>3795.7100076453</v>
+        <v>3795.7100076628</v>
       </c>
       <c r="O69" t="n">
-        <v>1821940.803669744</v>
+        <v>1821940.803678144</v>
       </c>
       <c r="P69" t="n">
         <v>6200</v>
@@ -3480,10 +3480,10 @@
         <v>1447715.296734982</v>
       </c>
       <c r="P73" t="n">
-        <v>8200</v>
+        <v>8900</v>
       </c>
       <c r="Q73" t="n">
-        <v>2427200</v>
+        <v>2634400</v>
       </c>
     </row>
     <row r="74">
@@ -3754,10 +3754,10 @@
         <v>1878144</v>
       </c>
       <c r="P79" t="n">
-        <v>8200</v>
+        <v>8900</v>
       </c>
       <c r="Q79" t="n">
-        <v>3148800</v>
+        <v>3417600</v>
       </c>
     </row>
     <row r="80">
@@ -4253,10 +4253,10 @@
         <v>1584</v>
       </c>
       <c r="N90" t="n">
-        <v>3472.276379862</v>
+        <v>3472.276393501</v>
       </c>
       <c r="O90" t="n">
-        <v>5500085.785701408</v>
+        <v>5500085.807305584</v>
       </c>
       <c r="P90" t="n">
         <v>5900</v>
@@ -5066,7 +5066,7 @@
         </is>
       </c>
       <c r="J108" t="n">
-        <v>432</v>
+        <v>396</v>
       </c>
       <c r="K108" t="n">
         <v>0</v>
@@ -5075,19 +5075,19 @@
         <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>432</v>
+        <v>396</v>
       </c>
       <c r="N108" t="n">
         <v>11921.4</v>
       </c>
       <c r="O108" t="n">
-        <v>5150044.8</v>
+        <v>4720874.399999999</v>
       </c>
       <c r="P108" t="n">
         <v>19900</v>
       </c>
       <c r="Q108" t="n">
-        <v>8596800</v>
+        <v>7880400</v>
       </c>
     </row>
     <row r="109">
@@ -5620,10 +5620,10 @@
         <v>480</v>
       </c>
       <c r="N120" t="n">
-        <v>4196.8725467746</v>
+        <v>4196.8725524769</v>
       </c>
       <c r="O120" t="n">
-        <v>2014498.822451808</v>
+        <v>2014498.825188912</v>
       </c>
       <c r="P120" t="n">
         <v>5900</v>
@@ -5789,10 +5789,10 @@
         <v>528</v>
       </c>
       <c r="N124" t="n">
-        <v>22485.695378691</v>
+        <v>22485.69534282</v>
       </c>
       <c r="O124" t="n">
-        <v>11872447.15994885</v>
+        <v>11872447.14100896</v>
       </c>
       <c r="P124" t="n">
         <v>36500</v>
@@ -5961,10 +5961,10 @@
         <v>310</v>
       </c>
       <c r="N128" t="n">
-        <v>2680.7396929825</v>
+        <v>2680.7396925972</v>
       </c>
       <c r="O128" t="n">
-        <v>831029.304824575</v>
+        <v>831029.3047051319</v>
       </c>
       <c r="P128" t="n">
         <v>4900</v>
@@ -6191,10 +6191,10 @@
         <v>850</v>
       </c>
       <c r="N133" t="n">
-        <v>6207.9882013781</v>
+        <v>6207.9881978301</v>
       </c>
       <c r="O133" t="n">
-        <v>5276789.971171385</v>
+        <v>5276789.968155585</v>
       </c>
       <c r="P133" t="n">
         <v>9900</v>
@@ -6240,10 +6240,10 @@
         <v>36</v>
       </c>
       <c r="N134" t="n">
-        <v>4285.1966145833</v>
+        <v>4285.1966318538</v>
       </c>
       <c r="O134" t="n">
-        <v>154267.0781249988</v>
+        <v>154267.0787467368</v>
       </c>
       <c r="P134" t="n">
         <v>6900</v>
@@ -6414,16 +6414,16 @@
         <v>908</v>
       </c>
       <c r="N138" t="n">
-        <v>4814.2633516301</v>
+        <v>4814.2633494176</v>
       </c>
       <c r="O138" t="n">
-        <v>4371351.123280131</v>
+        <v>4371351.121271181</v>
       </c>
       <c r="P138" t="n">
-        <v>9900</v>
+        <v>7900</v>
       </c>
       <c r="Q138" t="n">
-        <v>8989200</v>
+        <v>7173200</v>
       </c>
     </row>
     <row r="139">
@@ -6489,7 +6489,7 @@
         </is>
       </c>
       <c r="J140" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="K140" t="n">
         <v>0</v>
@@ -6498,19 +6498,19 @@
         <v>0</v>
       </c>
       <c r="M140" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N140" t="n">
         <v>60174</v>
       </c>
       <c r="O140" t="n">
-        <v>5596182</v>
+        <v>5415660</v>
       </c>
       <c r="P140" t="n">
         <v>96900</v>
       </c>
       <c r="Q140" t="n">
-        <v>9011700</v>
+        <v>8721000</v>
       </c>
     </row>
     <row r="141">
@@ -6910,10 +6910,10 @@
         <v>221</v>
       </c>
       <c r="N149" t="n">
-        <v>8332.7795967742</v>
+        <v>8332.7795945946</v>
       </c>
       <c r="O149" t="n">
-        <v>1841544.290887098</v>
+        <v>1841544.290405407</v>
       </c>
       <c r="P149" t="n">
         <v>14900</v>
@@ -7337,12 +7337,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>C4277</t>
+          <t>C4281</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>FICHAS DE ARMAR C4277</t>
+          <t>FICHAS DE ARMAR C4281</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -7356,7 +7356,7 @@
         </is>
       </c>
       <c r="J159" t="n">
-        <v>42</v>
+        <v>96</v>
       </c>
       <c r="K159" t="n">
         <v>0</v>
@@ -7365,30 +7365,30 @@
         <v>0</v>
       </c>
       <c r="M159" t="n">
-        <v>42</v>
+        <v>96</v>
       </c>
       <c r="N159" t="n">
-        <v>18536</v>
+        <v>15824</v>
       </c>
       <c r="O159" t="n">
-        <v>778512</v>
+        <v>1519104</v>
       </c>
       <c r="P159" t="n">
-        <v>30900</v>
+        <v>26900</v>
       </c>
       <c r="Q159" t="n">
-        <v>1297800</v>
+        <v>2582400</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>C4281</t>
+          <t>C4282</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>FICHAS DE ARMAR C4281</t>
+          <t>FICHAS DE ARMAR C4282</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -7402,7 +7402,7 @@
         </is>
       </c>
       <c r="J160" t="n">
-        <v>96</v>
+        <v>26</v>
       </c>
       <c r="K160" t="n">
         <v>0</v>
@@ -7411,30 +7411,30 @@
         <v>0</v>
       </c>
       <c r="M160" t="n">
-        <v>96</v>
+        <v>26</v>
       </c>
       <c r="N160" t="n">
-        <v>15824</v>
+        <v>55139</v>
       </c>
       <c r="O160" t="n">
-        <v>1519104</v>
+        <v>1433614</v>
       </c>
       <c r="P160" t="n">
-        <v>26900</v>
+        <v>89900</v>
       </c>
       <c r="Q160" t="n">
-        <v>2582400</v>
+        <v>2337400</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>C4282</t>
+          <t>C4284</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>FICHAS DE ARMAR C4282</t>
+          <t>FICHAS DE ARMAR C4284</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -7448,7 +7448,7 @@
         </is>
       </c>
       <c r="J161" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="K161" t="n">
         <v>0</v>
@@ -7457,30 +7457,30 @@
         <v>0</v>
       </c>
       <c r="M161" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="N161" t="n">
-        <v>55139</v>
+        <v>61602</v>
       </c>
       <c r="O161" t="n">
-        <v>1433614</v>
+        <v>924030</v>
       </c>
       <c r="P161" t="n">
-        <v>89900</v>
+        <v>101900</v>
       </c>
       <c r="Q161" t="n">
-        <v>2337400</v>
+        <v>1528500</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>C4284</t>
+          <t>C4285</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>FICHAS DE ARMAR C4284</t>
+          <t>FICHAS DE ARMAR C4285</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -7494,7 +7494,7 @@
         </is>
       </c>
       <c r="J162" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K162" t="n">
         <v>0</v>
@@ -7503,30 +7503,30 @@
         <v>0</v>
       </c>
       <c r="M162" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="N162" t="n">
-        <v>61602</v>
+        <v>42899</v>
       </c>
       <c r="O162" t="n">
-        <v>924030</v>
+        <v>815081</v>
       </c>
       <c r="P162" t="n">
-        <v>101900</v>
+        <v>70900</v>
       </c>
       <c r="Q162" t="n">
-        <v>1528500</v>
+        <v>1347100</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>C4285</t>
+          <t>C4294</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>FICHAS DE ARMAR C4285</t>
+          <t>FICHAS DE ARMAR C4294</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -7540,7 +7540,7 @@
         </is>
       </c>
       <c r="J163" t="n">
-        <v>19</v>
+        <v>128</v>
       </c>
       <c r="K163" t="n">
         <v>0</v>
@@ -7549,30 +7549,30 @@
         <v>0</v>
       </c>
       <c r="M163" t="n">
-        <v>19</v>
+        <v>128</v>
       </c>
       <c r="N163" t="n">
-        <v>42899</v>
+        <v>3486</v>
       </c>
       <c r="O163" t="n">
-        <v>815081</v>
+        <v>446208</v>
       </c>
       <c r="P163" t="n">
-        <v>70900</v>
+        <v>6900</v>
       </c>
       <c r="Q163" t="n">
-        <v>1347100</v>
+        <v>883200</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>C4294</t>
+          <t>C4295</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>FICHAS DE ARMAR C4294</t>
+          <t>FICHAS DE ARMAR C4295</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -7586,7 +7586,7 @@
         </is>
       </c>
       <c r="J164" t="n">
-        <v>128</v>
+        <v>680</v>
       </c>
       <c r="K164" t="n">
         <v>0</v>
@@ -7595,30 +7595,30 @@
         <v>0</v>
       </c>
       <c r="M164" t="n">
-        <v>128</v>
+        <v>680</v>
       </c>
       <c r="N164" t="n">
-        <v>3486</v>
+        <v>1778.4728955224</v>
       </c>
       <c r="O164" t="n">
-        <v>446208</v>
+        <v>1209361.568955232</v>
       </c>
       <c r="P164" t="n">
-        <v>6900</v>
+        <v>4900</v>
       </c>
       <c r="Q164" t="n">
-        <v>883200</v>
+        <v>3332000</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>C4295</t>
+          <t>C4302</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>FICHAS DE ARMAR C4295</t>
+          <t>MUÑECA GRANDE CON VESTIDO Y SOMBRERO EN BOLSA C4302</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -7632,7 +7632,7 @@
         </is>
       </c>
       <c r="J165" t="n">
-        <v>680</v>
+        <v>192</v>
       </c>
       <c r="K165" t="n">
         <v>0</v>
@@ -7641,30 +7641,30 @@
         <v>0</v>
       </c>
       <c r="M165" t="n">
-        <v>680</v>
+        <v>192</v>
       </c>
       <c r="N165" t="n">
-        <v>1778.4728955224</v>
+        <v>22739</v>
       </c>
       <c r="O165" t="n">
-        <v>1209361.568955232</v>
+        <v>4365888</v>
       </c>
       <c r="P165" t="n">
-        <v>4900</v>
+        <v>36900</v>
       </c>
       <c r="Q165" t="n">
-        <v>3332000</v>
+        <v>7084800</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>C4302</t>
+          <t>C4303</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>MUÑECA GRANDE CON VESTIDO Y SOMBRERO EN BOLSA C4302</t>
+          <t>BEBE CON PIJAMA MED BOLSA PVC C4303</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="J166" t="n">
-        <v>192</v>
+        <v>421</v>
       </c>
       <c r="K166" t="n">
         <v>0</v>
@@ -7687,30 +7687,30 @@
         <v>0</v>
       </c>
       <c r="M166" t="n">
-        <v>192</v>
+        <v>421</v>
       </c>
       <c r="N166" t="n">
-        <v>22739</v>
+        <v>18016</v>
       </c>
       <c r="O166" t="n">
-        <v>4365888</v>
+        <v>7584736</v>
       </c>
       <c r="P166" t="n">
-        <v>36900</v>
+        <v>29900</v>
       </c>
       <c r="Q166" t="n">
-        <v>7084800</v>
+        <v>12587900</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>C4303</t>
+          <t>C4304</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>BEBE CON PIJAMA MED BOLSA PVC C4303</t>
+          <t>MUÑECA BEBE CON CHUPO EN BOLSA C4304</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -7724,7 +7724,7 @@
         </is>
       </c>
       <c r="J167" t="n">
-        <v>421</v>
+        <v>160</v>
       </c>
       <c r="K167" t="n">
         <v>0</v>
@@ -7733,30 +7733,30 @@
         <v>0</v>
       </c>
       <c r="M167" t="n">
-        <v>421</v>
+        <v>160</v>
       </c>
       <c r="N167" t="n">
-        <v>18016</v>
+        <v>16058</v>
       </c>
       <c r="O167" t="n">
-        <v>7584736</v>
+        <v>2569280</v>
       </c>
       <c r="P167" t="n">
-        <v>29900</v>
+        <v>25900</v>
       </c>
       <c r="Q167" t="n">
-        <v>12587900</v>
+        <v>4144000</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>C4304</t>
+          <t>C4305</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>MUÑECA BEBE CON CHUPO EN BOLSA C4304</t>
+          <t>MUÑECA BEBE GRANDE CON PIJAMA EN BOLSA C4305</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -7770,7 +7770,7 @@
         </is>
       </c>
       <c r="J168" t="n">
-        <v>160</v>
+        <v>396</v>
       </c>
       <c r="K168" t="n">
         <v>0</v>
@@ -7779,30 +7779,30 @@
         <v>0</v>
       </c>
       <c r="M168" t="n">
-        <v>160</v>
+        <v>396</v>
       </c>
       <c r="N168" t="n">
-        <v>16058</v>
+        <v>25534</v>
       </c>
       <c r="O168" t="n">
-        <v>2569280</v>
+        <v>10111464</v>
       </c>
       <c r="P168" t="n">
-        <v>25900</v>
+        <v>40900</v>
       </c>
       <c r="Q168" t="n">
-        <v>4144000</v>
+        <v>16196400</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>C4305</t>
+          <t>C4310</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>MUÑECA BEBE GRANDE CON PIJAMA EN BOLSA C4305</t>
+          <t>MUÑECA CON CARRO HUMO RECARGABLE C4310</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -7816,7 +7816,7 @@
         </is>
       </c>
       <c r="J169" t="n">
-        <v>396</v>
+        <v>100</v>
       </c>
       <c r="K169" t="n">
         <v>0</v>
@@ -7825,30 +7825,30 @@
         <v>0</v>
       </c>
       <c r="M169" t="n">
-        <v>396</v>
+        <v>100</v>
       </c>
       <c r="N169" t="n">
-        <v>25534</v>
+        <v>72889</v>
       </c>
       <c r="O169" t="n">
-        <v>10111464</v>
+        <v>7288900</v>
       </c>
       <c r="P169" t="n">
-        <v>40900</v>
+        <v>117500</v>
       </c>
       <c r="Q169" t="n">
-        <v>16196400</v>
+        <v>11750000</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>C4310</t>
+          <t>C4386</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>MUÑECA CON CARRO HUMO RECARGABLE C4310</t>
+          <t>MALETA VIAJERA HERRAMIENTAS</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -7862,7 +7862,7 @@
         </is>
       </c>
       <c r="J170" t="n">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="K170" t="n">
         <v>0</v>
@@ -7871,30 +7871,30 @@
         <v>0</v>
       </c>
       <c r="M170" t="n">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="N170" t="n">
-        <v>72889</v>
+        <v>44055</v>
       </c>
       <c r="O170" t="n">
-        <v>7288900</v>
+        <v>3171960</v>
       </c>
       <c r="P170" t="n">
-        <v>117500</v>
+        <v>70900</v>
       </c>
       <c r="Q170" t="n">
-        <v>11750000</v>
+        <v>5104800</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>C4386</t>
+          <t>C4387</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>MALETA VIAJERA HERRAMIENTAS</t>
+          <t>MAQUILLAJE DONNA C4387</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -7908,7 +7908,7 @@
         </is>
       </c>
       <c r="J171" t="n">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="K171" t="n">
         <v>0</v>
@@ -7917,35 +7917,38 @@
         <v>0</v>
       </c>
       <c r="M171" t="n">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="N171" t="n">
-        <v>44055</v>
+        <v>4917</v>
       </c>
       <c r="O171" t="n">
-        <v>3171960</v>
+        <v>472032</v>
       </c>
       <c r="P171" t="n">
-        <v>70900</v>
+        <v>8600</v>
       </c>
       <c r="Q171" t="n">
-        <v>5104800</v>
+        <v>825600</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>C4387</t>
-        </is>
+          <t>C439</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>6914919077302</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>MAQUILLAJE DONNA C4387</t>
+          <t>globo burbuja 10</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>GLOBOS</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -7954,7 +7957,7 @@
         </is>
       </c>
       <c r="J172" t="n">
-        <v>96</v>
+        <v>38365</v>
       </c>
       <c r="K172" t="n">
         <v>0</v>
@@ -7963,38 +7966,35 @@
         <v>0</v>
       </c>
       <c r="M172" t="n">
-        <v>96</v>
+        <v>38365</v>
       </c>
       <c r="N172" t="n">
-        <v>4917</v>
+        <v>239.91</v>
       </c>
       <c r="O172" t="n">
-        <v>472032</v>
+        <v>9204147.15</v>
       </c>
       <c r="P172" t="n">
-        <v>8600</v>
+        <v>300</v>
       </c>
       <c r="Q172" t="n">
-        <v>825600</v>
+        <v>11509500</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>C439</t>
-        </is>
-      </c>
-      <c r="B173" t="n">
-        <v>6914919077302</v>
+          <t>C4393</t>
+        </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>globo burbuja 10</t>
+          <t>MESA DE BILLAR C4393</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>GLOBOS</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -8003,7 +8003,7 @@
         </is>
       </c>
       <c r="J173" t="n">
-        <v>38365</v>
+        <v>84</v>
       </c>
       <c r="K173" t="n">
         <v>0</v>
@@ -8012,30 +8012,30 @@
         <v>0</v>
       </c>
       <c r="M173" t="n">
-        <v>38365</v>
+        <v>84</v>
       </c>
       <c r="N173" t="n">
-        <v>239.91</v>
+        <v>32295</v>
       </c>
       <c r="O173" t="n">
-        <v>9204147.15</v>
+        <v>2712780</v>
       </c>
       <c r="P173" t="n">
-        <v>300</v>
+        <v>51900</v>
       </c>
       <c r="Q173" t="n">
-        <v>11509500</v>
+        <v>4359600</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>C4393</t>
+          <t>C4406</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>MESA DE BILLAR C4393</t>
+          <t>LANZADORA AUTOMATICA</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="J174" t="n">
-        <v>84</v>
+        <v>14</v>
       </c>
       <c r="K174" t="n">
         <v>0</v>
@@ -8058,30 +8058,30 @@
         <v>0</v>
       </c>
       <c r="M174" t="n">
-        <v>84</v>
+        <v>14</v>
       </c>
       <c r="N174" t="n">
-        <v>32295</v>
+        <v>55898</v>
       </c>
       <c r="O174" t="n">
-        <v>2712780</v>
+        <v>782572</v>
       </c>
       <c r="P174" t="n">
-        <v>51900</v>
+        <v>89900</v>
       </c>
       <c r="Q174" t="n">
-        <v>4359600</v>
+        <v>1258600</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>C4406</t>
+          <t>C4408</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>LANZADORA AUTOMATICA</t>
+          <t>CANCHA DE FUTBOL BOLSA PVC C4408</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -8095,7 +8095,7 @@
         </is>
       </c>
       <c r="J175" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="K175" t="n">
         <v>0</v>
@@ -8104,30 +8104,30 @@
         <v>0</v>
       </c>
       <c r="M175" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="N175" t="n">
-        <v>55898</v>
+        <v>11857</v>
       </c>
       <c r="O175" t="n">
-        <v>782572</v>
+        <v>355710</v>
       </c>
       <c r="P175" t="n">
-        <v>89900</v>
+        <v>19900</v>
       </c>
       <c r="Q175" t="n">
-        <v>1258600</v>
+        <v>597000</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>C4408</t>
+          <t>C4410</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>CANCHA DE FUTBOL BOLSA PVC C4408</t>
+          <t>PIANO MUSICAL CONEJO MED C4410</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -8141,7 +8141,7 @@
         </is>
       </c>
       <c r="J176" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="K176" t="n">
         <v>0</v>
@@ -8150,30 +8150,30 @@
         <v>0</v>
       </c>
       <c r="M176" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="N176" t="n">
-        <v>11857</v>
+        <v>7713</v>
       </c>
       <c r="O176" t="n">
-        <v>355710</v>
+        <v>431928</v>
       </c>
       <c r="P176" t="n">
-        <v>19900</v>
+        <v>12500</v>
       </c>
       <c r="Q176" t="n">
-        <v>597000</v>
+        <v>700000</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>C4410</t>
+          <t>C4415</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>PIANO MUSICAL CONEJO MED C4410</t>
+          <t>MOVIL BEBES LUZ-SONIDOS</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -8187,7 +8187,7 @@
         </is>
       </c>
       <c r="J177" t="n">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="K177" t="n">
         <v>0</v>
@@ -8196,30 +8196,30 @@
         <v>0</v>
       </c>
       <c r="M177" t="n">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="N177" t="n">
-        <v>7713</v>
+        <v>28116</v>
       </c>
       <c r="O177" t="n">
-        <v>431928</v>
+        <v>337392</v>
       </c>
       <c r="P177" t="n">
-        <v>12500</v>
+        <v>45900</v>
       </c>
       <c r="Q177" t="n">
-        <v>700000</v>
+        <v>550800</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>C4415</t>
+          <t>C4416</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>MOVIL BEBES LUZ-SONIDOS</t>
+          <t>AJEDREZ MAGNETICO  C4416</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -8233,7 +8233,7 @@
         </is>
       </c>
       <c r="J178" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K178" t="n">
         <v>0</v>
@@ -8242,30 +8242,30 @@
         <v>0</v>
       </c>
       <c r="M178" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="N178" t="n">
-        <v>28116</v>
+        <v>24847</v>
       </c>
       <c r="O178" t="n">
-        <v>337392</v>
+        <v>894492</v>
       </c>
       <c r="P178" t="n">
-        <v>45900</v>
+        <v>39900</v>
       </c>
       <c r="Q178" t="n">
-        <v>550800</v>
+        <v>1436400</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>C4416</t>
+          <t>C4433</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>AJEDREZ MAGNETICO  C4416</t>
+          <t>AVION LUCES SONIDOS</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -8279,7 +8279,7 @@
         </is>
       </c>
       <c r="J179" t="n">
-        <v>36</v>
+        <v>180</v>
       </c>
       <c r="K179" t="n">
         <v>0</v>
@@ -8288,30 +8288,30 @@
         <v>0</v>
       </c>
       <c r="M179" t="n">
-        <v>36</v>
+        <v>180</v>
       </c>
       <c r="N179" t="n">
-        <v>24847</v>
+        <v>10411</v>
       </c>
       <c r="O179" t="n">
-        <v>894492</v>
+        <v>1873980</v>
       </c>
       <c r="P179" t="n">
-        <v>39900</v>
+        <v>16900</v>
       </c>
       <c r="Q179" t="n">
-        <v>1436400</v>
+        <v>3042000</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>C4433</t>
+          <t>C4443</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>AVION LUCES SONIDOS</t>
+          <t>CARRITO BURBUJERO DINOSAURIO C4443</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -8325,7 +8325,7 @@
         </is>
       </c>
       <c r="J180" t="n">
-        <v>180</v>
+        <v>36</v>
       </c>
       <c r="K180" t="n">
         <v>0</v>
@@ -8334,30 +8334,30 @@
         <v>0</v>
       </c>
       <c r="M180" t="n">
-        <v>180</v>
+        <v>36</v>
       </c>
       <c r="N180" t="n">
-        <v>10642.355555556</v>
+        <v>17644.653392857</v>
       </c>
       <c r="O180" t="n">
-        <v>1915624.00000008</v>
+        <v>635207.522142852</v>
       </c>
       <c r="P180" t="n">
-        <v>16900</v>
+        <v>28200</v>
       </c>
       <c r="Q180" t="n">
-        <v>3042000</v>
+        <v>1015200</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>C4443</t>
+          <t>C446-IO</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>CARRITO BURBUJERO DINOSAURIO C4443</t>
+          <t>GLOBO UNICORNIO PQÑO 4PATAS</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="J181" t="n">
-        <v>36</v>
+        <v>2200</v>
       </c>
       <c r="K181" t="n">
         <v>0</v>
@@ -8380,30 +8380,30 @@
         <v>0</v>
       </c>
       <c r="M181" t="n">
-        <v>36</v>
+        <v>2200</v>
       </c>
       <c r="N181" t="n">
-        <v>17644.653392857</v>
+        <v>880</v>
       </c>
       <c r="O181" t="n">
-        <v>635207.522142852</v>
+        <v>1936000</v>
       </c>
       <c r="P181" t="n">
-        <v>28200</v>
+        <v>1100</v>
       </c>
       <c r="Q181" t="n">
-        <v>1015200</v>
+        <v>2420000</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>C446-IO</t>
+          <t>C4466</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>GLOBO UNICORNIO PQÑO 4PATAS</t>
+          <t>MAQUINA DE SLIME C4466</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -8417,7 +8417,7 @@
         </is>
       </c>
       <c r="J182" t="n">
-        <v>2200</v>
+        <v>136</v>
       </c>
       <c r="K182" t="n">
         <v>0</v>
@@ -8426,30 +8426,30 @@
         <v>0</v>
       </c>
       <c r="M182" t="n">
-        <v>2200</v>
+        <v>136</v>
       </c>
       <c r="N182" t="n">
-        <v>880</v>
+        <v>21676</v>
       </c>
       <c r="O182" t="n">
-        <v>1936000</v>
+        <v>2947936</v>
       </c>
       <c r="P182" t="n">
-        <v>1100</v>
+        <v>34900</v>
       </c>
       <c r="Q182" t="n">
-        <v>2420000</v>
+        <v>4746400</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>C4466</t>
+          <t>C4468</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>MAQUINA DE SLIME C4466</t>
+          <t>MAQUINA PARA HACER PULSERAS C4468</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -8463,7 +8463,7 @@
         </is>
       </c>
       <c r="J183" t="n">
-        <v>136</v>
+        <v>103</v>
       </c>
       <c r="K183" t="n">
         <v>0</v>
@@ -8472,30 +8472,30 @@
         <v>0</v>
       </c>
       <c r="M183" t="n">
-        <v>136</v>
+        <v>103</v>
       </c>
       <c r="N183" t="n">
-        <v>21676</v>
+        <v>9384</v>
       </c>
       <c r="O183" t="n">
-        <v>2947936</v>
+        <v>966552</v>
       </c>
       <c r="P183" t="n">
-        <v>34900</v>
+        <v>15900</v>
       </c>
       <c r="Q183" t="n">
-        <v>4746400</v>
+        <v>1637700</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>C4468</t>
+          <t>C4475</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>MAQUINA PARA HACER PULSERAS C4468</t>
+          <t>LANZADORAS BIOGEL MODELOS STD C4475</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="J184" t="n">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="K184" t="n">
         <v>0</v>
@@ -8518,30 +8518,30 @@
         <v>0</v>
       </c>
       <c r="M184" t="n">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="N184" t="n">
-        <v>9384</v>
+        <v>32332</v>
       </c>
       <c r="O184" t="n">
-        <v>966552</v>
+        <v>3976836</v>
       </c>
       <c r="P184" t="n">
-        <v>15900</v>
+        <v>55900</v>
       </c>
       <c r="Q184" t="n">
-        <v>1637700</v>
+        <v>6875700</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>C4475</t>
+          <t>C4485</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>LANZADORAS BIOGEL MODELOS STD C4475</t>
+          <t>LANZADORA AGUA BIOGEL C4485</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -8555,7 +8555,7 @@
         </is>
       </c>
       <c r="J185" t="n">
-        <v>123</v>
+        <v>20</v>
       </c>
       <c r="K185" t="n">
         <v>0</v>
@@ -8564,30 +8564,30 @@
         <v>0</v>
       </c>
       <c r="M185" t="n">
-        <v>123</v>
+        <v>20</v>
       </c>
       <c r="N185" t="n">
-        <v>32332</v>
+        <v>34912</v>
       </c>
       <c r="O185" t="n">
-        <v>3976836</v>
+        <v>698240</v>
       </c>
       <c r="P185" t="n">
-        <v>55900</v>
+        <v>56900</v>
       </c>
       <c r="Q185" t="n">
-        <v>6875700</v>
+        <v>1138000</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>C4485</t>
+          <t>C4486</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>LANZADORA AGUA BIOGEL C4485</t>
+          <t>CHILLONES DINOSAURIOS C4486</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -8601,7 +8601,7 @@
         </is>
       </c>
       <c r="J186" t="n">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="K186" t="n">
         <v>0</v>
@@ -8610,30 +8610,30 @@
         <v>0</v>
       </c>
       <c r="M186" t="n">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="N186" t="n">
-        <v>34912</v>
+        <v>3519</v>
       </c>
       <c r="O186" t="n">
-        <v>698240</v>
+        <v>263925</v>
       </c>
       <c r="P186" t="n">
-        <v>56900</v>
+        <v>5900</v>
       </c>
       <c r="Q186" t="n">
-        <v>1138000</v>
+        <v>442500</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>C4486</t>
+          <t>C4487</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>CHILLONES DINOSAURIOS C4486</t>
+          <t>JUEGO DOMINO TREN C4487</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -8647,7 +8647,7 @@
         </is>
       </c>
       <c r="J187" t="n">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="K187" t="n">
         <v>0</v>
@@ -8656,30 +8656,30 @@
         <v>0</v>
       </c>
       <c r="M187" t="n">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="N187" t="n">
-        <v>3519</v>
+        <v>15760</v>
       </c>
       <c r="O187" t="n">
-        <v>263925</v>
+        <v>315200</v>
       </c>
       <c r="P187" t="n">
-        <v>5900</v>
+        <v>25000</v>
       </c>
       <c r="Q187" t="n">
-        <v>442500</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>C4487</t>
+          <t>C4488</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>JUEGO DOMINO TREN C4487</t>
+          <t>RANITA LUZ Y SONIDO C4488</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="J188" t="n">
-        <v>20</v>
+        <v>124</v>
       </c>
       <c r="K188" t="n">
         <v>0</v>
@@ -8702,30 +8702,30 @@
         <v>0</v>
       </c>
       <c r="M188" t="n">
-        <v>20</v>
+        <v>124</v>
       </c>
       <c r="N188" t="n">
-        <v>15760</v>
+        <v>9003</v>
       </c>
       <c r="O188" t="n">
-        <v>315200</v>
+        <v>1116372</v>
       </c>
       <c r="P188" t="n">
-        <v>25000</v>
+        <v>14900</v>
       </c>
       <c r="Q188" t="n">
-        <v>500000</v>
+        <v>1847600</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>C4488</t>
+          <t>C4489</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>RANITA LUZ Y SONIDO C4488</t>
+          <t>PATO LUZ Y SONIDO C4489</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -8739,7 +8739,7 @@
         </is>
       </c>
       <c r="J189" t="n">
-        <v>124</v>
+        <v>216</v>
       </c>
       <c r="K189" t="n">
         <v>0</v>
@@ -8748,30 +8748,30 @@
         <v>0</v>
       </c>
       <c r="M189" t="n">
-        <v>124</v>
+        <v>216</v>
       </c>
       <c r="N189" t="n">
-        <v>9003</v>
+        <v>9178</v>
       </c>
       <c r="O189" t="n">
-        <v>1116372</v>
+        <v>1982448</v>
       </c>
       <c r="P189" t="n">
         <v>14900</v>
       </c>
       <c r="Q189" t="n">
-        <v>1847600</v>
+        <v>3218400</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>C4489</t>
+          <t>C4493</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>PATO LUZ Y SONIDO C4489</t>
+          <t>ARCO STD NIÑO Y NIÑA LASER C4493</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -8785,7 +8785,7 @@
         </is>
       </c>
       <c r="J190" t="n">
-        <v>216</v>
+        <v>147</v>
       </c>
       <c r="K190" t="n">
         <v>0</v>
@@ -8794,30 +8794,30 @@
         <v>0</v>
       </c>
       <c r="M190" t="n">
-        <v>216</v>
+        <v>147</v>
       </c>
       <c r="N190" t="n">
-        <v>9178</v>
+        <v>13922</v>
       </c>
       <c r="O190" t="n">
-        <v>1982448</v>
+        <v>2046534</v>
       </c>
       <c r="P190" t="n">
-        <v>14900</v>
+        <v>22900</v>
       </c>
       <c r="Q190" t="n">
-        <v>3218400</v>
+        <v>3366300</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>C4493</t>
+          <t>C4499</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>ARCO STD NIÑO Y NIÑA LASER C4493</t>
+          <t>PIANO ELEFANTE PQÑ C4499</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -8831,7 +8831,7 @@
         </is>
       </c>
       <c r="J191" t="n">
-        <v>147</v>
+        <v>234</v>
       </c>
       <c r="K191" t="n">
         <v>0</v>
@@ -8840,30 +8840,30 @@
         <v>0</v>
       </c>
       <c r="M191" t="n">
-        <v>147</v>
+        <v>234</v>
       </c>
       <c r="N191" t="n">
-        <v>13922</v>
+        <v>6414</v>
       </c>
       <c r="O191" t="n">
-        <v>2046534</v>
+        <v>1500876</v>
       </c>
       <c r="P191" t="n">
-        <v>22900</v>
+        <v>10900</v>
       </c>
       <c r="Q191" t="n">
-        <v>3366300</v>
+        <v>2550600</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>C4499</t>
+          <t>C4504</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>PIANO ELEFANTE PQÑ C4499</t>
+          <t>CASTILLO ACCESORIOS STD C4504</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -8877,7 +8877,7 @@
         </is>
       </c>
       <c r="J192" t="n">
-        <v>234</v>
+        <v>12</v>
       </c>
       <c r="K192" t="n">
         <v>0</v>
@@ -8886,30 +8886,30 @@
         <v>0</v>
       </c>
       <c r="M192" t="n">
-        <v>234</v>
+        <v>12</v>
       </c>
       <c r="N192" t="n">
-        <v>6414</v>
+        <v>23376.36</v>
       </c>
       <c r="O192" t="n">
-        <v>1500876</v>
+        <v>280516.32</v>
       </c>
       <c r="P192" t="n">
-        <v>10900</v>
+        <v>40900</v>
       </c>
       <c r="Q192" t="n">
-        <v>2550600</v>
+        <v>490800</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>C4504</t>
+          <t>C4505</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>CASTILLO ACCESORIOS STD C4504</t>
+          <t>PESCADITO Y TIBURON  LUZ Y SONIDO C4505</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -8923,7 +8923,7 @@
         </is>
       </c>
       <c r="J193" t="n">
-        <v>12</v>
+        <v>460</v>
       </c>
       <c r="K193" t="n">
         <v>0</v>
@@ -8932,30 +8932,30 @@
         <v>0</v>
       </c>
       <c r="M193" t="n">
-        <v>12</v>
+        <v>460</v>
       </c>
       <c r="N193" t="n">
-        <v>23376.36</v>
+        <v>13210</v>
       </c>
       <c r="O193" t="n">
-        <v>280516.32</v>
+        <v>6076600</v>
       </c>
       <c r="P193" t="n">
-        <v>40900</v>
+        <v>23900</v>
       </c>
       <c r="Q193" t="n">
-        <v>490800</v>
+        <v>10994000</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>C4505</t>
+          <t>C4510</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>PESCADITO Y TIBURON  LUZ Y SONIDO C4505</t>
+          <t>TOCADOR CASTILLO MUSICA Y LUZ C4510</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -8969,7 +8969,7 @@
         </is>
       </c>
       <c r="J194" t="n">
-        <v>460</v>
+        <v>144</v>
       </c>
       <c r="K194" t="n">
         <v>0</v>
@@ -8978,30 +8978,30 @@
         <v>0</v>
       </c>
       <c r="M194" t="n">
-        <v>460</v>
+        <v>144</v>
       </c>
       <c r="N194" t="n">
-        <v>13210</v>
+        <v>52443</v>
       </c>
       <c r="O194" t="n">
-        <v>6076600</v>
+        <v>7551792</v>
       </c>
       <c r="P194" t="n">
-        <v>23900</v>
+        <v>83900</v>
       </c>
       <c r="Q194" t="n">
-        <v>10994000</v>
+        <v>12081600</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>C4510</t>
+          <t>C4511</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>TOCADOR CASTILLO MUSICA Y LUZ C4510</t>
+          <t>BURBUJERO MODELOS STDS C4511</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -9015,7 +9015,7 @@
         </is>
       </c>
       <c r="J195" t="n">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="K195" t="n">
         <v>0</v>
@@ -9024,35 +9024,30 @@
         <v>0</v>
       </c>
       <c r="M195" t="n">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="N195" t="n">
-        <v>52443</v>
+        <v>3903.7404686036</v>
       </c>
       <c r="O195" t="n">
-        <v>7551792</v>
+        <v>503582.5204498644</v>
       </c>
       <c r="P195" t="n">
-        <v>83900</v>
+        <v>7500</v>
       </c>
       <c r="Q195" t="n">
-        <v>12081600</v>
+        <v>967500</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>C4511</t>
+          <t>C4512</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>BURBUJERO MODELOS STDS C4511</t>
-        </is>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>MAQUILLAJE ESTUCHE UNICORNIO C4512</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -9061,7 +9056,7 @@
         </is>
       </c>
       <c r="J196" t="n">
-        <v>129</v>
+        <v>40</v>
       </c>
       <c r="K196" t="n">
         <v>0</v>
@@ -9070,30 +9065,30 @@
         <v>0</v>
       </c>
       <c r="M196" t="n">
-        <v>129</v>
+        <v>40</v>
       </c>
       <c r="N196" t="n">
-        <v>3903.7403351955</v>
+        <v>20726</v>
       </c>
       <c r="O196" t="n">
-        <v>503582.5032402195</v>
+        <v>829040</v>
       </c>
       <c r="P196" t="n">
-        <v>7500</v>
+        <v>33900</v>
       </c>
       <c r="Q196" t="n">
-        <v>967500</v>
+        <v>1356000</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>C4512</t>
+          <t>C4513</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>MAQUILLAJE ESTUCHE UNICORNIO C4512</t>
+          <t>ESTUCHE MAQUILLAJE UNICORNIO CON BALACA C4513</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -9102,7 +9097,7 @@
         </is>
       </c>
       <c r="J197" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="K197" t="n">
         <v>0</v>
@@ -9111,30 +9106,35 @@
         <v>0</v>
       </c>
       <c r="M197" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="N197" t="n">
-        <v>20726</v>
+        <v>35864.602181818</v>
       </c>
       <c r="O197" t="n">
-        <v>829040</v>
+        <v>1255261.07636363</v>
       </c>
       <c r="P197" t="n">
-        <v>33900</v>
+        <v>62900</v>
       </c>
       <c r="Q197" t="n">
-        <v>1356000</v>
+        <v>2201500</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>C4513</t>
+          <t>C4514</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>ESTUCHE MAQUILLAJE UNICORNIO CON BALACA C4513</t>
+          <t>ESTUCHE MAQUILLAJE PARA UÑAS C4514</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -9143,7 +9143,7 @@
         </is>
       </c>
       <c r="J198" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="K198" t="n">
         <v>0</v>
@@ -9152,30 +9152,30 @@
         <v>0</v>
       </c>
       <c r="M198" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="N198" t="n">
-        <v>35864.602181818</v>
+        <v>20731</v>
       </c>
       <c r="O198" t="n">
-        <v>1255261.07636363</v>
+        <v>953626</v>
       </c>
       <c r="P198" t="n">
-        <v>62900</v>
+        <v>33900</v>
       </c>
       <c r="Q198" t="n">
-        <v>2201500</v>
+        <v>1559400</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>C4514</t>
+          <t>C4521</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>ESTUCHE MAQUILLAJE PARA UÑAS C4514</t>
+          <t>JUEGO DE AJEDREZ 3EN1</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -9189,7 +9189,7 @@
         </is>
       </c>
       <c r="J199" t="n">
-        <v>46</v>
+        <v>118</v>
       </c>
       <c r="K199" t="n">
         <v>0</v>
@@ -9198,30 +9198,30 @@
         <v>0</v>
       </c>
       <c r="M199" t="n">
-        <v>46</v>
+        <v>118</v>
       </c>
       <c r="N199" t="n">
-        <v>20731</v>
+        <v>4202</v>
       </c>
       <c r="O199" t="n">
-        <v>953626</v>
+        <v>495836</v>
       </c>
       <c r="P199" t="n">
-        <v>33900</v>
+        <v>7900</v>
       </c>
       <c r="Q199" t="n">
-        <v>1559400</v>
+        <v>932200</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>C4521</t>
+          <t>C4523</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>JUEGO DE AJEDREZ 3EN1</t>
+          <t>PIANO TAPETE MUSICAL C4523</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -9235,7 +9235,7 @@
         </is>
       </c>
       <c r="J200" t="n">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="K200" t="n">
         <v>0</v>
@@ -9244,30 +9244,30 @@
         <v>0</v>
       </c>
       <c r="M200" t="n">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="N200" t="n">
-        <v>4202</v>
+        <v>16469</v>
       </c>
       <c r="O200" t="n">
-        <v>495836</v>
+        <v>2371536</v>
       </c>
       <c r="P200" t="n">
-        <v>7900</v>
+        <v>26900</v>
       </c>
       <c r="Q200" t="n">
-        <v>932200</v>
+        <v>3873600</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>C4523</t>
+          <t>C4525</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>PIANO TAPETE MUSICAL C4523</t>
+          <t>LANZADORA CATAPULTA C4525</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -9281,7 +9281,7 @@
         </is>
       </c>
       <c r="J201" t="n">
-        <v>144</v>
+        <v>18</v>
       </c>
       <c r="K201" t="n">
         <v>0</v>
@@ -9290,30 +9290,30 @@
         <v>0</v>
       </c>
       <c r="M201" t="n">
-        <v>144</v>
+        <v>18</v>
       </c>
       <c r="N201" t="n">
-        <v>16469</v>
+        <v>11922</v>
       </c>
       <c r="O201" t="n">
-        <v>2371536</v>
+        <v>214596</v>
       </c>
       <c r="P201" t="n">
-        <v>26900</v>
+        <v>19900</v>
       </c>
       <c r="Q201" t="n">
-        <v>3873600</v>
+        <v>358200</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>C4525</t>
+          <t>C4527</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>LANZADORA CATAPULTA C4525</t>
+          <t>MINI PIANO C4527</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -9327,7 +9327,7 @@
         </is>
       </c>
       <c r="J202" t="n">
-        <v>18</v>
+        <v>108</v>
       </c>
       <c r="K202" t="n">
         <v>0</v>
@@ -9336,30 +9336,30 @@
         <v>0</v>
       </c>
       <c r="M202" t="n">
-        <v>18</v>
+        <v>108</v>
       </c>
       <c r="N202" t="n">
-        <v>11922</v>
+        <v>12556</v>
       </c>
       <c r="O202" t="n">
-        <v>214596</v>
+        <v>1356048</v>
       </c>
       <c r="P202" t="n">
-        <v>19900</v>
+        <v>21900</v>
       </c>
       <c r="Q202" t="n">
-        <v>358200</v>
+        <v>2365200</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>C4527</t>
+          <t>C4530</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>MINI PIANO C4527</t>
+          <t>CARRO FORMULAY DINO BURBUJERA C4530</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -9373,7 +9373,7 @@
         </is>
       </c>
       <c r="J203" t="n">
-        <v>108</v>
+        <v>144</v>
       </c>
       <c r="K203" t="n">
         <v>0</v>
@@ -9382,30 +9382,30 @@
         <v>0</v>
       </c>
       <c r="M203" t="n">
-        <v>108</v>
+        <v>144</v>
       </c>
       <c r="N203" t="n">
-        <v>12556</v>
+        <v>5869.1722639485</v>
       </c>
       <c r="O203" t="n">
-        <v>1356048</v>
+        <v>845160.806008584</v>
       </c>
       <c r="P203" t="n">
-        <v>21900</v>
+        <v>9500</v>
       </c>
       <c r="Q203" t="n">
-        <v>2365200</v>
+        <v>1368000</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>C4530</t>
+          <t>C4531</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>CARRO FORMULAY DINO BURBUJERA C4530</t>
+          <t>CARROS RETRO/GRUA STD BOLSA PVC C4531</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -9419,7 +9419,7 @@
         </is>
       </c>
       <c r="J204" t="n">
-        <v>144</v>
+        <v>259</v>
       </c>
       <c r="K204" t="n">
         <v>0</v>
@@ -9428,30 +9428,30 @@
         <v>0</v>
       </c>
       <c r="M204" t="n">
-        <v>144</v>
+        <v>259</v>
       </c>
       <c r="N204" t="n">
-        <v>5869.1723052295</v>
+        <v>6849.2</v>
       </c>
       <c r="O204" t="n">
-        <v>845160.811953048</v>
+        <v>1773942.8</v>
       </c>
       <c r="P204" t="n">
-        <v>9500</v>
+        <v>11500</v>
       </c>
       <c r="Q204" t="n">
-        <v>1368000</v>
+        <v>2978500</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>C4531</t>
+          <t>C4534</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>CARROS RETRO/GRUA STD BOLSA PVC C4531</t>
+          <t>CARROS RETROS STD CAJA X 12 C4534</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -9465,7 +9465,7 @@
         </is>
       </c>
       <c r="J205" t="n">
-        <v>259</v>
+        <v>702</v>
       </c>
       <c r="K205" t="n">
         <v>0</v>
@@ -9474,30 +9474,30 @@
         <v>0</v>
       </c>
       <c r="M205" t="n">
-        <v>259</v>
+        <v>702</v>
       </c>
       <c r="N205" t="n">
-        <v>6849.2</v>
+        <v>5772</v>
       </c>
       <c r="O205" t="n">
-        <v>1773942.8</v>
+        <v>4051944</v>
       </c>
       <c r="P205" t="n">
-        <v>11500</v>
+        <v>9900</v>
       </c>
       <c r="Q205" t="n">
-        <v>2978500</v>
+        <v>6949800</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>C4534</t>
+          <t>C4541</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>CARROS RETROS STD CAJA X 12 C4534</t>
+          <t>LANZADORADARDOS MED C4541</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -9511,7 +9511,7 @@
         </is>
       </c>
       <c r="J206" t="n">
-        <v>702</v>
+        <v>456</v>
       </c>
       <c r="K206" t="n">
         <v>0</v>
@@ -9520,30 +9520,30 @@
         <v>0</v>
       </c>
       <c r="M206" t="n">
-        <v>702</v>
+        <v>456</v>
       </c>
       <c r="N206" t="n">
-        <v>5772</v>
+        <v>6645</v>
       </c>
       <c r="O206" t="n">
-        <v>4051944</v>
+        <v>3030120</v>
       </c>
       <c r="P206" t="n">
-        <v>9900</v>
+        <v>10900</v>
       </c>
       <c r="Q206" t="n">
-        <v>6949800</v>
+        <v>4970400</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>C4541</t>
+          <t>C4542</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>LANZADORADARDOS MED C4541</t>
+          <t>LANZDORA DE DARDOS Y BIOGEL C4542</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -9557,7 +9557,7 @@
         </is>
       </c>
       <c r="J207" t="n">
-        <v>456</v>
+        <v>256</v>
       </c>
       <c r="K207" t="n">
         <v>0</v>
@@ -9566,30 +9566,30 @@
         <v>0</v>
       </c>
       <c r="M207" t="n">
-        <v>456</v>
+        <v>256</v>
       </c>
       <c r="N207" t="n">
-        <v>6645</v>
+        <v>13098</v>
       </c>
       <c r="O207" t="n">
-        <v>3030120</v>
+        <v>3353088</v>
       </c>
       <c r="P207" t="n">
-        <v>10900</v>
+        <v>21200</v>
       </c>
       <c r="Q207" t="n">
-        <v>4970400</v>
+        <v>5427200</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>C4542</t>
+          <t>C4545</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>LANZDORA DE DARDOS Y BIOGEL C4542</t>
+          <t>TAPETE PIANO PARA BEBE C4545</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -9603,7 +9603,7 @@
         </is>
       </c>
       <c r="J208" t="n">
-        <v>256</v>
+        <v>132</v>
       </c>
       <c r="K208" t="n">
         <v>0</v>
@@ -9612,30 +9612,30 @@
         <v>0</v>
       </c>
       <c r="M208" t="n">
-        <v>256</v>
+        <v>132</v>
       </c>
       <c r="N208" t="n">
-        <v>13098</v>
+        <v>27186</v>
       </c>
       <c r="O208" t="n">
-        <v>3353088</v>
+        <v>3588552</v>
       </c>
       <c r="P208" t="n">
-        <v>21200</v>
+        <v>43900</v>
       </c>
       <c r="Q208" t="n">
-        <v>5427200</v>
+        <v>5794800</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>C4545</t>
+          <t>C4547</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>TAPETE PIANO PARA BEBE C4545</t>
+          <t>CASA VILLA ACCESORIOS C4547</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -9649,7 +9649,7 @@
         </is>
       </c>
       <c r="J209" t="n">
-        <v>132</v>
+        <v>84</v>
       </c>
       <c r="K209" t="n">
         <v>0</v>
@@ -9658,30 +9658,30 @@
         <v>0</v>
       </c>
       <c r="M209" t="n">
-        <v>132</v>
+        <v>84</v>
       </c>
       <c r="N209" t="n">
-        <v>27186</v>
+        <v>72535</v>
       </c>
       <c r="O209" t="n">
-        <v>3588552</v>
+        <v>6092940</v>
       </c>
       <c r="P209" t="n">
-        <v>43900</v>
+        <v>116900</v>
       </c>
       <c r="Q209" t="n">
-        <v>5794800</v>
+        <v>9819600</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>C4547</t>
+          <t>C4548</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>CASA VILLA ACCESORIOS C4547</t>
+          <t>CARRO DIDACTICO X4 BEBE</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -9695,7 +9695,7 @@
         </is>
       </c>
       <c r="J210" t="n">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="K210" t="n">
         <v>0</v>
@@ -9704,30 +9704,30 @@
         <v>0</v>
       </c>
       <c r="M210" t="n">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="N210" t="n">
-        <v>72535</v>
+        <v>7562</v>
       </c>
       <c r="O210" t="n">
-        <v>6092940</v>
+        <v>794010</v>
       </c>
       <c r="P210" t="n">
-        <v>116900</v>
+        <v>12900</v>
       </c>
       <c r="Q210" t="n">
-        <v>9819600</v>
+        <v>1354500</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>C4548</t>
+          <t>C4550</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>CARRO DIDACTICO X4 BEBE</t>
+          <t>HELICOPTERO  FASHION C4550</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -9741,7 +9741,7 @@
         </is>
       </c>
       <c r="J211" t="n">
-        <v>105</v>
+        <v>245</v>
       </c>
       <c r="K211" t="n">
         <v>0</v>
@@ -9750,30 +9750,30 @@
         <v>0</v>
       </c>
       <c r="M211" t="n">
-        <v>105</v>
+        <v>245</v>
       </c>
       <c r="N211" t="n">
-        <v>7562</v>
+        <v>13565</v>
       </c>
       <c r="O211" t="n">
-        <v>794010</v>
+        <v>3323425</v>
       </c>
       <c r="P211" t="n">
-        <v>12900</v>
+        <v>22500</v>
       </c>
       <c r="Q211" t="n">
-        <v>1354500</v>
+        <v>5512500</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>C4550</t>
+          <t>C4551</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>HELICOPTERO  FASHION C4550</t>
+          <t>PRINCESS EN CASTILLO Y CARRUAJE C4551</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -9787,7 +9787,7 @@
         </is>
       </c>
       <c r="J212" t="n">
-        <v>245</v>
+        <v>1162</v>
       </c>
       <c r="K212" t="n">
         <v>0</v>
@@ -9796,30 +9796,30 @@
         <v>0</v>
       </c>
       <c r="M212" t="n">
-        <v>245</v>
+        <v>1162</v>
       </c>
       <c r="N212" t="n">
-        <v>13565</v>
+        <v>7635</v>
       </c>
       <c r="O212" t="n">
-        <v>3323425</v>
+        <v>8871870</v>
       </c>
       <c r="P212" t="n">
-        <v>22500</v>
+        <v>13900</v>
       </c>
       <c r="Q212" t="n">
-        <v>5512500</v>
+        <v>16151800</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>C4551</t>
+          <t>C4555</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>PRINCESS EN CASTILLO Y CARRUAJE C4551</t>
+          <t>SONAJERO EN BOLSA 5 PCS C4555</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -9833,7 +9833,7 @@
         </is>
       </c>
       <c r="J213" t="n">
-        <v>1162</v>
+        <v>336</v>
       </c>
       <c r="K213" t="n">
         <v>0</v>
@@ -9842,30 +9842,30 @@
         <v>0</v>
       </c>
       <c r="M213" t="n">
-        <v>1162</v>
+        <v>336</v>
       </c>
       <c r="N213" t="n">
-        <v>7635</v>
+        <v>5438</v>
       </c>
       <c r="O213" t="n">
-        <v>8871870</v>
+        <v>1827168</v>
       </c>
       <c r="P213" t="n">
-        <v>13900</v>
+        <v>8900</v>
       </c>
       <c r="Q213" t="n">
-        <v>16151800</v>
+        <v>2990400</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>C4555</t>
+          <t>C4556</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>SONAJERO EN BOLSA 5 PCS C4555</t>
+          <t>SONAJERO EN CAJA 8PCS C4556</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -9879,7 +9879,7 @@
         </is>
       </c>
       <c r="J214" t="n">
-        <v>336</v>
+        <v>48</v>
       </c>
       <c r="K214" t="n">
         <v>0</v>
@@ -9888,30 +9888,30 @@
         <v>0</v>
       </c>
       <c r="M214" t="n">
-        <v>336</v>
+        <v>48</v>
       </c>
       <c r="N214" t="n">
-        <v>5438</v>
+        <v>16086</v>
       </c>
       <c r="O214" t="n">
-        <v>1827168</v>
+        <v>772128</v>
       </c>
       <c r="P214" t="n">
-        <v>8900</v>
+        <v>25900</v>
       </c>
       <c r="Q214" t="n">
-        <v>2990400</v>
+        <v>1243200</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>C4556</t>
+          <t>C4557</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>SONAJERO EN CAJA 8PCS C4556</t>
+          <t>JUEGO DE UÑAS Y MAQUILLAJE C4557</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -9925,7 +9925,7 @@
         </is>
       </c>
       <c r="J215" t="n">
-        <v>48</v>
+        <v>508</v>
       </c>
       <c r="K215" t="n">
         <v>0</v>
@@ -9934,30 +9934,30 @@
         <v>0</v>
       </c>
       <c r="M215" t="n">
-        <v>48</v>
+        <v>508</v>
       </c>
       <c r="N215" t="n">
-        <v>16086</v>
+        <v>8806</v>
       </c>
       <c r="O215" t="n">
-        <v>772128</v>
+        <v>4473448</v>
       </c>
       <c r="P215" t="n">
-        <v>25900</v>
+        <v>14900</v>
       </c>
       <c r="Q215" t="n">
-        <v>1243200</v>
+        <v>7569200</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>C4557</t>
+          <t>C4559</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>JUEGO DE UÑAS Y MAQUILLAJE C4557</t>
+          <t>PIANO DIDACTICO 3en1 C4559</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -9971,7 +9971,7 @@
         </is>
       </c>
       <c r="J216" t="n">
-        <v>560</v>
+        <v>180</v>
       </c>
       <c r="K216" t="n">
         <v>0</v>
@@ -9980,30 +9980,30 @@
         <v>0</v>
       </c>
       <c r="M216" t="n">
-        <v>560</v>
+        <v>180</v>
       </c>
       <c r="N216" t="n">
-        <v>8806</v>
+        <v>19008</v>
       </c>
       <c r="O216" t="n">
-        <v>4931360</v>
+        <v>3421440</v>
       </c>
       <c r="P216" t="n">
-        <v>14900</v>
+        <v>30900</v>
       </c>
       <c r="Q216" t="n">
-        <v>8344000</v>
+        <v>5562000</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>C4559</t>
+          <t>C4560</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>PIANO DIDACTICO 3en1 C4559</t>
+          <t>PIANO TAPETE C4560</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -10017,7 +10017,7 @@
         </is>
       </c>
       <c r="J217" t="n">
-        <v>180</v>
+        <v>460</v>
       </c>
       <c r="K217" t="n">
         <v>0</v>
@@ -10026,30 +10026,30 @@
         <v>0</v>
       </c>
       <c r="M217" t="n">
-        <v>180</v>
+        <v>460</v>
       </c>
       <c r="N217" t="n">
-        <v>19008</v>
+        <v>11302</v>
       </c>
       <c r="O217" t="n">
-        <v>3421440</v>
+        <v>5198920</v>
       </c>
       <c r="P217" t="n">
-        <v>30900</v>
+        <v>18900</v>
       </c>
       <c r="Q217" t="n">
-        <v>5562000</v>
+        <v>8694000</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>C4560</t>
+          <t>C4561</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>PIANO TAPETE C4560</t>
+          <t>ABECEDARIO INGLES MUSICAL C4561</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -10063,7 +10063,7 @@
         </is>
       </c>
       <c r="J218" t="n">
-        <v>460</v>
+        <v>180</v>
       </c>
       <c r="K218" t="n">
         <v>0</v>
@@ -10072,30 +10072,30 @@
         <v>0</v>
       </c>
       <c r="M218" t="n">
-        <v>460</v>
+        <v>180</v>
       </c>
       <c r="N218" t="n">
-        <v>11302</v>
+        <v>17992</v>
       </c>
       <c r="O218" t="n">
-        <v>5198920</v>
+        <v>3238560</v>
       </c>
       <c r="P218" t="n">
-        <v>18900</v>
+        <v>28900</v>
       </c>
       <c r="Q218" t="n">
-        <v>8694000</v>
+        <v>5202000</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>C4561</t>
+          <t>C4566</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>ABECEDARIO INGLES MUSICAL C4561</t>
+          <t>CARRO MINI CONTROL MODELOS STDS C4566</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -10109,7 +10109,7 @@
         </is>
       </c>
       <c r="J219" t="n">
-        <v>180</v>
+        <v>250</v>
       </c>
       <c r="K219" t="n">
         <v>0</v>
@@ -10118,30 +10118,30 @@
         <v>0</v>
       </c>
       <c r="M219" t="n">
-        <v>180</v>
+        <v>250</v>
       </c>
       <c r="N219" t="n">
-        <v>17992</v>
+        <v>11348</v>
       </c>
       <c r="O219" t="n">
-        <v>3238560</v>
+        <v>2837000</v>
       </c>
       <c r="P219" t="n">
-        <v>28900</v>
+        <v>19900</v>
       </c>
       <c r="Q219" t="n">
-        <v>5202000</v>
+        <v>4975000</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>C4566</t>
+          <t>C4567</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>CARRO MINI CONTROL MODELOS STDS C4566</t>
+          <t>JUEGO MESA FORMA DE ANIMALES C4567</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -10155,7 +10155,7 @@
         </is>
       </c>
       <c r="J220" t="n">
-        <v>250</v>
+        <v>192</v>
       </c>
       <c r="K220" t="n">
         <v>0</v>
@@ -10164,30 +10164,30 @@
         <v>0</v>
       </c>
       <c r="M220" t="n">
-        <v>250</v>
+        <v>192</v>
       </c>
       <c r="N220" t="n">
-        <v>11348</v>
+        <v>17075.989514768</v>
       </c>
       <c r="O220" t="n">
-        <v>2837000</v>
+        <v>3278589.986835456</v>
       </c>
       <c r="P220" t="n">
-        <v>19900</v>
+        <v>27500</v>
       </c>
       <c r="Q220" t="n">
-        <v>4975000</v>
+        <v>5280000</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>C4567</t>
+          <t>C4570</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>JUEGO MESA FORMA DE ANIMALES C4567</t>
+          <t>CUBO MAGICO C4570 EQY766</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -10201,7 +10201,7 @@
         </is>
       </c>
       <c r="J221" t="n">
-        <v>192</v>
+        <v>60</v>
       </c>
       <c r="K221" t="n">
         <v>0</v>
@@ -10210,30 +10210,30 @@
         <v>0</v>
       </c>
       <c r="M221" t="n">
-        <v>192</v>
+        <v>60</v>
       </c>
       <c r="N221" t="n">
-        <v>17075.989514768</v>
+        <v>10398</v>
       </c>
       <c r="O221" t="n">
-        <v>3278589.986835456</v>
+        <v>623880</v>
       </c>
       <c r="P221" t="n">
-        <v>27500</v>
+        <v>16900</v>
       </c>
       <c r="Q221" t="n">
-        <v>5280000</v>
+        <v>1014000</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>C4570</t>
+          <t>C4572</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>CUBO MAGICO C4570 EQY766</t>
+          <t>CUBO MAGICO C4572 EQY10130</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -10247,7 +10247,7 @@
         </is>
       </c>
       <c r="J222" t="n">
-        <v>60</v>
+        <v>108</v>
       </c>
       <c r="K222" t="n">
         <v>0</v>
@@ -10256,30 +10256,30 @@
         <v>0</v>
       </c>
       <c r="M222" t="n">
-        <v>60</v>
+        <v>108</v>
       </c>
       <c r="N222" t="n">
-        <v>10398</v>
+        <v>4518</v>
       </c>
       <c r="O222" t="n">
-        <v>623880</v>
+        <v>487944</v>
       </c>
       <c r="P222" t="n">
-        <v>16900</v>
+        <v>7900</v>
       </c>
       <c r="Q222" t="n">
-        <v>1014000</v>
+        <v>853200</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>C4572</t>
+          <t>C4577</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>CUBO MAGICO C4572 EQY10130</t>
+          <t>PISTA DINOSAURIO C4577</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -10293,7 +10293,7 @@
         </is>
       </c>
       <c r="J223" t="n">
-        <v>108</v>
+        <v>67</v>
       </c>
       <c r="K223" t="n">
         <v>0</v>
@@ -10302,30 +10302,30 @@
         <v>0</v>
       </c>
       <c r="M223" t="n">
-        <v>108</v>
+        <v>67</v>
       </c>
       <c r="N223" t="n">
-        <v>4518</v>
+        <v>21346</v>
       </c>
       <c r="O223" t="n">
-        <v>487944</v>
+        <v>1430182</v>
       </c>
       <c r="P223" t="n">
-        <v>7900</v>
+        <v>34900</v>
       </c>
       <c r="Q223" t="n">
-        <v>853200</v>
+        <v>2338300</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>C4577</t>
+          <t>C4578</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>PISTA DINOSAURIO C4577</t>
+          <t>LANZADORA DE AGUA BOLSA PVC C4578</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -10339,7 +10339,7 @@
         </is>
       </c>
       <c r="J224" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="K224" t="n">
         <v>0</v>
@@ -10348,30 +10348,30 @@
         <v>0</v>
       </c>
       <c r="M224" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="N224" t="n">
-        <v>21346</v>
+        <v>18001</v>
       </c>
       <c r="O224" t="n">
-        <v>1430182</v>
+        <v>1080060</v>
       </c>
       <c r="P224" t="n">
-        <v>34900</v>
+        <v>28900</v>
       </c>
       <c r="Q224" t="n">
-        <v>2338300</v>
+        <v>1734000</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>C4578</t>
+          <t>C4579</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>LANZADORA DE AGUA BOLSA PVC C4578</t>
+          <t>LANZADORA DE AGUA C4579</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -10385,7 +10385,7 @@
         </is>
       </c>
       <c r="J225" t="n">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="K225" t="n">
         <v>0</v>
@@ -10394,30 +10394,33 @@
         <v>0</v>
       </c>
       <c r="M225" t="n">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="N225" t="n">
-        <v>18001</v>
+        <v>10219</v>
       </c>
       <c r="O225" t="n">
-        <v>1512084</v>
+        <v>694892</v>
       </c>
       <c r="P225" t="n">
-        <v>28900</v>
+        <v>16900</v>
       </c>
       <c r="Q225" t="n">
-        <v>2427600</v>
+        <v>1149200</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>C4579</t>
-        </is>
+          <t>C458</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>6920190230459</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>LANZADORA DE AGUA C4579</t>
+          <t>BURRO SENCILLO SONIDO</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -10427,11 +10430,11 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J226" t="n">
-        <v>68</v>
+        <v>420</v>
       </c>
       <c r="K226" t="n">
         <v>0</v>
@@ -10440,33 +10443,30 @@
         <v>0</v>
       </c>
       <c r="M226" t="n">
-        <v>68</v>
+        <v>420</v>
       </c>
       <c r="N226" t="n">
-        <v>10219</v>
+        <v>10755</v>
       </c>
       <c r="O226" t="n">
-        <v>694892</v>
+        <v>4517100</v>
       </c>
       <c r="P226" t="n">
-        <v>16900</v>
+        <v>17900</v>
       </c>
       <c r="Q226" t="n">
-        <v>1149200</v>
+        <v>7518000</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>C458</t>
-        </is>
-      </c>
-      <c r="B227" t="n">
-        <v>6920190230459</v>
+          <t>C4581</t>
+        </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>BURRO SENCILLO SONIDO</t>
+          <t>ESPADA BURBUJERA C4581</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -10476,11 +10476,11 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J227" t="n">
-        <v>420</v>
+        <v>106</v>
       </c>
       <c r="K227" t="n">
         <v>0</v>
@@ -10489,30 +10489,30 @@
         <v>0</v>
       </c>
       <c r="M227" t="n">
-        <v>420</v>
+        <v>106</v>
       </c>
       <c r="N227" t="n">
-        <v>10755</v>
+        <v>17168</v>
       </c>
       <c r="O227" t="n">
-        <v>4517100</v>
+        <v>1819808</v>
       </c>
       <c r="P227" t="n">
-        <v>17900</v>
+        <v>27900</v>
       </c>
       <c r="Q227" t="n">
-        <v>7518000</v>
+        <v>2957400</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>C4581</t>
+          <t>C4584</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>ESPADA BURBUJERA C4581</t>
+          <t>LANZADORA DARDOS C4584</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -10526,7 +10526,7 @@
         </is>
       </c>
       <c r="J228" t="n">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="K228" t="n">
         <v>0</v>
@@ -10535,30 +10535,30 @@
         <v>0</v>
       </c>
       <c r="M228" t="n">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="N228" t="n">
-        <v>17168</v>
+        <v>27254</v>
       </c>
       <c r="O228" t="n">
-        <v>1819808</v>
+        <v>3597528</v>
       </c>
       <c r="P228" t="n">
-        <v>27900</v>
+        <v>43900</v>
       </c>
       <c r="Q228" t="n">
-        <v>2957400</v>
+        <v>5794800</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>C4584</t>
+          <t>C4596</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>LANZADORA DARDOS C4584</t>
+          <t>JUEGO ANTIESTRES C4596</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -10572,7 +10572,7 @@
         </is>
       </c>
       <c r="J229" t="n">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="K229" t="n">
         <v>0</v>
@@ -10581,30 +10581,30 @@
         <v>0</v>
       </c>
       <c r="M229" t="n">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="N229" t="n">
-        <v>27254</v>
+        <v>4303</v>
       </c>
       <c r="O229" t="n">
-        <v>3597528</v>
+        <v>464724</v>
       </c>
       <c r="P229" t="n">
-        <v>43900</v>
+        <v>7900</v>
       </c>
       <c r="Q229" t="n">
-        <v>5794800</v>
+        <v>853200</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>C4596</t>
+          <t>C4599</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>JUEGO ANTIESTRES C4596</t>
+          <t>VARA HELICE DINOSAURIO C4599</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -10618,7 +10618,7 @@
         </is>
       </c>
       <c r="J230" t="n">
-        <v>108</v>
+        <v>720</v>
       </c>
       <c r="K230" t="n">
         <v>0</v>
@@ -10627,30 +10627,30 @@
         <v>0</v>
       </c>
       <c r="M230" t="n">
-        <v>108</v>
+        <v>720</v>
       </c>
       <c r="N230" t="n">
-        <v>4303</v>
+        <v>5588</v>
       </c>
       <c r="O230" t="n">
-        <v>464724</v>
+        <v>4023360</v>
       </c>
       <c r="P230" t="n">
-        <v>7900</v>
+        <v>9500</v>
       </c>
       <c r="Q230" t="n">
-        <v>853200</v>
+        <v>6840000</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>C4599</t>
+          <t>C4601</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>VARA HELICE DINOSAURIO C4599</t>
+          <t>SET PERRO PATROL C4601</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -10664,7 +10664,7 @@
         </is>
       </c>
       <c r="J231" t="n">
-        <v>720</v>
+        <v>60</v>
       </c>
       <c r="K231" t="n">
         <v>0</v>
@@ -10673,30 +10673,30 @@
         <v>0</v>
       </c>
       <c r="M231" t="n">
-        <v>720</v>
+        <v>60</v>
       </c>
       <c r="N231" t="n">
-        <v>5588</v>
+        <v>14050</v>
       </c>
       <c r="O231" t="n">
-        <v>4023360</v>
+        <v>843000</v>
       </c>
       <c r="P231" t="n">
-        <v>9500</v>
+        <v>23900</v>
       </c>
       <c r="Q231" t="n">
-        <v>6840000</v>
+        <v>1434000</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>C4601</t>
+          <t>C4602</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>SET PERRO PATROL C4601</t>
+          <t>AVION CON PISTA MODELOS STD C4602</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -10710,7 +10710,7 @@
         </is>
       </c>
       <c r="J232" t="n">
-        <v>60</v>
+        <v>285</v>
       </c>
       <c r="K232" t="n">
         <v>0</v>
@@ -10719,30 +10719,30 @@
         <v>0</v>
       </c>
       <c r="M232" t="n">
-        <v>60</v>
+        <v>285</v>
       </c>
       <c r="N232" t="n">
-        <v>14050</v>
+        <v>8700</v>
       </c>
       <c r="O232" t="n">
-        <v>843000</v>
+        <v>2479500</v>
       </c>
       <c r="P232" t="n">
-        <v>23900</v>
+        <v>14900</v>
       </c>
       <c r="Q232" t="n">
-        <v>1434000</v>
+        <v>4246500</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>C4602</t>
+          <t>C4603</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>AVION CON PISTA MODELOS STD C4602</t>
+          <t>MAQUILLAJE BLISTER SENCILLO C4603</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="J233" t="n">
-        <v>285</v>
+        <v>385</v>
       </c>
       <c r="K233" t="n">
         <v>0</v>
@@ -10765,30 +10765,30 @@
         <v>0</v>
       </c>
       <c r="M233" t="n">
-        <v>285</v>
+        <v>385</v>
       </c>
       <c r="N233" t="n">
-        <v>8700</v>
+        <v>3639.35</v>
       </c>
       <c r="O233" t="n">
-        <v>2479500</v>
+        <v>1401149.75</v>
       </c>
       <c r="P233" t="n">
-        <v>14900</v>
+        <v>7500</v>
       </c>
       <c r="Q233" t="n">
-        <v>4246500</v>
+        <v>2887500</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>C4603</t>
+          <t>C4604</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>MAQUILLAJE BLISTER SENCILLO C4603</t>
+          <t>MQUILLAJE BLISTER MODELOS STDS C4604</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -10802,7 +10802,7 @@
         </is>
       </c>
       <c r="J234" t="n">
-        <v>385</v>
+        <v>1709</v>
       </c>
       <c r="K234" t="n">
         <v>0</v>
@@ -10811,30 +10811,30 @@
         <v>0</v>
       </c>
       <c r="M234" t="n">
-        <v>385</v>
+        <v>1709</v>
       </c>
       <c r="N234" t="n">
-        <v>3639.35</v>
+        <v>1326</v>
       </c>
       <c r="O234" t="n">
-        <v>1401149.75</v>
+        <v>2266134</v>
       </c>
       <c r="P234" t="n">
-        <v>7500</v>
+        <v>2500</v>
       </c>
       <c r="Q234" t="n">
-        <v>2887500</v>
+        <v>4272500</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>C4604</t>
+          <t>C4605</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>MQUILLAJE BLISTER MODELOS STDS C4604</t>
+          <t>MAQUILLAJE BLISTER  CORAZON C4605</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -10848,7 +10848,7 @@
         </is>
       </c>
       <c r="J235" t="n">
-        <v>1709</v>
+        <v>176</v>
       </c>
       <c r="K235" t="n">
         <v>0</v>
@@ -10857,30 +10857,30 @@
         <v>0</v>
       </c>
       <c r="M235" t="n">
-        <v>1709</v>
+        <v>176</v>
       </c>
       <c r="N235" t="n">
-        <v>1326</v>
+        <v>5640</v>
       </c>
       <c r="O235" t="n">
-        <v>2266134</v>
+        <v>992640</v>
       </c>
       <c r="P235" t="n">
-        <v>2500</v>
+        <v>9900</v>
       </c>
       <c r="Q235" t="n">
-        <v>4272500</v>
+        <v>1742400</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>C4605</t>
+          <t>C4606</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>MAQUILLAJE BLISTER  CORAZON C4605</t>
+          <t>SONAJERO EN CAJA 6PCS C4606</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -10894,7 +10894,7 @@
         </is>
       </c>
       <c r="J236" t="n">
-        <v>176</v>
+        <v>279</v>
       </c>
       <c r="K236" t="n">
         <v>0</v>
@@ -10903,30 +10903,30 @@
         <v>0</v>
       </c>
       <c r="M236" t="n">
-        <v>176</v>
+        <v>279</v>
       </c>
       <c r="N236" t="n">
-        <v>5640</v>
+        <v>10713.21</v>
       </c>
       <c r="O236" t="n">
-        <v>992640</v>
+        <v>2988985.59</v>
       </c>
       <c r="P236" t="n">
-        <v>9900</v>
+        <v>20900</v>
       </c>
       <c r="Q236" t="n">
-        <v>1742400</v>
+        <v>5831100</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>C4606</t>
+          <t>C4607</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>SONAJERO EN CAJA 6PCS C4606</t>
+          <t>MAQUILLAJE SIRENA C4607</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -10940,7 +10940,7 @@
         </is>
       </c>
       <c r="J237" t="n">
-        <v>279</v>
+        <v>159</v>
       </c>
       <c r="K237" t="n">
         <v>0</v>
@@ -10949,30 +10949,30 @@
         <v>0</v>
       </c>
       <c r="M237" t="n">
-        <v>279</v>
+        <v>159</v>
       </c>
       <c r="N237" t="n">
-        <v>10713.21</v>
+        <v>10817</v>
       </c>
       <c r="O237" t="n">
-        <v>2988985.59</v>
+        <v>1719903</v>
       </c>
       <c r="P237" t="n">
-        <v>20900</v>
+        <v>17900</v>
       </c>
       <c r="Q237" t="n">
-        <v>5831100</v>
+        <v>2846100</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>C4607</t>
+          <t>C4609</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>MAQUILLAJE SIRENA C4607</t>
+          <t>MAQUILLAJE UNICORNIO C4609</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -10986,7 +10986,7 @@
         </is>
       </c>
       <c r="J238" t="n">
-        <v>159</v>
+        <v>79</v>
       </c>
       <c r="K238" t="n">
         <v>0</v>
@@ -10995,30 +10995,30 @@
         <v>0</v>
       </c>
       <c r="M238" t="n">
-        <v>159</v>
+        <v>79</v>
       </c>
       <c r="N238" t="n">
-        <v>10817</v>
+        <v>12489</v>
       </c>
       <c r="O238" t="n">
-        <v>1719903</v>
+        <v>986631</v>
       </c>
       <c r="P238" t="n">
-        <v>17900</v>
+        <v>20900</v>
       </c>
       <c r="Q238" t="n">
-        <v>2846100</v>
+        <v>1651100</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>C4609</t>
+          <t>C4612</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>MAQUILLAJE UNICORNIO C4609</t>
+          <t>CARRUAJE MUÑECA C4612</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -11032,7 +11032,7 @@
         </is>
       </c>
       <c r="J239" t="n">
-        <v>79</v>
+        <v>166</v>
       </c>
       <c r="K239" t="n">
         <v>0</v>
@@ -11041,30 +11041,30 @@
         <v>0</v>
       </c>
       <c r="M239" t="n">
-        <v>79</v>
+        <v>166</v>
       </c>
       <c r="N239" t="n">
-        <v>12489</v>
+        <v>21762</v>
       </c>
       <c r="O239" t="n">
-        <v>986631</v>
+        <v>3612492</v>
       </c>
       <c r="P239" t="n">
-        <v>20900</v>
+        <v>35900</v>
       </c>
       <c r="Q239" t="n">
-        <v>1651100</v>
+        <v>5959400</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>C4612</t>
+          <t>C4613</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>CARRUAJE MUÑECA C4612</t>
+          <t>DIDACTICOS ARMABLES STD C4613</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -11078,7 +11078,7 @@
         </is>
       </c>
       <c r="J240" t="n">
-        <v>166</v>
+        <v>934</v>
       </c>
       <c r="K240" t="n">
         <v>0</v>
@@ -11087,30 +11087,30 @@
         <v>0</v>
       </c>
       <c r="M240" t="n">
-        <v>166</v>
+        <v>934</v>
       </c>
       <c r="N240" t="n">
-        <v>21762</v>
+        <v>3821</v>
       </c>
       <c r="O240" t="n">
-        <v>3612492</v>
+        <v>3568814</v>
       </c>
       <c r="P240" t="n">
-        <v>35900</v>
+        <v>5900</v>
       </c>
       <c r="Q240" t="n">
-        <v>5959400</v>
+        <v>5510600</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>C4613</t>
+          <t>C4614</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>DIDACTICOS ARMABLES STD C4613</t>
+          <t>CASTILLO NIÑA C4614</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -11124,7 +11124,7 @@
         </is>
       </c>
       <c r="J241" t="n">
-        <v>934</v>
+        <v>144</v>
       </c>
       <c r="K241" t="n">
         <v>0</v>
@@ -11133,30 +11133,30 @@
         <v>0</v>
       </c>
       <c r="M241" t="n">
-        <v>934</v>
+        <v>144</v>
       </c>
       <c r="N241" t="n">
-        <v>3821</v>
+        <v>15472</v>
       </c>
       <c r="O241" t="n">
-        <v>3568814</v>
+        <v>2227968</v>
       </c>
       <c r="P241" t="n">
-        <v>5900</v>
+        <v>25900</v>
       </c>
       <c r="Q241" t="n">
-        <v>5510600</v>
+        <v>3729600</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>C4614</t>
+          <t>C4616</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>CASTILLO NIÑA C4614</t>
+          <t>CARRO TRANSFORME AMARILLO RECARGABLE C4616</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -11170,7 +11170,7 @@
         </is>
       </c>
       <c r="J242" t="n">
-        <v>144</v>
+        <v>8</v>
       </c>
       <c r="K242" t="n">
         <v>0</v>
@@ -11179,30 +11179,30 @@
         <v>0</v>
       </c>
       <c r="M242" t="n">
-        <v>144</v>
+        <v>8</v>
       </c>
       <c r="N242" t="n">
-        <v>15472</v>
+        <v>48522</v>
       </c>
       <c r="O242" t="n">
-        <v>2227968</v>
+        <v>388176</v>
       </c>
       <c r="P242" t="n">
-        <v>25900</v>
+        <v>77900</v>
       </c>
       <c r="Q242" t="n">
-        <v>3729600</v>
+        <v>623200</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>C4616</t>
+          <t>C4622</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>CARRO TRANSFORME AMARILLO RECARGABLE C4616</t>
+          <t>CARRO COLECCION X8 C4622</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -11216,7 +11216,7 @@
         </is>
       </c>
       <c r="J243" t="n">
-        <v>8</v>
+        <v>240</v>
       </c>
       <c r="K243" t="n">
         <v>0</v>
@@ -11225,30 +11225,30 @@
         <v>0</v>
       </c>
       <c r="M243" t="n">
-        <v>8</v>
+        <v>240</v>
       </c>
       <c r="N243" t="n">
-        <v>48522</v>
+        <v>5476</v>
       </c>
       <c r="O243" t="n">
-        <v>388176</v>
+        <v>1314240</v>
       </c>
       <c r="P243" t="n">
-        <v>77900</v>
+        <v>8900</v>
       </c>
       <c r="Q243" t="n">
-        <v>623200</v>
+        <v>2136000</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>C4622</t>
+          <t>C4629</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>CARRO COLECCION X8 C4622</t>
+          <t>COMPUTADOR USB CABLE C4629</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -11262,7 +11262,7 @@
         </is>
       </c>
       <c r="J244" t="n">
-        <v>240</v>
+        <v>36</v>
       </c>
       <c r="K244" t="n">
         <v>0</v>
@@ -11271,30 +11271,30 @@
         <v>0</v>
       </c>
       <c r="M244" t="n">
-        <v>240</v>
+        <v>36</v>
       </c>
       <c r="N244" t="n">
-        <v>5476</v>
+        <v>64612</v>
       </c>
       <c r="O244" t="n">
-        <v>1314240</v>
+        <v>2326032</v>
       </c>
       <c r="P244" t="n">
-        <v>8900</v>
+        <v>103900</v>
       </c>
       <c r="Q244" t="n">
-        <v>2136000</v>
+        <v>3740400</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>C4629</t>
+          <t>C4630</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>COMPUTADOR USB CABLE C4629</t>
+          <t>COMPUTADOR USB INGLES/ESPAÑOL C4630</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -11308,7 +11308,7 @@
         </is>
       </c>
       <c r="J245" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="K245" t="n">
         <v>0</v>
@@ -11317,30 +11317,30 @@
         <v>0</v>
       </c>
       <c r="M245" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="N245" t="n">
-        <v>64612</v>
+        <v>38252</v>
       </c>
       <c r="O245" t="n">
-        <v>2326032</v>
+        <v>2142112</v>
       </c>
       <c r="P245" t="n">
-        <v>103900</v>
+        <v>61900</v>
       </c>
       <c r="Q245" t="n">
-        <v>3740400</v>
+        <v>3466400</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>C4630</t>
+          <t>C4631</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>COMPUTADOR USB INGLES/ESPAÑOL C4630</t>
+          <t>SQUISHY MOSTRICO STD C4631</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -11354,7 +11354,7 @@
         </is>
       </c>
       <c r="J246" t="n">
-        <v>56</v>
+        <v>864</v>
       </c>
       <c r="K246" t="n">
         <v>0</v>
@@ -11363,30 +11363,30 @@
         <v>0</v>
       </c>
       <c r="M246" t="n">
-        <v>56</v>
+        <v>864</v>
       </c>
       <c r="N246" t="n">
-        <v>38252</v>
+        <v>1516.0386973545</v>
       </c>
       <c r="O246" t="n">
-        <v>2142112</v>
+        <v>1309857.434514288</v>
       </c>
       <c r="P246" t="n">
-        <v>61900</v>
+        <v>2300</v>
       </c>
       <c r="Q246" t="n">
-        <v>3466400</v>
+        <v>1987200</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>C4631</t>
+          <t>C466-IO</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>SQUISHY MOSTRICO STD C4631</t>
+          <t>GLOBO FIGURAS TORNASOL Y MATE</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -11400,7 +11400,7 @@
         </is>
       </c>
       <c r="J247" t="n">
-        <v>864</v>
+        <v>1050</v>
       </c>
       <c r="K247" t="n">
         <v>0</v>
@@ -11409,30 +11409,30 @@
         <v>0</v>
       </c>
       <c r="M247" t="n">
-        <v>864</v>
+        <v>1050</v>
       </c>
       <c r="N247" t="n">
-        <v>1516.0386990066</v>
+        <v>356.78</v>
       </c>
       <c r="O247" t="n">
-        <v>1309857.435941702</v>
+        <v>374619</v>
       </c>
       <c r="P247" t="n">
-        <v>2300</v>
+        <v>300</v>
       </c>
       <c r="Q247" t="n">
-        <v>1987200</v>
+        <v>315000</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>C466-IO</t>
+          <t>C4728</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>GLOBO FIGURAS TORNASOL Y MATE</t>
+          <t>FLIOTADOR DONA DINOSAURIO #60 C4728</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -11446,7 +11446,7 @@
         </is>
       </c>
       <c r="J248" t="n">
-        <v>1050</v>
+        <v>550</v>
       </c>
       <c r="K248" t="n">
         <v>0</v>
@@ -11455,44 +11455,42 @@
         <v>0</v>
       </c>
       <c r="M248" t="n">
-        <v>1050</v>
+        <v>550</v>
       </c>
       <c r="N248" t="n">
-        <v>356.78</v>
+        <v>2454</v>
       </c>
       <c r="O248" t="n">
-        <v>374619</v>
+        <v>1349700</v>
       </c>
       <c r="P248" t="n">
-        <v>300</v>
+        <v>4200</v>
       </c>
       <c r="Q248" t="n">
-        <v>315000</v>
+        <v>2310000</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>C4728</t>
-        </is>
+          <t>C476</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>6932001041468</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>FLIOTADOR DONA DINOSAURIO #60 C4728</t>
-        </is>
-      </c>
-      <c r="E249" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>YENGA MADERA GRABDE</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J249" t="n">
-        <v>550</v>
+        <v>54</v>
       </c>
       <c r="K249" t="n">
         <v>0</v>
@@ -11501,42 +11499,44 @@
         <v>0</v>
       </c>
       <c r="M249" t="n">
-        <v>550</v>
+        <v>54</v>
       </c>
       <c r="N249" t="n">
-        <v>2454</v>
+        <v>5347.73</v>
       </c>
       <c r="O249" t="n">
-        <v>1349700</v>
+        <v>288777.42</v>
       </c>
       <c r="P249" t="n">
-        <v>4200</v>
+        <v>9500</v>
       </c>
       <c r="Q249" t="n">
-        <v>2310000</v>
+        <v>513000</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>C476</t>
-        </is>
-      </c>
-      <c r="B250" t="n">
-        <v>6932001041468</v>
+          <t>C4812</t>
+        </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>YENGA MADERA GRABDE</t>
+          <t>BURBUJERO DE ESPADA 44cm</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J250" t="n">
-        <v>54</v>
+        <v>4032</v>
       </c>
       <c r="K250" t="n">
         <v>0</v>
@@ -11545,30 +11545,30 @@
         <v>0</v>
       </c>
       <c r="M250" t="n">
-        <v>54</v>
+        <v>4032</v>
       </c>
       <c r="N250" t="n">
-        <v>5347.73</v>
+        <v>1801</v>
       </c>
       <c r="O250" t="n">
-        <v>288777.42</v>
+        <v>7261632</v>
       </c>
       <c r="P250" t="n">
-        <v>9500</v>
+        <v>2900</v>
       </c>
       <c r="Q250" t="n">
-        <v>513000</v>
+        <v>11692800</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>C4812</t>
+          <t>C494-IO</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>BURBUJERO DE ESPADA 44cm</t>
+          <t>GLOBO METALIZADO DULCES</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -11582,7 +11582,7 @@
         </is>
       </c>
       <c r="J251" t="n">
-        <v>4032</v>
+        <v>1352</v>
       </c>
       <c r="K251" t="n">
         <v>0</v>
@@ -11591,30 +11591,33 @@
         <v>0</v>
       </c>
       <c r="M251" t="n">
-        <v>4032</v>
+        <v>1352</v>
       </c>
       <c r="N251" t="n">
-        <v>1801</v>
+        <v>1200</v>
       </c>
       <c r="O251" t="n">
-        <v>7261632</v>
+        <v>1622400</v>
       </c>
       <c r="P251" t="n">
-        <v>2900</v>
+        <v>1500</v>
       </c>
       <c r="Q251" t="n">
-        <v>11692800</v>
+        <v>2028000</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>C494-IO</t>
-        </is>
+          <t>C4945</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>7700154271143</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>GLOBO METALIZADO DULCES</t>
+          <t>MUÑECA CON MASCOTA Y COCHE C4945</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -11628,7 +11631,7 @@
         </is>
       </c>
       <c r="J252" t="n">
-        <v>1352</v>
+        <v>372</v>
       </c>
       <c r="K252" t="n">
         <v>0</v>
@@ -11637,25 +11640,25 @@
         <v>0</v>
       </c>
       <c r="M252" t="n">
-        <v>1352</v>
+        <v>372</v>
       </c>
       <c r="N252" t="n">
-        <v>1200</v>
+        <v>11690</v>
       </c>
       <c r="O252" t="n">
-        <v>1622400</v>
+        <v>4348680</v>
       </c>
       <c r="P252" t="n">
-        <v>1500</v>
+        <v>18900</v>
       </c>
       <c r="Q252" t="n">
-        <v>2028000</v>
+        <v>7030800</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>C4945</t>
+          <t>C4946</t>
         </is>
       </c>
       <c r="B253" t="n">
@@ -11663,7 +11666,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>MUÑECA CON MASCOTA Y COCHE C4945</t>
+          <t>MUÑECA CON ODONTOLOGIA C4946</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -11677,7 +11680,7 @@
         </is>
       </c>
       <c r="J253" t="n">
-        <v>372</v>
+        <v>276</v>
       </c>
       <c r="K253" t="n">
         <v>0</v>
@@ -11686,25 +11689,25 @@
         <v>0</v>
       </c>
       <c r="M253" t="n">
-        <v>372</v>
+        <v>276</v>
       </c>
       <c r="N253" t="n">
-        <v>11690</v>
+        <v>13518</v>
       </c>
       <c r="O253" t="n">
-        <v>4348680</v>
+        <v>3730968</v>
       </c>
       <c r="P253" t="n">
-        <v>18900</v>
+        <v>21900</v>
       </c>
       <c r="Q253" t="n">
-        <v>7030800</v>
+        <v>6044400</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>C4946</t>
+          <t>C4947</t>
         </is>
       </c>
       <c r="B254" t="n">
@@ -11712,7 +11715,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>MUÑECA CON ODONTOLOGIA C4946</t>
+          <t>MUÑECA CON MASCOTAS   C4947</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -11726,7 +11729,7 @@
         </is>
       </c>
       <c r="J254" t="n">
-        <v>276</v>
+        <v>396</v>
       </c>
       <c r="K254" t="n">
         <v>0</v>
@@ -11735,25 +11738,25 @@
         <v>0</v>
       </c>
       <c r="M254" t="n">
-        <v>276</v>
+        <v>396</v>
       </c>
       <c r="N254" t="n">
-        <v>13518</v>
+        <v>9736</v>
       </c>
       <c r="O254" t="n">
-        <v>3730968</v>
+        <v>3855456</v>
       </c>
       <c r="P254" t="n">
-        <v>21900</v>
+        <v>15900</v>
       </c>
       <c r="Q254" t="n">
-        <v>6044400</v>
+        <v>6296400</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>C4947</t>
+          <t>C4958</t>
         </is>
       </c>
       <c r="B255" t="n">
@@ -11761,7 +11764,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>MUÑECA CON MASCOTAS   C4947</t>
+          <t>MUÑECA PATINADORA CONTROL REMOTO</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -11775,7 +11778,7 @@
         </is>
       </c>
       <c r="J255" t="n">
-        <v>396</v>
+        <v>24</v>
       </c>
       <c r="K255" t="n">
         <v>0</v>
@@ -11784,25 +11787,25 @@
         <v>0</v>
       </c>
       <c r="M255" t="n">
-        <v>396</v>
+        <v>24</v>
       </c>
       <c r="N255" t="n">
-        <v>9736</v>
+        <v>44470</v>
       </c>
       <c r="O255" t="n">
-        <v>3855456</v>
+        <v>1067280</v>
       </c>
       <c r="P255" t="n">
-        <v>15900</v>
+        <v>71900</v>
       </c>
       <c r="Q255" t="n">
-        <v>6296400</v>
+        <v>1725600</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>C4958</t>
+          <t>C4959</t>
         </is>
       </c>
       <c r="B256" t="n">
@@ -11810,7 +11813,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>MUÑECA PATINADORA CONTROL REMOTO</t>
+          <t>MUÑECA POP ACCESORIOS C4959</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -11824,7 +11827,7 @@
         </is>
       </c>
       <c r="J256" t="n">
-        <v>24</v>
+        <v>544</v>
       </c>
       <c r="K256" t="n">
         <v>0</v>
@@ -11833,47 +11836,42 @@
         <v>0</v>
       </c>
       <c r="M256" t="n">
-        <v>24</v>
+        <v>544</v>
       </c>
       <c r="N256" t="n">
-        <v>44470</v>
+        <v>5215</v>
       </c>
       <c r="O256" t="n">
-        <v>1067280</v>
+        <v>2836960</v>
       </c>
       <c r="P256" t="n">
-        <v>71900</v>
+        <v>8900</v>
       </c>
       <c r="Q256" t="n">
-        <v>1725600</v>
+        <v>4841600</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>C4959</t>
+          <t>C502</t>
         </is>
       </c>
       <c r="B257" t="n">
-        <v>7700154271143</v>
+        <v>6952216485215</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>MUÑECA POP ACCESORIOS C4959</t>
-        </is>
-      </c>
-      <c r="E257" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>C502 MUNECA NANCY GRANDE</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J257" t="n">
-        <v>544</v>
+        <v>43</v>
       </c>
       <c r="K257" t="n">
         <v>0</v>
@@ -11882,42 +11880,47 @@
         <v>0</v>
       </c>
       <c r="M257" t="n">
-        <v>544</v>
+        <v>43</v>
       </c>
       <c r="N257" t="n">
-        <v>5215</v>
+        <v>15423.36</v>
       </c>
       <c r="O257" t="n">
-        <v>2836960</v>
+        <v>663204.48</v>
       </c>
       <c r="P257" t="n">
-        <v>8900</v>
+        <v>24900</v>
       </c>
       <c r="Q257" t="n">
-        <v>4841600</v>
+        <v>1070700</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>C502</t>
+          <t>C5030</t>
         </is>
       </c>
       <c r="B258" t="n">
-        <v>6952216485215</v>
+        <v>6999899236062</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>C502 MUNECA NANCY GRANDE</t>
+          <t>INFLABLE DONA LLANTA C5030</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>INFLABLES</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J258" t="n">
-        <v>43</v>
+        <v>121</v>
       </c>
       <c r="K258" t="n">
         <v>0</v>
@@ -11926,33 +11929,33 @@
         <v>0</v>
       </c>
       <c r="M258" t="n">
-        <v>43</v>
+        <v>121</v>
       </c>
       <c r="N258" t="n">
-        <v>15423.36</v>
+        <v>2857.22</v>
       </c>
       <c r="O258" t="n">
-        <v>663204.48</v>
+        <v>345723.62</v>
       </c>
       <c r="P258" t="n">
-        <v>24900</v>
+        <v>4900</v>
       </c>
       <c r="Q258" t="n">
-        <v>1070700</v>
+        <v>592900</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>C5030</t>
+          <t>C5032</t>
         </is>
       </c>
       <c r="B259" t="n">
-        <v>6999899236062</v>
+        <v>6999899236154</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>INFLABLE DONA LLANTA C5030</t>
+          <t>INFLABLE TECHITO PIECITOS  FIGURAS STD C5032</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -11966,7 +11969,7 @@
         </is>
       </c>
       <c r="J259" t="n">
-        <v>121</v>
+        <v>534</v>
       </c>
       <c r="K259" t="n">
         <v>0</v>
@@ -11975,47 +11978,42 @@
         <v>0</v>
       </c>
       <c r="M259" t="n">
-        <v>121</v>
+        <v>534</v>
       </c>
       <c r="N259" t="n">
-        <v>2857.22</v>
+        <v>8945.379999999999</v>
       </c>
       <c r="O259" t="n">
-        <v>345723.62</v>
+        <v>4776832.92</v>
       </c>
       <c r="P259" t="n">
-        <v>4900</v>
+        <v>14900</v>
       </c>
       <c r="Q259" t="n">
-        <v>592900</v>
+        <v>7956600</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>C5032</t>
+          <t>C506</t>
         </is>
       </c>
       <c r="B260" t="n">
-        <v>6999899236154</v>
+        <v>6952365180054</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>INFLABLE TECHITO PIECITOS  FIGURAS STD C5032</t>
-        </is>
-      </c>
-      <c r="E260" t="inlineStr">
-        <is>
-          <t>INFLABLES</t>
+          <t>GLOBO BURBUJA 30</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J260" t="n">
-        <v>534</v>
+        <v>3650</v>
       </c>
       <c r="K260" t="n">
         <v>0</v>
@@ -12024,42 +12022,44 @@
         <v>0</v>
       </c>
       <c r="M260" t="n">
-        <v>534</v>
+        <v>3650</v>
       </c>
       <c r="N260" t="n">
-        <v>8949.4124778362</v>
+        <v>675.2255375485</v>
       </c>
       <c r="O260" t="n">
-        <v>4778986.263164531</v>
+        <v>2464573.212052025</v>
       </c>
       <c r="P260" t="n">
-        <v>14900</v>
+        <v>1300</v>
       </c>
       <c r="Q260" t="n">
-        <v>7956600</v>
+        <v>4745000</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>C506</t>
-        </is>
-      </c>
-      <c r="B261" t="n">
-        <v>6952365180054</v>
+          <t>C510-IO</t>
+        </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>GLOBO BURBUJA 30</t>
+          <t>GLOBO BURBUJA METALIZADO</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>GLOBOS</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J261" t="n">
-        <v>3650</v>
+        <v>3896</v>
       </c>
       <c r="K261" t="n">
         <v>0</v>
@@ -12068,44 +12068,42 @@
         <v>0</v>
       </c>
       <c r="M261" t="n">
-        <v>3650</v>
+        <v>3896</v>
       </c>
       <c r="N261" t="n">
-        <v>675.2255375485</v>
+        <v>960</v>
       </c>
       <c r="O261" t="n">
-        <v>2464573.212052025</v>
+        <v>3740160</v>
       </c>
       <c r="P261" t="n">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="Q261" t="n">
-        <v>4745000</v>
+        <v>4675200</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>C510-IO</t>
-        </is>
+          <t>C515</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>6953626330010</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>GLOBO BURBUJA METALIZADO</t>
-        </is>
-      </c>
-      <c r="E262" t="inlineStr">
-        <is>
-          <t>GLOBOS</t>
+          <t>GLOBO FIGURAS BURBUJA</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J262" t="n">
-        <v>3896</v>
+        <v>3800</v>
       </c>
       <c r="K262" t="n">
         <v>0</v>
@@ -12114,42 +12112,44 @@
         <v>0</v>
       </c>
       <c r="M262" t="n">
-        <v>3896</v>
+        <v>3800</v>
       </c>
       <c r="N262" t="n">
-        <v>960</v>
+        <v>583.7204926325001</v>
       </c>
       <c r="O262" t="n">
-        <v>3740160</v>
+        <v>2218137.8720035</v>
       </c>
       <c r="P262" t="n">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="Q262" t="n">
-        <v>4675200</v>
+        <v>2280000</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>C515</t>
-        </is>
-      </c>
-      <c r="B263" t="n">
-        <v>6953626330010</v>
+          <t>C5214</t>
+        </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>GLOBO FIGURAS BURBUJA</t>
+          <t>CUBO C5214</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J263" t="n">
-        <v>3800</v>
+        <v>1440</v>
       </c>
       <c r="K263" t="n">
         <v>0</v>
@@ -12158,44 +12158,42 @@
         <v>0</v>
       </c>
       <c r="M263" t="n">
-        <v>3800</v>
+        <v>1440</v>
       </c>
       <c r="N263" t="n">
-        <v>583.7204926325001</v>
+        <v>1690.8700098184</v>
       </c>
       <c r="O263" t="n">
-        <v>2218137.8720035</v>
+        <v>2434852.814138496</v>
       </c>
       <c r="P263" t="n">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="Q263" t="n">
-        <v>2280000</v>
+        <v>4320000</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>C5214</t>
-        </is>
+          <t>C523</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>6957430180212</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>CUBO C5214</t>
-        </is>
-      </c>
-      <c r="E264" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
+          <t>GLOBO NUMERO 16PLATEADO Y DORADO</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J264" t="n">
-        <v>1440</v>
+        <v>2556</v>
       </c>
       <c r="K264" t="n">
         <v>0</v>
@@ -12204,33 +12202,33 @@
         <v>0</v>
       </c>
       <c r="M264" t="n">
-        <v>1440</v>
+        <v>2556</v>
       </c>
       <c r="N264" t="n">
-        <v>1690.8700097895</v>
+        <v>481.48790068997</v>
       </c>
       <c r="O264" t="n">
-        <v>2434852.81409688</v>
+        <v>1230683.074163563</v>
       </c>
       <c r="P264" t="n">
-        <v>3000</v>
+        <v>650</v>
       </c>
       <c r="Q264" t="n">
-        <v>4320000</v>
+        <v>1661400</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>C523</t>
+          <t>C524</t>
         </is>
       </c>
       <c r="B265" t="n">
-        <v>6957430180212</v>
+        <v>6957430180229</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>GLOBO NUMERO 16PLATEADO Y DORADO</t>
+          <t>GLOBO NUMERO 30 PLATEADO Y DORADO</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -12239,7 +12237,7 @@
         </is>
       </c>
       <c r="J265" t="n">
-        <v>2556</v>
+        <v>614</v>
       </c>
       <c r="K265" t="n">
         <v>0</v>
@@ -12248,42 +12246,47 @@
         <v>0</v>
       </c>
       <c r="M265" t="n">
-        <v>2556</v>
+        <v>614</v>
       </c>
       <c r="N265" t="n">
-        <v>481.48790068997</v>
+        <v>872.15420863309</v>
       </c>
       <c r="O265" t="n">
-        <v>1230683.074163563</v>
+        <v>535502.6841007172</v>
       </c>
       <c r="P265" t="n">
-        <v>650</v>
+        <v>1200</v>
       </c>
       <c r="Q265" t="n">
-        <v>1661400</v>
+        <v>736800</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>C524</t>
+          <t>C5246/C5247</t>
         </is>
       </c>
       <c r="B266" t="n">
-        <v>6957430180229</v>
+        <v>6900077483239</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>GLOBO NUMERO 30 PLATEADO Y DORADO</t>
+          <t>MARIONETA DE DEDO ANIMALES STDS C5246/C5247</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J266" t="n">
-        <v>614</v>
+        <v>130</v>
       </c>
       <c r="K266" t="n">
         <v>0</v>
@@ -12292,47 +12295,42 @@
         <v>0</v>
       </c>
       <c r="M266" t="n">
-        <v>614</v>
+        <v>130</v>
       </c>
       <c r="N266" t="n">
-        <v>872.15420863309</v>
+        <v>8702.219999999999</v>
       </c>
       <c r="O266" t="n">
-        <v>535502.6841007172</v>
+        <v>1131288.6</v>
       </c>
       <c r="P266" t="n">
-        <v>1200</v>
+        <v>8900</v>
       </c>
       <c r="Q266" t="n">
-        <v>736800</v>
+        <v>1157000</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>C5246/C5247</t>
+          <t>C525</t>
         </is>
       </c>
       <c r="B267" t="n">
-        <v>6900077483239</v>
+        <v>6957430180236</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>MARIONETA DE DEDO ANIMALES STDS C5246/C5247</t>
-        </is>
-      </c>
-      <c r="E267" t="inlineStr">
-        <is>
-          <t>DIDACTICO</t>
+          <t>GLOBO NUMERO 16 COLORES Y PUNTOS</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J267" t="n">
-        <v>130</v>
+        <v>1436</v>
       </c>
       <c r="K267" t="n">
         <v>0</v>
@@ -12341,33 +12339,33 @@
         <v>0</v>
       </c>
       <c r="M267" t="n">
-        <v>130</v>
+        <v>1436</v>
       </c>
       <c r="N267" t="n">
-        <v>8702.219999999999</v>
+        <v>345.55838583542</v>
       </c>
       <c r="O267" t="n">
-        <v>1131288.6</v>
+        <v>496221.8420596631</v>
       </c>
       <c r="P267" t="n">
-        <v>8900</v>
+        <v>600</v>
       </c>
       <c r="Q267" t="n">
-        <v>1157000</v>
+        <v>861600</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>C525</t>
+          <t>C526</t>
         </is>
       </c>
       <c r="B268" t="n">
-        <v>6957430180236</v>
+        <v>6957430180243</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>GLOBO NUMERO 16 COLORES Y PUNTOS</t>
+          <t>GLOBO NUMERO 30 COLORES Y PUNTOS</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -12376,7 +12374,7 @@
         </is>
       </c>
       <c r="J268" t="n">
-        <v>1436</v>
+        <v>11416</v>
       </c>
       <c r="K268" t="n">
         <v>0</v>
@@ -12385,42 +12383,47 @@
         <v>0</v>
       </c>
       <c r="M268" t="n">
-        <v>1436</v>
+        <v>11416</v>
       </c>
       <c r="N268" t="n">
-        <v>345.55838583542</v>
+        <v>711.33664496242</v>
       </c>
       <c r="O268" t="n">
-        <v>496221.8420596631</v>
+        <v>8120619.138890986</v>
       </c>
       <c r="P268" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="Q268" t="n">
-        <v>861600</v>
+        <v>10274400</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>C526</t>
+          <t>C527-IO</t>
         </is>
       </c>
       <c r="B269" t="n">
-        <v>6957430180243</v>
+        <v>6957430180526</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>GLOBO NUMERO 30 COLORES Y PUNTOS</t>
+          <t>GLOBO FELIZ CUMPLEAÑOS LISTON</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>GLOBOS</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J269" t="n">
-        <v>11416</v>
+        <v>1242</v>
       </c>
       <c r="K269" t="n">
         <v>0</v>
@@ -12429,38 +12432,35 @@
         <v>0</v>
       </c>
       <c r="M269" t="n">
-        <v>11416</v>
+        <v>1242</v>
       </c>
       <c r="N269" t="n">
-        <v>711.33664496242</v>
+        <v>815.0599999999999</v>
       </c>
       <c r="O269" t="n">
-        <v>8120619.138890986</v>
+        <v>1012304.52</v>
       </c>
       <c r="P269" t="n">
         <v>900</v>
       </c>
       <c r="Q269" t="n">
-        <v>10274400</v>
+        <v>1117800</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>C527-IO</t>
-        </is>
-      </c>
-      <c r="B270" t="n">
-        <v>6957430180526</v>
+          <t>C541</t>
+        </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>GLOBO FELIZ CUMPLEAÑOS LISTON</t>
+          <t>GLOBO LLAMA PQÑO</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>GLOBOS</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -12469,7 +12469,7 @@
         </is>
       </c>
       <c r="J270" t="n">
-        <v>1242</v>
+        <v>2150</v>
       </c>
       <c r="K270" t="n">
         <v>0</v>
@@ -12478,30 +12478,30 @@
         <v>0</v>
       </c>
       <c r="M270" t="n">
-        <v>1242</v>
+        <v>2150</v>
       </c>
       <c r="N270" t="n">
-        <v>815.0599999999999</v>
+        <v>800</v>
       </c>
       <c r="O270" t="n">
-        <v>1012304.52</v>
+        <v>1720000</v>
       </c>
       <c r="P270" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="Q270" t="n">
-        <v>1117800</v>
+        <v>2150000</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>C541</t>
+          <t>C575-IO</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>GLOBO LLAMA PQÑO</t>
+          <t>GLOBO UNICORNIO PQÑO</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -12515,7 +12515,7 @@
         </is>
       </c>
       <c r="J271" t="n">
-        <v>2150</v>
+        <v>1001</v>
       </c>
       <c r="K271" t="n">
         <v>0</v>
@@ -12524,35 +12524,38 @@
         <v>0</v>
       </c>
       <c r="M271" t="n">
-        <v>2150</v>
+        <v>1001</v>
       </c>
       <c r="N271" t="n">
-        <v>800</v>
+        <v>320</v>
       </c>
       <c r="O271" t="n">
-        <v>1720000</v>
+        <v>320320</v>
       </c>
       <c r="P271" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="Q271" t="n">
-        <v>2150000</v>
+        <v>400400</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>C575-IO</t>
-        </is>
+          <t>C596-IO</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>8596162180268</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>GLOBO UNICORNIO PQÑO</t>
+          <t>GLOBO TE AMO</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>GLOBOS</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -12561,7 +12564,7 @@
         </is>
       </c>
       <c r="J272" t="n">
-        <v>1001</v>
+        <v>1455</v>
       </c>
       <c r="K272" t="n">
         <v>0</v>
@@ -12570,33 +12573,33 @@
         <v>0</v>
       </c>
       <c r="M272" t="n">
-        <v>1001</v>
+        <v>1455</v>
       </c>
       <c r="N272" t="n">
-        <v>320</v>
+        <v>1044.54</v>
       </c>
       <c r="O272" t="n">
-        <v>320320</v>
+        <v>1519805.7</v>
       </c>
       <c r="P272" t="n">
-        <v>400</v>
+        <v>1200</v>
       </c>
       <c r="Q272" t="n">
-        <v>400400</v>
+        <v>1746000</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>C596-IO</t>
+          <t>C60-IO</t>
         </is>
       </c>
       <c r="B273" t="n">
-        <v>8596162180268</v>
+        <v>6524521011245</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>GLOBO TE AMO</t>
+          <t>GLOBO TIKTOK BOUQUET</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -12610,7 +12613,7 @@
         </is>
       </c>
       <c r="J273" t="n">
-        <v>1455</v>
+        <v>740</v>
       </c>
       <c r="K273" t="n">
         <v>0</v>
@@ -12619,38 +12622,35 @@
         <v>0</v>
       </c>
       <c r="M273" t="n">
-        <v>1455</v>
+        <v>740</v>
       </c>
       <c r="N273" t="n">
-        <v>1044.54</v>
+        <v>1989.05</v>
       </c>
       <c r="O273" t="n">
-        <v>1519805.7</v>
+        <v>1471897</v>
       </c>
       <c r="P273" t="n">
-        <v>1200</v>
+        <v>3000</v>
       </c>
       <c r="Q273" t="n">
-        <v>1746000</v>
+        <v>2220000</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>C60-IO</t>
-        </is>
-      </c>
-      <c r="B274" t="n">
-        <v>6524521011245</v>
+          <t>C6074</t>
+        </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>GLOBO TIKTOK BOUQUET</t>
+          <t>FIGURAS ALIMENTOS DECORATIVOS C6074</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>GLOBOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -12659,7 +12659,7 @@
         </is>
       </c>
       <c r="J274" t="n">
-        <v>740</v>
+        <v>25</v>
       </c>
       <c r="K274" t="n">
         <v>0</v>
@@ -12668,44 +12668,42 @@
         <v>0</v>
       </c>
       <c r="M274" t="n">
-        <v>740</v>
+        <v>25</v>
       </c>
       <c r="N274" t="n">
-        <v>1989.05</v>
+        <v>9447.25</v>
       </c>
       <c r="O274" t="n">
-        <v>1471897</v>
+        <v>236181.25</v>
       </c>
       <c r="P274" t="n">
-        <v>3000</v>
+        <v>9900</v>
       </c>
       <c r="Q274" t="n">
-        <v>2220000</v>
+        <v>247500</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>C6074</t>
-        </is>
+          <t>C629</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>7791638082188</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>FIGURAS ALIMENTOS DECORATIVOS C6074</t>
-        </is>
-      </c>
-      <c r="E275" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
+          <t>BURBUJERO PITO STD</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J275" t="n">
-        <v>25</v>
+        <v>14112</v>
       </c>
       <c r="K275" t="n">
         <v>0</v>
@@ -12714,42 +12712,47 @@
         <v>0</v>
       </c>
       <c r="M275" t="n">
-        <v>25</v>
+        <v>14112</v>
       </c>
       <c r="N275" t="n">
-        <v>9447.25</v>
+        <v>703.79458486774</v>
       </c>
       <c r="O275" t="n">
-        <v>236181.25</v>
+        <v>9931949.181653546</v>
       </c>
       <c r="P275" t="n">
-        <v>9900</v>
+        <v>900</v>
       </c>
       <c r="Q275" t="n">
-        <v>247500</v>
+        <v>12700800</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>C629</t>
+          <t>C6406</t>
         </is>
       </c>
       <c r="B276" t="n">
-        <v>7791638082188</v>
+        <v>6820212541115</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>BURBUJERO PITO STD</t>
+          <t>PAJAROS MUSICALES DECORATIVOS C6406</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J276" t="n">
-        <v>14112</v>
+        <v>52</v>
       </c>
       <c r="K276" t="n">
         <v>0</v>
@@ -12758,47 +12761,39 @@
         <v>0</v>
       </c>
       <c r="M276" t="n">
-        <v>14112</v>
+        <v>52</v>
       </c>
       <c r="N276" t="n">
-        <v>703.7945904135599</v>
+        <v>14260.14</v>
       </c>
       <c r="O276" t="n">
-        <v>9931949.259916158</v>
+        <v>741527.28</v>
       </c>
       <c r="P276" t="n">
-        <v>900</v>
+        <v>15900</v>
       </c>
       <c r="Q276" t="n">
-        <v>12700800</v>
+        <v>826800</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>C6406</t>
-        </is>
-      </c>
-      <c r="B277" t="n">
-        <v>6820212541115</v>
+          <t>C642</t>
+        </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>PAJAROS MUSICALES DECORATIVOS C6406</t>
-        </is>
-      </c>
-      <c r="E277" t="inlineStr">
-        <is>
-          <t>MICELANEOS</t>
+          <t>LANZADOR AGUA</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J277" t="n">
-        <v>52</v>
+        <v>599</v>
       </c>
       <c r="K277" t="n">
         <v>0</v>
@@ -12807,39 +12802,44 @@
         <v>0</v>
       </c>
       <c r="M277" t="n">
-        <v>52</v>
+        <v>599</v>
       </c>
       <c r="N277" t="n">
-        <v>14260.14</v>
+        <v>2529.19</v>
       </c>
       <c r="O277" t="n">
-        <v>741527.28</v>
+        <v>1514984.81</v>
       </c>
       <c r="P277" t="n">
-        <v>15900</v>
+        <v>5100</v>
       </c>
       <c r="Q277" t="n">
-        <v>826800</v>
+        <v>3054900</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>C642</t>
+          <t>C671-LJ</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>LANZADOR AGUA</t>
+          <t>GLOBO UNICORNIO MEDIANO</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J278" t="n">
-        <v>599</v>
+        <v>1397</v>
       </c>
       <c r="K278" t="n">
         <v>0</v>
@@ -12848,35 +12848,38 @@
         <v>0</v>
       </c>
       <c r="M278" t="n">
-        <v>599</v>
+        <v>1397</v>
       </c>
       <c r="N278" t="n">
-        <v>2529.19</v>
+        <v>400</v>
       </c>
       <c r="O278" t="n">
-        <v>1514984.81</v>
+        <v>558800</v>
       </c>
       <c r="P278" t="n">
-        <v>5100</v>
+        <v>500</v>
       </c>
       <c r="Q278" t="n">
-        <v>3054900</v>
+        <v>698500</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>C671-LJ</t>
-        </is>
+          <t>C7005</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>6874123039124</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>GLOBO UNICORNIO MEDIANO</t>
+          <t>MAQUINA DE COSER C7005</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -12885,7 +12888,7 @@
         </is>
       </c>
       <c r="J279" t="n">
-        <v>1397</v>
+        <v>208</v>
       </c>
       <c r="K279" t="n">
         <v>0</v>
@@ -12894,38 +12897,38 @@
         <v>0</v>
       </c>
       <c r="M279" t="n">
-        <v>1397</v>
+        <v>208</v>
       </c>
       <c r="N279" t="n">
-        <v>400</v>
+        <v>6078.992616408</v>
       </c>
       <c r="O279" t="n">
-        <v>558800</v>
+        <v>1264430.464212864</v>
       </c>
       <c r="P279" t="n">
-        <v>500</v>
+        <v>18500</v>
       </c>
       <c r="Q279" t="n">
-        <v>698500</v>
+        <v>3848000</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>C7005</t>
+          <t>C7009</t>
         </is>
       </c>
       <c r="B280" t="n">
-        <v>6874123039124</v>
+        <v>2024250256831</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>MAQUINA DE COSER C7005</t>
+          <t>LANZADORA DE AGUA  TUBO CON HELICE C7009</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>LANZADORES</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -12934,7 +12937,7 @@
         </is>
       </c>
       <c r="J280" t="n">
-        <v>208</v>
+        <v>12</v>
       </c>
       <c r="K280" t="n">
         <v>0</v>
@@ -12943,33 +12946,33 @@
         <v>0</v>
       </c>
       <c r="M280" t="n">
-        <v>208</v>
+        <v>12</v>
       </c>
       <c r="N280" t="n">
-        <v>6078.992616408</v>
+        <v>5899.18</v>
       </c>
       <c r="O280" t="n">
-        <v>1264430.464212864</v>
+        <v>70790.16</v>
       </c>
       <c r="P280" t="n">
-        <v>18500</v>
+        <v>12500</v>
       </c>
       <c r="Q280" t="n">
-        <v>3848000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>C7009</t>
+          <t>C7038</t>
         </is>
       </c>
       <c r="B281" t="n">
-        <v>2024250256831</v>
+        <v>5132595141631</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>LANZADORA DE AGUA  TUBO CON HELICE C7009</t>
+          <t>LANZADORA DE AGUA GLOBO C7038</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -12983,7 +12986,7 @@
         </is>
       </c>
       <c r="J281" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="K281" t="n">
         <v>0</v>
@@ -12992,38 +12995,38 @@
         <v>0</v>
       </c>
       <c r="M281" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="N281" t="n">
-        <v>5899.18</v>
+        <v>18423.71</v>
       </c>
       <c r="O281" t="n">
-        <v>70790.16</v>
+        <v>423745.33</v>
       </c>
       <c r="P281" t="n">
-        <v>12500</v>
+        <v>10000</v>
       </c>
       <c r="Q281" t="n">
-        <v>150000</v>
+        <v>230000</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>C7038</t>
+          <t>C7039</t>
         </is>
       </c>
       <c r="B282" t="n">
-        <v>5132595141631</v>
+        <v>5132594521182</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>LANZADORA DE AGUA GLOBO C7038</t>
+          <t>LANZADOR AGUA GLOBO DELFIN C7039/M90-4</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>LANZADORES</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -13032,7 +13035,7 @@
         </is>
       </c>
       <c r="J282" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K282" t="n">
         <v>0</v>
@@ -13041,38 +13044,38 @@
         <v>0</v>
       </c>
       <c r="M282" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="N282" t="n">
-        <v>18423.71</v>
+        <v>10985.78</v>
       </c>
       <c r="O282" t="n">
-        <v>423745.33</v>
+        <v>219715.6</v>
       </c>
       <c r="P282" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="Q282" t="n">
-        <v>230000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>C7039</t>
+          <t>C7040</t>
         </is>
       </c>
       <c r="B283" t="n">
-        <v>5132594521182</v>
+        <v>6920373004365</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>LANZADOR AGUA GLOBO DELFIN C7039/M90-4</t>
+          <t>GARAJE EXIBICION CON LUZ C7040</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -13081,7 +13084,7 @@
         </is>
       </c>
       <c r="J283" t="n">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="K283" t="n">
         <v>0</v>
@@ -13090,38 +13093,38 @@
         <v>0</v>
       </c>
       <c r="M283" t="n">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="N283" t="n">
-        <v>10985.78</v>
+        <v>23452.77</v>
       </c>
       <c r="O283" t="n">
-        <v>219715.6</v>
+        <v>1102280.19</v>
       </c>
       <c r="P283" t="n">
-        <v>15000</v>
+        <v>39900</v>
       </c>
       <c r="Q283" t="n">
-        <v>300000</v>
+        <v>1875300</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>C7040</t>
+          <t>C7042</t>
         </is>
       </c>
       <c r="B284" t="n">
-        <v>6920373004365</v>
+        <v>2024081616255</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>GARAJE EXIBICION CON LUZ C7040</t>
+          <t>CANCHA BASKETBALL WIN24 C7042</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -13130,7 +13133,7 @@
         </is>
       </c>
       <c r="J284" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="K284" t="n">
         <v>0</v>
@@ -13139,38 +13142,35 @@
         <v>0</v>
       </c>
       <c r="M284" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="N284" t="n">
-        <v>23452.77</v>
+        <v>9694.41</v>
       </c>
       <c r="O284" t="n">
-        <v>1102280.19</v>
+        <v>96944.10000000001</v>
       </c>
       <c r="P284" t="n">
-        <v>39900</v>
+        <v>32500</v>
       </c>
       <c r="Q284" t="n">
-        <v>1875300</v>
+        <v>325000</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>C7042</t>
-        </is>
-      </c>
-      <c r="B285" t="n">
-        <v>2024081616255</v>
+          <t>C7080-BC</t>
+        </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>CANCHA BASKETBALL WIN24 C7042</t>
+          <t>ROBOT TRANSFORME STD C7080-BC</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MUÑECOS</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -13179,7 +13179,7 @@
         </is>
       </c>
       <c r="J285" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="K285" t="n">
         <v>0</v>
@@ -13188,44 +13188,42 @@
         <v>0</v>
       </c>
       <c r="M285" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="N285" t="n">
-        <v>9694.41</v>
+        <v>10556.12</v>
       </c>
       <c r="O285" t="n">
-        <v>96944.10000000001</v>
+        <v>411688.6800000001</v>
       </c>
       <c r="P285" t="n">
-        <v>32500</v>
+        <v>32900</v>
       </c>
       <c r="Q285" t="n">
-        <v>325000</v>
+        <v>1283100</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>C7080-BC</t>
-        </is>
+          <t>C71</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>5899989622205</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>ROBOT TRANSFORME STD C7080-BC</t>
-        </is>
-      </c>
-      <c r="E286" t="inlineStr">
-        <is>
-          <t>MUÑECOS</t>
+          <t>C71 INFLABLE PONY ROSADO-AZUL</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J286" t="n">
-        <v>39</v>
+        <v>392</v>
       </c>
       <c r="K286" t="n">
         <v>0</v>
@@ -13234,42 +13232,44 @@
         <v>0</v>
       </c>
       <c r="M286" t="n">
-        <v>39</v>
+        <v>392</v>
       </c>
       <c r="N286" t="n">
-        <v>10556.12</v>
+        <v>1669.6</v>
       </c>
       <c r="O286" t="n">
-        <v>411688.6800000001</v>
+        <v>654483.2</v>
       </c>
       <c r="P286" t="n">
-        <v>32900</v>
+        <v>2900</v>
       </c>
       <c r="Q286" t="n">
-        <v>1283100</v>
+        <v>1136800</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>C71</t>
-        </is>
-      </c>
-      <c r="B287" t="n">
-        <v>5899989622205</v>
+          <t>C7117</t>
+        </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>C71 INFLABLE PONY ROSADO-AZUL</t>
+          <t>BINGO LOTTO C7117</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>JUEGOS DE MESA</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J287" t="n">
-        <v>392</v>
+        <v>17</v>
       </c>
       <c r="K287" t="n">
         <v>0</v>
@@ -13278,35 +13278,35 @@
         <v>0</v>
       </c>
       <c r="M287" t="n">
-        <v>392</v>
+        <v>17</v>
       </c>
       <c r="N287" t="n">
-        <v>1669.6</v>
+        <v>5798.41</v>
       </c>
       <c r="O287" t="n">
-        <v>654483.2</v>
+        <v>98572.97</v>
       </c>
       <c r="P287" t="n">
-        <v>2900</v>
+        <v>14900</v>
       </c>
       <c r="Q287" t="n">
-        <v>1136800</v>
+        <v>253300</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>C7117</t>
+          <t>C7124</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>BINGO LOTTO C7117</t>
+          <t>TRAILER TRANFORME XQ05 C7124</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>JUEGOS DE MESA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -13315,7 +13315,7 @@
         </is>
       </c>
       <c r="J288" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="K288" t="n">
         <v>0</v>
@@ -13324,35 +13324,35 @@
         <v>0</v>
       </c>
       <c r="M288" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="N288" t="n">
-        <v>5798.41</v>
+        <v>19587.53</v>
       </c>
       <c r="O288" t="n">
-        <v>98572.97</v>
+        <v>783501.2</v>
       </c>
       <c r="P288" t="n">
-        <v>14900</v>
+        <v>65000</v>
       </c>
       <c r="Q288" t="n">
-        <v>253300</v>
+        <v>2600000</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>C7124</t>
+          <t>C7132</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>TRAILER TRANFORME XQ05 C7124</t>
+          <t>SET PULSERAS Y CAUCHOS C7132</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -13361,7 +13361,7 @@
         </is>
       </c>
       <c r="J289" t="n">
-        <v>40</v>
+        <v>144</v>
       </c>
       <c r="K289" t="n">
         <v>0</v>
@@ -13370,30 +13370,33 @@
         <v>0</v>
       </c>
       <c r="M289" t="n">
-        <v>40</v>
+        <v>144</v>
       </c>
       <c r="N289" t="n">
-        <v>19587.53</v>
+        <v>3100.87</v>
       </c>
       <c r="O289" t="n">
-        <v>783501.2</v>
+        <v>446525.28</v>
       </c>
       <c r="P289" t="n">
-        <v>65000</v>
+        <v>9900</v>
       </c>
       <c r="Q289" t="n">
-        <v>2600000</v>
+        <v>1425600</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>C7132</t>
-        </is>
+          <t>C7147-A</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>6912209205022</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>SET PULSERAS Y CAUCHOS C7132</t>
+          <t>ANIMAL DINOSAURIO TRICERATOPS CONLUZ C7147-A</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -13407,7 +13410,7 @@
         </is>
       </c>
       <c r="J290" t="n">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="K290" t="n">
         <v>0</v>
@@ -13416,33 +13419,33 @@
         <v>0</v>
       </c>
       <c r="M290" t="n">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="N290" t="n">
-        <v>3100.87</v>
+        <v>10348.08</v>
       </c>
       <c r="O290" t="n">
-        <v>446525.28</v>
+        <v>413923.2</v>
       </c>
       <c r="P290" t="n">
-        <v>9900</v>
+        <v>16900</v>
       </c>
       <c r="Q290" t="n">
-        <v>1425600</v>
+        <v>676000</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>C7147-A</t>
+          <t>C7213</t>
         </is>
       </c>
       <c r="B291" t="n">
-        <v>6912209205022</v>
+        <v>6987540143012</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>ANIMAL DINOSAURIO TRICERATOPS CONLUZ C7147-A</t>
+          <t>PESCADO CON LUZ Y SONIDO C7213</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -13456,7 +13459,7 @@
         </is>
       </c>
       <c r="J291" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="K291" t="n">
         <v>0</v>
@@ -13465,33 +13468,33 @@
         <v>0</v>
       </c>
       <c r="M291" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="N291" t="n">
-        <v>10348.08</v>
+        <v>9746.8802105263</v>
       </c>
       <c r="O291" t="n">
-        <v>413923.2</v>
+        <v>467850.2501052624</v>
       </c>
       <c r="P291" t="n">
-        <v>16900</v>
+        <v>18500</v>
       </c>
       <c r="Q291" t="n">
-        <v>676000</v>
+        <v>888000</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>C7213</t>
+          <t>C7221</t>
         </is>
       </c>
       <c r="B292" t="n">
-        <v>6987540143012</v>
+        <v>7453100037446</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>PESCADO CON LUZ Y SONIDO C7213</t>
+          <t>RELOJ CON FICHAS ARMABLES  C7221</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -13505,7 +13508,7 @@
         </is>
       </c>
       <c r="J292" t="n">
-        <v>48</v>
+        <v>347</v>
       </c>
       <c r="K292" t="n">
         <v>0</v>
@@ -13514,33 +13517,33 @@
         <v>0</v>
       </c>
       <c r="M292" t="n">
-        <v>48</v>
+        <v>347</v>
       </c>
       <c r="N292" t="n">
-        <v>9746.8802105263</v>
+        <v>2672.89</v>
       </c>
       <c r="O292" t="n">
-        <v>467850.2501052624</v>
+        <v>927492.83</v>
       </c>
       <c r="P292" t="n">
-        <v>18500</v>
+        <v>10200</v>
       </c>
       <c r="Q292" t="n">
-        <v>888000</v>
+        <v>3539400</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>C7221</t>
+          <t>C7222</t>
         </is>
       </c>
       <c r="B293" t="n">
-        <v>7453100037446</v>
+        <v>7453100037453</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>RELOJ CON FICHAS ARMABLES  C7221</t>
+          <t>RELOJ DIDACTICO CARACOL C7222</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -13554,7 +13557,7 @@
         </is>
       </c>
       <c r="J293" t="n">
-        <v>347</v>
+        <v>230</v>
       </c>
       <c r="K293" t="n">
         <v>0</v>
@@ -13563,38 +13566,38 @@
         <v>0</v>
       </c>
       <c r="M293" t="n">
-        <v>347</v>
+        <v>230</v>
       </c>
       <c r="N293" t="n">
-        <v>2672.89</v>
+        <v>4795.69</v>
       </c>
       <c r="O293" t="n">
-        <v>927492.83</v>
+        <v>1103008.7</v>
       </c>
       <c r="P293" t="n">
         <v>10200</v>
       </c>
       <c r="Q293" t="n">
-        <v>3539400</v>
+        <v>2346000</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>C7222</t>
+          <t>C7294</t>
         </is>
       </c>
       <c r="B294" t="n">
-        <v>7453100037453</v>
+        <v>6895675680022</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>RELOJ DIDACTICO CARACOL C7222</t>
+          <t>JUEGO DEPORTIVO HOCHEY C7294</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -13603,7 +13606,7 @@
         </is>
       </c>
       <c r="J294" t="n">
-        <v>230</v>
+        <v>60</v>
       </c>
       <c r="K294" t="n">
         <v>0</v>
@@ -13612,38 +13615,35 @@
         <v>0</v>
       </c>
       <c r="M294" t="n">
-        <v>230</v>
+        <v>60</v>
       </c>
       <c r="N294" t="n">
-        <v>4795.69</v>
+        <v>4337.31</v>
       </c>
       <c r="O294" t="n">
-        <v>1103008.7</v>
+        <v>260238.6</v>
       </c>
       <c r="P294" t="n">
-        <v>10200</v>
+        <v>12900</v>
       </c>
       <c r="Q294" t="n">
-        <v>2346000</v>
+        <v>774000</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>C7294</t>
-        </is>
-      </c>
-      <c r="B295" t="n">
-        <v>6895675680022</v>
+          <t>C736</t>
+        </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>JUEGO DEPORTIVO HOCHEY C7294</t>
+          <t>GLOBO CORAZON GDE MENSAJE</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -13652,7 +13652,7 @@
         </is>
       </c>
       <c r="J295" t="n">
-        <v>60</v>
+        <v>2700</v>
       </c>
       <c r="K295" t="n">
         <v>0</v>
@@ -13661,35 +13661,38 @@
         <v>0</v>
       </c>
       <c r="M295" t="n">
-        <v>60</v>
+        <v>2700</v>
       </c>
       <c r="N295" t="n">
-        <v>4337.31</v>
+        <v>640</v>
       </c>
       <c r="O295" t="n">
-        <v>260238.6</v>
+        <v>1728000</v>
       </c>
       <c r="P295" t="n">
-        <v>12900</v>
+        <v>800</v>
       </c>
       <c r="Q295" t="n">
-        <v>774000</v>
+        <v>2160000</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>C736</t>
-        </is>
+          <t>C7365</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>6920240750050</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>GLOBO CORAZON GDE MENSAJE</t>
+          <t>DIDACTICO JIRAFA EN BOLSA C7365</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -13698,7 +13701,7 @@
         </is>
       </c>
       <c r="J296" t="n">
-        <v>2700</v>
+        <v>19</v>
       </c>
       <c r="K296" t="n">
         <v>0</v>
@@ -13707,33 +13710,33 @@
         <v>0</v>
       </c>
       <c r="M296" t="n">
-        <v>2700</v>
+        <v>19</v>
       </c>
       <c r="N296" t="n">
-        <v>640</v>
+        <v>4190.77</v>
       </c>
       <c r="O296" t="n">
-        <v>1728000</v>
+        <v>79624.63</v>
       </c>
       <c r="P296" t="n">
-        <v>800</v>
+        <v>5900</v>
       </c>
       <c r="Q296" t="n">
-        <v>2160000</v>
+        <v>112100</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>C7365</t>
+          <t>C7366</t>
         </is>
       </c>
       <c r="B297" t="n">
-        <v>6920240750050</v>
+        <v>6920240750098</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>DIDACTICO JIRAFA EN BOLSA C7365</t>
+          <t>TREN DIDACTICO EN BOLSA C7366</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -13747,7 +13750,7 @@
         </is>
       </c>
       <c r="J297" t="n">
-        <v>19</v>
+        <v>104</v>
       </c>
       <c r="K297" t="n">
         <v>0</v>
@@ -13756,33 +13759,33 @@
         <v>0</v>
       </c>
       <c r="M297" t="n">
-        <v>19</v>
+        <v>104</v>
       </c>
       <c r="N297" t="n">
-        <v>4190.77</v>
+        <v>3499.72</v>
       </c>
       <c r="O297" t="n">
-        <v>79624.63</v>
+        <v>363970.88</v>
       </c>
       <c r="P297" t="n">
-        <v>5900</v>
+        <v>6900</v>
       </c>
       <c r="Q297" t="n">
-        <v>112100</v>
+        <v>717600</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>C7366</t>
+          <t>C7368</t>
         </is>
       </c>
       <c r="B298" t="n">
-        <v>6920240750098</v>
+        <v>6920240750159</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>TREN DIDACTICO EN BOLSA C7366</t>
+          <t>MOTO DIDACTICA EN BOLSA C736</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -13796,7 +13799,7 @@
         </is>
       </c>
       <c r="J298" t="n">
-        <v>104</v>
+        <v>158</v>
       </c>
       <c r="K298" t="n">
         <v>0</v>
@@ -13805,38 +13808,35 @@
         <v>0</v>
       </c>
       <c r="M298" t="n">
-        <v>104</v>
+        <v>158</v>
       </c>
       <c r="N298" t="n">
-        <v>3499.72</v>
+        <v>4578.04</v>
       </c>
       <c r="O298" t="n">
-        <v>363970.88</v>
+        <v>723330.3199999999</v>
       </c>
       <c r="P298" t="n">
-        <v>6900</v>
+        <v>7500</v>
       </c>
       <c r="Q298" t="n">
-        <v>717600</v>
+        <v>1185000</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>C7368</t>
-        </is>
-      </c>
-      <c r="B299" t="n">
-        <v>6920240750159</v>
+          <t>C740-IO</t>
+        </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>MOTO DIDACTICA EN BOLSA C736</t>
+          <t>GLOBO UNICORNIO MED</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -13845,7 +13845,7 @@
         </is>
       </c>
       <c r="J299" t="n">
-        <v>158</v>
+        <v>1876</v>
       </c>
       <c r="K299" t="n">
         <v>0</v>
@@ -13854,35 +13854,38 @@
         <v>0</v>
       </c>
       <c r="M299" t="n">
-        <v>158</v>
+        <v>1876</v>
       </c>
       <c r="N299" t="n">
-        <v>4578.04</v>
+        <v>480</v>
       </c>
       <c r="O299" t="n">
-        <v>723330.3199999999</v>
+        <v>900480</v>
       </c>
       <c r="P299" t="n">
-        <v>7500</v>
+        <v>600</v>
       </c>
       <c r="Q299" t="n">
-        <v>1185000</v>
+        <v>1125600</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>C740-IO</t>
-        </is>
+          <t>C7413</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>6921202412870</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>GLOBO UNICORNIO MED</t>
+          <t>DIDACTICO TORRE DE AROS C7413</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -13891,7 +13894,7 @@
         </is>
       </c>
       <c r="J300" t="n">
-        <v>1876</v>
+        <v>120</v>
       </c>
       <c r="K300" t="n">
         <v>0</v>
@@ -13900,38 +13903,35 @@
         <v>0</v>
       </c>
       <c r="M300" t="n">
-        <v>1876</v>
+        <v>120</v>
       </c>
       <c r="N300" t="n">
-        <v>480</v>
+        <v>4159.0003030303</v>
       </c>
       <c r="O300" t="n">
-        <v>900480</v>
+        <v>499080.036363636</v>
       </c>
       <c r="P300" t="n">
-        <v>600</v>
+        <v>8900</v>
       </c>
       <c r="Q300" t="n">
-        <v>1125600</v>
+        <v>1068000</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>C7413</t>
-        </is>
-      </c>
-      <c r="B301" t="n">
-        <v>6921202412870</v>
+          <t>C744-IO</t>
+        </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>DIDACTICO TORRE DE AROS C7413</t>
+          <t>GLOBO FELIZ CUMPLEAÑOS COLORES Y PUNTOS</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>GLOBOS</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -13940,7 +13940,7 @@
         </is>
       </c>
       <c r="J301" t="n">
-        <v>120</v>
+        <v>478</v>
       </c>
       <c r="K301" t="n">
         <v>0</v>
@@ -13949,35 +13949,35 @@
         <v>0</v>
       </c>
       <c r="M301" t="n">
-        <v>120</v>
+        <v>478</v>
       </c>
       <c r="N301" t="n">
-        <v>4159.0003030303</v>
+        <v>1554.12</v>
       </c>
       <c r="O301" t="n">
-        <v>499080.036363636</v>
+        <v>742869.36</v>
       </c>
       <c r="P301" t="n">
-        <v>8900</v>
+        <v>1900</v>
       </c>
       <c r="Q301" t="n">
-        <v>1068000</v>
+        <v>908200</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>C744-IO</t>
+          <t>C7462</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>GLOBO FELIZ CUMPLEAÑOS COLORES Y PUNTOS</t>
+          <t>SET DE BELLEZA ACCESORIOS PARA EL CABELLO C7462</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>GLOBOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -13986,7 +13986,7 @@
         </is>
       </c>
       <c r="J302" t="n">
-        <v>478</v>
+        <v>11</v>
       </c>
       <c r="K302" t="n">
         <v>0</v>
@@ -13995,30 +13995,33 @@
         <v>0</v>
       </c>
       <c r="M302" t="n">
-        <v>478</v>
+        <v>11</v>
       </c>
       <c r="N302" t="n">
-        <v>1554.12</v>
+        <v>14751.820377358</v>
       </c>
       <c r="O302" t="n">
-        <v>742869.36</v>
+        <v>162270.024150938</v>
       </c>
       <c r="P302" t="n">
-        <v>1900</v>
+        <v>37100</v>
       </c>
       <c r="Q302" t="n">
-        <v>908200</v>
+        <v>408100</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>C7462</t>
-        </is>
+          <t>C7467</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>6920241023009</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>SET DE BELLEZA ACCESORIOS PARA EL CABELLO C7462</t>
+          <t>ARCO Y FLECHA PARA NIÑAS C7467</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -14032,7 +14035,7 @@
         </is>
       </c>
       <c r="J303" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K303" t="n">
         <v>0</v>
@@ -14041,38 +14044,38 @@
         <v>0</v>
       </c>
       <c r="M303" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="N303" t="n">
-        <v>14751.820377358</v>
+        <v>15347.45</v>
       </c>
       <c r="O303" t="n">
-        <v>162270.024150938</v>
+        <v>230211.75</v>
       </c>
       <c r="P303" t="n">
-        <v>37100</v>
+        <v>23900</v>
       </c>
       <c r="Q303" t="n">
-        <v>408100</v>
+        <v>358500</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>C7467</t>
+          <t>C7488</t>
         </is>
       </c>
       <c r="B304" t="n">
-        <v>6920241023009</v>
+        <v>6945158254520</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>ARCO Y FLECHA PARA NIÑAS C7467</t>
+          <t>SOPORTE CELULAR CON LUZ C7488</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -14081,7 +14084,7 @@
         </is>
       </c>
       <c r="J304" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="K304" t="n">
         <v>0</v>
@@ -14090,38 +14093,38 @@
         <v>0</v>
       </c>
       <c r="M304" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="N304" t="n">
-        <v>15347.45</v>
+        <v>8919.16</v>
       </c>
       <c r="O304" t="n">
-        <v>230211.75</v>
+        <v>258655.64</v>
       </c>
       <c r="P304" t="n">
-        <v>23900</v>
+        <v>10000</v>
       </c>
       <c r="Q304" t="n">
-        <v>358500</v>
+        <v>290000</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>C7488</t>
+          <t>C7513</t>
         </is>
       </c>
       <c r="B305" t="n">
-        <v>6945158254520</v>
+        <v>6905698382824</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>SOPORTE CELULAR CON LUZ C7488</t>
+          <t>SONAJERO BOLA LUZ GDE C7513</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -14130,7 +14133,7 @@
         </is>
       </c>
       <c r="J305" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="K305" t="n">
         <v>0</v>
@@ -14139,47 +14142,42 @@
         <v>0</v>
       </c>
       <c r="M305" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="N305" t="n">
-        <v>8919.16</v>
+        <v>1024.29</v>
       </c>
       <c r="O305" t="n">
-        <v>258655.64</v>
+        <v>1024.29</v>
       </c>
       <c r="P305" t="n">
-        <v>10000</v>
+        <v>2900</v>
       </c>
       <c r="Q305" t="n">
-        <v>290000</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>C7513</t>
+          <t>C752</t>
         </is>
       </c>
       <c r="B306" t="n">
-        <v>6905698382824</v>
+        <v>8596162180497</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>SONAJERO BOLA LUZ GDE C7513</t>
-        </is>
-      </c>
-      <c r="E306" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
+          <t>GLOBO UNICORNIO MED 4 PATAS</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J306" t="n">
-        <v>1</v>
+        <v>1398</v>
       </c>
       <c r="K306" t="n">
         <v>0</v>
@@ -14188,33 +14186,33 @@
         <v>0</v>
       </c>
       <c r="M306" t="n">
-        <v>1</v>
+        <v>1398</v>
       </c>
       <c r="N306" t="n">
-        <v>1024.29</v>
+        <v>1163.7447787403</v>
       </c>
       <c r="O306" t="n">
-        <v>1024.29</v>
+        <v>1626915.200678939</v>
       </c>
       <c r="P306" t="n">
-        <v>2900</v>
+        <v>1500</v>
       </c>
       <c r="Q306" t="n">
-        <v>2900</v>
+        <v>2097000</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>C752</t>
+          <t>C753</t>
         </is>
       </c>
       <c r="B307" t="n">
-        <v>8596162180497</v>
+        <v>8596162180503</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>GLOBO UNICORNIO MED 4 PATAS</t>
+          <t>GLOBO UNICORNIO GDE 4 PATAS</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -14223,7 +14221,7 @@
         </is>
       </c>
       <c r="J307" t="n">
-        <v>1398</v>
+        <v>277</v>
       </c>
       <c r="K307" t="n">
         <v>0</v>
@@ -14232,42 +14230,47 @@
         <v>0</v>
       </c>
       <c r="M307" t="n">
-        <v>1398</v>
+        <v>277</v>
       </c>
       <c r="N307" t="n">
-        <v>1163.7447787403</v>
+        <v>5113.4625508318</v>
       </c>
       <c r="O307" t="n">
-        <v>1626915.200678939</v>
+        <v>1416429.126580409</v>
       </c>
       <c r="P307" t="n">
-        <v>1500</v>
+        <v>7000</v>
       </c>
       <c r="Q307" t="n">
-        <v>2097000</v>
+        <v>1939000</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>C753</t>
+          <t>C7533</t>
         </is>
       </c>
       <c r="B308" t="n">
-        <v>8596162180503</v>
+        <v>6923669699979</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>GLOBO UNICORNIO GDE 4 PATAS</t>
+          <t>REPUESTO BIOGEL NEON C7533</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J308" t="n">
-        <v>277</v>
+        <v>12023</v>
       </c>
       <c r="K308" t="n">
         <v>0</v>
@@ -14276,33 +14279,33 @@
         <v>0</v>
       </c>
       <c r="M308" t="n">
-        <v>277</v>
+        <v>12023</v>
       </c>
       <c r="N308" t="n">
-        <v>5113.4625508318</v>
+        <v>509.69</v>
       </c>
       <c r="O308" t="n">
-        <v>1416429.126580409</v>
+        <v>6128002.87</v>
       </c>
       <c r="P308" t="n">
-        <v>7000</v>
+        <v>750</v>
       </c>
       <c r="Q308" t="n">
-        <v>1939000</v>
+        <v>9017250</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>C7533</t>
+          <t>C7534</t>
         </is>
       </c>
       <c r="B309" t="n">
-        <v>6923669699979</v>
+        <v>6951241752002</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>REPUESTO BIOGEL NEON C7533</t>
+          <t>GORRO PELUCHE LUZ C7534-A-B-C-D-E-F</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -14316,7 +14319,7 @@
         </is>
       </c>
       <c r="J309" t="n">
-        <v>12023</v>
+        <v>499</v>
       </c>
       <c r="K309" t="n">
         <v>0</v>
@@ -14325,38 +14328,35 @@
         <v>0</v>
       </c>
       <c r="M309" t="n">
-        <v>12023</v>
+        <v>499</v>
       </c>
       <c r="N309" t="n">
-        <v>509.69</v>
+        <v>7046.9398262758</v>
       </c>
       <c r="O309" t="n">
-        <v>6128002.87</v>
+        <v>3516422.973311624</v>
       </c>
       <c r="P309" t="n">
-        <v>750</v>
+        <v>9900</v>
       </c>
       <c r="Q309" t="n">
-        <v>9017250</v>
+        <v>4940100</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>C7534</t>
-        </is>
-      </c>
-      <c r="B310" t="n">
-        <v>6951241752002</v>
+          <t>C7535</t>
+        </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>GORRO PELUCHE LUZ C7534-A-B-C-D-E-F</t>
+          <t>CARRO METALICO X13 CON CAMION C7535</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -14365,7 +14365,7 @@
         </is>
       </c>
       <c r="J310" t="n">
-        <v>499</v>
+        <v>30</v>
       </c>
       <c r="K310" t="n">
         <v>0</v>
@@ -14374,35 +14374,35 @@
         <v>0</v>
       </c>
       <c r="M310" t="n">
-        <v>499</v>
+        <v>30</v>
       </c>
       <c r="N310" t="n">
-        <v>7046.9398262758</v>
+        <v>24338.47</v>
       </c>
       <c r="O310" t="n">
-        <v>3516422.973311624</v>
+        <v>730154.1000000001</v>
       </c>
       <c r="P310" t="n">
-        <v>9900</v>
+        <v>27900</v>
       </c>
       <c r="Q310" t="n">
-        <v>4940100</v>
+        <v>837000</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>C7535</t>
+          <t>C7560</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>CARRO METALICO X13 CON CAMION C7535</t>
+          <t>BARRA LUMINOSA 48CM C7560/211</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -14411,7 +14411,7 @@
         </is>
       </c>
       <c r="J311" t="n">
-        <v>30</v>
+        <v>188</v>
       </c>
       <c r="K311" t="n">
         <v>0</v>
@@ -14420,30 +14420,33 @@
         <v>0</v>
       </c>
       <c r="M311" t="n">
-        <v>30</v>
+        <v>188</v>
       </c>
       <c r="N311" t="n">
-        <v>24338.47</v>
+        <v>796.3099999999999</v>
       </c>
       <c r="O311" t="n">
-        <v>730154.1000000001</v>
+        <v>149706.28</v>
       </c>
       <c r="P311" t="n">
-        <v>27900</v>
+        <v>2500</v>
       </c>
       <c r="Q311" t="n">
-        <v>837000</v>
+        <v>470000</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>C7560</t>
-        </is>
+          <t>C7588</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>7588228020244</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>BARRA LUMINOSA 48CM C7560/211</t>
+          <t>SONAJERO LUZ PANDITA C7588</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -14457,7 +14460,7 @@
         </is>
       </c>
       <c r="J312" t="n">
-        <v>188</v>
+        <v>1429</v>
       </c>
       <c r="K312" t="n">
         <v>0</v>
@@ -14466,38 +14469,38 @@
         <v>0</v>
       </c>
       <c r="M312" t="n">
-        <v>188</v>
+        <v>1429</v>
       </c>
       <c r="N312" t="n">
-        <v>796.3099999999999</v>
+        <v>641.78</v>
       </c>
       <c r="O312" t="n">
-        <v>149706.28</v>
+        <v>917103.62</v>
       </c>
       <c r="P312" t="n">
         <v>2500</v>
       </c>
       <c r="Q312" t="n">
-        <v>470000</v>
+        <v>3572500</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>C7588</t>
+          <t>C7610</t>
         </is>
       </c>
       <c r="B313" t="n">
-        <v>7588228020244</v>
+        <v>6999899236093</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>SONAJERO LUZ PANDITA C7588</t>
+          <t>BOTE TIMON PISCINA 80X60 C7610</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>INFLABLES</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -14506,7 +14509,7 @@
         </is>
       </c>
       <c r="J313" t="n">
-        <v>1429</v>
+        <v>276</v>
       </c>
       <c r="K313" t="n">
         <v>0</v>
@@ -14515,38 +14518,38 @@
         <v>0</v>
       </c>
       <c r="M313" t="n">
-        <v>1429</v>
+        <v>276</v>
       </c>
       <c r="N313" t="n">
-        <v>641.78</v>
+        <v>7811.9</v>
       </c>
       <c r="O313" t="n">
-        <v>917103.62</v>
+        <v>2156084.4</v>
       </c>
       <c r="P313" t="n">
-        <v>2500</v>
+        <v>13900</v>
       </c>
       <c r="Q313" t="n">
-        <v>3572500</v>
+        <v>3836400</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>C7610</t>
+          <t>C7614-F</t>
         </is>
       </c>
       <c r="B314" t="n">
-        <v>6999899236093</v>
+        <v>6999899236130</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>BOTE TIMON PISCINA 80X60 C7610</t>
+          <t>FLOTADOR DONA FLAMINGO C7614-F</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>INFLABLES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -14555,7 +14558,7 @@
         </is>
       </c>
       <c r="J314" t="n">
-        <v>276</v>
+        <v>382</v>
       </c>
       <c r="K314" t="n">
         <v>0</v>
@@ -14564,47 +14567,42 @@
         <v>0</v>
       </c>
       <c r="M314" t="n">
-        <v>276</v>
+        <v>382</v>
       </c>
       <c r="N314" t="n">
-        <v>7811.9</v>
+        <v>3155</v>
       </c>
       <c r="O314" t="n">
-        <v>2156084.4</v>
+        <v>1205210</v>
       </c>
       <c r="P314" t="n">
-        <v>13900</v>
+        <v>5900</v>
       </c>
       <c r="Q314" t="n">
-        <v>3836400</v>
+        <v>2253800</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>C7614-F</t>
+          <t>C784</t>
         </is>
       </c>
       <c r="B315" t="n">
-        <v>6999899236130</v>
+        <v>8913992935507</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>FLOTADOR DONA FLAMINGO C7614-F</t>
-        </is>
-      </c>
-      <c r="E315" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>GLOBO MENSAJE CUADRADO</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J315" t="n">
-        <v>382</v>
+        <v>1450</v>
       </c>
       <c r="K315" t="n">
         <v>0</v>
@@ -14613,33 +14611,33 @@
         <v>0</v>
       </c>
       <c r="M315" t="n">
-        <v>382</v>
+        <v>1450</v>
       </c>
       <c r="N315" t="n">
-        <v>3155</v>
+        <v>704.89696969697</v>
       </c>
       <c r="O315" t="n">
-        <v>1205210</v>
+        <v>1022100.606060607</v>
       </c>
       <c r="P315" t="n">
-        <v>5900</v>
+        <v>900</v>
       </c>
       <c r="Q315" t="n">
-        <v>2253800</v>
+        <v>1305000</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>C784</t>
+          <t>C819</t>
         </is>
       </c>
       <c r="B316" t="n">
-        <v>8913992935507</v>
+        <v>2087202108190</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>GLOBO MENSAJE CUADRADO</t>
+          <t>TROMPO EMOJI</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -14648,7 +14646,7 @@
         </is>
       </c>
       <c r="J316" t="n">
-        <v>1450</v>
+        <v>468</v>
       </c>
       <c r="K316" t="n">
         <v>0</v>
@@ -14657,33 +14655,33 @@
         <v>0</v>
       </c>
       <c r="M316" t="n">
-        <v>1450</v>
+        <v>468</v>
       </c>
       <c r="N316" t="n">
-        <v>704.89696969697</v>
+        <v>6761.25</v>
       </c>
       <c r="O316" t="n">
-        <v>1022100.606060607</v>
+        <v>3164265</v>
       </c>
       <c r="P316" t="n">
-        <v>900</v>
+        <v>5200</v>
       </c>
       <c r="Q316" t="n">
-        <v>1305000</v>
+        <v>2433600</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>C819</t>
+          <t>C84</t>
         </is>
       </c>
       <c r="B317" t="n">
-        <v>2087202108190</v>
+        <v>2021010563031</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>TROMPO EMOJI</t>
+          <t>LANZADOR DE AGUA</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -14692,7 +14690,7 @@
         </is>
       </c>
       <c r="J317" t="n">
-        <v>468</v>
+        <v>182</v>
       </c>
       <c r="K317" t="n">
         <v>0</v>
@@ -14701,33 +14699,35 @@
         <v>0</v>
       </c>
       <c r="M317" t="n">
-        <v>468</v>
+        <v>182</v>
       </c>
       <c r="N317" t="n">
-        <v>6761.25</v>
+        <v>1008.8110899183</v>
       </c>
       <c r="O317" t="n">
-        <v>3164265</v>
+        <v>183603.6183651306</v>
       </c>
       <c r="P317" t="n">
-        <v>5200</v>
+        <v>1500</v>
       </c>
       <c r="Q317" t="n">
-        <v>2433600</v>
+        <v>273000</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>C84</t>
-        </is>
-      </c>
-      <c r="B318" t="n">
-        <v>2021010563031</v>
+          <t>C879</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>CG-2016-212</t>
+        </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>LANZADOR DE AGUA</t>
+          <t>VELA MARIPOSA</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -14736,7 +14736,7 @@
         </is>
       </c>
       <c r="J318" t="n">
-        <v>182</v>
+        <v>121</v>
       </c>
       <c r="K318" t="n">
         <v>0</v>
@@ -14745,44 +14745,49 @@
         <v>0</v>
       </c>
       <c r="M318" t="n">
-        <v>182</v>
+        <v>121</v>
       </c>
       <c r="N318" t="n">
-        <v>1008.8110899183</v>
+        <v>1520</v>
       </c>
       <c r="O318" t="n">
-        <v>183603.6183651306</v>
+        <v>183920</v>
       </c>
       <c r="P318" t="n">
-        <v>1500</v>
+        <v>1900</v>
       </c>
       <c r="Q318" t="n">
-        <v>273000</v>
+        <v>229900</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>C879</t>
+          <t>C880</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>CG-2016-212</t>
+          <t>cg2016213</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>VELA MARIPOSA</t>
+          <t>VELA FLOR</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>VELA</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J319" t="n">
-        <v>121</v>
+        <v>200</v>
       </c>
       <c r="K319" t="n">
         <v>0</v>
@@ -14791,49 +14796,39 @@
         <v>0</v>
       </c>
       <c r="M319" t="n">
-        <v>121</v>
+        <v>200</v>
       </c>
       <c r="N319" t="n">
         <v>1520</v>
       </c>
       <c r="O319" t="n">
-        <v>183920</v>
+        <v>304000</v>
       </c>
       <c r="P319" t="n">
         <v>1900</v>
       </c>
       <c r="Q319" t="n">
-        <v>229900</v>
+        <v>380000</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>C880</t>
-        </is>
-      </c>
-      <c r="B320" t="inlineStr">
-        <is>
-          <t>cg2016213</t>
+          <t>C888</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>VELA FLOR</t>
-        </is>
-      </c>
-      <c r="E320" t="inlineStr">
-        <is>
-          <t>VELA</t>
+          <t>PELOTA CHILLON PUYAS SIN LUZ</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J320" t="n">
-        <v>200</v>
+        <v>169</v>
       </c>
       <c r="K320" t="n">
         <v>0</v>
@@ -14842,39 +14837,44 @@
         <v>0</v>
       </c>
       <c r="M320" t="n">
-        <v>200</v>
+        <v>169</v>
       </c>
       <c r="N320" t="n">
-        <v>1520</v>
+        <v>1213.6821400778</v>
       </c>
       <c r="O320" t="n">
-        <v>304000</v>
+        <v>205112.2816731482</v>
       </c>
       <c r="P320" t="n">
-        <v>1900</v>
+        <v>1500</v>
       </c>
       <c r="Q320" t="n">
-        <v>380000</v>
+        <v>253500</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>C888</t>
+          <t>FG037</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>PELOTA CHILLON PUYAS SIN LUZ</t>
+          <t>SNORKEL 66046A</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J321" t="n">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="K321" t="n">
         <v>0</v>
@@ -14883,30 +14883,30 @@
         <v>0</v>
       </c>
       <c r="M321" t="n">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="N321" t="n">
-        <v>1213.6821400778</v>
+        <v>13493.858287462</v>
       </c>
       <c r="O321" t="n">
-        <v>205112.2816731482</v>
+        <v>2415400.633455698</v>
       </c>
       <c r="P321" t="n">
-        <v>1500</v>
+        <v>16900</v>
       </c>
       <c r="Q321" t="n">
-        <v>253500</v>
+        <v>3025100</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>FG037</t>
+          <t>FG039</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>SNORKEL 66046A</t>
+          <t>GAFA DE NATACION BLISTER 2404-2</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -14920,7 +14920,7 @@
         </is>
       </c>
       <c r="J322" t="n">
-        <v>179</v>
+        <v>347</v>
       </c>
       <c r="K322" t="n">
         <v>0</v>
@@ -14929,35 +14929,40 @@
         <v>0</v>
       </c>
       <c r="M322" t="n">
-        <v>179</v>
+        <v>347</v>
       </c>
       <c r="N322" t="n">
-        <v>13493.858287462</v>
+        <v>2644.9</v>
       </c>
       <c r="O322" t="n">
-        <v>2415400.633455698</v>
+        <v>917780.3</v>
       </c>
       <c r="P322" t="n">
-        <v>16900</v>
+        <v>3900</v>
       </c>
       <c r="Q322" t="n">
-        <v>3025100</v>
+        <v>1353300</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>FG039</t>
+          <t>MG16332</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>MG16332</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>GAFA DE NATACION BLISTER 2404-2</t>
+          <t>LANZADOR  ARCO Y FLECA CON LASER MG16332</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -14966,7 +14971,7 @@
         </is>
       </c>
       <c r="J323" t="n">
-        <v>347</v>
+        <v>4</v>
       </c>
       <c r="K323" t="n">
         <v>0</v>
@@ -14975,35 +14980,30 @@
         <v>0</v>
       </c>
       <c r="M323" t="n">
-        <v>347</v>
+        <v>4</v>
       </c>
       <c r="N323" t="n">
-        <v>2644.9</v>
+        <v>8439.969999999999</v>
       </c>
       <c r="O323" t="n">
-        <v>917780.3</v>
+        <v>33759.88</v>
       </c>
       <c r="P323" t="n">
-        <v>3900</v>
+        <v>29500</v>
       </c>
       <c r="Q323" t="n">
-        <v>1353300</v>
+        <v>118000</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>MG16332</t>
-        </is>
-      </c>
-      <c r="B324" t="inlineStr">
-        <is>
-          <t>MG16332</t>
+          <t>MG20430</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>LANZADOR  ARCO Y FLECA CON LASER MG16332</t>
+          <t>SET PLASTILINA CON MOLDES BARBERIA MALETA MG20430</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -15017,7 +15017,7 @@
         </is>
       </c>
       <c r="J324" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="K324" t="n">
         <v>0</v>
@@ -15026,35 +15026,35 @@
         <v>0</v>
       </c>
       <c r="M324" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="N324" t="n">
-        <v>8439.969999999999</v>
+        <v>12189.831111111</v>
       </c>
       <c r="O324" t="n">
-        <v>33759.88</v>
+        <v>219416.959999998</v>
       </c>
       <c r="P324" t="n">
-        <v>29500</v>
+        <v>30900</v>
       </c>
       <c r="Q324" t="n">
-        <v>118000</v>
+        <v>556200</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>MG20430</t>
+          <t>MG40210</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>SET PLASTILINA CON MOLDES BARBERIA MALETA MG20430</t>
+          <t>SONAJERO OSO MG40210</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -15063,7 +15063,7 @@
         </is>
       </c>
       <c r="J325" t="n">
-        <v>18</v>
+        <v>263</v>
       </c>
       <c r="K325" t="n">
         <v>0</v>
@@ -15072,35 +15072,40 @@
         <v>0</v>
       </c>
       <c r="M325" t="n">
-        <v>18</v>
+        <v>263</v>
       </c>
       <c r="N325" t="n">
-        <v>12189.831111111</v>
+        <v>571.87</v>
       </c>
       <c r="O325" t="n">
-        <v>219416.959999998</v>
+        <v>150401.81</v>
       </c>
       <c r="P325" t="n">
-        <v>30900</v>
+        <v>2500</v>
       </c>
       <c r="Q325" t="n">
-        <v>556200</v>
+        <v>657500</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>MG40210</t>
+          <t>MG40720</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>MG40720</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>SONAJERO OSO MG40210</t>
+          <t>MAQUINA DE COSER MINI MG40720</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -15109,7 +15114,7 @@
         </is>
       </c>
       <c r="J326" t="n">
-        <v>263</v>
+        <v>64</v>
       </c>
       <c r="K326" t="n">
         <v>0</v>
@@ -15118,69 +15123,18 @@
         <v>0</v>
       </c>
       <c r="M326" t="n">
-        <v>263</v>
+        <v>64</v>
       </c>
       <c r="N326" t="n">
-        <v>571.87</v>
+        <v>9917.040000000001</v>
       </c>
       <c r="O326" t="n">
-        <v>150401.81</v>
+        <v>634690.5600000001</v>
       </c>
       <c r="P326" t="n">
-        <v>2500</v>
+        <v>15900</v>
       </c>
       <c r="Q326" t="n">
-        <v>657500</v>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" t="inlineStr">
-        <is>
-          <t>MG40720</t>
-        </is>
-      </c>
-      <c r="B327" t="inlineStr">
-        <is>
-          <t>MG40720</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>MAQUINA DE COSER MINI MG40720</t>
-        </is>
-      </c>
-      <c r="E327" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
-        </is>
-      </c>
-      <c r="I327" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J327" t="n">
-        <v>64</v>
-      </c>
-      <c r="K327" t="n">
-        <v>0</v>
-      </c>
-      <c r="L327" t="n">
-        <v>0</v>
-      </c>
-      <c r="M327" t="n">
-        <v>64</v>
-      </c>
-      <c r="N327" t="n">
-        <v>9917.040000000001</v>
-      </c>
-      <c r="O327" t="n">
-        <v>634690.5600000001</v>
-      </c>
-      <c r="P327" t="n">
-        <v>15900</v>
-      </c>
-      <c r="Q327" t="n">
         <v>1017600</v>
       </c>
     </row>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -597,22 +597,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>74676.599</v>
       </c>
       <c r="O5" t="n">
-        <v>298706.396</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>144900</v>
       </c>
       <c r="Q5" t="n">
-        <v>579600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1355,10 +1355,10 @@
         <v>62</v>
       </c>
       <c r="N24" t="n">
-        <v>21333.69</v>
+        <v>21425.250901288</v>
       </c>
       <c r="O24" t="n">
-        <v>1322688.78</v>
+        <v>1328365.555879856</v>
       </c>
       <c r="P24" t="n">
         <v>30000</v>
@@ -1729,22 +1729,22 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M33" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="N33" t="n">
         <v>141416.88465116</v>
       </c>
       <c r="O33" t="n">
-        <v>9192097.502325401</v>
+        <v>7777928.655813801</v>
       </c>
       <c r="P33" t="n">
         <v>251900</v>
       </c>
       <c r="Q33" t="n">
-        <v>16373500</v>
+        <v>13854500</v>
       </c>
     </row>
     <row r="34">
@@ -1865,22 +1865,22 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M36" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="N36" t="n">
-        <v>27000</v>
+        <v>28500</v>
       </c>
       <c r="O36" t="n">
-        <v>1674000</v>
+        <v>1425000</v>
       </c>
       <c r="P36" t="n">
         <v>20000</v>
       </c>
       <c r="Q36" t="n">
-        <v>1240000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="37">
@@ -2888,10 +2888,10 @@
         <v>248</v>
       </c>
       <c r="N60" t="n">
-        <v>13593.35</v>
+        <v>13694.165945612</v>
       </c>
       <c r="O60" t="n">
-        <v>3371150.8</v>
+        <v>3396153.154511776</v>
       </c>
       <c r="P60" t="n">
         <v>25500</v>
@@ -3065,10 +3065,10 @@
         <v>350</v>
       </c>
       <c r="N64" t="n">
-        <v>2582.2547091633</v>
+        <v>2582.2546851654</v>
       </c>
       <c r="O64" t="n">
-        <v>903789.1482071551</v>
+        <v>903789.1398078901</v>
       </c>
       <c r="P64" t="n">
         <v>4500</v>
@@ -3474,10 +3474,10 @@
         <v>296</v>
       </c>
       <c r="N73" t="n">
-        <v>4890.9300565371</v>
+        <v>4890.9300570207</v>
       </c>
       <c r="O73" t="n">
-        <v>1447715.296734982</v>
+        <v>1447715.296878127</v>
       </c>
       <c r="P73" t="n">
         <v>8900</v>
@@ -3840,10 +3840,10 @@
         <v>291</v>
       </c>
       <c r="N81" t="n">
-        <v>14822.378814083</v>
+        <v>14831.53974042</v>
       </c>
       <c r="O81" t="n">
-        <v>4313312.234898153</v>
+        <v>4315978.064462219</v>
       </c>
       <c r="P81" t="n">
         <v>24900</v>
@@ -4161,10 +4161,10 @@
         <v>336</v>
       </c>
       <c r="N88" t="n">
-        <v>12422.46300928</v>
+        <v>12422.463013274</v>
       </c>
       <c r="O88" t="n">
-        <v>4173947.57111808</v>
+        <v>4173947.572460064</v>
       </c>
       <c r="P88" t="n">
         <v>19900</v>
@@ -4253,10 +4253,10 @@
         <v>1584</v>
       </c>
       <c r="N90" t="n">
-        <v>3472.276393501</v>
+        <v>3472.2764071985</v>
       </c>
       <c r="O90" t="n">
-        <v>5500085.807305584</v>
+        <v>5500085.829002423</v>
       </c>
       <c r="P90" t="n">
         <v>5900</v>
@@ -4343,10 +4343,10 @@
         <v>1356</v>
       </c>
       <c r="N92" t="n">
-        <v>4371.1729731899</v>
+        <v>4371.1729736673</v>
       </c>
       <c r="O92" t="n">
-        <v>5927310.551645505</v>
+        <v>5927310.552292858</v>
       </c>
       <c r="P92" t="n">
         <v>8900</v>
@@ -6414,10 +6414,10 @@
         <v>908</v>
       </c>
       <c r="N138" t="n">
-        <v>4814.2633494176</v>
+        <v>4814.2633472037</v>
       </c>
       <c r="O138" t="n">
-        <v>4371351.121271181</v>
+        <v>4371351.119260959</v>
       </c>
       <c r="P138" t="n">
         <v>7900</v>
@@ -6818,10 +6818,10 @@
         <v>144</v>
       </c>
       <c r="N147" t="n">
-        <v>27123.764587738</v>
+        <v>27123.764576271</v>
       </c>
       <c r="O147" t="n">
-        <v>3905822.100634272</v>
+        <v>3905822.098983024</v>
       </c>
       <c r="P147" t="n">
         <v>44500</v>
@@ -7048,10 +7048,10 @@
         <v>31</v>
       </c>
       <c r="N152" t="n">
-        <v>12981.59</v>
+        <v>13033.935120968</v>
       </c>
       <c r="O152" t="n">
-        <v>402429.29</v>
+        <v>404051.9887500081</v>
       </c>
       <c r="P152" t="n">
         <v>21900</v>
@@ -7782,10 +7782,10 @@
         <v>396</v>
       </c>
       <c r="N168" t="n">
-        <v>25534</v>
+        <v>25577.697661152</v>
       </c>
       <c r="O168" t="n">
-        <v>10111464</v>
+        <v>10128768.27381619</v>
       </c>
       <c r="P168" t="n">
         <v>40900</v>
@@ -8107,10 +8107,10 @@
         <v>30</v>
       </c>
       <c r="N175" t="n">
-        <v>11857</v>
+        <v>12039.415384615</v>
       </c>
       <c r="O175" t="n">
-        <v>355710</v>
+        <v>361182.46153845</v>
       </c>
       <c r="P175" t="n">
         <v>19900</v>
@@ -8291,10 +8291,10 @@
         <v>180</v>
       </c>
       <c r="N179" t="n">
-        <v>10411</v>
+        <v>10448.858181818</v>
       </c>
       <c r="O179" t="n">
-        <v>1873980</v>
+        <v>1880794.47272724</v>
       </c>
       <c r="P179" t="n">
         <v>16900</v>
@@ -8705,10 +8705,10 @@
         <v>124</v>
       </c>
       <c r="N188" t="n">
-        <v>9003</v>
+        <v>9018.1565656566</v>
       </c>
       <c r="O188" t="n">
-        <v>1116372</v>
+        <v>1118251.414141418</v>
       </c>
       <c r="P188" t="n">
         <v>14900</v>
@@ -10075,10 +10075,10 @@
         <v>180</v>
       </c>
       <c r="N218" t="n">
-        <v>17992</v>
+        <v>18015.518954248</v>
       </c>
       <c r="O218" t="n">
-        <v>3238560</v>
+        <v>3242793.41176464</v>
       </c>
       <c r="P218" t="n">
         <v>28900</v>
@@ -10722,10 +10722,10 @@
         <v>285</v>
       </c>
       <c r="N232" t="n">
-        <v>8700</v>
+        <v>8711.0687022901</v>
       </c>
       <c r="O232" t="n">
-        <v>2479500</v>
+        <v>2482654.580152679</v>
       </c>
       <c r="P232" t="n">
         <v>14900</v>
@@ -11136,10 +11136,10 @@
         <v>144</v>
       </c>
       <c r="N241" t="n">
-        <v>15472</v>
+        <v>15516.07977208</v>
       </c>
       <c r="O241" t="n">
-        <v>2227968</v>
+        <v>2234315.48717952</v>
       </c>
       <c r="P241" t="n">
         <v>25900</v>
@@ -11366,10 +11366,10 @@
         <v>864</v>
       </c>
       <c r="N246" t="n">
-        <v>1516.0386973545</v>
+        <v>1516.0386972166</v>
       </c>
       <c r="O246" t="n">
-        <v>1309857.434514288</v>
+        <v>1309857.434395142</v>
       </c>
       <c r="P246" t="n">
         <v>2300</v>
@@ -11692,10 +11692,10 @@
         <v>276</v>
       </c>
       <c r="N253" t="n">
-        <v>13518</v>
+        <v>13521.774923206</v>
       </c>
       <c r="O253" t="n">
-        <v>3730968</v>
+        <v>3732009.878804856</v>
       </c>
       <c r="P253" t="n">
         <v>21900</v>
@@ -11883,10 +11883,10 @@
         <v>43</v>
       </c>
       <c r="N257" t="n">
-        <v>15423.36</v>
+        <v>15547.741935484</v>
       </c>
       <c r="O257" t="n">
-        <v>663204.48</v>
+        <v>668552.903225812</v>
       </c>
       <c r="P257" t="n">
         <v>24900</v>
@@ -12715,10 +12715,10 @@
         <v>14112</v>
       </c>
       <c r="N275" t="n">
-        <v>703.79458486774</v>
+        <v>703.7945831140599</v>
       </c>
       <c r="O275" t="n">
-        <v>9931949.181653546</v>
+        <v>9931949.156905614</v>
       </c>
       <c r="P275" t="n">
         <v>900</v>
@@ -13139,22 +13139,22 @@
         <v>0</v>
       </c>
       <c r="L284" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M284" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N284" t="n">
-        <v>9694.41</v>
+        <v>12723.913125</v>
       </c>
       <c r="O284" t="n">
-        <v>96944.10000000001</v>
+        <v>0</v>
       </c>
       <c r="P284" t="n">
         <v>32500</v>
       </c>
       <c r="Q284" t="n">
-        <v>325000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="285">
